--- a/dashboards/Adani Group.xlsx
+++ b/dashboards/Adani Group.xlsx
@@ -504,7 +504,7 @@
         <v>20.26000022888184</v>
       </c>
       <c r="H2" t="n">
-        <v>372.3961486816406</v>
+        <v>372.3961181640625</v>
       </c>
       <c r="I2" t="n">
         <v>1741.24853515625</v>
@@ -518,7 +518,7 @@
         <v>44565</v>
       </c>
       <c r="B3" t="n">
-        <v>2126.263427734375</v>
+        <v>2126.26318359375</v>
       </c>
       <c r="C3" t="n">
         <v>1754.949951171875</v>
@@ -539,7 +539,7 @@
         <v>375.7160034179688</v>
       </c>
       <c r="I3" t="n">
-        <v>1751.383666992188</v>
+        <v>1751.383544921875</v>
       </c>
       <c r="J3" t="n">
         <v>114.25</v>
@@ -550,19 +550,19 @@
         <v>44566</v>
       </c>
       <c r="B4" t="n">
-        <v>2142.513916015625</v>
+        <v>2142.51416015625</v>
       </c>
       <c r="C4" t="n">
         <v>1761.050048828125</v>
       </c>
       <c r="D4" t="n">
-        <v>1711.629150390625</v>
+        <v>1711.629028320312</v>
       </c>
       <c r="E4" t="n">
         <v>1399.650024414062</v>
       </c>
       <c r="F4" t="n">
-        <v>734.8313598632812</v>
+        <v>734.8314208984375</v>
       </c>
       <c r="G4" t="n">
         <v>19.96999931335449</v>
@@ -571,7 +571,7 @@
         <v>378.8433227539062</v>
       </c>
       <c r="I4" t="n">
-        <v>1769.107666015625</v>
+        <v>1769.107788085938</v>
       </c>
       <c r="J4" t="n">
         <v>125.6500015258789</v>
@@ -582,7 +582,7 @@
         <v>44567</v>
       </c>
       <c r="B5" t="n">
-        <v>2129.130859375</v>
+        <v>2129.131103515625</v>
       </c>
       <c r="C5" t="n">
         <v>1760.050048828125</v>
@@ -594,16 +594,16 @@
         <v>1409.800048828125</v>
       </c>
       <c r="F5" t="n">
-        <v>720.1328125</v>
+        <v>720.1328735351562</v>
       </c>
       <c r="G5" t="n">
         <v>19.96999931335449</v>
       </c>
       <c r="H5" t="n">
-        <v>372.4442749023438</v>
+        <v>372.4442138671875</v>
       </c>
       <c r="I5" t="n">
-        <v>1795.868530273438</v>
+        <v>1795.868408203125</v>
       </c>
       <c r="J5" t="n">
         <v>119.9499969482422</v>
@@ -614,13 +614,13 @@
         <v>44568</v>
       </c>
       <c r="B6" t="n">
-        <v>2183.905517578125</v>
+        <v>2183.90576171875</v>
       </c>
       <c r="C6" t="n">
         <v>1776</v>
       </c>
       <c r="D6" t="n">
-        <v>1695.315551757812</v>
+        <v>1695.3154296875</v>
       </c>
       <c r="E6" t="n">
         <v>1423.099975585938</v>
@@ -646,13 +646,13 @@
         <v>44571</v>
       </c>
       <c r="B7" t="n">
-        <v>2217.888671875</v>
+        <v>2217.88818359375</v>
       </c>
       <c r="C7" t="n">
         <v>1819.699951171875</v>
       </c>
       <c r="D7" t="n">
-        <v>1748.696411132812</v>
+        <v>1748.6962890625</v>
       </c>
       <c r="E7" t="n">
         <v>1438.900024414062</v>
@@ -667,7 +667,7 @@
         <v>384.2800903320312</v>
       </c>
       <c r="I7" t="n">
-        <v>1760.769897460938</v>
+        <v>1760.769775390625</v>
       </c>
       <c r="J7" t="n">
         <v>120.0500030517578</v>
@@ -678,7 +678,7 @@
         <v>44572</v>
       </c>
       <c r="B8" t="n">
-        <v>2196.332275390625</v>
+        <v>2196.33251953125</v>
       </c>
       <c r="C8" t="n">
         <v>1867.449951171875</v>
@@ -690,7 +690,7 @@
         <v>1567.949951171875</v>
       </c>
       <c r="F8" t="n">
-        <v>744.7601928710938</v>
+        <v>744.76025390625</v>
       </c>
       <c r="G8" t="n">
         <v>21.70999908447266</v>
@@ -710,19 +710,19 @@
         <v>44573</v>
       </c>
       <c r="B9" t="n">
-        <v>2212.774658203125</v>
+        <v>2212.774169921875</v>
       </c>
       <c r="C9" t="n">
         <v>1928.25</v>
       </c>
       <c r="D9" t="n">
-        <v>1826.023803710938</v>
+        <v>1826.023559570312</v>
       </c>
       <c r="E9" t="n">
         <v>1647.550048828125</v>
       </c>
       <c r="F9" t="n">
-        <v>743.25146484375</v>
+        <v>743.2514038085938</v>
       </c>
       <c r="G9" t="n">
         <v>23.8799991607666</v>
@@ -731,7 +731,7 @@
         <v>382.8848266601562</v>
       </c>
       <c r="I9" t="n">
-        <v>1794.071044921875</v>
+        <v>1794.071166992188</v>
       </c>
       <c r="J9" t="n">
         <v>120</v>
@@ -763,7 +763,7 @@
         <v>381.4414367675781</v>
       </c>
       <c r="I10" t="n">
-        <v>1818.585083007812</v>
+        <v>1818.585205078125</v>
       </c>
       <c r="J10" t="n">
         <v>119.9499969482422</v>
@@ -774,7 +774,7 @@
         <v>44575</v>
       </c>
       <c r="B11" t="n">
-        <v>2254.166015625</v>
+        <v>2254.165771484375</v>
       </c>
       <c r="C11" t="n">
         <v>2020.599975585938</v>
@@ -792,7 +792,7 @@
         <v>23.43000030517578</v>
       </c>
       <c r="H11" t="n">
-        <v>387.5037231445312</v>
+        <v>387.5036926269531</v>
       </c>
       <c r="I11" t="n">
         <v>1803.207763671875</v>
@@ -806,7 +806,7 @@
         <v>44578</v>
       </c>
       <c r="B12" t="n">
-        <v>2273.81005859375</v>
+        <v>2273.809814453125</v>
       </c>
       <c r="C12" t="n">
         <v>2002.699951171875</v>
@@ -818,7 +818,7 @@
         <v>1835.300048828125</v>
       </c>
       <c r="F12" t="n">
-        <v>758.3394165039062</v>
+        <v>758.33935546875</v>
       </c>
       <c r="G12" t="n">
         <v>23.20999908447266</v>
@@ -827,7 +827,7 @@
         <v>392.4112243652344</v>
       </c>
       <c r="I12" t="n">
-        <v>1796.168090820312</v>
+        <v>1796.16796875</v>
       </c>
       <c r="J12" t="n">
         <v>117.4000015258789</v>
@@ -838,13 +838,13 @@
         <v>44579</v>
       </c>
       <c r="B13" t="n">
-        <v>2153.93701171875</v>
+        <v>2153.937255859375</v>
       </c>
       <c r="C13" t="n">
         <v>2026.75</v>
       </c>
       <c r="D13" t="n">
-        <v>1836.849609375</v>
+        <v>1836.849487304688</v>
       </c>
       <c r="E13" t="n">
         <v>1900.099975585938</v>
@@ -856,10 +856,10 @@
         <v>21.95000076293945</v>
       </c>
       <c r="H13" t="n">
-        <v>366.2857055664062</v>
+        <v>366.2857666015625</v>
       </c>
       <c r="I13" t="n">
-        <v>1812.793579101562</v>
+        <v>1812.793701171875</v>
       </c>
       <c r="J13" t="n">
         <v>115.5999984741211</v>
@@ -882,7 +882,7 @@
         <v>1938.449951171875</v>
       </c>
       <c r="F14" t="n">
-        <v>724.4158325195312</v>
+        <v>724.4158935546875</v>
       </c>
       <c r="G14" t="n">
         <v>22.78000068664551</v>
@@ -891,7 +891,7 @@
         <v>360.7046203613281</v>
       </c>
       <c r="I14" t="n">
-        <v>1792.27392578125</v>
+        <v>1792.273803710938</v>
       </c>
       <c r="J14" t="n">
         <v>117.3000030517578</v>
@@ -914,16 +914,16 @@
         <v>1966.699951171875</v>
       </c>
       <c r="F15" t="n">
-        <v>718.380615234375</v>
+        <v>718.3806762695312</v>
       </c>
       <c r="G15" t="n">
         <v>22.75</v>
       </c>
       <c r="H15" t="n">
-        <v>360.9452209472656</v>
+        <v>360.9451904296875</v>
       </c>
       <c r="I15" t="n">
-        <v>1801.060913085938</v>
+        <v>1801.060791015625</v>
       </c>
       <c r="J15" t="n">
         <v>119.8000030517578</v>
@@ -934,13 +934,13 @@
         <v>44582</v>
       </c>
       <c r="B16" t="n">
-        <v>2118.08984375</v>
+        <v>2118.090087890625</v>
       </c>
       <c r="C16" t="n">
         <v>2066.800048828125</v>
       </c>
       <c r="D16" t="n">
-        <v>1824.277587890625</v>
+        <v>1824.277465820312</v>
       </c>
       <c r="E16" t="n">
         <v>1934.550048828125</v>
@@ -952,10 +952,10 @@
         <v>21.98999977111816</v>
       </c>
       <c r="H16" t="n">
-        <v>354.7385864257812</v>
+        <v>354.7386169433594</v>
       </c>
       <c r="I16" t="n">
-        <v>1824.626342773438</v>
+        <v>1824.62646484375</v>
       </c>
       <c r="J16" t="n">
         <v>114.4000015258789</v>
@@ -972,7 +972,7 @@
         <v>2035.900024414062</v>
       </c>
       <c r="D17" t="n">
-        <v>1711.978515625</v>
+        <v>1711.978393554688</v>
       </c>
       <c r="E17" t="n">
         <v>1837.849975585938</v>
@@ -987,7 +987,7 @@
         <v>339.5348205566406</v>
       </c>
       <c r="I17" t="n">
-        <v>1778.543823242188</v>
+        <v>1778.5439453125</v>
       </c>
       <c r="J17" t="n">
         <v>106.6999969482422</v>
@@ -1004,13 +1004,13 @@
         <v>1992.449951171875</v>
       </c>
       <c r="D18" t="n">
-        <v>1737.521240234375</v>
+        <v>1737.521484375</v>
       </c>
       <c r="E18" t="n">
         <v>1929</v>
       </c>
       <c r="F18" t="n">
-        <v>692.1957397460938</v>
+        <v>692.19580078125</v>
       </c>
       <c r="G18" t="n">
         <v>21.43000030517578</v>
@@ -1019,7 +1019,7 @@
         <v>338.2357788085938</v>
       </c>
       <c r="I18" t="n">
-        <v>1822.529296875</v>
+        <v>1822.529418945312</v>
       </c>
       <c r="J18" t="n">
         <v>108.8000030517578</v>
@@ -1036,13 +1036,13 @@
         <v>2009.300048828125</v>
       </c>
       <c r="D19" t="n">
-        <v>1682.244750976562</v>
+        <v>1682.24462890625</v>
       </c>
       <c r="E19" t="n">
         <v>1910.25</v>
       </c>
       <c r="F19" t="n">
-        <v>690.2489013671875</v>
+        <v>690.2489624023438</v>
       </c>
       <c r="G19" t="n">
         <v>21.1299991607666</v>
@@ -1062,7 +1062,7 @@
         <v>44589</v>
       </c>
       <c r="B20" t="n">
-        <v>2118.281005859375</v>
+        <v>2118.28125</v>
       </c>
       <c r="C20" t="n">
         <v>1986.800048828125</v>
@@ -1080,7 +1080,7 @@
         <v>21.14999961853027</v>
       </c>
       <c r="H20" t="n">
-        <v>347.0885925292969</v>
+        <v>347.088623046875</v>
       </c>
       <c r="I20" t="n">
         <v>1828.221069335938</v>
@@ -1112,10 +1112,10 @@
         <v>21.25</v>
       </c>
       <c r="H21" t="n">
-        <v>351.3706970214844</v>
+        <v>351.3706665039062</v>
       </c>
       <c r="I21" t="n">
-        <v>1818.585083007812</v>
+        <v>1818.585205078125</v>
       </c>
       <c r="J21" t="n">
         <v>111</v>
@@ -1126,7 +1126,7 @@
         <v>44593</v>
       </c>
       <c r="B22" t="n">
-        <v>2229.742431640625</v>
+        <v>2229.741943359375</v>
       </c>
       <c r="C22" t="n">
         <v>1986.900024414062</v>
@@ -1138,13 +1138,13 @@
         <v>1904</v>
       </c>
       <c r="F22" t="n">
-        <v>719.1107177734375</v>
+        <v>719.1107788085938</v>
       </c>
       <c r="G22" t="n">
         <v>21.60000038146973</v>
       </c>
       <c r="H22" t="n">
-        <v>366.045166015625</v>
+        <v>366.0451965332031</v>
       </c>
       <c r="I22" t="n">
         <v>1861.921752929688</v>
@@ -1158,7 +1158,7 @@
         <v>44594</v>
       </c>
       <c r="B23" t="n">
-        <v>2204.88818359375</v>
+        <v>2204.887939453125</v>
       </c>
       <c r="C23" t="n">
         <v>2016</v>
@@ -1179,7 +1179,7 @@
         <v>365.6602783203125</v>
       </c>
       <c r="I23" t="n">
-        <v>1874.353515625</v>
+        <v>1874.353393554688</v>
       </c>
       <c r="J23" t="n">
         <v>112.0500030517578</v>
@@ -1190,19 +1190,19 @@
         <v>44595</v>
       </c>
       <c r="B24" t="n">
-        <v>2192.508544921875</v>
+        <v>2192.509033203125</v>
       </c>
       <c r="C24" t="n">
         <v>2006.199951171875</v>
       </c>
       <c r="D24" t="n">
-        <v>1747.947998046875</v>
+        <v>1747.947875976562</v>
       </c>
       <c r="E24" t="n">
         <v>1912.550048828125</v>
       </c>
       <c r="F24" t="n">
-        <v>713.0269165039062</v>
+        <v>713.02685546875</v>
       </c>
       <c r="G24" t="n">
         <v>21.52000045776367</v>
@@ -1211,7 +1211,7 @@
         <v>367.4885864257812</v>
       </c>
       <c r="I24" t="n">
-        <v>1848.940795898438</v>
+        <v>1848.940673828125</v>
       </c>
       <c r="J24" t="n">
         <v>115.1500015258789</v>
@@ -1240,10 +1240,10 @@
         <v>21.70999908447266</v>
       </c>
       <c r="H25" t="n">
-        <v>366.045166015625</v>
+        <v>366.0451965332031</v>
       </c>
       <c r="I25" t="n">
-        <v>1848.391357421875</v>
+        <v>1848.391479492188</v>
       </c>
       <c r="J25" t="n">
         <v>112.9499969482422</v>
@@ -1254,13 +1254,13 @@
         <v>44599</v>
       </c>
       <c r="B26" t="n">
-        <v>2181.611083984375</v>
+        <v>2181.611328125</v>
       </c>
       <c r="C26" t="n">
         <v>2028.5</v>
       </c>
       <c r="D26" t="n">
-        <v>1727.942626953125</v>
+        <v>1727.942749023438</v>
       </c>
       <c r="E26" t="n">
         <v>2024.650024414062</v>
@@ -1272,7 +1272,7 @@
         <v>22.34000015258789</v>
       </c>
       <c r="H26" t="n">
-        <v>368.2102661132812</v>
+        <v>368.2102966308594</v>
       </c>
       <c r="I26" t="n">
         <v>1817.48681640625</v>
@@ -1298,13 +1298,13 @@
         <v>1928</v>
       </c>
       <c r="F27" t="n">
-        <v>698.7177124023438</v>
+        <v>698.7176513671875</v>
       </c>
       <c r="G27" t="n">
         <v>21.6299991607666</v>
       </c>
       <c r="H27" t="n">
-        <v>362.0999145507812</v>
+        <v>362.0998840332031</v>
       </c>
       <c r="I27" t="n">
         <v>1806.403076171875</v>
@@ -1330,7 +1330,7 @@
         <v>1919.800048828125</v>
       </c>
       <c r="F28" t="n">
-        <v>713.9515991210938</v>
+        <v>713.95166015625</v>
       </c>
       <c r="G28" t="n">
         <v>21.52000045776367</v>
@@ -1339,7 +1339,7 @@
         <v>368.3546142578125</v>
       </c>
       <c r="I28" t="n">
-        <v>1762.417358398438</v>
+        <v>1762.41748046875</v>
       </c>
       <c r="J28" t="n">
         <v>117.4000015258789</v>
@@ -1356,13 +1356,13 @@
         <v>2036.400024414062</v>
       </c>
       <c r="D29" t="n">
-        <v>1782.121704101562</v>
+        <v>1782.121826171875</v>
       </c>
       <c r="E29" t="n">
         <v>1907.949951171875</v>
       </c>
       <c r="F29" t="n">
-        <v>711.6153564453125</v>
+        <v>711.6154174804688</v>
       </c>
       <c r="G29" t="n">
         <v>24.54999923706055</v>
@@ -1382,19 +1382,19 @@
         <v>44603</v>
       </c>
       <c r="B30" t="n">
-        <v>2150.209228515625</v>
+        <v>2150.20947265625</v>
       </c>
       <c r="C30" t="n">
         <v>2016.050048828125</v>
       </c>
       <c r="D30" t="n">
-        <v>1760.370361328125</v>
+        <v>1760.370239257812</v>
       </c>
       <c r="E30" t="n">
         <v>1907.599975585938</v>
       </c>
       <c r="F30" t="n">
-        <v>704.4608764648438</v>
+        <v>704.4609375</v>
       </c>
       <c r="G30" t="n">
         <v>25</v>
@@ -1420,7 +1420,7 @@
         <v>1915.25</v>
       </c>
       <c r="D31" t="n">
-        <v>1660.243774414062</v>
+        <v>1660.243896484375</v>
       </c>
       <c r="E31" t="n">
         <v>1862.150024414062</v>
@@ -1432,10 +1432,10 @@
         <v>22.67000007629395</v>
       </c>
       <c r="H31" t="n">
-        <v>341.6999206542969</v>
+        <v>341.6998901367188</v>
       </c>
       <c r="I31" t="n">
-        <v>1709.794555664062</v>
+        <v>1709.79443359375</v>
       </c>
       <c r="J31" t="n">
         <v>174.3000030517578</v>
@@ -1452,22 +1452,22 @@
         <v>1926.949951171875</v>
       </c>
       <c r="D32" t="n">
-        <v>1740.365112304688</v>
+        <v>1740.364990234375</v>
       </c>
       <c r="E32" t="n">
         <v>1889.5</v>
       </c>
       <c r="F32" t="n">
-        <v>701.4432373046875</v>
+        <v>701.4432983398438</v>
       </c>
       <c r="G32" t="n">
         <v>23.59000015258789</v>
       </c>
       <c r="H32" t="n">
-        <v>349.8310241699219</v>
+        <v>349.8310546875</v>
       </c>
       <c r="I32" t="n">
-        <v>1735.1572265625</v>
+        <v>1735.157348632812</v>
       </c>
       <c r="J32" t="n">
         <v>156.8999938964844</v>
@@ -1478,13 +1478,13 @@
         <v>44608</v>
       </c>
       <c r="B33" t="n">
-        <v>2140.697265625</v>
+        <v>2140.697509765625</v>
       </c>
       <c r="C33" t="n">
         <v>1932.550048828125</v>
       </c>
       <c r="D33" t="n">
-        <v>1734.228515625</v>
+        <v>1734.228637695312</v>
       </c>
       <c r="E33" t="n">
         <v>1931.75</v>
@@ -1496,7 +1496,7 @@
         <v>25.35000038146973</v>
       </c>
       <c r="H33" t="n">
-        <v>347.0885925292969</v>
+        <v>347.088623046875</v>
       </c>
       <c r="I33" t="n">
         <v>1683.882568359375</v>
@@ -1510,7 +1510,7 @@
         <v>44609</v>
       </c>
       <c r="B34" t="n">
-        <v>2128.701171875</v>
+        <v>2128.700927734375</v>
       </c>
       <c r="C34" t="n">
         <v>2020.849975585938</v>
@@ -1522,7 +1522,7 @@
         <v>2047.599975585938</v>
       </c>
       <c r="F34" t="n">
-        <v>714.6817626953125</v>
+        <v>714.6817016601562</v>
       </c>
       <c r="G34" t="n">
         <v>26.39999961853027</v>
@@ -1548,22 +1548,22 @@
         <v>1958.099975585938</v>
       </c>
       <c r="D35" t="n">
-        <v>1732.4326171875</v>
+        <v>1732.432739257812</v>
       </c>
       <c r="E35" t="n">
         <v>2041.849975585938</v>
       </c>
       <c r="F35" t="n">
-        <v>708.1597900390625</v>
+        <v>708.1598510742188</v>
       </c>
       <c r="G35" t="n">
         <v>26.31999969482422</v>
       </c>
       <c r="H35" t="n">
-        <v>325.5819702148438</v>
+        <v>325.5820007324219</v>
       </c>
       <c r="I35" t="n">
-        <v>1662.763549804688</v>
+        <v>1662.763427734375</v>
       </c>
       <c r="J35" t="n">
         <v>164.6499938964844</v>
@@ -1574,25 +1574,25 @@
         <v>44613</v>
       </c>
       <c r="B36" t="n">
-        <v>2088.599853515625</v>
+        <v>2088.599609375</v>
       </c>
       <c r="C36" t="n">
         <v>1895.900024414062</v>
       </c>
       <c r="D36" t="n">
-        <v>1681.446533203125</v>
+        <v>1681.446411132812</v>
       </c>
       <c r="E36" t="n">
         <v>1955.900024414062</v>
       </c>
       <c r="F36" t="n">
-        <v>692.1957397460938</v>
+        <v>692.19580078125</v>
       </c>
       <c r="G36" t="n">
         <v>24.03000068664551</v>
       </c>
       <c r="H36" t="n">
-        <v>325.7744445800781</v>
+        <v>325.7744750976562</v>
       </c>
       <c r="I36" t="n">
         <v>1588.77197265625</v>
@@ -1606,7 +1606,7 @@
         <v>44614</v>
       </c>
       <c r="B37" t="n">
-        <v>2069.958740234375</v>
+        <v>2069.959228515625</v>
       </c>
       <c r="C37" t="n">
         <v>1969.099975585938</v>
@@ -1624,7 +1624,7 @@
         <v>24.11000061035156</v>
       </c>
       <c r="H37" t="n">
-        <v>324.6197814941406</v>
+        <v>324.6197509765625</v>
       </c>
       <c r="I37" t="n">
         <v>1585.177124023438</v>
@@ -1644,7 +1644,7 @@
         <v>2060.14990234375</v>
       </c>
       <c r="D38" t="n">
-        <v>1684.938598632812</v>
+        <v>1684.9384765625</v>
       </c>
       <c r="E38" t="n">
         <v>1987.349975585938</v>
@@ -1670,19 +1670,19 @@
         <v>44616</v>
       </c>
       <c r="B39" t="n">
-        <v>1925.232299804688</v>
+        <v>1925.232177734375</v>
       </c>
       <c r="C39" t="n">
         <v>1957.300048828125</v>
       </c>
       <c r="D39" t="n">
-        <v>1540.510986328125</v>
+        <v>1540.511108398438</v>
       </c>
       <c r="E39" t="n">
         <v>1849.75</v>
       </c>
       <c r="F39" t="n">
-        <v>637.4412231445312</v>
+        <v>637.441162109375</v>
       </c>
       <c r="G39" t="n">
         <v>22.22999954223633</v>
@@ -1691,7 +1691,7 @@
         <v>295.3669128417969</v>
       </c>
       <c r="I39" t="n">
-        <v>1562.760131835938</v>
+        <v>1562.760009765625</v>
       </c>
       <c r="J39" t="n">
         <v>135.5</v>
@@ -1702,7 +1702,7 @@
         <v>44617</v>
       </c>
       <c r="B40" t="n">
-        <v>1968.774780273438</v>
+        <v>1968.774658203125</v>
       </c>
       <c r="C40" t="n">
         <v>2032.849975585938</v>
@@ -1723,7 +1723,7 @@
         <v>297.0509033203125</v>
       </c>
       <c r="I40" t="n">
-        <v>1570.898071289062</v>
+        <v>1570.89794921875</v>
       </c>
       <c r="J40" t="n">
         <v>143.9499969482422</v>
@@ -1734,7 +1734,7 @@
         <v>44620</v>
       </c>
       <c r="B41" t="n">
-        <v>1997.070190429688</v>
+        <v>1997.069702148438</v>
       </c>
       <c r="C41" t="n">
         <v>2134.39990234375</v>
@@ -1746,16 +1746,16 @@
         <v>1843.400024414062</v>
       </c>
       <c r="F41" t="n">
-        <v>688.6915283203125</v>
+        <v>688.6914672851562</v>
       </c>
       <c r="G41" t="n">
         <v>24.75</v>
       </c>
       <c r="H41" t="n">
-        <v>302.3914489746094</v>
+        <v>302.3914184570312</v>
       </c>
       <c r="I41" t="n">
-        <v>1586.17578125</v>
+        <v>1586.175659179688</v>
       </c>
       <c r="J41" t="n">
         <v>149.25</v>
@@ -1766,13 +1766,13 @@
         <v>44622</v>
       </c>
       <c r="B42" t="n">
-        <v>1976.613037109375</v>
+        <v>1976.613159179688</v>
       </c>
       <c r="C42" t="n">
         <v>2241.050048828125</v>
       </c>
       <c r="D42" t="n">
-        <v>1638.143310546875</v>
+        <v>1638.143188476562</v>
       </c>
       <c r="E42" t="n">
         <v>1882.550048828125</v>
@@ -1787,7 +1787,7 @@
         <v>292.6725769042969</v>
       </c>
       <c r="I42" t="n">
-        <v>1665.45947265625</v>
+        <v>1665.459350585938</v>
       </c>
       <c r="J42" t="n">
         <v>153.5</v>
@@ -1798,7 +1798,7 @@
         <v>44623</v>
       </c>
       <c r="B43" t="n">
-        <v>1869.788696289062</v>
+        <v>1869.78857421875</v>
       </c>
       <c r="C43" t="n">
         <v>2353.10009765625</v>
@@ -1819,7 +1819,7 @@
         <v>279.2490234375</v>
       </c>
       <c r="I43" t="n">
-        <v>1748.687622070312</v>
+        <v>1748.6875</v>
       </c>
       <c r="J43" t="n">
         <v>155.5500030517578</v>
@@ -1830,7 +1830,7 @@
         <v>44624</v>
       </c>
       <c r="B44" t="n">
-        <v>1921.934448242188</v>
+        <v>1921.934326171875</v>
       </c>
       <c r="C44" t="n">
         <v>2323.199951171875</v>
@@ -1862,25 +1862,25 @@
         <v>44627</v>
       </c>
       <c r="B45" t="n">
-        <v>1864.196411132812</v>
+        <v>1864.196533203125</v>
       </c>
       <c r="C45" t="n">
         <v>2207.35009765625</v>
       </c>
       <c r="D45" t="n">
-        <v>1560.56640625</v>
+        <v>1560.566284179688</v>
       </c>
       <c r="E45" t="n">
         <v>1803.75</v>
       </c>
       <c r="F45" t="n">
-        <v>659.7810668945312</v>
+        <v>659.7811279296875</v>
       </c>
       <c r="G45" t="n">
         <v>23.29000091552734</v>
       </c>
       <c r="H45" t="n">
-        <v>270.588623046875</v>
+        <v>270.5886535644531</v>
       </c>
       <c r="I45" t="n">
         <v>1712.440673828125</v>
@@ -1906,16 +1906,16 @@
         <v>1783.949951171875</v>
       </c>
       <c r="F46" t="n">
-        <v>670.537353515625</v>
+        <v>670.5372924804688</v>
       </c>
       <c r="G46" t="n">
         <v>23.73999977111816</v>
       </c>
       <c r="H46" t="n">
-        <v>272.2244873046875</v>
+        <v>272.2244567871094</v>
       </c>
       <c r="I46" t="n">
-        <v>1627.265502929688</v>
+        <v>1627.265625</v>
       </c>
       <c r="J46" t="n">
         <v>172.3500061035156</v>
@@ -1932,7 +1932,7 @@
         <v>2164.64990234375</v>
       </c>
       <c r="D47" t="n">
-        <v>1652.8603515625</v>
+        <v>1652.860473632812</v>
       </c>
       <c r="E47" t="n">
         <v>1828.75</v>
@@ -1944,10 +1944,10 @@
         <v>24.26000022888184</v>
       </c>
       <c r="H47" t="n">
-        <v>280.6442565917969</v>
+        <v>280.644287109375</v>
       </c>
       <c r="I47" t="n">
-        <v>1612.986328125</v>
+        <v>1612.986450195312</v>
       </c>
       <c r="J47" t="n">
         <v>176.3500061035156</v>
@@ -1958,7 +1958,7 @@
         <v>44630</v>
       </c>
       <c r="B48" t="n">
-        <v>1957.351318359375</v>
+        <v>1957.351196289062</v>
       </c>
       <c r="C48" t="n">
         <v>2272.75</v>
@@ -1976,10 +1976,10 @@
         <v>24.5</v>
       </c>
       <c r="H48" t="n">
-        <v>282.1357727050781</v>
+        <v>282.1358032226562</v>
       </c>
       <c r="I48" t="n">
-        <v>1693.568481445312</v>
+        <v>1693.568603515625</v>
       </c>
       <c r="J48" t="n">
         <v>171.3500061035156</v>
@@ -1990,7 +1990,7 @@
         <v>44631</v>
       </c>
       <c r="B49" t="n">
-        <v>1951.902587890625</v>
+        <v>1951.902465820312</v>
       </c>
       <c r="C49" t="n">
         <v>2307.25</v>
@@ -2008,10 +2008,10 @@
         <v>24.36000061035156</v>
       </c>
       <c r="H49" t="n">
-        <v>282.3763732910156</v>
+        <v>282.3763427734375</v>
       </c>
       <c r="I49" t="n">
-        <v>1659.418334960938</v>
+        <v>1659.41845703125</v>
       </c>
       <c r="J49" t="n">
         <v>169</v>
@@ -2022,7 +2022,7 @@
         <v>44634</v>
       </c>
       <c r="B50" t="n">
-        <v>1967.340698242188</v>
+        <v>1967.3408203125</v>
       </c>
       <c r="C50" t="n">
         <v>2268.300048828125</v>
@@ -2034,7 +2034,7 @@
         <v>1822.400024414062</v>
       </c>
       <c r="F50" t="n">
-        <v>711.1287231445312</v>
+        <v>711.1287841796875</v>
       </c>
       <c r="G50" t="n">
         <v>24.43000030517578</v>
@@ -2060,7 +2060,7 @@
         <v>2217.550048828125</v>
       </c>
       <c r="D51" t="n">
-        <v>1697.610473632812</v>
+        <v>1697.6103515625</v>
       </c>
       <c r="E51" t="n">
         <v>1798.75</v>
@@ -2072,10 +2072,10 @@
         <v>24.45999908447266</v>
       </c>
       <c r="H51" t="n">
-        <v>283.964111328125</v>
+        <v>283.9640808105469</v>
       </c>
       <c r="I51" t="n">
-        <v>1622.023193359375</v>
+        <v>1622.0234375</v>
       </c>
       <c r="J51" t="n">
         <v>179.1499938964844</v>
@@ -2098,16 +2098,16 @@
         <v>1833.650024414062</v>
       </c>
       <c r="F52" t="n">
-        <v>704.5581665039062</v>
+        <v>704.5582275390625</v>
       </c>
       <c r="G52" t="n">
         <v>24.57999992370605</v>
       </c>
       <c r="H52" t="n">
-        <v>297.6763610839844</v>
+        <v>297.6763305664062</v>
       </c>
       <c r="I52" t="n">
-        <v>1682.634399414062</v>
+        <v>1682.63427734375</v>
       </c>
       <c r="J52" t="n">
         <v>197.0500030517578</v>
@@ -2118,13 +2118,13 @@
         <v>44637</v>
       </c>
       <c r="B53" t="n">
-        <v>2029.093505859375</v>
+        <v>2029.093383789062</v>
       </c>
       <c r="C53" t="n">
         <v>2389.800048828125</v>
       </c>
       <c r="D53" t="n">
-        <v>1815.597045898438</v>
+        <v>1815.59716796875</v>
       </c>
       <c r="E53" t="n">
         <v>1901.199951171875</v>
@@ -2139,7 +2139,7 @@
         <v>294.6452026367188</v>
       </c>
       <c r="I53" t="n">
-        <v>1764.21484375</v>
+        <v>1764.215087890625</v>
       </c>
       <c r="J53" t="n">
         <v>206.6000061035156</v>
@@ -2150,7 +2150,7 @@
         <v>44641</v>
       </c>
       <c r="B54" t="n">
-        <v>1965.142211914062</v>
+        <v>1965.141967773438</v>
       </c>
       <c r="C54" t="n">
         <v>2289.050048828125</v>
@@ -2168,7 +2168,7 @@
         <v>24.90999984741211</v>
       </c>
       <c r="H54" t="n">
-        <v>289.0159606933594</v>
+        <v>289.0159912109375</v>
       </c>
       <c r="I54" t="n">
         <v>1811.49560546875</v>
@@ -2194,7 +2194,7 @@
         <v>1877.449951171875</v>
       </c>
       <c r="F55" t="n">
-        <v>719.5001220703125</v>
+        <v>719.5001831054688</v>
       </c>
       <c r="G55" t="n">
         <v>24.75</v>
@@ -2214,7 +2214,7 @@
         <v>44643</v>
       </c>
       <c r="B56" t="n">
-        <v>1978.525024414062</v>
+        <v>1978.525146484375</v>
       </c>
       <c r="C56" t="n">
         <v>2406.699951171875</v>
@@ -2235,7 +2235,7 @@
         <v>286.6103210449219</v>
       </c>
       <c r="I56" t="n">
-        <v>1895.222778320312</v>
+        <v>1895.222900390625</v>
       </c>
       <c r="J56" t="n">
         <v>250.5</v>
@@ -2246,7 +2246,7 @@
         <v>44644</v>
       </c>
       <c r="B57" t="n">
-        <v>1988.705688476562</v>
+        <v>1988.705444335938</v>
       </c>
       <c r="C57" t="n">
         <v>2414.39990234375</v>
@@ -2258,7 +2258,7 @@
         <v>1911.400024414062</v>
       </c>
       <c r="F57" t="n">
-        <v>713.9515991210938</v>
+        <v>713.95166015625</v>
       </c>
       <c r="G57" t="n">
         <v>26.43000030517578</v>
@@ -2290,16 +2290,16 @@
         <v>1921.25</v>
       </c>
       <c r="F58" t="n">
-        <v>723.4911499023438</v>
+        <v>723.4910888671875</v>
       </c>
       <c r="G58" t="n">
         <v>28.63999938964844</v>
       </c>
       <c r="H58" t="n">
-        <v>286.5621337890625</v>
+        <v>286.5621643066406</v>
       </c>
       <c r="I58" t="n">
-        <v>2051.593994140625</v>
+        <v>2051.593505859375</v>
       </c>
       <c r="J58" t="n">
         <v>252.1000061035156</v>
@@ -2328,7 +2328,7 @@
         <v>30.45000076293945</v>
       </c>
       <c r="H59" t="n">
-        <v>280.78857421875</v>
+        <v>280.7886047363281</v>
       </c>
       <c r="I59" t="n">
         <v>2138.06689453125</v>
@@ -2342,7 +2342,7 @@
         <v>44649</v>
       </c>
       <c r="B60" t="n">
-        <v>2034.733154296875</v>
+        <v>2034.733520507812</v>
       </c>
       <c r="C60" t="n">
         <v>2461.550048828125</v>
@@ -2354,7 +2354,7 @@
         <v>1923.300048828125</v>
       </c>
       <c r="F60" t="n">
-        <v>741.6939697265625</v>
+        <v>741.6940307617188</v>
       </c>
       <c r="G60" t="n">
         <v>34.70999908447266</v>
@@ -2363,7 +2363,7 @@
         <v>291.0367431640625</v>
       </c>
       <c r="I60" t="n">
-        <v>2177.609375</v>
+        <v>2177.609130859375</v>
       </c>
       <c r="J60" t="n">
         <v>227.5500030517578</v>
@@ -2386,7 +2386,7 @@
         <v>1857.150024414062</v>
       </c>
       <c r="F61" t="n">
-        <v>746.9991455078125</v>
+        <v>746.9990844726562</v>
       </c>
       <c r="G61" t="n">
         <v>34.29999923706055</v>
@@ -2412,22 +2412,22 @@
         <v>2368.14990234375</v>
       </c>
       <c r="D62" t="n">
-        <v>2010.262573242188</v>
+        <v>2010.262451171875</v>
       </c>
       <c r="E62" t="n">
         <v>1914.699951171875</v>
       </c>
       <c r="F62" t="n">
-        <v>753.6182861328125</v>
+        <v>753.6183471679688</v>
       </c>
       <c r="G62" t="n">
         <v>37.02000045776367</v>
       </c>
       <c r="H62" t="n">
-        <v>294.0831909179688</v>
+        <v>294.0832214355469</v>
       </c>
       <c r="I62" t="n">
-        <v>2146.654541015625</v>
+        <v>2146.654296875</v>
       </c>
       <c r="J62" t="n">
         <v>227</v>
@@ -2444,22 +2444,22 @@
         <v>2421.449951171875</v>
       </c>
       <c r="D63" t="n">
-        <v>2039.09814453125</v>
+        <v>2039.098022460938</v>
       </c>
       <c r="E63" t="n">
         <v>1945.099975585938</v>
       </c>
       <c r="F63" t="n">
-        <v>764.8612670898438</v>
+        <v>764.861328125</v>
       </c>
       <c r="G63" t="n">
         <v>40.68999862670898</v>
       </c>
       <c r="H63" t="n">
-        <v>299.6847839355469</v>
+        <v>299.684814453125</v>
       </c>
       <c r="I63" t="n">
-        <v>2246.208251953125</v>
+        <v>2246.208740234375</v>
       </c>
       <c r="J63" t="n">
         <v>223.25</v>
@@ -2476,7 +2476,7 @@
         <v>2453.5</v>
       </c>
       <c r="D64" t="n">
-        <v>2061.2490234375</v>
+        <v>2061.248779296875</v>
       </c>
       <c r="E64" t="n">
         <v>2110.449951171875</v>
@@ -2488,10 +2488,10 @@
         <v>42.38999938964844</v>
       </c>
       <c r="H64" t="n">
-        <v>306.2691345214844</v>
+        <v>306.2691040039062</v>
       </c>
       <c r="I64" t="n">
-        <v>2366.33251953125</v>
+        <v>2366.332763671875</v>
       </c>
       <c r="J64" t="n">
         <v>224.0500030517578</v>
@@ -2502,13 +2502,13 @@
         <v>44656</v>
       </c>
       <c r="B65" t="n">
-        <v>2111.847412109375</v>
+        <v>2111.84765625</v>
       </c>
       <c r="C65" t="n">
         <v>2443.85009765625</v>
       </c>
       <c r="D65" t="n">
-        <v>2135.083740234375</v>
+        <v>2135.083984375</v>
       </c>
       <c r="E65" t="n">
         <v>2189.800048828125</v>
@@ -2520,10 +2520,10 @@
         <v>46.61999893188477</v>
       </c>
       <c r="H65" t="n">
-        <v>311.3301696777344</v>
+        <v>311.3302001953125</v>
       </c>
       <c r="I65" t="n">
-        <v>2464.538818359375</v>
+        <v>2464.53857421875</v>
       </c>
       <c r="J65" t="n">
         <v>224.5</v>
@@ -2540,19 +2540,19 @@
         <v>2484.050048828125</v>
       </c>
       <c r="D66" t="n">
-        <v>2155.18896484375</v>
+        <v>2155.189208984375</v>
       </c>
       <c r="E66" t="n">
         <v>2197.39990234375</v>
       </c>
       <c r="F66" t="n">
-        <v>827.2572021484375</v>
+        <v>827.2572631835938</v>
       </c>
       <c r="G66" t="n">
         <v>48.95000076293945</v>
       </c>
       <c r="H66" t="n">
-        <v>315.1628723144531</v>
+        <v>315.162841796875</v>
       </c>
       <c r="I66" t="n">
         <v>2533.23779296875</v>
@@ -2572,7 +2572,7 @@
         <v>2449.64990234375</v>
       </c>
       <c r="D67" t="n">
-        <v>2094.374755859375</v>
+        <v>2094.37451171875</v>
       </c>
       <c r="E67" t="n">
         <v>2166</v>
@@ -2587,7 +2587,7 @@
         <v>319.978271484375</v>
       </c>
       <c r="I67" t="n">
-        <v>2359.2431640625</v>
+        <v>2359.24267578125</v>
       </c>
       <c r="J67" t="n">
         <v>212.1999969482422</v>
@@ -2630,13 +2630,13 @@
         <v>44662</v>
       </c>
       <c r="B69" t="n">
-        <v>2193.633544921875</v>
+        <v>2193.6337890625</v>
       </c>
       <c r="C69" t="n">
         <v>2756.5</v>
       </c>
       <c r="D69" t="n">
-        <v>2175.343994140625</v>
+        <v>2175.34423828125</v>
       </c>
       <c r="E69" t="n">
         <v>2665.14990234375</v>
@@ -2651,7 +2651,7 @@
         <v>353.9808654785156</v>
       </c>
       <c r="I69" t="n">
-        <v>2661.1005859375</v>
+        <v>2661.100830078125</v>
       </c>
       <c r="J69" t="n">
         <v>214.4499969482422</v>
@@ -2674,7 +2674,7 @@
         <v>2792.39990234375</v>
       </c>
       <c r="F70" t="n">
-        <v>822.4387817382812</v>
+        <v>822.4388427734375</v>
       </c>
       <c r="G70" t="n">
         <v>46.15999984741211</v>
@@ -2694,7 +2694,7 @@
         <v>44664</v>
       </c>
       <c r="B71" t="n">
-        <v>2169.809814453125</v>
+        <v>2169.81005859375</v>
       </c>
       <c r="C71" t="n">
         <v>2690.75</v>
@@ -2712,10 +2712,10 @@
         <v>44.65000152587891</v>
       </c>
       <c r="H71" t="n">
-        <v>362.8255004882812</v>
+        <v>362.8254699707031</v>
       </c>
       <c r="I71" t="n">
-        <v>2497.19091796875</v>
+        <v>2497.190673828125</v>
       </c>
       <c r="J71" t="n">
         <v>200.1000061035156</v>
@@ -2732,7 +2732,7 @@
         <v>2728.300048828125</v>
       </c>
       <c r="D72" t="n">
-        <v>2228.87451171875</v>
+        <v>2228.874267578125</v>
       </c>
       <c r="E72" t="n">
         <v>2970.5</v>
@@ -2758,7 +2758,7 @@
         <v>44670</v>
       </c>
       <c r="B73" t="n">
-        <v>2020.335693359375</v>
+        <v>2020.3359375</v>
       </c>
       <c r="C73" t="n">
         <v>2598.050048828125</v>
@@ -2770,16 +2770,16 @@
         <v>2911.949951171875</v>
       </c>
       <c r="F73" t="n">
-        <v>797.5194091796875</v>
+        <v>797.519287109375</v>
       </c>
       <c r="G73" t="n">
         <v>46.4900016784668</v>
       </c>
       <c r="H73" t="n">
-        <v>348.1336059570312</v>
+        <v>348.1335754394531</v>
       </c>
       <c r="I73" t="n">
-        <v>2365.93310546875</v>
+        <v>2365.933349609375</v>
       </c>
       <c r="J73" t="n">
         <v>218.75</v>
@@ -2796,13 +2796,13 @@
         <v>2687.550048828125</v>
       </c>
       <c r="D74" t="n">
-        <v>2179.085693359375</v>
+        <v>2179.08544921875</v>
       </c>
       <c r="E74" t="n">
         <v>2810.85009765625</v>
       </c>
       <c r="F74" t="n">
-        <v>805.6473999023438</v>
+        <v>805.6474609375</v>
       </c>
       <c r="G74" t="n">
         <v>47.0099983215332</v>
@@ -2811,7 +2811,7 @@
         <v>364.8891906738281</v>
       </c>
       <c r="I74" t="n">
-        <v>2474.7734375</v>
+        <v>2474.773681640625</v>
       </c>
       <c r="J74" t="n">
         <v>213.0500030517578</v>
@@ -2840,7 +2840,7 @@
         <v>49.36000061035156</v>
       </c>
       <c r="H75" t="n">
-        <v>370.8347778320312</v>
+        <v>370.8347473144531</v>
       </c>
       <c r="I75" t="n">
         <v>2439.775146484375</v>
@@ -2866,7 +2866,7 @@
         <v>2882.800048828125</v>
       </c>
       <c r="F76" t="n">
-        <v>850.9113159179688</v>
+        <v>850.9111938476562</v>
       </c>
       <c r="G76" t="n">
         <v>51.81999969482422</v>
@@ -2898,16 +2898,16 @@
         <v>2824</v>
       </c>
       <c r="F77" t="n">
-        <v>836.6994018554688</v>
+        <v>836.6993408203125</v>
       </c>
       <c r="G77" t="n">
         <v>54.40999984741211</v>
       </c>
       <c r="H77" t="n">
-        <v>369.8520202636719</v>
+        <v>369.8519897460938</v>
       </c>
       <c r="I77" t="n">
-        <v>2416.459228515625</v>
+        <v>2416.458984375</v>
       </c>
       <c r="J77" t="n">
         <v>201.8500061035156</v>
@@ -2936,10 +2936,10 @@
         <v>57.13000106811523</v>
       </c>
       <c r="H78" t="n">
-        <v>378.5000610351562</v>
+        <v>378.5000915527344</v>
       </c>
       <c r="I78" t="n">
-        <v>2558.750732421875</v>
+        <v>2558.7509765625</v>
       </c>
       <c r="J78" t="n">
         <v>206.3500061035156</v>
@@ -2968,7 +2968,7 @@
         <v>59.84000015258789</v>
       </c>
       <c r="H79" t="n">
-        <v>377.9104614257812</v>
+        <v>377.9104309082031</v>
       </c>
       <c r="I79" t="n">
         <v>2499.337890625</v>
@@ -3003,7 +3003,7 @@
         <v>376.7311706542969</v>
       </c>
       <c r="I80" t="n">
-        <v>2558.850830078125</v>
+        <v>2558.8505859375</v>
       </c>
       <c r="J80" t="n">
         <v>199.8999938964844</v>
@@ -3020,7 +3020,7 @@
         <v>2789.5</v>
       </c>
       <c r="D81" t="n">
-        <v>2326.8056640625</v>
+        <v>2326.805908203125</v>
       </c>
       <c r="E81" t="n">
         <v>2882.800048828125</v>
@@ -3052,7 +3052,7 @@
         <v>2804.449951171875</v>
       </c>
       <c r="D82" t="n">
-        <v>2334.289306640625</v>
+        <v>2334.2890625</v>
       </c>
       <c r="E82" t="n">
         <v>2830.35009765625</v>
@@ -3064,7 +3064,7 @@
         <v>56.06999969482422</v>
       </c>
       <c r="H82" t="n">
-        <v>371.6209411621094</v>
+        <v>371.6209106445312</v>
       </c>
       <c r="I82" t="n">
         <v>2484.559326171875</v>
@@ -3078,7 +3078,7 @@
         <v>44685</v>
       </c>
       <c r="B83" t="n">
-        <v>2259.652099609375</v>
+        <v>2259.65234375</v>
       </c>
       <c r="C83" t="n">
         <v>2783.300048828125</v>
@@ -3090,7 +3090,7 @@
         <v>2671.35009765625</v>
       </c>
       <c r="F83" t="n">
-        <v>791.192138671875</v>
+        <v>791.1920776367188</v>
       </c>
       <c r="G83" t="n">
         <v>53.27000045776367</v>
@@ -3116,13 +3116,13 @@
         <v>2801.64990234375</v>
       </c>
       <c r="D84" t="n">
-        <v>2250.3759765625</v>
+        <v>2250.37646484375</v>
       </c>
       <c r="E84" t="n">
         <v>2845.89990234375</v>
       </c>
       <c r="F84" t="n">
-        <v>789.78076171875</v>
+        <v>789.7807006835938</v>
       </c>
       <c r="G84" t="n">
         <v>55.63000106811523</v>
@@ -3131,7 +3131,7 @@
         <v>360.0246887207031</v>
       </c>
       <c r="I84" t="n">
-        <v>2446.914306640625</v>
+        <v>2446.914794921875</v>
       </c>
       <c r="J84" t="n">
         <v>180.3500061035156</v>
@@ -3142,25 +3142,25 @@
         <v>44687</v>
       </c>
       <c r="B85" t="n">
-        <v>2205.962890625</v>
+        <v>2205.963134765625</v>
       </c>
       <c r="C85" t="n">
         <v>2816.5</v>
       </c>
       <c r="D85" t="n">
-        <v>2242.693359375</v>
+        <v>2242.693603515625</v>
       </c>
       <c r="E85" t="n">
         <v>2874.800048828125</v>
       </c>
       <c r="F85" t="n">
-        <v>789.829345703125</v>
+        <v>789.8294067382812</v>
       </c>
       <c r="G85" t="n">
         <v>58.40999984741211</v>
       </c>
       <c r="H85" t="n">
-        <v>359.0910339355469</v>
+        <v>359.091064453125</v>
       </c>
       <c r="I85" t="n">
         <v>2434.083251953125</v>
@@ -3174,19 +3174,19 @@
         <v>44690</v>
       </c>
       <c r="B86" t="n">
-        <v>2193.633544921875</v>
+        <v>2193.6337890625</v>
       </c>
       <c r="C86" t="n">
         <v>2703.449951171875</v>
       </c>
       <c r="D86" t="n">
-        <v>2192.75537109375</v>
+        <v>2192.755126953125</v>
       </c>
       <c r="E86" t="n">
         <v>2706.39990234375</v>
       </c>
       <c r="F86" t="n">
-        <v>771.5292358398438</v>
+        <v>771.5291137695312</v>
       </c>
       <c r="G86" t="n">
         <v>56.31999969482422</v>
@@ -3195,7 +3195,7 @@
         <v>360.4177551269531</v>
       </c>
       <c r="I86" t="n">
-        <v>2371.774658203125</v>
+        <v>2371.7744140625</v>
       </c>
       <c r="J86" t="n">
         <v>170.6999969482422</v>
@@ -3206,28 +3206,28 @@
         <v>44691</v>
       </c>
       <c r="B87" t="n">
-        <v>2159.887939453125</v>
+        <v>2159.8876953125</v>
       </c>
       <c r="C87" t="n">
         <v>2482.550048828125</v>
       </c>
       <c r="D87" t="n">
-        <v>2104.80126953125</v>
+        <v>2104.801513671875</v>
       </c>
       <c r="E87" t="n">
         <v>2486.699951171875</v>
       </c>
       <c r="F87" t="n">
-        <v>748.6538696289062</v>
+        <v>748.6539916992188</v>
       </c>
       <c r="G87" t="n">
         <v>53.5099983215332</v>
       </c>
       <c r="H87" t="n">
-        <v>352.0154113769531</v>
+        <v>352.0154418945312</v>
       </c>
       <c r="I87" t="n">
-        <v>2357.195556640625</v>
+        <v>2357.19580078125</v>
       </c>
       <c r="J87" t="n">
         <v>166.1499938964844</v>
@@ -3238,13 +3238,13 @@
         <v>44692</v>
       </c>
       <c r="B88" t="n">
-        <v>2129.53125</v>
+        <v>2129.531005859375</v>
       </c>
       <c r="C88" t="n">
         <v>2296</v>
       </c>
       <c r="D88" t="n">
-        <v>2114.57958984375</v>
+        <v>2114.579345703125</v>
       </c>
       <c r="E88" t="n">
         <v>2648.050048828125</v>
@@ -3256,10 +3256,10 @@
         <v>51.06000137329102</v>
       </c>
       <c r="H88" t="n">
-        <v>352.8507385253906</v>
+        <v>352.8507080078125</v>
       </c>
       <c r="I88" t="n">
-        <v>2351.604248046875</v>
+        <v>2351.60400390625</v>
       </c>
       <c r="J88" t="n">
         <v>157.9499969482422</v>
@@ -3308,13 +3308,13 @@
         <v>2190.60009765625</v>
       </c>
       <c r="D90" t="n">
-        <v>2049.57470703125</v>
+        <v>2049.574462890625</v>
       </c>
       <c r="E90" t="n">
         <v>2171.550048828125</v>
       </c>
       <c r="F90" t="n">
-        <v>687.134033203125</v>
+        <v>687.1339721679688</v>
       </c>
       <c r="G90" t="n">
         <v>50.93000030517578</v>
@@ -3323,7 +3323,7 @@
         <v>352.8998718261719</v>
       </c>
       <c r="I90" t="n">
-        <v>2365.633544921875</v>
+        <v>2365.6337890625</v>
       </c>
       <c r="J90" t="n">
         <v>157.5</v>
@@ -3334,7 +3334,7 @@
         <v>44697</v>
       </c>
       <c r="B91" t="n">
-        <v>2157.578857421875</v>
+        <v>2157.5791015625</v>
       </c>
       <c r="C91" t="n">
         <v>2249.89990234375</v>
@@ -3346,16 +3346,16 @@
         <v>2281.699951171875</v>
       </c>
       <c r="F91" t="n">
-        <v>693.5586547851562</v>
+        <v>693.55859375</v>
       </c>
       <c r="G91" t="n">
         <v>53.47000122070312</v>
       </c>
       <c r="H91" t="n">
-        <v>361.6462097167969</v>
+        <v>361.6461791992188</v>
       </c>
       <c r="I91" t="n">
-        <v>2385.055419921875</v>
+        <v>2385.054931640625</v>
       </c>
       <c r="J91" t="n">
         <v>165.3500061035156</v>
@@ -3372,7 +3372,7 @@
         <v>2333.39990234375</v>
       </c>
       <c r="D92" t="n">
-        <v>2179.9833984375</v>
+        <v>2179.983642578125</v>
       </c>
       <c r="E92" t="n">
         <v>2285.800048828125</v>
@@ -3387,7 +3387,7 @@
         <v>362.4323425292969</v>
       </c>
       <c r="I92" t="n">
-        <v>2496.84130859375</v>
+        <v>2496.841552734375</v>
       </c>
       <c r="J92" t="n">
         <v>172.6000061035156</v>
@@ -3419,7 +3419,7 @@
         <v>354.8653564453125</v>
       </c>
       <c r="I93" t="n">
-        <v>2482.063232421875</v>
+        <v>2482.062744140625</v>
       </c>
       <c r="J93" t="n">
         <v>176.1999969482422</v>
@@ -3430,13 +3430,13 @@
         <v>44700</v>
       </c>
       <c r="B94" t="n">
-        <v>2191.76708984375</v>
+        <v>2191.767333984375</v>
       </c>
       <c r="C94" t="n">
         <v>2265</v>
       </c>
       <c r="D94" t="n">
-        <v>2110.039794921875</v>
+        <v>2110.03955078125</v>
       </c>
       <c r="E94" t="n">
         <v>2317.5</v>
@@ -3451,7 +3451,7 @@
         <v>357.7152404785156</v>
       </c>
       <c r="I94" t="n">
-        <v>2375.02001953125</v>
+        <v>2375.019775390625</v>
       </c>
       <c r="J94" t="n">
         <v>167.3999938964844</v>
@@ -3462,7 +3462,7 @@
         <v>44701</v>
       </c>
       <c r="B95" t="n">
-        <v>2200.01904296875</v>
+        <v>2200.019287109375</v>
       </c>
       <c r="C95" t="n">
         <v>2310.949951171875</v>
@@ -3483,7 +3483,7 @@
         <v>356.7325134277344</v>
       </c>
       <c r="I95" t="n">
-        <v>2376.8671875</v>
+        <v>2376.867431640625</v>
       </c>
       <c r="J95" t="n">
         <v>168.3999938964844</v>
@@ -3500,13 +3500,13 @@
         <v>2199.199951171875</v>
       </c>
       <c r="D96" t="n">
-        <v>2165.81494140625</v>
+        <v>2165.815185546875</v>
       </c>
       <c r="E96" t="n">
         <v>2248.35009765625</v>
       </c>
       <c r="F96" t="n">
-        <v>733.517333984375</v>
+        <v>733.5172729492188</v>
       </c>
       <c r="G96" t="n">
         <v>65.56999969482422</v>
@@ -3532,13 +3532,13 @@
         <v>2196.5</v>
       </c>
       <c r="D97" t="n">
-        <v>2155.388427734375</v>
+        <v>2155.38818359375</v>
       </c>
       <c r="E97" t="n">
         <v>2136.300048828125</v>
       </c>
       <c r="F97" t="n">
-        <v>732.154541015625</v>
+        <v>732.1544799804688</v>
       </c>
       <c r="G97" t="n">
         <v>62.29999923706055</v>
@@ -3547,7 +3547,7 @@
         <v>355.2092895507812</v>
       </c>
       <c r="I97" t="n">
-        <v>2324.84326171875</v>
+        <v>2324.843505859375</v>
       </c>
       <c r="J97" t="n">
         <v>159.0500030517578</v>
@@ -3558,7 +3558,7 @@
         <v>44706</v>
       </c>
       <c r="B98" t="n">
-        <v>2147.65673828125</v>
+        <v>2147.656494140625</v>
       </c>
       <c r="C98" t="n">
         <v>2087.949951171875</v>
@@ -3570,7 +3570,7 @@
         <v>2187.35009765625</v>
       </c>
       <c r="F98" t="n">
-        <v>689.0809326171875</v>
+        <v>689.0808715820312</v>
       </c>
       <c r="G98" t="n">
         <v>59.86999893188477</v>
@@ -3579,7 +3579,7 @@
         <v>355.4549560546875</v>
       </c>
       <c r="I98" t="n">
-        <v>2213.706298828125</v>
+        <v>2213.705810546875</v>
       </c>
       <c r="J98" t="n">
         <v>155.3500061035156</v>
@@ -3590,7 +3590,7 @@
         <v>44707</v>
       </c>
       <c r="B99" t="n">
-        <v>2169.17138671875</v>
+        <v>2169.171630859375</v>
       </c>
       <c r="C99" t="n">
         <v>2148.10009765625</v>
@@ -3608,10 +3608,10 @@
         <v>62.86000061035156</v>
       </c>
       <c r="H99" t="n">
-        <v>359.0910339355469</v>
+        <v>359.091064453125</v>
       </c>
       <c r="I99" t="n">
-        <v>2387.851318359375</v>
+        <v>2387.85107421875</v>
       </c>
       <c r="J99" t="n">
         <v>155.3000030517578</v>
@@ -3622,7 +3622,7 @@
         <v>44708</v>
       </c>
       <c r="B100" t="n">
-        <v>2159.396484375</v>
+        <v>2159.396728515625</v>
       </c>
       <c r="C100" t="n">
         <v>2186.25</v>
@@ -3666,7 +3666,7 @@
         <v>2151.64990234375</v>
       </c>
       <c r="F101" t="n">
-        <v>715.16845703125</v>
+        <v>715.1683349609375</v>
       </c>
       <c r="G101" t="n">
         <v>68.05000305175781</v>
@@ -3675,7 +3675,7 @@
         <v>365.1348876953125</v>
       </c>
       <c r="I101" t="n">
-        <v>2585.711181640625</v>
+        <v>2585.7109375</v>
       </c>
       <c r="J101" t="n">
         <v>162.3999938964844</v>
@@ -3698,16 +3698,16 @@
         <v>1888.949951171875</v>
       </c>
       <c r="F102" t="n">
-        <v>720.1815185546875</v>
+        <v>720.1814575195312</v>
       </c>
       <c r="G102" t="n">
         <v>64.65000152587891</v>
       </c>
       <c r="H102" t="n">
-        <v>363.0220336914062</v>
+        <v>363.0220031738281</v>
       </c>
       <c r="I102" t="n">
-        <v>2394.39111328125</v>
+        <v>2394.3916015625</v>
       </c>
       <c r="J102" t="n">
         <v>170.5</v>
@@ -3724,7 +3724,7 @@
         <v>1957.900024414062</v>
       </c>
       <c r="D103" t="n">
-        <v>2146.10888671875</v>
+        <v>2146.109130859375</v>
       </c>
       <c r="E103" t="n">
         <v>1848.400024414062</v>
@@ -3739,7 +3739,7 @@
         <v>365.233154296875</v>
       </c>
       <c r="I103" t="n">
-        <v>2322.496826171875</v>
+        <v>2322.49658203125</v>
       </c>
       <c r="J103" t="n">
         <v>179</v>
@@ -3768,10 +3768,10 @@
         <v>59.06999969482422</v>
       </c>
       <c r="H104" t="n">
-        <v>367.0512084960938</v>
+        <v>367.0512390136719</v>
       </c>
       <c r="I104" t="n">
-        <v>2442.271728515625</v>
+        <v>2442.271484375</v>
       </c>
       <c r="J104" t="n">
         <v>173.0500030517578</v>
@@ -3788,13 +3788,13 @@
         <v>1956.050048828125</v>
       </c>
       <c r="D105" t="n">
-        <v>2185.122314453125</v>
+        <v>2185.1220703125</v>
       </c>
       <c r="E105" t="n">
         <v>1855.900024414062</v>
       </c>
       <c r="F105" t="n">
-        <v>720.2302856445312</v>
+        <v>720.230224609375</v>
       </c>
       <c r="G105" t="n">
         <v>56.81999969482422</v>
@@ -3803,7 +3803,7 @@
         <v>360.5651550292969</v>
       </c>
       <c r="I105" t="n">
-        <v>2386.952392578125</v>
+        <v>2386.9521484375</v>
       </c>
       <c r="J105" t="n">
         <v>170</v>
@@ -3814,7 +3814,7 @@
         <v>44718</v>
       </c>
       <c r="B106" t="n">
-        <v>2100.648193359375</v>
+        <v>2100.64794921875</v>
       </c>
       <c r="C106" t="n">
         <v>2017.099975585938</v>
@@ -3826,7 +3826,7 @@
         <v>1802.349975585938</v>
       </c>
       <c r="F106" t="n">
-        <v>721.5442504882812</v>
+        <v>721.5443115234375</v>
       </c>
       <c r="G106" t="n">
         <v>59.65999984741211</v>
@@ -3835,7 +3835,7 @@
         <v>358.5997009277344</v>
       </c>
       <c r="I106" t="n">
-        <v>2476.471435546875</v>
+        <v>2476.47119140625</v>
       </c>
       <c r="J106" t="n">
         <v>178.5</v>
@@ -3852,13 +3852,13 @@
         <v>2046</v>
       </c>
       <c r="D107" t="n">
-        <v>2222.58837890625</v>
+        <v>2222.588623046875</v>
       </c>
       <c r="E107" t="n">
         <v>1829.25</v>
       </c>
       <c r="F107" t="n">
-        <v>715.0223999023438</v>
+        <v>715.0224609375</v>
       </c>
       <c r="G107" t="n">
         <v>58.27999877929688</v>
@@ -3867,7 +3867,7 @@
         <v>357.0765075683594</v>
       </c>
       <c r="I107" t="n">
-        <v>2495.29345703125</v>
+        <v>2495.293212890625</v>
       </c>
       <c r="J107" t="n">
         <v>206.5</v>
@@ -3884,22 +3884,22 @@
         <v>2091.89990234375</v>
       </c>
       <c r="D108" t="n">
-        <v>2172.3505859375</v>
+        <v>2172.350830078125</v>
       </c>
       <c r="E108" t="n">
         <v>1801.900024414062</v>
       </c>
       <c r="F108" t="n">
-        <v>709.2305297851562</v>
+        <v>709.2305908203125</v>
       </c>
       <c r="G108" t="n">
         <v>56.90000152587891</v>
       </c>
       <c r="H108" t="n">
-        <v>356.7816162109375</v>
+        <v>356.7816467285156</v>
       </c>
       <c r="I108" t="n">
-        <v>2443.768798828125</v>
+        <v>2443.769287109375</v>
       </c>
       <c r="J108" t="n">
         <v>210.6999969482422</v>
@@ -3928,10 +3928,10 @@
         <v>57.54999923706055</v>
       </c>
       <c r="H109" t="n">
-        <v>358.9927673339844</v>
+        <v>358.9927978515625</v>
       </c>
       <c r="I109" t="n">
-        <v>2494.394775390625</v>
+        <v>2494.39501953125</v>
       </c>
       <c r="J109" t="n">
         <v>204.0500030517578</v>
@@ -3942,19 +3942,19 @@
         <v>44722</v>
       </c>
       <c r="B110" t="n">
-        <v>2097.84814453125</v>
+        <v>2097.847900390625</v>
       </c>
       <c r="C110" t="n">
         <v>2051.89990234375</v>
       </c>
       <c r="D110" t="n">
-        <v>2198.193115234375</v>
+        <v>2198.19287109375</v>
       </c>
       <c r="E110" t="n">
         <v>1757.599975585938</v>
       </c>
       <c r="F110" t="n">
-        <v>707.0890502929688</v>
+        <v>707.089111328125</v>
       </c>
       <c r="G110" t="n">
         <v>56.02000045776367</v>
@@ -3963,7 +3963,7 @@
         <v>358.8453674316406</v>
       </c>
       <c r="I110" t="n">
-        <v>2394.791015625</v>
+        <v>2394.790771484375</v>
       </c>
       <c r="J110" t="n">
         <v>199.3000030517578</v>
@@ -3995,7 +3995,7 @@
         <v>356.4377136230469</v>
       </c>
       <c r="I111" t="n">
-        <v>2334.12939453125</v>
+        <v>2334.1298828125</v>
       </c>
       <c r="J111" t="n">
         <v>180</v>
@@ -4024,7 +4024,7 @@
         <v>53.33000183105469</v>
       </c>
       <c r="H112" t="n">
-        <v>353.342041015625</v>
+        <v>353.3420715332031</v>
       </c>
       <c r="I112" t="n">
         <v>2371.225341796875</v>
@@ -4038,7 +4038,7 @@
         <v>44727</v>
       </c>
       <c r="B113" t="n">
-        <v>2085.322509765625</v>
+        <v>2085.322265625</v>
       </c>
       <c r="C113" t="n">
         <v>2057.300048828125</v>
@@ -4050,7 +4050,7 @@
         <v>1757.849975585938</v>
       </c>
       <c r="F113" t="n">
-        <v>685.0411987304688</v>
+        <v>685.0411376953125</v>
       </c>
       <c r="G113" t="n">
         <v>54.40999984741211</v>
@@ -4070,13 +4070,13 @@
         <v>44728</v>
       </c>
       <c r="B114" t="n">
-        <v>2047.597900390625</v>
+        <v>2047.597778320312</v>
       </c>
       <c r="C114" t="n">
         <v>2124.64990234375</v>
       </c>
       <c r="D114" t="n">
-        <v>2078.3603515625</v>
+        <v>2078.360107421875</v>
       </c>
       <c r="E114" t="n">
         <v>1711.099975585938</v>
@@ -4088,10 +4088,10 @@
         <v>51.86000061035156</v>
       </c>
       <c r="H114" t="n">
-        <v>353.1946716308594</v>
+        <v>353.1946411132812</v>
       </c>
       <c r="I114" t="n">
-        <v>2373.022705078125</v>
+        <v>2373.0224609375</v>
       </c>
       <c r="J114" t="n">
         <v>182.8500061035156</v>
@@ -4108,7 +4108,7 @@
         <v>2032.599975585938</v>
       </c>
       <c r="D115" t="n">
-        <v>2091.1318359375</v>
+        <v>2091.132080078125</v>
       </c>
       <c r="E115" t="n">
         <v>1711.25</v>
@@ -4120,10 +4120,10 @@
         <v>52.2599983215332</v>
       </c>
       <c r="H115" t="n">
-        <v>351.1800842285156</v>
+        <v>351.1800537109375</v>
       </c>
       <c r="I115" t="n">
-        <v>2145.90576171875</v>
+        <v>2145.9052734375</v>
       </c>
       <c r="J115" t="n">
         <v>177.3999938964844</v>
@@ -4146,7 +4146,7 @@
         <v>1743.650024414062</v>
       </c>
       <c r="F116" t="n">
-        <v>645.5205688476562</v>
+        <v>645.5205078125</v>
       </c>
       <c r="G116" t="n">
         <v>49.65000152587891</v>
@@ -4155,7 +4155,7 @@
         <v>351.1309204101562</v>
       </c>
       <c r="I116" t="n">
-        <v>1986.289428710938</v>
+        <v>1986.289306640625</v>
       </c>
       <c r="J116" t="n">
         <v>162.25</v>
@@ -4166,7 +4166,7 @@
         <v>44733</v>
       </c>
       <c r="B117" t="n">
-        <v>2049.5625</v>
+        <v>2049.562744140625</v>
       </c>
       <c r="C117" t="n">
         <v>2215.050048828125</v>
@@ -4178,7 +4178,7 @@
         <v>1809.099975585938</v>
       </c>
       <c r="F117" t="n">
-        <v>670.7806396484375</v>
+        <v>670.7807006835938</v>
       </c>
       <c r="G117" t="n">
         <v>50.81000137329102</v>
@@ -4198,13 +4198,13 @@
         <v>44734</v>
       </c>
       <c r="B118" t="n">
-        <v>2026.03369140625</v>
+        <v>2026.033813476562</v>
       </c>
       <c r="C118" t="n">
         <v>2122.35009765625</v>
       </c>
       <c r="D118" t="n">
-        <v>2084.54638671875</v>
+        <v>2084.546630859375</v>
       </c>
       <c r="E118" t="n">
         <v>1736.099975585938</v>
@@ -4219,7 +4219,7 @@
         <v>351.7697143554688</v>
       </c>
       <c r="I118" t="n">
-        <v>2267.4775390625</v>
+        <v>2267.477294921875</v>
       </c>
       <c r="J118" t="n">
         <v>172.3500061035156</v>
@@ -4230,13 +4230,13 @@
         <v>44735</v>
       </c>
       <c r="B119" t="n">
-        <v>2053.6396484375</v>
+        <v>2053.639404296875</v>
       </c>
       <c r="C119" t="n">
         <v>2105</v>
       </c>
       <c r="D119" t="n">
-        <v>2105.649658203125</v>
+        <v>2105.6494140625</v>
       </c>
       <c r="E119" t="n">
         <v>1796.75</v>
@@ -4248,10 +4248,10 @@
         <v>50.52000045776367</v>
       </c>
       <c r="H119" t="n">
-        <v>352.75244140625</v>
+        <v>352.7524719238281</v>
       </c>
       <c r="I119" t="n">
-        <v>2261.336181640625</v>
+        <v>2261.33642578125</v>
       </c>
       <c r="J119" t="n">
         <v>173</v>
@@ -4280,10 +4280,10 @@
         <v>52.88999938964844</v>
       </c>
       <c r="H120" t="n">
-        <v>354.3739318847656</v>
+        <v>354.3739624023438</v>
       </c>
       <c r="I120" t="n">
-        <v>2288.2470703125</v>
+        <v>2288.247314453125</v>
       </c>
       <c r="J120" t="n">
         <v>171.8000030517578</v>
@@ -4294,7 +4294,7 @@
         <v>44739</v>
       </c>
       <c r="B121" t="n">
-        <v>2078.64208984375</v>
+        <v>2078.641845703125</v>
       </c>
       <c r="C121" t="n">
         <v>2140.550048828125</v>
@@ -4306,7 +4306,7 @@
         <v>1917.650024414062</v>
       </c>
       <c r="F121" t="n">
-        <v>669.466552734375</v>
+        <v>669.4664916992188</v>
       </c>
       <c r="G121" t="n">
         <v>54.58000183105469</v>
@@ -4315,7 +4315,7 @@
         <v>358.8453674316406</v>
       </c>
       <c r="I121" t="n">
-        <v>2286.449951171875</v>
+        <v>2286.449462890625</v>
       </c>
       <c r="J121" t="n">
         <v>175.75</v>
@@ -4332,7 +4332,7 @@
         <v>2163.39990234375</v>
       </c>
       <c r="D122" t="n">
-        <v>2199.689697265625</v>
+        <v>2199.689453125</v>
       </c>
       <c r="E122" t="n">
         <v>1909.849975585938</v>
@@ -4347,7 +4347,7 @@
         <v>360.1229553222656</v>
       </c>
       <c r="I122" t="n">
-        <v>2390.896728515625</v>
+        <v>2390.896484375</v>
       </c>
       <c r="J122" t="n">
         <v>178.3500061035156</v>
@@ -4358,7 +4358,7 @@
         <v>44741</v>
       </c>
       <c r="B123" t="n">
-        <v>2117.349365234375</v>
+        <v>2117.34912109375</v>
       </c>
       <c r="C123" t="n">
         <v>2347.89990234375</v>
@@ -4370,7 +4370,7 @@
         <v>1901.699951171875</v>
       </c>
       <c r="F123" t="n">
-        <v>659.7810668945312</v>
+        <v>659.7811279296875</v>
       </c>
       <c r="G123" t="n">
         <v>54.0099983215332</v>
@@ -4379,7 +4379,7 @@
         <v>359.1893615722656</v>
       </c>
       <c r="I123" t="n">
-        <v>2344.2646484375</v>
+        <v>2344.264892578125</v>
       </c>
       <c r="J123" t="n">
         <v>176.8999938964844</v>
@@ -4390,7 +4390,7 @@
         <v>44742</v>
       </c>
       <c r="B124" t="n">
-        <v>2084.634765625</v>
+        <v>2084.635009765625</v>
       </c>
       <c r="C124" t="n">
         <v>2473.64990234375</v>
@@ -4411,7 +4411,7 @@
         <v>356.7325134277344</v>
       </c>
       <c r="I124" t="n">
-        <v>2389.3984375</v>
+        <v>2389.398681640625</v>
       </c>
       <c r="J124" t="n">
         <v>176</v>
@@ -4422,25 +4422,25 @@
         <v>44743</v>
       </c>
       <c r="B125" t="n">
-        <v>2128.990966796875</v>
+        <v>2128.99072265625</v>
       </c>
       <c r="C125" t="n">
         <v>2400.64990234375</v>
       </c>
       <c r="D125" t="n">
-        <v>2227.22802734375</v>
+        <v>2227.228271484375</v>
       </c>
       <c r="E125" t="n">
         <v>1963.650024414062</v>
       </c>
       <c r="F125" t="n">
-        <v>659.87841796875</v>
+        <v>659.8784790039062</v>
       </c>
       <c r="G125" t="n">
         <v>52.65000152587891</v>
       </c>
       <c r="H125" t="n">
-        <v>361.2039489746094</v>
+        <v>361.2039184570312</v>
       </c>
       <c r="I125" t="n">
         <v>2385.50439453125</v>
@@ -4454,7 +4454,7 @@
         <v>44746</v>
       </c>
       <c r="B126" t="n">
-        <v>2126.534912109375</v>
+        <v>2126.53466796875</v>
       </c>
       <c r="C126" t="n">
         <v>2423.10009765625</v>
@@ -4472,10 +4472,10 @@
         <v>52.34000015258789</v>
       </c>
       <c r="H126" t="n">
-        <v>362.1866760253906</v>
+        <v>362.1867065429688</v>
       </c>
       <c r="I126" t="n">
-        <v>2393.293212890625</v>
+        <v>2393.29296875</v>
       </c>
       <c r="J126" t="n">
         <v>168.8000030517578</v>
@@ -4504,10 +4504,10 @@
         <v>52.54999923706055</v>
       </c>
       <c r="H127" t="n">
-        <v>360.3194580078125</v>
+        <v>360.3194885253906</v>
       </c>
       <c r="I127" t="n">
-        <v>2406.9228515625</v>
+        <v>2406.923095703125</v>
       </c>
       <c r="J127" t="n">
         <v>166.4499969482422</v>
@@ -4518,13 +4518,13 @@
         <v>44748</v>
       </c>
       <c r="B128" t="n">
-        <v>2136.113525390625</v>
+        <v>2136.11328125</v>
       </c>
       <c r="C128" t="n">
         <v>2511.64990234375</v>
       </c>
       <c r="D128" t="n">
-        <v>2267.787841796875</v>
+        <v>2267.78759765625</v>
       </c>
       <c r="E128" t="n">
         <v>1903.699951171875</v>
@@ -4536,10 +4536,10 @@
         <v>52.54000091552734</v>
       </c>
       <c r="H128" t="n">
-        <v>361.8918762207031</v>
+        <v>361.891845703125</v>
       </c>
       <c r="I128" t="n">
-        <v>2471.728271484375</v>
+        <v>2471.72802734375</v>
       </c>
       <c r="J128" t="n">
         <v>164.8500061035156</v>
@@ -4556,7 +4556,7 @@
         <v>2466.10009765625</v>
       </c>
       <c r="D129" t="n">
-        <v>2269.234375</v>
+        <v>2269.234130859375</v>
       </c>
       <c r="E129" t="n">
         <v>1909.699951171875</v>
@@ -4568,10 +4568,10 @@
         <v>55.11999893188477</v>
       </c>
       <c r="H129" t="n">
-        <v>360.6143493652344</v>
+        <v>360.6143188476562</v>
       </c>
       <c r="I129" t="n">
-        <v>2482.11328125</v>
+        <v>2482.11279296875</v>
       </c>
       <c r="J129" t="n">
         <v>167.4499969482422</v>
@@ -4588,7 +4588,7 @@
         <v>2545.89990234375</v>
       </c>
       <c r="D130" t="n">
-        <v>2287.942626953125</v>
+        <v>2287.9423828125</v>
       </c>
       <c r="E130" t="n">
         <v>1921</v>
@@ -4600,10 +4600,10 @@
         <v>54.31000137329102</v>
       </c>
       <c r="H130" t="n">
-        <v>362.0884399414062</v>
+        <v>362.0884094238281</v>
       </c>
       <c r="I130" t="n">
-        <v>2537.082275390625</v>
+        <v>2537.08251953125</v>
       </c>
       <c r="J130" t="n">
         <v>190.5</v>
@@ -4626,13 +4626,13 @@
         <v>2207.35009765625</v>
       </c>
       <c r="F131" t="n">
-        <v>709.8145751953125</v>
+        <v>709.8146362304688</v>
       </c>
       <c r="G131" t="n">
         <v>57.02000045776367</v>
       </c>
       <c r="H131" t="n">
-        <v>362.8255004882812</v>
+        <v>362.8254699707031</v>
       </c>
       <c r="I131" t="n">
         <v>2712.675048828125</v>
@@ -4646,13 +4646,13 @@
         <v>44754</v>
       </c>
       <c r="B132" t="n">
-        <v>2129.13818359375</v>
+        <v>2129.138427734375</v>
       </c>
       <c r="C132" t="n">
         <v>2749.800048828125</v>
       </c>
       <c r="D132" t="n">
-        <v>2360.380859375</v>
+        <v>2360.380615234375</v>
       </c>
       <c r="E132" t="n">
         <v>2294.75</v>
@@ -4667,7 +4667,7 @@
         <v>364.4961242675781</v>
       </c>
       <c r="I132" t="n">
-        <v>2793.456787109375</v>
+        <v>2793.45703125</v>
       </c>
       <c r="J132" t="n">
         <v>196.8500061035156</v>
@@ -4678,7 +4678,7 @@
         <v>44755</v>
       </c>
       <c r="B133" t="n">
-        <v>2135.32763671875</v>
+        <v>2135.327392578125</v>
       </c>
       <c r="C133" t="n">
         <v>2730.800048828125</v>
@@ -4690,7 +4690,7 @@
         <v>2104.75</v>
       </c>
       <c r="F133" t="n">
-        <v>707.4297485351562</v>
+        <v>707.4298095703125</v>
       </c>
       <c r="G133" t="n">
         <v>57.33000183105469</v>
@@ -4699,7 +4699,7 @@
         <v>364.7909240722656</v>
       </c>
       <c r="I133" t="n">
-        <v>2668.190185546875</v>
+        <v>2668.1904296875</v>
       </c>
       <c r="J133" t="n">
         <v>201.6000061035156</v>
@@ -4710,13 +4710,13 @@
         <v>44756</v>
       </c>
       <c r="B134" t="n">
-        <v>2122.310546875</v>
+        <v>2122.310302734375</v>
       </c>
       <c r="C134" t="n">
         <v>2889.14990234375</v>
       </c>
       <c r="D134" t="n">
-        <v>2378.771728515625</v>
+        <v>2378.77197265625</v>
       </c>
       <c r="E134" t="n">
         <v>2087</v>
@@ -4754,16 +4754,16 @@
         <v>2072.64990234375</v>
       </c>
       <c r="F135" t="n">
-        <v>716.398193359375</v>
+        <v>716.3981323242188</v>
       </c>
       <c r="G135" t="n">
         <v>57.34999847412109</v>
       </c>
       <c r="H135" t="n">
-        <v>362.7763671875</v>
+        <v>362.7763366699219</v>
       </c>
       <c r="I135" t="n">
-        <v>2803.854248046875</v>
+        <v>2803.85400390625</v>
       </c>
       <c r="J135" t="n">
         <v>187.6999969482422</v>
@@ -4774,13 +4774,13 @@
         <v>44760</v>
       </c>
       <c r="B136" t="n">
-        <v>2135.769775390625</v>
+        <v>2135.76953125</v>
       </c>
       <c r="C136" t="n">
         <v>2980.5</v>
       </c>
       <c r="D136" t="n">
-        <v>2419.1982421875</v>
+        <v>2419.198486328125</v>
       </c>
       <c r="E136" t="n">
         <v>2093.25</v>
@@ -4795,7 +4795,7 @@
         <v>364.2995910644531</v>
       </c>
       <c r="I136" t="n">
-        <v>2828.919677734375</v>
+        <v>2828.919921875</v>
       </c>
       <c r="J136" t="n">
         <v>192.5</v>
@@ -4806,19 +4806,19 @@
         <v>44761</v>
       </c>
       <c r="B137" t="n">
-        <v>2130.6611328125</v>
+        <v>2130.660888671875</v>
       </c>
       <c r="C137" t="n">
         <v>3029.75</v>
       </c>
       <c r="D137" t="n">
-        <v>2446.847900390625</v>
+        <v>2446.84814453125</v>
       </c>
       <c r="E137" t="n">
         <v>2109</v>
       </c>
       <c r="F137" t="n">
-        <v>734.1390991210938</v>
+        <v>734.1390380859375</v>
       </c>
       <c r="G137" t="n">
         <v>58.66999816894531</v>
@@ -4844,7 +4844,7 @@
         <v>3018.75</v>
       </c>
       <c r="D138" t="n">
-        <v>2446.648681640625</v>
+        <v>2446.6484375</v>
       </c>
       <c r="E138" t="n">
         <v>2084.300048828125</v>
@@ -4859,7 +4859,7 @@
         <v>361.498779296875</v>
       </c>
       <c r="I138" t="n">
-        <v>2776.14208984375</v>
+        <v>2776.141845703125</v>
       </c>
       <c r="J138" t="n">
         <v>242.5</v>
@@ -4870,28 +4870,28 @@
         <v>44763</v>
       </c>
       <c r="B139" t="n">
-        <v>2136.3095703125</v>
+        <v>2136.31005859375</v>
       </c>
       <c r="C139" t="n">
         <v>3043.75</v>
       </c>
       <c r="D139" t="n">
-        <v>2490.968017578125</v>
+        <v>2490.9677734375</v>
       </c>
       <c r="E139" t="n">
         <v>2109.75</v>
       </c>
       <c r="F139" t="n">
-        <v>739.2849731445312</v>
+        <v>739.284912109375</v>
       </c>
       <c r="G139" t="n">
         <v>58.79999923706055</v>
       </c>
       <c r="H139" t="n">
-        <v>364.3487243652344</v>
+        <v>364.3486938476562</v>
       </c>
       <c r="I139" t="n">
-        <v>2872.66015625</v>
+        <v>2872.659912109375</v>
       </c>
       <c r="J139" t="n">
         <v>230.4499969482422</v>
@@ -4902,25 +4902,25 @@
         <v>44764</v>
       </c>
       <c r="B140" t="n">
-        <v>2153.403564453125</v>
+        <v>2153.40380859375</v>
       </c>
       <c r="C140" t="n">
         <v>2977.449951171875</v>
       </c>
       <c r="D140" t="n">
-        <v>2494.860595703125</v>
+        <v>2494.8603515625</v>
       </c>
       <c r="E140" t="n">
         <v>2120.449951171875</v>
       </c>
       <c r="F140" t="n">
-        <v>739.2849731445312</v>
+        <v>739.284912109375</v>
       </c>
       <c r="G140" t="n">
         <v>58.2599983215332</v>
       </c>
       <c r="H140" t="n">
-        <v>366.1176147460938</v>
+        <v>366.1175842285156</v>
       </c>
       <c r="I140" t="n">
         <v>2870.262939453125</v>
@@ -4934,28 +4934,28 @@
         <v>44767</v>
       </c>
       <c r="B141" t="n">
-        <v>2165.68408203125</v>
+        <v>2165.683837890625</v>
       </c>
       <c r="C141" t="n">
         <v>2969.75</v>
       </c>
       <c r="D141" t="n">
-        <v>2545.968017578125</v>
+        <v>2545.9677734375</v>
       </c>
       <c r="E141" t="n">
         <v>2137.60009765625</v>
       </c>
       <c r="F141" t="n">
-        <v>735.0702514648438</v>
+        <v>735.0703125</v>
       </c>
       <c r="G141" t="n">
         <v>58.34000015258789</v>
       </c>
       <c r="H141" t="n">
-        <v>364.7417907714844</v>
+        <v>364.7417602539062</v>
       </c>
       <c r="I141" t="n">
-        <v>2874.906494140625</v>
+        <v>2874.90673828125</v>
       </c>
       <c r="J141" t="n">
         <v>273.0499877929688</v>
@@ -4972,7 +4972,7 @@
         <v>2993.75</v>
       </c>
       <c r="D142" t="n">
-        <v>2555.05078125</v>
+        <v>2555.051025390625</v>
       </c>
       <c r="E142" t="n">
         <v>2103.64990234375</v>
@@ -4984,7 +4984,7 @@
         <v>59.54000091552734</v>
       </c>
       <c r="H142" t="n">
-        <v>363.5625305175781</v>
+        <v>363.5625610351562</v>
       </c>
       <c r="I142" t="n">
         <v>2894.230224609375</v>
@@ -5016,7 +5016,7 @@
         <v>62.4900016784668</v>
       </c>
       <c r="H143" t="n">
-        <v>364.4469909667969</v>
+        <v>364.4469604492188</v>
       </c>
       <c r="I143" t="n">
         <v>2956.04541015625</v>
@@ -5030,7 +5030,7 @@
         <v>44770</v>
       </c>
       <c r="B144" t="n">
-        <v>2142.40087890625</v>
+        <v>2142.400634765625</v>
       </c>
       <c r="C144" t="n">
         <v>3012.64990234375</v>
@@ -5048,7 +5048,7 @@
         <v>64.38999938964844</v>
       </c>
       <c r="H144" t="n">
-        <v>364.4469909667969</v>
+        <v>364.4469604492188</v>
       </c>
       <c r="I144" t="n">
         <v>3001.78271484375</v>
@@ -5074,13 +5074,13 @@
         <v>2174.699951171875</v>
       </c>
       <c r="F145" t="n">
-        <v>748.54736328125</v>
+        <v>748.5474243164062</v>
       </c>
       <c r="G145" t="n">
         <v>62.79000091552734</v>
       </c>
       <c r="H145" t="n">
-        <v>368.3287353515625</v>
+        <v>368.3287658691406</v>
       </c>
       <c r="I145" t="n">
         <v>3122.91650390625</v>
@@ -5094,13 +5094,13 @@
         <v>44774</v>
       </c>
       <c r="B146" t="n">
-        <v>2187.395751953125</v>
+        <v>2187.395263671875</v>
       </c>
       <c r="C146" t="n">
         <v>3261.75</v>
       </c>
       <c r="D146" t="n">
-        <v>2655.31884765625</v>
+        <v>2655.318603515625</v>
       </c>
       <c r="E146" t="n">
         <v>2273.699951171875</v>
@@ -5138,7 +5138,7 @@
         <v>2296.14990234375</v>
       </c>
       <c r="F147" t="n">
-        <v>786.381591796875</v>
+        <v>786.3815307617188</v>
       </c>
       <c r="G147" t="n">
         <v>65.70999908447266</v>
@@ -5164,13 +5164,13 @@
         <v>3505.35009765625</v>
       </c>
       <c r="D148" t="n">
-        <v>2706.475830078125</v>
+        <v>2706.4755859375</v>
       </c>
       <c r="E148" t="n">
         <v>2204.60009765625</v>
       </c>
       <c r="F148" t="n">
-        <v>791.184326171875</v>
+        <v>791.1843872070312</v>
       </c>
       <c r="G148" t="n">
         <v>67.91999816894531</v>
@@ -5202,13 +5202,13 @@
         <v>2190.949951171875</v>
       </c>
       <c r="F149" t="n">
-        <v>791.2333984375</v>
+        <v>791.2333374023438</v>
       </c>
       <c r="G149" t="n">
         <v>69.44999694824219</v>
       </c>
       <c r="H149" t="n">
-        <v>374.6674194335938</v>
+        <v>374.6673889160156</v>
       </c>
       <c r="I149" t="n">
         <v>3345.061767578125</v>
@@ -5234,7 +5234,7 @@
         <v>2106.199951171875</v>
       </c>
       <c r="F150" t="n">
-        <v>794.1737670898438</v>
+        <v>794.173828125</v>
       </c>
       <c r="G150" t="n">
         <v>66.41000366210938</v>
@@ -5243,7 +5243,7 @@
         <v>376.0432434082031</v>
       </c>
       <c r="I150" t="n">
-        <v>3342.814697265625</v>
+        <v>3342.81494140625</v>
       </c>
       <c r="J150" t="n">
         <v>298.7999877929688</v>
@@ -5272,7 +5272,7 @@
         <v>65.72000122070312</v>
       </c>
       <c r="H151" t="n">
-        <v>373.6355590820312</v>
+        <v>373.6355285644531</v>
       </c>
       <c r="I151" t="n">
         <v>3360.39111328125</v>
@@ -5336,7 +5336,7 @@
         <v>68.48000335693359</v>
       </c>
       <c r="H153" t="n">
-        <v>373.6355590820312</v>
+        <v>373.6355285644531</v>
       </c>
       <c r="I153" t="n">
         <v>3347.708251953125</v>
@@ -5368,7 +5368,7 @@
         <v>69.02999877929688</v>
       </c>
       <c r="H154" t="n">
-        <v>378.1560974121094</v>
+        <v>378.1561279296875</v>
       </c>
       <c r="I154" t="n">
         <v>3420.7080078125</v>
@@ -5382,7 +5382,7 @@
         <v>44789</v>
       </c>
       <c r="B155" t="n">
-        <v>2231.407470703125</v>
+        <v>2231.4072265625</v>
       </c>
       <c r="C155" t="n">
         <v>3581.60009765625</v>
@@ -5400,7 +5400,7 @@
         <v>72.47000122070312</v>
       </c>
       <c r="H155" t="n">
-        <v>389.2610168457031</v>
+        <v>389.2610473632812</v>
       </c>
       <c r="I155" t="n">
         <v>3484.920166015625</v>
@@ -5414,7 +5414,7 @@
         <v>44790</v>
       </c>
       <c r="B156" t="n">
-        <v>2243</v>
+        <v>2242.999755859375</v>
       </c>
       <c r="C156" t="n">
         <v>3597.64990234375</v>
@@ -5432,7 +5432,7 @@
         <v>76.08999633789062</v>
       </c>
       <c r="H156" t="n">
-        <v>391.4230041503906</v>
+        <v>391.4230346679688</v>
       </c>
       <c r="I156" t="n">
         <v>3467.094482421875</v>
@@ -5464,7 +5464,7 @@
         <v>79.88999938964844</v>
       </c>
       <c r="H157" t="n">
-        <v>402.5279235839844</v>
+        <v>402.5279541015625</v>
       </c>
       <c r="I157" t="n">
         <v>3458.556396484375</v>
@@ -5478,13 +5478,13 @@
         <v>44792</v>
       </c>
       <c r="B158" t="n">
-        <v>2309.509521484375</v>
+        <v>2309.509765625</v>
       </c>
       <c r="C158" t="n">
         <v>3635.25</v>
       </c>
       <c r="D158" t="n">
-        <v>3124.514892578125</v>
+        <v>3124.51513671875</v>
       </c>
       <c r="E158" t="n">
         <v>2411.35009765625</v>
@@ -5496,7 +5496,7 @@
         <v>82.38999938964844</v>
       </c>
       <c r="H158" t="n">
-        <v>413.1906127929688</v>
+        <v>413.1905822753906</v>
       </c>
       <c r="I158" t="n">
         <v>3386.25537109375</v>
@@ -5510,7 +5510,7 @@
         <v>44795</v>
       </c>
       <c r="B159" t="n">
-        <v>2242.80322265625</v>
+        <v>2242.803466796875</v>
       </c>
       <c r="C159" t="n">
         <v>3486.39990234375</v>
@@ -5522,7 +5522,7 @@
         <v>2519.75</v>
       </c>
       <c r="F159" t="n">
-        <v>823.57861328125</v>
+        <v>823.5786743164062</v>
       </c>
       <c r="G159" t="n">
         <v>86.5</v>
@@ -5542,7 +5542,7 @@
         <v>44796</v>
       </c>
       <c r="B160" t="n">
-        <v>2255.673095703125</v>
+        <v>2255.67333984375</v>
       </c>
       <c r="C160" t="n">
         <v>3601.89990234375</v>
@@ -5554,7 +5554,7 @@
         <v>2412.89990234375</v>
       </c>
       <c r="F160" t="n">
-        <v>815.9823608398438</v>
+        <v>815.9822998046875</v>
       </c>
       <c r="G160" t="n">
         <v>82.18000030517578</v>
@@ -5574,13 +5574,13 @@
         <v>44797</v>
       </c>
       <c r="B161" t="n">
-        <v>2261.174560546875</v>
+        <v>2261.1748046875</v>
       </c>
       <c r="C161" t="n">
         <v>3700.39990234375</v>
       </c>
       <c r="D161" t="n">
-        <v>3128.956787109375</v>
+        <v>3128.95703125</v>
       </c>
       <c r="E161" t="n">
         <v>2358.85009765625</v>
@@ -5618,7 +5618,7 @@
         <v>2368.300048828125</v>
       </c>
       <c r="F162" t="n">
-        <v>799.8097534179688</v>
+        <v>799.8096923828125</v>
       </c>
       <c r="G162" t="n">
         <v>78.69999694824219</v>
@@ -5638,19 +5638,19 @@
         <v>44799</v>
       </c>
       <c r="B163" t="n">
-        <v>2245.308837890625</v>
+        <v>2245.30859375</v>
       </c>
       <c r="C163" t="n">
         <v>3751.199951171875</v>
       </c>
       <c r="D163" t="n">
-        <v>3133.847900390625</v>
+        <v>3133.84814453125</v>
       </c>
       <c r="E163" t="n">
         <v>2392.75</v>
       </c>
       <c r="F163" t="n">
-        <v>821.0791625976562</v>
+        <v>821.0792236328125</v>
       </c>
       <c r="G163" t="n">
         <v>75.09999847412109</v>
@@ -5682,7 +5682,7 @@
         <v>2337.85009765625</v>
       </c>
       <c r="F164" t="n">
-        <v>819.8049926757812</v>
+        <v>819.804931640625</v>
       </c>
       <c r="G164" t="n">
         <v>78.84999847412109</v>
@@ -5702,7 +5702,7 @@
         <v>44803</v>
       </c>
       <c r="B165" t="n">
-        <v>2259.2587890625</v>
+        <v>2259.259033203125</v>
       </c>
       <c r="C165" t="n">
         <v>3960.699951171875</v>
@@ -5723,7 +5723,7 @@
         <v>404.1494140625</v>
       </c>
       <c r="I165" t="n">
-        <v>3739.8203125</v>
+        <v>3739.820556640625</v>
       </c>
       <c r="J165" t="n">
         <v>471.5</v>
@@ -5766,7 +5766,7 @@
         <v>44806</v>
       </c>
       <c r="B167" t="n">
-        <v>2249.778564453125</v>
+        <v>2249.77880859375</v>
       </c>
       <c r="C167" t="n">
         <v>3866.550048828125</v>
@@ -5778,13 +5778,13 @@
         <v>2383.10009765625</v>
       </c>
       <c r="F167" t="n">
-        <v>835.0465087890625</v>
+        <v>835.0464477539062</v>
       </c>
       <c r="G167" t="n">
         <v>80.25</v>
       </c>
       <c r="H167" t="n">
-        <v>408.4243469238281</v>
+        <v>408.42431640625</v>
       </c>
       <c r="I167" t="n">
         <v>3617.887939453125</v>
@@ -5816,7 +5816,7 @@
         <v>77.97000122070312</v>
       </c>
       <c r="H168" t="n">
-        <v>410.7337951660156</v>
+        <v>410.7337646484375</v>
       </c>
       <c r="I168" t="n">
         <v>3525.763916015625</v>
@@ -5830,7 +5830,7 @@
         <v>44810</v>
       </c>
       <c r="B169" t="n">
-        <v>2288.97705078125</v>
+        <v>2288.976806640625</v>
       </c>
       <c r="C169" t="n">
         <v>3964.050048828125</v>
@@ -5848,7 +5848,7 @@
         <v>81.55000305175781</v>
       </c>
       <c r="H169" t="n">
-        <v>428.9634399414062</v>
+        <v>428.9634704589844</v>
       </c>
       <c r="I169" t="n">
         <v>3677.8056640625</v>
@@ -5862,7 +5862,7 @@
         <v>44811</v>
       </c>
       <c r="B170" t="n">
-        <v>2363.05126953125</v>
+        <v>2363.051025390625</v>
       </c>
       <c r="C170" t="n">
         <v>3893.10009765625</v>
@@ -5894,13 +5894,13 @@
         <v>44812</v>
       </c>
       <c r="B171" t="n">
-        <v>2378.572998046875</v>
+        <v>2378.5732421875</v>
       </c>
       <c r="C171" t="n">
         <v>3925.949951171875</v>
       </c>
       <c r="D171" t="n">
-        <v>3456.51123046875</v>
+        <v>3456.510986328125</v>
       </c>
       <c r="E171" t="n">
         <v>2334.050048828125</v>
@@ -5912,10 +5912,10 @@
         <v>80.37999725341797</v>
       </c>
       <c r="H171" t="n">
-        <v>453.9249267578125</v>
+        <v>453.9248962402344</v>
       </c>
       <c r="I171" t="n">
-        <v>3624.927734375</v>
+        <v>3624.927978515625</v>
       </c>
       <c r="J171" t="n">
         <v>468</v>
@@ -5926,13 +5926,13 @@
         <v>44813</v>
       </c>
       <c r="B172" t="n">
-        <v>2324.000244140625</v>
+        <v>2324</v>
       </c>
       <c r="C172" t="n">
         <v>3931.10009765625</v>
       </c>
       <c r="D172" t="n">
-        <v>3444.93212890625</v>
+        <v>3444.931884765625</v>
       </c>
       <c r="E172" t="n">
         <v>2315.89990234375</v>
@@ -5990,7 +5990,7 @@
         <v>44817</v>
       </c>
       <c r="B174" t="n">
-        <v>2527.556640625</v>
+        <v>2527.556396484375</v>
       </c>
       <c r="C174" t="n">
         <v>4037.050048828125</v>
@@ -6028,7 +6028,7 @@
         <v>3978.14990234375</v>
       </c>
       <c r="D175" t="n">
-        <v>3565.612548828125</v>
+        <v>3565.61279296875</v>
       </c>
       <c r="E175" t="n">
         <v>2293.60009765625</v>
@@ -6040,7 +6040,7 @@
         <v>76.91000366210938</v>
       </c>
       <c r="H175" t="n">
-        <v>515.5422973632812</v>
+        <v>515.5423583984375</v>
       </c>
       <c r="I175" t="n">
         <v>3559.517578125</v>
@@ -6072,7 +6072,7 @@
         <v>79.83999633789062</v>
       </c>
       <c r="H176" t="n">
-        <v>529.447998046875</v>
+        <v>529.4480590820312</v>
       </c>
       <c r="I176" t="n">
         <v>3596.417236328125</v>
@@ -6086,13 +6086,13 @@
         <v>44820</v>
       </c>
       <c r="B177" t="n">
-        <v>2565.576171875</v>
+        <v>2565.575927734375</v>
       </c>
       <c r="C177" t="n">
         <v>4094.75</v>
       </c>
       <c r="D177" t="n">
-        <v>3695.476318359375</v>
+        <v>3695.47607421875</v>
       </c>
       <c r="E177" t="n">
         <v>2316.60009765625</v>
@@ -6104,7 +6104,7 @@
         <v>77.55000305175781</v>
       </c>
       <c r="H177" t="n">
-        <v>507.7787780761719</v>
+        <v>507.7787475585938</v>
       </c>
       <c r="I177" t="n">
         <v>3523.96630859375</v>
@@ -6118,13 +6118,13 @@
         <v>44823</v>
       </c>
       <c r="B178" t="n">
-        <v>2594.655517578125</v>
+        <v>2594.6552734375</v>
       </c>
       <c r="C178" t="n">
         <v>4029.39990234375</v>
       </c>
       <c r="D178" t="n">
-        <v>3771.787109375</v>
+        <v>3771.787353515625</v>
       </c>
       <c r="E178" t="n">
         <v>2346.35009765625</v>
@@ -6136,10 +6136,10 @@
         <v>78.37000274658203</v>
       </c>
       <c r="H178" t="n">
-        <v>555.146484375</v>
+        <v>555.1465454101562</v>
       </c>
       <c r="I178" t="n">
-        <v>3615.091552734375</v>
+        <v>3615.091796875</v>
       </c>
       <c r="J178" t="n">
         <v>442.25</v>
@@ -6168,7 +6168,7 @@
         <v>79.65000152587891</v>
       </c>
       <c r="H179" t="n">
-        <v>564.4332885742188</v>
+        <v>564.433349609375</v>
       </c>
       <c r="I179" t="n">
         <v>3669.916259765625</v>
@@ -6203,7 +6203,7 @@
         <v>532.0031127929688</v>
       </c>
       <c r="I180" t="n">
-        <v>3560.6162109375</v>
+        <v>3560.616455078125</v>
       </c>
       <c r="J180" t="n">
         <v>421.2000122070312</v>
@@ -6214,7 +6214,7 @@
         <v>44826</v>
       </c>
       <c r="B181" t="n">
-        <v>2510.757080078125</v>
+        <v>2510.75732421875</v>
       </c>
       <c r="C181" t="n">
         <v>3997.89990234375</v>
@@ -6232,10 +6232,10 @@
         <v>79.25</v>
       </c>
       <c r="H181" t="n">
-        <v>524.8291625976562</v>
+        <v>524.8292236328125</v>
       </c>
       <c r="I181" t="n">
-        <v>3624.927734375</v>
+        <v>3624.927978515625</v>
       </c>
       <c r="J181" t="n">
         <v>408.4500122070312</v>
@@ -6258,16 +6258,16 @@
         <v>2323.85009765625</v>
       </c>
       <c r="F182" t="n">
-        <v>895.6692504882812</v>
+        <v>895.669189453125</v>
       </c>
       <c r="G182" t="n">
         <v>77.12000274658203</v>
       </c>
       <c r="H182" t="n">
-        <v>530.0377197265625</v>
+        <v>530.03759765625</v>
       </c>
       <c r="I182" t="n">
-        <v>3540.39404296875</v>
+        <v>3540.393798828125</v>
       </c>
       <c r="J182" t="n">
         <v>388.0499877929688</v>
@@ -6278,7 +6278,7 @@
         <v>44830</v>
       </c>
       <c r="B183" t="n">
-        <v>2336.427734375</v>
+        <v>2336.427490234375</v>
       </c>
       <c r="C183" t="n">
         <v>3713</v>
@@ -6290,16 +6290,16 @@
         <v>2210.35009765625</v>
       </c>
       <c r="F183" t="n">
-        <v>846.269287109375</v>
+        <v>846.2693481445312</v>
       </c>
       <c r="G183" t="n">
         <v>73.30000305175781</v>
       </c>
       <c r="H183" t="n">
-        <v>502.3737182617188</v>
+        <v>502.3737487792969</v>
       </c>
       <c r="I183" t="n">
-        <v>3366.4326171875</v>
+        <v>3366.432373046875</v>
       </c>
       <c r="J183" t="n">
         <v>368.6499938964844</v>
@@ -6348,7 +6348,7 @@
         <v>3602.10009765625</v>
       </c>
       <c r="D185" t="n">
-        <v>3542.304931640625</v>
+        <v>3542.3046875</v>
       </c>
       <c r="E185" t="n">
         <v>2051.050048828125</v>
@@ -6360,10 +6360,10 @@
         <v>73.55000305175781</v>
       </c>
       <c r="H185" t="n">
-        <v>491.416259765625</v>
+        <v>491.4162292480469</v>
       </c>
       <c r="I185" t="n">
-        <v>3443.327392578125</v>
+        <v>3443.3271484375</v>
       </c>
       <c r="J185" t="n">
         <v>367.75</v>
@@ -6406,7 +6406,7 @@
         <v>44834</v>
       </c>
       <c r="B187" t="n">
-        <v>2373.169921875</v>
+        <v>2373.169677734375</v>
       </c>
       <c r="C187" t="n">
         <v>3289.800048828125</v>
@@ -6424,7 +6424,7 @@
         <v>74.69999694824219</v>
       </c>
       <c r="H187" t="n">
-        <v>506.6977233886719</v>
+        <v>506.6976928710938</v>
       </c>
       <c r="I187" t="n">
         <v>3335.275390625</v>
@@ -6438,13 +6438,13 @@
         <v>44837</v>
       </c>
       <c r="B188" t="n">
-        <v>2260.830810546875</v>
+        <v>2260.8310546875</v>
       </c>
       <c r="C188" t="n">
         <v>3123.64990234375</v>
       </c>
       <c r="D188" t="n">
-        <v>3151.56591796875</v>
+        <v>3151.566162109375</v>
       </c>
       <c r="E188" t="n">
         <v>2074.050048828125</v>
@@ -6470,13 +6470,13 @@
         <v>44838</v>
       </c>
       <c r="B189" t="n">
-        <v>2318.15478515625</v>
+        <v>2318.154541015625</v>
       </c>
       <c r="C189" t="n">
         <v>3318.60009765625</v>
       </c>
       <c r="D189" t="n">
-        <v>3231.819580078125</v>
+        <v>3231.81982421875</v>
       </c>
       <c r="E189" t="n">
         <v>2134.199951171875</v>
@@ -6491,7 +6491,7 @@
         <v>483.7017822265625</v>
       </c>
       <c r="I189" t="n">
-        <v>3211.74462890625</v>
+        <v>3211.744873046875</v>
       </c>
       <c r="J189" t="n">
         <v>341.6499938964844</v>
@@ -6540,7 +6540,7 @@
         <v>3278.60009765625</v>
       </c>
       <c r="D191" t="n">
-        <v>3271.6474609375</v>
+        <v>3271.647216796875</v>
       </c>
       <c r="E191" t="n">
         <v>2204.14990234375</v>
@@ -6552,10 +6552,10 @@
         <v>74.56999969482422</v>
       </c>
       <c r="H191" t="n">
-        <v>512.7906494140625</v>
+        <v>512.7907104492188</v>
       </c>
       <c r="I191" t="n">
-        <v>3183.233642578125</v>
+        <v>3183.23388671875</v>
       </c>
       <c r="J191" t="n">
         <v>349.8500061035156</v>
@@ -6566,7 +6566,7 @@
         <v>44844</v>
       </c>
       <c r="B192" t="n">
-        <v>2327.586181640625</v>
+        <v>2327.585693359375</v>
       </c>
       <c r="C192" t="n">
         <v>3191.449951171875</v>
@@ -6578,16 +6578,16 @@
         <v>2155.89990234375</v>
       </c>
       <c r="F192" t="n">
-        <v>792.06640625</v>
+        <v>792.0663452148438</v>
       </c>
       <c r="G192" t="n">
         <v>73.06999969482422</v>
       </c>
       <c r="H192" t="n">
-        <v>513.6260986328125</v>
+        <v>513.6260375976562</v>
       </c>
       <c r="I192" t="n">
-        <v>3156.670166015625</v>
+        <v>3156.67041015625</v>
       </c>
       <c r="J192" t="n">
         <v>340.8999938964844</v>
@@ -6619,7 +6619,7 @@
         <v>491.5636596679688</v>
       </c>
       <c r="I193" t="n">
-        <v>3169.253173828125</v>
+        <v>3169.25341796875</v>
       </c>
       <c r="J193" t="n">
         <v>337.3500061035156</v>
@@ -6630,13 +6630,13 @@
         <v>44846</v>
       </c>
       <c r="B194" t="n">
-        <v>2276.05810546875</v>
+        <v>2276.058349609375</v>
       </c>
       <c r="C194" t="n">
         <v>3187.949951171875</v>
       </c>
       <c r="D194" t="n">
-        <v>3217.795166015625</v>
+        <v>3217.794921875</v>
       </c>
       <c r="E194" t="n">
         <v>2099.10009765625</v>
@@ -6651,7 +6651,7 @@
         <v>496.7230224609375</v>
       </c>
       <c r="I194" t="n">
-        <v>3198.462890625</v>
+        <v>3198.463134765625</v>
       </c>
       <c r="J194" t="n">
         <v>341</v>
@@ -6674,7 +6674,7 @@
         <v>2083.35009765625</v>
       </c>
       <c r="F195" t="n">
-        <v>769.1798095703125</v>
+        <v>769.1797485351562</v>
       </c>
       <c r="G195" t="n">
         <v>69.37000274658203</v>
@@ -6683,7 +6683,7 @@
         <v>488.271484375</v>
       </c>
       <c r="I195" t="n">
-        <v>3172.998046875</v>
+        <v>3172.997802734375</v>
       </c>
       <c r="J195" t="n">
         <v>335.5499877929688</v>
@@ -6694,13 +6694,13 @@
         <v>44848</v>
       </c>
       <c r="B196" t="n">
-        <v>2204.1943359375</v>
+        <v>2204.19482421875</v>
       </c>
       <c r="C196" t="n">
         <v>3035.300048828125</v>
       </c>
       <c r="D196" t="n">
-        <v>3203.671142578125</v>
+        <v>3203.6708984375</v>
       </c>
       <c r="E196" t="n">
         <v>2033.150024414062</v>
@@ -6715,7 +6715,7 @@
         <v>493.1851806640625</v>
       </c>
       <c r="I196" t="n">
-        <v>3042.97607421875</v>
+        <v>3042.975830078125</v>
       </c>
       <c r="J196" t="n">
         <v>329.3500061035156</v>
@@ -6732,7 +6732,7 @@
         <v>3074.35009765625</v>
       </c>
       <c r="D197" t="n">
-        <v>3206.76513671875</v>
+        <v>3206.765380859375</v>
       </c>
       <c r="E197" t="n">
         <v>2154.449951171875</v>
@@ -6744,7 +6744,7 @@
         <v>68.12999725341797</v>
       </c>
       <c r="H197" t="n">
-        <v>511.562255859375</v>
+        <v>511.5622863769531</v>
       </c>
       <c r="I197" t="n">
         <v>3095.054931640625</v>
@@ -6758,7 +6758,7 @@
         <v>44852</v>
       </c>
       <c r="B198" t="n">
-        <v>2180.223876953125</v>
+        <v>2180.2236328125</v>
       </c>
       <c r="C198" t="n">
         <v>3243</v>
@@ -6808,7 +6808,7 @@
         <v>66.72000122070312</v>
       </c>
       <c r="H199" t="n">
-        <v>501.8823547363281</v>
+        <v>501.8823852539062</v>
       </c>
       <c r="I199" t="n">
         <v>3162.512451171875</v>
@@ -6828,13 +6828,13 @@
         <v>3270.050048828125</v>
       </c>
       <c r="D200" t="n">
-        <v>3351.0029296875</v>
+        <v>3351.003173828125</v>
       </c>
       <c r="E200" t="n">
         <v>2138.89990234375</v>
       </c>
       <c r="F200" t="n">
-        <v>803.7793579101562</v>
+        <v>803.7794189453125</v>
       </c>
       <c r="G200" t="n">
         <v>67.69000244140625</v>
@@ -6843,7 +6843,7 @@
         <v>508.761474609375</v>
       </c>
       <c r="I200" t="n">
-        <v>3272.611328125</v>
+        <v>3272.611572265625</v>
       </c>
       <c r="J200" t="n">
         <v>325.7999877929688</v>
@@ -6854,13 +6854,13 @@
         <v>44855</v>
       </c>
       <c r="B201" t="n">
-        <v>2216.86767578125</v>
+        <v>2216.867919921875</v>
       </c>
       <c r="C201" t="n">
         <v>3273.699951171875</v>
       </c>
       <c r="D201" t="n">
-        <v>3305.885009765625</v>
+        <v>3305.884765625</v>
       </c>
       <c r="E201" t="n">
         <v>2105.300048828125</v>
@@ -6875,7 +6875,7 @@
         <v>503.7495422363281</v>
       </c>
       <c r="I201" t="n">
-        <v>3257.2822265625</v>
+        <v>3257.282470703125</v>
       </c>
       <c r="J201" t="n">
         <v>323.25</v>
@@ -6892,13 +6892,13 @@
         <v>3283.949951171875</v>
       </c>
       <c r="D202" t="n">
-        <v>3303.7890625</v>
+        <v>3303.789306640625</v>
       </c>
       <c r="E202" t="n">
         <v>2121.25</v>
       </c>
       <c r="F202" t="n">
-        <v>789.5181274414062</v>
+        <v>789.51806640625</v>
       </c>
       <c r="G202" t="n">
         <v>67.11000061035156</v>
@@ -6939,7 +6939,7 @@
         <v>504.2409057617188</v>
       </c>
       <c r="I203" t="n">
-        <v>3378.316162109375</v>
+        <v>3378.31591796875</v>
       </c>
       <c r="J203" t="n">
         <v>323.8500061035156</v>
@@ -6950,13 +6950,13 @@
         <v>44861</v>
       </c>
       <c r="B204" t="n">
-        <v>2272.324951171875</v>
+        <v>2272.3251953125</v>
       </c>
       <c r="C204" t="n">
         <v>3282.449951171875</v>
       </c>
       <c r="D204" t="n">
-        <v>3318.961181640625</v>
+        <v>3318.96142578125</v>
       </c>
       <c r="E204" t="n">
         <v>2117.60009765625</v>
@@ -6968,7 +6968,7 @@
         <v>67.48000335693359</v>
       </c>
       <c r="H204" t="n">
-        <v>518.4906005859375</v>
+        <v>518.4905395507812</v>
       </c>
       <c r="I204" t="n">
         <v>3502.945068359375</v>
@@ -7000,7 +7000,7 @@
         <v>66.66000366210938</v>
       </c>
       <c r="H205" t="n">
-        <v>511.1201171875</v>
+        <v>511.1200561523438</v>
       </c>
       <c r="I205" t="n">
         <v>3439.33251953125</v>
@@ -7032,7 +7032,7 @@
         <v>66.98000335693359</v>
       </c>
       <c r="H206" t="n">
-        <v>523.7482299804688</v>
+        <v>523.7481689453125</v>
       </c>
       <c r="I206" t="n">
         <v>3597.9150390625</v>
@@ -7046,13 +7046,13 @@
         <v>44866</v>
       </c>
       <c r="B207" t="n">
-        <v>2385.35205078125</v>
+        <v>2385.351806640625</v>
       </c>
       <c r="C207" t="n">
         <v>3342.449951171875</v>
       </c>
       <c r="D207" t="n">
-        <v>3569.205810546875</v>
+        <v>3569.2060546875</v>
       </c>
       <c r="E207" t="n">
         <v>2121.25</v>
@@ -7067,7 +7067,7 @@
         <v>534.6565551757812</v>
       </c>
       <c r="I207" t="n">
-        <v>3676.15771484375</v>
+        <v>3676.157958984375</v>
       </c>
       <c r="J207" t="n">
         <v>318</v>
@@ -7110,13 +7110,13 @@
         <v>44868</v>
       </c>
       <c r="B209" t="n">
-        <v>2412.171875</v>
+        <v>2412.171630859375</v>
       </c>
       <c r="C209" t="n">
         <v>3292.14990234375</v>
       </c>
       <c r="D209" t="n">
-        <v>3583.87890625</v>
+        <v>3583.879150390625</v>
       </c>
       <c r="E209" t="n">
         <v>2106.699951171875</v>
@@ -7128,7 +7128,7 @@
         <v>67.34999847412109</v>
       </c>
       <c r="H209" t="n">
-        <v>530.1851196289062</v>
+        <v>530.18505859375</v>
       </c>
       <c r="I209" t="n">
         <v>3655.88525390625</v>
@@ -7142,7 +7142,7 @@
         <v>44869</v>
       </c>
       <c r="B210" t="n">
-        <v>2437.076171875</v>
+        <v>2437.075927734375</v>
       </c>
       <c r="C210" t="n">
         <v>3319.449951171875</v>
@@ -7154,13 +7154,13 @@
         <v>2121.25</v>
       </c>
       <c r="F210" t="n">
-        <v>845.7792358398438</v>
+        <v>845.7791748046875</v>
       </c>
       <c r="G210" t="n">
         <v>69.37000274658203</v>
       </c>
       <c r="H210" t="n">
-        <v>548.9552612304688</v>
+        <v>548.955322265625</v>
       </c>
       <c r="I210" t="n">
         <v>3754.10107421875</v>
@@ -7174,13 +7174,13 @@
         <v>44872</v>
       </c>
       <c r="B211" t="n">
-        <v>2441.251220703125</v>
+        <v>2441.25146484375</v>
       </c>
       <c r="C211" t="n">
         <v>3332.449951171875</v>
       </c>
       <c r="D211" t="n">
-        <v>3953.4072265625</v>
+        <v>3953.406982421875</v>
       </c>
       <c r="E211" t="n">
         <v>2165.699951171875</v>
@@ -7192,7 +7192,7 @@
         <v>69.72000122070312</v>
       </c>
       <c r="H211" t="n">
-        <v>558.2913208007812</v>
+        <v>558.2913818359375</v>
       </c>
       <c r="I211" t="n">
         <v>3795.194580078125</v>
@@ -7212,7 +7212,7 @@
         <v>3290</v>
       </c>
       <c r="D212" t="n">
-        <v>3989.940185546875</v>
+        <v>3989.9404296875</v>
       </c>
       <c r="E212" t="n">
         <v>2215.5</v>
@@ -7224,7 +7224,7 @@
         <v>73.16000366210938</v>
       </c>
       <c r="H212" t="n">
-        <v>554.75341796875</v>
+        <v>554.7534790039062</v>
       </c>
       <c r="I212" t="n">
         <v>3790.00146484375</v>
@@ -7250,13 +7250,13 @@
         <v>2176</v>
       </c>
       <c r="F213" t="n">
-        <v>875.7230224609375</v>
+        <v>875.7230834960938</v>
       </c>
       <c r="G213" t="n">
         <v>74.27999877929688</v>
       </c>
       <c r="H213" t="n">
-        <v>548.5131225585938</v>
+        <v>548.5130615234375</v>
       </c>
       <c r="I213" t="n">
         <v>3702.0224609375</v>
@@ -7270,7 +7270,7 @@
         <v>44876</v>
       </c>
       <c r="B214" t="n">
-        <v>2348.609619140625</v>
+        <v>2348.60986328125</v>
       </c>
       <c r="C214" t="n">
         <v>3292.050048828125</v>
@@ -7282,7 +7282,7 @@
         <v>2196.699951171875</v>
       </c>
       <c r="F214" t="n">
-        <v>876.752197265625</v>
+        <v>876.7521362304688</v>
       </c>
       <c r="G214" t="n">
         <v>72.04000091552734</v>
@@ -7291,7 +7291,7 @@
         <v>547.9234008789062</v>
       </c>
       <c r="I214" t="n">
-        <v>3795.394287109375</v>
+        <v>3795.39404296875</v>
       </c>
       <c r="J214" t="n">
         <v>357.8500061035156</v>
@@ -7302,7 +7302,7 @@
         <v>44879</v>
       </c>
       <c r="B215" t="n">
-        <v>2392.621826171875</v>
+        <v>2392.62158203125</v>
       </c>
       <c r="C215" t="n">
         <v>3287.64990234375</v>
@@ -7314,16 +7314,16 @@
         <v>2178.550048828125</v>
       </c>
       <c r="F215" t="n">
-        <v>877.2913208007812</v>
+        <v>877.291259765625</v>
       </c>
       <c r="G215" t="n">
         <v>71.95999908447266</v>
       </c>
       <c r="H215" t="n">
-        <v>570.2806396484375</v>
+        <v>570.2807006835938</v>
       </c>
       <c r="I215" t="n">
-        <v>3864.9990234375</v>
+        <v>3864.998779296875</v>
       </c>
       <c r="J215" t="n">
         <v>364.8500061035156</v>
@@ -7378,16 +7378,16 @@
         <v>2110.14990234375</v>
       </c>
       <c r="F217" t="n">
-        <v>869.7440185546875</v>
+        <v>869.7440795898438</v>
       </c>
       <c r="G217" t="n">
         <v>69.02999877929688</v>
       </c>
       <c r="H217" t="n">
-        <v>567.2342529296875</v>
+        <v>567.2341918945312</v>
       </c>
       <c r="I217" t="n">
-        <v>3804.431640625</v>
+        <v>3804.431884765625</v>
       </c>
       <c r="J217" t="n">
         <v>402.1499938964844</v>
@@ -7398,7 +7398,7 @@
         <v>44882</v>
       </c>
       <c r="B218" t="n">
-        <v>2405.09814453125</v>
+        <v>2405.098388671875</v>
       </c>
       <c r="C218" t="n">
         <v>3117.550048828125</v>
@@ -7410,16 +7410,16 @@
         <v>2102.60009765625</v>
       </c>
       <c r="F218" t="n">
-        <v>873.1746215820312</v>
+        <v>873.174560546875</v>
       </c>
       <c r="G218" t="n">
         <v>67.19999694824219</v>
       </c>
       <c r="H218" t="n">
-        <v>564.2859497070312</v>
+        <v>564.2860107421875</v>
       </c>
       <c r="I218" t="n">
-        <v>3748.30859375</v>
+        <v>3748.308837890625</v>
       </c>
       <c r="J218" t="n">
         <v>422.25</v>
@@ -7430,7 +7430,7 @@
         <v>44883</v>
       </c>
       <c r="B219" t="n">
-        <v>2417.427734375</v>
+        <v>2417.427490234375</v>
       </c>
       <c r="C219" t="n">
         <v>3116.25</v>
@@ -7448,10 +7448,10 @@
         <v>67.30000305175781</v>
       </c>
       <c r="H219" t="n">
-        <v>564.1876831054688</v>
+        <v>564.187744140625</v>
       </c>
       <c r="I219" t="n">
-        <v>3639.65771484375</v>
+        <v>3639.657470703125</v>
       </c>
       <c r="J219" t="n">
         <v>401.1499938964844</v>
@@ -7494,7 +7494,7 @@
         <v>44887</v>
       </c>
       <c r="B221" t="n">
-        <v>2417.5751953125</v>
+        <v>2417.575439453125</v>
       </c>
       <c r="C221" t="n">
         <v>2875.14990234375</v>
@@ -7512,7 +7512,7 @@
         <v>65.69999694824219</v>
       </c>
       <c r="H221" t="n">
-        <v>556.0802001953125</v>
+        <v>556.0801391601562</v>
       </c>
       <c r="I221" t="n">
         <v>3666.370849609375</v>
@@ -7526,13 +7526,13 @@
         <v>44888</v>
       </c>
       <c r="B222" t="n">
-        <v>2415.659423828125</v>
+        <v>2415.6591796875</v>
       </c>
       <c r="C222" t="n">
         <v>2856.85009765625</v>
       </c>
       <c r="D222" t="n">
-        <v>3896.2109375</v>
+        <v>3896.211181640625</v>
       </c>
       <c r="E222" t="n">
         <v>2036.5</v>
@@ -7547,7 +7547,7 @@
         <v>553.18115234375</v>
       </c>
       <c r="I222" t="n">
-        <v>3747.31005859375</v>
+        <v>3747.309814453125</v>
       </c>
       <c r="J222" t="n">
         <v>358.5499877929688</v>
@@ -7564,7 +7564,7 @@
         <v>2790.85009765625</v>
       </c>
       <c r="D223" t="n">
-        <v>3913.978759765625</v>
+        <v>3913.978515625</v>
       </c>
       <c r="E223" t="n">
         <v>2043.050048828125</v>
@@ -7576,7 +7576,7 @@
         <v>64.98999786376953</v>
       </c>
       <c r="H223" t="n">
-        <v>548.2182006835938</v>
+        <v>548.21826171875</v>
       </c>
       <c r="I223" t="n">
         <v>3725.8896484375</v>
@@ -7608,10 +7608,10 @@
         <v>64.79000091552734</v>
       </c>
       <c r="H224" t="n">
-        <v>554.90087890625</v>
+        <v>554.9009399414062</v>
       </c>
       <c r="I224" t="n">
-        <v>3659.730224609375</v>
+        <v>3659.73046875</v>
       </c>
       <c r="J224" t="n">
         <v>385.6000061035156</v>
@@ -7634,7 +7634,7 @@
         <v>1990.699951171875</v>
       </c>
       <c r="F225" t="n">
-        <v>861.1676025390625</v>
+        <v>861.1676635742188</v>
       </c>
       <c r="G225" t="n">
         <v>65.65000152587891</v>
@@ -7672,7 +7672,7 @@
         <v>64.94000244140625</v>
       </c>
       <c r="H226" t="n">
-        <v>555.1956787109375</v>
+        <v>555.1957397460938</v>
       </c>
       <c r="I226" t="n">
         <v>3595.06884765625</v>
@@ -7730,7 +7730,7 @@
         <v>2113.550048828125</v>
       </c>
       <c r="F228" t="n">
-        <v>872.8805541992188</v>
+        <v>872.880615234375</v>
       </c>
       <c r="G228" t="n">
         <v>66.08000183105469</v>
@@ -7756,13 +7756,13 @@
         <v>2745.699951171875</v>
       </c>
       <c r="D229" t="n">
-        <v>3915.3759765625</v>
+        <v>3915.376220703125</v>
       </c>
       <c r="E229" t="n">
         <v>2062.300048828125</v>
       </c>
       <c r="F229" t="n">
-        <v>870.5772094726562</v>
+        <v>870.5772705078125</v>
       </c>
       <c r="G229" t="n">
         <v>65.05999755859375</v>
@@ -7782,7 +7782,7 @@
         <v>44900</v>
       </c>
       <c r="B230" t="n">
-        <v>2575.007080078125</v>
+        <v>2575.0068359375</v>
       </c>
       <c r="C230" t="n">
         <v>2716.14990234375</v>
@@ -7803,7 +7803,7 @@
         <v>563.45068359375</v>
       </c>
       <c r="I230" t="n">
-        <v>3585.1826171875</v>
+        <v>3585.182373046875</v>
       </c>
       <c r="J230" t="n">
         <v>392.9500122070312</v>
@@ -7832,7 +7832,7 @@
         <v>64.95999908447266</v>
       </c>
       <c r="H231" t="n">
-        <v>570.968505859375</v>
+        <v>570.9685668945312</v>
       </c>
       <c r="I231" t="n">
         <v>3691.78662109375</v>
@@ -7846,7 +7846,7 @@
         <v>44902</v>
       </c>
       <c r="B232" t="n">
-        <v>2560.12353515625</v>
+        <v>2560.123291015625</v>
       </c>
       <c r="C232" t="n">
         <v>2741.550048828125</v>
@@ -7858,13 +7858,13 @@
         <v>2032.699951171875</v>
       </c>
       <c r="F232" t="n">
-        <v>869.1559448242188</v>
+        <v>869.156005859375</v>
       </c>
       <c r="G232" t="n">
         <v>64.88999938964844</v>
       </c>
       <c r="H232" t="n">
-        <v>571.9513549804688</v>
+        <v>571.9512939453125</v>
       </c>
       <c r="I232" t="n">
         <v>3725.240478515625</v>
@@ -7878,7 +7878,7 @@
         <v>44903</v>
       </c>
       <c r="B233" t="n">
-        <v>2575.154541015625</v>
+        <v>2575.154296875</v>
       </c>
       <c r="C233" t="n">
         <v>2691.39990234375</v>
@@ -7910,7 +7910,7 @@
         <v>44904</v>
       </c>
       <c r="B234" t="n">
-        <v>2573.435302734375</v>
+        <v>2573.43505859375</v>
       </c>
       <c r="C234" t="n">
         <v>2646.39990234375</v>
@@ -7928,7 +7928,7 @@
         <v>63.20999908447266</v>
       </c>
       <c r="H234" t="n">
-        <v>570.968505859375</v>
+        <v>570.9685668945312</v>
       </c>
       <c r="I234" t="n">
         <v>3616.33984375</v>
@@ -7942,7 +7942,7 @@
         <v>44907</v>
       </c>
       <c r="B235" t="n">
-        <v>2595.93212890625</v>
+        <v>2595.932373046875</v>
       </c>
       <c r="C235" t="n">
         <v>2687.85009765625</v>
@@ -7954,13 +7954,13 @@
         <v>2024.050048828125</v>
       </c>
       <c r="F235" t="n">
-        <v>863.8140869140625</v>
+        <v>863.8140258789062</v>
       </c>
       <c r="G235" t="n">
         <v>62.04000091552734</v>
       </c>
       <c r="H235" t="n">
-        <v>574.9486083984375</v>
+        <v>574.9486694335938</v>
       </c>
       <c r="I235" t="n">
         <v>3636.012939453125</v>
@@ -7986,16 +7986,16 @@
         <v>2021.400024414062</v>
       </c>
       <c r="F236" t="n">
-        <v>877.0462646484375</v>
+        <v>877.0463256835938</v>
       </c>
       <c r="G236" t="n">
         <v>64.59999847412109</v>
       </c>
       <c r="H236" t="n">
-        <v>574.4572143554688</v>
+        <v>574.457275390625</v>
       </c>
       <c r="I236" t="n">
-        <v>3581.387939453125</v>
+        <v>3581.3876953125</v>
       </c>
       <c r="J236" t="n">
         <v>358.2999877929688</v>
@@ -8006,7 +8006,7 @@
         <v>44909</v>
       </c>
       <c r="B237" t="n">
-        <v>2621.671630859375</v>
+        <v>2621.671875</v>
       </c>
       <c r="C237" t="n">
         <v>2672.449951171875</v>
@@ -8018,7 +8018,7 @@
         <v>2018.150024414062</v>
       </c>
       <c r="F237" t="n">
-        <v>882.6820678710938</v>
+        <v>882.68212890625</v>
       </c>
       <c r="G237" t="n">
         <v>63.86999893188477</v>
@@ -8038,7 +8038,7 @@
         <v>44910</v>
       </c>
       <c r="B238" t="n">
-        <v>2589.15380859375</v>
+        <v>2589.153564453125</v>
       </c>
       <c r="C238" t="n">
         <v>2657</v>
@@ -8050,13 +8050,13 @@
         <v>2024.900024414062</v>
       </c>
       <c r="F238" t="n">
-        <v>866.4114990234375</v>
+        <v>866.4115600585938</v>
       </c>
       <c r="G238" t="n">
         <v>63.09000015258789</v>
       </c>
       <c r="H238" t="n">
-        <v>551.5104370117188</v>
+        <v>551.510498046875</v>
       </c>
       <c r="I238" t="n">
         <v>3545.88671875</v>
@@ -8070,25 +8070,25 @@
         <v>44911</v>
       </c>
       <c r="B239" t="n">
-        <v>2570.7333984375</v>
+        <v>2570.733642578125</v>
       </c>
       <c r="C239" t="n">
         <v>2643.5</v>
       </c>
       <c r="D239" t="n">
-        <v>3973.5703125</v>
+        <v>3973.570068359375</v>
       </c>
       <c r="E239" t="n">
         <v>2044.25</v>
       </c>
       <c r="F239" t="n">
-        <v>843.3777465820312</v>
+        <v>843.3778076171875</v>
       </c>
       <c r="G239" t="n">
         <v>61.58000183105469</v>
       </c>
       <c r="H239" t="n">
-        <v>546.4494018554688</v>
+        <v>546.4493408203125</v>
       </c>
       <c r="I239" t="n">
         <v>3579.889892578125</v>
@@ -8102,7 +8102,7 @@
         <v>44914</v>
       </c>
       <c r="B240" t="n">
-        <v>2592.10107421875</v>
+        <v>2592.100830078125</v>
       </c>
       <c r="C240" t="n">
         <v>2679.300048828125</v>
@@ -8120,7 +8120,7 @@
         <v>61.15999984741211</v>
       </c>
       <c r="H240" t="n">
-        <v>554.1146240234375</v>
+        <v>554.1146850585938</v>
       </c>
       <c r="I240" t="n">
         <v>3613.49365234375</v>
@@ -8146,7 +8146,7 @@
         <v>2061.64990234375</v>
       </c>
       <c r="F241" t="n">
-        <v>866.7056274414062</v>
+        <v>866.70556640625</v>
       </c>
       <c r="G241" t="n">
         <v>61.15000152587891</v>
@@ -8155,7 +8155,7 @@
         <v>550.4293823242188</v>
       </c>
       <c r="I241" t="n">
-        <v>3609.24951171875</v>
+        <v>3609.249267578125</v>
       </c>
       <c r="J241" t="n">
         <v>359.1000061035156</v>
@@ -8166,7 +8166,7 @@
         <v>44916</v>
       </c>
       <c r="B242" t="n">
-        <v>2496.266357421875</v>
+        <v>2496.2666015625</v>
       </c>
       <c r="C242" t="n">
         <v>2615.75</v>
@@ -8184,7 +8184,7 @@
         <v>58.09999847412109</v>
       </c>
       <c r="H242" t="n">
-        <v>529.890380859375</v>
+        <v>529.8903198242188</v>
       </c>
       <c r="I242" t="n">
         <v>3539.844482421875</v>
@@ -8198,7 +8198,7 @@
         <v>44917</v>
       </c>
       <c r="B243" t="n">
-        <v>2469.49560546875</v>
+        <v>2469.495849609375</v>
       </c>
       <c r="C243" t="n">
         <v>2518</v>
@@ -8219,7 +8219,7 @@
         <v>523.64990234375</v>
       </c>
       <c r="I243" t="n">
-        <v>3546.685546875</v>
+        <v>3546.685302734375</v>
       </c>
       <c r="J243" t="n">
         <v>331.6499938964844</v>
@@ -8242,7 +8242,7 @@
         <v>1809.050048828125</v>
       </c>
       <c r="F244" t="n">
-        <v>778.3441772460938</v>
+        <v>778.34423828125</v>
       </c>
       <c r="G244" t="n">
         <v>52.43999862670898</v>
@@ -8294,28 +8294,28 @@
         <v>44922</v>
       </c>
       <c r="B246" t="n">
-        <v>2434.423583984375</v>
+        <v>2434.42333984375</v>
       </c>
       <c r="C246" t="n">
         <v>2501.800048828125</v>
       </c>
       <c r="D246" t="n">
-        <v>3762.803466796875</v>
+        <v>3762.80322265625</v>
       </c>
       <c r="E246" t="n">
         <v>1908.699951171875</v>
       </c>
       <c r="F246" t="n">
-        <v>800.9369506835938</v>
+        <v>800.9368896484375</v>
       </c>
       <c r="G246" t="n">
         <v>57.81000137329102</v>
       </c>
       <c r="H246" t="n">
-        <v>514.2648315429688</v>
+        <v>514.2647705078125</v>
       </c>
       <c r="I246" t="n">
-        <v>3348.3076171875</v>
+        <v>3348.307373046875</v>
       </c>
       <c r="J246" t="n">
         <v>338.4500122070312</v>
@@ -8326,7 +8326,7 @@
         <v>44923</v>
       </c>
       <c r="B247" t="n">
-        <v>2412.171875</v>
+        <v>2412.171630859375</v>
       </c>
       <c r="C247" t="n">
         <v>2564.449951171875</v>
@@ -8344,7 +8344,7 @@
         <v>60.70000076293945</v>
       </c>
       <c r="H247" t="n">
-        <v>509.4494323730469</v>
+        <v>509.4494018554688</v>
       </c>
       <c r="I247" t="n">
         <v>3600.861083984375</v>
@@ -8364,22 +8364,22 @@
         <v>2669.5</v>
       </c>
       <c r="D248" t="n">
-        <v>3803.679443359375</v>
+        <v>3803.67919921875</v>
       </c>
       <c r="E248" t="n">
         <v>1910.25</v>
       </c>
       <c r="F248" t="n">
-        <v>803.2892456054688</v>
+        <v>803.289306640625</v>
       </c>
       <c r="G248" t="n">
         <v>60.90000152587891</v>
       </c>
       <c r="H248" t="n">
-        <v>513.724365234375</v>
+        <v>513.7243041992188</v>
       </c>
       <c r="I248" t="n">
-        <v>3787.8046875</v>
+        <v>3787.804443359375</v>
       </c>
       <c r="J248" t="n">
         <v>339.2999877929688</v>
@@ -8390,13 +8390,13 @@
         <v>44925</v>
       </c>
       <c r="B249" t="n">
-        <v>2398.663818359375</v>
+        <v>2398.66357421875</v>
       </c>
       <c r="C249" t="n">
         <v>2589.25</v>
       </c>
       <c r="D249" t="n">
-        <v>3851.342529296875</v>
+        <v>3851.3427734375</v>
       </c>
       <c r="E249" t="n">
         <v>1931.800048828125</v>
@@ -8434,13 +8434,13 @@
         <v>1888.699951171875</v>
       </c>
       <c r="F250" t="n">
-        <v>805.9847412109375</v>
+        <v>805.9846801757812</v>
       </c>
       <c r="G250" t="n">
         <v>59.63000106811523</v>
       </c>
       <c r="H250" t="n">
-        <v>517.4095458984375</v>
+        <v>517.4096069335938</v>
       </c>
       <c r="I250" t="n">
         <v>3545.73681640625</v>
@@ -8466,13 +8466,13 @@
         <v>1892.949951171875</v>
       </c>
       <c r="F251" t="n">
-        <v>804.1715087890625</v>
+        <v>804.1714477539062</v>
       </c>
       <c r="G251" t="n">
         <v>58.95000076293945</v>
       </c>
       <c r="H251" t="n">
-        <v>521.7827758789062</v>
+        <v>521.78271484375</v>
       </c>
       <c r="I251" t="n">
         <v>3593.720703125</v>
@@ -8492,13 +8492,13 @@
         <v>2512.699951171875</v>
       </c>
       <c r="D252" t="n">
-        <v>3820.099365234375</v>
+        <v>3820.099609375</v>
       </c>
       <c r="E252" t="n">
         <v>1860.5</v>
       </c>
       <c r="F252" t="n">
-        <v>793.9288330078125</v>
+        <v>793.9287719726562</v>
       </c>
       <c r="G252" t="n">
         <v>57.31999969482422</v>
@@ -8507,7 +8507,7 @@
         <v>509.8916320800781</v>
       </c>
       <c r="I252" t="n">
-        <v>3472.537109375</v>
+        <v>3472.537353515625</v>
       </c>
       <c r="J252" t="n">
         <v>333.7999877929688</v>
@@ -8536,7 +8536,7 @@
         <v>57.75</v>
       </c>
       <c r="H253" t="n">
-        <v>515.689697265625</v>
+        <v>515.6897583007812</v>
       </c>
       <c r="I253" t="n">
         <v>3628.722900390625</v>
@@ -8562,13 +8562,13 @@
         <v>1838.25</v>
       </c>
       <c r="F254" t="n">
-        <v>790.106201171875</v>
+        <v>790.1061401367188</v>
       </c>
       <c r="G254" t="n">
         <v>56.68000030517578</v>
       </c>
       <c r="H254" t="n">
-        <v>510.8251953125</v>
+        <v>510.8252258300781</v>
       </c>
       <c r="I254" t="n">
         <v>3550.530029296875</v>
@@ -8600,7 +8600,7 @@
         <v>57.54000091552734</v>
       </c>
       <c r="H255" t="n">
-        <v>515.689697265625</v>
+        <v>515.6897583007812</v>
       </c>
       <c r="I255" t="n">
         <v>3624.029296875</v>
@@ -8632,7 +8632,7 @@
         <v>55.84000015258789</v>
       </c>
       <c r="H256" t="n">
-        <v>505.5675964355469</v>
+        <v>505.567626953125</v>
       </c>
       <c r="I256" t="n">
         <v>3651.3916015625</v>
@@ -8652,13 +8652,13 @@
         <v>2585.35009765625</v>
       </c>
       <c r="D257" t="n">
-        <v>3629.19677734375</v>
+        <v>3629.197021484375</v>
       </c>
       <c r="E257" t="n">
         <v>1877.150024414062</v>
       </c>
       <c r="F257" t="n">
-        <v>780.6475830078125</v>
+        <v>780.6476440429688</v>
       </c>
       <c r="G257" t="n">
         <v>55.2400016784668</v>
@@ -8678,7 +8678,7 @@
         <v>44938</v>
       </c>
       <c r="B258" t="n">
-        <v>2322.8212890625</v>
+        <v>2322.821044921875</v>
       </c>
       <c r="C258" t="n">
         <v>2624</v>
@@ -8696,10 +8696,10 @@
         <v>54.72999954223633</v>
       </c>
       <c r="H258" t="n">
-        <v>501.5875549316406</v>
+        <v>501.5875244140625</v>
       </c>
       <c r="I258" t="n">
-        <v>3644.0517578125</v>
+        <v>3644.051513671875</v>
       </c>
       <c r="J258" t="n">
         <v>291.3999938964844</v>
@@ -8710,13 +8710,13 @@
         <v>44939</v>
       </c>
       <c r="B259" t="n">
-        <v>2325.57177734375</v>
+        <v>2325.572021484375</v>
       </c>
       <c r="C259" t="n">
         <v>2689.050048828125</v>
       </c>
       <c r="D259" t="n">
-        <v>3714.3916015625</v>
+        <v>3714.391845703125</v>
       </c>
       <c r="E259" t="n">
         <v>1915.650024414062</v>
@@ -8728,7 +8728,7 @@
         <v>55.7400016784668</v>
       </c>
       <c r="H259" t="n">
-        <v>509.6950988769531</v>
+        <v>509.695068359375</v>
       </c>
       <c r="I259" t="n">
         <v>3710.011474609375</v>
@@ -8742,13 +8742,13 @@
         <v>44942</v>
       </c>
       <c r="B260" t="n">
-        <v>2319.873779296875</v>
+        <v>2319.8740234375</v>
       </c>
       <c r="C260" t="n">
         <v>2703.10009765625</v>
       </c>
       <c r="D260" t="n">
-        <v>3613.225830078125</v>
+        <v>3613.2255859375</v>
       </c>
       <c r="E260" t="n">
         <v>2089.800048828125</v>
@@ -8760,7 +8760,7 @@
         <v>54.59000015258789</v>
       </c>
       <c r="H260" t="n">
-        <v>508.0735473632812</v>
+        <v>508.0735778808594</v>
       </c>
       <c r="I260" t="n">
         <v>3725.58984375</v>
@@ -8780,13 +8780,13 @@
         <v>2725.050048828125</v>
       </c>
       <c r="D261" t="n">
-        <v>3632.740478515625</v>
+        <v>3632.74072265625</v>
       </c>
       <c r="E261" t="n">
         <v>2166.14990234375</v>
       </c>
       <c r="F261" t="n">
-        <v>769.1798095703125</v>
+        <v>769.1797485351562</v>
       </c>
       <c r="G261" t="n">
         <v>56.38999938964844</v>
@@ -8795,7 +8795,7 @@
         <v>508.56494140625</v>
       </c>
       <c r="I261" t="n">
-        <v>3844.726806640625</v>
+        <v>3844.7265625</v>
       </c>
       <c r="J261" t="n">
         <v>296.7999877929688</v>
@@ -8824,10 +8824,10 @@
         <v>55.7400016784668</v>
       </c>
       <c r="H262" t="n">
-        <v>511.4640502929688</v>
+        <v>511.4639892578125</v>
       </c>
       <c r="I262" t="n">
-        <v>3800.2373046875</v>
+        <v>3800.23779296875</v>
       </c>
       <c r="J262" t="n">
         <v>299.7000122070312</v>
@@ -8844,22 +8844,22 @@
         <v>2734.10009765625</v>
       </c>
       <c r="D263" t="n">
-        <v>3457.25927734375</v>
+        <v>3457.259521484375</v>
       </c>
       <c r="E263" t="n">
         <v>1954.300048828125</v>
       </c>
       <c r="F263" t="n">
-        <v>760.6524047851562</v>
+        <v>760.65234375</v>
       </c>
       <c r="G263" t="n">
         <v>55.5099983215332</v>
       </c>
       <c r="H263" t="n">
-        <v>510.2846984863281</v>
+        <v>510.2847290039062</v>
       </c>
       <c r="I263" t="n">
-        <v>3830.296142578125</v>
+        <v>3830.296630859375</v>
       </c>
       <c r="J263" t="n">
         <v>288.2999877929688</v>
@@ -8876,7 +8876,7 @@
         <v>2737.949951171875</v>
       </c>
       <c r="D264" t="n">
-        <v>3449.872802734375</v>
+        <v>3449.873046875</v>
       </c>
       <c r="E264" t="n">
         <v>1975.599975585938</v>
@@ -8902,7 +8902,7 @@
         <v>44949</v>
       </c>
       <c r="B265" t="n">
-        <v>2282.59130859375</v>
+        <v>2282.591552734375</v>
       </c>
       <c r="C265" t="n">
         <v>2784.10009765625</v>
@@ -8940,7 +8940,7 @@
         <v>2762.14990234375</v>
       </c>
       <c r="D266" t="n">
-        <v>3435.748779296875</v>
+        <v>3435.7490234375</v>
       </c>
       <c r="E266" t="n">
         <v>1916.800048828125</v>
@@ -8952,10 +8952,10 @@
         <v>54.93000030517578</v>
       </c>
       <c r="H266" t="n">
-        <v>490.3352355957031</v>
+        <v>490.3352661132812</v>
       </c>
       <c r="I266" t="n">
-        <v>3886.41943359375</v>
+        <v>3886.419189453125</v>
       </c>
       <c r="J266" t="n">
         <v>284</v>
@@ -8966,7 +8966,7 @@
         <v>44951</v>
       </c>
       <c r="B267" t="n">
-        <v>2127.614990234375</v>
+        <v>2127.615478515625</v>
       </c>
       <c r="C267" t="n">
         <v>2517.75</v>
@@ -8998,7 +8998,7 @@
         <v>44953</v>
       </c>
       <c r="B268" t="n">
-        <v>1846.693969726562</v>
+        <v>1846.69384765625</v>
       </c>
       <c r="C268" t="n">
         <v>2014.199951171875</v>
@@ -9030,7 +9030,7 @@
         <v>44956</v>
       </c>
       <c r="B269" t="n">
-        <v>1870.664794921875</v>
+        <v>1870.664916992188</v>
       </c>
       <c r="C269" t="n">
         <v>1708.199951171875</v>
@@ -9048,7 +9048,7 @@
         <v>47.11000061035156</v>
       </c>
       <c r="H269" t="n">
-        <v>380.8095092773438</v>
+        <v>380.8095397949219</v>
       </c>
       <c r="I269" t="n">
         <v>2339.191650390625</v>
@@ -9074,7 +9074,7 @@
         <v>1223.900024414062</v>
       </c>
       <c r="F270" t="n">
-        <v>600.494384765625</v>
+        <v>600.4944458007812</v>
       </c>
       <c r="G270" t="n">
         <v>44.7599983215332</v>
@@ -9115,7 +9115,7 @@
         <v>328.3315124511719</v>
       </c>
       <c r="I271" t="n">
-        <v>1894.80126953125</v>
+        <v>1894.801147460938</v>
       </c>
       <c r="J271" t="n">
         <v>235.6999969482422</v>
@@ -9126,7 +9126,7 @@
         <v>44959</v>
       </c>
       <c r="B272" t="n">
-        <v>1808.870849609375</v>
+        <v>1808.870971679688</v>
       </c>
       <c r="C272" t="n">
         <v>1551.150024414062</v>
@@ -9164,7 +9164,7 @@
         <v>1396.050048828125</v>
       </c>
       <c r="D273" t="n">
-        <v>1583.918212890625</v>
+        <v>1583.918334960938</v>
       </c>
       <c r="E273" t="n">
         <v>935.9000244140625</v>
@@ -9190,7 +9190,7 @@
         <v>44963</v>
       </c>
       <c r="B274" t="n">
-        <v>1934.914916992188</v>
+        <v>1934.914794921875</v>
       </c>
       <c r="C274" t="n">
         <v>1256.449951171875</v>
@@ -9208,10 +9208,10 @@
         <v>36.47000122070312</v>
       </c>
       <c r="H274" t="n">
-        <v>373.1933288574219</v>
+        <v>373.1932983398438</v>
       </c>
       <c r="I274" t="n">
-        <v>1539.138793945312</v>
+        <v>1539.138916015625</v>
       </c>
       <c r="J274" t="n">
         <v>216.0500030517578</v>
@@ -9222,7 +9222,7 @@
         <v>44964</v>
       </c>
       <c r="B275" t="n">
-        <v>1958.984130859375</v>
+        <v>1958.984008789062</v>
       </c>
       <c r="C275" t="n">
         <v>1252.199951171875</v>
@@ -9234,7 +9234,7 @@
         <v>844.6500244140625</v>
       </c>
       <c r="F275" t="n">
-        <v>542.175048828125</v>
+        <v>542.1749877929688</v>
       </c>
       <c r="G275" t="n">
         <v>34.65000152587891</v>
@@ -9254,7 +9254,7 @@
         <v>44965</v>
       </c>
       <c r="B276" t="n">
-        <v>1939.041015625</v>
+        <v>1939.040893554688</v>
       </c>
       <c r="C276" t="n">
         <v>1314.800048828125</v>
@@ -9275,7 +9275,7 @@
         <v>378.0087280273438</v>
       </c>
       <c r="I276" t="n">
-        <v>1389.0947265625</v>
+        <v>1389.094604492188</v>
       </c>
       <c r="J276" t="n">
         <v>227.6999969482422</v>
@@ -9318,25 +9318,25 @@
         <v>44967</v>
       </c>
       <c r="B278" t="n">
-        <v>1847.332641601562</v>
+        <v>1847.33251953125</v>
       </c>
       <c r="C278" t="n">
         <v>1186.650024414062</v>
       </c>
       <c r="D278" t="n">
-        <v>1843.595581054688</v>
+        <v>1843.595703125</v>
       </c>
       <c r="E278" t="n">
         <v>724.25</v>
       </c>
       <c r="F278" t="n">
-        <v>572.3638305664062</v>
+        <v>572.3638916015625</v>
       </c>
       <c r="G278" t="n">
         <v>32.84000015258789</v>
       </c>
       <c r="H278" t="n">
-        <v>354.5705261230469</v>
+        <v>354.5704650878906</v>
       </c>
       <c r="I278" t="n">
         <v>1253.680419921875</v>
@@ -9382,7 +9382,7 @@
         <v>44971</v>
       </c>
       <c r="B280" t="n">
-        <v>1798.113525390625</v>
+        <v>1798.113647460938</v>
       </c>
       <c r="C280" t="n">
         <v>1071</v>
@@ -9400,10 +9400,10 @@
         <v>29.63999938964844</v>
       </c>
       <c r="H280" t="n">
-        <v>330.6900634765625</v>
+        <v>330.6900939941406</v>
       </c>
       <c r="I280" t="n">
-        <v>1131.498168945312</v>
+        <v>1131.498046875</v>
       </c>
       <c r="J280" t="n">
         <v>188.1999969482422</v>
@@ -9420,7 +9420,7 @@
         <v>1017.450012207031</v>
       </c>
       <c r="D281" t="n">
-        <v>1775.868896484375</v>
+        <v>1775.868774414062</v>
       </c>
       <c r="E281" t="n">
         <v>621</v>
@@ -9435,7 +9435,7 @@
         <v>338.8958740234375</v>
       </c>
       <c r="I281" t="n">
-        <v>1074.92578125</v>
+        <v>1074.925659179688</v>
       </c>
       <c r="J281" t="n">
         <v>197.0500030517578</v>
@@ -9452,7 +9452,7 @@
         <v>968.5499877929688</v>
       </c>
       <c r="D282" t="n">
-        <v>1793.337158203125</v>
+        <v>1793.337036132812</v>
       </c>
       <c r="E282" t="n">
         <v>616.2999877929688</v>
@@ -9478,19 +9478,19 @@
         <v>44974</v>
       </c>
       <c r="B283" t="n">
-        <v>1807.053466796875</v>
+        <v>1807.053588867188</v>
       </c>
       <c r="C283" t="n">
         <v>920.4000244140625</v>
       </c>
       <c r="D283" t="n">
-        <v>1719.571166992188</v>
+        <v>1719.5712890625</v>
       </c>
       <c r="E283" t="n">
         <v>628.6500244140625</v>
       </c>
       <c r="F283" t="n">
-        <v>567.1689453125</v>
+        <v>567.1690063476562</v>
       </c>
       <c r="G283" t="n">
         <v>31.03000068664551</v>
@@ -9499,7 +9499,7 @@
         <v>347.1999816894531</v>
       </c>
       <c r="I283" t="n">
-        <v>970.1693115234375</v>
+        <v>970.1692504882812</v>
       </c>
       <c r="J283" t="n">
         <v>217.1999969482422</v>
@@ -9522,7 +9522,7 @@
         <v>597.25</v>
       </c>
       <c r="F284" t="n">
-        <v>568.1981201171875</v>
+        <v>568.1981811523438</v>
       </c>
       <c r="G284" t="n">
         <v>32.58000183105469</v>
@@ -9560,7 +9560,7 @@
         <v>34.20000076293945</v>
       </c>
       <c r="H285" t="n">
-        <v>346.7577819824219</v>
+        <v>346.7577514648438</v>
       </c>
       <c r="I285" t="n">
         <v>875.5989990234375</v>
@@ -9580,7 +9580,7 @@
         <v>789.2000122070312</v>
       </c>
       <c r="D286" t="n">
-        <v>1402.298461914062</v>
+        <v>1402.298583984375</v>
       </c>
       <c r="E286" t="n">
         <v>539.0499877929688</v>
@@ -9612,7 +9612,7 @@
         <v>749.75</v>
       </c>
       <c r="D287" t="n">
-        <v>1380.138793945312</v>
+        <v>1380.138916015625</v>
       </c>
       <c r="E287" t="n">
         <v>512.0999755859375</v>
@@ -9624,7 +9624,7 @@
         <v>30.8700008392334</v>
       </c>
       <c r="H287" t="n">
-        <v>331.0831298828125</v>
+        <v>331.0831604003906</v>
       </c>
       <c r="I287" t="n">
         <v>790.2659912109375</v>
@@ -9638,7 +9638,7 @@
         <v>44981</v>
       </c>
       <c r="B288" t="n">
-        <v>1699.577392578125</v>
+        <v>1699.577270507812</v>
       </c>
       <c r="C288" t="n">
         <v>712.2999877929688</v>
@@ -9656,10 +9656,10 @@
         <v>29.32999992370605</v>
       </c>
       <c r="H288" t="n">
-        <v>339.2889709472656</v>
+        <v>339.2890014648438</v>
       </c>
       <c r="I288" t="n">
-        <v>750.770263671875</v>
+        <v>750.7703247070312</v>
       </c>
       <c r="J288" t="n">
         <v>190.6000061035156</v>
@@ -9676,13 +9676,13 @@
         <v>676.7000122070312</v>
       </c>
       <c r="D289" t="n">
-        <v>1191.33251953125</v>
+        <v>1191.332397460938</v>
       </c>
       <c r="E289" t="n">
         <v>462.2000122070312</v>
       </c>
       <c r="F289" t="n">
-        <v>550.849365234375</v>
+        <v>550.8493041992188</v>
       </c>
       <c r="G289" t="n">
         <v>27.8700008392334</v>
@@ -9691,7 +9691,7 @@
         <v>324.2040100097656</v>
       </c>
       <c r="I289" t="n">
-        <v>713.271728515625</v>
+        <v>713.2716674804688</v>
       </c>
       <c r="J289" t="n">
         <v>181.1000061035156</v>
@@ -9708,22 +9708,22 @@
         <v>642.9000244140625</v>
       </c>
       <c r="D290" t="n">
-        <v>1361.373046875</v>
+        <v>1361.372924804688</v>
       </c>
       <c r="E290" t="n">
         <v>485.2999877929688</v>
       </c>
       <c r="F290" t="n">
-        <v>580.6951293945312</v>
+        <v>580.6951904296875</v>
       </c>
       <c r="G290" t="n">
         <v>29.26000022888184</v>
       </c>
       <c r="H290" t="n">
-        <v>336.193359375</v>
+        <v>336.1933898925781</v>
       </c>
       <c r="I290" t="n">
-        <v>677.6205444335938</v>
+        <v>677.6204833984375</v>
       </c>
       <c r="J290" t="n">
         <v>190.1499938964844</v>
@@ -9734,7 +9734,7 @@
         <v>44986</v>
       </c>
       <c r="B291" t="n">
-        <v>1738.33349609375</v>
+        <v>1738.333618164062</v>
       </c>
       <c r="C291" t="n">
         <v>675</v>
@@ -9752,7 +9752,7 @@
         <v>30.71999931335449</v>
       </c>
       <c r="H291" t="n">
-        <v>347.4947814941406</v>
+        <v>347.4948120117188</v>
       </c>
       <c r="I291" t="n">
         <v>710.6752319335938</v>
@@ -9772,7 +9772,7 @@
         <v>708.75</v>
       </c>
       <c r="D292" t="n">
-        <v>1604.3310546875</v>
+        <v>1604.330932617188</v>
       </c>
       <c r="E292" t="n">
         <v>535</v>
@@ -9804,7 +9804,7 @@
         <v>744.1500244140625</v>
       </c>
       <c r="D293" t="n">
-        <v>1876.08642578125</v>
+        <v>1876.086547851562</v>
       </c>
       <c r="E293" t="n">
         <v>561.75</v>
@@ -9830,7 +9830,7 @@
         <v>44991</v>
       </c>
       <c r="B294" t="n">
-        <v>1832.9892578125</v>
+        <v>1832.989379882812</v>
       </c>
       <c r="C294" t="n">
         <v>781.3499755859375</v>
@@ -9851,7 +9851,7 @@
         <v>378.8440246582031</v>
       </c>
       <c r="I294" t="n">
-        <v>819.226318359375</v>
+        <v>819.2263793945312</v>
       </c>
       <c r="J294" t="n">
         <v>230.8000030517578</v>
@@ -9862,7 +9862,7 @@
         <v>44993</v>
       </c>
       <c r="B295" t="n">
-        <v>1853.325317382812</v>
+        <v>1853.3251953125</v>
       </c>
       <c r="C295" t="n">
         <v>820.4000244140625</v>
@@ -9894,13 +9894,13 @@
         <v>44994</v>
       </c>
       <c r="B296" t="n">
-        <v>1827.3896484375</v>
+        <v>1827.389404296875</v>
       </c>
       <c r="C296" t="n">
         <v>861.4000244140625</v>
       </c>
       <c r="D296" t="n">
-        <v>1949.602905273438</v>
+        <v>1949.602783203125</v>
       </c>
       <c r="E296" t="n">
         <v>650.2000122070312</v>
@@ -9912,7 +9912,7 @@
         <v>39.18000030517578</v>
       </c>
       <c r="H296" t="n">
-        <v>378.057861328125</v>
+        <v>378.0578918457031</v>
       </c>
       <c r="I296" t="n">
         <v>903.1611938476562</v>
@@ -9932,13 +9932,13 @@
         <v>904.4500122070312</v>
       </c>
       <c r="D297" t="n">
-        <v>1892.756103515625</v>
+        <v>1892.755981445312</v>
       </c>
       <c r="E297" t="n">
         <v>682.7000122070312</v>
       </c>
       <c r="F297" t="n">
-        <v>683.954833984375</v>
+        <v>683.9548950195312</v>
       </c>
       <c r="G297" t="n">
         <v>40.97999954223633</v>
@@ -9964,7 +9964,7 @@
         <v>949.6500244140625</v>
       </c>
       <c r="D298" t="n">
-        <v>1870.995727539062</v>
+        <v>1870.995849609375</v>
       </c>
       <c r="E298" t="n">
         <v>716.7999877929688</v>
@@ -9976,7 +9976,7 @@
         <v>43.02000045776367</v>
       </c>
       <c r="H298" t="n">
-        <v>361.6462097167969</v>
+        <v>361.6461791992188</v>
       </c>
       <c r="I298" t="n">
         <v>995.6842651367188</v>
@@ -9990,13 +9990,13 @@
         <v>44999</v>
       </c>
       <c r="B299" t="n">
-        <v>1707.829833984375</v>
+        <v>1707.829711914062</v>
       </c>
       <c r="C299" t="n">
         <v>902.2000122070312</v>
       </c>
       <c r="D299" t="n">
-        <v>1735.043090820312</v>
+        <v>1735.043212890625</v>
       </c>
       <c r="E299" t="n">
         <v>706.0999755859375</v>
@@ -10022,19 +10022,19 @@
         <v>45000</v>
       </c>
       <c r="B300" t="n">
-        <v>1709.401489257812</v>
+        <v>1709.4013671875</v>
       </c>
       <c r="C300" t="n">
         <v>928.3499755859375</v>
       </c>
       <c r="D300" t="n">
-        <v>1835.66015625</v>
+        <v>1835.660034179688</v>
       </c>
       <c r="E300" t="n">
         <v>740.4000244140625</v>
       </c>
       <c r="F300" t="n">
-        <v>665.8709716796875</v>
+        <v>665.8710327148438</v>
       </c>
       <c r="G300" t="n">
         <v>40.36000061035156</v>
@@ -10054,7 +10054,7 @@
         <v>45001</v>
       </c>
       <c r="B301" t="n">
-        <v>1719.5205078125</v>
+        <v>1719.520385742188</v>
       </c>
       <c r="C301" t="n">
         <v>973.7000122070312</v>
@@ -10072,7 +10072,7 @@
         <v>39.7400016784668</v>
       </c>
       <c r="H301" t="n">
-        <v>372.2597045898438</v>
+        <v>372.2596740722656</v>
       </c>
       <c r="I301" t="n">
         <v>887.1832275390625</v>
@@ -10098,13 +10098,13 @@
         <v>816.25</v>
       </c>
       <c r="F302" t="n">
-        <v>666.8511962890625</v>
+        <v>666.8511352539062</v>
       </c>
       <c r="G302" t="n">
         <v>39.9900016784668</v>
       </c>
       <c r="H302" t="n">
-        <v>371.9157409667969</v>
+        <v>371.915771484375</v>
       </c>
       <c r="I302" t="n">
         <v>896.5203247070312</v>
@@ -10118,13 +10118,13 @@
         <v>45005</v>
       </c>
       <c r="B303" t="n">
-        <v>1665.7822265625</v>
+        <v>1665.782104492188</v>
       </c>
       <c r="C303" t="n">
         <v>1009.099975585938</v>
       </c>
       <c r="D303" t="n">
-        <v>1801.671875</v>
+        <v>1801.671752929688</v>
       </c>
       <c r="E303" t="n">
         <v>848.6500244140625</v>
@@ -10136,7 +10136,7 @@
         <v>38.04000091552734</v>
       </c>
       <c r="H303" t="n">
-        <v>359.0910339355469</v>
+        <v>359.091064453125</v>
       </c>
       <c r="I303" t="n">
         <v>851.7318115234375</v>
@@ -10156,7 +10156,7 @@
         <v>1006.099975585938</v>
       </c>
       <c r="D304" t="n">
-        <v>1820.936767578125</v>
+        <v>1820.936889648438</v>
       </c>
       <c r="E304" t="n">
         <v>891.0499877929688</v>
@@ -10188,7 +10188,7 @@
         <v>1032.800048828125</v>
       </c>
       <c r="D305" t="n">
-        <v>1812.102905273438</v>
+        <v>1812.10302734375</v>
       </c>
       <c r="E305" t="n">
         <v>935.5999755859375</v>
@@ -10200,7 +10200,7 @@
         <v>40.81000137329102</v>
       </c>
       <c r="H305" t="n">
-        <v>369.0658264160156</v>
+        <v>369.0657958984375</v>
       </c>
       <c r="I305" t="n">
         <v>934.0188598632812</v>
@@ -10252,22 +10252,22 @@
         <v>1124.550048828125</v>
       </c>
       <c r="D307" t="n">
-        <v>1737.488647460938</v>
+        <v>1737.48876953125</v>
       </c>
       <c r="E307" t="n">
         <v>1029.349975585938</v>
       </c>
       <c r="F307" t="n">
-        <v>625.3414306640625</v>
+        <v>625.3413696289062</v>
       </c>
       <c r="G307" t="n">
         <v>38.52000045776367</v>
       </c>
       <c r="H307" t="n">
-        <v>365.3805541992188</v>
+        <v>365.3805236816406</v>
       </c>
       <c r="I307" t="n">
-        <v>1006.070129394531</v>
+        <v>1006.070068359375</v>
       </c>
       <c r="J307" t="n">
         <v>192.1000061035156</v>
@@ -10278,7 +10278,7 @@
         <v>45012</v>
       </c>
       <c r="B308" t="n">
-        <v>1655.319580078125</v>
+        <v>1655.319458007812</v>
       </c>
       <c r="C308" t="n">
         <v>1068.400024414062</v>
@@ -10290,13 +10290,13 @@
         <v>984.9000244140625</v>
       </c>
       <c r="F308" t="n">
-        <v>616.6179809570312</v>
+        <v>616.6180419921875</v>
       </c>
       <c r="G308" t="n">
         <v>36.59999847412109</v>
       </c>
       <c r="H308" t="n">
-        <v>363.6116333007812</v>
+        <v>363.6116638183594</v>
       </c>
       <c r="I308" t="n">
         <v>956.5379638671875</v>
@@ -10316,7 +10316,7 @@
         <v>1015</v>
       </c>
       <c r="D309" t="n">
-        <v>1597.942504882812</v>
+        <v>1597.942626953125</v>
       </c>
       <c r="E309" t="n">
         <v>935.6500244140625</v>
@@ -10328,10 +10328,10 @@
         <v>34.77000045776367</v>
       </c>
       <c r="H309" t="n">
-        <v>352.75244140625</v>
+        <v>352.7524719238281</v>
       </c>
       <c r="I309" t="n">
-        <v>908.7035522460938</v>
+        <v>908.70361328125</v>
       </c>
       <c r="J309" t="n">
         <v>173.9499969482422</v>
@@ -10348,7 +10348,7 @@
         <v>1003.450012207031</v>
       </c>
       <c r="D310" t="n">
-        <v>1737.239135742188</v>
+        <v>1737.2392578125</v>
       </c>
       <c r="E310" t="n">
         <v>894.3499755859375</v>
@@ -10360,7 +10360,7 @@
         <v>36.5</v>
       </c>
       <c r="H310" t="n">
-        <v>357.616943359375</v>
+        <v>357.6169738769531</v>
       </c>
       <c r="I310" t="n">
         <v>870.5060424804688</v>
@@ -10374,7 +10374,7 @@
         <v>45016</v>
       </c>
       <c r="B311" t="n">
-        <v>1637.881713867188</v>
+        <v>1637.8818359375</v>
       </c>
       <c r="C311" t="n">
         <v>993.0499877929688</v>
@@ -10386,13 +10386,13 @@
         <v>881.1500244140625</v>
       </c>
       <c r="F311" t="n">
-        <v>619.362548828125</v>
+        <v>619.3624877929688</v>
       </c>
       <c r="G311" t="n">
         <v>38.31999969482422</v>
       </c>
       <c r="H311" t="n">
-        <v>359.2384948730469</v>
+        <v>359.2384643554688</v>
       </c>
       <c r="I311" t="n">
         <v>866.5614013671875</v>
@@ -10406,7 +10406,7 @@
         <v>45019</v>
       </c>
       <c r="B312" t="n">
-        <v>1678.94677734375</v>
+        <v>1678.946655273438</v>
       </c>
       <c r="C312" t="n">
         <v>943.4000244140625</v>
@@ -10418,13 +10418,13 @@
         <v>837.4500122070312</v>
       </c>
       <c r="F312" t="n">
-        <v>615.34375</v>
+        <v>615.3438110351562</v>
       </c>
       <c r="G312" t="n">
         <v>38.11000061035156</v>
       </c>
       <c r="H312" t="n">
-        <v>368.3287353515625</v>
+        <v>368.3287658691406</v>
       </c>
       <c r="I312" t="n">
         <v>844.192138671875</v>
@@ -10438,13 +10438,13 @@
         <v>45021</v>
       </c>
       <c r="B313" t="n">
-        <v>1658.266845703125</v>
+        <v>1658.266723632812</v>
       </c>
       <c r="C313" t="n">
         <v>907.8499755859375</v>
       </c>
       <c r="D313" t="n">
-        <v>1694.916137695312</v>
+        <v>1694.916259765625</v>
       </c>
       <c r="E313" t="n">
         <v>815.5999755859375</v>
@@ -10470,13 +10470,13 @@
         <v>45022</v>
       </c>
       <c r="B314" t="n">
-        <v>1681.893920898438</v>
+        <v>1681.893798828125</v>
       </c>
       <c r="C314" t="n">
         <v>953.2000122070312</v>
       </c>
       <c r="D314" t="n">
-        <v>1750.864379882812</v>
+        <v>1750.864501953125</v>
       </c>
       <c r="E314" t="n">
         <v>856.3499755859375</v>
@@ -10502,7 +10502,7 @@
         <v>45026</v>
       </c>
       <c r="B315" t="n">
-        <v>1710.334838867188</v>
+        <v>1710.334716796875</v>
       </c>
       <c r="C315" t="n">
         <v>1000.849975585938</v>
@@ -10520,10 +10520,10 @@
         <v>38.79999923706055</v>
       </c>
       <c r="H315" t="n">
-        <v>377.7138671875</v>
+        <v>377.7138977050781</v>
       </c>
       <c r="I315" t="n">
-        <v>904.9088134765625</v>
+        <v>904.9088745117188</v>
       </c>
       <c r="J315" t="n">
         <v>195.25</v>
@@ -10534,7 +10534,7 @@
         <v>45027</v>
       </c>
       <c r="B316" t="n">
-        <v>1706.84716796875</v>
+        <v>1706.847290039062</v>
       </c>
       <c r="C316" t="n">
         <v>1050.849975585938</v>
@@ -10546,7 +10546,7 @@
         <v>944.0999755859375</v>
       </c>
       <c r="F316" t="n">
-        <v>640.9750366210938</v>
+        <v>640.9749755859375</v>
       </c>
       <c r="G316" t="n">
         <v>38.79999923706055</v>
@@ -10566,7 +10566,7 @@
         <v>45028</v>
       </c>
       <c r="B317" t="n">
-        <v>1727.0849609375</v>
+        <v>1727.085083007812</v>
       </c>
       <c r="C317" t="n">
         <v>1043.449951171875</v>
@@ -10587,7 +10587,7 @@
         <v>389.2118835449219</v>
       </c>
       <c r="I317" t="n">
-        <v>937.56396484375</v>
+        <v>937.5640258789062</v>
       </c>
       <c r="J317" t="n">
         <v>187</v>
@@ -10598,7 +10598,7 @@
         <v>45029</v>
       </c>
       <c r="B318" t="n">
-        <v>1736.466918945312</v>
+        <v>1736.467163085938</v>
       </c>
       <c r="C318" t="n">
         <v>1030.849975585938</v>
@@ -10616,7 +10616,7 @@
         <v>37.83000183105469</v>
       </c>
       <c r="H318" t="n">
-        <v>385.8705749511719</v>
+        <v>385.87060546875</v>
       </c>
       <c r="I318" t="n">
         <v>912.8978881835938</v>
@@ -10636,7 +10636,7 @@
         <v>1039.5</v>
       </c>
       <c r="D319" t="n">
-        <v>1875.337768554688</v>
+        <v>1875.337890625</v>
       </c>
       <c r="E319" t="n">
         <v>962.5499877929688</v>
@@ -10651,7 +10651,7 @@
         <v>384.78955078125</v>
       </c>
       <c r="I319" t="n">
-        <v>945.503173828125</v>
+        <v>945.5031127929688</v>
       </c>
       <c r="J319" t="n">
         <v>188.1999969482422</v>
@@ -10662,28 +10662,28 @@
         <v>45034</v>
       </c>
       <c r="B320" t="n">
-        <v>1729.14794921875</v>
+        <v>1729.148071289062</v>
       </c>
       <c r="C320" t="n">
         <v>1032.050048828125</v>
       </c>
       <c r="D320" t="n">
-        <v>1847.588256835938</v>
+        <v>1847.58837890625</v>
       </c>
       <c r="E320" t="n">
         <v>952.25</v>
       </c>
       <c r="F320" t="n">
-        <v>645.483642578125</v>
+        <v>645.4837036132812</v>
       </c>
       <c r="G320" t="n">
         <v>37.66999816894531</v>
       </c>
       <c r="H320" t="n">
-        <v>376.4363098144531</v>
+        <v>376.4363403320312</v>
       </c>
       <c r="I320" t="n">
-        <v>946.7513427734375</v>
+        <v>946.75146484375</v>
       </c>
       <c r="J320" t="n">
         <v>187.1000061035156</v>
@@ -10706,7 +10706,7 @@
         <v>935.7999877929688</v>
       </c>
       <c r="F321" t="n">
-        <v>645.3367309570312</v>
+        <v>645.336669921875</v>
       </c>
       <c r="G321" t="n">
         <v>37.45999908447266</v>
@@ -10744,7 +10744,7 @@
         <v>39.15999984741211</v>
       </c>
       <c r="H322" t="n">
-        <v>374.1269226074219</v>
+        <v>374.1268920898438</v>
       </c>
       <c r="I322" t="n">
         <v>926.9285888671875</v>
@@ -10758,7 +10758,7 @@
         <v>45037</v>
       </c>
       <c r="B323" t="n">
-        <v>1687.7392578125</v>
+        <v>1687.739135742188</v>
       </c>
       <c r="C323" t="n">
         <v>994.9000244140625</v>
@@ -10776,10 +10776,10 @@
         <v>39.84999847412109</v>
       </c>
       <c r="H323" t="n">
-        <v>368.6236267089844</v>
+        <v>368.6235961914062</v>
       </c>
       <c r="I323" t="n">
-        <v>916.5428466796875</v>
+        <v>916.5427856445312</v>
       </c>
       <c r="J323" t="n">
         <v>183.6999969482422</v>
@@ -10802,7 +10802,7 @@
         <v>887.0999755859375</v>
       </c>
       <c r="F324" t="n">
-        <v>657.980712890625</v>
+        <v>657.9807739257812</v>
       </c>
       <c r="G324" t="n">
         <v>40.27999877929688</v>
@@ -10822,19 +10822,19 @@
         <v>45041</v>
       </c>
       <c r="B325" t="n">
-        <v>1705.619140625</v>
+        <v>1705.619384765625</v>
       </c>
       <c r="C325" t="n">
         <v>1012.950012207031</v>
       </c>
       <c r="D325" t="n">
-        <v>1841.249755859375</v>
+        <v>1841.249877929688</v>
       </c>
       <c r="E325" t="n">
         <v>931.1500244140625</v>
       </c>
       <c r="F325" t="n">
-        <v>658.1277465820312</v>
+        <v>658.1278076171875</v>
       </c>
       <c r="G325" t="n">
         <v>41.13000106811523</v>
@@ -10892,7 +10892,7 @@
         <v>982.2999877929688</v>
       </c>
       <c r="D327" t="n">
-        <v>1849.6845703125</v>
+        <v>1849.684448242188</v>
       </c>
       <c r="E327" t="n">
         <v>917.0499877929688</v>
@@ -10904,7 +10904,7 @@
         <v>42.83000183105469</v>
       </c>
       <c r="H327" t="n">
-        <v>382.0870361328125</v>
+        <v>382.0870666503906</v>
       </c>
       <c r="I327" t="n">
         <v>915.84375</v>
@@ -10930,7 +10930,7 @@
         <v>951</v>
       </c>
       <c r="F328" t="n">
-        <v>667.7822265625</v>
+        <v>667.7822875976562</v>
       </c>
       <c r="G328" t="n">
         <v>44.97000122070312</v>
@@ -10971,7 +10971,7 @@
         <v>387.5903625488281</v>
       </c>
       <c r="I329" t="n">
-        <v>957.736328125</v>
+        <v>957.7363891601562</v>
       </c>
       <c r="J329" t="n">
         <v>185.6999969482422</v>
@@ -10982,25 +10982,25 @@
         <v>45049</v>
       </c>
       <c r="B330" t="n">
-        <v>1712.938232421875</v>
+        <v>1712.938110351562</v>
       </c>
       <c r="C330" t="n">
         <v>993.0499877929688</v>
       </c>
       <c r="D330" t="n">
-        <v>1835.66015625</v>
+        <v>1835.660034179688</v>
       </c>
       <c r="E330" t="n">
         <v>942.0499877929688</v>
       </c>
       <c r="F330" t="n">
-        <v>656.3634643554688</v>
+        <v>656.363525390625</v>
       </c>
       <c r="G330" t="n">
         <v>46.33000183105469</v>
       </c>
       <c r="H330" t="n">
-        <v>377.0259704589844</v>
+        <v>377.0260009765625</v>
       </c>
       <c r="I330" t="n">
         <v>921.685791015625</v>
@@ -11014,7 +11014,7 @@
         <v>45050</v>
       </c>
       <c r="B331" t="n">
-        <v>1735.238891601562</v>
+        <v>1735.239013671875</v>
       </c>
       <c r="C331" t="n">
         <v>1011.549987792969</v>
@@ -11046,7 +11046,7 @@
         <v>45051</v>
       </c>
       <c r="B332" t="n">
-        <v>1733.617919921875</v>
+        <v>1733.618041992188</v>
       </c>
       <c r="C332" t="n">
         <v>999</v>
@@ -11058,7 +11058,7 @@
         <v>940.5499877929688</v>
       </c>
       <c r="F332" t="n">
-        <v>670.3306884765625</v>
+        <v>670.3307495117188</v>
       </c>
       <c r="G332" t="n">
         <v>47.97000122070312</v>
@@ -11090,7 +11090,7 @@
         <v>917.2999877929688</v>
       </c>
       <c r="F333" t="n">
-        <v>671.5068969726562</v>
+        <v>671.5068359375</v>
       </c>
       <c r="G333" t="n">
         <v>47.7400016784668</v>
@@ -11110,7 +11110,7 @@
         <v>45055</v>
       </c>
       <c r="B334" t="n">
-        <v>1728.362182617188</v>
+        <v>1728.362060546875</v>
       </c>
       <c r="C334" t="n">
         <v>901.5999755859375</v>
@@ -11122,7 +11122,7 @@
         <v>903.1500244140625</v>
       </c>
       <c r="F334" t="n">
-        <v>676.7997436523438</v>
+        <v>676.7998046875</v>
       </c>
       <c r="G334" t="n">
         <v>48.06000137329102</v>
@@ -11154,7 +11154,7 @@
         <v>902.3499755859375</v>
       </c>
       <c r="F335" t="n">
-        <v>677.289794921875</v>
+        <v>677.2898559570312</v>
       </c>
       <c r="G335" t="n">
         <v>47.63999938964844</v>
@@ -11174,7 +11174,7 @@
         <v>45057</v>
       </c>
       <c r="B336" t="n">
-        <v>1754.739990234375</v>
+        <v>1754.739868164062</v>
       </c>
       <c r="C336" t="n">
         <v>917.25</v>
@@ -11244,7 +11244,7 @@
         <v>840.5999755859375</v>
       </c>
       <c r="D338" t="n">
-        <v>1912.570068359375</v>
+        <v>1912.570190429688</v>
       </c>
       <c r="E338" t="n">
         <v>868.7000122070312</v>
@@ -11259,7 +11259,7 @@
         <v>399.5797119140625</v>
       </c>
       <c r="I338" t="n">
-        <v>776.3851318359375</v>
+        <v>776.3851928710938</v>
       </c>
       <c r="J338" t="n">
         <v>178.6000061035156</v>
@@ -11270,7 +11270,7 @@
         <v>45062</v>
       </c>
       <c r="B339" t="n">
-        <v>1752.136596679688</v>
+        <v>1752.136474609375</v>
       </c>
       <c r="C339" t="n">
         <v>812.0999755859375</v>
@@ -11291,7 +11291,7 @@
         <v>393.9781188964844</v>
       </c>
       <c r="I339" t="n">
-        <v>737.5882568359375</v>
+        <v>737.5883178710938</v>
       </c>
       <c r="J339" t="n">
         <v>175.6499938964844</v>
@@ -11314,7 +11314,7 @@
         <v>875.4000244140625</v>
       </c>
       <c r="F340" t="n">
-        <v>671.0167236328125</v>
+        <v>671.0167846679688</v>
       </c>
       <c r="G340" t="n">
         <v>46.86999893188477</v>
@@ -11323,7 +11323,7 @@
         <v>399.284912109375</v>
       </c>
       <c r="I340" t="n">
-        <v>700.7388305664062</v>
+        <v>700.7388916015625</v>
       </c>
       <c r="J340" t="n">
         <v>173</v>
@@ -11340,13 +11340,13 @@
         <v>751.5999755859375</v>
       </c>
       <c r="D341" t="n">
-        <v>1886.567504882812</v>
+        <v>1886.5673828125</v>
       </c>
       <c r="E341" t="n">
         <v>860.5499877929688</v>
       </c>
       <c r="F341" t="n">
-        <v>651.7567138671875</v>
+        <v>651.7567749023438</v>
       </c>
       <c r="G341" t="n">
         <v>45.0099983215332</v>
@@ -11416,10 +11416,10 @@
         <v>49.58000183105469</v>
       </c>
       <c r="H343" t="n">
-        <v>416.5810546875</v>
+        <v>416.5810241699219</v>
       </c>
       <c r="I343" t="n">
-        <v>721.5103149414062</v>
+        <v>721.5103759765625</v>
       </c>
       <c r="J343" t="n">
         <v>186.9499969482422</v>
@@ -11442,13 +11442,13 @@
         <v>988.7999877929688</v>
       </c>
       <c r="F344" t="n">
-        <v>719.4857177734375</v>
+        <v>719.4856567382812</v>
       </c>
       <c r="G344" t="n">
         <v>52.04999923706055</v>
       </c>
       <c r="H344" t="n">
-        <v>419.9223327636719</v>
+        <v>419.9223022460938</v>
       </c>
       <c r="I344" t="n">
         <v>757.5609130859375</v>
@@ -11462,7 +11462,7 @@
         <v>45070</v>
       </c>
       <c r="B345" t="n">
-        <v>1749.091064453125</v>
+        <v>1749.090942382812</v>
       </c>
       <c r="C345" t="n">
         <v>911.4000244140625</v>
@@ -11494,7 +11494,7 @@
         <v>45071</v>
       </c>
       <c r="B346" t="n">
-        <v>1746.880615234375</v>
+        <v>1746.880737304688</v>
       </c>
       <c r="C346" t="n">
         <v>891.75</v>
@@ -11506,7 +11506,7 @@
         <v>970.6500244140625</v>
       </c>
       <c r="F346" t="n">
-        <v>710.1251831054688</v>
+        <v>710.125244140625</v>
       </c>
       <c r="G346" t="n">
         <v>51.83000183105469</v>
@@ -11515,7 +11515,7 @@
         <v>411.9621887207031</v>
       </c>
       <c r="I346" t="n">
-        <v>795.3092651367188</v>
+        <v>795.3092041015625</v>
       </c>
       <c r="J346" t="n">
         <v>216.3500061035156</v>
@@ -11558,13 +11558,13 @@
         <v>45075</v>
       </c>
       <c r="B348" t="n">
-        <v>1762.844970703125</v>
+        <v>1762.8447265625</v>
       </c>
       <c r="C348" t="n">
         <v>832.2000122070312</v>
       </c>
       <c r="D348" t="n">
-        <v>2529.447509765625</v>
+        <v>2529.44775390625</v>
       </c>
       <c r="E348" t="n">
         <v>977.8499755859375</v>
@@ -11576,10 +11576,10 @@
         <v>51.27999877929688</v>
       </c>
       <c r="H348" t="n">
-        <v>419.6275024414062</v>
+        <v>419.6274719238281</v>
       </c>
       <c r="I348" t="n">
-        <v>728.2012329101562</v>
+        <v>728.201171875</v>
       </c>
       <c r="J348" t="n">
         <v>238.5</v>
@@ -11596,22 +11596,22 @@
         <v>804.2999877929688</v>
       </c>
       <c r="D349" t="n">
-        <v>2491.916259765625</v>
+        <v>2491.916015625</v>
       </c>
       <c r="E349" t="n">
         <v>966.8499755859375</v>
       </c>
       <c r="F349" t="n">
-        <v>719.4857177734375</v>
+        <v>719.4856567382812</v>
       </c>
       <c r="G349" t="n">
         <v>50.22000122070312</v>
       </c>
       <c r="H349" t="n">
-        <v>423.4601745605469</v>
+        <v>423.4601440429688</v>
       </c>
       <c r="I349" t="n">
-        <v>697.0938110351562</v>
+        <v>697.0938720703125</v>
       </c>
       <c r="J349" t="n">
         <v>250.3999938964844</v>
@@ -11628,7 +11628,7 @@
         <v>776.7000122070312</v>
       </c>
       <c r="D350" t="n">
-        <v>2488.822021484375</v>
+        <v>2488.82177734375</v>
       </c>
       <c r="E350" t="n">
         <v>977.7000122070312</v>
@@ -11643,7 +11643,7 @@
         <v>416.2861938476562</v>
       </c>
       <c r="I350" t="n">
-        <v>663.2402954101562</v>
+        <v>663.2403564453125</v>
       </c>
       <c r="J350" t="n">
         <v>237.8999938964844</v>
@@ -11660,7 +11660,7 @@
         <v>815.5</v>
       </c>
       <c r="D351" t="n">
-        <v>2487.62353515625</v>
+        <v>2487.623779296875</v>
       </c>
       <c r="E351" t="n">
         <v>993.9500122070312</v>
@@ -11672,10 +11672,10 @@
         <v>50.83000183105469</v>
       </c>
       <c r="H351" t="n">
-        <v>421.8386535644531</v>
+        <v>421.838623046875</v>
       </c>
       <c r="I351" t="n">
-        <v>693.39892578125</v>
+        <v>693.3988647460938</v>
       </c>
       <c r="J351" t="n">
         <v>241</v>
@@ -11692,7 +11692,7 @@
         <v>794.6500244140625</v>
       </c>
       <c r="D352" t="n">
-        <v>2440.609619140625</v>
+        <v>2440.609375</v>
       </c>
       <c r="E352" t="n">
         <v>983.5499877929688</v>
@@ -11704,7 +11704,7 @@
         <v>51.13000106811523</v>
       </c>
       <c r="H352" t="n">
-        <v>430.4866943359375</v>
+        <v>430.4867248535156</v>
       </c>
       <c r="I352" t="n">
         <v>673.4762573242188</v>
@@ -11718,7 +11718,7 @@
         <v>45082</v>
       </c>
       <c r="B353" t="n">
-        <v>1778.612548828125</v>
+        <v>1778.612670898438</v>
       </c>
       <c r="C353" t="n">
         <v>828</v>
@@ -11736,7 +11736,7 @@
         <v>51.88999938964844</v>
       </c>
       <c r="H353" t="n">
-        <v>431.469482421875</v>
+        <v>431.4694519042969</v>
       </c>
       <c r="I353" t="n">
         <v>680.5665283203125</v>
@@ -11750,7 +11750,7 @@
         <v>45083</v>
       </c>
       <c r="B354" t="n">
-        <v>1823.65625</v>
+        <v>1823.656372070312</v>
       </c>
       <c r="C354" t="n">
         <v>816.25</v>
@@ -11768,10 +11768,10 @@
         <v>52.59999847412109</v>
       </c>
       <c r="H354" t="n">
-        <v>451.222412109375</v>
+        <v>451.2223815917969</v>
       </c>
       <c r="I354" t="n">
-        <v>677.4708251953125</v>
+        <v>677.4707641601562</v>
       </c>
       <c r="J354" t="n">
         <v>236.3000030517578</v>
@@ -11782,7 +11782,7 @@
         <v>45084</v>
       </c>
       <c r="B355" t="n">
-        <v>1819.186157226562</v>
+        <v>1819.186401367188</v>
       </c>
       <c r="C355" t="n">
         <v>837.25</v>
@@ -11794,13 +11794,13 @@
         <v>985.5499877929688</v>
       </c>
       <c r="F355" t="n">
-        <v>728.9932861328125</v>
+        <v>728.9932250976562</v>
       </c>
       <c r="G355" t="n">
         <v>54.97000122070312</v>
       </c>
       <c r="H355" t="n">
-        <v>447.8811340332031</v>
+        <v>447.881103515625</v>
       </c>
       <c r="I355" t="n">
         <v>679.1185302734375</v>
@@ -11832,7 +11832,7 @@
         <v>55.83000183105469</v>
       </c>
       <c r="H356" t="n">
-        <v>443.9010314941406</v>
+        <v>443.9010620117188</v>
       </c>
       <c r="I356" t="n">
         <v>669.9810791015625</v>
@@ -11852,7 +11852,7 @@
         <v>830.7000122070312</v>
       </c>
       <c r="D357" t="n">
-        <v>2446.697998046875</v>
+        <v>2446.6982421875</v>
       </c>
       <c r="E357" t="n">
         <v>963.6500244140625</v>
@@ -11864,7 +11864,7 @@
         <v>55.2400016784668</v>
       </c>
       <c r="H357" t="n">
-        <v>447.83203125</v>
+        <v>447.8320007324219</v>
       </c>
       <c r="I357" t="n">
         <v>668.1834716796875</v>
@@ -11890,7 +11890,7 @@
         <v>961.0999755859375</v>
       </c>
       <c r="F358" t="n">
-        <v>727.3759765625</v>
+        <v>727.3759155273438</v>
       </c>
       <c r="G358" t="n">
         <v>54.31000137329102</v>
@@ -11899,7 +11899,7 @@
         <v>448.4215698242188</v>
       </c>
       <c r="I358" t="n">
-        <v>669.2821044921875</v>
+        <v>669.2820434570312</v>
       </c>
       <c r="J358" t="n">
         <v>228.5500030517578</v>
@@ -11922,7 +11922,7 @@
         <v>955.2999877929688</v>
       </c>
       <c r="F359" t="n">
-        <v>723.2103271484375</v>
+        <v>723.2102661132812</v>
       </c>
       <c r="G359" t="n">
         <v>53.56000137329102</v>
@@ -11931,7 +11931,7 @@
         <v>451.02587890625</v>
       </c>
       <c r="I359" t="n">
-        <v>662.24169921875</v>
+        <v>662.2416381835938</v>
       </c>
       <c r="J359" t="n">
         <v>239.9499969482422</v>
@@ -11963,7 +11963,7 @@
         <v>456.5783081054688</v>
       </c>
       <c r="I360" t="n">
-        <v>653.4536743164062</v>
+        <v>653.4537353515625</v>
       </c>
       <c r="J360" t="n">
         <v>245.25</v>
@@ -11980,13 +11980,13 @@
         <v>814.7000122070312</v>
       </c>
       <c r="D361" t="n">
-        <v>2481.135498046875</v>
+        <v>2481.1357421875</v>
       </c>
       <c r="E361" t="n">
         <v>962.5999755859375</v>
       </c>
       <c r="F361" t="n">
-        <v>724.8275756835938</v>
+        <v>724.8275146484375</v>
       </c>
       <c r="G361" t="n">
         <v>53.84999847412109</v>
@@ -12006,13 +12006,13 @@
         <v>45093</v>
       </c>
       <c r="B362" t="n">
-        <v>1822.821166992188</v>
+        <v>1822.8212890625</v>
       </c>
       <c r="C362" t="n">
         <v>810.9000244140625</v>
       </c>
       <c r="D362" t="n">
-        <v>2505.04248046875</v>
+        <v>2505.042236328125</v>
       </c>
       <c r="E362" t="n">
         <v>975.0499877929688</v>
@@ -12044,13 +12044,13 @@
         <v>806.5999755859375</v>
       </c>
       <c r="D363" t="n">
-        <v>2397.03857421875</v>
+        <v>2397.038818359375</v>
       </c>
       <c r="E363" t="n">
         <v>960.3499755859375</v>
       </c>
       <c r="F363" t="n">
-        <v>721.053955078125</v>
+        <v>721.0540161132812</v>
       </c>
       <c r="G363" t="n">
         <v>52.72999954223633</v>
@@ -12059,7 +12059,7 @@
         <v>445.0311889648438</v>
       </c>
       <c r="I363" t="n">
-        <v>656.6493530273438</v>
+        <v>656.6492919921875</v>
       </c>
       <c r="J363" t="n">
         <v>232.3999938964844</v>
@@ -12070,25 +12070,25 @@
         <v>45097</v>
       </c>
       <c r="B364" t="n">
-        <v>1805.874389648438</v>
+        <v>1805.874633789062</v>
       </c>
       <c r="C364" t="n">
         <v>811.9500122070312</v>
       </c>
       <c r="D364" t="n">
-        <v>2410.4140625</v>
+        <v>2410.414306640625</v>
       </c>
       <c r="E364" t="n">
         <v>961.7000122070312</v>
       </c>
       <c r="F364" t="n">
-        <v>723.1612548828125</v>
+        <v>723.1613159179688</v>
       </c>
       <c r="G364" t="n">
         <v>52.34000015258789</v>
       </c>
       <c r="H364" t="n">
-        <v>441.1985168457031</v>
+        <v>441.1985473632812</v>
       </c>
       <c r="I364" t="n">
         <v>657.6978759765625</v>
@@ -12134,7 +12134,7 @@
         <v>45099</v>
       </c>
       <c r="B366" t="n">
-        <v>1799.5380859375</v>
+        <v>1799.537963867188</v>
       </c>
       <c r="C366" t="n">
         <v>804.4000244140625</v>
@@ -12152,7 +12152,7 @@
         <v>51.31999969482422</v>
       </c>
       <c r="H366" t="n">
-        <v>437.1693115234375</v>
+        <v>437.1693420410156</v>
       </c>
       <c r="I366" t="n">
         <v>654.252685546875</v>
@@ -12178,7 +12178,7 @@
         <v>959.8499755859375</v>
       </c>
       <c r="F367" t="n">
-        <v>700.1275024414062</v>
+        <v>700.1275634765625</v>
       </c>
       <c r="G367" t="n">
         <v>48.47999954223633</v>
@@ -12198,28 +12198,28 @@
         <v>45103</v>
       </c>
       <c r="B368" t="n">
-        <v>1760.781860351562</v>
+        <v>1760.78173828125</v>
       </c>
       <c r="C368" t="n">
         <v>770.75</v>
       </c>
       <c r="D368" t="n">
-        <v>2291.430908203125</v>
+        <v>2291.4306640625</v>
       </c>
       <c r="E368" t="n">
         <v>968.4500122070312</v>
       </c>
       <c r="F368" t="n">
-        <v>710.0271606445312</v>
+        <v>710.0272216796875</v>
       </c>
       <c r="G368" t="n">
         <v>50.11999893188477</v>
       </c>
       <c r="H368" t="n">
-        <v>424.59033203125</v>
+        <v>424.5902709960938</v>
       </c>
       <c r="I368" t="n">
-        <v>643.1178588867188</v>
+        <v>643.117919921875</v>
       </c>
       <c r="J368" t="n">
         <v>224.8999938964844</v>
@@ -12248,7 +12248,7 @@
         <v>50.61999893188477</v>
       </c>
       <c r="H369" t="n">
-        <v>426.3592529296875</v>
+        <v>426.3592834472656</v>
       </c>
       <c r="I369" t="n">
         <v>640.621337890625</v>
@@ -12262,13 +12262,13 @@
         <v>45105</v>
       </c>
       <c r="B370" t="n">
-        <v>1780.479125976562</v>
+        <v>1780.479248046875</v>
       </c>
       <c r="C370" t="n">
         <v>819.1500244140625</v>
       </c>
       <c r="D370" t="n">
-        <v>2397.6376953125</v>
+        <v>2397.637451171875</v>
       </c>
       <c r="E370" t="n">
         <v>956.6500244140625</v>
@@ -12283,7 +12283,7 @@
         <v>426.7523498535156</v>
       </c>
       <c r="I370" t="n">
-        <v>653.6034545898438</v>
+        <v>653.603515625</v>
       </c>
       <c r="J370" t="n">
         <v>230.8500061035156</v>
@@ -12294,13 +12294,13 @@
         <v>45107</v>
       </c>
       <c r="B371" t="n">
-        <v>1781.805297851562</v>
+        <v>1781.805419921875</v>
       </c>
       <c r="C371" t="n">
         <v>767.25</v>
       </c>
       <c r="D371" t="n">
-        <v>2383.712646484375</v>
+        <v>2383.712890625</v>
       </c>
       <c r="E371" t="n">
         <v>945.9000244140625</v>
@@ -12315,7 +12315,7 @@
         <v>418.5464782714844</v>
       </c>
       <c r="I371" t="n">
-        <v>653.703369140625</v>
+        <v>653.7033081054688</v>
       </c>
       <c r="J371" t="n">
         <v>227.3999938964844</v>
@@ -12326,7 +12326,7 @@
         <v>45110</v>
       </c>
       <c r="B372" t="n">
-        <v>1793.005004882812</v>
+        <v>1793.0048828125</v>
       </c>
       <c r="C372" t="n">
         <v>773.25</v>
@@ -12358,7 +12358,7 @@
         <v>45111</v>
       </c>
       <c r="B373" t="n">
-        <v>1788.436645507812</v>
+        <v>1788.436767578125</v>
       </c>
       <c r="C373" t="n">
         <v>770.5999755859375</v>
@@ -12370,13 +12370,13 @@
         <v>946</v>
       </c>
       <c r="F373" t="n">
-        <v>726.98388671875</v>
+        <v>726.9839477539062</v>
       </c>
       <c r="G373" t="n">
         <v>49.41999816894531</v>
       </c>
       <c r="H373" t="n">
-        <v>425.2290954589844</v>
+        <v>425.2290649414062</v>
       </c>
       <c r="I373" t="n">
         <v>649.2594604492188</v>
@@ -12408,7 +12408,7 @@
         <v>49.13000106811523</v>
       </c>
       <c r="H374" t="n">
-        <v>424.9342956542969</v>
+        <v>424.9342651367188</v>
       </c>
       <c r="I374" t="n">
         <v>649.0098266601562</v>
@@ -12422,13 +12422,13 @@
         <v>45113</v>
       </c>
       <c r="B375" t="n">
-        <v>1788.338500976562</v>
+        <v>1788.338623046875</v>
       </c>
       <c r="C375" t="n">
         <v>769.3499755859375</v>
       </c>
       <c r="D375" t="n">
-        <v>2398.53564453125</v>
+        <v>2398.535888671875</v>
       </c>
       <c r="E375" t="n">
         <v>962.2000122070312</v>
@@ -12443,7 +12443,7 @@
         <v>424.0497741699219</v>
       </c>
       <c r="I375" t="n">
-        <v>647.861328125</v>
+        <v>647.8613891601562</v>
       </c>
       <c r="J375" t="n">
         <v>227</v>
@@ -12536,7 +12536,7 @@
         <v>48.84000015258789</v>
       </c>
       <c r="H378" t="n">
-        <v>414.9065246582031</v>
+        <v>414.9065551757812</v>
       </c>
       <c r="I378" t="n">
         <v>640.2688598632812</v>
@@ -12568,7 +12568,7 @@
         <v>48.16999816894531</v>
       </c>
       <c r="H379" t="n">
-        <v>416.685791015625</v>
+        <v>416.6857604980469</v>
       </c>
       <c r="I379" t="n">
         <v>635.0740356445312</v>
@@ -12600,7 +12600,7 @@
         <v>47.43999862670898</v>
       </c>
       <c r="H380" t="n">
-        <v>412.0894165039062</v>
+        <v>412.0894470214844</v>
       </c>
       <c r="I380" t="n">
         <v>629.6293334960938</v>
@@ -12696,7 +12696,7 @@
         <v>49.31000137329102</v>
       </c>
       <c r="H383" t="n">
-        <v>411.3974914550781</v>
+        <v>411.3975219726562</v>
       </c>
       <c r="I383" t="n">
         <v>645.114013671875</v>
@@ -12722,7 +12722,7 @@
         <v>979.6500244140625</v>
       </c>
       <c r="F384" t="n">
-        <v>716.8882446289062</v>
+        <v>716.8883056640625</v>
       </c>
       <c r="G384" t="n">
         <v>49.13999938964844</v>
@@ -12754,7 +12754,7 @@
         <v>985</v>
       </c>
       <c r="F385" t="n">
-        <v>717.9174194335938</v>
+        <v>717.91748046875</v>
       </c>
       <c r="G385" t="n">
         <v>48.83000183105469</v>
@@ -12882,7 +12882,7 @@
         <v>1140.400024414062</v>
       </c>
       <c r="F389" t="n">
-        <v>737.7166748046875</v>
+        <v>737.7167358398438</v>
       </c>
       <c r="G389" t="n">
         <v>51.09999847412109</v>
@@ -12914,13 +12914,13 @@
         <v>1119.199951171875</v>
       </c>
       <c r="F390" t="n">
-        <v>733.8939819335938</v>
+        <v>733.89404296875</v>
       </c>
       <c r="G390" t="n">
         <v>50.59999847412109</v>
       </c>
       <c r="H390" t="n">
-        <v>444.5603637695312</v>
+        <v>444.5603942871094</v>
       </c>
       <c r="I390" t="n">
         <v>653.8056030273438</v>
@@ -13016,7 +13016,7 @@
         <v>54.63999938964844</v>
       </c>
       <c r="H393" t="n">
-        <v>456.2242431640625</v>
+        <v>456.2242126464844</v>
       </c>
       <c r="I393" t="n">
         <v>660.9984741210938</v>
@@ -13080,7 +13080,7 @@
         <v>54.97000122070312</v>
       </c>
       <c r="H395" t="n">
-        <v>468.8764953613281</v>
+        <v>468.8765258789062</v>
       </c>
       <c r="I395" t="n">
         <v>654.8544921875</v>
@@ -13144,7 +13144,7 @@
         <v>54.65999984741211</v>
       </c>
       <c r="H397" t="n">
-        <v>468.6294250488281</v>
+        <v>468.62939453125</v>
       </c>
       <c r="I397" t="n">
         <v>650.0592041015625</v>
@@ -13304,7 +13304,7 @@
         <v>57.22000122070312</v>
       </c>
       <c r="H402" t="n">
-        <v>435.8619079589844</v>
+        <v>435.8619384765625</v>
       </c>
       <c r="I402" t="n">
         <v>634.9740600585938</v>
@@ -13400,7 +13400,7 @@
         <v>60.91999816894531</v>
       </c>
       <c r="H405" t="n">
-        <v>447.822265625</v>
+        <v>447.8222961425781</v>
       </c>
       <c r="I405" t="n">
         <v>653.8554077148438</v>
@@ -13464,7 +13464,7 @@
         <v>69.48000335693359</v>
       </c>
       <c r="H407" t="n">
-        <v>458.4482421875</v>
+        <v>458.4482727050781</v>
       </c>
       <c r="I407" t="n">
         <v>671.8876342773438</v>
@@ -13528,7 +13528,7 @@
         <v>65.76000213623047</v>
       </c>
       <c r="H409" t="n">
-        <v>443.7696228027344</v>
+        <v>443.7695922851562</v>
       </c>
       <c r="I409" t="n">
         <v>661.2481689453125</v>
@@ -13784,7 +13784,7 @@
         <v>68.48999786376953</v>
       </c>
       <c r="H417" t="n">
-        <v>435.12060546875</v>
+        <v>435.1205749511719</v>
       </c>
       <c r="I417" t="n">
         <v>632.7763061523438</v>
@@ -13816,7 +13816,7 @@
         <v>69.51000213623047</v>
       </c>
       <c r="H418" t="n">
-        <v>432.6988525390625</v>
+        <v>432.6988220214844</v>
       </c>
       <c r="I418" t="n">
         <v>644.0651245117188</v>
@@ -13880,7 +13880,7 @@
         <v>73.83000183105469</v>
       </c>
       <c r="H420" t="n">
-        <v>434.1321411132812</v>
+        <v>434.1321105957031</v>
       </c>
       <c r="I420" t="n">
         <v>644.1649780273438</v>
@@ -13912,7 +13912,7 @@
         <v>79.68000030517578</v>
       </c>
       <c r="H421" t="n">
-        <v>445.6971130371094</v>
+        <v>445.6970825195312</v>
       </c>
       <c r="I421" t="n">
         <v>658.2510986328125</v>
@@ -14072,7 +14072,7 @@
         <v>75</v>
       </c>
       <c r="H426" t="n">
-        <v>431.6115417480469</v>
+        <v>431.6115112304688</v>
       </c>
       <c r="I426" t="n">
         <v>638.5206298828125</v>
@@ -14296,7 +14296,7 @@
         <v>75.08000183105469</v>
       </c>
       <c r="H433" t="n">
-        <v>415.0547790527344</v>
+        <v>415.0548095703125</v>
       </c>
       <c r="I433" t="n">
         <v>621.5372924804688</v>
@@ -14328,7 +14328,7 @@
         <v>75.48999786376953</v>
       </c>
       <c r="H434" t="n">
-        <v>419.8982849121094</v>
+        <v>419.8982543945312</v>
       </c>
       <c r="I434" t="n">
         <v>612.6460571289062</v>
@@ -14456,7 +14456,7 @@
         <v>72.86000061035156</v>
       </c>
       <c r="H438" t="n">
-        <v>430.6725158691406</v>
+        <v>430.6724853515625</v>
       </c>
       <c r="I438" t="n">
         <v>604.0045776367188</v>
@@ -14648,7 +14648,7 @@
         <v>65.93000030517578</v>
       </c>
       <c r="H444" t="n">
-        <v>438.1353759765625</v>
+        <v>438.1353454589844</v>
       </c>
       <c r="I444" t="n">
         <v>594.6138916015625</v>
@@ -14680,7 +14680,7 @@
         <v>67.09999847412109</v>
       </c>
       <c r="H445" t="n">
-        <v>437.5423278808594</v>
+        <v>437.5422973632812</v>
       </c>
       <c r="I445" t="n">
         <v>594.9635009765625</v>
@@ -14712,7 +14712,7 @@
         <v>66.79000091552734</v>
       </c>
       <c r="H446" t="n">
-        <v>428.0036315917969</v>
+        <v>428.003662109375</v>
       </c>
       <c r="I446" t="n">
         <v>592.4659423828125</v>
@@ -14744,7 +14744,7 @@
         <v>68.88999938964844</v>
       </c>
       <c r="H447" t="n">
-        <v>432.4022827148438</v>
+        <v>432.4023132324219</v>
       </c>
       <c r="I447" t="n">
         <v>591.3670654296875</v>
@@ -14872,7 +14872,7 @@
         <v>65.47000122070312</v>
       </c>
       <c r="H451" t="n">
-        <v>411.4963073730469</v>
+        <v>411.496337890625</v>
       </c>
       <c r="I451" t="n">
         <v>533.224365234375</v>
@@ -15032,7 +15032,7 @@
         <v>74.58999633789062</v>
       </c>
       <c r="H456" t="n">
-        <v>414.8571166992188</v>
+        <v>414.8571472167969</v>
       </c>
       <c r="I456" t="n">
         <v>553.2545776367188</v>
@@ -15224,7 +15224,7 @@
         <v>79.87999725341797</v>
       </c>
       <c r="H462" t="n">
-        <v>413.2756042480469</v>
+        <v>413.2755737304688</v>
       </c>
       <c r="I462" t="n">
         <v>538.9686889648438</v>
@@ -15288,7 +15288,7 @@
         <v>78.19999694824219</v>
       </c>
       <c r="H464" t="n">
-        <v>413.3250122070312</v>
+        <v>413.3249816894531</v>
       </c>
       <c r="I464" t="n">
         <v>539.218505859375</v>
@@ -15320,7 +15320,7 @@
         <v>77.91000366210938</v>
       </c>
       <c r="H465" t="n">
-        <v>415.0547790527344</v>
+        <v>415.0548095703125</v>
       </c>
       <c r="I465" t="n">
         <v>535.9217529296875</v>
@@ -15352,7 +15352,7 @@
         <v>77.45999908447266</v>
       </c>
       <c r="H466" t="n">
-        <v>416.240966796875</v>
+        <v>416.2409973144531</v>
       </c>
       <c r="I466" t="n">
         <v>533.5240478515625</v>
@@ -15384,7 +15384,7 @@
         <v>77.98999786376953</v>
       </c>
       <c r="H467" t="n">
-        <v>416.6363830566406</v>
+        <v>416.6363525390625</v>
       </c>
       <c r="I467" t="n">
         <v>530.527099609375</v>
@@ -15544,7 +15544,7 @@
         <v>89.23999786376953</v>
       </c>
       <c r="H472" t="n">
-        <v>426.2244567871094</v>
+        <v>426.2244262695312</v>
       </c>
       <c r="I472" t="n">
         <v>643.5656127929688</v>
@@ -15576,7 +15576,7 @@
         <v>86.62000274658203</v>
       </c>
       <c r="H473" t="n">
-        <v>430.6230773925781</v>
+        <v>430.623046875</v>
       </c>
       <c r="I473" t="n">
         <v>731.82861328125</v>
@@ -15704,7 +15704,7 @@
         <v>107.629997253418</v>
       </c>
       <c r="H477" t="n">
-        <v>503.1761169433594</v>
+        <v>503.1760864257812</v>
       </c>
       <c r="I477" t="n">
         <v>876.9855346679688</v>
@@ -15768,7 +15768,7 @@
         <v>112.4800033569336</v>
       </c>
       <c r="H479" t="n">
-        <v>499.2716979980469</v>
+        <v>499.271728515625</v>
       </c>
       <c r="I479" t="n">
         <v>1157.459106445312</v>
@@ -15864,7 +15864,7 @@
         <v>103.3899993896484</v>
       </c>
       <c r="H482" t="n">
-        <v>495.5649719238281</v>
+        <v>495.56494140625</v>
       </c>
       <c r="I482" t="n">
         <v>1113.102783203125</v>
@@ -15896,7 +15896,7 @@
         <v>101.1399993896484</v>
       </c>
       <c r="H483" t="n">
-        <v>503.1761169433594</v>
+        <v>503.1760864257812</v>
       </c>
       <c r="I483" t="n">
         <v>1003.560729980469</v>
@@ -15960,7 +15960,7 @@
         <v>107.7699966430664</v>
       </c>
       <c r="H485" t="n">
-        <v>516.3720703125</v>
+        <v>516.3721313476562</v>
       </c>
       <c r="I485" t="n">
         <v>1045.9189453125</v>
@@ -16024,7 +16024,7 @@
         <v>107.0899963378906</v>
       </c>
       <c r="H487" t="n">
-        <v>516.3226318359375</v>
+        <v>516.3226928710938</v>
       </c>
       <c r="I487" t="n">
         <v>1025.239379882812</v>
@@ -16216,7 +16216,7 @@
         <v>104.6800003051758</v>
       </c>
       <c r="H493" t="n">
-        <v>508.3161010742188</v>
+        <v>508.3161315917969</v>
       </c>
       <c r="I493" t="n">
         <v>979.3845825195312</v>
@@ -16280,7 +16280,7 @@
         <v>104.6500015258789</v>
       </c>
       <c r="H495" t="n">
-        <v>528.134765625</v>
+        <v>528.1347045898438</v>
       </c>
       <c r="I495" t="n">
         <v>999.9642944335938</v>
@@ -16376,7 +16376,7 @@
         <v>111.7099990844727</v>
       </c>
       <c r="H498" t="n">
-        <v>543.1099853515625</v>
+        <v>543.1099243164062</v>
       </c>
       <c r="I498" t="n">
         <v>1114.001831054688</v>
@@ -16440,7 +16440,7 @@
         <v>108.3399963378906</v>
       </c>
       <c r="H500" t="n">
-        <v>524.0821533203125</v>
+        <v>524.0820922851562</v>
       </c>
       <c r="I500" t="n">
         <v>1067.197998046875</v>
@@ -16664,7 +16664,7 @@
         <v>104.2900009155273</v>
       </c>
       <c r="H507" t="n">
-        <v>514.5433959960938</v>
+        <v>514.5433349609375</v>
       </c>
       <c r="I507" t="n">
         <v>1003.111145019531</v>
@@ -16728,7 +16728,7 @@
         <v>103.3499984741211</v>
       </c>
       <c r="H509" t="n">
-        <v>530.9024658203125</v>
+        <v>530.9024047851562</v>
       </c>
       <c r="I509" t="n">
         <v>989.5245971679688</v>
@@ -16792,7 +16792,7 @@
         <v>103.9899978637695</v>
       </c>
       <c r="H511" t="n">
-        <v>521.3638305664062</v>
+        <v>521.36376953125</v>
       </c>
       <c r="I511" t="n">
         <v>1001.213134765625</v>
@@ -16856,7 +16856,7 @@
         <v>114.0899963378906</v>
       </c>
       <c r="H513" t="n">
-        <v>567.4754638671875</v>
+        <v>567.4755249023438</v>
       </c>
       <c r="I513" t="n">
         <v>1034.680053710938</v>
@@ -16984,7 +16984,7 @@
         <v>111.879997253418</v>
       </c>
       <c r="H517" t="n">
-        <v>550.9682006835938</v>
+        <v>550.96826171875</v>
       </c>
       <c r="I517" t="n">
         <v>998.2659912109375</v>
@@ -17048,7 +17048,7 @@
         <v>109.9400024414062</v>
       </c>
       <c r="H519" t="n">
-        <v>560.0620727539062</v>
+        <v>560.06201171875</v>
       </c>
       <c r="I519" t="n">
         <v>993.97021484375</v>
@@ -17080,7 +17080,7 @@
         <v>113.9400024414062</v>
       </c>
       <c r="H520" t="n">
-        <v>561.6436157226562</v>
+        <v>561.6436767578125</v>
       </c>
       <c r="I520" t="n">
         <v>1039.02587890625</v>
@@ -17208,7 +17208,7 @@
         <v>112.4199981689453</v>
       </c>
       <c r="H524" t="n">
-        <v>561.6929931640625</v>
+        <v>561.6930541992188</v>
       </c>
       <c r="I524" t="n">
         <v>1006.807556152344</v>
@@ -17240,7 +17240,7 @@
         <v>112.7799987792969</v>
       </c>
       <c r="H525" t="n">
-        <v>564.3124389648438</v>
+        <v>564.3123779296875</v>
       </c>
       <c r="I525" t="n">
         <v>1009.5048828125</v>
@@ -17272,7 +17272,7 @@
         <v>112.370002746582</v>
       </c>
       <c r="H526" t="n">
-        <v>565.6469116210938</v>
+        <v>565.6468505859375</v>
       </c>
       <c r="I526" t="n">
         <v>1006.457946777344</v>
@@ -17336,7 +17336,7 @@
         <v>113.5299987792969</v>
       </c>
       <c r="H528" t="n">
-        <v>578.1015014648438</v>
+        <v>578.1014404296875</v>
       </c>
       <c r="I528" t="n">
         <v>1010.703674316406</v>
@@ -17368,7 +17368,7 @@
         <v>110.7300033569336</v>
       </c>
       <c r="H529" t="n">
-        <v>582.0059204101562</v>
+        <v>582.005859375</v>
       </c>
       <c r="I529" t="n">
         <v>1011.053344726562</v>
@@ -17400,7 +17400,7 @@
         <v>108.1500015258789</v>
       </c>
       <c r="H530" t="n">
-        <v>581.0173950195312</v>
+        <v>581.0174560546875</v>
       </c>
       <c r="I530" t="n">
         <v>1020.044494628906</v>
@@ -17432,7 +17432,7 @@
         <v>112.4499969482422</v>
       </c>
       <c r="H531" t="n">
-        <v>585.9102783203125</v>
+        <v>585.9103393554688</v>
       </c>
       <c r="I531" t="n">
         <v>1017.147399902344</v>
@@ -17496,7 +17496,7 @@
         <v>114.0899963378906</v>
       </c>
       <c r="H533" t="n">
-        <v>601.577392578125</v>
+        <v>601.5773315429688</v>
       </c>
       <c r="I533" t="n">
         <v>1074.490966796875</v>
@@ -17592,7 +17592,7 @@
         <v>109.9899978637695</v>
       </c>
       <c r="H536" t="n">
-        <v>598.9086303710938</v>
+        <v>598.90869140625</v>
       </c>
       <c r="I536" t="n">
         <v>1024.64013671875</v>
@@ -17656,7 +17656,7 @@
         <v>111.9800033569336</v>
       </c>
       <c r="H538" t="n">
-        <v>610.0287475585938</v>
+        <v>610.02880859375</v>
       </c>
       <c r="I538" t="n">
         <v>1024.889770507812</v>
@@ -17720,7 +17720,7 @@
         <v>115.3399963378906</v>
       </c>
       <c r="H540" t="n">
-        <v>591.3963012695312</v>
+        <v>591.396240234375</v>
       </c>
       <c r="I540" t="n">
         <v>1004.859497070312</v>
@@ -17944,7 +17944,7 @@
         <v>105.879997253418</v>
       </c>
       <c r="H547" t="n">
-        <v>577.90380859375</v>
+        <v>577.9037475585938</v>
       </c>
       <c r="I547" t="n">
         <v>946.317138671875</v>
@@ -18168,7 +18168,7 @@
         <v>106.7600021362305</v>
       </c>
       <c r="H554" t="n">
-        <v>605.2840576171875</v>
+        <v>605.2841186523438</v>
       </c>
       <c r="I554" t="n">
         <v>925.6375122070312</v>
@@ -18232,7 +18232,7 @@
         <v>117.6900024414062</v>
       </c>
       <c r="H556" t="n">
-        <v>627.3762817382812</v>
+        <v>627.376220703125</v>
       </c>
       <c r="I556" t="n">
         <v>975.2886352539062</v>
@@ -18264,7 +18264,7 @@
         <v>123.5699996948242</v>
       </c>
       <c r="H557" t="n">
-        <v>627.6234130859375</v>
+        <v>627.6233520507812</v>
       </c>
       <c r="I557" t="n">
         <v>974.93896484375</v>
@@ -18552,7 +18552,7 @@
         <v>119.620002746582</v>
       </c>
       <c r="H566" t="n">
-        <v>608.1506958007812</v>
+        <v>608.150634765625</v>
       </c>
       <c r="I566" t="n">
         <v>919.243896484375</v>
@@ -18712,7 +18712,7 @@
         <v>118.4700012207031</v>
       </c>
       <c r="H571" t="n">
-        <v>630.9840698242188</v>
+        <v>630.984130859375</v>
       </c>
       <c r="I571" t="n">
         <v>917.2457885742188</v>
@@ -18744,7 +18744,7 @@
         <v>118.3199996948242</v>
       </c>
       <c r="H572" t="n">
-        <v>625.0533447265625</v>
+        <v>625.0532836914062</v>
       </c>
       <c r="I572" t="n">
         <v>918.244873046875</v>
@@ -18776,7 +18776,7 @@
         <v>119.2200012207031</v>
       </c>
       <c r="H573" t="n">
-        <v>622.384521484375</v>
+        <v>622.3845825195312</v>
       </c>
       <c r="I573" t="n">
         <v>918.1448974609375</v>
@@ -18872,7 +18872,7 @@
         <v>120.9400024414062</v>
       </c>
       <c r="H576" t="n">
-        <v>615.2676391601562</v>
+        <v>615.267578125</v>
       </c>
       <c r="I576" t="n">
         <v>929.4837646484375</v>
@@ -18904,7 +18904,7 @@
         <v>117.8099975585938</v>
       </c>
       <c r="H577" t="n">
-        <v>600.440673828125</v>
+        <v>600.4407348632812</v>
       </c>
       <c r="I577" t="n">
         <v>916.2468872070312</v>
@@ -19000,7 +19000,7 @@
         <v>122.5599975585938</v>
       </c>
       <c r="H580" t="n">
-        <v>567.6731567382812</v>
+        <v>567.6732177734375</v>
       </c>
       <c r="I580" t="n">
         <v>877.684814453125</v>
@@ -19064,7 +19064,7 @@
         <v>118.9800033569336</v>
       </c>
       <c r="H582" t="n">
-        <v>581.4127807617188</v>
+        <v>581.412841796875</v>
       </c>
       <c r="I582" t="n">
         <v>861.001220703125</v>
@@ -19160,7 +19160,7 @@
         <v>128.0700073242188</v>
       </c>
       <c r="H585" t="n">
-        <v>608.2990112304688</v>
+        <v>608.2989501953125</v>
       </c>
       <c r="I585" t="n">
         <v>905.906982421875</v>
@@ -19384,7 +19384,7 @@
         <v>135.7799987792969</v>
       </c>
       <c r="H592" t="n">
-        <v>622.384521484375</v>
+        <v>622.3845825195312</v>
       </c>
       <c r="I592" t="n">
         <v>950.7628173828125</v>
@@ -19576,7 +19576,7 @@
         <v>145.3300018310547</v>
       </c>
       <c r="H598" t="n">
-        <v>591.9893798828125</v>
+        <v>591.9894409179688</v>
       </c>
       <c r="I598" t="n">
         <v>935.3280029296875</v>
@@ -19800,7 +19800,7 @@
         <v>149.3500061035156</v>
       </c>
       <c r="H605" t="n">
-        <v>671.4066772460938</v>
+        <v>671.4066162109375</v>
       </c>
       <c r="I605" t="n">
         <v>945.8179321289062</v>
@@ -19832,7 +19832,7 @@
         <v>149.6300048828125</v>
       </c>
       <c r="H606" t="n">
-        <v>668.3331298828125</v>
+        <v>668.3331909179688</v>
       </c>
       <c r="I606" t="n">
         <v>939.5724487304688</v>
@@ -19864,7 +19864,7 @@
         <v>147.7299957275391</v>
       </c>
       <c r="H607" t="n">
-        <v>661.0955810546875</v>
+        <v>661.0956420898438</v>
       </c>
       <c r="I607" t="n">
         <v>926.7317504882812</v>
@@ -20024,7 +20024,7 @@
         <v>143.9799957275391</v>
       </c>
       <c r="H612" t="n">
-        <v>651.4290161132812</v>
+        <v>651.4290771484375</v>
       </c>
       <c r="I612" t="n">
         <v>893.006103515625</v>
@@ -20056,7 +20056,7 @@
         <v>143.1399993896484</v>
       </c>
       <c r="H613" t="n">
-        <v>654.998291015625</v>
+        <v>654.9982299804688</v>
       </c>
       <c r="I613" t="n">
         <v>902.1494140625</v>
@@ -20152,7 +20152,7 @@
         <v>142.1199951171875</v>
       </c>
       <c r="H616" t="n">
-        <v>686.4270629882812</v>
+        <v>686.427001953125</v>
       </c>
       <c r="I616" t="n">
         <v>903.9481201171875</v>
@@ -20504,7 +20504,7 @@
         <v>139.8999938964844</v>
       </c>
       <c r="H627" t="n">
-        <v>684.3450317382812</v>
+        <v>684.344970703125</v>
       </c>
       <c r="I627" t="n">
         <v>889.4585571289062</v>
@@ -20568,7 +20568,7 @@
         <v>139.2299957275391</v>
       </c>
       <c r="H629" t="n">
-        <v>681.221923828125</v>
+        <v>681.2219848632812</v>
       </c>
       <c r="I629" t="n">
         <v>885.4614868164062</v>
@@ -20600,7 +20600,7 @@
         <v>139.4799957275391</v>
       </c>
       <c r="H630" t="n">
-        <v>685.435546875</v>
+        <v>685.4356079101562</v>
       </c>
       <c r="I630" t="n">
         <v>878.5165405273438</v>
@@ -20952,7 +20952,7 @@
         <v>138.3800048828125</v>
       </c>
       <c r="H641" t="n">
-        <v>637.7966918945312</v>
+        <v>637.796630859375</v>
       </c>
       <c r="I641" t="n">
         <v>874.7692260742188</v>
@@ -20984,7 +20984,7 @@
         <v>138.3099975585938</v>
       </c>
       <c r="H642" t="n">
-        <v>633.0377197265625</v>
+        <v>633.0377807617188</v>
       </c>
       <c r="I642" t="n">
         <v>874.3694458007812</v>
@@ -21112,7 +21112,7 @@
         <v>134.8099975585938</v>
       </c>
       <c r="H646" t="n">
-        <v>617.86865234375</v>
+        <v>617.8685913085938</v>
       </c>
       <c r="I646" t="n">
         <v>842.642333984375</v>
@@ -21176,7 +21176,7 @@
         <v>139.3999938964844</v>
       </c>
       <c r="H648" t="n">
-        <v>628.2787475585938</v>
+        <v>628.27880859375</v>
       </c>
       <c r="I648" t="n">
         <v>855.73291015625</v>
@@ -21240,7 +21240,7 @@
         <v>139.0299987792969</v>
       </c>
       <c r="H650" t="n">
-        <v>623.8668212890625</v>
+        <v>623.8668823242188</v>
       </c>
       <c r="I650" t="n">
         <v>858.430908203125</v>
@@ -21304,7 +21304,7 @@
         <v>135.1600036621094</v>
       </c>
       <c r="H652" t="n">
-        <v>628.1795654296875</v>
+        <v>628.1796264648438</v>
       </c>
       <c r="I652" t="n">
         <v>857.6815185546875</v>
@@ -21400,7 +21400,7 @@
         <v>128.3099975585938</v>
       </c>
       <c r="H655" t="n">
-        <v>611.1267700195312</v>
+        <v>611.1268310546875</v>
       </c>
       <c r="I655" t="n">
         <v>848.1883544921875</v>
@@ -21432,7 +21432,7 @@
         <v>128.8600006103516</v>
       </c>
       <c r="H656" t="n">
-        <v>607.2601318359375</v>
+        <v>607.2601928710938</v>
       </c>
       <c r="I656" t="n">
         <v>836.896484375</v>
@@ -21464,7 +21464,7 @@
         <v>126.4100036621094</v>
       </c>
       <c r="H657" t="n">
-        <v>611.7711791992188</v>
+        <v>611.771240234375</v>
       </c>
       <c r="I657" t="n">
         <v>829.7516479492188</v>
@@ -21528,7 +21528,7 @@
         <v>131.8200073242188</v>
       </c>
       <c r="H659" t="n">
-        <v>612.5148315429688</v>
+        <v>612.5147705078125</v>
       </c>
       <c r="I659" t="n">
         <v>850.4866943359375</v>
@@ -21624,7 +21624,7 @@
         <v>126.9400024414062</v>
       </c>
       <c r="H662" t="n">
-        <v>617.918212890625</v>
+        <v>617.9181518554688</v>
       </c>
       <c r="I662" t="n">
         <v>826.1542358398438</v>
@@ -21656,7 +21656,7 @@
         <v>127.0400009155273</v>
       </c>
       <c r="H663" t="n">
-        <v>624.7592163085938</v>
+        <v>624.7591552734375</v>
       </c>
       <c r="I663" t="n">
         <v>814.1629028320312</v>
@@ -21720,7 +21720,7 @@
         <v>125.4400024414062</v>
       </c>
       <c r="H665" t="n">
-        <v>617.6703491210938</v>
+        <v>617.6702880859375</v>
       </c>
       <c r="I665" t="n">
         <v>804.2200317382812</v>
@@ -21784,7 +21784,7 @@
         <v>126.6900024414062</v>
       </c>
       <c r="H667" t="n">
-        <v>624.2138061523438</v>
+        <v>624.2138671875</v>
       </c>
       <c r="I667" t="n">
         <v>800.1729736328125</v>
@@ -21848,7 +21848,7 @@
         <v>133.2700042724609</v>
       </c>
       <c r="H669" t="n">
-        <v>617.6703491210938</v>
+        <v>617.6702880859375</v>
       </c>
       <c r="I669" t="n">
         <v>798.9238891601562</v>
@@ -21944,7 +21944,7 @@
         <v>133.0299987792969</v>
       </c>
       <c r="H672" t="n">
-        <v>611.2754516601562</v>
+        <v>611.2755126953125</v>
       </c>
       <c r="I672" t="n">
         <v>788.1316528320312</v>
@@ -22200,7 +22200,7 @@
         <v>128.9499969482422</v>
       </c>
       <c r="H680" t="n">
-        <v>612.1678466796875</v>
+        <v>612.1677856445312</v>
       </c>
       <c r="I680" t="n">
         <v>771.6935424804688</v>
@@ -22424,7 +22424,7 @@
         <v>126.8899993896484</v>
       </c>
       <c r="H687" t="n">
-        <v>583.8621215820312</v>
+        <v>583.862060546875</v>
       </c>
       <c r="I687" t="n">
         <v>753.8063354492188</v>
@@ -22488,7 +22488,7 @@
         <v>125.1600036621094</v>
       </c>
       <c r="H689" t="n">
-        <v>584.0108032226562</v>
+        <v>584.0107421875</v>
       </c>
       <c r="I689" t="n">
         <v>746.2618408203125</v>
@@ -22648,7 +22648,7 @@
         <v>117.5699996948242</v>
       </c>
       <c r="H694" t="n">
-        <v>551.0947875976562</v>
+        <v>551.0947265625</v>
       </c>
       <c r="I694" t="n">
         <v>699.9453125</v>
@@ -22712,7 +22712,7 @@
         <v>118.4599990844727</v>
       </c>
       <c r="H696" t="n">
-        <v>547.9717407226562</v>
+        <v>547.9718017578125</v>
       </c>
       <c r="I696" t="n">
         <v>723.628173828125</v>
@@ -22776,7 +22776,7 @@
         <v>118.4599990844727</v>
       </c>
       <c r="H698" t="n">
-        <v>570.0809326171875</v>
+        <v>570.0809936523438</v>
       </c>
       <c r="I698" t="n">
         <v>710.3877563476562</v>
@@ -22808,7 +22808,7 @@
         <v>118.4100036621094</v>
       </c>
       <c r="H699" t="n">
-        <v>574.74072265625</v>
+        <v>574.7407836914062</v>
       </c>
       <c r="I699" t="n">
         <v>713.0358276367188</v>
@@ -22840,7 +22840,7 @@
         <v>118.5400009155273</v>
       </c>
       <c r="H700" t="n">
-        <v>575.58349609375</v>
+        <v>575.5834350585938</v>
       </c>
       <c r="I700" t="n">
         <v>717.8323364257812</v>
@@ -22968,7 +22968,7 @@
         <v>123.2600021362305</v>
       </c>
       <c r="H704" t="n">
-        <v>577.66552734375</v>
+        <v>577.6655883789062</v>
       </c>
       <c r="I704" t="n">
         <v>741.7650756835938</v>
@@ -23128,7 +23128,7 @@
         <v>109.4000015258789</v>
       </c>
       <c r="H709" t="n">
-        <v>540.6845703125</v>
+        <v>540.6846313476562</v>
       </c>
       <c r="I709" t="n">
         <v>678.4108276367188</v>
@@ -23160,7 +23160,7 @@
         <v>109.8199996948242</v>
       </c>
       <c r="H710" t="n">
-        <v>539.8419189453125</v>
+        <v>539.8418579101562</v>
       </c>
       <c r="I710" t="n">
         <v>683.4071655273438</v>
@@ -23224,7 +23224,7 @@
         <v>104.8199996948242</v>
       </c>
       <c r="H712" t="n">
-        <v>544.8486328125</v>
+        <v>544.8486938476562</v>
       </c>
       <c r="I712" t="n">
         <v>671.2659301757812</v>
@@ -23352,7 +23352,7 @@
         <v>87.52999877929688</v>
       </c>
       <c r="H716" t="n">
-        <v>489.4764709472656</v>
+        <v>489.4765014648438</v>
       </c>
       <c r="I716" t="n">
         <v>579.032470703125</v>
@@ -23448,7 +23448,7 @@
         <v>110.9599990844727</v>
       </c>
       <c r="H719" t="n">
-        <v>526.953125</v>
+        <v>526.9530639648438</v>
       </c>
       <c r="I719" t="n">
         <v>811.7645874023438</v>
@@ -23640,7 +23640,7 @@
         <v>107.1800003051758</v>
       </c>
       <c r="H725" t="n">
-        <v>566.41259765625</v>
+        <v>566.4126586914062</v>
       </c>
       <c r="I725" t="n">
         <v>728.9743041992188</v>
@@ -23800,7 +23800,7 @@
         <v>105.9800033569336</v>
       </c>
       <c r="H730" t="n">
-        <v>572.0142822265625</v>
+        <v>572.0143432617188</v>
       </c>
       <c r="I730" t="n">
         <v>712.1864624023438</v>
@@ -23928,7 +23928,7 @@
         <v>99.58000183105469</v>
       </c>
       <c r="H734" t="n">
-        <v>544.1051025390625</v>
+        <v>544.1050415039062</v>
       </c>
       <c r="I734" t="n">
         <v>673.864013671875</v>
@@ -23992,7 +23992,7 @@
         <v>99.19999694824219</v>
       </c>
       <c r="H736" t="n">
-        <v>538.453857421875</v>
+        <v>538.4537963867188</v>
       </c>
       <c r="I736" t="n">
         <v>670.4664916992188</v>
@@ -24024,7 +24024,7 @@
         <v>101.4300003051758</v>
       </c>
       <c r="H737" t="n">
-        <v>544.1051025390625</v>
+        <v>544.1050415039062</v>
       </c>
       <c r="I737" t="n">
         <v>671.5157470703125</v>
@@ -24088,7 +24088,7 @@
         <v>107.8899993896484</v>
       </c>
       <c r="H739" t="n">
-        <v>539.9410400390625</v>
+        <v>539.9409790039062</v>
       </c>
       <c r="I739" t="n">
         <v>750.6087646484375</v>
@@ -24120,7 +24120,7 @@
         <v>105.8899993896484</v>
       </c>
       <c r="H740" t="n">
-        <v>531.21630859375</v>
+        <v>531.2162475585938</v>
       </c>
       <c r="I740" t="n">
         <v>760.5015869140625</v>
@@ -24184,7 +24184,7 @@
         <v>104.3600006103516</v>
       </c>
       <c r="H742" t="n">
-        <v>545.1460571289062</v>
+        <v>545.1461181640625</v>
       </c>
       <c r="I742" t="n">
         <v>733.9207763671875</v>
@@ -24216,7 +24216,7 @@
         <v>104.0899963378906</v>
       </c>
       <c r="H743" t="n">
-        <v>544.0059814453125</v>
+        <v>544.0059204101562</v>
       </c>
       <c r="I743" t="n">
         <v>727.1256713867188</v>
@@ -24280,7 +24280,7 @@
         <v>101.9700012207031</v>
       </c>
       <c r="H745" t="n">
-        <v>531.166748046875</v>
+        <v>531.1666870117188</v>
       </c>
       <c r="I745" t="n">
         <v>702.7931518554688</v>
@@ -24312,7 +24312,7 @@
         <v>100.9899978637695</v>
       </c>
       <c r="H746" t="n">
-        <v>533.447021484375</v>
+        <v>533.4470825195312</v>
       </c>
       <c r="I746" t="n">
         <v>704.4420166015625</v>
@@ -24344,7 +24344,7 @@
         <v>99.58000183105469</v>
       </c>
       <c r="H747" t="n">
-        <v>520.7565307617188</v>
+        <v>520.756591796875</v>
       </c>
       <c r="I747" t="n">
         <v>681.658447265625</v>
@@ -24408,7 +24408,7 @@
         <v>89.98000335693359</v>
       </c>
       <c r="H749" t="n">
-        <v>488.9807739257812</v>
+        <v>488.9807434082031</v>
       </c>
       <c r="I749" t="n">
         <v>627.747314453125</v>
@@ -24600,7 +24600,7 @@
         <v>105.75</v>
       </c>
       <c r="H755" t="n">
-        <v>527.2009887695312</v>
+        <v>527.200927734375</v>
       </c>
       <c r="I755" t="n">
         <v>665.81982421875</v>
@@ -24664,7 +24664,7 @@
         <v>104.3600006103516</v>
       </c>
       <c r="H757" t="n">
-        <v>544.1051025390625</v>
+        <v>544.1050415039062</v>
       </c>
       <c r="I757" t="n">
         <v>657.775634765625</v>
@@ -24696,7 +24696,7 @@
         <v>102.9700012207031</v>
       </c>
       <c r="H758" t="n">
-        <v>547.0794677734375</v>
+        <v>547.0794067382812</v>
       </c>
       <c r="I758" t="n">
         <v>641.0377197265625</v>
@@ -24760,7 +24760,7 @@
         <v>99.44000244140625</v>
       </c>
       <c r="H760" t="n">
-        <v>538.5034790039062</v>
+        <v>538.50341796875</v>
       </c>
       <c r="I760" t="n">
         <v>615.6060180664062</v>
@@ -25016,7 +25016,7 @@
         <v>100.6900024414062</v>
       </c>
       <c r="H768" t="n">
-        <v>509.7515869140625</v>
+        <v>509.7515563964844</v>
       </c>
       <c r="I768" t="n">
         <v>634.24267578125</v>
@@ -25208,7 +25208,7 @@
         <v>97.73000335693359</v>
       </c>
       <c r="H774" t="n">
-        <v>485.3124084472656</v>
+        <v>485.3123779296875</v>
       </c>
       <c r="I774" t="n">
         <v>573.3365478515625</v>
@@ -25240,7 +25240,7 @@
         <v>98.05000305175781</v>
       </c>
       <c r="H775" t="n">
-        <v>484.1226806640625</v>
+        <v>484.1226501464844</v>
       </c>
       <c r="I775" t="n">
         <v>574.0360107421875</v>
@@ -25272,7 +25272,7 @@
         <v>96.94999694824219</v>
       </c>
       <c r="H776" t="n">
-        <v>482.5859375</v>
+        <v>482.5859069824219</v>
       </c>
       <c r="I776" t="n">
         <v>578.9824829101562</v>
@@ -25304,7 +25304,7 @@
         <v>96.51000213623047</v>
       </c>
       <c r="H777" t="n">
-        <v>475.7944946289062</v>
+        <v>475.7945251464844</v>
       </c>
       <c r="I777" t="n">
         <v>582.2301635742188</v>
@@ -25432,7 +25432,7 @@
         <v>99.55999755859375</v>
       </c>
       <c r="H781" t="n">
-        <v>465.2356262207031</v>
+        <v>465.2356567382812</v>
       </c>
       <c r="I781" t="n">
         <v>578.6326904296875</v>
@@ -25464,7 +25464,7 @@
         <v>99.44999694824219</v>
       </c>
       <c r="H782" t="n">
-        <v>465.7809448242188</v>
+        <v>465.7809143066406</v>
       </c>
       <c r="I782" t="n">
         <v>580.3314819335938</v>
@@ -25496,7 +25496,7 @@
         <v>95.79000091552734</v>
       </c>
       <c r="H783" t="n">
-        <v>460.972412109375</v>
+        <v>460.9724426269531</v>
       </c>
       <c r="I783" t="n">
         <v>556.74853515625</v>
@@ -25528,7 +25528,7 @@
         <v>96.62999725341797</v>
       </c>
       <c r="H784" t="n">
-        <v>467.7638244628906</v>
+        <v>467.7637939453125</v>
       </c>
       <c r="I784" t="n">
         <v>551.40234375</v>
@@ -25560,7 +25560,7 @@
         <v>96.65000152587891</v>
       </c>
       <c r="H785" t="n">
-        <v>470.9364318847656</v>
+        <v>470.9364624023438</v>
       </c>
       <c r="I785" t="n">
         <v>546.7557373046875</v>
@@ -25624,7 +25624,7 @@
         <v>100.629997253418</v>
       </c>
       <c r="H787" t="n">
-        <v>494.2353820800781</v>
+        <v>494.2354125976562</v>
       </c>
       <c r="I787" t="n">
         <v>595.4706420898438</v>
@@ -25688,7 +25688,7 @@
         <v>101.0100021362305</v>
       </c>
       <c r="H789" t="n">
-        <v>485.4115600585938</v>
+        <v>485.4115295410156</v>
       </c>
       <c r="I789" t="n">
         <v>605.3134765625</v>
@@ -25816,7 +25816,7 @@
         <v>102.2399978637695</v>
       </c>
       <c r="H793" t="n">
-        <v>486.3534240722656</v>
+        <v>486.3533935546875</v>
       </c>
       <c r="I793" t="n">
         <v>602.9152221679688</v>
@@ -25848,7 +25848,7 @@
         <v>102.2399978637695</v>
       </c>
       <c r="H794" t="n">
-        <v>486.3534240722656</v>
+        <v>486.3533935546875</v>
       </c>
       <c r="I794" t="n">
         <v>602.9152221679688</v>
@@ -25912,7 +25912,7 @@
         <v>103.9300003051758</v>
       </c>
       <c r="H796" t="n">
-        <v>500.3823547363281</v>
+        <v>500.3823852539062</v>
       </c>
       <c r="I796" t="n">
         <v>619.2034912109375</v>
@@ -26040,7 +26040,7 @@
         <v>99.56999969482422</v>
       </c>
       <c r="H800" t="n">
-        <v>527.8949584960938</v>
+        <v>527.89501953125</v>
       </c>
       <c r="I800" t="n">
         <v>597.6190185546875</v>
@@ -26104,7 +26104,7 @@
         <v>101.8600006103516</v>
       </c>
       <c r="H802" t="n">
-        <v>533.7444458007812</v>
+        <v>533.7445068359375</v>
       </c>
       <c r="I802" t="n">
         <v>602.1657104492188</v>
@@ -26168,7 +26168,7 @@
         <v>102.7099990844727</v>
       </c>
       <c r="H804" t="n">
-        <v>529.4812622070312</v>
+        <v>529.4813232421875</v>
       </c>
       <c r="I804" t="n">
         <v>598.3185424804688</v>
@@ -26264,7 +26264,7 @@
         <v>101.9899978637695</v>
       </c>
       <c r="H807" t="n">
-        <v>520.7069702148438</v>
+        <v>520.70703125</v>
       </c>
       <c r="I807" t="n">
         <v>569.2894287109375</v>
@@ -26360,7 +26360,7 @@
         <v>103.6500015258789</v>
       </c>
       <c r="H810" t="n">
-        <v>543.9564208984375</v>
+        <v>543.9563598632812</v>
       </c>
       <c r="I810" t="n">
         <v>591.6233520507812</v>
@@ -26456,7 +26456,7 @@
         <v>109.9400024414062</v>
       </c>
       <c r="H813" t="n">
-        <v>564.9254150390625</v>
+        <v>564.9254760742188</v>
       </c>
       <c r="I813" t="n">
         <v>607.8117065429688</v>
@@ -26616,7 +26616,7 @@
         <v>109.870002746582</v>
       </c>
       <c r="H818" t="n">
-        <v>544.0059814453125</v>
+        <v>544.0059204101562</v>
       </c>
       <c r="I818" t="n">
         <v>599.567626953125</v>
@@ -26712,7 +26712,7 @@
         <v>106.4100036621094</v>
       </c>
       <c r="H821" t="n">
-        <v>535.0829467773438</v>
+        <v>535.0830078125</v>
       </c>
       <c r="I821" t="n">
         <v>599.7675170898438</v>
@@ -26776,7 +26776,7 @@
         <v>111.2900009155273</v>
       </c>
       <c r="H823" t="n">
-        <v>536.7684326171875</v>
+        <v>536.7683715820312</v>
       </c>
       <c r="I823" t="n">
         <v>665.0703735351562</v>
@@ -26872,7 +26872,7 @@
         <v>104.0400009155273</v>
       </c>
       <c r="H826" t="n">
-        <v>519.9138793945312</v>
+        <v>519.913818359375</v>
       </c>
       <c r="I826" t="n">
         <v>609.3106079101562</v>
@@ -27128,7 +27128,7 @@
         <v>111.2399978637695</v>
       </c>
       <c r="H834" t="n">
-        <v>557.24169921875</v>
+        <v>557.2417602539062</v>
       </c>
       <c r="I834" t="n">
         <v>659.4744262695312</v>
@@ -27288,7 +27288,7 @@
         <v>110.5100021362305</v>
       </c>
       <c r="H839" t="n">
-        <v>557.8861694335938</v>
+        <v>557.88623046875</v>
       </c>
       <c r="I839" t="n">
         <v>673.8140869140625</v>
@@ -27320,7 +27320,7 @@
         <v>110.1399993896484</v>
       </c>
       <c r="H840" t="n">
-        <v>556.84521484375</v>
+        <v>556.8451538085938</v>
       </c>
       <c r="I840" t="n">
         <v>672.5150756835938</v>
@@ -27352,7 +27352,7 @@
         <v>110.3899993896484</v>
       </c>
       <c r="H841" t="n">
-        <v>556.6469116210938</v>
+        <v>556.6468505859375</v>
       </c>
       <c r="I841" t="n">
         <v>680.2593994140625</v>
@@ -27544,7 +27544,7 @@
         <v>111.0500030517578</v>
       </c>
       <c r="H847" t="n">
-        <v>550.4007568359375</v>
+        <v>550.4008178710938</v>
       </c>
       <c r="I847" t="n">
         <v>679.4600219726562</v>
@@ -27576,7 +27576,7 @@
         <v>112.620002746582</v>
       </c>
       <c r="H848" t="n">
-        <v>555.2092895507812</v>
+        <v>555.209228515625</v>
       </c>
       <c r="I848" t="n">
         <v>690.3021850585938</v>
@@ -39220,7 +39220,7 @@
         <v>2.208437546514141</v>
       </c>
       <c r="H19" t="n">
-        <v>2.556976611417694</v>
+        <v>2.556964913081172</v>
       </c>
       <c r="I19" t="n">
         <v>13.9203514219733</v>
@@ -39252,7 +39252,7 @@
         <v>4.466918343308368</v>
       </c>
       <c r="H20" t="n">
-        <v>0.250775626255817</v>
+        <v>0.2507755975789339</v>
       </c>
       <c r="I20" t="n">
         <v>-0.3982613619074926</v>
@@ -39284,7 +39284,7 @@
         <v>6.336777990196563</v>
       </c>
       <c r="H21" t="n">
-        <v>15.78663533429408</v>
+        <v>15.78664090943846</v>
       </c>
       <c r="I21" t="n">
         <v>8.15757427726731</v>
@@ -39316,7 +39316,7 @@
         <v>-6.673809932633279</v>
       </c>
       <c r="H22" t="n">
-        <v>-9.331122166279437</v>
+        <v>-9.33111616376282</v>
       </c>
       <c r="I22" t="n">
         <v>-13.36495026383427</v>
@@ -39348,7 +39348,7 @@
         <v>-3.069222796045945</v>
       </c>
       <c r="H23" t="n">
-        <v>-4.292649304045937</v>
+        <v>-4.292638307557917</v>
       </c>
       <c r="I23" t="n">
         <v>-15.49832272048813</v>
@@ -39380,7 +39380,7 @@
         <v>-4.569213893886648</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8090252038547074</v>
+        <v>0.8090252975613055</v>
       </c>
       <c r="I24" t="n">
         <v>-6.315008228225805</v>
@@ -39412,7 +39412,7 @@
         <v>-6.394467498322587</v>
       </c>
       <c r="H25" t="n">
-        <v>-8.448882121149136</v>
+        <v>-8.44888301707284</v>
       </c>
       <c r="I25" t="n">
         <v>13.08554187517776</v>
@@ -39444,7 +39444,7 @@
         <v>-9.67004132070446</v>
       </c>
       <c r="H26" t="n">
-        <v>-8.220688992032056</v>
+        <v>-8.220698724355202</v>
       </c>
       <c r="I26" t="n">
         <v>-8.664971619347462</v>
@@ -39476,7 +39476,7 @@
         <v>3.812983091364663</v>
       </c>
       <c r="H27" t="n">
-        <v>2.511957438194501</v>
+        <v>2.511947210787713</v>
       </c>
       <c r="I27" t="n">
         <v>-5.280907910030197</v>
@@ -39508,7 +39508,7 @@
         <v>-13.94240303127289</v>
       </c>
       <c r="H28" t="n">
-        <v>-9.250694296187289</v>
+        <v>-9.250685242315114</v>
       </c>
       <c r="I28" t="n">
         <v>-7.280442020723066</v>
@@ -39636,7 +39636,7 @@
         <v>14.73397846832833</v>
       </c>
       <c r="H32" t="n">
-        <v>1.232976914127226</v>
+        <v>1.232966706077199</v>
       </c>
       <c r="I32" t="n">
         <v>0.2752207373969195</v>
@@ -39668,7 +39668,7 @@
         <v>-2.936626775408835</v>
       </c>
       <c r="H33" t="n">
-        <v>1.064507492928168</v>
+        <v>1.064507384443547</v>
       </c>
       <c r="I33" t="n">
         <v>-9.662184894372693</v>
@@ -39700,7 +39700,7 @@
         <v>-2.265863720466688</v>
       </c>
       <c r="H34" t="n">
-        <v>8.138513568615835</v>
+        <v>8.138524589079953</v>
       </c>
       <c r="I34" t="n">
         <v>1.313789268309984</v>
@@ -39828,7 +39828,7 @@
         <v>-3.815071313970964</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.0823883492873545</v>
+        <v>-0.08238108742454342</v>
       </c>
       <c r="I38" t="n">
         <v>-7.982063030449627</v>
@@ -39860,7 +39860,7 @@
         <v>17.47587201091527</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.8403317134902943</v>
+        <v>-0.8403389202663925</v>
       </c>
       <c r="I39" t="n">
         <v>-3.546709577533214</v>
@@ -39906,13 +39906,13 @@
         <v>45138</v>
       </c>
       <c r="B41" t="n">
-        <v>11.82700102606444</v>
+        <v>11.82699336487048</v>
       </c>
       <c r="C41" t="n">
         <v>6.966440170352728</v>
       </c>
       <c r="D41" t="n">
-        <v>4.411857938502117</v>
+        <v>4.411847244606748</v>
       </c>
       <c r="E41" t="n">
         <v>15.58304478376236</v>
@@ -39927,7 +39927,7 @@
         <v>9.344487405733215</v>
       </c>
       <c r="I41" t="n">
-        <v>1.429253550515419</v>
+        <v>1.429263020790783</v>
       </c>
       <c r="J41" t="n">
         <v>0.6376483051671933</v>
@@ -39938,13 +39938,13 @@
         <v>45107</v>
       </c>
       <c r="B42" t="n">
-        <v>2.053786671141311</v>
+        <v>2.053793662779313</v>
       </c>
       <c r="C42" t="n">
         <v>-1.216687531673721</v>
       </c>
       <c r="D42" t="n">
-        <v>-4.223257994852958</v>
+        <v>-4.223238790160777</v>
       </c>
       <c r="E42" t="n">
         <v>-3.252530162210432</v>
@@ -39959,7 +39959,7 @@
         <v>0.5429640610794095</v>
       </c>
       <c r="I42" t="n">
-        <v>-1.437929259655957</v>
+        <v>-1.437947532468964</v>
       </c>
       <c r="J42" t="n">
         <v>-4.413619280952474</v>
@@ -39976,13 +39976,13 @@
         <v>-24.55194044908406</v>
       </c>
       <c r="D43" t="n">
-        <v>29.5280660459768</v>
+        <v>29.52805333994046</v>
       </c>
       <c r="E43" t="n">
         <v>2.807572261517488</v>
       </c>
       <c r="F43" t="n">
-        <v>8.447095607106657</v>
+        <v>8.447085695065649</v>
       </c>
       <c r="G43" t="n">
         <v>11.02957293714546</v>
@@ -39991,7 +39991,7 @@
         <v>6.834800182265521</v>
       </c>
       <c r="I43" t="n">
-        <v>-29.71957821123238</v>
+        <v>-29.71957174362697</v>
       </c>
       <c r="J43" t="n">
         <v>25.50777634729149</v>
@@ -40002,7 +40002,7 @@
         <v>45046</v>
       </c>
       <c r="B44" t="n">
-        <v>5.737160059376079</v>
+        <v>5.737152178851423</v>
       </c>
       <c r="C44" t="n">
         <v>3.66547140892719</v>
@@ -40014,13 +40014,13 @@
         <v>7.927137678102603</v>
       </c>
       <c r="F44" t="n">
-        <v>7.817663148343112</v>
+        <v>7.81768362776154</v>
       </c>
       <c r="G44" t="n">
         <v>17.35386633308638</v>
       </c>
       <c r="H44" t="n">
-        <v>8.466692553990661</v>
+        <v>8.466701768317897</v>
       </c>
       <c r="I44" t="n">
         <v>8.902338132359366</v>
@@ -40034,28 +40034,28 @@
         <v>45016</v>
       </c>
       <c r="B45" t="n">
-        <v>-3.724662344575824</v>
+        <v>-3.72465516923437</v>
       </c>
       <c r="C45" t="n">
         <v>54.46413907015047</v>
       </c>
       <c r="D45" t="n">
-        <v>28.3462220758856</v>
+        <v>28.34623358431443</v>
       </c>
       <c r="E45" t="n">
         <v>81.56811180262491</v>
       </c>
       <c r="F45" t="n">
-        <v>6.658815870198675</v>
+        <v>6.658794148900937</v>
       </c>
       <c r="G45" t="n">
         <v>30.96377100161289</v>
       </c>
       <c r="H45" t="n">
-        <v>6.854726560003721</v>
+        <v>6.854707782997771</v>
       </c>
       <c r="I45" t="n">
-        <v>27.8829882720756</v>
+        <v>27.88299979085103</v>
       </c>
       <c r="J45" t="n">
         <v>0.815147568504071</v>
@@ -40072,22 +40072,22 @@
         <v>-63.75986333629861</v>
       </c>
       <c r="D46" t="n">
-        <v>-54.13933910520381</v>
+        <v>-54.13934321739424</v>
       </c>
       <c r="E46" t="n">
         <v>-60.34806944094112</v>
       </c>
       <c r="F46" t="n">
-        <v>-3.297159119784521</v>
+        <v>-3.297158784656318</v>
       </c>
       <c r="G46" t="n">
         <v>-34.62913019188968</v>
       </c>
       <c r="H46" t="n">
-        <v>-14.73082086991037</v>
+        <v>-14.73081312969551</v>
       </c>
       <c r="I46" t="n">
-        <v>-67.81377477152465</v>
+        <v>-67.81377767062695</v>
       </c>
       <c r="J46" t="n">
         <v>-23.35752147577641</v>
@@ -40098,19 +40098,19 @@
         <v>44957</v>
       </c>
       <c r="B47" t="n">
-        <v>-19.38483614178508</v>
+        <v>-19.38482793661753</v>
       </c>
       <c r="C47" t="n">
         <v>-31.48595153036594</v>
       </c>
       <c r="D47" t="n">
-        <v>-22.92301937376114</v>
+        <v>-22.92302425975112</v>
       </c>
       <c r="E47" t="n">
         <v>-36.64458052185531</v>
       </c>
       <c r="F47" t="n">
-        <v>-25.11306682409529</v>
+        <v>-25.11305921247429</v>
       </c>
       <c r="G47" t="n">
         <v>-25.28793450920587</v>
@@ -40130,13 +40130,13 @@
         <v>44926</v>
       </c>
       <c r="B48" t="n">
-        <v>-4.745918392870885</v>
+        <v>-4.745928088014839</v>
       </c>
       <c r="C48" t="n">
         <v>-10.97644834106928</v>
       </c>
       <c r="D48" t="n">
-        <v>-1.519948125216897</v>
+        <v>-1.51994188246356</v>
       </c>
       <c r="E48" t="n">
         <v>-8.726669084425943</v>
@@ -40180,7 +40180,7 @@
         <v>-0.6419831048444791</v>
       </c>
       <c r="H49" t="n">
-        <v>7.092594636276428</v>
+        <v>7.092607116345362</v>
       </c>
       <c r="I49" t="n">
         <v>0.8298941579935271</v>
@@ -40194,7 +40194,7 @@
         <v>44865</v>
       </c>
       <c r="B50" t="n">
-        <v>-1.049390031627995</v>
+        <v>-1.049379852050869</v>
       </c>
       <c r="C50" t="n">
         <v>1.790379399037678</v>
@@ -40212,7 +40212,7 @@
         <v>-10.33466386438756</v>
       </c>
       <c r="H50" t="n">
-        <v>3.365025301034952</v>
+        <v>3.365019480867559</v>
       </c>
       <c r="I50" t="n">
         <v>7.87460157490274</v>
@@ -40226,7 +40226,7 @@
         <v>44834</v>
       </c>
       <c r="B51" t="n">
-        <v>5.041969223002041</v>
+        <v>5.041947065704555</v>
       </c>
       <c r="C51" t="n">
         <v>-16.93892268070564</v>
@@ -40244,10 +40244,10 @@
         <v>-9.771716243293183</v>
       </c>
       <c r="H51" t="n">
-        <v>25.37386069556771</v>
+        <v>25.3738531445044</v>
       </c>
       <c r="I51" t="n">
-        <v>-10.81722885248916</v>
+        <v>-10.81723467446301</v>
       </c>
       <c r="J51" t="n">
         <v>-20.88017226023993</v>
@@ -40258,7 +40258,7 @@
         <v>44804</v>
       </c>
       <c r="B52" t="n">
-        <v>3.245925021466056</v>
+        <v>3.2459361784547</v>
       </c>
       <c r="C52" t="n">
         <v>27.37007418275781</v>
@@ -40270,16 +40270,16 @@
         <v>12.02464734774498</v>
       </c>
       <c r="F52" t="n">
-        <v>10.27236998744312</v>
+        <v>10.27236099604043</v>
       </c>
       <c r="G52" t="n">
         <v>31.85220530081916</v>
       </c>
       <c r="H52" t="n">
-        <v>9.725192544846495</v>
+        <v>9.725183453655561</v>
       </c>
       <c r="I52" t="n">
-        <v>19.7540922987248</v>
+        <v>19.75410011643701</v>
       </c>
       <c r="J52" t="n">
         <v>83.74902135029218</v>
@@ -40290,7 +40290,7 @@
         <v>44773</v>
       </c>
       <c r="B53" t="n">
-        <v>4.96948937210786</v>
+        <v>4.969477078676809</v>
       </c>
       <c r="C53" t="n">
         <v>25.70898148157286</v>
@@ -40302,16 +40302,16 @@
         <v>12.70211332333331</v>
       </c>
       <c r="F53" t="n">
-        <v>14.4246082042711</v>
+        <v>14.42461753424029</v>
       </c>
       <c r="G53" t="n">
         <v>19.44074810734559</v>
       </c>
       <c r="H53" t="n">
-        <v>3.250677044378025</v>
+        <v>3.250685599129</v>
       </c>
       <c r="I53" t="n">
-        <v>30.69885938210128</v>
+        <v>30.69884602773665</v>
       </c>
       <c r="J53" t="n">
         <v>45.79545801336116</v>
@@ -40322,7 +40322,7 @@
         <v>44742</v>
       </c>
       <c r="B54" t="n">
-        <v>-3.477534159208084</v>
+        <v>-3.477522855043191</v>
       </c>
       <c r="C54" t="n">
         <v>20.37225802159368</v>
@@ -40334,16 +40334,16 @@
         <v>2.151990548444327</v>
       </c>
       <c r="F54" t="n">
-        <v>-9.16402572525814</v>
+        <v>-9.164018026937349</v>
       </c>
       <c r="G54" t="n">
         <v>-18.6852305428317</v>
       </c>
       <c r="H54" t="n">
-        <v>-1.732545046843736</v>
+        <v>-1.73253678595402</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2085154657297417</v>
+        <v>-0.2085256195610063</v>
       </c>
       <c r="J54" t="n">
         <v>3.2258064516129</v>
@@ -40360,22 +40360,22 @@
         <v>-26.33088367090877</v>
       </c>
       <c r="D55" t="n">
-        <v>-7.051877972794152</v>
+        <v>-7.051887725396422</v>
       </c>
       <c r="E55" t="n">
         <v>-34.47516583955436</v>
       </c>
       <c r="F55" t="n">
-        <v>-13.60928974471389</v>
+        <v>-13.6092970662993</v>
       </c>
       <c r="G55" t="n">
         <v>15.30230404450439</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.7522815575130015</v>
+        <v>-0.752289900808234</v>
       </c>
       <c r="I55" t="n">
-        <v>-2.164478240198264</v>
+        <v>-2.164458288883464</v>
       </c>
       <c r="J55" t="n">
         <v>-10.23953527808792</v>
@@ -40392,22 +40392,22 @@
         <v>17.7923744286306</v>
       </c>
       <c r="D56" t="n">
-        <v>15.74635547782128</v>
+        <v>15.74637465106719</v>
       </c>
       <c r="E56" t="n">
         <v>50.56145204702873</v>
       </c>
       <c r="F56" t="n">
-        <v>10.61741361378157</v>
+        <v>10.61740465493502</v>
       </c>
       <c r="G56" t="n">
         <v>51.45866829146802</v>
       </c>
       <c r="H56" t="n">
-        <v>24.37762270562873</v>
+        <v>24.37760979872503</v>
       </c>
       <c r="I56" t="n">
-        <v>14.00827300201519</v>
+        <v>14.00828596826276</v>
       </c>
       <c r="J56" t="n">
         <v>-16.3215872474704</v>
@@ -40418,28 +40418,28 @@
         <v>44651</v>
       </c>
       <c r="B57" t="n">
-        <v>2.97728013308558</v>
+        <v>2.977305310912381</v>
       </c>
       <c r="C57" t="n">
         <v>10.95155597333577</v>
       </c>
       <c r="D57" t="n">
-        <v>22.51817510009613</v>
+        <v>22.51816766035562</v>
       </c>
       <c r="E57" t="n">
         <v>3.867848856109002</v>
       </c>
       <c r="F57" t="n">
-        <v>9.427552850962662</v>
+        <v>9.427571411441527</v>
       </c>
       <c r="G57" t="n">
         <v>49.57575942530777</v>
       </c>
       <c r="H57" t="n">
-        <v>-2.747517525648757</v>
+        <v>-2.747497618774175</v>
       </c>
       <c r="I57" t="n">
-        <v>35.33522364866361</v>
+        <v>35.33521867213445</v>
       </c>
       <c r="J57" t="n">
         <v>52.09380234505863</v>
@@ -40450,7 +40450,7 @@
         <v>44620</v>
       </c>
       <c r="B58" t="n">
-        <v>-8.601110865295015</v>
+        <v>-8.601133212213041</v>
       </c>
       <c r="C58" t="n">
         <v>8.295696174558387</v>
@@ -40462,16 +40462,16 @@
         <v>-1.834542248835702</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.228524456736058</v>
+        <v>-1.228533210339366</v>
       </c>
       <c r="G58" t="n">
         <v>16.47058823529413</v>
       </c>
       <c r="H58" t="n">
-        <v>-13.93948000276193</v>
+        <v>-13.93948121344685</v>
       </c>
       <c r="I58" t="n">
-        <v>-12.77967711983119</v>
+        <v>-12.77968968676688</v>
       </c>
       <c r="J58" t="n">
         <v>34.45945945945945</v>
@@ -40786,7 +40786,7 @@
         <v>15.01079994493293</v>
       </c>
       <c r="H8" t="n">
-        <v>7.655597813986703</v>
+        <v>7.655585503272211</v>
       </c>
       <c r="I8" t="n">
         <v>12.18076476276884</v>
@@ -40818,7 +40818,7 @@
         <v>-3.805835114293932</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4759148328340679</v>
+        <v>0.4759378669163983</v>
       </c>
       <c r="I9" t="n">
         <v>-20.81992716245783</v>
@@ -40850,7 +40850,7 @@
         <v>-19.30960692134881</v>
       </c>
       <c r="H10" t="n">
-        <v>-15.29523148281967</v>
+        <v>-15.29524121514283</v>
       </c>
       <c r="I10" t="n">
         <v>-3.235852580585286</v>
@@ -40914,7 +40914,7 @@
         <v>34.61970620542895</v>
       </c>
       <c r="H12" t="n">
-        <v>9.785827814008584</v>
+        <v>9.785816743513021</v>
       </c>
       <c r="I12" t="n">
         <v>-3.271604999325783</v>
@@ -40946,7 +40946,7 @@
         <v>1.64715164909115</v>
       </c>
       <c r="H13" t="n">
-        <v>17.5561300283027</v>
+        <v>17.55614188233498</v>
       </c>
       <c r="I13" t="n">
         <v>-6.214895854726277</v>
@@ -40978,7 +40978,7 @@
         <v>39.13101305001452</v>
       </c>
       <c r="H14" t="n">
-        <v>22.62241185496832</v>
+        <v>22.62242076698209</v>
       </c>
       <c r="I14" t="n">
         <v>61.10070412299044</v>
@@ -40992,13 +40992,13 @@
         <v>45199</v>
       </c>
       <c r="B15" t="n">
-        <v>11.51389277013355</v>
+        <v>11.5138851303904</v>
       </c>
       <c r="C15" t="n">
         <v>5.604431410883026</v>
       </c>
       <c r="D15" t="n">
-        <v>1.131447577129419</v>
+        <v>1.131437219214715</v>
       </c>
       <c r="E15" t="n">
         <v>4.360925989567699</v>
@@ -41010,10 +41010,10 @@
         <v>51.07063441994313</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3229764699508975</v>
+        <v>0.3229691786272859</v>
       </c>
       <c r="I15" t="n">
-        <v>-6.28072516525251</v>
+        <v>-6.280716414844623</v>
       </c>
       <c r="J15" t="n">
         <v>-8.333332214981715</v>
@@ -41024,28 +41024,28 @@
         <v>45107</v>
       </c>
       <c r="B16" t="n">
-        <v>8.787178143930685</v>
+        <v>8.787177489027776</v>
       </c>
       <c r="C16" t="n">
         <v>-22.73802835392045</v>
       </c>
       <c r="D16" t="n">
-        <v>36.4249059446292</v>
+        <v>36.42491991731245</v>
       </c>
       <c r="E16" t="n">
         <v>7.348351382394469</v>
       </c>
       <c r="F16" t="n">
-        <v>16.98842962045543</v>
+        <v>16.98844114909532</v>
       </c>
       <c r="G16" t="n">
         <v>30.40188313846057</v>
       </c>
       <c r="H16" t="n">
-        <v>16.5093619544856</v>
+        <v>16.50937185204364</v>
       </c>
       <c r="I16" t="n">
-        <v>-24.56352566485572</v>
+        <v>-24.56353270822924</v>
       </c>
       <c r="J16" t="n">
         <v>18.62284690483378</v>
@@ -41056,25 +41056,25 @@
         <v>45016</v>
       </c>
       <c r="B17" t="n">
-        <v>-31.71691250225065</v>
+        <v>-31.71690046316888</v>
       </c>
       <c r="C17" t="n">
         <v>-61.64719560517645</v>
       </c>
       <c r="D17" t="n">
-        <v>-54.63216110402858</v>
+        <v>-54.63216397994308</v>
       </c>
       <c r="E17" t="n">
         <v>-54.3871000029952</v>
       </c>
       <c r="F17" t="n">
-        <v>-22.76004075566347</v>
+        <v>-22.76004836728446</v>
       </c>
       <c r="G17" t="n">
         <v>-36.03738976394022</v>
       </c>
       <c r="H17" t="n">
-        <v>-30.25185472226123</v>
+        <v>-30.25186064741821</v>
       </c>
       <c r="I17" t="n">
         <v>-76.50189047530399</v>
@@ -41088,13 +41088,13 @@
         <v>44926</v>
       </c>
       <c r="B18" t="n">
-        <v>1.074254997477486</v>
+        <v>1.074255107991839</v>
       </c>
       <c r="C18" t="n">
         <v>-21.29460874309583</v>
       </c>
       <c r="D18" t="n">
-        <v>11.65015127704323</v>
+        <v>11.65015835466292</v>
       </c>
       <c r="E18" t="n">
         <v>-14.55237052788174</v>
@@ -41106,7 +41106,7 @@
         <v>-19.79919371493109</v>
       </c>
       <c r="H18" t="n">
-        <v>1.648564929586116</v>
+        <v>1.648571051713899</v>
       </c>
       <c r="I18" t="n">
         <v>10.5693401676328</v>
@@ -41120,7 +41120,7 @@
         <v>44834</v>
       </c>
       <c r="B19" t="n">
-        <v>13.84104117459124</v>
+        <v>13.84101613074176</v>
       </c>
       <c r="C19" t="n">
         <v>32.99376139327897</v>
@@ -41138,10 +41138,10 @@
         <v>42.09624763531581</v>
       </c>
       <c r="H19" t="n">
-        <v>42.03855951339208</v>
+        <v>42.03855095864111</v>
       </c>
       <c r="I19" t="n">
-        <v>39.58640544331568</v>
+        <v>39.58639118085186</v>
       </c>
       <c r="J19" t="n">
         <v>111.9602203369141</v>
@@ -41152,28 +41152,28 @@
         <v>44742</v>
       </c>
       <c r="B20" t="n">
-        <v>1.36668177907604</v>
+        <v>1.366693650568096</v>
       </c>
       <c r="C20" t="n">
         <v>4.454954472923656</v>
       </c>
       <c r="D20" t="n">
-        <v>8.743009427151494</v>
+        <v>8.74301603041523</v>
       </c>
       <c r="E20" t="n">
         <v>0.7781910896766497</v>
       </c>
       <c r="F20" t="n">
-        <v>-13.19426413035678</v>
+        <v>-13.19427116070798</v>
       </c>
       <c r="G20" t="n">
         <v>42.00431940783369</v>
       </c>
       <c r="H20" t="n">
-        <v>21.30326534957958</v>
+        <v>21.30325276170784</v>
       </c>
       <c r="I20" t="n">
-        <v>11.30800936277003</v>
+        <v>11.30803339499058</v>
       </c>
       <c r="J20" t="n">
         <v>-22.46696035242291</v>

--- a/dashboards/Adani Group.xlsx
+++ b/dashboards/Adani Group.xlsx
@@ -486,7 +486,7 @@
         <v>44564</v>
       </c>
       <c r="B2" t="n">
-        <v>2152.120849609375</v>
+        <v>2152.12109375</v>
       </c>
       <c r="C2" t="n">
         <v>1731.099975585938</v>
@@ -518,25 +518,25 @@
         <v>44565</v>
       </c>
       <c r="B3" t="n">
-        <v>2126.262939453125</v>
+        <v>2126.26318359375</v>
       </c>
       <c r="C3" t="n">
         <v>1754.949951171875</v>
       </c>
       <c r="D3" t="n">
-        <v>1715.171264648438</v>
+        <v>1715.171142578125</v>
       </c>
       <c r="E3" t="n">
         <v>1366.699951171875</v>
       </c>
       <c r="F3" t="n">
-        <v>719.597412109375</v>
+        <v>719.5974731445312</v>
       </c>
       <c r="G3" t="n">
         <v>20.11000061035156</v>
       </c>
       <c r="H3" t="n">
-        <v>375.7160034179688</v>
+        <v>375.7159729003906</v>
       </c>
       <c r="I3" t="n">
         <v>1751.383544921875</v>
@@ -556,7 +556,7 @@
         <v>1761.050048828125</v>
       </c>
       <c r="D4" t="n">
-        <v>1711.629150390625</v>
+        <v>1711.629028320312</v>
       </c>
       <c r="E4" t="n">
         <v>1399.650024414062</v>
@@ -571,7 +571,7 @@
         <v>378.8433227539062</v>
       </c>
       <c r="I4" t="n">
-        <v>1769.107543945312</v>
+        <v>1769.107666015625</v>
       </c>
       <c r="J4" t="n">
         <v>125.6500015258789</v>
@@ -603,7 +603,7 @@
         <v>372.4442749023438</v>
       </c>
       <c r="I5" t="n">
-        <v>1795.868530273438</v>
+        <v>1795.86865234375</v>
       </c>
       <c r="J5" t="n">
         <v>119.9499969482422</v>
@@ -614,7 +614,7 @@
         <v>44568</v>
       </c>
       <c r="B6" t="n">
-        <v>2183.905517578125</v>
+        <v>2183.9052734375</v>
       </c>
       <c r="C6" t="n">
         <v>1776</v>
@@ -626,16 +626,16 @@
         <v>1423.099975585938</v>
       </c>
       <c r="F6" t="n">
-        <v>716.53125</v>
+        <v>716.5311279296875</v>
       </c>
       <c r="G6" t="n">
         <v>20.04000091552734</v>
       </c>
       <c r="H6" t="n">
-        <v>382.2593383789062</v>
+        <v>382.2593688964844</v>
       </c>
       <c r="I6" t="n">
-        <v>1785.18408203125</v>
+        <v>1785.184204101562</v>
       </c>
       <c r="J6" t="n">
         <v>120.0500030517578</v>
@@ -664,7 +664,7 @@
         <v>21.73999977111816</v>
       </c>
       <c r="H7" t="n">
-        <v>384.2800903320312</v>
+        <v>384.2801208496094</v>
       </c>
       <c r="I7" t="n">
         <v>1760.769897460938</v>
@@ -678,13 +678,13 @@
         <v>44572</v>
       </c>
       <c r="B8" t="n">
-        <v>2196.332763671875</v>
+        <v>2196.33251953125</v>
       </c>
       <c r="C8" t="n">
         <v>1867.449951171875</v>
       </c>
       <c r="D8" t="n">
-        <v>1839.792846679688</v>
+        <v>1839.79296875</v>
       </c>
       <c r="E8" t="n">
         <v>1567.949951171875</v>
@@ -696,7 +696,7 @@
         <v>21.70999908447266</v>
       </c>
       <c r="H8" t="n">
-        <v>382.6442565917969</v>
+        <v>382.6442260742188</v>
       </c>
       <c r="I8" t="n">
         <v>1777.345581054688</v>
@@ -710,19 +710,19 @@
         <v>44573</v>
       </c>
       <c r="B9" t="n">
-        <v>2212.7744140625</v>
+        <v>2212.774658203125</v>
       </c>
       <c r="C9" t="n">
         <v>1928.25</v>
       </c>
       <c r="D9" t="n">
-        <v>1826.023681640625</v>
+        <v>1826.023559570312</v>
       </c>
       <c r="E9" t="n">
         <v>1647.550048828125</v>
       </c>
       <c r="F9" t="n">
-        <v>743.2514038085938</v>
+        <v>743.25146484375</v>
       </c>
       <c r="G9" t="n">
         <v>23.8799991607666</v>
@@ -731,7 +731,7 @@
         <v>382.8847961425781</v>
       </c>
       <c r="I9" t="n">
-        <v>1794.071044921875</v>
+        <v>1794.070922851562</v>
       </c>
       <c r="J9" t="n">
         <v>120</v>
@@ -742,19 +742,19 @@
         <v>44574</v>
       </c>
       <c r="B10" t="n">
-        <v>2212.15283203125</v>
+        <v>2212.153076171875</v>
       </c>
       <c r="C10" t="n">
         <v>2019.699951171875</v>
       </c>
       <c r="D10" t="n">
-        <v>1849.221923828125</v>
+        <v>1849.221801757812</v>
       </c>
       <c r="E10" t="n">
         <v>1661.800048828125</v>
       </c>
       <c r="F10" t="n">
-        <v>751.6715698242188</v>
+        <v>751.6714477539062</v>
       </c>
       <c r="G10" t="n">
         <v>23.29000091552734</v>
@@ -774,19 +774,19 @@
         <v>44575</v>
       </c>
       <c r="B11" t="n">
-        <v>2254.166259765625</v>
+        <v>2254.165771484375</v>
       </c>
       <c r="C11" t="n">
         <v>2020.599975585938</v>
       </c>
       <c r="D11" t="n">
-        <v>1866.084350585938</v>
+        <v>1866.084228515625</v>
       </c>
       <c r="E11" t="n">
         <v>1697.949951171875</v>
       </c>
       <c r="F11" t="n">
-        <v>759.3615112304688</v>
+        <v>759.3614501953125</v>
       </c>
       <c r="G11" t="n">
         <v>23.43000030517578</v>
@@ -795,7 +795,7 @@
         <v>387.5037231445312</v>
       </c>
       <c r="I11" t="n">
-        <v>1803.207763671875</v>
+        <v>1803.207641601562</v>
       </c>
       <c r="J11" t="n">
         <v>118.9000015258789</v>
@@ -806,7 +806,7 @@
         <v>44578</v>
       </c>
       <c r="B12" t="n">
-        <v>2273.809814453125</v>
+        <v>2273.810302734375</v>
       </c>
       <c r="C12" t="n">
         <v>2002.699951171875</v>
@@ -818,7 +818,7 @@
         <v>1835.300048828125</v>
       </c>
       <c r="F12" t="n">
-        <v>758.3394165039062</v>
+        <v>758.33935546875</v>
       </c>
       <c r="G12" t="n">
         <v>23.20999908447266</v>
@@ -856,10 +856,10 @@
         <v>21.95000076293945</v>
       </c>
       <c r="H13" t="n">
-        <v>366.2857666015625</v>
+        <v>366.2857360839844</v>
       </c>
       <c r="I13" t="n">
-        <v>1812.793579101562</v>
+        <v>1812.793701171875</v>
       </c>
       <c r="J13" t="n">
         <v>115.5999984741211</v>
@@ -870,7 +870,7 @@
         <v>44580</v>
       </c>
       <c r="B14" t="n">
-        <v>2133.432861328125</v>
+        <v>2133.4326171875</v>
       </c>
       <c r="C14" t="n">
         <v>2043.25</v>
@@ -888,7 +888,7 @@
         <v>22.78000068664551</v>
       </c>
       <c r="H14" t="n">
-        <v>360.7046203613281</v>
+        <v>360.7046508789062</v>
       </c>
       <c r="I14" t="n">
         <v>1792.273803710938</v>
@@ -902,28 +902,28 @@
         <v>44581</v>
       </c>
       <c r="B15" t="n">
-        <v>2154.654296875</v>
+        <v>2154.65380859375</v>
       </c>
       <c r="C15" t="n">
         <v>2039.75</v>
       </c>
       <c r="D15" t="n">
-        <v>1861.693969726562</v>
+        <v>1861.694091796875</v>
       </c>
       <c r="E15" t="n">
         <v>1966.699951171875</v>
       </c>
       <c r="F15" t="n">
-        <v>718.3806762695312</v>
+        <v>718.380615234375</v>
       </c>
       <c r="G15" t="n">
         <v>22.75</v>
       </c>
       <c r="H15" t="n">
-        <v>360.9452209472656</v>
+        <v>360.9451904296875</v>
       </c>
       <c r="I15" t="n">
-        <v>1801.060913085938</v>
+        <v>1801.060791015625</v>
       </c>
       <c r="J15" t="n">
         <v>119.8000030517578</v>
@@ -934,7 +934,7 @@
         <v>44582</v>
       </c>
       <c r="B16" t="n">
-        <v>2118.090087890625</v>
+        <v>2118.09033203125</v>
       </c>
       <c r="C16" t="n">
         <v>2066.800048828125</v>
@@ -952,7 +952,7 @@
         <v>21.98999977111816</v>
       </c>
       <c r="H16" t="n">
-        <v>354.7386169433594</v>
+        <v>354.7385559082031</v>
       </c>
       <c r="I16" t="n">
         <v>1824.62646484375</v>
@@ -966,7 +966,7 @@
         <v>44585</v>
       </c>
       <c r="B17" t="n">
-        <v>2071.9189453125</v>
+        <v>2071.918701171875</v>
       </c>
       <c r="C17" t="n">
         <v>2035.900024414062</v>
@@ -978,13 +978,13 @@
         <v>1837.849975585938</v>
       </c>
       <c r="F17" t="n">
-        <v>683.7757568359375</v>
+        <v>683.7758178710938</v>
       </c>
       <c r="G17" t="n">
         <v>20.55999946594238</v>
       </c>
       <c r="H17" t="n">
-        <v>339.5348510742188</v>
+        <v>339.5348205566406</v>
       </c>
       <c r="I17" t="n">
         <v>1778.543823242188</v>
@@ -998,25 +998,25 @@
         <v>44586</v>
       </c>
       <c r="B18" t="n">
-        <v>2083.86767578125</v>
+        <v>2083.867919921875</v>
       </c>
       <c r="C18" t="n">
         <v>1992.449951171875</v>
       </c>
       <c r="D18" t="n">
-        <v>1737.521362304688</v>
+        <v>1737.521484375</v>
       </c>
       <c r="E18" t="n">
         <v>1929</v>
       </c>
       <c r="F18" t="n">
-        <v>692.1957397460938</v>
+        <v>692.19580078125</v>
       </c>
       <c r="G18" t="n">
         <v>21.43000030517578</v>
       </c>
       <c r="H18" t="n">
-        <v>338.2357482910156</v>
+        <v>338.2357788085938</v>
       </c>
       <c r="I18" t="n">
         <v>1822.529296875</v>
@@ -1051,7 +1051,7 @@
         <v>338.3800964355469</v>
       </c>
       <c r="I19" t="n">
-        <v>1828.071166992188</v>
+        <v>1828.0712890625</v>
       </c>
       <c r="J19" t="n">
         <v>117.5999984741211</v>
@@ -1080,10 +1080,10 @@
         <v>21.14999961853027</v>
       </c>
       <c r="H20" t="n">
-        <v>347.0885620117188</v>
+        <v>347.088623046875</v>
       </c>
       <c r="I20" t="n">
-        <v>1828.22119140625</v>
+        <v>1828.220947265625</v>
       </c>
       <c r="J20" t="n">
         <v>112.8499984741211</v>
@@ -1094,19 +1094,19 @@
         <v>44592</v>
       </c>
       <c r="B21" t="n">
-        <v>2185.0048828125</v>
+        <v>2185.004638671875</v>
       </c>
       <c r="C21" t="n">
         <v>1970.900024414062</v>
       </c>
       <c r="D21" t="n">
-        <v>1711.130249023438</v>
+        <v>1711.130126953125</v>
       </c>
       <c r="E21" t="n">
         <v>1877.849975585938</v>
       </c>
       <c r="F21" t="n">
-        <v>697.257568359375</v>
+        <v>697.2575073242188</v>
       </c>
       <c r="G21" t="n">
         <v>21.25</v>
@@ -1126,7 +1126,7 @@
         <v>44593</v>
       </c>
       <c r="B22" t="n">
-        <v>2229.74169921875</v>
+        <v>2229.741943359375</v>
       </c>
       <c r="C22" t="n">
         <v>1986.900024414062</v>
@@ -1164,22 +1164,22 @@
         <v>2016</v>
       </c>
       <c r="D23" t="n">
-        <v>1775.386596679688</v>
+        <v>1775.38671875</v>
       </c>
       <c r="E23" t="n">
         <v>1916.300048828125</v>
       </c>
       <c r="F23" t="n">
-        <v>725.3892822265625</v>
+        <v>725.3892211914062</v>
       </c>
       <c r="G23" t="n">
         <v>21.67000007629395</v>
       </c>
       <c r="H23" t="n">
-        <v>365.6602783203125</v>
+        <v>365.6603088378906</v>
       </c>
       <c r="I23" t="n">
-        <v>1874.353515625</v>
+        <v>1874.353393554688</v>
       </c>
       <c r="J23" t="n">
         <v>112.0500030517578</v>
@@ -1202,13 +1202,13 @@
         <v>1912.550048828125</v>
       </c>
       <c r="F24" t="n">
-        <v>713.0269775390625</v>
+        <v>713.0269165039062</v>
       </c>
       <c r="G24" t="n">
         <v>21.52000045776367</v>
       </c>
       <c r="H24" t="n">
-        <v>367.4885864257812</v>
+        <v>367.4885559082031</v>
       </c>
       <c r="I24" t="n">
         <v>1848.940795898438</v>
@@ -1222,7 +1222,7 @@
         <v>44596</v>
       </c>
       <c r="B25" t="n">
-        <v>2174.48974609375</v>
+        <v>2174.4892578125</v>
       </c>
       <c r="C25" t="n">
         <v>2033.099975585938</v>
@@ -1234,7 +1234,7 @@
         <v>1950.349975585938</v>
       </c>
       <c r="F25" t="n">
-        <v>707.6244506835938</v>
+        <v>707.6243896484375</v>
       </c>
       <c r="G25" t="n">
         <v>21.70999908447266</v>
@@ -1243,7 +1243,7 @@
         <v>366.045166015625</v>
       </c>
       <c r="I25" t="n">
-        <v>1848.391357421875</v>
+        <v>1848.3916015625</v>
       </c>
       <c r="J25" t="n">
         <v>112.9499969482422</v>
@@ -1286,7 +1286,7 @@
         <v>44600</v>
       </c>
       <c r="B27" t="n">
-        <v>2203.167236328125</v>
+        <v>2203.16748046875</v>
       </c>
       <c r="C27" t="n">
         <v>1968.300048828125</v>
@@ -1298,16 +1298,16 @@
         <v>1928</v>
       </c>
       <c r="F27" t="n">
-        <v>698.7177124023438</v>
+        <v>698.7176513671875</v>
       </c>
       <c r="G27" t="n">
         <v>21.6299991607666</v>
       </c>
       <c r="H27" t="n">
-        <v>362.0998840332031</v>
+        <v>362.0999145507812</v>
       </c>
       <c r="I27" t="n">
-        <v>1806.402954101562</v>
+        <v>1806.403076171875</v>
       </c>
       <c r="J27" t="n">
         <v>115.5999984741211</v>
@@ -1330,13 +1330,13 @@
         <v>1919.800048828125</v>
       </c>
       <c r="F28" t="n">
-        <v>713.9517211914062</v>
+        <v>713.95166015625</v>
       </c>
       <c r="G28" t="n">
         <v>21.52000045776367</v>
       </c>
       <c r="H28" t="n">
-        <v>368.3545837402344</v>
+        <v>368.3546447753906</v>
       </c>
       <c r="I28" t="n">
         <v>1762.417358398438</v>
@@ -1350,13 +1350,13 @@
         <v>44602</v>
       </c>
       <c r="B29" t="n">
-        <v>2202.020263671875</v>
+        <v>2202.0205078125</v>
       </c>
       <c r="C29" t="n">
         <v>2036.400024414062</v>
       </c>
       <c r="D29" t="n">
-        <v>1782.121948242188</v>
+        <v>1782.121826171875</v>
       </c>
       <c r="E29" t="n">
         <v>1907.949951171875</v>
@@ -1368,7 +1368,7 @@
         <v>24.54999923706055</v>
       </c>
       <c r="H29" t="n">
-        <v>360.7046203613281</v>
+        <v>360.7046508789062</v>
       </c>
       <c r="I29" t="n">
         <v>1807.901000976562</v>
@@ -1394,16 +1394,16 @@
         <v>1907.599975585938</v>
       </c>
       <c r="F30" t="n">
-        <v>704.4608154296875</v>
+        <v>704.4609375</v>
       </c>
       <c r="G30" t="n">
         <v>25</v>
       </c>
       <c r="H30" t="n">
-        <v>354.0169067382812</v>
+        <v>354.0168762207031</v>
       </c>
       <c r="I30" t="n">
-        <v>1787.680541992188</v>
+        <v>1787.680419921875</v>
       </c>
       <c r="J30" t="n">
         <v>161.1999969482422</v>
@@ -1414,28 +1414,28 @@
         <v>44606</v>
       </c>
       <c r="B31" t="n">
-        <v>2058.96630859375</v>
+        <v>2058.966064453125</v>
       </c>
       <c r="C31" t="n">
         <v>1915.25</v>
       </c>
       <c r="D31" t="n">
-        <v>1660.243774414062</v>
+        <v>1660.243896484375</v>
       </c>
       <c r="E31" t="n">
         <v>1862.150024414062</v>
       </c>
       <c r="F31" t="n">
-        <v>677.2538452148438</v>
+        <v>677.25390625</v>
       </c>
       <c r="G31" t="n">
         <v>22.67000007629395</v>
       </c>
       <c r="H31" t="n">
-        <v>341.6999206542969</v>
+        <v>341.6998901367188</v>
       </c>
       <c r="I31" t="n">
-        <v>1709.794799804688</v>
+        <v>1709.794677734375</v>
       </c>
       <c r="J31" t="n">
         <v>174.3000030517578</v>
@@ -1464,10 +1464,10 @@
         <v>23.59000015258789</v>
       </c>
       <c r="H32" t="n">
-        <v>349.8310852050781</v>
+        <v>349.8310241699219</v>
       </c>
       <c r="I32" t="n">
-        <v>1735.1572265625</v>
+        <v>1735.157348632812</v>
       </c>
       <c r="J32" t="n">
         <v>156.8999938964844</v>
@@ -1478,7 +1478,7 @@
         <v>44608</v>
       </c>
       <c r="B33" t="n">
-        <v>2140.697509765625</v>
+        <v>2140.697265625</v>
       </c>
       <c r="C33" t="n">
         <v>1932.550048828125</v>
@@ -1496,10 +1496,10 @@
         <v>25.35000038146973</v>
       </c>
       <c r="H33" t="n">
-        <v>347.0885620117188</v>
+        <v>347.088623046875</v>
       </c>
       <c r="I33" t="n">
-        <v>1683.882568359375</v>
+        <v>1683.882690429688</v>
       </c>
       <c r="J33" t="n">
         <v>165.8500061035156</v>
@@ -1522,16 +1522,16 @@
         <v>2047.599975585938</v>
       </c>
       <c r="F34" t="n">
-        <v>714.6817626953125</v>
+        <v>714.6817016601562</v>
       </c>
       <c r="G34" t="n">
         <v>26.39999961853027</v>
       </c>
       <c r="H34" t="n">
-        <v>346.2225952148438</v>
+        <v>346.2225646972656</v>
       </c>
       <c r="I34" t="n">
-        <v>1724.3232421875</v>
+        <v>1724.323364257812</v>
       </c>
       <c r="J34" t="n">
         <v>163.6000061035156</v>
@@ -1563,7 +1563,7 @@
         <v>325.5820007324219</v>
       </c>
       <c r="I35" t="n">
-        <v>1662.763549804688</v>
+        <v>1662.763427734375</v>
       </c>
       <c r="J35" t="n">
         <v>164.6499938964844</v>
@@ -1580,22 +1580,22 @@
         <v>1895.900024414062</v>
       </c>
       <c r="D36" t="n">
-        <v>1681.446533203125</v>
+        <v>1681.446411132812</v>
       </c>
       <c r="E36" t="n">
         <v>1955.900024414062</v>
       </c>
       <c r="F36" t="n">
-        <v>692.1957397460938</v>
+        <v>692.19580078125</v>
       </c>
       <c r="G36" t="n">
         <v>24.03000068664551</v>
       </c>
       <c r="H36" t="n">
-        <v>325.7744445800781</v>
+        <v>325.7744140625</v>
       </c>
       <c r="I36" t="n">
-        <v>1588.77197265625</v>
+        <v>1588.771850585938</v>
       </c>
       <c r="J36" t="n">
         <v>162.3999938964844</v>
@@ -1618,7 +1618,7 @@
         <v>1971.949951171875</v>
       </c>
       <c r="F37" t="n">
-        <v>686.7933349609375</v>
+        <v>686.7933959960938</v>
       </c>
       <c r="G37" t="n">
         <v>24.11000061035156</v>
@@ -1644,19 +1644,19 @@
         <v>2060.14990234375</v>
       </c>
       <c r="D38" t="n">
-        <v>1684.938598632812</v>
+        <v>1684.9384765625</v>
       </c>
       <c r="E38" t="n">
         <v>1987.349975585938</v>
       </c>
       <c r="F38" t="n">
-        <v>687.9127197265625</v>
+        <v>687.9127807617188</v>
       </c>
       <c r="G38" t="n">
         <v>25.11000061035156</v>
       </c>
       <c r="H38" t="n">
-        <v>318.4612426757812</v>
+        <v>318.4612121582031</v>
       </c>
       <c r="I38" t="n">
         <v>1639.397827148438</v>
@@ -1670,7 +1670,7 @@
         <v>44616</v>
       </c>
       <c r="B39" t="n">
-        <v>1925.232177734375</v>
+        <v>1925.232299804688</v>
       </c>
       <c r="C39" t="n">
         <v>1957.300048828125</v>
@@ -1682,7 +1682,7 @@
         <v>1849.75</v>
       </c>
       <c r="F39" t="n">
-        <v>637.441162109375</v>
+        <v>637.4411010742188</v>
       </c>
       <c r="G39" t="n">
         <v>22.22999954223633</v>
@@ -1691,7 +1691,7 @@
         <v>295.3669128417969</v>
       </c>
       <c r="I39" t="n">
-        <v>1562.760131835938</v>
+        <v>1562.76025390625</v>
       </c>
       <c r="J39" t="n">
         <v>135.5</v>
@@ -1702,7 +1702,7 @@
         <v>44617</v>
       </c>
       <c r="B40" t="n">
-        <v>1968.774780273438</v>
+        <v>1968.774658203125</v>
       </c>
       <c r="C40" t="n">
         <v>2032.849975585938</v>
@@ -1720,7 +1720,7 @@
         <v>24.80999946594238</v>
       </c>
       <c r="H40" t="n">
-        <v>297.0508728027344</v>
+        <v>297.0508422851562</v>
       </c>
       <c r="I40" t="n">
         <v>1570.898071289062</v>
@@ -1766,7 +1766,7 @@
         <v>44622</v>
       </c>
       <c r="B42" t="n">
-        <v>1976.613159179688</v>
+        <v>1976.61328125</v>
       </c>
       <c r="C42" t="n">
         <v>2241.050048828125</v>
@@ -1778,7 +1778,7 @@
         <v>1882.550048828125</v>
       </c>
       <c r="F42" t="n">
-        <v>691.4170532226562</v>
+        <v>691.4171142578125</v>
       </c>
       <c r="G42" t="n">
         <v>24.6200008392334</v>
@@ -1787,7 +1787,7 @@
         <v>292.6725463867188</v>
       </c>
       <c r="I42" t="n">
-        <v>1665.459716796875</v>
+        <v>1665.459594726562</v>
       </c>
       <c r="J42" t="n">
         <v>153.5</v>
@@ -1810,13 +1810,13 @@
         <v>1950.900024414062</v>
       </c>
       <c r="F43" t="n">
-        <v>687.9127197265625</v>
+        <v>687.9127807617188</v>
       </c>
       <c r="G43" t="n">
         <v>24.54000091552734</v>
       </c>
       <c r="H43" t="n">
-        <v>279.2489929199219</v>
+        <v>279.2490234375</v>
       </c>
       <c r="I43" t="n">
         <v>1748.687622070312</v>
@@ -1830,19 +1830,19 @@
         <v>44624</v>
       </c>
       <c r="B44" t="n">
-        <v>1921.934204101562</v>
+        <v>1921.934326171875</v>
       </c>
       <c r="C44" t="n">
         <v>2323.199951171875</v>
       </c>
       <c r="D44" t="n">
-        <v>1611.402709960938</v>
+        <v>1611.40283203125</v>
       </c>
       <c r="E44" t="n">
         <v>1894.300048828125</v>
       </c>
       <c r="F44" t="n">
-        <v>681.5369873046875</v>
+        <v>681.5369262695312</v>
       </c>
       <c r="G44" t="n">
         <v>23.95000076293945</v>
@@ -1851,7 +1851,7 @@
         <v>281.5584411621094</v>
       </c>
       <c r="I44" t="n">
-        <v>1802.558715820312</v>
+        <v>1802.55859375</v>
       </c>
       <c r="J44" t="n">
         <v>167.6999969482422</v>
@@ -1862,7 +1862,7 @@
         <v>44627</v>
       </c>
       <c r="B45" t="n">
-        <v>1864.196533203125</v>
+        <v>1864.196411132812</v>
       </c>
       <c r="C45" t="n">
         <v>2207.35009765625</v>
@@ -1874,13 +1874,13 @@
         <v>1803.75</v>
       </c>
       <c r="F45" t="n">
-        <v>659.7811279296875</v>
+        <v>659.781005859375</v>
       </c>
       <c r="G45" t="n">
         <v>23.29000091552734</v>
       </c>
       <c r="H45" t="n">
-        <v>270.5885925292969</v>
+        <v>270.588623046875</v>
       </c>
       <c r="I45" t="n">
         <v>1712.440673828125</v>
@@ -1906,7 +1906,7 @@
         <v>1783.949951171875</v>
       </c>
       <c r="F46" t="n">
-        <v>670.5372924804688</v>
+        <v>670.5372314453125</v>
       </c>
       <c r="G46" t="n">
         <v>23.73999977111816</v>
@@ -1915,7 +1915,7 @@
         <v>272.2244567871094</v>
       </c>
       <c r="I46" t="n">
-        <v>1627.265502929688</v>
+        <v>1627.265625</v>
       </c>
       <c r="J46" t="n">
         <v>172.3500061035156</v>
@@ -1926,28 +1926,28 @@
         <v>44629</v>
       </c>
       <c r="B47" t="n">
-        <v>1912.661865234375</v>
+        <v>1912.661743164062</v>
       </c>
       <c r="C47" t="n">
         <v>2164.64990234375</v>
       </c>
       <c r="D47" t="n">
-        <v>1652.860229492188</v>
+        <v>1652.860473632812</v>
       </c>
       <c r="E47" t="n">
         <v>1828.75</v>
       </c>
       <c r="F47" t="n">
-        <v>695.115966796875</v>
+        <v>695.1160888671875</v>
       </c>
       <c r="G47" t="n">
         <v>24.26000022888184</v>
       </c>
       <c r="H47" t="n">
-        <v>280.6442565917969</v>
+        <v>280.6442260742188</v>
       </c>
       <c r="I47" t="n">
-        <v>1612.986328125</v>
+        <v>1612.986572265625</v>
       </c>
       <c r="J47" t="n">
         <v>176.3500061035156</v>
@@ -1958,7 +1958,7 @@
         <v>44630</v>
       </c>
       <c r="B48" t="n">
-        <v>1957.351196289062</v>
+        <v>1957.351318359375</v>
       </c>
       <c r="C48" t="n">
         <v>2272.75</v>
@@ -1976,10 +1976,10 @@
         <v>24.5</v>
       </c>
       <c r="H48" t="n">
-        <v>282.1357421875</v>
+        <v>282.1357727050781</v>
       </c>
       <c r="I48" t="n">
-        <v>1693.568481445312</v>
+        <v>1693.568359375</v>
       </c>
       <c r="J48" t="n">
         <v>171.3500061035156</v>
@@ -2011,7 +2011,7 @@
         <v>282.3763732910156</v>
       </c>
       <c r="I49" t="n">
-        <v>1659.418334960938</v>
+        <v>1659.41845703125</v>
       </c>
       <c r="J49" t="n">
         <v>169</v>
@@ -2022,7 +2022,7 @@
         <v>44634</v>
       </c>
       <c r="B50" t="n">
-        <v>1967.3408203125</v>
+        <v>1967.340576171875</v>
       </c>
       <c r="C50" t="n">
         <v>2268.300048828125</v>
@@ -2043,7 +2043,7 @@
         <v>280.2112731933594</v>
       </c>
       <c r="I50" t="n">
-        <v>1647.935180664062</v>
+        <v>1647.93505859375</v>
       </c>
       <c r="J50" t="n">
         <v>162.8999938964844</v>
@@ -2054,7 +2054,7 @@
         <v>44635</v>
       </c>
       <c r="B51" t="n">
-        <v>1969.539428710938</v>
+        <v>1969.539306640625</v>
       </c>
       <c r="C51" t="n">
         <v>2217.550048828125</v>
@@ -2066,7 +2066,7 @@
         <v>1798.75</v>
       </c>
       <c r="F51" t="n">
-        <v>702.1246948242188</v>
+        <v>702.1246337890625</v>
       </c>
       <c r="G51" t="n">
         <v>24.45999908447266</v>
@@ -2092,22 +2092,22 @@
         <v>2305.39990234375</v>
       </c>
       <c r="D52" t="n">
-        <v>1754.084106445312</v>
+        <v>1754.084228515625</v>
       </c>
       <c r="E52" t="n">
         <v>1833.650024414062</v>
       </c>
       <c r="F52" t="n">
-        <v>704.5581665039062</v>
+        <v>704.5582275390625</v>
       </c>
       <c r="G52" t="n">
         <v>24.57999992370605</v>
       </c>
       <c r="H52" t="n">
-        <v>297.6763305664062</v>
+        <v>297.6763610839844</v>
       </c>
       <c r="I52" t="n">
-        <v>1682.63427734375</v>
+        <v>1682.634399414062</v>
       </c>
       <c r="J52" t="n">
         <v>197.0500030517578</v>
@@ -2118,7 +2118,7 @@
         <v>44637</v>
       </c>
       <c r="B53" t="n">
-        <v>2029.09326171875</v>
+        <v>2029.093139648438</v>
       </c>
       <c r="C53" t="n">
         <v>2389.800048828125</v>
@@ -2150,7 +2150,7 @@
         <v>44641</v>
       </c>
       <c r="B54" t="n">
-        <v>1965.14208984375</v>
+        <v>1965.142211914062</v>
       </c>
       <c r="C54" t="n">
         <v>2289.050048828125</v>
@@ -2162,13 +2162,13 @@
         <v>1876.050048828125</v>
       </c>
       <c r="F54" t="n">
-        <v>715.6065063476562</v>
+        <v>715.6064453125</v>
       </c>
       <c r="G54" t="n">
         <v>24.90999984741211</v>
       </c>
       <c r="H54" t="n">
-        <v>289.0159912109375</v>
+        <v>289.0159606933594</v>
       </c>
       <c r="I54" t="n">
         <v>1811.49560546875</v>
@@ -2188,7 +2188,7 @@
         <v>2338.050048828125</v>
       </c>
       <c r="D55" t="n">
-        <v>1827.470458984375</v>
+        <v>1827.470581054688</v>
       </c>
       <c r="E55" t="n">
         <v>1877.449951171875</v>
@@ -2200,10 +2200,10 @@
         <v>24.75</v>
       </c>
       <c r="H55" t="n">
-        <v>289.5452270507812</v>
+        <v>289.5451965332031</v>
       </c>
       <c r="I55" t="n">
-        <v>1881.193237304688</v>
+        <v>1881.193481445312</v>
       </c>
       <c r="J55" t="n">
         <v>238.6000061035156</v>
@@ -2235,7 +2235,7 @@
         <v>286.6103210449219</v>
       </c>
       <c r="I56" t="n">
-        <v>1895.222900390625</v>
+        <v>1895.223022460938</v>
       </c>
       <c r="J56" t="n">
         <v>250.5</v>
@@ -2246,7 +2246,7 @@
         <v>44644</v>
       </c>
       <c r="B57" t="n">
-        <v>1988.705444335938</v>
+        <v>1988.705688476562</v>
       </c>
       <c r="C57" t="n">
         <v>2414.39990234375</v>
@@ -2258,7 +2258,7 @@
         <v>1911.400024414062</v>
       </c>
       <c r="F57" t="n">
-        <v>713.9517211914062</v>
+        <v>713.95166015625</v>
       </c>
       <c r="G57" t="n">
         <v>26.43000030517578</v>
@@ -2267,7 +2267,7 @@
         <v>285.8404846191406</v>
       </c>
       <c r="I57" t="n">
-        <v>1976.853271484375</v>
+        <v>1976.853149414062</v>
       </c>
       <c r="J57" t="n">
         <v>263</v>
@@ -2278,28 +2278,28 @@
         <v>44645</v>
       </c>
       <c r="B58" t="n">
-        <v>1973.219848632812</v>
+        <v>1973.219604492188</v>
       </c>
       <c r="C58" t="n">
         <v>2448.75</v>
       </c>
       <c r="D58" t="n">
-        <v>1862.841674804688</v>
+        <v>1862.841552734375</v>
       </c>
       <c r="E58" t="n">
         <v>1921.25</v>
       </c>
       <c r="F58" t="n">
-        <v>723.4910888671875</v>
+        <v>723.4911499023438</v>
       </c>
       <c r="G58" t="n">
         <v>28.63999938964844</v>
       </c>
       <c r="H58" t="n">
-        <v>286.5621643066406</v>
+        <v>286.5621948242188</v>
       </c>
       <c r="I58" t="n">
-        <v>2051.593994140625</v>
+        <v>2051.59375</v>
       </c>
       <c r="J58" t="n">
         <v>252.1000061035156</v>
@@ -2322,7 +2322,7 @@
         <v>1930.849975585938</v>
       </c>
       <c r="F59" t="n">
-        <v>717.4072875976562</v>
+        <v>717.4072265625</v>
       </c>
       <c r="G59" t="n">
         <v>30.45000076293945</v>
@@ -2342,19 +2342,19 @@
         <v>44649</v>
       </c>
       <c r="B60" t="n">
-        <v>2034.733520507812</v>
+        <v>2034.733276367188</v>
       </c>
       <c r="C60" t="n">
         <v>2461.550048828125</v>
       </c>
       <c r="D60" t="n">
-        <v>1912.979736328125</v>
+        <v>1912.979614257812</v>
       </c>
       <c r="E60" t="n">
         <v>1923.300048828125</v>
       </c>
       <c r="F60" t="n">
-        <v>741.6939086914062</v>
+        <v>741.6939697265625</v>
       </c>
       <c r="G60" t="n">
         <v>34.70999908447266</v>
@@ -2363,7 +2363,7 @@
         <v>291.0367126464844</v>
       </c>
       <c r="I60" t="n">
-        <v>2177.609375</v>
+        <v>2177.609130859375</v>
       </c>
       <c r="J60" t="n">
         <v>227.5500030517578</v>
@@ -2374,7 +2374,7 @@
         <v>44650</v>
       </c>
       <c r="B61" t="n">
-        <v>2056.097900390625</v>
+        <v>2056.09814453125</v>
       </c>
       <c r="C61" t="n">
         <v>2377.39990234375</v>
@@ -2386,7 +2386,7 @@
         <v>1857.150024414062</v>
       </c>
       <c r="F61" t="n">
-        <v>746.9991455078125</v>
+        <v>746.9990234375</v>
       </c>
       <c r="G61" t="n">
         <v>34.29999923706055</v>
@@ -2395,7 +2395,7 @@
         <v>297.8175964355469</v>
       </c>
       <c r="I61" t="n">
-        <v>2121.541259765625</v>
+        <v>2121.541015625</v>
       </c>
       <c r="J61" t="n">
         <v>238.8999938964844</v>
@@ -2406,25 +2406,25 @@
         <v>44651</v>
       </c>
       <c r="B62" t="n">
-        <v>2056.5283203125</v>
+        <v>2056.528564453125</v>
       </c>
       <c r="C62" t="n">
         <v>2368.14990234375</v>
       </c>
       <c r="D62" t="n">
-        <v>2010.262329101562</v>
+        <v>2010.262451171875</v>
       </c>
       <c r="E62" t="n">
         <v>1914.699951171875</v>
       </c>
       <c r="F62" t="n">
-        <v>753.6183471679688</v>
+        <v>753.6182861328125</v>
       </c>
       <c r="G62" t="n">
         <v>37.02000045776367</v>
       </c>
       <c r="H62" t="n">
-        <v>294.0832214355469</v>
+        <v>294.0831909179688</v>
       </c>
       <c r="I62" t="n">
         <v>2146.654296875</v>
@@ -2456,10 +2456,10 @@
         <v>40.68999862670898</v>
       </c>
       <c r="H63" t="n">
-        <v>299.6847839355469</v>
+        <v>299.684814453125</v>
       </c>
       <c r="I63" t="n">
-        <v>2246.208251953125</v>
+        <v>2246.20849609375</v>
       </c>
       <c r="J63" t="n">
         <v>223.25</v>
@@ -2476,13 +2476,13 @@
         <v>2453.5</v>
       </c>
       <c r="D64" t="n">
-        <v>2061.2490234375</v>
+        <v>2061.248779296875</v>
       </c>
       <c r="E64" t="n">
         <v>2110.449951171875</v>
       </c>
       <c r="F64" t="n">
-        <v>796.7892456054688</v>
+        <v>796.789306640625</v>
       </c>
       <c r="G64" t="n">
         <v>42.38999938964844</v>
@@ -2491,7 +2491,7 @@
         <v>306.2691040039062</v>
       </c>
       <c r="I64" t="n">
-        <v>2366.33251953125</v>
+        <v>2366.332763671875</v>
       </c>
       <c r="J64" t="n">
         <v>224.0500030517578</v>
@@ -2508,13 +2508,13 @@
         <v>2443.85009765625</v>
       </c>
       <c r="D65" t="n">
-        <v>2135.083740234375</v>
+        <v>2135.083984375</v>
       </c>
       <c r="E65" t="n">
         <v>2189.800048828125</v>
       </c>
       <c r="F65" t="n">
-        <v>825.5050659179688</v>
+        <v>825.505126953125</v>
       </c>
       <c r="G65" t="n">
         <v>46.61999893188477</v>
@@ -2523,7 +2523,7 @@
         <v>311.3302001953125</v>
       </c>
       <c r="I65" t="n">
-        <v>2464.538818359375</v>
+        <v>2464.538330078125</v>
       </c>
       <c r="J65" t="n">
         <v>224.5</v>
@@ -2540,7 +2540,7 @@
         <v>2484.050048828125</v>
       </c>
       <c r="D66" t="n">
-        <v>2155.188720703125</v>
+        <v>2155.189208984375</v>
       </c>
       <c r="E66" t="n">
         <v>2197.39990234375</v>
@@ -2552,7 +2552,7 @@
         <v>48.95000076293945</v>
       </c>
       <c r="H66" t="n">
-        <v>315.1629028320312</v>
+        <v>315.162841796875</v>
       </c>
       <c r="I66" t="n">
         <v>2533.23779296875</v>
@@ -2572,13 +2572,13 @@
         <v>2449.64990234375</v>
       </c>
       <c r="D67" t="n">
-        <v>2094.374755859375</v>
+        <v>2094.37451171875</v>
       </c>
       <c r="E67" t="n">
         <v>2166</v>
       </c>
       <c r="F67" t="n">
-        <v>795.669921875</v>
+        <v>795.6698608398438</v>
       </c>
       <c r="G67" t="n">
         <v>46.5099983215332</v>
@@ -2587,7 +2587,7 @@
         <v>319.978271484375</v>
       </c>
       <c r="I67" t="n">
-        <v>2359.2431640625</v>
+        <v>2359.242919921875</v>
       </c>
       <c r="J67" t="n">
         <v>212.1999969482422</v>
@@ -2598,7 +2598,7 @@
         <v>44659</v>
       </c>
       <c r="B68" t="n">
-        <v>2132.380126953125</v>
+        <v>2132.38037109375</v>
       </c>
       <c r="C68" t="n">
         <v>2540.25</v>
@@ -2610,7 +2610,7 @@
         <v>2321.85009765625</v>
       </c>
       <c r="F68" t="n">
-        <v>816.9876098632812</v>
+        <v>816.9876708984375</v>
       </c>
       <c r="G68" t="n">
         <v>44.18999862670898</v>
@@ -2630,19 +2630,19 @@
         <v>44662</v>
       </c>
       <c r="B69" t="n">
-        <v>2193.633544921875</v>
+        <v>2193.6337890625</v>
       </c>
       <c r="C69" t="n">
         <v>2756.5</v>
       </c>
       <c r="D69" t="n">
-        <v>2175.34375</v>
+        <v>2175.34423828125</v>
       </c>
       <c r="E69" t="n">
         <v>2665.14990234375</v>
       </c>
       <c r="F69" t="n">
-        <v>831.832275390625</v>
+        <v>831.8322143554688</v>
       </c>
       <c r="G69" t="n">
         <v>46.31999969482422</v>
@@ -2651,7 +2651,7 @@
         <v>353.9808654785156</v>
       </c>
       <c r="I69" t="n">
-        <v>2661.1005859375</v>
+        <v>2661.100830078125</v>
       </c>
       <c r="J69" t="n">
         <v>214.4499969482422</v>
@@ -2674,7 +2674,7 @@
         <v>2792.39990234375</v>
       </c>
       <c r="F70" t="n">
-        <v>822.4388427734375</v>
+        <v>822.4387817382812</v>
       </c>
       <c r="G70" t="n">
         <v>46.15999984741211</v>
@@ -2706,13 +2706,13 @@
         <v>2864.300048828125</v>
       </c>
       <c r="F71" t="n">
-        <v>818.1557006835938</v>
+        <v>818.15576171875</v>
       </c>
       <c r="G71" t="n">
         <v>44.65000152587891</v>
       </c>
       <c r="H71" t="n">
-        <v>362.8255004882812</v>
+        <v>362.8255310058594</v>
       </c>
       <c r="I71" t="n">
         <v>2497.19091796875</v>
@@ -2732,7 +2732,7 @@
         <v>2728.300048828125</v>
       </c>
       <c r="D72" t="n">
-        <v>2228.87451171875</v>
+        <v>2228.874267578125</v>
       </c>
       <c r="E72" t="n">
         <v>2970.5</v>
@@ -2744,7 +2744,7 @@
         <v>46.88000106811523</v>
       </c>
       <c r="H72" t="n">
-        <v>357.1256408691406</v>
+        <v>357.1256103515625</v>
       </c>
       <c r="I72" t="n">
         <v>2491.349365234375</v>
@@ -2758,7 +2758,7 @@
         <v>44670</v>
       </c>
       <c r="B73" t="n">
-        <v>2020.335815429688</v>
+        <v>2020.335693359375</v>
       </c>
       <c r="C73" t="n">
         <v>2598.050048828125</v>
@@ -2770,13 +2770,13 @@
         <v>2911.949951171875</v>
       </c>
       <c r="F73" t="n">
-        <v>797.519287109375</v>
+        <v>797.5193481445312</v>
       </c>
       <c r="G73" t="n">
         <v>46.4900016784668</v>
       </c>
       <c r="H73" t="n">
-        <v>348.1336059570312</v>
+        <v>348.1336364746094</v>
       </c>
       <c r="I73" t="n">
         <v>2365.93310546875</v>
@@ -2796,7 +2796,7 @@
         <v>2687.550048828125</v>
       </c>
       <c r="D74" t="n">
-        <v>2179.085693359375</v>
+        <v>2179.08544921875</v>
       </c>
       <c r="E74" t="n">
         <v>2810.85009765625</v>
@@ -2808,7 +2808,7 @@
         <v>47.0099983215332</v>
       </c>
       <c r="H74" t="n">
-        <v>364.8891906738281</v>
+        <v>364.8892211914062</v>
       </c>
       <c r="I74" t="n">
         <v>2474.7734375</v>
@@ -2822,7 +2822,7 @@
         <v>44672</v>
       </c>
       <c r="B75" t="n">
-        <v>2230.179443359375</v>
+        <v>2230.1796875</v>
       </c>
       <c r="C75" t="n">
         <v>2699.60009765625</v>
@@ -2840,7 +2840,7 @@
         <v>49.36000061035156</v>
       </c>
       <c r="H75" t="n">
-        <v>370.8347778320312</v>
+        <v>370.8347473144531</v>
       </c>
       <c r="I75" t="n">
         <v>2439.775146484375</v>
@@ -2854,13 +2854,13 @@
         <v>44673</v>
       </c>
       <c r="B76" t="n">
-        <v>2223.44970703125</v>
+        <v>2223.449951171875</v>
       </c>
       <c r="C76" t="n">
         <v>2658.550048828125</v>
       </c>
       <c r="D76" t="n">
-        <v>2268.236328125</v>
+        <v>2268.236572265625</v>
       </c>
       <c r="E76" t="n">
         <v>2882.800048828125</v>
@@ -2872,10 +2872,10 @@
         <v>51.81999969482422</v>
       </c>
       <c r="H76" t="n">
-        <v>367.7391662597656</v>
+        <v>367.7391357421875</v>
       </c>
       <c r="I76" t="n">
-        <v>2409.46923828125</v>
+        <v>2409.468994140625</v>
       </c>
       <c r="J76" t="n">
         <v>211.1999969482422</v>
@@ -2907,7 +2907,7 @@
         <v>369.8520202636719</v>
       </c>
       <c r="I77" t="n">
-        <v>2416.459228515625</v>
+        <v>2416.458984375</v>
       </c>
       <c r="J77" t="n">
         <v>201.8500061035156</v>
@@ -2936,7 +2936,7 @@
         <v>57.13000106811523</v>
       </c>
       <c r="H78" t="n">
-        <v>378.5000915527344</v>
+        <v>378.5000610351562</v>
       </c>
       <c r="I78" t="n">
         <v>2558.750732421875</v>
@@ -2968,10 +2968,10 @@
         <v>59.84000015258789</v>
       </c>
       <c r="H79" t="n">
-        <v>377.9104614257812</v>
+        <v>377.910400390625</v>
       </c>
       <c r="I79" t="n">
-        <v>2499.337890625</v>
+        <v>2499.337646484375</v>
       </c>
       <c r="J79" t="n">
         <v>200.8999938964844</v>
@@ -2994,16 +2994,16 @@
         <v>2912.199951171875</v>
       </c>
       <c r="F80" t="n">
-        <v>863.5169067382812</v>
+        <v>863.5169677734375</v>
       </c>
       <c r="G80" t="n">
         <v>56.84999847412109</v>
       </c>
       <c r="H80" t="n">
-        <v>376.7311706542969</v>
+        <v>376.7311401367188</v>
       </c>
       <c r="I80" t="n">
-        <v>2558.850830078125</v>
+        <v>2558.850341796875</v>
       </c>
       <c r="J80" t="n">
         <v>199.8999938964844</v>
@@ -3026,16 +3026,16 @@
         <v>2882.800048828125</v>
       </c>
       <c r="F81" t="n">
-        <v>833.6331176757812</v>
+        <v>833.633056640625</v>
       </c>
       <c r="G81" t="n">
         <v>56.06999969482422</v>
       </c>
       <c r="H81" t="n">
-        <v>365.773681640625</v>
+        <v>365.7736511230469</v>
       </c>
       <c r="I81" t="n">
-        <v>2447.36376953125</v>
+        <v>2447.363525390625</v>
       </c>
       <c r="J81" t="n">
         <v>189.9499969482422</v>
@@ -3058,16 +3058,16 @@
         <v>2830.35009765625</v>
       </c>
       <c r="F82" t="n">
-        <v>833.7791137695312</v>
+        <v>833.779052734375</v>
       </c>
       <c r="G82" t="n">
         <v>56.06999969482422</v>
       </c>
       <c r="H82" t="n">
-        <v>371.6209411621094</v>
+        <v>371.6209106445312</v>
       </c>
       <c r="I82" t="n">
-        <v>2484.559326171875</v>
+        <v>2484.5595703125</v>
       </c>
       <c r="J82" t="n">
         <v>186.3999938964844</v>
@@ -3096,7 +3096,7 @@
         <v>53.27000045776367</v>
       </c>
       <c r="H83" t="n">
-        <v>361.7444763183594</v>
+        <v>361.7444458007812</v>
       </c>
       <c r="I83" t="n">
         <v>2443.4697265625</v>
@@ -3110,7 +3110,7 @@
         <v>44686</v>
       </c>
       <c r="B84" t="n">
-        <v>2237.793212890625</v>
+        <v>2237.79345703125</v>
       </c>
       <c r="C84" t="n">
         <v>2801.64990234375</v>
@@ -3122,7 +3122,7 @@
         <v>2845.89990234375</v>
       </c>
       <c r="F84" t="n">
-        <v>789.7806396484375</v>
+        <v>789.7807006835938</v>
       </c>
       <c r="G84" t="n">
         <v>55.63000106811523</v>
@@ -3131,7 +3131,7 @@
         <v>360.0246887207031</v>
       </c>
       <c r="I84" t="n">
-        <v>2446.914306640625</v>
+        <v>2446.91455078125</v>
       </c>
       <c r="J84" t="n">
         <v>180.3500061035156</v>
@@ -3160,10 +3160,10 @@
         <v>58.40999984741211</v>
       </c>
       <c r="H85" t="n">
-        <v>359.0910339355469</v>
+        <v>359.091064453125</v>
       </c>
       <c r="I85" t="n">
-        <v>2434.083251953125</v>
+        <v>2434.0830078125</v>
       </c>
       <c r="J85" t="n">
         <v>174.3500061035156</v>
@@ -3174,7 +3174,7 @@
         <v>44690</v>
       </c>
       <c r="B86" t="n">
-        <v>2193.633544921875</v>
+        <v>2193.6337890625</v>
       </c>
       <c r="C86" t="n">
         <v>2703.449951171875</v>
@@ -3195,7 +3195,7 @@
         <v>360.4177856445312</v>
       </c>
       <c r="I86" t="n">
-        <v>2371.774658203125</v>
+        <v>2371.7744140625</v>
       </c>
       <c r="J86" t="n">
         <v>170.6999969482422</v>
@@ -3206,19 +3206,19 @@
         <v>44691</v>
       </c>
       <c r="B87" t="n">
-        <v>2159.8876953125</v>
+        <v>2159.887939453125</v>
       </c>
       <c r="C87" t="n">
         <v>2482.550048828125</v>
       </c>
       <c r="D87" t="n">
-        <v>2104.80126953125</v>
+        <v>2104.801513671875</v>
       </c>
       <c r="E87" t="n">
         <v>2486.699951171875</v>
       </c>
       <c r="F87" t="n">
-        <v>748.6539306640625</v>
+        <v>748.6538696289062</v>
       </c>
       <c r="G87" t="n">
         <v>53.5099983215332</v>
@@ -3227,7 +3227,7 @@
         <v>352.0154113769531</v>
       </c>
       <c r="I87" t="n">
-        <v>2357.195556640625</v>
+        <v>2357.196044921875</v>
       </c>
       <c r="J87" t="n">
         <v>166.1499938964844</v>
@@ -3238,25 +3238,25 @@
         <v>44692</v>
       </c>
       <c r="B88" t="n">
-        <v>2129.53076171875</v>
+        <v>2129.531005859375</v>
       </c>
       <c r="C88" t="n">
         <v>2296</v>
       </c>
       <c r="D88" t="n">
-        <v>2114.57958984375</v>
+        <v>2114.579345703125</v>
       </c>
       <c r="E88" t="n">
         <v>2648.050048828125</v>
       </c>
       <c r="F88" t="n">
-        <v>739.698486328125</v>
+        <v>739.6985473632812</v>
       </c>
       <c r="G88" t="n">
         <v>51.06000137329102</v>
       </c>
       <c r="H88" t="n">
-        <v>352.8507080078125</v>
+        <v>352.8507385253906</v>
       </c>
       <c r="I88" t="n">
         <v>2351.604248046875</v>
@@ -3276,13 +3276,13 @@
         <v>2187.050048828125</v>
       </c>
       <c r="D89" t="n">
-        <v>2040.644653320312</v>
+        <v>2040.64453125</v>
       </c>
       <c r="E89" t="n">
         <v>2436.800048828125</v>
       </c>
       <c r="F89" t="n">
-        <v>694.3372802734375</v>
+        <v>694.3372192382812</v>
       </c>
       <c r="G89" t="n">
         <v>48.5099983215332</v>
@@ -3308,13 +3308,13 @@
         <v>2190.60009765625</v>
       </c>
       <c r="D90" t="n">
-        <v>2049.57470703125</v>
+        <v>2049.574462890625</v>
       </c>
       <c r="E90" t="n">
         <v>2171.550048828125</v>
       </c>
       <c r="F90" t="n">
-        <v>687.1340942382812</v>
+        <v>687.1341552734375</v>
       </c>
       <c r="G90" t="n">
         <v>50.93000030517578</v>
@@ -3323,7 +3323,7 @@
         <v>352.8998718261719</v>
       </c>
       <c r="I90" t="n">
-        <v>2365.633544921875</v>
+        <v>2365.6337890625</v>
       </c>
       <c r="J90" t="n">
         <v>157.5</v>
@@ -3340,22 +3340,22 @@
         <v>2249.89990234375</v>
       </c>
       <c r="D91" t="n">
-        <v>2101.209228515625</v>
+        <v>2101.20947265625</v>
       </c>
       <c r="E91" t="n">
         <v>2281.699951171875</v>
       </c>
       <c r="F91" t="n">
-        <v>693.5585327148438</v>
+        <v>693.55859375</v>
       </c>
       <c r="G91" t="n">
         <v>53.47000122070312</v>
       </c>
       <c r="H91" t="n">
-        <v>361.6462097167969</v>
+        <v>361.6461791992188</v>
       </c>
       <c r="I91" t="n">
-        <v>2385.055419921875</v>
+        <v>2385.05517578125</v>
       </c>
       <c r="J91" t="n">
         <v>165.3500061035156</v>
@@ -3366,13 +3366,13 @@
         <v>44698</v>
       </c>
       <c r="B92" t="n">
-        <v>2186.707763671875</v>
+        <v>2186.7080078125</v>
       </c>
       <c r="C92" t="n">
         <v>2333.39990234375</v>
       </c>
       <c r="D92" t="n">
-        <v>2179.9833984375</v>
+        <v>2179.983642578125</v>
       </c>
       <c r="E92" t="n">
         <v>2285.800048828125</v>
@@ -3410,7 +3410,7 @@
         <v>2396.10009765625</v>
       </c>
       <c r="F93" t="n">
-        <v>739.6011962890625</v>
+        <v>739.6011352539062</v>
       </c>
       <c r="G93" t="n">
         <v>58.93999862670898</v>
@@ -3419,7 +3419,7 @@
         <v>354.8653259277344</v>
       </c>
       <c r="I93" t="n">
-        <v>2482.063232421875</v>
+        <v>2482.06298828125</v>
       </c>
       <c r="J93" t="n">
         <v>176.1999969482422</v>
@@ -3430,13 +3430,13 @@
         <v>44700</v>
       </c>
       <c r="B94" t="n">
-        <v>2191.766845703125</v>
+        <v>2191.76708984375</v>
       </c>
       <c r="C94" t="n">
         <v>2265</v>
       </c>
       <c r="D94" t="n">
-        <v>2110.039794921875</v>
+        <v>2110.03955078125</v>
       </c>
       <c r="E94" t="n">
         <v>2317.5</v>
@@ -3448,7 +3448,7 @@
         <v>59.47999954223633</v>
       </c>
       <c r="H94" t="n">
-        <v>357.7152099609375</v>
+        <v>357.7152709960938</v>
       </c>
       <c r="I94" t="n">
         <v>2375.02001953125</v>
@@ -3474,16 +3474,16 @@
         <v>2273.64990234375</v>
       </c>
       <c r="F95" t="n">
-        <v>747.1450805664062</v>
+        <v>747.1451416015625</v>
       </c>
       <c r="G95" t="n">
         <v>62.45000076293945</v>
       </c>
       <c r="H95" t="n">
-        <v>356.7325134277344</v>
+        <v>356.7325439453125</v>
       </c>
       <c r="I95" t="n">
-        <v>2376.8671875</v>
+        <v>2376.867431640625</v>
       </c>
       <c r="J95" t="n">
         <v>168.3999938964844</v>
@@ -3494,28 +3494,28 @@
         <v>44704</v>
       </c>
       <c r="B96" t="n">
-        <v>2174.476318359375</v>
+        <v>2174.4765625</v>
       </c>
       <c r="C96" t="n">
         <v>2199.199951171875</v>
       </c>
       <c r="D96" t="n">
-        <v>2165.81494140625</v>
+        <v>2165.815185546875</v>
       </c>
       <c r="E96" t="n">
         <v>2248.35009765625</v>
       </c>
       <c r="F96" t="n">
-        <v>733.5172119140625</v>
+        <v>733.517333984375</v>
       </c>
       <c r="G96" t="n">
         <v>65.56999969482422</v>
       </c>
       <c r="H96" t="n">
-        <v>357.1747741699219</v>
+        <v>357.1747436523438</v>
       </c>
       <c r="I96" t="n">
-        <v>2328.188720703125</v>
+        <v>2328.18896484375</v>
       </c>
       <c r="J96" t="n">
         <v>160.6000061035156</v>
@@ -3526,25 +3526,25 @@
         <v>44705</v>
       </c>
       <c r="B97" t="n">
-        <v>2172.069580078125</v>
+        <v>2172.06982421875</v>
       </c>
       <c r="C97" t="n">
         <v>2196.5</v>
       </c>
       <c r="D97" t="n">
-        <v>2155.388427734375</v>
+        <v>2155.38818359375</v>
       </c>
       <c r="E97" t="n">
         <v>2136.300048828125</v>
       </c>
       <c r="F97" t="n">
-        <v>732.154541015625</v>
+        <v>732.1546020507812</v>
       </c>
       <c r="G97" t="n">
         <v>62.29999923706055</v>
       </c>
       <c r="H97" t="n">
-        <v>355.2092895507812</v>
+        <v>355.2093200683594</v>
       </c>
       <c r="I97" t="n">
         <v>2324.84326171875</v>
@@ -3558,19 +3558,19 @@
         <v>44706</v>
       </c>
       <c r="B98" t="n">
-        <v>2147.65673828125</v>
+        <v>2147.656494140625</v>
       </c>
       <c r="C98" t="n">
         <v>2087.949951171875</v>
       </c>
       <c r="D98" t="n">
-        <v>2069.530029296875</v>
+        <v>2069.5302734375</v>
       </c>
       <c r="E98" t="n">
         <v>2187.35009765625</v>
       </c>
       <c r="F98" t="n">
-        <v>689.080810546875</v>
+        <v>689.0809326171875</v>
       </c>
       <c r="G98" t="n">
         <v>59.86999893188477</v>
@@ -3579,7 +3579,7 @@
         <v>355.4549560546875</v>
       </c>
       <c r="I98" t="n">
-        <v>2213.70654296875</v>
+        <v>2213.706298828125</v>
       </c>
       <c r="J98" t="n">
         <v>155.3500061035156</v>
@@ -3590,13 +3590,13 @@
         <v>44707</v>
       </c>
       <c r="B99" t="n">
-        <v>2169.17138671875</v>
+        <v>2169.171630859375</v>
       </c>
       <c r="C99" t="n">
         <v>2148.10009765625</v>
       </c>
       <c r="D99" t="n">
-        <v>2041.842041015625</v>
+        <v>2041.841918945312</v>
       </c>
       <c r="E99" t="n">
         <v>2164</v>
@@ -3608,7 +3608,7 @@
         <v>62.86000061035156</v>
       </c>
       <c r="H99" t="n">
-        <v>359.0910339355469</v>
+        <v>359.091064453125</v>
       </c>
       <c r="I99" t="n">
         <v>2387.851318359375</v>
@@ -3628,7 +3628,7 @@
         <v>2186.25</v>
       </c>
       <c r="D100" t="n">
-        <v>2075.5166015625</v>
+        <v>2075.516845703125</v>
       </c>
       <c r="E100" t="n">
         <v>2166.449951171875</v>
@@ -3640,10 +3640,10 @@
         <v>65.62000274658203</v>
       </c>
       <c r="H100" t="n">
-        <v>359.9755554199219</v>
+        <v>359.9755249023438</v>
       </c>
       <c r="I100" t="n">
-        <v>2452.85546875</v>
+        <v>2452.855712890625</v>
       </c>
       <c r="J100" t="n">
         <v>154.6999969482422</v>
@@ -3654,7 +3654,7 @@
         <v>44711</v>
       </c>
       <c r="B101" t="n">
-        <v>2169.515380859375</v>
+        <v>2169.515625</v>
       </c>
       <c r="C101" t="n">
         <v>2162</v>
@@ -3672,10 +3672,10 @@
         <v>68.05000305175781</v>
       </c>
       <c r="H101" t="n">
-        <v>365.1348876953125</v>
+        <v>365.1348571777344</v>
       </c>
       <c r="I101" t="n">
-        <v>2585.7109375</v>
+        <v>2585.71142578125</v>
       </c>
       <c r="J101" t="n">
         <v>162.3999938964844</v>
@@ -3698,7 +3698,7 @@
         <v>1888.949951171875</v>
       </c>
       <c r="F102" t="n">
-        <v>720.1814575195312</v>
+        <v>720.1815185546875</v>
       </c>
       <c r="G102" t="n">
         <v>64.65000152587891</v>
@@ -3707,7 +3707,7 @@
         <v>363.0220336914062</v>
       </c>
       <c r="I102" t="n">
-        <v>2394.39111328125</v>
+        <v>2394.391357421875</v>
       </c>
       <c r="J102" t="n">
         <v>170.5</v>
@@ -3730,13 +3730,13 @@
         <v>1848.400024414062</v>
       </c>
       <c r="F103" t="n">
-        <v>717.3099365234375</v>
+        <v>717.3098754882812</v>
       </c>
       <c r="G103" t="n">
         <v>61.41999816894531</v>
       </c>
       <c r="H103" t="n">
-        <v>365.2331848144531</v>
+        <v>365.2331237792969</v>
       </c>
       <c r="I103" t="n">
         <v>2322.496826171875</v>
@@ -3762,7 +3762,7 @@
         <v>1925.800048828125</v>
       </c>
       <c r="F104" t="n">
-        <v>728.5529174804688</v>
+        <v>728.5528564453125</v>
       </c>
       <c r="G104" t="n">
         <v>59.06999969482422</v>
@@ -3771,7 +3771,7 @@
         <v>367.0512084960938</v>
       </c>
       <c r="I104" t="n">
-        <v>2442.271728515625</v>
+        <v>2442.271484375</v>
       </c>
       <c r="J104" t="n">
         <v>173.0500030517578</v>
@@ -3788,13 +3788,13 @@
         <v>1956.050048828125</v>
       </c>
       <c r="D105" t="n">
-        <v>2185.122314453125</v>
+        <v>2185.1220703125</v>
       </c>
       <c r="E105" t="n">
         <v>1855.900024414062</v>
       </c>
       <c r="F105" t="n">
-        <v>720.230224609375</v>
+        <v>720.2301635742188</v>
       </c>
       <c r="G105" t="n">
         <v>56.81999969482422</v>
@@ -3803,7 +3803,7 @@
         <v>360.5651550292969</v>
       </c>
       <c r="I105" t="n">
-        <v>2386.952392578125</v>
+        <v>2386.9521484375</v>
       </c>
       <c r="J105" t="n">
         <v>170</v>
@@ -3814,7 +3814,7 @@
         <v>44718</v>
       </c>
       <c r="B106" t="n">
-        <v>2100.648193359375</v>
+        <v>2100.6484375</v>
       </c>
       <c r="C106" t="n">
         <v>2017.099975585938</v>
@@ -3826,7 +3826,7 @@
         <v>1802.349975585938</v>
       </c>
       <c r="F106" t="n">
-        <v>721.5443115234375</v>
+        <v>721.5442504882812</v>
       </c>
       <c r="G106" t="n">
         <v>59.65999984741211</v>
@@ -3835,7 +3835,7 @@
         <v>358.5997009277344</v>
       </c>
       <c r="I106" t="n">
-        <v>2476.471435546875</v>
+        <v>2476.47119140625</v>
       </c>
       <c r="J106" t="n">
         <v>178.5</v>
@@ -3858,13 +3858,13 @@
         <v>1829.25</v>
       </c>
       <c r="F107" t="n">
-        <v>715.0223999023438</v>
+        <v>715.0223388671875</v>
       </c>
       <c r="G107" t="n">
         <v>58.27999877929688</v>
       </c>
       <c r="H107" t="n">
-        <v>357.0765075683594</v>
+        <v>357.0764770507812</v>
       </c>
       <c r="I107" t="n">
         <v>2495.29345703125</v>
@@ -3884,22 +3884,22 @@
         <v>2091.89990234375</v>
       </c>
       <c r="D108" t="n">
-        <v>2172.3505859375</v>
+        <v>2172.350830078125</v>
       </c>
       <c r="E108" t="n">
         <v>1801.900024414062</v>
       </c>
       <c r="F108" t="n">
-        <v>709.2305908203125</v>
+        <v>709.2305297851562</v>
       </c>
       <c r="G108" t="n">
         <v>56.90000152587891</v>
       </c>
       <c r="H108" t="n">
-        <v>356.7816162109375</v>
+        <v>356.7816467285156</v>
       </c>
       <c r="I108" t="n">
-        <v>2443.768798828125</v>
+        <v>2443.76904296875</v>
       </c>
       <c r="J108" t="n">
         <v>210.6999969482422</v>
@@ -3916,7 +3916,7 @@
         <v>2116.5</v>
       </c>
       <c r="D109" t="n">
-        <v>2214.257080078125</v>
+        <v>2214.2568359375</v>
       </c>
       <c r="E109" t="n">
         <v>1812.650024414062</v>
@@ -3928,10 +3928,10 @@
         <v>57.54999923706055</v>
       </c>
       <c r="H109" t="n">
-        <v>358.9927673339844</v>
+        <v>358.9927978515625</v>
       </c>
       <c r="I109" t="n">
-        <v>2494.394775390625</v>
+        <v>2494.39501953125</v>
       </c>
       <c r="J109" t="n">
         <v>204.0500030517578</v>
@@ -3948,13 +3948,13 @@
         <v>2051.89990234375</v>
       </c>
       <c r="D110" t="n">
-        <v>2198.193115234375</v>
+        <v>2198.19287109375</v>
       </c>
       <c r="E110" t="n">
         <v>1757.599975585938</v>
       </c>
       <c r="F110" t="n">
-        <v>707.089111328125</v>
+        <v>707.0890502929688</v>
       </c>
       <c r="G110" t="n">
         <v>56.02000045776367</v>
@@ -3963,7 +3963,7 @@
         <v>358.8453674316406</v>
       </c>
       <c r="I110" t="n">
-        <v>2394.791015625</v>
+        <v>2394.790771484375</v>
       </c>
       <c r="J110" t="n">
         <v>199.3000030517578</v>
@@ -3974,7 +3974,7 @@
         <v>44725</v>
       </c>
       <c r="B111" t="n">
-        <v>2083.94677734375</v>
+        <v>2083.947021484375</v>
       </c>
       <c r="C111" t="n">
         <v>2051.89990234375</v>
@@ -3992,10 +3992,10 @@
         <v>53.2400016784668</v>
       </c>
       <c r="H111" t="n">
-        <v>356.4377136230469</v>
+        <v>356.437744140625</v>
       </c>
       <c r="I111" t="n">
-        <v>2334.12939453125</v>
+        <v>2334.129638671875</v>
       </c>
       <c r="J111" t="n">
         <v>180</v>
@@ -4018,13 +4018,13 @@
         <v>1788.75</v>
       </c>
       <c r="F112" t="n">
-        <v>685.9658813476562</v>
+        <v>685.9659423828125</v>
       </c>
       <c r="G112" t="n">
         <v>53.33000183105469</v>
       </c>
       <c r="H112" t="n">
-        <v>353.342041015625</v>
+        <v>353.3421020507812</v>
       </c>
       <c r="I112" t="n">
         <v>2371.225341796875</v>
@@ -4038,13 +4038,13 @@
         <v>44727</v>
       </c>
       <c r="B113" t="n">
-        <v>2085.322021484375</v>
+        <v>2085.322265625</v>
       </c>
       <c r="C113" t="n">
         <v>2057.300048828125</v>
       </c>
       <c r="D113" t="n">
-        <v>2179.734130859375</v>
+        <v>2179.734375</v>
       </c>
       <c r="E113" t="n">
         <v>1757.849975585938</v>
@@ -4056,7 +4056,7 @@
         <v>54.40999984741211</v>
       </c>
       <c r="H113" t="n">
-        <v>355.70068359375</v>
+        <v>355.7006530761719</v>
       </c>
       <c r="I113" t="n">
         <v>2348.359130859375</v>
@@ -4070,28 +4070,28 @@
         <v>44728</v>
       </c>
       <c r="B114" t="n">
-        <v>2047.59765625</v>
+        <v>2047.597534179688</v>
       </c>
       <c r="C114" t="n">
         <v>2124.64990234375</v>
       </c>
       <c r="D114" t="n">
-        <v>2078.3603515625</v>
+        <v>2078.360107421875</v>
       </c>
       <c r="E114" t="n">
         <v>1711.099975585938</v>
       </c>
       <c r="F114" t="n">
-        <v>663.577392578125</v>
+        <v>663.5774536132812</v>
       </c>
       <c r="G114" t="n">
         <v>51.86000061035156</v>
       </c>
       <c r="H114" t="n">
-        <v>353.1946411132812</v>
+        <v>353.1946716308594</v>
       </c>
       <c r="I114" t="n">
-        <v>2373.022705078125</v>
+        <v>2373.0224609375</v>
       </c>
       <c r="J114" t="n">
         <v>182.8500061035156</v>
@@ -4114,7 +4114,7 @@
         <v>1711.25</v>
       </c>
       <c r="F115" t="n">
-        <v>651.1663818359375</v>
+        <v>651.1663208007812</v>
       </c>
       <c r="G115" t="n">
         <v>52.2599983215332</v>
@@ -4123,7 +4123,7 @@
         <v>351.1800842285156</v>
       </c>
       <c r="I115" t="n">
-        <v>2145.90576171875</v>
+        <v>2145.905517578125</v>
       </c>
       <c r="J115" t="n">
         <v>177.3999938964844</v>
@@ -4146,7 +4146,7 @@
         <v>1743.650024414062</v>
       </c>
       <c r="F116" t="n">
-        <v>645.5205688476562</v>
+        <v>645.5205078125</v>
       </c>
       <c r="G116" t="n">
         <v>49.65000152587891</v>
@@ -4155,7 +4155,7 @@
         <v>351.1309204101562</v>
       </c>
       <c r="I116" t="n">
-        <v>1986.289306640625</v>
+        <v>1986.28955078125</v>
       </c>
       <c r="J116" t="n">
         <v>162.25</v>
@@ -4172,7 +4172,7 @@
         <v>2215.050048828125</v>
       </c>
       <c r="D117" t="n">
-        <v>2156.984619140625</v>
+        <v>2156.98486328125</v>
       </c>
       <c r="E117" t="n">
         <v>1809.099975585938</v>
@@ -4184,7 +4184,7 @@
         <v>50.81000137329102</v>
       </c>
       <c r="H117" t="n">
-        <v>352.7032775878906</v>
+        <v>352.7033081054688</v>
       </c>
       <c r="I117" t="n">
         <v>2379.413330078125</v>
@@ -4210,16 +4210,16 @@
         <v>1736.099975585938</v>
       </c>
       <c r="F118" t="n">
-        <v>650.5335693359375</v>
+        <v>650.5336303710938</v>
       </c>
       <c r="G118" t="n">
         <v>49.45999908447266</v>
       </c>
       <c r="H118" t="n">
-        <v>351.7696838378906</v>
+        <v>351.7697143554688</v>
       </c>
       <c r="I118" t="n">
-        <v>2267.4775390625</v>
+        <v>2267.477294921875</v>
       </c>
       <c r="J118" t="n">
         <v>172.3500061035156</v>
@@ -4242,13 +4242,13 @@
         <v>1796.75</v>
       </c>
       <c r="F119" t="n">
-        <v>657.3475341796875</v>
+        <v>657.3474731445312</v>
       </c>
       <c r="G119" t="n">
         <v>50.52000045776367</v>
       </c>
       <c r="H119" t="n">
-        <v>352.7524719238281</v>
+        <v>352.75244140625</v>
       </c>
       <c r="I119" t="n">
         <v>2261.336181640625</v>
@@ -4280,7 +4280,7 @@
         <v>52.88999938964844</v>
       </c>
       <c r="H120" t="n">
-        <v>354.3739624023438</v>
+        <v>354.3739318847656</v>
       </c>
       <c r="I120" t="n">
         <v>2288.2470703125</v>
@@ -4306,7 +4306,7 @@
         <v>1917.650024414062</v>
       </c>
       <c r="F121" t="n">
-        <v>669.4664916992188</v>
+        <v>669.466552734375</v>
       </c>
       <c r="G121" t="n">
         <v>54.58000183105469</v>
@@ -4315,7 +4315,7 @@
         <v>358.8453674316406</v>
       </c>
       <c r="I121" t="n">
-        <v>2286.449951171875</v>
+        <v>2286.44970703125</v>
       </c>
       <c r="J121" t="n">
         <v>175.75</v>
@@ -4332,13 +4332,13 @@
         <v>2163.39990234375</v>
       </c>
       <c r="D122" t="n">
-        <v>2199.689697265625</v>
+        <v>2199.689453125</v>
       </c>
       <c r="E122" t="n">
         <v>1909.849975585938</v>
       </c>
       <c r="F122" t="n">
-        <v>660.0244750976562</v>
+        <v>660.0244140625</v>
       </c>
       <c r="G122" t="n">
         <v>54.04999923706055</v>
@@ -4370,13 +4370,13 @@
         <v>1901.699951171875</v>
       </c>
       <c r="F123" t="n">
-        <v>659.7811279296875</v>
+        <v>659.781005859375</v>
       </c>
       <c r="G123" t="n">
         <v>54.0099983215332</v>
       </c>
       <c r="H123" t="n">
-        <v>359.1893920898438</v>
+        <v>359.1893310546875</v>
       </c>
       <c r="I123" t="n">
         <v>2344.2646484375</v>
@@ -4402,13 +4402,13 @@
         <v>1929.599975585938</v>
       </c>
       <c r="F124" t="n">
-        <v>654.1838989257812</v>
+        <v>654.1840209960938</v>
       </c>
       <c r="G124" t="n">
         <v>52.56999969482422</v>
       </c>
       <c r="H124" t="n">
-        <v>356.7325134277344</v>
+        <v>356.7325439453125</v>
       </c>
       <c r="I124" t="n">
         <v>2389.3984375</v>
@@ -4434,13 +4434,13 @@
         <v>1963.650024414062</v>
       </c>
       <c r="F125" t="n">
-        <v>659.87841796875</v>
+        <v>659.8784790039062</v>
       </c>
       <c r="G125" t="n">
         <v>52.65000152587891</v>
       </c>
       <c r="H125" t="n">
-        <v>361.2039184570312</v>
+        <v>361.2039489746094</v>
       </c>
       <c r="I125" t="n">
         <v>2385.50439453125</v>
@@ -4466,7 +4466,7 @@
         <v>1883.599975585938</v>
       </c>
       <c r="F126" t="n">
-        <v>663.8693237304688</v>
+        <v>663.869384765625</v>
       </c>
       <c r="G126" t="n">
         <v>52.34000015258789</v>
@@ -4504,7 +4504,7 @@
         <v>52.54999923706055</v>
       </c>
       <c r="H127" t="n">
-        <v>360.3194885253906</v>
+        <v>360.3195190429688</v>
       </c>
       <c r="I127" t="n">
         <v>2406.9228515625</v>
@@ -4518,7 +4518,7 @@
         <v>44748</v>
       </c>
       <c r="B128" t="n">
-        <v>2136.11328125</v>
+        <v>2136.113525390625</v>
       </c>
       <c r="C128" t="n">
         <v>2511.64990234375</v>
@@ -4530,7 +4530,7 @@
         <v>1903.699951171875</v>
       </c>
       <c r="F128" t="n">
-        <v>675.89111328125</v>
+        <v>675.8910522460938</v>
       </c>
       <c r="G128" t="n">
         <v>52.54000091552734</v>
@@ -4562,16 +4562,16 @@
         <v>1909.699951171875</v>
       </c>
       <c r="F129" t="n">
-        <v>684.8950805664062</v>
+        <v>684.8952026367188</v>
       </c>
       <c r="G129" t="n">
         <v>55.11999893188477</v>
       </c>
       <c r="H129" t="n">
-        <v>360.6143493652344</v>
+        <v>360.6143188476562</v>
       </c>
       <c r="I129" t="n">
-        <v>2482.11328125</v>
+        <v>2482.113037109375</v>
       </c>
       <c r="J129" t="n">
         <v>167.4499969482422</v>
@@ -4582,7 +4582,7 @@
         <v>44750</v>
       </c>
       <c r="B130" t="n">
-        <v>2131.201416015625</v>
+        <v>2131.201171875</v>
       </c>
       <c r="C130" t="n">
         <v>2545.89990234375</v>
@@ -4600,10 +4600,10 @@
         <v>54.31000137329102</v>
       </c>
       <c r="H130" t="n">
-        <v>362.0884399414062</v>
+        <v>362.0884094238281</v>
       </c>
       <c r="I130" t="n">
-        <v>2537.082275390625</v>
+        <v>2537.08251953125</v>
       </c>
       <c r="J130" t="n">
         <v>190.5</v>
@@ -4626,16 +4626,16 @@
         <v>2207.35009765625</v>
       </c>
       <c r="F131" t="n">
-        <v>709.814697265625</v>
+        <v>709.8146362304688</v>
       </c>
       <c r="G131" t="n">
         <v>57.02000045776367</v>
       </c>
       <c r="H131" t="n">
-        <v>362.8255004882812</v>
+        <v>362.8255310058594</v>
       </c>
       <c r="I131" t="n">
-        <v>2712.675048828125</v>
+        <v>2712.6748046875</v>
       </c>
       <c r="J131" t="n">
         <v>191.0500030517578</v>
@@ -4664,10 +4664,10 @@
         <v>58.54999923706055</v>
       </c>
       <c r="H132" t="n">
-        <v>364.49609375</v>
+        <v>364.4961242675781</v>
       </c>
       <c r="I132" t="n">
-        <v>2793.456787109375</v>
+        <v>2793.45654296875</v>
       </c>
       <c r="J132" t="n">
         <v>196.8500061035156</v>
@@ -4678,25 +4678,25 @@
         <v>44755</v>
       </c>
       <c r="B133" t="n">
-        <v>2135.3271484375</v>
+        <v>2135.327392578125</v>
       </c>
       <c r="C133" t="n">
         <v>2730.800048828125</v>
       </c>
       <c r="D133" t="n">
-        <v>2348.2578125</v>
+        <v>2348.257568359375</v>
       </c>
       <c r="E133" t="n">
         <v>2104.75</v>
       </c>
       <c r="F133" t="n">
-        <v>707.4297485351562</v>
+        <v>707.4298095703125</v>
       </c>
       <c r="G133" t="n">
         <v>57.33000183105469</v>
       </c>
       <c r="H133" t="n">
-        <v>364.7909240722656</v>
+        <v>364.7909851074219</v>
       </c>
       <c r="I133" t="n">
         <v>2668.190185546875</v>
@@ -4731,7 +4731,7 @@
         <v>363.5133972167969</v>
       </c>
       <c r="I134" t="n">
-        <v>2761.062744140625</v>
+        <v>2761.063232421875</v>
       </c>
       <c r="J134" t="n">
         <v>193.8500061035156</v>
@@ -4754,16 +4754,16 @@
         <v>2072.64990234375</v>
       </c>
       <c r="F135" t="n">
-        <v>716.3982543945312</v>
+        <v>716.398193359375</v>
       </c>
       <c r="G135" t="n">
         <v>57.34999847412109</v>
       </c>
       <c r="H135" t="n">
-        <v>362.7763671875</v>
+        <v>362.7763366699219</v>
       </c>
       <c r="I135" t="n">
-        <v>2803.854248046875</v>
+        <v>2803.85400390625</v>
       </c>
       <c r="J135" t="n">
         <v>187.6999969482422</v>
@@ -4786,13 +4786,13 @@
         <v>2093.25</v>
       </c>
       <c r="F136" t="n">
-        <v>725.0725708007812</v>
+        <v>725.0726928710938</v>
       </c>
       <c r="G136" t="n">
         <v>57.97000122070312</v>
       </c>
       <c r="H136" t="n">
-        <v>364.2995910644531</v>
+        <v>364.2996215820312</v>
       </c>
       <c r="I136" t="n">
         <v>2828.919921875</v>
@@ -4812,7 +4812,7 @@
         <v>3029.75</v>
       </c>
       <c r="D137" t="n">
-        <v>2446.848388671875</v>
+        <v>2446.84814453125</v>
       </c>
       <c r="E137" t="n">
         <v>2109</v>
@@ -4850,7 +4850,7 @@
         <v>2084.300048828125</v>
       </c>
       <c r="F138" t="n">
-        <v>728.7971801757812</v>
+        <v>728.7972412109375</v>
       </c>
       <c r="G138" t="n">
         <v>57.97999954223633</v>
@@ -4859,7 +4859,7 @@
         <v>361.498779296875</v>
       </c>
       <c r="I138" t="n">
-        <v>2776.142333984375</v>
+        <v>2776.14208984375</v>
       </c>
       <c r="J138" t="n">
         <v>242.5</v>
@@ -4882,16 +4882,16 @@
         <v>2109.75</v>
       </c>
       <c r="F139" t="n">
-        <v>739.2849731445312</v>
+        <v>739.284912109375</v>
       </c>
       <c r="G139" t="n">
         <v>58.79999923706055</v>
       </c>
       <c r="H139" t="n">
-        <v>364.3486938476562</v>
+        <v>364.3487243652344</v>
       </c>
       <c r="I139" t="n">
-        <v>2872.659912109375</v>
+        <v>2872.66015625</v>
       </c>
       <c r="J139" t="n">
         <v>230.4499969482422</v>
@@ -4908,22 +4908,22 @@
         <v>2977.449951171875</v>
       </c>
       <c r="D140" t="n">
-        <v>2494.860595703125</v>
+        <v>2494.8603515625</v>
       </c>
       <c r="E140" t="n">
         <v>2120.449951171875</v>
       </c>
       <c r="F140" t="n">
-        <v>739.2849731445312</v>
+        <v>739.284912109375</v>
       </c>
       <c r="G140" t="n">
         <v>58.2599983215332</v>
       </c>
       <c r="H140" t="n">
-        <v>366.1176147460938</v>
+        <v>366.1176452636719</v>
       </c>
       <c r="I140" t="n">
-        <v>2870.26318359375</v>
+        <v>2870.262939453125</v>
       </c>
       <c r="J140" t="n">
         <v>276.5</v>
@@ -4934,7 +4934,7 @@
         <v>44767</v>
       </c>
       <c r="B141" t="n">
-        <v>2165.68408203125</v>
+        <v>2165.683837890625</v>
       </c>
       <c r="C141" t="n">
         <v>2969.75</v>
@@ -4952,7 +4952,7 @@
         <v>58.34000015258789</v>
       </c>
       <c r="H141" t="n">
-        <v>364.7417602539062</v>
+        <v>364.7417907714844</v>
       </c>
       <c r="I141" t="n">
         <v>2874.90673828125</v>
@@ -4978,7 +4978,7 @@
         <v>2103.64990234375</v>
       </c>
       <c r="F142" t="n">
-        <v>734.2371215820312</v>
+        <v>734.237060546875</v>
       </c>
       <c r="G142" t="n">
         <v>59.54000091552734</v>
@@ -5004,13 +5004,13 @@
         <v>2996.10009765625</v>
       </c>
       <c r="D143" t="n">
-        <v>2544.0712890625</v>
+        <v>2544.071044921875</v>
       </c>
       <c r="E143" t="n">
         <v>2099.199951171875</v>
       </c>
       <c r="F143" t="n">
-        <v>745.5579223632812</v>
+        <v>745.5579833984375</v>
       </c>
       <c r="G143" t="n">
         <v>62.4900016784668</v>
@@ -5019,7 +5019,7 @@
         <v>364.4469909667969</v>
       </c>
       <c r="I143" t="n">
-        <v>2956.04541015625</v>
+        <v>2956.045654296875</v>
       </c>
       <c r="J143" t="n">
         <v>252.5</v>
@@ -5051,7 +5051,7 @@
         <v>364.4469909667969</v>
       </c>
       <c r="I144" t="n">
-        <v>3001.782470703125</v>
+        <v>3001.78271484375</v>
       </c>
       <c r="J144" t="n">
         <v>256.6000061035156</v>
@@ -5080,10 +5080,10 @@
         <v>62.79000091552734</v>
       </c>
       <c r="H145" t="n">
-        <v>368.3287353515625</v>
+        <v>368.3287658691406</v>
       </c>
       <c r="I145" t="n">
-        <v>3122.91650390625</v>
+        <v>3122.916259765625</v>
       </c>
       <c r="J145" t="n">
         <v>256.6000061035156</v>
@@ -5100,22 +5100,22 @@
         <v>3261.75</v>
       </c>
       <c r="D146" t="n">
-        <v>2655.31884765625</v>
+        <v>2655.318603515625</v>
       </c>
       <c r="E146" t="n">
         <v>2273.699951171875</v>
       </c>
       <c r="F146" t="n">
-        <v>785.3524169921875</v>
+        <v>785.3523559570312</v>
       </c>
       <c r="G146" t="n">
         <v>64.37000274658203</v>
       </c>
       <c r="H146" t="n">
-        <v>368.9184265136719</v>
+        <v>368.9183959960938</v>
       </c>
       <c r="I146" t="n">
-        <v>3213.242431640625</v>
+        <v>3213.24267578125</v>
       </c>
       <c r="J146" t="n">
         <v>265.4500122070312</v>
@@ -5126,13 +5126,13 @@
         <v>44775</v>
       </c>
       <c r="B147" t="n">
-        <v>2188.47607421875</v>
+        <v>2188.475830078125</v>
       </c>
       <c r="C147" t="n">
         <v>3421.449951171875</v>
       </c>
       <c r="D147" t="n">
-        <v>2678.776123046875</v>
+        <v>2678.77587890625</v>
       </c>
       <c r="E147" t="n">
         <v>2296.14990234375</v>
@@ -5144,7 +5144,7 @@
         <v>65.70999908447266</v>
       </c>
       <c r="H147" t="n">
-        <v>372.1123352050781</v>
+        <v>372.1122741699219</v>
       </c>
       <c r="I147" t="n">
         <v>3244.39990234375</v>
@@ -5196,13 +5196,13 @@
         <v>3530.449951171875</v>
       </c>
       <c r="D149" t="n">
-        <v>2718.65380859375</v>
+        <v>2718.653564453125</v>
       </c>
       <c r="E149" t="n">
         <v>2190.949951171875</v>
       </c>
       <c r="F149" t="n">
-        <v>791.2333374023438</v>
+        <v>791.2332763671875</v>
       </c>
       <c r="G149" t="n">
         <v>69.44999694824219</v>
@@ -5211,7 +5211,7 @@
         <v>374.6674194335938</v>
       </c>
       <c r="I149" t="n">
-        <v>3345.0615234375</v>
+        <v>3345.061767578125</v>
       </c>
       <c r="J149" t="n">
         <v>296.6000061035156</v>
@@ -5222,13 +5222,13 @@
         <v>44778</v>
       </c>
       <c r="B150" t="n">
-        <v>2215.14892578125</v>
+        <v>2215.148681640625</v>
       </c>
       <c r="C150" t="n">
         <v>3313.550048828125</v>
       </c>
       <c r="D150" t="n">
-        <v>2693.499267578125</v>
+        <v>2693.4990234375</v>
       </c>
       <c r="E150" t="n">
         <v>2106.199951171875</v>
@@ -5240,7 +5240,7 @@
         <v>66.41000366210938</v>
       </c>
       <c r="H150" t="n">
-        <v>376.043212890625</v>
+        <v>376.0432434082031</v>
       </c>
       <c r="I150" t="n">
         <v>3342.81494140625</v>
@@ -5266,13 +5266,13 @@
         <v>2165.199951171875</v>
       </c>
       <c r="F151" t="n">
-        <v>785.744384765625</v>
+        <v>785.7445068359375</v>
       </c>
       <c r="G151" t="n">
         <v>65.72000122070312</v>
       </c>
       <c r="H151" t="n">
-        <v>373.6355590820312</v>
+        <v>373.6355285644531</v>
       </c>
       <c r="I151" t="n">
         <v>3360.390869140625</v>
@@ -5292,13 +5292,13 @@
         <v>3436.14990234375</v>
       </c>
       <c r="D152" t="n">
-        <v>2822.065185546875</v>
+        <v>2822.0654296875</v>
       </c>
       <c r="E152" t="n">
         <v>2164.949951171875</v>
       </c>
       <c r="F152" t="n">
-        <v>774.8646240234375</v>
+        <v>774.86474609375</v>
       </c>
       <c r="G152" t="n">
         <v>67.94999694824219</v>
@@ -5307,7 +5307,7 @@
         <v>373.4881286621094</v>
       </c>
       <c r="I152" t="n">
-        <v>3346.809326171875</v>
+        <v>3346.8095703125</v>
       </c>
       <c r="J152" t="n">
         <v>294.5</v>
@@ -5318,25 +5318,25 @@
         <v>44784</v>
       </c>
       <c r="B153" t="n">
-        <v>2189.703857421875</v>
+        <v>2189.7041015625</v>
       </c>
       <c r="C153" t="n">
         <v>3493.949951171875</v>
       </c>
       <c r="D153" t="n">
-        <v>2828.903076171875</v>
+        <v>2828.90283203125</v>
       </c>
       <c r="E153" t="n">
         <v>2164.89990234375</v>
       </c>
       <c r="F153" t="n">
-        <v>777.02099609375</v>
+        <v>777.0210571289062</v>
       </c>
       <c r="G153" t="n">
         <v>68.48000335693359</v>
       </c>
       <c r="H153" t="n">
-        <v>373.6355590820312</v>
+        <v>373.6355285644531</v>
       </c>
       <c r="I153" t="n">
         <v>3347.708251953125</v>
@@ -5368,7 +5368,7 @@
         <v>69.02999877929688</v>
       </c>
       <c r="H154" t="n">
-        <v>378.1561279296875</v>
+        <v>378.1560974121094</v>
       </c>
       <c r="I154" t="n">
         <v>3420.7080078125</v>
@@ -5394,13 +5394,13 @@
         <v>2218.199951171875</v>
       </c>
       <c r="F155" t="n">
-        <v>807.798095703125</v>
+        <v>807.7979736328125</v>
       </c>
       <c r="G155" t="n">
         <v>72.47000122070312</v>
       </c>
       <c r="H155" t="n">
-        <v>389.2610168457031</v>
+        <v>389.2610473632812</v>
       </c>
       <c r="I155" t="n">
         <v>3484.919921875</v>
@@ -5426,7 +5426,7 @@
         <v>2227.050048828125</v>
       </c>
       <c r="F156" t="n">
-        <v>808.3861694335938</v>
+        <v>808.3861083984375</v>
       </c>
       <c r="G156" t="n">
         <v>76.08999633789062</v>
@@ -5446,7 +5446,7 @@
         <v>44791</v>
       </c>
       <c r="B157" t="n">
-        <v>2282.001953125</v>
+        <v>2282.002197265625</v>
       </c>
       <c r="C157" t="n">
         <v>3599.550048828125</v>
@@ -5467,7 +5467,7 @@
         <v>402.5279541015625</v>
       </c>
       <c r="I157" t="n">
-        <v>3458.55615234375</v>
+        <v>3458.556396484375</v>
       </c>
       <c r="J157" t="n">
         <v>333.0499877929688</v>
@@ -5510,13 +5510,13 @@
         <v>44795</v>
       </c>
       <c r="B159" t="n">
-        <v>2242.80322265625</v>
+        <v>2242.803466796875</v>
       </c>
       <c r="C159" t="n">
         <v>3486.39990234375</v>
       </c>
       <c r="D159" t="n">
-        <v>3046.05810546875</v>
+        <v>3046.057861328125</v>
       </c>
       <c r="E159" t="n">
         <v>2519.75</v>
@@ -5563,7 +5563,7 @@
         <v>398.4495849609375</v>
       </c>
       <c r="I160" t="n">
-        <v>3426.25048828125</v>
+        <v>3426.250732421875</v>
       </c>
       <c r="J160" t="n">
         <v>369.75</v>
@@ -5574,7 +5574,7 @@
         <v>44797</v>
       </c>
       <c r="B161" t="n">
-        <v>2261.1748046875</v>
+        <v>2261.174560546875</v>
       </c>
       <c r="C161" t="n">
         <v>3700.39990234375</v>
@@ -5586,7 +5586,7 @@
         <v>2358.85009765625</v>
       </c>
       <c r="F161" t="n">
-        <v>819.7069702148438</v>
+        <v>819.7069091796875</v>
       </c>
       <c r="G161" t="n">
         <v>78.08000183105469</v>
@@ -5627,7 +5627,7 @@
         <v>390.2928771972656</v>
       </c>
       <c r="I162" t="n">
-        <v>3360.5908203125</v>
+        <v>3360.590576171875</v>
       </c>
       <c r="J162" t="n">
         <v>407.6000061035156</v>
@@ -5650,13 +5650,13 @@
         <v>2392.75</v>
       </c>
       <c r="F163" t="n">
-        <v>821.0791625976562</v>
+        <v>821.0792236328125</v>
       </c>
       <c r="G163" t="n">
         <v>75.09999847412109</v>
       </c>
       <c r="H163" t="n">
-        <v>395.8945007324219</v>
+        <v>395.8944702148438</v>
       </c>
       <c r="I163" t="n">
         <v>3454.9111328125</v>
@@ -5676,22 +5676,22 @@
         <v>3855.550048828125</v>
       </c>
       <c r="D164" t="n">
-        <v>3136.892333984375</v>
+        <v>3136.892578125</v>
       </c>
       <c r="E164" t="n">
         <v>2337.85009765625</v>
       </c>
       <c r="F164" t="n">
-        <v>819.8049926757812</v>
+        <v>819.804931640625</v>
       </c>
       <c r="G164" t="n">
         <v>78.84999847412109</v>
       </c>
       <c r="H164" t="n">
-        <v>396.4841613769531</v>
+        <v>396.4841003417969</v>
       </c>
       <c r="I164" t="n">
-        <v>3532.5546875</v>
+        <v>3532.554931640625</v>
       </c>
       <c r="J164" t="n">
         <v>449.0499877929688</v>
@@ -5702,13 +5702,13 @@
         <v>44803</v>
       </c>
       <c r="B165" t="n">
-        <v>2259.259033203125</v>
+        <v>2259.25927734375</v>
       </c>
       <c r="C165" t="n">
         <v>3960.699951171875</v>
       </c>
       <c r="D165" t="n">
-        <v>3188.548828125</v>
+        <v>3188.548583984375</v>
       </c>
       <c r="E165" t="n">
         <v>2436.199951171875</v>
@@ -5723,7 +5723,7 @@
         <v>404.1494140625</v>
       </c>
       <c r="I165" t="n">
-        <v>3739.820556640625</v>
+        <v>3739.8203125</v>
       </c>
       <c r="J165" t="n">
         <v>471.5</v>
@@ -5734,13 +5734,13 @@
         <v>44805</v>
       </c>
       <c r="B166" t="n">
-        <v>2255.968017578125</v>
+        <v>2255.9677734375</v>
       </c>
       <c r="C166" t="n">
         <v>3880.449951171875</v>
       </c>
       <c r="D166" t="n">
-        <v>3227.377685546875</v>
+        <v>3227.3779296875</v>
       </c>
       <c r="E166" t="n">
         <v>2393.10009765625</v>
@@ -5752,10 +5752,10 @@
         <v>81.69999694824219</v>
       </c>
       <c r="H166" t="n">
-        <v>402.7244567871094</v>
+        <v>402.7244873046875</v>
       </c>
       <c r="I166" t="n">
-        <v>3634.265380859375</v>
+        <v>3634.26513671875</v>
       </c>
       <c r="J166" t="n">
         <v>495.0499877929688</v>
@@ -5784,7 +5784,7 @@
         <v>80.25</v>
       </c>
       <c r="H167" t="n">
-        <v>408.4243469238281</v>
+        <v>408.4243774414062</v>
       </c>
       <c r="I167" t="n">
         <v>3617.887939453125</v>
@@ -5816,10 +5816,10 @@
         <v>77.97000122070312</v>
       </c>
       <c r="H168" t="n">
-        <v>410.7337951660156</v>
+        <v>410.7337646484375</v>
       </c>
       <c r="I168" t="n">
-        <v>3525.76416015625</v>
+        <v>3525.763916015625</v>
       </c>
       <c r="J168" t="n">
         <v>545.75</v>
@@ -5842,13 +5842,13 @@
         <v>2374.89990234375</v>
       </c>
       <c r="F169" t="n">
-        <v>833.4782104492188</v>
+        <v>833.4781494140625</v>
       </c>
       <c r="G169" t="n">
         <v>81.55000305175781</v>
       </c>
       <c r="H169" t="n">
-        <v>428.9634704589844</v>
+        <v>428.9635009765625</v>
       </c>
       <c r="I169" t="n">
         <v>3677.8056640625</v>
@@ -5862,7 +5862,7 @@
         <v>44811</v>
       </c>
       <c r="B170" t="n">
-        <v>2363.051025390625</v>
+        <v>2363.05126953125</v>
       </c>
       <c r="C170" t="n">
         <v>3893.10009765625</v>
@@ -5874,13 +5874,13 @@
         <v>2346.949951171875</v>
       </c>
       <c r="F170" t="n">
-        <v>857.5410766601562</v>
+        <v>857.5411376953125</v>
       </c>
       <c r="G170" t="n">
         <v>81.26000213623047</v>
       </c>
       <c r="H170" t="n">
-        <v>441.1493835449219</v>
+        <v>441.1494140625</v>
       </c>
       <c r="I170" t="n">
         <v>3656.235107421875</v>
@@ -5894,7 +5894,7 @@
         <v>44812</v>
       </c>
       <c r="B171" t="n">
-        <v>2378.5732421875</v>
+        <v>2378.572998046875</v>
       </c>
       <c r="C171" t="n">
         <v>3925.949951171875</v>
@@ -5906,7 +5906,7 @@
         <v>2334.050048828125</v>
       </c>
       <c r="F171" t="n">
-        <v>867.48974609375</v>
+        <v>867.4896850585938</v>
       </c>
       <c r="G171" t="n">
         <v>80.37999725341797</v>
@@ -5915,7 +5915,7 @@
         <v>453.9249267578125</v>
       </c>
       <c r="I171" t="n">
-        <v>3624.927734375</v>
+        <v>3624.927978515625</v>
       </c>
       <c r="J171" t="n">
         <v>468</v>
@@ -5938,7 +5938,7 @@
         <v>2315.89990234375</v>
       </c>
       <c r="F172" t="n">
-        <v>888.857177734375</v>
+        <v>888.8571166992188</v>
       </c>
       <c r="G172" t="n">
         <v>79.40000152587891</v>
@@ -5964,7 +5964,7 @@
         <v>4006</v>
       </c>
       <c r="D173" t="n">
-        <v>3457.509033203125</v>
+        <v>3457.50927734375</v>
       </c>
       <c r="E173" t="n">
         <v>2355.949951171875</v>
@@ -5976,7 +5976,7 @@
         <v>79.51999664306641</v>
       </c>
       <c r="H173" t="n">
-        <v>467.4375</v>
+        <v>467.4375305175781</v>
       </c>
       <c r="I173" t="n">
         <v>3630.420654296875</v>
@@ -5996,19 +5996,19 @@
         <v>4037.050048828125</v>
       </c>
       <c r="D174" t="n">
-        <v>3549.34228515625</v>
+        <v>3549.342041015625</v>
       </c>
       <c r="E174" t="n">
         <v>2335.64990234375</v>
       </c>
       <c r="F174" t="n">
-        <v>929.9747924804688</v>
+        <v>929.974853515625</v>
       </c>
       <c r="G174" t="n">
         <v>78.72000122070312</v>
       </c>
       <c r="H174" t="n">
-        <v>478.1002197265625</v>
+        <v>478.1001892089844</v>
       </c>
       <c r="I174" t="n">
         <v>3599.812255859375</v>
@@ -6022,7 +6022,7 @@
         <v>44818</v>
       </c>
       <c r="B175" t="n">
-        <v>2694.9599609375</v>
+        <v>2694.959716796875</v>
       </c>
       <c r="C175" t="n">
         <v>3978.14990234375</v>
@@ -6040,10 +6040,10 @@
         <v>76.91000366210938</v>
       </c>
       <c r="H175" t="n">
-        <v>515.5423583984375</v>
+        <v>515.5422973632812</v>
       </c>
       <c r="I175" t="n">
-        <v>3559.517822265625</v>
+        <v>3559.517578125</v>
       </c>
       <c r="J175" t="n">
         <v>465.6499938964844</v>
@@ -6054,13 +6054,13 @@
         <v>44819</v>
       </c>
       <c r="B176" t="n">
-        <v>2699.380615234375</v>
+        <v>2699.380859375</v>
       </c>
       <c r="C176" t="n">
         <v>4105.39990234375</v>
       </c>
       <c r="D176" t="n">
-        <v>3741.891845703125</v>
+        <v>3741.8916015625</v>
       </c>
       <c r="E176" t="n">
         <v>2343.89990234375</v>
@@ -6098,7 +6098,7 @@
         <v>2316.60009765625</v>
       </c>
       <c r="F177" t="n">
-        <v>919.585205078125</v>
+        <v>919.5850830078125</v>
       </c>
       <c r="G177" t="n">
         <v>77.55000305175781</v>
@@ -6118,13 +6118,13 @@
         <v>44823</v>
       </c>
       <c r="B178" t="n">
-        <v>2594.655517578125</v>
+        <v>2594.65576171875</v>
       </c>
       <c r="C178" t="n">
         <v>4029.39990234375</v>
       </c>
       <c r="D178" t="n">
-        <v>3771.787109375</v>
+        <v>3771.787353515625</v>
       </c>
       <c r="E178" t="n">
         <v>2346.35009765625</v>
@@ -6139,7 +6139,7 @@
         <v>555.1465454101562</v>
       </c>
       <c r="I178" t="n">
-        <v>3615.091796875</v>
+        <v>3615.091552734375</v>
       </c>
       <c r="J178" t="n">
         <v>442.25</v>
@@ -6162,16 +6162,16 @@
         <v>2399.949951171875</v>
       </c>
       <c r="F179" t="n">
-        <v>950.9992065429688</v>
+        <v>950.999267578125</v>
       </c>
       <c r="G179" t="n">
         <v>79.65000152587891</v>
       </c>
       <c r="H179" t="n">
-        <v>564.4332885742188</v>
+        <v>564.433349609375</v>
       </c>
       <c r="I179" t="n">
-        <v>3669.916015625</v>
+        <v>3669.91650390625</v>
       </c>
       <c r="J179" t="n">
         <v>438.5</v>
@@ -6194,16 +6194,16 @@
         <v>2362.800048828125</v>
       </c>
       <c r="F180" t="n">
-        <v>914.390380859375</v>
+        <v>914.3903198242188</v>
       </c>
       <c r="G180" t="n">
         <v>78.09999847412109</v>
       </c>
       <c r="H180" t="n">
-        <v>532.0031127929688</v>
+        <v>532.0030517578125</v>
       </c>
       <c r="I180" t="n">
-        <v>3560.616455078125</v>
+        <v>3560.6162109375</v>
       </c>
       <c r="J180" t="n">
         <v>421.2000122070312</v>
@@ -6235,7 +6235,7 @@
         <v>524.8291625976562</v>
       </c>
       <c r="I181" t="n">
-        <v>3624.927734375</v>
+        <v>3624.927978515625</v>
       </c>
       <c r="J181" t="n">
         <v>408.4500122070312</v>
@@ -6258,7 +6258,7 @@
         <v>2323.85009765625</v>
       </c>
       <c r="F182" t="n">
-        <v>895.6692504882812</v>
+        <v>895.6693115234375</v>
       </c>
       <c r="G182" t="n">
         <v>77.12000274658203</v>
@@ -6267,7 +6267,7 @@
         <v>530.0376586914062</v>
       </c>
       <c r="I182" t="n">
-        <v>3540.394287109375</v>
+        <v>3540.393798828125</v>
       </c>
       <c r="J182" t="n">
         <v>388.0499877929688</v>
@@ -6316,7 +6316,7 @@
         <v>3606.5</v>
       </c>
       <c r="D184" t="n">
-        <v>3552.63623046875</v>
+        <v>3552.635986328125</v>
       </c>
       <c r="E184" t="n">
         <v>2146.300048828125</v>
@@ -6342,7 +6342,7 @@
         <v>44832</v>
       </c>
       <c r="B185" t="n">
-        <v>2308.96923828125</v>
+        <v>2308.969482421875</v>
       </c>
       <c r="C185" t="n">
         <v>3602.10009765625</v>
@@ -6363,7 +6363,7 @@
         <v>491.4162292480469</v>
       </c>
       <c r="I185" t="n">
-        <v>3443.327392578125</v>
+        <v>3443.3271484375</v>
       </c>
       <c r="J185" t="n">
         <v>367.75</v>
@@ -6386,16 +6386,16 @@
         <v>2004.050048828125</v>
       </c>
       <c r="F186" t="n">
-        <v>800.2017822265625</v>
+        <v>800.2017211914062</v>
       </c>
       <c r="G186" t="n">
         <v>73.88999938964844</v>
       </c>
       <c r="H186" t="n">
-        <v>497.6074523925781</v>
+        <v>497.6074829101562</v>
       </c>
       <c r="I186" t="n">
-        <v>3367.631103515625</v>
+        <v>3367.630859375</v>
       </c>
       <c r="J186" t="n">
         <v>386.1000061035156</v>
@@ -6412,7 +6412,7 @@
         <v>3289.800048828125</v>
       </c>
       <c r="D187" t="n">
-        <v>3449.473876953125</v>
+        <v>3449.4736328125</v>
       </c>
       <c r="E187" t="n">
         <v>2260.800048828125</v>
@@ -6424,10 +6424,10 @@
         <v>74.69999694824219</v>
       </c>
       <c r="H187" t="n">
-        <v>506.6977233886719</v>
+        <v>506.69775390625</v>
       </c>
       <c r="I187" t="n">
-        <v>3335.275390625</v>
+        <v>3335.275146484375</v>
       </c>
       <c r="J187" t="n">
         <v>373.0499877929688</v>
@@ -6444,19 +6444,19 @@
         <v>3123.64990234375</v>
       </c>
       <c r="D188" t="n">
-        <v>3151.56591796875</v>
+        <v>3151.566162109375</v>
       </c>
       <c r="E188" t="n">
         <v>2074.050048828125</v>
       </c>
       <c r="F188" t="n">
-        <v>768.8367309570312</v>
+        <v>768.836669921875</v>
       </c>
       <c r="G188" t="n">
         <v>70.97000122070312</v>
       </c>
       <c r="H188" t="n">
-        <v>480.2130432128906</v>
+        <v>480.2130737304688</v>
       </c>
       <c r="I188" t="n">
         <v>3096.552978515625</v>
@@ -6470,7 +6470,7 @@
         <v>44838</v>
       </c>
       <c r="B189" t="n">
-        <v>2318.15478515625</v>
+        <v>2318.154541015625</v>
       </c>
       <c r="C189" t="n">
         <v>3318.60009765625</v>
@@ -6514,7 +6514,7 @@
         <v>2201.699951171875</v>
       </c>
       <c r="F190" t="n">
-        <v>807.7490234375</v>
+        <v>807.7489624023438</v>
       </c>
       <c r="G190" t="n">
         <v>74.01999664306641</v>
@@ -6523,7 +6523,7 @@
         <v>498.1479797363281</v>
       </c>
       <c r="I190" t="n">
-        <v>3303.468994140625</v>
+        <v>3303.46923828125</v>
       </c>
       <c r="J190" t="n">
         <v>352.75</v>
@@ -6534,13 +6534,13 @@
         <v>44841</v>
       </c>
       <c r="B191" t="n">
-        <v>2342.8134765625</v>
+        <v>2342.813232421875</v>
       </c>
       <c r="C191" t="n">
         <v>3278.60009765625</v>
       </c>
       <c r="D191" t="n">
-        <v>3271.6474609375</v>
+        <v>3271.647216796875</v>
       </c>
       <c r="E191" t="n">
         <v>2204.14990234375</v>
@@ -6552,7 +6552,7 @@
         <v>74.56999969482422</v>
       </c>
       <c r="H191" t="n">
-        <v>512.7907104492188</v>
+        <v>512.7906494140625</v>
       </c>
       <c r="I191" t="n">
         <v>3183.234130859375</v>
@@ -6578,7 +6578,7 @@
         <v>2155.89990234375</v>
       </c>
       <c r="F192" t="n">
-        <v>792.0664672851562</v>
+        <v>792.06640625</v>
       </c>
       <c r="G192" t="n">
         <v>73.06999969482422</v>
@@ -6616,7 +6616,7 @@
         <v>71.37000274658203</v>
       </c>
       <c r="H193" t="n">
-        <v>491.5636596679688</v>
+        <v>491.5636901855469</v>
       </c>
       <c r="I193" t="n">
         <v>3169.253173828125</v>
@@ -6630,13 +6630,13 @@
         <v>44846</v>
       </c>
       <c r="B194" t="n">
-        <v>2276.05859375</v>
+        <v>2276.058349609375</v>
       </c>
       <c r="C194" t="n">
         <v>3187.949951171875</v>
       </c>
       <c r="D194" t="n">
-        <v>3217.795166015625</v>
+        <v>3217.794921875</v>
       </c>
       <c r="E194" t="n">
         <v>2099.10009765625</v>
@@ -6648,7 +6648,7 @@
         <v>71.36000061035156</v>
       </c>
       <c r="H194" t="n">
-        <v>496.7230224609375</v>
+        <v>496.7230529785156</v>
       </c>
       <c r="I194" t="n">
         <v>3198.463134765625</v>
@@ -6662,7 +6662,7 @@
         <v>44847</v>
       </c>
       <c r="B195" t="n">
-        <v>2214.26416015625</v>
+        <v>2214.264404296875</v>
       </c>
       <c r="C195" t="n">
         <v>3121.10009765625</v>
@@ -6683,7 +6683,7 @@
         <v>488.271484375</v>
       </c>
       <c r="I195" t="n">
-        <v>3172.998046875</v>
+        <v>3172.997802734375</v>
       </c>
       <c r="J195" t="n">
         <v>335.5499877929688</v>
@@ -6700,13 +6700,13 @@
         <v>3035.300048828125</v>
       </c>
       <c r="D196" t="n">
-        <v>3203.671142578125</v>
+        <v>3203.6708984375</v>
       </c>
       <c r="E196" t="n">
         <v>2033.150024414062</v>
       </c>
       <c r="F196" t="n">
-        <v>764.6220092773438</v>
+        <v>764.6220703125</v>
       </c>
       <c r="G196" t="n">
         <v>66.25</v>
@@ -6715,7 +6715,7 @@
         <v>493.1851806640625</v>
       </c>
       <c r="I196" t="n">
-        <v>3042.97607421875</v>
+        <v>3042.975830078125</v>
       </c>
       <c r="J196" t="n">
         <v>329.3500061035156</v>
@@ -6726,7 +6726,7 @@
         <v>44851</v>
       </c>
       <c r="B197" t="n">
-        <v>2230.179443359375</v>
+        <v>2230.1796875</v>
       </c>
       <c r="C197" t="n">
         <v>3074.35009765625</v>
@@ -6747,7 +6747,7 @@
         <v>511.562255859375</v>
       </c>
       <c r="I197" t="n">
-        <v>3095.0546875</v>
+        <v>3095.054931640625</v>
       </c>
       <c r="J197" t="n">
         <v>324.75</v>
@@ -6758,7 +6758,7 @@
         <v>44852</v>
       </c>
       <c r="B198" t="n">
-        <v>2180.2236328125</v>
+        <v>2180.223388671875</v>
       </c>
       <c r="C198" t="n">
         <v>3243</v>
@@ -6776,10 +6776,10 @@
         <v>69.12000274658203</v>
       </c>
       <c r="H198" t="n">
-        <v>499.0815734863281</v>
+        <v>499.08154296875</v>
       </c>
       <c r="I198" t="n">
-        <v>3148.53173828125</v>
+        <v>3148.531494140625</v>
       </c>
       <c r="J198" t="n">
         <v>326.2999877929688</v>
@@ -6802,7 +6802,7 @@
         <v>2119.800048828125</v>
       </c>
       <c r="F199" t="n">
-        <v>789.076904296875</v>
+        <v>789.0769653320312</v>
       </c>
       <c r="G199" t="n">
         <v>66.72000122070312</v>
@@ -6811,7 +6811,7 @@
         <v>501.8823852539062</v>
       </c>
       <c r="I199" t="n">
-        <v>3162.51220703125</v>
+        <v>3162.512451171875</v>
       </c>
       <c r="J199" t="n">
         <v>332.3999938964844</v>
@@ -6860,13 +6860,13 @@
         <v>3273.699951171875</v>
       </c>
       <c r="D201" t="n">
-        <v>3305.885009765625</v>
+        <v>3305.884765625</v>
       </c>
       <c r="E201" t="n">
         <v>2105.300048828125</v>
       </c>
       <c r="F201" t="n">
-        <v>785.744384765625</v>
+        <v>785.7445068359375</v>
       </c>
       <c r="G201" t="n">
         <v>66.44000244140625</v>
@@ -6886,19 +6886,19 @@
         <v>44858</v>
       </c>
       <c r="B202" t="n">
-        <v>2217.407958984375</v>
+        <v>2217.408203125</v>
       </c>
       <c r="C202" t="n">
         <v>3283.949951171875</v>
       </c>
       <c r="D202" t="n">
-        <v>3303.7890625</v>
+        <v>3303.789306640625</v>
       </c>
       <c r="E202" t="n">
         <v>2121.25</v>
       </c>
       <c r="F202" t="n">
-        <v>789.5181274414062</v>
+        <v>789.51806640625</v>
       </c>
       <c r="G202" t="n">
         <v>67.11000061035156</v>
@@ -6907,7 +6907,7 @@
         <v>507.9753112792969</v>
       </c>
       <c r="I202" t="n">
-        <v>3262.824951171875</v>
+        <v>3262.82470703125</v>
       </c>
       <c r="J202" t="n">
         <v>328.8999938964844</v>
@@ -6936,10 +6936,10 @@
         <v>66.47000122070312</v>
       </c>
       <c r="H203" t="n">
-        <v>504.2409057617188</v>
+        <v>504.2408752441406</v>
       </c>
       <c r="I203" t="n">
-        <v>3378.31640625</v>
+        <v>3378.316162109375</v>
       </c>
       <c r="J203" t="n">
         <v>323.8500061035156</v>
@@ -6968,7 +6968,7 @@
         <v>67.48000335693359</v>
       </c>
       <c r="H204" t="n">
-        <v>518.4906005859375</v>
+        <v>518.4905395507812</v>
       </c>
       <c r="I204" t="n">
         <v>3502.9453125</v>
@@ -6994,16 +6994,16 @@
         <v>2098.550048828125</v>
       </c>
       <c r="F205" t="n">
-        <v>804.0243530273438</v>
+        <v>804.0244140625</v>
       </c>
       <c r="G205" t="n">
         <v>66.66000366210938</v>
       </c>
       <c r="H205" t="n">
-        <v>511.1200866699219</v>
+        <v>511.1200561523438</v>
       </c>
       <c r="I205" t="n">
-        <v>3439.33251953125</v>
+        <v>3439.332763671875</v>
       </c>
       <c r="J205" t="n">
         <v>312.7000122070312</v>
@@ -7014,7 +7014,7 @@
         <v>44865</v>
       </c>
       <c r="B206" t="n">
-        <v>2348.26611328125</v>
+        <v>2348.265869140625</v>
       </c>
       <c r="C206" t="n">
         <v>3348.699951171875</v>
@@ -7026,7 +7026,7 @@
         <v>2102.89990234375</v>
       </c>
       <c r="F206" t="n">
-        <v>807.2099609375</v>
+        <v>807.2098999023438</v>
       </c>
       <c r="G206" t="n">
         <v>66.98000335693359</v>
@@ -7064,7 +7064,7 @@
         <v>69.77999877929688</v>
       </c>
       <c r="H207" t="n">
-        <v>534.6565551757812</v>
+        <v>534.656494140625</v>
       </c>
       <c r="I207" t="n">
         <v>3676.15771484375</v>
@@ -7090,13 +7090,13 @@
         <v>2137.050048828125</v>
       </c>
       <c r="F208" t="n">
-        <v>816.864501953125</v>
+        <v>816.8644409179688</v>
       </c>
       <c r="G208" t="n">
         <v>68.62999725341797</v>
       </c>
       <c r="H208" t="n">
-        <v>535.5901489257812</v>
+        <v>535.590087890625</v>
       </c>
       <c r="I208" t="n">
         <v>3632.318115234375</v>
@@ -7110,19 +7110,19 @@
         <v>44868</v>
       </c>
       <c r="B209" t="n">
-        <v>2412.172119140625</v>
+        <v>2412.171875</v>
       </c>
       <c r="C209" t="n">
         <v>3292.14990234375</v>
       </c>
       <c r="D209" t="n">
-        <v>3583.87890625</v>
+        <v>3583.879150390625</v>
       </c>
       <c r="E209" t="n">
         <v>2106.699951171875</v>
       </c>
       <c r="F209" t="n">
-        <v>817.3056030273438</v>
+        <v>817.3055419921875</v>
       </c>
       <c r="G209" t="n">
         <v>67.34999847412109</v>
@@ -7131,7 +7131,7 @@
         <v>530.1851196289062</v>
       </c>
       <c r="I209" t="n">
-        <v>3655.88525390625</v>
+        <v>3655.885498046875</v>
       </c>
       <c r="J209" t="n">
         <v>318.6000061035156</v>
@@ -7163,7 +7163,7 @@
         <v>548.955322265625</v>
       </c>
       <c r="I210" t="n">
-        <v>3754.100830078125</v>
+        <v>3754.10107421875</v>
       </c>
       <c r="J210" t="n">
         <v>334.5</v>
@@ -7174,7 +7174,7 @@
         <v>44872</v>
       </c>
       <c r="B211" t="n">
-        <v>2441.2509765625</v>
+        <v>2441.251220703125</v>
       </c>
       <c r="C211" t="n">
         <v>3332.449951171875</v>
@@ -7186,7 +7186,7 @@
         <v>2165.699951171875</v>
       </c>
       <c r="F211" t="n">
-        <v>836.0755615234375</v>
+        <v>836.07568359375</v>
       </c>
       <c r="G211" t="n">
         <v>69.72000122070312</v>
@@ -7212,13 +7212,13 @@
         <v>3290</v>
       </c>
       <c r="D212" t="n">
-        <v>3989.940185546875</v>
+        <v>3989.9404296875</v>
       </c>
       <c r="E212" t="n">
         <v>2215.5</v>
       </c>
       <c r="F212" t="n">
-        <v>873.1255493164062</v>
+        <v>873.1256103515625</v>
       </c>
       <c r="G212" t="n">
         <v>73.16000366210938</v>
@@ -7227,7 +7227,7 @@
         <v>554.75341796875</v>
       </c>
       <c r="I212" t="n">
-        <v>3790.00146484375</v>
+        <v>3790.001708984375</v>
       </c>
       <c r="J212" t="n">
         <v>368.75</v>
@@ -7259,7 +7259,7 @@
         <v>548.5131225585938</v>
       </c>
       <c r="I213" t="n">
-        <v>3702.022216796875</v>
+        <v>3702.0224609375</v>
       </c>
       <c r="J213" t="n">
         <v>366.8999938964844</v>
@@ -7270,13 +7270,13 @@
         <v>44876</v>
       </c>
       <c r="B214" t="n">
-        <v>2348.609619140625</v>
+        <v>2348.609375</v>
       </c>
       <c r="C214" t="n">
         <v>3292.050048828125</v>
       </c>
       <c r="D214" t="n">
-        <v>4001.569580078125</v>
+        <v>4001.5693359375</v>
       </c>
       <c r="E214" t="n">
         <v>2196.699951171875</v>
@@ -7288,7 +7288,7 @@
         <v>72.04000091552734</v>
       </c>
       <c r="H214" t="n">
-        <v>547.9234008789062</v>
+        <v>547.9234619140625</v>
       </c>
       <c r="I214" t="n">
         <v>3795.39404296875</v>
@@ -7302,13 +7302,13 @@
         <v>44879</v>
       </c>
       <c r="B215" t="n">
-        <v>2392.62158203125</v>
+        <v>2392.621826171875</v>
       </c>
       <c r="C215" t="n">
         <v>3287.64990234375</v>
       </c>
       <c r="D215" t="n">
-        <v>4015.24462890625</v>
+        <v>4015.244384765625</v>
       </c>
       <c r="E215" t="n">
         <v>2178.550048828125</v>
@@ -7323,7 +7323,7 @@
         <v>570.2806396484375</v>
       </c>
       <c r="I215" t="n">
-        <v>3864.998779296875</v>
+        <v>3864.99853515625</v>
       </c>
       <c r="J215" t="n">
         <v>364.8500061035156</v>
@@ -7352,7 +7352,7 @@
         <v>71.41000366210938</v>
       </c>
       <c r="H216" t="n">
-        <v>576.3245239257812</v>
+        <v>576.324462890625</v>
       </c>
       <c r="I216" t="n">
         <v>3879.978271484375</v>
@@ -7372,22 +7372,22 @@
         <v>3271.14990234375</v>
       </c>
       <c r="D217" t="n">
-        <v>3949.41455078125</v>
+        <v>3949.414306640625</v>
       </c>
       <c r="E217" t="n">
         <v>2110.14990234375</v>
       </c>
       <c r="F217" t="n">
-        <v>869.7440795898438</v>
+        <v>869.7440185546875</v>
       </c>
       <c r="G217" t="n">
         <v>69.02999877929688</v>
       </c>
       <c r="H217" t="n">
-        <v>567.2342529296875</v>
+        <v>567.2341918945312</v>
       </c>
       <c r="I217" t="n">
-        <v>3804.431396484375</v>
+        <v>3804.431884765625</v>
       </c>
       <c r="J217" t="n">
         <v>402.1499938964844</v>
@@ -7404,19 +7404,19 @@
         <v>3117.550048828125</v>
       </c>
       <c r="D218" t="n">
-        <v>4010.8525390625</v>
+        <v>4010.852294921875</v>
       </c>
       <c r="E218" t="n">
         <v>2102.60009765625</v>
       </c>
       <c r="F218" t="n">
-        <v>873.174560546875</v>
+        <v>873.1746215820312</v>
       </c>
       <c r="G218" t="n">
         <v>67.19999694824219</v>
       </c>
       <c r="H218" t="n">
-        <v>564.2859497070312</v>
+        <v>564.2860107421875</v>
       </c>
       <c r="I218" t="n">
         <v>3748.308837890625</v>
@@ -7451,7 +7451,7 @@
         <v>564.1876831054688</v>
       </c>
       <c r="I219" t="n">
-        <v>3639.657470703125</v>
+        <v>3639.65771484375</v>
       </c>
       <c r="J219" t="n">
         <v>401.1499938964844</v>
@@ -7462,13 +7462,13 @@
         <v>44886</v>
       </c>
       <c r="B220" t="n">
-        <v>2413.547119140625</v>
+        <v>2413.54736328125</v>
       </c>
       <c r="C220" t="n">
         <v>3018.699951171875</v>
       </c>
       <c r="D220" t="n">
-        <v>3994.582275390625</v>
+        <v>3994.58203125</v>
       </c>
       <c r="E220" t="n">
         <v>2003.300048828125</v>
@@ -7480,10 +7480,10 @@
         <v>66.23999786376953</v>
       </c>
       <c r="H220" t="n">
-        <v>554.3111572265625</v>
+        <v>554.3112182617188</v>
       </c>
       <c r="I220" t="n">
-        <v>3655.9853515625</v>
+        <v>3655.985595703125</v>
       </c>
       <c r="J220" t="n">
         <v>381.1000061035156</v>
@@ -7506,13 +7506,13 @@
         <v>1986.099975585938</v>
       </c>
       <c r="F221" t="n">
-        <v>864.9412841796875</v>
+        <v>864.9413452148438</v>
       </c>
       <c r="G221" t="n">
         <v>65.69999694824219</v>
       </c>
       <c r="H221" t="n">
-        <v>556.0802001953125</v>
+        <v>556.0801391601562</v>
       </c>
       <c r="I221" t="n">
         <v>3666.37109375</v>
@@ -7526,13 +7526,13 @@
         <v>44888</v>
       </c>
       <c r="B222" t="n">
-        <v>2415.6591796875</v>
+        <v>2415.659423828125</v>
       </c>
       <c r="C222" t="n">
         <v>2856.85009765625</v>
       </c>
       <c r="D222" t="n">
-        <v>3896.2109375</v>
+        <v>3896.211181640625</v>
       </c>
       <c r="E222" t="n">
         <v>2036.5</v>
@@ -7544,10 +7544,10 @@
         <v>65.19000244140625</v>
       </c>
       <c r="H222" t="n">
-        <v>553.1810913085938</v>
+        <v>553.18115234375</v>
       </c>
       <c r="I222" t="n">
-        <v>3747.309814453125</v>
+        <v>3747.31005859375</v>
       </c>
       <c r="J222" t="n">
         <v>358.5499877929688</v>
@@ -7558,7 +7558,7 @@
         <v>44889</v>
       </c>
       <c r="B223" t="n">
-        <v>2418.066162109375</v>
+        <v>2418.06640625</v>
       </c>
       <c r="C223" t="n">
         <v>2790.85009765625</v>
@@ -7579,7 +7579,7 @@
         <v>548.2182006835938</v>
       </c>
       <c r="I223" t="n">
-        <v>3725.8896484375</v>
+        <v>3725.889404296875</v>
       </c>
       <c r="J223" t="n">
         <v>367.25</v>
@@ -7602,7 +7602,7 @@
         <v>2023.949951171875</v>
       </c>
       <c r="F224" t="n">
-        <v>862.1477661132812</v>
+        <v>862.1478271484375</v>
       </c>
       <c r="G224" t="n">
         <v>64.79000091552734</v>
@@ -7611,7 +7611,7 @@
         <v>554.90087890625</v>
       </c>
       <c r="I224" t="n">
-        <v>3659.730224609375</v>
+        <v>3659.73046875</v>
       </c>
       <c r="J224" t="n">
         <v>385.6000061035156</v>
@@ -7622,13 +7622,13 @@
         <v>44893</v>
       </c>
       <c r="B225" t="n">
-        <v>2482.66015625</v>
+        <v>2482.660400390625</v>
       </c>
       <c r="C225" t="n">
         <v>2716.14990234375</v>
       </c>
       <c r="D225" t="n">
-        <v>3879.091796875</v>
+        <v>3879.092041015625</v>
       </c>
       <c r="E225" t="n">
         <v>1990.699951171875</v>
@@ -7654,13 +7654,13 @@
         <v>44894</v>
       </c>
       <c r="B226" t="n">
-        <v>2469.83984375</v>
+        <v>2469.839599609375</v>
       </c>
       <c r="C226" t="n">
         <v>2782.699951171875</v>
       </c>
       <c r="D226" t="n">
-        <v>3871.356201171875</v>
+        <v>3871.35595703125</v>
       </c>
       <c r="E226" t="n">
         <v>2012.050048828125</v>
@@ -7672,10 +7672,10 @@
         <v>64.94000244140625</v>
       </c>
       <c r="H226" t="n">
-        <v>555.1956787109375</v>
+        <v>555.1956176757812</v>
       </c>
       <c r="I226" t="n">
-        <v>3595.068603515625</v>
+        <v>3595.06884765625</v>
       </c>
       <c r="J226" t="n">
         <v>425.0499877929688</v>
@@ -7692,13 +7692,13 @@
         <v>2908.5</v>
       </c>
       <c r="D227" t="n">
-        <v>3910.7841796875</v>
+        <v>3910.784423828125</v>
       </c>
       <c r="E227" t="n">
         <v>2116.5</v>
       </c>
       <c r="F227" t="n">
-        <v>863.52001953125</v>
+        <v>863.5200805664062</v>
       </c>
       <c r="G227" t="n">
         <v>66.55000305175781</v>
@@ -7707,7 +7707,7 @@
         <v>560.8955688476562</v>
       </c>
       <c r="I227" t="n">
-        <v>3627.774169921875</v>
+        <v>3627.77392578125</v>
       </c>
       <c r="J227" t="n">
         <v>446.2999877929688</v>
@@ -7718,7 +7718,7 @@
         <v>44896</v>
       </c>
       <c r="B228" t="n">
-        <v>2532.0263671875</v>
+        <v>2532.026611328125</v>
       </c>
       <c r="C228" t="n">
         <v>2834.25</v>
@@ -7730,7 +7730,7 @@
         <v>2113.550048828125</v>
       </c>
       <c r="F228" t="n">
-        <v>872.880615234375</v>
+        <v>872.8805541992188</v>
       </c>
       <c r="G228" t="n">
         <v>66.08000183105469</v>
@@ -7739,7 +7739,7 @@
         <v>570.91943359375</v>
       </c>
       <c r="I228" t="n">
-        <v>3607.4521484375</v>
+        <v>3607.451904296875</v>
       </c>
       <c r="J228" t="n">
         <v>424.7999877929688</v>
@@ -7750,7 +7750,7 @@
         <v>44897</v>
       </c>
       <c r="B229" t="n">
-        <v>2563.41455078125</v>
+        <v>2563.414794921875</v>
       </c>
       <c r="C229" t="n">
         <v>2745.699951171875</v>
@@ -7768,7 +7768,7 @@
         <v>65.05999755859375</v>
       </c>
       <c r="H229" t="n">
-        <v>567.9712524414062</v>
+        <v>567.97119140625</v>
       </c>
       <c r="I229" t="n">
         <v>3574.74658203125</v>
@@ -7782,28 +7782,28 @@
         <v>44900</v>
       </c>
       <c r="B230" t="n">
-        <v>2575.00732421875</v>
+        <v>2575.007080078125</v>
       </c>
       <c r="C230" t="n">
         <v>2716.14990234375</v>
       </c>
       <c r="D230" t="n">
-        <v>3923.261474609375</v>
+        <v>3923.26171875</v>
       </c>
       <c r="E230" t="n">
         <v>2042.099975585938</v>
       </c>
       <c r="F230" t="n">
-        <v>875.4290161132812</v>
+        <v>875.428955078125</v>
       </c>
       <c r="G230" t="n">
         <v>64.61000061035156</v>
       </c>
       <c r="H230" t="n">
-        <v>563.45068359375</v>
+        <v>563.4506225585938</v>
       </c>
       <c r="I230" t="n">
-        <v>3585.182373046875</v>
+        <v>3585.1826171875</v>
       </c>
       <c r="J230" t="n">
         <v>392.9500122070312</v>
@@ -7814,7 +7814,7 @@
         <v>44901</v>
       </c>
       <c r="B231" t="n">
-        <v>2575.05615234375</v>
+        <v>2575.056396484375</v>
       </c>
       <c r="C231" t="n">
         <v>2773</v>
@@ -7826,16 +7826,16 @@
         <v>2063.300048828125</v>
       </c>
       <c r="F231" t="n">
-        <v>878.66357421875</v>
+        <v>878.6635131835938</v>
       </c>
       <c r="G231" t="n">
         <v>64.95999908447266</v>
       </c>
       <c r="H231" t="n">
-        <v>570.968505859375</v>
+        <v>570.9685668945312</v>
       </c>
       <c r="I231" t="n">
-        <v>3691.78662109375</v>
+        <v>3691.786376953125</v>
       </c>
       <c r="J231" t="n">
         <v>373.3500061035156</v>
@@ -7858,13 +7858,13 @@
         <v>2032.699951171875</v>
       </c>
       <c r="F232" t="n">
-        <v>869.156005859375</v>
+        <v>869.1558837890625</v>
       </c>
       <c r="G232" t="n">
         <v>64.88999938964844</v>
       </c>
       <c r="H232" t="n">
-        <v>571.9512939453125</v>
+        <v>571.9513549804688</v>
       </c>
       <c r="I232" t="n">
         <v>3725.240478515625</v>
@@ -7890,7 +7890,7 @@
         <v>2052.699951171875</v>
       </c>
       <c r="F233" t="n">
-        <v>875.1839599609375</v>
+        <v>875.1840209960938</v>
       </c>
       <c r="G233" t="n">
         <v>64.75</v>
@@ -7899,7 +7899,7 @@
         <v>577.60205078125</v>
       </c>
       <c r="I233" t="n">
-        <v>3689.839111328125</v>
+        <v>3689.8388671875</v>
       </c>
       <c r="J233" t="n">
         <v>339.3999938964844</v>
@@ -7916,7 +7916,7 @@
         <v>2646.39990234375</v>
       </c>
       <c r="D234" t="n">
-        <v>3989.541259765625</v>
+        <v>3989.541015625</v>
       </c>
       <c r="E234" t="n">
         <v>2053.449951171875</v>
@@ -7928,7 +7928,7 @@
         <v>63.20999908447266</v>
       </c>
       <c r="H234" t="n">
-        <v>570.968505859375</v>
+        <v>570.9685668945312</v>
       </c>
       <c r="I234" t="n">
         <v>3616.33984375</v>
@@ -7954,13 +7954,13 @@
         <v>2024.050048828125</v>
       </c>
       <c r="F235" t="n">
-        <v>863.8140869140625</v>
+        <v>863.8141479492188</v>
       </c>
       <c r="G235" t="n">
         <v>62.04000091552734</v>
       </c>
       <c r="H235" t="n">
-        <v>574.9486694335938</v>
+        <v>574.9486083984375</v>
       </c>
       <c r="I235" t="n">
         <v>3636.012939453125</v>
@@ -7974,7 +7974,7 @@
         <v>44908</v>
       </c>
       <c r="B236" t="n">
-        <v>2612.78076171875</v>
+        <v>2612.781005859375</v>
       </c>
       <c r="C236" t="n">
         <v>2652.800048828125</v>
@@ -7986,13 +7986,13 @@
         <v>2021.400024414062</v>
       </c>
       <c r="F236" t="n">
-        <v>877.0462646484375</v>
+        <v>877.0463256835938</v>
       </c>
       <c r="G236" t="n">
         <v>64.59999847412109</v>
       </c>
       <c r="H236" t="n">
-        <v>574.457275390625</v>
+        <v>574.4572143554688</v>
       </c>
       <c r="I236" t="n">
         <v>3581.3876953125</v>
@@ -8006,28 +8006,28 @@
         <v>44909</v>
       </c>
       <c r="B237" t="n">
-        <v>2621.671875</v>
+        <v>2621.672119140625</v>
       </c>
       <c r="C237" t="n">
         <v>2672.449951171875</v>
       </c>
       <c r="D237" t="n">
-        <v>4048.433837890625</v>
+        <v>4048.43359375</v>
       </c>
       <c r="E237" t="n">
         <v>2018.150024414062</v>
       </c>
       <c r="F237" t="n">
-        <v>882.68212890625</v>
+        <v>882.6821899414062</v>
       </c>
       <c r="G237" t="n">
         <v>63.86999893188477</v>
       </c>
       <c r="H237" t="n">
-        <v>572.1478271484375</v>
+        <v>572.14794921875</v>
       </c>
       <c r="I237" t="n">
-        <v>3513.031494140625</v>
+        <v>3513.03173828125</v>
       </c>
       <c r="J237" t="n">
         <v>376.2000122070312</v>
@@ -8050,13 +8050,13 @@
         <v>2024.900024414062</v>
       </c>
       <c r="F238" t="n">
-        <v>866.4114990234375</v>
+        <v>866.4115600585938</v>
       </c>
       <c r="G238" t="n">
         <v>63.09000015258789</v>
       </c>
       <c r="H238" t="n">
-        <v>551.510498046875</v>
+        <v>551.5104370117188</v>
       </c>
       <c r="I238" t="n">
         <v>3545.886474609375</v>
@@ -8082,13 +8082,13 @@
         <v>2044.25</v>
       </c>
       <c r="F239" t="n">
-        <v>843.3777465820312</v>
+        <v>843.3778076171875</v>
       </c>
       <c r="G239" t="n">
         <v>61.58000183105469</v>
       </c>
       <c r="H239" t="n">
-        <v>546.4493408203125</v>
+        <v>546.4494018554688</v>
       </c>
       <c r="I239" t="n">
         <v>3579.889892578125</v>
@@ -8108,7 +8108,7 @@
         <v>2679.300048828125</v>
       </c>
       <c r="D240" t="n">
-        <v>4067.8984375</v>
+        <v>4067.898681640625</v>
       </c>
       <c r="E240" t="n">
         <v>2062.050048828125</v>
@@ -8120,10 +8120,10 @@
         <v>61.15999984741211</v>
       </c>
       <c r="H240" t="n">
-        <v>554.1146240234375</v>
+        <v>554.1146850585938</v>
       </c>
       <c r="I240" t="n">
-        <v>3613.493408203125</v>
+        <v>3613.49365234375</v>
       </c>
       <c r="J240" t="n">
         <v>368.8999938964844</v>
@@ -8134,7 +8134,7 @@
         <v>44915</v>
       </c>
       <c r="B241" t="n">
-        <v>2546.90966796875</v>
+        <v>2546.909912109375</v>
       </c>
       <c r="C241" t="n">
         <v>2688.35009765625</v>
@@ -8146,13 +8146,13 @@
         <v>2061.64990234375</v>
       </c>
       <c r="F241" t="n">
-        <v>866.70556640625</v>
+        <v>866.7056274414062</v>
       </c>
       <c r="G241" t="n">
         <v>61.15000152587891</v>
       </c>
       <c r="H241" t="n">
-        <v>550.4293823242188</v>
+        <v>550.429443359375</v>
       </c>
       <c r="I241" t="n">
         <v>3609.24951171875</v>
@@ -8178,13 +8178,13 @@
         <v>1968.25</v>
       </c>
       <c r="F242" t="n">
-        <v>840.6334228515625</v>
+        <v>840.6333618164062</v>
       </c>
       <c r="G242" t="n">
         <v>58.09999847412109</v>
       </c>
       <c r="H242" t="n">
-        <v>529.8903198242188</v>
+        <v>529.890380859375</v>
       </c>
       <c r="I242" t="n">
         <v>3539.8447265625</v>
@@ -8204,7 +8204,7 @@
         <v>2518</v>
       </c>
       <c r="D243" t="n">
-        <v>3861.524169921875</v>
+        <v>3861.52392578125</v>
       </c>
       <c r="E243" t="n">
         <v>1980.75</v>
@@ -8219,7 +8219,7 @@
         <v>523.64990234375</v>
       </c>
       <c r="I243" t="n">
-        <v>3546.685546875</v>
+        <v>3546.68505859375</v>
       </c>
       <c r="J243" t="n">
         <v>331.6499938964844</v>
@@ -8236,22 +8236,22 @@
         <v>2270.199951171875</v>
       </c>
       <c r="D244" t="n">
-        <v>3635.585205078125</v>
+        <v>3635.5849609375</v>
       </c>
       <c r="E244" t="n">
         <v>1809.050048828125</v>
       </c>
       <c r="F244" t="n">
-        <v>778.34423828125</v>
+        <v>778.3441772460938</v>
       </c>
       <c r="G244" t="n">
         <v>52.43999862670898</v>
       </c>
       <c r="H244" t="n">
-        <v>482.7681884765625</v>
+        <v>482.7681579589844</v>
       </c>
       <c r="I244" t="n">
-        <v>3228.17236328125</v>
+        <v>3228.172119140625</v>
       </c>
       <c r="J244" t="n">
         <v>340.6499938964844</v>
@@ -8274,7 +8274,7 @@
         <v>1876.849975585938</v>
       </c>
       <c r="F245" t="n">
-        <v>790.0570678710938</v>
+        <v>790.05712890625</v>
       </c>
       <c r="G245" t="n">
         <v>55.06000137329102</v>
@@ -8283,7 +8283,7 @@
         <v>505.2728271484375</v>
       </c>
       <c r="I245" t="n">
-        <v>3307.16357421875</v>
+        <v>3307.163818359375</v>
       </c>
       <c r="J245" t="n">
         <v>343.2999877929688</v>
@@ -8312,10 +8312,10 @@
         <v>57.81000137329102</v>
       </c>
       <c r="H246" t="n">
-        <v>514.2648315429688</v>
+        <v>514.2647705078125</v>
       </c>
       <c r="I246" t="n">
-        <v>3348.307373046875</v>
+        <v>3348.30712890625</v>
       </c>
       <c r="J246" t="n">
         <v>338.4500122070312</v>
@@ -8326,7 +8326,7 @@
         <v>44923</v>
       </c>
       <c r="B247" t="n">
-        <v>2412.172119140625</v>
+        <v>2412.171875</v>
       </c>
       <c r="C247" t="n">
         <v>2564.449951171875</v>
@@ -8347,7 +8347,7 @@
         <v>509.449462890625</v>
       </c>
       <c r="I247" t="n">
-        <v>3600.861083984375</v>
+        <v>3600.861328125</v>
       </c>
       <c r="J247" t="n">
         <v>331.1000061035156</v>
@@ -8358,28 +8358,28 @@
         <v>44924</v>
       </c>
       <c r="B248" t="n">
-        <v>2404.803955078125</v>
+        <v>2404.80419921875</v>
       </c>
       <c r="C248" t="n">
         <v>2669.5</v>
       </c>
       <c r="D248" t="n">
-        <v>3803.679443359375</v>
+        <v>3803.67919921875</v>
       </c>
       <c r="E248" t="n">
         <v>1910.25</v>
       </c>
       <c r="F248" t="n">
-        <v>803.289306640625</v>
+        <v>803.2892456054688</v>
       </c>
       <c r="G248" t="n">
         <v>60.90000152587891</v>
       </c>
       <c r="H248" t="n">
-        <v>513.724365234375</v>
+        <v>513.7243041992188</v>
       </c>
       <c r="I248" t="n">
-        <v>3787.8046875</v>
+        <v>3787.804443359375</v>
       </c>
       <c r="J248" t="n">
         <v>339.2999877929688</v>
@@ -8396,7 +8396,7 @@
         <v>2589.25</v>
       </c>
       <c r="D249" t="n">
-        <v>3851.342529296875</v>
+        <v>3851.3427734375</v>
       </c>
       <c r="E249" t="n">
         <v>1931.800048828125</v>
@@ -8466,13 +8466,13 @@
         <v>1892.949951171875</v>
       </c>
       <c r="F251" t="n">
-        <v>804.1715087890625</v>
+        <v>804.1714477539062</v>
       </c>
       <c r="G251" t="n">
         <v>58.95000076293945</v>
       </c>
       <c r="H251" t="n">
-        <v>521.7827758789062</v>
+        <v>521.78271484375</v>
       </c>
       <c r="I251" t="n">
         <v>3593.720703125</v>
@@ -8486,13 +8486,13 @@
         <v>44930</v>
       </c>
       <c r="B252" t="n">
-        <v>2366.931884765625</v>
+        <v>2366.931640625</v>
       </c>
       <c r="C252" t="n">
         <v>2512.699951171875</v>
       </c>
       <c r="D252" t="n">
-        <v>3820.099365234375</v>
+        <v>3820.099609375</v>
       </c>
       <c r="E252" t="n">
         <v>1860.5</v>
@@ -8507,7 +8507,7 @@
         <v>509.8915710449219</v>
       </c>
       <c r="I252" t="n">
-        <v>3472.537109375</v>
+        <v>3472.537353515625</v>
       </c>
       <c r="J252" t="n">
         <v>333.7999877929688</v>
@@ -8530,7 +8530,7 @@
         <v>1860</v>
       </c>
       <c r="F253" t="n">
-        <v>803.3383178710938</v>
+        <v>803.3382568359375</v>
       </c>
       <c r="G253" t="n">
         <v>57.75</v>
@@ -8556,7 +8556,7 @@
         <v>2523.35009765625</v>
       </c>
       <c r="D254" t="n">
-        <v>3817.3046875</v>
+        <v>3817.304443359375</v>
       </c>
       <c r="E254" t="n">
         <v>1838.25</v>
@@ -8568,10 +8568,10 @@
         <v>56.68000030517578</v>
       </c>
       <c r="H254" t="n">
-        <v>510.8251647949219</v>
+        <v>510.8252563476562</v>
       </c>
       <c r="I254" t="n">
-        <v>3550.530029296875</v>
+        <v>3550.52978515625</v>
       </c>
       <c r="J254" t="n">
         <v>318.5</v>
@@ -8582,7 +8582,7 @@
         <v>44935</v>
       </c>
       <c r="B255" t="n">
-        <v>2421.30810546875</v>
+        <v>2421.308349609375</v>
       </c>
       <c r="C255" t="n">
         <v>2614.5</v>
@@ -8620,7 +8620,7 @@
         <v>2652</v>
       </c>
       <c r="D256" t="n">
-        <v>3640.2763671875</v>
+        <v>3640.276611328125</v>
       </c>
       <c r="E256" t="n">
         <v>1895.199951171875</v>
@@ -8652,13 +8652,13 @@
         <v>2585.35009765625</v>
       </c>
       <c r="D257" t="n">
-        <v>3629.19677734375</v>
+        <v>3629.197021484375</v>
       </c>
       <c r="E257" t="n">
         <v>1877.150024414062</v>
       </c>
       <c r="F257" t="n">
-        <v>780.6475830078125</v>
+        <v>780.6476440429688</v>
       </c>
       <c r="G257" t="n">
         <v>55.2400016784668</v>
@@ -8678,7 +8678,7 @@
         <v>44938</v>
       </c>
       <c r="B258" t="n">
-        <v>2322.821044921875</v>
+        <v>2322.8212890625</v>
       </c>
       <c r="C258" t="n">
         <v>2624</v>
@@ -8690,13 +8690,13 @@
         <v>1889.849975585938</v>
       </c>
       <c r="F258" t="n">
-        <v>777.2171020507812</v>
+        <v>777.217041015625</v>
       </c>
       <c r="G258" t="n">
         <v>54.72999954223633</v>
       </c>
       <c r="H258" t="n">
-        <v>501.5875549316406</v>
+        <v>501.5875244140625</v>
       </c>
       <c r="I258" t="n">
         <v>3644.0517578125</v>
@@ -8716,22 +8716,22 @@
         <v>2689.050048828125</v>
       </c>
       <c r="D259" t="n">
-        <v>3714.3916015625</v>
+        <v>3714.391845703125</v>
       </c>
       <c r="E259" t="n">
         <v>1915.650024414062</v>
       </c>
       <c r="F259" t="n">
-        <v>778.88330078125</v>
+        <v>778.8833618164062</v>
       </c>
       <c r="G259" t="n">
         <v>55.7400016784668</v>
       </c>
       <c r="H259" t="n">
-        <v>509.6951599121094</v>
+        <v>509.6950988769531</v>
       </c>
       <c r="I259" t="n">
-        <v>3710.011474609375</v>
+        <v>3710.01123046875</v>
       </c>
       <c r="J259" t="n">
         <v>304.5499877929688</v>
@@ -8748,7 +8748,7 @@
         <v>2703.10009765625</v>
       </c>
       <c r="D260" t="n">
-        <v>3613.225830078125</v>
+        <v>3613.2255859375</v>
       </c>
       <c r="E260" t="n">
         <v>2089.800048828125</v>
@@ -8760,7 +8760,7 @@
         <v>54.59000015258789</v>
       </c>
       <c r="H260" t="n">
-        <v>508.0735473632812</v>
+        <v>508.0735778808594</v>
       </c>
       <c r="I260" t="n">
         <v>3725.58984375</v>
@@ -8774,13 +8774,13 @@
         <v>44943</v>
       </c>
       <c r="B261" t="n">
-        <v>2304.74462890625</v>
+        <v>2304.744873046875</v>
       </c>
       <c r="C261" t="n">
         <v>2725.050048828125</v>
       </c>
       <c r="D261" t="n">
-        <v>3632.740478515625</v>
+        <v>3632.74072265625</v>
       </c>
       <c r="E261" t="n">
         <v>2166.14990234375</v>
@@ -8792,10 +8792,10 @@
         <v>56.38999938964844</v>
       </c>
       <c r="H261" t="n">
-        <v>508.5649108886719</v>
+        <v>508.56494140625</v>
       </c>
       <c r="I261" t="n">
-        <v>3844.7265625</v>
+        <v>3844.726318359375</v>
       </c>
       <c r="J261" t="n">
         <v>296.7999877929688</v>
@@ -8818,16 +8818,16 @@
         <v>2096.89990234375</v>
       </c>
       <c r="F262" t="n">
-        <v>770.89501953125</v>
+        <v>770.8950805664062</v>
       </c>
       <c r="G262" t="n">
         <v>55.7400016784668</v>
       </c>
       <c r="H262" t="n">
-        <v>511.4640197753906</v>
+        <v>511.4639892578125</v>
       </c>
       <c r="I262" t="n">
-        <v>3800.237548828125</v>
+        <v>3800.23779296875</v>
       </c>
       <c r="J262" t="n">
         <v>299.7000122070312</v>
@@ -8856,10 +8856,10 @@
         <v>55.5099983215332</v>
       </c>
       <c r="H263" t="n">
-        <v>510.28466796875</v>
+        <v>510.2846984863281</v>
       </c>
       <c r="I263" t="n">
-        <v>3830.296142578125</v>
+        <v>3830.29638671875</v>
       </c>
       <c r="J263" t="n">
         <v>288.2999877929688</v>
@@ -8882,16 +8882,16 @@
         <v>1975.599975585938</v>
       </c>
       <c r="F264" t="n">
-        <v>759.0841064453125</v>
+        <v>759.0841674804688</v>
       </c>
       <c r="G264" t="n">
         <v>55.0099983215332</v>
       </c>
       <c r="H264" t="n">
-        <v>508.8106384277344</v>
+        <v>508.8106079101562</v>
       </c>
       <c r="I264" t="n">
-        <v>3913.531982421875</v>
+        <v>3913.5322265625</v>
       </c>
       <c r="J264" t="n">
         <v>280.75</v>
@@ -8920,7 +8920,7 @@
         <v>54.63999938964844</v>
       </c>
       <c r="H265" t="n">
-        <v>492.4481201171875</v>
+        <v>492.4480895996094</v>
       </c>
       <c r="I265" t="n">
         <v>3895.7568359375</v>
@@ -8934,7 +8934,7 @@
         <v>44950</v>
       </c>
       <c r="B266" t="n">
-        <v>2294.6259765625</v>
+        <v>2294.625732421875</v>
       </c>
       <c r="C266" t="n">
         <v>2762.14990234375</v>
@@ -8946,16 +8946,16 @@
         <v>1916.800048828125</v>
       </c>
       <c r="F266" t="n">
-        <v>746.0970458984375</v>
+        <v>746.0971069335938</v>
       </c>
       <c r="G266" t="n">
         <v>54.93000030517578</v>
       </c>
       <c r="H266" t="n">
-        <v>490.3352355957031</v>
+        <v>490.3352661132812</v>
       </c>
       <c r="I266" t="n">
-        <v>3886.41943359375</v>
+        <v>3886.419189453125</v>
       </c>
       <c r="J266" t="n">
         <v>284</v>
@@ -8984,7 +8984,7 @@
         <v>52.20000076293945</v>
       </c>
       <c r="H267" t="n">
-        <v>452.2542724609375</v>
+        <v>452.2543029785156</v>
       </c>
       <c r="I267" t="n">
         <v>3654.986572265625</v>
@@ -9016,7 +9016,7 @@
         <v>49.59000015258789</v>
       </c>
       <c r="H268" t="n">
-        <v>373.8812255859375</v>
+        <v>373.8812561035156</v>
       </c>
       <c r="I268" t="n">
         <v>2923.989501953125</v>
@@ -9030,19 +9030,19 @@
         <v>44956</v>
       </c>
       <c r="B269" t="n">
-        <v>1870.664916992188</v>
+        <v>1870.664794921875</v>
       </c>
       <c r="C269" t="n">
         <v>1708.199951171875</v>
       </c>
       <c r="D269" t="n">
-        <v>2887.59619140625</v>
+        <v>2887.596435546875</v>
       </c>
       <c r="E269" t="n">
         <v>1189</v>
       </c>
       <c r="F269" t="n">
-        <v>585.1549072265625</v>
+        <v>585.1549682617188</v>
       </c>
       <c r="G269" t="n">
         <v>47.11000061035156</v>
@@ -9062,19 +9062,19 @@
         <v>44957</v>
       </c>
       <c r="B270" t="n">
-        <v>1933.686889648438</v>
+        <v>1933.686767578125</v>
       </c>
       <c r="C270" t="n">
         <v>1774</v>
       </c>
       <c r="D270" t="n">
-        <v>2968.498779296875</v>
+        <v>2968.49853515625</v>
       </c>
       <c r="E270" t="n">
         <v>1223.900024414062</v>
       </c>
       <c r="F270" t="n">
-        <v>600.494384765625</v>
+        <v>600.4944458007812</v>
       </c>
       <c r="G270" t="n">
         <v>44.7599983215332</v>
@@ -9112,10 +9112,10 @@
         <v>42.52999877929688</v>
       </c>
       <c r="H271" t="n">
-        <v>328.3314819335938</v>
+        <v>328.3315124511719</v>
       </c>
       <c r="I271" t="n">
-        <v>1894.801147460938</v>
+        <v>1894.801025390625</v>
       </c>
       <c r="J271" t="n">
         <v>235.6999969482422</v>
@@ -9126,13 +9126,13 @@
         <v>44959</v>
       </c>
       <c r="B272" t="n">
-        <v>1808.870971679688</v>
+        <v>1808.87109375</v>
       </c>
       <c r="C272" t="n">
         <v>1551.150024414062</v>
       </c>
       <c r="D272" t="n">
-        <v>1562.4072265625</v>
+        <v>1562.407348632812</v>
       </c>
       <c r="E272" t="n">
         <v>1039.849975585938</v>
@@ -9158,7 +9158,7 @@
         <v>44960</v>
       </c>
       <c r="B273" t="n">
-        <v>1892.867553710938</v>
+        <v>1892.867431640625</v>
       </c>
       <c r="C273" t="n">
         <v>1396.050048828125</v>
@@ -9176,7 +9176,7 @@
         <v>38.38999938964844</v>
       </c>
       <c r="H273" t="n">
-        <v>367.1495056152344</v>
+        <v>367.1494750976562</v>
       </c>
       <c r="I273" t="n">
         <v>1620.127807617188</v>
@@ -9196,13 +9196,13 @@
         <v>1256.449951171875</v>
       </c>
       <c r="D274" t="n">
-        <v>1569.84375</v>
+        <v>1569.843627929688</v>
       </c>
       <c r="E274" t="n">
         <v>889.0999755859375</v>
       </c>
       <c r="F274" t="n">
-        <v>534.6277465820312</v>
+        <v>534.627685546875</v>
       </c>
       <c r="G274" t="n">
         <v>36.47000122070312</v>
@@ -9234,7 +9234,7 @@
         <v>844.6500244140625</v>
       </c>
       <c r="F275" t="n">
-        <v>542.1749267578125</v>
+        <v>542.1749877929688</v>
       </c>
       <c r="G275" t="n">
         <v>34.65000152587891</v>
@@ -9243,7 +9243,7 @@
         <v>377.4190673828125</v>
       </c>
       <c r="I275" t="n">
-        <v>1462.1943359375</v>
+        <v>1462.194458007812</v>
       </c>
       <c r="J275" t="n">
         <v>216.8999938964844</v>
@@ -9266,16 +9266,16 @@
         <v>802.4500122070312</v>
       </c>
       <c r="F276" t="n">
-        <v>587.3602294921875</v>
+        <v>587.3602905273438</v>
       </c>
       <c r="G276" t="n">
         <v>36.38000106811523</v>
       </c>
       <c r="H276" t="n">
-        <v>378.0087280273438</v>
+        <v>378.0086975097656</v>
       </c>
       <c r="I276" t="n">
-        <v>1389.0947265625</v>
+        <v>1389.094604492188</v>
       </c>
       <c r="J276" t="n">
         <v>227.6999969482422</v>
@@ -9298,7 +9298,7 @@
         <v>762.3499755859375</v>
       </c>
       <c r="F277" t="n">
-        <v>570.7465209960938</v>
+        <v>570.74658203125</v>
       </c>
       <c r="G277" t="n">
         <v>34.56000137329102</v>
@@ -9318,13 +9318,13 @@
         <v>44967</v>
       </c>
       <c r="B278" t="n">
-        <v>1847.33251953125</v>
+        <v>1847.332641601562</v>
       </c>
       <c r="C278" t="n">
         <v>1186.650024414062</v>
       </c>
       <c r="D278" t="n">
-        <v>1843.595581054688</v>
+        <v>1843.595703125</v>
       </c>
       <c r="E278" t="n">
         <v>724.25</v>
@@ -9368,7 +9368,7 @@
         <v>31.20000076293945</v>
       </c>
       <c r="H279" t="n">
-        <v>336.5373229980469</v>
+        <v>336.537353515625</v>
       </c>
       <c r="I279" t="n">
         <v>1191.016357421875</v>
@@ -9403,7 +9403,7 @@
         <v>330.6900634765625</v>
       </c>
       <c r="I280" t="n">
-        <v>1131.498168945312</v>
+        <v>1131.498046875</v>
       </c>
       <c r="J280" t="n">
         <v>188.1999969482422</v>
@@ -9414,7 +9414,7 @@
         <v>44972</v>
       </c>
       <c r="B281" t="n">
-        <v>1819.579345703125</v>
+        <v>1819.579223632812</v>
       </c>
       <c r="C281" t="n">
         <v>1017.450012207031</v>
@@ -9426,13 +9426,13 @@
         <v>621</v>
       </c>
       <c r="F281" t="n">
-        <v>557.7593994140625</v>
+        <v>557.759521484375</v>
       </c>
       <c r="G281" t="n">
         <v>28.15999984741211</v>
       </c>
       <c r="H281" t="n">
-        <v>338.8959045410156</v>
+        <v>338.8958740234375</v>
       </c>
       <c r="I281" t="n">
         <v>1074.925659179688</v>
@@ -9458,7 +9458,7 @@
         <v>616.2999877929688</v>
       </c>
       <c r="F282" t="n">
-        <v>565.7477416992188</v>
+        <v>565.747802734375</v>
       </c>
       <c r="G282" t="n">
         <v>29.55999946594238</v>
@@ -9490,7 +9490,7 @@
         <v>628.6500244140625</v>
       </c>
       <c r="F283" t="n">
-        <v>567.1689453125</v>
+        <v>567.1690063476562</v>
       </c>
       <c r="G283" t="n">
         <v>31.03000068664551</v>
@@ -9522,13 +9522,13 @@
         <v>597.25</v>
       </c>
       <c r="F284" t="n">
-        <v>568.1981811523438</v>
+        <v>568.1981201171875</v>
       </c>
       <c r="G284" t="n">
         <v>32.58000183105469</v>
       </c>
       <c r="H284" t="n">
-        <v>346.3646850585938</v>
+        <v>346.3647155761719</v>
       </c>
       <c r="I284" t="n">
         <v>921.6858520507812</v>
@@ -9554,7 +9554,7 @@
         <v>567.4000244140625</v>
       </c>
       <c r="F285" t="n">
-        <v>571.6287841796875</v>
+        <v>571.6287231445312</v>
       </c>
       <c r="G285" t="n">
         <v>34.20000076293945</v>
@@ -9563,7 +9563,7 @@
         <v>346.7577819824219</v>
       </c>
       <c r="I285" t="n">
-        <v>875.5990600585938</v>
+        <v>875.5989990234375</v>
       </c>
       <c r="J285" t="n">
         <v>211.1999969482422</v>
@@ -9574,13 +9574,13 @@
         <v>44979</v>
       </c>
       <c r="B286" t="n">
-        <v>1721.386840820312</v>
+        <v>1721.386962890625</v>
       </c>
       <c r="C286" t="n">
         <v>789.2000122070312</v>
       </c>
       <c r="D286" t="n">
-        <v>1402.298461914062</v>
+        <v>1402.298583984375</v>
       </c>
       <c r="E286" t="n">
         <v>539.0499877929688</v>
@@ -9595,7 +9595,7 @@
         <v>329.6090393066406</v>
       </c>
       <c r="I286" t="n">
-        <v>831.8589477539062</v>
+        <v>831.8590087890625</v>
       </c>
       <c r="J286" t="n">
         <v>201.5</v>
@@ -9612,7 +9612,7 @@
         <v>749.75</v>
       </c>
       <c r="D287" t="n">
-        <v>1380.138793945312</v>
+        <v>1380.138916015625</v>
       </c>
       <c r="E287" t="n">
         <v>512.0999755859375</v>
@@ -9624,10 +9624,10 @@
         <v>30.8700008392334</v>
       </c>
       <c r="H287" t="n">
-        <v>331.0831298828125</v>
+        <v>331.0831604003906</v>
       </c>
       <c r="I287" t="n">
-        <v>790.26611328125</v>
+        <v>790.2659912109375</v>
       </c>
       <c r="J287" t="n">
         <v>199.1000061035156</v>
@@ -9638,7 +9638,7 @@
         <v>44981</v>
       </c>
       <c r="B288" t="n">
-        <v>1699.577392578125</v>
+        <v>1699.577514648438</v>
       </c>
       <c r="C288" t="n">
         <v>712.2999877929688</v>
@@ -9650,16 +9650,16 @@
         <v>486.5</v>
       </c>
       <c r="F288" t="n">
-        <v>547.8109130859375</v>
+        <v>547.8108520507812</v>
       </c>
       <c r="G288" t="n">
         <v>29.32999992370605</v>
       </c>
       <c r="H288" t="n">
-        <v>339.2890014648438</v>
+        <v>339.2889709472656</v>
       </c>
       <c r="I288" t="n">
-        <v>750.7702026367188</v>
+        <v>750.770263671875</v>
       </c>
       <c r="J288" t="n">
         <v>190.6000061035156</v>
@@ -9691,7 +9691,7 @@
         <v>324.2040100097656</v>
       </c>
       <c r="I289" t="n">
-        <v>713.271728515625</v>
+        <v>713.2716674804688</v>
       </c>
       <c r="J289" t="n">
         <v>181.1000061035156</v>
@@ -9714,13 +9714,13 @@
         <v>485.2999877929688</v>
       </c>
       <c r="F290" t="n">
-        <v>580.6951904296875</v>
+        <v>580.6952514648438</v>
       </c>
       <c r="G290" t="n">
         <v>29.26000022888184</v>
       </c>
       <c r="H290" t="n">
-        <v>336.1933898925781</v>
+        <v>336.193359375</v>
       </c>
       <c r="I290" t="n">
         <v>677.6205444335938</v>
@@ -9746,7 +9746,7 @@
         <v>509.5499877929688</v>
       </c>
       <c r="F291" t="n">
-        <v>590.1537475585938</v>
+        <v>590.1536865234375</v>
       </c>
       <c r="G291" t="n">
         <v>30.71999931335449</v>
@@ -9755,7 +9755,7 @@
         <v>347.4948120117188</v>
       </c>
       <c r="I291" t="n">
-        <v>710.67529296875</v>
+        <v>710.6752319335938</v>
       </c>
       <c r="J291" t="n">
         <v>199.6499938964844</v>
@@ -9772,7 +9772,7 @@
         <v>708.75</v>
       </c>
       <c r="D292" t="n">
-        <v>1604.3310546875</v>
+        <v>1604.330932617188</v>
       </c>
       <c r="E292" t="n">
         <v>535</v>
@@ -9784,10 +9784,10 @@
         <v>32.25</v>
       </c>
       <c r="H292" t="n">
-        <v>364.2995910644531</v>
+        <v>364.2996215820312</v>
       </c>
       <c r="I292" t="n">
-        <v>743.0807495117188</v>
+        <v>743.080810546875</v>
       </c>
       <c r="J292" t="n">
         <v>209.5500030517578</v>
@@ -9798,28 +9798,28 @@
         <v>44988</v>
       </c>
       <c r="B293" t="n">
-        <v>1860.742553710938</v>
+        <v>1860.742431640625</v>
       </c>
       <c r="C293" t="n">
         <v>744.1500244140625</v>
       </c>
       <c r="D293" t="n">
-        <v>1876.08642578125</v>
+        <v>1876.086547851562</v>
       </c>
       <c r="E293" t="n">
         <v>561.75</v>
       </c>
       <c r="F293" t="n">
-        <v>671.06591796875</v>
+        <v>671.0658569335938</v>
       </c>
       <c r="G293" t="n">
         <v>33.86000061035156</v>
       </c>
       <c r="H293" t="n">
-        <v>385.0844116210938</v>
+        <v>385.0843811035156</v>
       </c>
       <c r="I293" t="n">
-        <v>780.2297973632812</v>
+        <v>780.2298583984375</v>
       </c>
       <c r="J293" t="n">
         <v>220</v>
@@ -9848,10 +9848,10 @@
         <v>35.54999923706055</v>
       </c>
       <c r="H294" t="n">
-        <v>378.843994140625</v>
+        <v>378.8440551757812</v>
       </c>
       <c r="I294" t="n">
-        <v>819.226318359375</v>
+        <v>819.2263793945312</v>
       </c>
       <c r="J294" t="n">
         <v>230.8000030517578</v>
@@ -9874,7 +9874,7 @@
         <v>619.25</v>
       </c>
       <c r="F295" t="n">
-        <v>697.9222412109375</v>
+        <v>697.9221801757812</v>
       </c>
       <c r="G295" t="n">
         <v>37.31999969482422</v>
@@ -9906,13 +9906,13 @@
         <v>650.2000122070312</v>
       </c>
       <c r="F296" t="n">
-        <v>683.4158325195312</v>
+        <v>683.415771484375</v>
       </c>
       <c r="G296" t="n">
         <v>39.18000030517578</v>
       </c>
       <c r="H296" t="n">
-        <v>378.0578918457031</v>
+        <v>378.057861328125</v>
       </c>
       <c r="I296" t="n">
         <v>903.1612548828125</v>
@@ -9926,13 +9926,13 @@
         <v>44995</v>
       </c>
       <c r="B297" t="n">
-        <v>1814.421630859375</v>
+        <v>1814.421508789062</v>
       </c>
       <c r="C297" t="n">
         <v>904.4500122070312</v>
       </c>
       <c r="D297" t="n">
-        <v>1892.756103515625</v>
+        <v>1892.755981445312</v>
       </c>
       <c r="E297" t="n">
         <v>682.7000122070312</v>
@@ -9947,7 +9947,7 @@
         <v>371.8174743652344</v>
       </c>
       <c r="I297" t="n">
-        <v>948.2993774414062</v>
+        <v>948.29931640625</v>
       </c>
       <c r="J297" t="n">
         <v>233.8999938964844</v>
@@ -9970,13 +9970,13 @@
         <v>716.7999877929688</v>
       </c>
       <c r="F298" t="n">
-        <v>667.6842651367188</v>
+        <v>667.684326171875</v>
       </c>
       <c r="G298" t="n">
         <v>43.02000045776367</v>
       </c>
       <c r="H298" t="n">
-        <v>361.6462097167969</v>
+        <v>361.6461791992188</v>
       </c>
       <c r="I298" t="n">
         <v>995.6842651367188</v>
@@ -9990,13 +9990,13 @@
         <v>44999</v>
       </c>
       <c r="B299" t="n">
-        <v>1707.82958984375</v>
+        <v>1707.829711914062</v>
       </c>
       <c r="C299" t="n">
         <v>902.2000122070312</v>
       </c>
       <c r="D299" t="n">
-        <v>1735.043090820312</v>
+        <v>1735.043212890625</v>
       </c>
       <c r="E299" t="n">
         <v>706.0999755859375</v>
@@ -10022,7 +10022,7 @@
         <v>45000</v>
       </c>
       <c r="B300" t="n">
-        <v>1709.401611328125</v>
+        <v>1709.401489257812</v>
       </c>
       <c r="C300" t="n">
         <v>928.3499755859375</v>
@@ -10034,7 +10034,7 @@
         <v>740.4000244140625</v>
       </c>
       <c r="F300" t="n">
-        <v>665.8710327148438</v>
+        <v>665.8709716796875</v>
       </c>
       <c r="G300" t="n">
         <v>40.36000061035156</v>
@@ -10043,7 +10043,7 @@
         <v>358.8453674316406</v>
       </c>
       <c r="I300" t="n">
-        <v>918.5900268554688</v>
+        <v>918.590087890625</v>
       </c>
       <c r="J300" t="n">
         <v>213.3000030517578</v>
@@ -10060,7 +10060,7 @@
         <v>973.7000122070312</v>
       </c>
       <c r="D301" t="n">
-        <v>1840.451538085938</v>
+        <v>1840.451416015625</v>
       </c>
       <c r="E301" t="n">
         <v>777.4000244140625</v>
@@ -10072,10 +10072,10 @@
         <v>39.7400016784668</v>
       </c>
       <c r="H301" t="n">
-        <v>372.2597351074219</v>
+        <v>372.2596740722656</v>
       </c>
       <c r="I301" t="n">
-        <v>887.1832275390625</v>
+        <v>887.1831665039062</v>
       </c>
       <c r="J301" t="n">
         <v>209.1000061035156</v>
@@ -10092,19 +10092,19 @@
         <v>1022.349975585938</v>
       </c>
       <c r="D302" t="n">
-        <v>1873.141967773438</v>
+        <v>1873.141845703125</v>
       </c>
       <c r="E302" t="n">
         <v>816.25</v>
       </c>
       <c r="F302" t="n">
-        <v>666.8511352539062</v>
+        <v>666.85107421875</v>
       </c>
       <c r="G302" t="n">
         <v>39.9900016784668</v>
       </c>
       <c r="H302" t="n">
-        <v>371.9157409667969</v>
+        <v>371.915771484375</v>
       </c>
       <c r="I302" t="n">
         <v>896.5203247070312</v>
@@ -10118,13 +10118,13 @@
         <v>45005</v>
       </c>
       <c r="B303" t="n">
-        <v>1665.7822265625</v>
+        <v>1665.782348632812</v>
       </c>
       <c r="C303" t="n">
         <v>1009.099975585938</v>
       </c>
       <c r="D303" t="n">
-        <v>1801.671875</v>
+        <v>1801.671752929688</v>
       </c>
       <c r="E303" t="n">
         <v>848.6500244140625</v>
@@ -10136,7 +10136,7 @@
         <v>38.04000091552734</v>
       </c>
       <c r="H303" t="n">
-        <v>359.0910339355469</v>
+        <v>359.091064453125</v>
       </c>
       <c r="I303" t="n">
         <v>851.7318115234375</v>
@@ -10156,22 +10156,22 @@
         <v>1006.099975585938</v>
       </c>
       <c r="D304" t="n">
-        <v>1820.936767578125</v>
+        <v>1820.936889648438</v>
       </c>
       <c r="E304" t="n">
         <v>891.0499877929688</v>
       </c>
       <c r="F304" t="n">
-        <v>651.6096801757812</v>
+        <v>651.6097412109375</v>
       </c>
       <c r="G304" t="n">
         <v>39.93999862670898</v>
       </c>
       <c r="H304" t="n">
-        <v>364.49609375</v>
+        <v>364.4961242675781</v>
       </c>
       <c r="I304" t="n">
-        <v>889.5797729492188</v>
+        <v>889.579833984375</v>
       </c>
       <c r="J304" t="n">
         <v>198.5500030517578</v>
@@ -10188,13 +10188,13 @@
         <v>1032.800048828125</v>
       </c>
       <c r="D305" t="n">
-        <v>1812.102905273438</v>
+        <v>1812.10302734375</v>
       </c>
       <c r="E305" t="n">
         <v>935.5999755859375</v>
       </c>
       <c r="F305" t="n">
-        <v>644.111572265625</v>
+        <v>644.1115112304688</v>
       </c>
       <c r="G305" t="n">
         <v>40.81000137329102</v>
@@ -10203,7 +10203,7 @@
         <v>369.0658264160156</v>
       </c>
       <c r="I305" t="n">
-        <v>934.0189208984375</v>
+        <v>934.0188598632812</v>
       </c>
       <c r="J305" t="n">
         <v>200.3999938964844</v>
@@ -10220,19 +10220,19 @@
         <v>1084.400024414062</v>
       </c>
       <c r="D306" t="n">
-        <v>1790.741821289062</v>
+        <v>1790.74169921875</v>
       </c>
       <c r="E306" t="n">
         <v>982.3499755859375</v>
       </c>
       <c r="F306" t="n">
-        <v>641.9551391601562</v>
+        <v>641.955078125</v>
       </c>
       <c r="G306" t="n">
         <v>40.27999877929688</v>
       </c>
       <c r="H306" t="n">
-        <v>365.7245483398438</v>
+        <v>365.7244873046875</v>
       </c>
       <c r="I306" t="n">
         <v>980.704833984375</v>
@@ -10246,7 +10246,7 @@
         <v>45009</v>
       </c>
       <c r="B307" t="n">
-        <v>1670.939819335938</v>
+        <v>1670.93994140625</v>
       </c>
       <c r="C307" t="n">
         <v>1124.550048828125</v>
@@ -10258,16 +10258,16 @@
         <v>1029.349975585938</v>
       </c>
       <c r="F307" t="n">
-        <v>625.3414306640625</v>
+        <v>625.3413696289062</v>
       </c>
       <c r="G307" t="n">
         <v>38.52000045776367</v>
       </c>
       <c r="H307" t="n">
-        <v>365.3805541992188</v>
+        <v>365.3805847167969</v>
       </c>
       <c r="I307" t="n">
-        <v>1006.070129394531</v>
+        <v>1006.070068359375</v>
       </c>
       <c r="J307" t="n">
         <v>192.1000061035156</v>
@@ -10290,16 +10290,16 @@
         <v>984.9000244140625</v>
       </c>
       <c r="F308" t="n">
-        <v>616.6179809570312</v>
+        <v>616.6180419921875</v>
       </c>
       <c r="G308" t="n">
         <v>36.59999847412109</v>
       </c>
       <c r="H308" t="n">
-        <v>363.6116333007812</v>
+        <v>363.6116638183594</v>
       </c>
       <c r="I308" t="n">
-        <v>956.5379638671875</v>
+        <v>956.5380249023438</v>
       </c>
       <c r="J308" t="n">
         <v>182.9499969482422</v>
@@ -10310,7 +10310,7 @@
         <v>45013</v>
       </c>
       <c r="B309" t="n">
-        <v>1585.568115234375</v>
+        <v>1585.568237304688</v>
       </c>
       <c r="C309" t="n">
         <v>1015</v>
@@ -10328,7 +10328,7 @@
         <v>34.77000045776367</v>
       </c>
       <c r="H309" t="n">
-        <v>352.7524719238281</v>
+        <v>352.75244140625</v>
       </c>
       <c r="I309" t="n">
         <v>908.70361328125</v>
@@ -10354,7 +10354,7 @@
         <v>894.3499755859375</v>
       </c>
       <c r="F310" t="n">
-        <v>624.0182495117188</v>
+        <v>624.0181884765625</v>
       </c>
       <c r="G310" t="n">
         <v>36.5</v>
@@ -10392,10 +10392,10 @@
         <v>38.31999969482422</v>
       </c>
       <c r="H311" t="n">
-        <v>359.2384948730469</v>
+        <v>359.2384643554688</v>
       </c>
       <c r="I311" t="n">
-        <v>866.5614624023438</v>
+        <v>866.5614013671875</v>
       </c>
       <c r="J311" t="n">
         <v>191.6999969482422</v>
@@ -10424,7 +10424,7 @@
         <v>38.11000061035156</v>
       </c>
       <c r="H312" t="n">
-        <v>368.3287353515625</v>
+        <v>368.3287658691406</v>
       </c>
       <c r="I312" t="n">
         <v>844.1920776367188</v>
@@ -10456,7 +10456,7 @@
         <v>38.02000045776367</v>
       </c>
       <c r="H313" t="n">
-        <v>373.3898620605469</v>
+        <v>373.389892578125</v>
       </c>
       <c r="I313" t="n">
         <v>820.8241577148438</v>
@@ -10488,10 +10488,10 @@
         <v>38.43999862670898</v>
       </c>
       <c r="H314" t="n">
-        <v>376.9768371582031</v>
+        <v>376.9768676757812</v>
       </c>
       <c r="I314" t="n">
-        <v>861.8179931640625</v>
+        <v>861.8179321289062</v>
       </c>
       <c r="J314" t="n">
         <v>194.3999938964844</v>
@@ -10502,13 +10502,13 @@
         <v>45026</v>
       </c>
       <c r="B315" t="n">
-        <v>1710.334716796875</v>
+        <v>1710.334594726562</v>
       </c>
       <c r="C315" t="n">
         <v>1000.849975585938</v>
       </c>
       <c r="D315" t="n">
-        <v>1793.98583984375</v>
+        <v>1793.985961914062</v>
       </c>
       <c r="E315" t="n">
         <v>899.1500244140625</v>
@@ -10520,10 +10520,10 @@
         <v>38.79999923706055</v>
       </c>
       <c r="H315" t="n">
-        <v>377.7138671875</v>
+        <v>377.7138977050781</v>
       </c>
       <c r="I315" t="n">
-        <v>904.9088745117188</v>
+        <v>904.9088134765625</v>
       </c>
       <c r="J315" t="n">
         <v>195.25</v>
@@ -10546,7 +10546,7 @@
         <v>944.0999755859375</v>
       </c>
       <c r="F316" t="n">
-        <v>640.9750366210938</v>
+        <v>640.9749755859375</v>
       </c>
       <c r="G316" t="n">
         <v>38.79999923706055</v>
@@ -10587,7 +10587,7 @@
         <v>389.2118835449219</v>
       </c>
       <c r="I317" t="n">
-        <v>937.56396484375</v>
+        <v>937.5640258789062</v>
       </c>
       <c r="J317" t="n">
         <v>187</v>
@@ -10598,7 +10598,7 @@
         <v>45029</v>
       </c>
       <c r="B318" t="n">
-        <v>1736.467041015625</v>
+        <v>1736.467163085938</v>
       </c>
       <c r="C318" t="n">
         <v>1030.849975585938</v>
@@ -10616,10 +10616,10 @@
         <v>37.83000183105469</v>
       </c>
       <c r="H318" t="n">
-        <v>385.8705749511719</v>
+        <v>385.87060546875</v>
       </c>
       <c r="I318" t="n">
-        <v>912.8978271484375</v>
+        <v>912.8978881835938</v>
       </c>
       <c r="J318" t="n">
         <v>191.6000061035156</v>
@@ -10630,7 +10630,7 @@
         <v>45033</v>
       </c>
       <c r="B319" t="n">
-        <v>1752.971557617188</v>
+        <v>1752.971435546875</v>
       </c>
       <c r="C319" t="n">
         <v>1039.5</v>
@@ -10642,7 +10642,7 @@
         <v>962.5499877929688</v>
       </c>
       <c r="F319" t="n">
-        <v>651.5116577148438</v>
+        <v>651.51171875</v>
       </c>
       <c r="G319" t="n">
         <v>37.88999938964844</v>
@@ -10651,7 +10651,7 @@
         <v>384.78955078125</v>
       </c>
       <c r="I319" t="n">
-        <v>945.503173828125</v>
+        <v>945.5031127929688</v>
       </c>
       <c r="J319" t="n">
         <v>188.1999969482422</v>
@@ -10662,13 +10662,13 @@
         <v>45034</v>
       </c>
       <c r="B320" t="n">
-        <v>1729.148071289062</v>
+        <v>1729.14794921875</v>
       </c>
       <c r="C320" t="n">
         <v>1032.050048828125</v>
       </c>
       <c r="D320" t="n">
-        <v>1847.588256835938</v>
+        <v>1847.58837890625</v>
       </c>
       <c r="E320" t="n">
         <v>952.25</v>
@@ -10680,10 +10680,10 @@
         <v>37.66999816894531</v>
       </c>
       <c r="H320" t="n">
-        <v>376.4363098144531</v>
+        <v>376.4363403320312</v>
       </c>
       <c r="I320" t="n">
-        <v>946.7513427734375</v>
+        <v>946.75146484375</v>
       </c>
       <c r="J320" t="n">
         <v>187.1000061035156</v>
@@ -10700,7 +10700,7 @@
         <v>1017.700012207031</v>
       </c>
       <c r="D321" t="n">
-        <v>1850.483154296875</v>
+        <v>1850.483032226562</v>
       </c>
       <c r="E321" t="n">
         <v>935.7999877929688</v>
@@ -10726,25 +10726,25 @@
         <v>45036</v>
       </c>
       <c r="B322" t="n">
-        <v>1707.534790039062</v>
+        <v>1707.534912109375</v>
       </c>
       <c r="C322" t="n">
         <v>1011.099975585938</v>
       </c>
       <c r="D322" t="n">
-        <v>1839.552978515625</v>
+        <v>1839.553100585938</v>
       </c>
       <c r="E322" t="n">
         <v>933.0499877929688</v>
       </c>
       <c r="F322" t="n">
-        <v>652.8838500976562</v>
+        <v>652.8839111328125</v>
       </c>
       <c r="G322" t="n">
         <v>39.15999984741211</v>
       </c>
       <c r="H322" t="n">
-        <v>374.1268920898438</v>
+        <v>374.1269226074219</v>
       </c>
       <c r="I322" t="n">
         <v>926.9286499023438</v>
@@ -10776,7 +10776,7 @@
         <v>39.84999847412109</v>
       </c>
       <c r="H323" t="n">
-        <v>368.6236267089844</v>
+        <v>368.6235961914062</v>
       </c>
       <c r="I323" t="n">
         <v>916.5427856445312</v>
@@ -10790,19 +10790,19 @@
         <v>45040</v>
       </c>
       <c r="B324" t="n">
-        <v>1704.1455078125</v>
+        <v>1704.145629882812</v>
       </c>
       <c r="C324" t="n">
         <v>965.0999755859375</v>
       </c>
       <c r="D324" t="n">
-        <v>1798.677368164062</v>
+        <v>1798.67724609375</v>
       </c>
       <c r="E324" t="n">
         <v>887.0999755859375</v>
       </c>
       <c r="F324" t="n">
-        <v>657.980712890625</v>
+        <v>657.9807739257812</v>
       </c>
       <c r="G324" t="n">
         <v>40.27999877929688</v>
@@ -10828,22 +10828,22 @@
         <v>1012.950012207031</v>
       </c>
       <c r="D325" t="n">
-        <v>1841.25</v>
+        <v>1841.249877929688</v>
       </c>
       <c r="E325" t="n">
         <v>931.1500244140625</v>
       </c>
       <c r="F325" t="n">
-        <v>658.1277465820312</v>
+        <v>658.1278076171875</v>
       </c>
       <c r="G325" t="n">
         <v>41.13000106811523</v>
       </c>
       <c r="H325" t="n">
-        <v>375.8958129882812</v>
+        <v>375.8958435058594</v>
       </c>
       <c r="I325" t="n">
-        <v>933.968994140625</v>
+        <v>933.9689331054688</v>
       </c>
       <c r="J325" t="n">
         <v>182.8000030517578</v>
@@ -10860,19 +10860,19 @@
         <v>987.7999877929688</v>
       </c>
       <c r="D326" t="n">
-        <v>1844.544067382812</v>
+        <v>1844.5439453125</v>
       </c>
       <c r="E326" t="n">
         <v>924.5999755859375</v>
       </c>
       <c r="F326" t="n">
-        <v>651.5116577148438</v>
+        <v>651.51171875</v>
       </c>
       <c r="G326" t="n">
         <v>42.27000045776367</v>
       </c>
       <c r="H326" t="n">
-        <v>379.7776184082031</v>
+        <v>379.7776489257812</v>
       </c>
       <c r="I326" t="n">
         <v>918.789794921875</v>
@@ -10886,13 +10886,13 @@
         <v>45043</v>
       </c>
       <c r="B327" t="n">
-        <v>1720.060668945312</v>
+        <v>1720.060791015625</v>
       </c>
       <c r="C327" t="n">
         <v>982.2999877929688</v>
       </c>
       <c r="D327" t="n">
-        <v>1849.6845703125</v>
+        <v>1849.684448242188</v>
       </c>
       <c r="E327" t="n">
         <v>917.0499877929688</v>
@@ -10924,13 +10924,13 @@
         <v>1029.449951171875</v>
       </c>
       <c r="D328" t="n">
-        <v>1921.453979492188</v>
+        <v>1921.453857421875</v>
       </c>
       <c r="E328" t="n">
         <v>951</v>
       </c>
       <c r="F328" t="n">
-        <v>667.7822265625</v>
+        <v>667.7823486328125</v>
       </c>
       <c r="G328" t="n">
         <v>44.97000122070312</v>
@@ -10939,7 +10939,7 @@
         <v>389.6541137695312</v>
       </c>
       <c r="I328" t="n">
-        <v>943.7056884765625</v>
+        <v>943.7056274414062</v>
       </c>
       <c r="J328" t="n">
         <v>189.5500030517578</v>
@@ -10950,13 +10950,13 @@
         <v>45048</v>
       </c>
       <c r="B329" t="n">
-        <v>1733.126831054688</v>
+        <v>1733.126708984375</v>
       </c>
       <c r="C329" t="n">
         <v>1021.950012207031</v>
       </c>
       <c r="D329" t="n">
-        <v>1916.363037109375</v>
+        <v>1916.363159179688</v>
       </c>
       <c r="E329" t="n">
         <v>974.6500244140625</v>
@@ -10982,7 +10982,7 @@
         <v>45049</v>
       </c>
       <c r="B330" t="n">
-        <v>1712.938354492188</v>
+        <v>1712.938232421875</v>
       </c>
       <c r="C330" t="n">
         <v>993.0499877929688</v>
@@ -11000,7 +11000,7 @@
         <v>46.33000183105469</v>
       </c>
       <c r="H330" t="n">
-        <v>377.0260009765625</v>
+        <v>377.0259704589844</v>
       </c>
       <c r="I330" t="n">
         <v>921.6858520507812</v>
@@ -11026,16 +11026,16 @@
         <v>945.5499877929688</v>
       </c>
       <c r="F331" t="n">
-        <v>666.2630615234375</v>
+        <v>666.2631225585938</v>
       </c>
       <c r="G331" t="n">
         <v>47.63000106811523</v>
       </c>
       <c r="H331" t="n">
-        <v>381.595703125</v>
+        <v>381.5956726074219</v>
       </c>
       <c r="I331" t="n">
-        <v>928.9259643554688</v>
+        <v>928.9259033203125</v>
       </c>
       <c r="J331" t="n">
         <v>183.3500061035156</v>
@@ -11064,7 +11064,7 @@
         <v>47.97000122070312</v>
       </c>
       <c r="H332" t="n">
-        <v>393.6341857910156</v>
+        <v>393.6342163085938</v>
       </c>
       <c r="I332" t="n">
         <v>917.54150390625</v>
@@ -11084,7 +11084,7 @@
         <v>949.0499877929688</v>
       </c>
       <c r="D333" t="n">
-        <v>1884.072143554688</v>
+        <v>1884.072021484375</v>
       </c>
       <c r="E333" t="n">
         <v>917.2999877929688</v>
@@ -11110,13 +11110,13 @@
         <v>45055</v>
       </c>
       <c r="B334" t="n">
-        <v>1728.3623046875</v>
+        <v>1728.362182617188</v>
       </c>
       <c r="C334" t="n">
         <v>901.5999755859375</v>
       </c>
       <c r="D334" t="n">
-        <v>1892.65625</v>
+        <v>1892.656372070312</v>
       </c>
       <c r="E334" t="n">
         <v>903.1500244140625</v>
@@ -11128,7 +11128,7 @@
         <v>48.06000137329102</v>
       </c>
       <c r="H334" t="n">
-        <v>398.6461181640625</v>
+        <v>398.6461486816406</v>
       </c>
       <c r="I334" t="n">
         <v>843.9423828125</v>
@@ -11142,13 +11142,13 @@
         <v>45056</v>
       </c>
       <c r="B335" t="n">
-        <v>1720.355346679688</v>
+        <v>1720.35546875</v>
       </c>
       <c r="C335" t="n">
         <v>890.6500244140625</v>
       </c>
       <c r="D335" t="n">
-        <v>1888.713623046875</v>
+        <v>1888.713500976562</v>
       </c>
       <c r="E335" t="n">
         <v>902.3499755859375</v>
@@ -11163,7 +11163,7 @@
         <v>401.2503662109375</v>
       </c>
       <c r="I335" t="n">
-        <v>834.9547729492188</v>
+        <v>834.9547119140625</v>
       </c>
       <c r="J335" t="n">
         <v>179.3500061035156</v>
@@ -11174,19 +11174,19 @@
         <v>45057</v>
       </c>
       <c r="B336" t="n">
-        <v>1754.739868164062</v>
+        <v>1754.739990234375</v>
       </c>
       <c r="C336" t="n">
         <v>917.25</v>
       </c>
       <c r="D336" t="n">
-        <v>1981.045532226562</v>
+        <v>1981.045654296875</v>
       </c>
       <c r="E336" t="n">
         <v>913.5499877929688</v>
       </c>
       <c r="F336" t="n">
-        <v>694.736572265625</v>
+        <v>694.7366943359375</v>
       </c>
       <c r="G336" t="n">
         <v>48.52999877929688</v>
@@ -11206,19 +11206,19 @@
         <v>45058</v>
       </c>
       <c r="B337" t="n">
-        <v>1766.381469726562</v>
+        <v>1766.381591796875</v>
       </c>
       <c r="C337" t="n">
         <v>884.7999877929688</v>
       </c>
       <c r="D337" t="n">
-        <v>1961.131713867188</v>
+        <v>1961.1318359375</v>
       </c>
       <c r="E337" t="n">
         <v>895.5999755859375</v>
       </c>
       <c r="F337" t="n">
-        <v>686.1112670898438</v>
+        <v>686.1113891601562</v>
       </c>
       <c r="G337" t="n">
         <v>48.16999816894531</v>
@@ -11244,7 +11244,7 @@
         <v>840.5999755859375</v>
       </c>
       <c r="D338" t="n">
-        <v>1912.570068359375</v>
+        <v>1912.570190429688</v>
       </c>
       <c r="E338" t="n">
         <v>868.7000122070312</v>
@@ -11256,10 +11256,10 @@
         <v>47.16999816894531</v>
       </c>
       <c r="H338" t="n">
-        <v>399.5797424316406</v>
+        <v>399.5797119140625</v>
       </c>
       <c r="I338" t="n">
-        <v>776.3850708007812</v>
+        <v>776.3851318359375</v>
       </c>
       <c r="J338" t="n">
         <v>178.6000061035156</v>
@@ -11276,7 +11276,7 @@
         <v>812.0999755859375</v>
       </c>
       <c r="D339" t="n">
-        <v>1885.719116210938</v>
+        <v>1885.718994140625</v>
       </c>
       <c r="E339" t="n">
         <v>874.1500244140625</v>
@@ -11308,7 +11308,7 @@
         <v>790</v>
       </c>
       <c r="D340" t="n">
-        <v>1896.050170898438</v>
+        <v>1896.050048828125</v>
       </c>
       <c r="E340" t="n">
         <v>875.4000244140625</v>
@@ -11320,10 +11320,10 @@
         <v>46.86999893188477</v>
       </c>
       <c r="H340" t="n">
-        <v>399.284912109375</v>
+        <v>399.2848815917969</v>
       </c>
       <c r="I340" t="n">
-        <v>700.7388305664062</v>
+        <v>700.7388916015625</v>
       </c>
       <c r="J340" t="n">
         <v>173</v>
@@ -11340,7 +11340,7 @@
         <v>751.5999755859375</v>
       </c>
       <c r="D341" t="n">
-        <v>1886.567504882812</v>
+        <v>1886.5673828125</v>
       </c>
       <c r="E341" t="n">
         <v>860.5499877929688</v>
@@ -11372,19 +11372,19 @@
         <v>787.3499755859375</v>
       </c>
       <c r="D342" t="n">
-        <v>1952.49755859375</v>
+        <v>1952.497436523438</v>
       </c>
       <c r="E342" t="n">
         <v>896.9500122070312</v>
       </c>
       <c r="F342" t="n">
-        <v>674.4473876953125</v>
+        <v>674.4473266601562</v>
       </c>
       <c r="G342" t="n">
         <v>47.22000122070312</v>
       </c>
       <c r="H342" t="n">
-        <v>396.1892700195312</v>
+        <v>396.1893005371094</v>
       </c>
       <c r="I342" t="n">
         <v>687.157470703125</v>
@@ -11410,7 +11410,7 @@
         <v>941.75</v>
       </c>
       <c r="F343" t="n">
-        <v>715.2220458984375</v>
+        <v>715.2219848632812</v>
       </c>
       <c r="G343" t="n">
         <v>49.58000183105469</v>
@@ -11419,7 +11419,7 @@
         <v>416.5810241699219</v>
       </c>
       <c r="I343" t="n">
-        <v>721.5103149414062</v>
+        <v>721.5103759765625</v>
       </c>
       <c r="J343" t="n">
         <v>186.9499969482422</v>
@@ -11451,7 +11451,7 @@
         <v>419.9223327636719</v>
       </c>
       <c r="I344" t="n">
-        <v>757.5609130859375</v>
+        <v>757.5609741210938</v>
       </c>
       <c r="J344" t="n">
         <v>196.25</v>
@@ -11468,19 +11468,19 @@
         <v>911.4000244140625</v>
       </c>
       <c r="D345" t="n">
-        <v>2471.103759765625</v>
+        <v>2471.10400390625</v>
       </c>
       <c r="E345" t="n">
         <v>984.25</v>
       </c>
       <c r="F345" t="n">
-        <v>703.9991455078125</v>
+        <v>703.9992065429688</v>
       </c>
       <c r="G345" t="n">
         <v>51.20999908447266</v>
       </c>
       <c r="H345" t="n">
-        <v>415.0086364746094</v>
+        <v>415.0086669921875</v>
       </c>
       <c r="I345" t="n">
         <v>795.4089965820312</v>
@@ -11506,13 +11506,13 @@
         <v>970.6500244140625</v>
       </c>
       <c r="F346" t="n">
-        <v>710.1251831054688</v>
+        <v>710.1251220703125</v>
       </c>
       <c r="G346" t="n">
         <v>51.83000183105469</v>
       </c>
       <c r="H346" t="n">
-        <v>411.962158203125</v>
+        <v>411.9621887207031</v>
       </c>
       <c r="I346" t="n">
         <v>795.3092041015625</v>
@@ -11526,7 +11526,7 @@
         <v>45072</v>
       </c>
       <c r="B347" t="n">
-        <v>1753.610229492188</v>
+        <v>1753.610107421875</v>
       </c>
       <c r="C347" t="n">
         <v>850.0999755859375</v>
@@ -11538,13 +11538,13 @@
         <v>963.3499755859375</v>
       </c>
       <c r="F347" t="n">
-        <v>712.4285278320312</v>
+        <v>712.4285888671875</v>
       </c>
       <c r="G347" t="n">
         <v>51.61000061035156</v>
       </c>
       <c r="H347" t="n">
-        <v>417.2197875976562</v>
+        <v>417.2197570800781</v>
       </c>
       <c r="I347" t="n">
         <v>759.6580810546875</v>
@@ -11558,7 +11558,7 @@
         <v>45075</v>
       </c>
       <c r="B348" t="n">
-        <v>1762.844848632812</v>
+        <v>1762.844970703125</v>
       </c>
       <c r="C348" t="n">
         <v>832.2000122070312</v>
@@ -11579,7 +11579,7 @@
         <v>419.6275024414062</v>
       </c>
       <c r="I348" t="n">
-        <v>728.2012329101562</v>
+        <v>728.201171875</v>
       </c>
       <c r="J348" t="n">
         <v>238.5</v>
@@ -11590,7 +11590,7 @@
         <v>45076</v>
       </c>
       <c r="B349" t="n">
-        <v>1766.774536132812</v>
+        <v>1766.774658203125</v>
       </c>
       <c r="C349" t="n">
         <v>804.2999877929688</v>
@@ -11611,7 +11611,7 @@
         <v>423.4601745605469</v>
       </c>
       <c r="I349" t="n">
-        <v>697.0938110351562</v>
+        <v>697.0938720703125</v>
       </c>
       <c r="J349" t="n">
         <v>250.3999938964844</v>
@@ -11640,7 +11640,7 @@
         <v>49.93000030517578</v>
       </c>
       <c r="H350" t="n">
-        <v>416.2862243652344</v>
+        <v>416.2861938476562</v>
       </c>
       <c r="I350" t="n">
         <v>663.2403564453125</v>
@@ -11666,16 +11666,16 @@
         <v>993.9500122070312</v>
       </c>
       <c r="F351" t="n">
-        <v>717.5253295898438</v>
+        <v>717.525390625</v>
       </c>
       <c r="G351" t="n">
         <v>50.83000183105469</v>
       </c>
       <c r="H351" t="n">
-        <v>421.838623046875</v>
+        <v>421.8386535644531</v>
       </c>
       <c r="I351" t="n">
-        <v>693.3989868164062</v>
+        <v>693.3988647460938</v>
       </c>
       <c r="J351" t="n">
         <v>241</v>
@@ -11730,16 +11730,16 @@
         <v>987.8499755859375</v>
       </c>
       <c r="F353" t="n">
-        <v>724.1414794921875</v>
+        <v>724.1414184570312</v>
       </c>
       <c r="G353" t="n">
         <v>51.88999938964844</v>
       </c>
       <c r="H353" t="n">
-        <v>431.4694519042969</v>
+        <v>431.469482421875</v>
       </c>
       <c r="I353" t="n">
-        <v>680.5665283203125</v>
+        <v>680.5665893554688</v>
       </c>
       <c r="J353" t="n">
         <v>238.8999938964844</v>
@@ -11762,16 +11762,16 @@
         <v>991.8499755859375</v>
       </c>
       <c r="F354" t="n">
-        <v>730.6105346679688</v>
+        <v>730.6104736328125</v>
       </c>
       <c r="G354" t="n">
         <v>52.59999847412109</v>
       </c>
       <c r="H354" t="n">
-        <v>451.2223815917969</v>
+        <v>451.2224426269531</v>
       </c>
       <c r="I354" t="n">
-        <v>677.4708251953125</v>
+        <v>677.4707641601562</v>
       </c>
       <c r="J354" t="n">
         <v>236.3000030517578</v>
@@ -11794,13 +11794,13 @@
         <v>985.5499877929688</v>
       </c>
       <c r="F355" t="n">
-        <v>728.9931640625</v>
+        <v>728.9932250976562</v>
       </c>
       <c r="G355" t="n">
         <v>54.97000122070312</v>
       </c>
       <c r="H355" t="n">
-        <v>447.8811340332031</v>
+        <v>447.881103515625</v>
       </c>
       <c r="I355" t="n">
         <v>679.1185302734375</v>
@@ -11826,7 +11826,7 @@
         <v>976</v>
       </c>
       <c r="F356" t="n">
-        <v>721.7891845703125</v>
+        <v>721.7891235351562</v>
       </c>
       <c r="G356" t="n">
         <v>55.83000183105469</v>
@@ -11846,7 +11846,7 @@
         <v>45086</v>
       </c>
       <c r="B357" t="n">
-        <v>1804.990600585938</v>
+        <v>1804.990478515625</v>
       </c>
       <c r="C357" t="n">
         <v>830.7000122070312</v>
@@ -11858,13 +11858,13 @@
         <v>963.6500244140625</v>
       </c>
       <c r="F357" t="n">
-        <v>720.3678588867188</v>
+        <v>720.3677978515625</v>
       </c>
       <c r="G357" t="n">
         <v>55.2400016784668</v>
       </c>
       <c r="H357" t="n">
-        <v>447.83203125</v>
+        <v>447.8320007324219</v>
       </c>
       <c r="I357" t="n">
         <v>668.1834716796875</v>
@@ -11878,7 +11878,7 @@
         <v>45089</v>
       </c>
       <c r="B358" t="n">
-        <v>1806.218505859375</v>
+        <v>1806.218627929688</v>
       </c>
       <c r="C358" t="n">
         <v>830.4000244140625</v>
@@ -11896,10 +11896,10 @@
         <v>54.31000137329102</v>
       </c>
       <c r="H358" t="n">
-        <v>448.4215698242188</v>
+        <v>448.4216003417969</v>
       </c>
       <c r="I358" t="n">
-        <v>669.2820434570312</v>
+        <v>669.281982421875</v>
       </c>
       <c r="J358" t="n">
         <v>228.5500030517578</v>
@@ -11928,10 +11928,10 @@
         <v>53.56000137329102</v>
       </c>
       <c r="H359" t="n">
-        <v>451.0258483886719</v>
+        <v>451.02587890625</v>
       </c>
       <c r="I359" t="n">
-        <v>662.24169921875</v>
+        <v>662.2416381835938</v>
       </c>
       <c r="J359" t="n">
         <v>239.9499969482422</v>
@@ -11954,16 +11954,16 @@
         <v>957.6500244140625</v>
       </c>
       <c r="F360" t="n">
-        <v>724.6805419921875</v>
+        <v>724.6804809570312</v>
       </c>
       <c r="G360" t="n">
         <v>53.04999923706055</v>
       </c>
       <c r="H360" t="n">
-        <v>456.5783386230469</v>
+        <v>456.5783081054688</v>
       </c>
       <c r="I360" t="n">
-        <v>653.4536743164062</v>
+        <v>653.4537353515625</v>
       </c>
       <c r="J360" t="n">
         <v>245.25</v>
@@ -11980,7 +11980,7 @@
         <v>814.7000122070312</v>
       </c>
       <c r="D361" t="n">
-        <v>2481.135498046875</v>
+        <v>2481.1357421875</v>
       </c>
       <c r="E361" t="n">
         <v>962.5999755859375</v>
@@ -11992,7 +11992,7 @@
         <v>53.84999847412109</v>
       </c>
       <c r="H361" t="n">
-        <v>450.4362487792969</v>
+        <v>450.4361877441406</v>
       </c>
       <c r="I361" t="n">
         <v>668.1834716796875</v>
@@ -12018,13 +12018,13 @@
         <v>975.0499877929688</v>
       </c>
       <c r="F362" t="n">
-        <v>732.57080078125</v>
+        <v>732.5708618164062</v>
       </c>
       <c r="G362" t="n">
         <v>53.22000122070312</v>
       </c>
       <c r="H362" t="n">
-        <v>452.9421997070312</v>
+        <v>452.9421691894531</v>
       </c>
       <c r="I362" t="n">
         <v>670.33056640625</v>
@@ -12038,7 +12038,7 @@
         <v>45096</v>
       </c>
       <c r="B363" t="n">
-        <v>1793.299682617188</v>
+        <v>1793.2998046875</v>
       </c>
       <c r="C363" t="n">
         <v>806.5999755859375</v>
@@ -12050,7 +12050,7 @@
         <v>960.3499755859375</v>
       </c>
       <c r="F363" t="n">
-        <v>721.0540161132812</v>
+        <v>721.053955078125</v>
       </c>
       <c r="G363" t="n">
         <v>52.72999954223633</v>
@@ -12059,7 +12059,7 @@
         <v>445.0311889648438</v>
       </c>
       <c r="I363" t="n">
-        <v>656.6493530273438</v>
+        <v>656.6492919921875</v>
       </c>
       <c r="J363" t="n">
         <v>232.3999938964844</v>
@@ -12070,7 +12070,7 @@
         <v>45097</v>
       </c>
       <c r="B364" t="n">
-        <v>1805.87451171875</v>
+        <v>1805.874633789062</v>
       </c>
       <c r="C364" t="n">
         <v>811.9500122070312</v>
@@ -12140,7 +12140,7 @@
         <v>804.4000244140625</v>
       </c>
       <c r="D366" t="n">
-        <v>2392.896240234375</v>
+        <v>2392.89599609375</v>
       </c>
       <c r="E366" t="n">
         <v>974.8499755859375</v>
@@ -12155,7 +12155,7 @@
         <v>437.1693115234375</v>
       </c>
       <c r="I366" t="n">
-        <v>654.2526245117188</v>
+        <v>654.252685546875</v>
       </c>
       <c r="J366" t="n">
         <v>222.4499969482422</v>
@@ -12184,7 +12184,7 @@
         <v>48.47999954223633</v>
       </c>
       <c r="H367" t="n">
-        <v>418.4481811523438</v>
+        <v>418.4482116699219</v>
       </c>
       <c r="I367" t="n">
         <v>633.43115234375</v>
@@ -12219,7 +12219,7 @@
         <v>424.5903015136719</v>
       </c>
       <c r="I368" t="n">
-        <v>643.1178588867188</v>
+        <v>643.117919921875</v>
       </c>
       <c r="J368" t="n">
         <v>224.8999938964844</v>
@@ -12280,10 +12280,10 @@
         <v>50.93000030517578</v>
       </c>
       <c r="H370" t="n">
-        <v>426.7523498535156</v>
+        <v>426.7523193359375</v>
       </c>
       <c r="I370" t="n">
-        <v>653.6034545898438</v>
+        <v>653.603515625</v>
       </c>
       <c r="J370" t="n">
         <v>230.8500061035156</v>
@@ -12312,10 +12312,10 @@
         <v>49.97000122070312</v>
       </c>
       <c r="H371" t="n">
-        <v>418.5464782714844</v>
+        <v>418.5465087890625</v>
       </c>
       <c r="I371" t="n">
-        <v>653.703369140625</v>
+        <v>653.7033081054688</v>
       </c>
       <c r="J371" t="n">
         <v>227.3999938964844</v>
@@ -12326,7 +12326,7 @@
         <v>45110</v>
       </c>
       <c r="B372" t="n">
-        <v>1793.005004882812</v>
+        <v>1793.005126953125</v>
       </c>
       <c r="C372" t="n">
         <v>773.25</v>
@@ -12347,7 +12347,7 @@
         <v>428.32470703125</v>
       </c>
       <c r="I372" t="n">
-        <v>656.7991333007812</v>
+        <v>656.7991943359375</v>
       </c>
       <c r="J372" t="n">
         <v>225.6499938964844</v>
@@ -12358,7 +12358,7 @@
         <v>45111</v>
       </c>
       <c r="B373" t="n">
-        <v>1788.436767578125</v>
+        <v>1788.436645507812</v>
       </c>
       <c r="C373" t="n">
         <v>770.5999755859375</v>
@@ -12370,7 +12370,7 @@
         <v>946</v>
       </c>
       <c r="F373" t="n">
-        <v>726.9840087890625</v>
+        <v>726.98388671875</v>
       </c>
       <c r="G373" t="n">
         <v>49.41999816894531</v>
@@ -12390,7 +12390,7 @@
         <v>45112</v>
       </c>
       <c r="B374" t="n">
-        <v>1788.78076171875</v>
+        <v>1788.780639648438</v>
       </c>
       <c r="C374" t="n">
         <v>770</v>
@@ -12434,16 +12434,16 @@
         <v>962.2000122070312</v>
       </c>
       <c r="F375" t="n">
-        <v>725.36669921875</v>
+        <v>725.3666381835938</v>
       </c>
       <c r="G375" t="n">
         <v>49.29000091552734</v>
       </c>
       <c r="H375" t="n">
-        <v>424.0497741699219</v>
+        <v>424.0498046875</v>
       </c>
       <c r="I375" t="n">
-        <v>647.861328125</v>
+        <v>647.8613891601562</v>
       </c>
       <c r="J375" t="n">
         <v>227</v>
@@ -12466,7 +12466,7 @@
         <v>951</v>
       </c>
       <c r="F376" t="n">
-        <v>704.4403076171875</v>
+        <v>704.4402465820312</v>
       </c>
       <c r="G376" t="n">
         <v>48.75</v>
@@ -12486,7 +12486,7 @@
         <v>45117</v>
       </c>
       <c r="B377" t="n">
-        <v>1772.14453125</v>
+        <v>1772.144409179688</v>
       </c>
       <c r="C377" t="n">
         <v>749.8499755859375</v>
@@ -12518,7 +12518,7 @@
         <v>45118</v>
       </c>
       <c r="B378" t="n">
-        <v>1760.838500976562</v>
+        <v>1760.83837890625</v>
       </c>
       <c r="C378" t="n">
         <v>754.0499877929688</v>
@@ -12530,7 +12530,7 @@
         <v>965.1500244140625</v>
       </c>
       <c r="F378" t="n">
-        <v>715.4180908203125</v>
+        <v>715.4180297851562</v>
       </c>
       <c r="G378" t="n">
         <v>48.84000015258789</v>
@@ -12594,7 +12594,7 @@
         <v>947.0499877929688</v>
       </c>
       <c r="F380" t="n">
-        <v>702.9700927734375</v>
+        <v>702.9700317382812</v>
       </c>
       <c r="G380" t="n">
         <v>47.43999862670898</v>
@@ -12626,7 +12626,7 @@
         <v>965.2000122070312</v>
       </c>
       <c r="F381" t="n">
-        <v>711.6934814453125</v>
+        <v>711.6934204101562</v>
       </c>
       <c r="G381" t="n">
         <v>48.38000106811523</v>
@@ -12646,7 +12646,7 @@
         <v>45124</v>
       </c>
       <c r="B382" t="n">
-        <v>1788.733520507812</v>
+        <v>1788.7333984375</v>
       </c>
       <c r="C382" t="n">
         <v>770.4500122070312</v>
@@ -12678,7 +12678,7 @@
         <v>45125</v>
       </c>
       <c r="B383" t="n">
-        <v>1772.539672851562</v>
+        <v>1772.53955078125</v>
       </c>
       <c r="C383" t="n">
         <v>783</v>
@@ -12690,7 +12690,7 @@
         <v>973.75</v>
       </c>
       <c r="F383" t="n">
-        <v>713.7026977539062</v>
+        <v>713.7028198242188</v>
       </c>
       <c r="G383" t="n">
         <v>49.31000137329102</v>
@@ -12722,7 +12722,7 @@
         <v>979.6500244140625</v>
       </c>
       <c r="F384" t="n">
-        <v>716.8883666992188</v>
+        <v>716.8883056640625</v>
       </c>
       <c r="G384" t="n">
         <v>49.13999938964844</v>
@@ -12742,7 +12742,7 @@
         <v>45127</v>
       </c>
       <c r="B385" t="n">
-        <v>1777.822265625</v>
+        <v>1777.822143554688</v>
       </c>
       <c r="C385" t="n">
         <v>780.2999877929688</v>
@@ -12786,7 +12786,7 @@
         <v>995.5499877929688</v>
       </c>
       <c r="F386" t="n">
-        <v>713.996826171875</v>
+        <v>713.9967651367188</v>
       </c>
       <c r="G386" t="n">
         <v>48.34999847412109</v>
@@ -12818,7 +12818,7 @@
         <v>989.1500244140625</v>
       </c>
       <c r="F387" t="n">
-        <v>720.7109375</v>
+        <v>720.7108764648438</v>
       </c>
       <c r="G387" t="n">
         <v>47.59999847412109</v>
@@ -12882,7 +12882,7 @@
         <v>1140.400024414062</v>
       </c>
       <c r="F389" t="n">
-        <v>737.7166137695312</v>
+        <v>737.7166748046875</v>
       </c>
       <c r="G389" t="n">
         <v>51.09999847412109</v>
@@ -12914,7 +12914,7 @@
         <v>1119.199951171875</v>
       </c>
       <c r="F390" t="n">
-        <v>733.8939819335938</v>
+        <v>733.89404296875</v>
       </c>
       <c r="G390" t="n">
         <v>50.59999847412109</v>
@@ -12998,7 +12998,7 @@
         <v>45139</v>
       </c>
       <c r="B393" t="n">
-        <v>1985.331176757812</v>
+        <v>1985.331298828125</v>
       </c>
       <c r="C393" t="n">
         <v>803.9500122070312</v>
@@ -13010,7 +13010,7 @@
         <v>1087.050048828125</v>
       </c>
       <c r="F393" t="n">
-        <v>755.2078247070312</v>
+        <v>755.207763671875</v>
       </c>
       <c r="G393" t="n">
         <v>54.63999938964844</v>
@@ -13094,7 +13094,7 @@
         <v>45142</v>
       </c>
       <c r="B396" t="n">
-        <v>2017.077026367188</v>
+        <v>2017.0771484375</v>
       </c>
       <c r="C396" t="n">
         <v>796.6500244140625</v>
@@ -13126,7 +13126,7 @@
         <v>45145</v>
       </c>
       <c r="B397" t="n">
-        <v>2005.524169921875</v>
+        <v>2005.524291992188</v>
       </c>
       <c r="C397" t="n">
         <v>832.7000122070312</v>
@@ -13202,7 +13202,7 @@
         <v>971.2999877929688</v>
       </c>
       <c r="F399" t="n">
-        <v>780.6165771484375</v>
+        <v>780.6165161132812</v>
       </c>
       <c r="G399" t="n">
         <v>55.43000030517578</v>
@@ -13222,7 +13222,7 @@
         <v>45148</v>
       </c>
       <c r="B400" t="n">
-        <v>1936.305053710938</v>
+        <v>1936.30517578125</v>
       </c>
       <c r="C400" t="n">
         <v>820.7999877929688</v>
@@ -13234,7 +13234,7 @@
         <v>973.9000244140625</v>
       </c>
       <c r="F400" t="n">
-        <v>792.1614990234375</v>
+        <v>792.1615600585938</v>
       </c>
       <c r="G400" t="n">
         <v>56.38000106811523</v>
@@ -13318,7 +13318,7 @@
         <v>45154</v>
       </c>
       <c r="B403" t="n">
-        <v>1868.369995117188</v>
+        <v>1868.369873046875</v>
       </c>
       <c r="C403" t="n">
         <v>818.0999755859375</v>
@@ -13362,7 +13362,7 @@
         <v>933.5</v>
       </c>
       <c r="F404" t="n">
-        <v>798.9207153320312</v>
+        <v>798.9208374023438</v>
       </c>
       <c r="G404" t="n">
         <v>57.31000137329102</v>
@@ -13382,7 +13382,7 @@
         <v>45156</v>
       </c>
       <c r="B405" t="n">
-        <v>1909.792602539062</v>
+        <v>1909.792724609375</v>
       </c>
       <c r="C405" t="n">
         <v>871.9000244140625</v>
@@ -13394,7 +13394,7 @@
         <v>994.75</v>
       </c>
       <c r="F405" t="n">
-        <v>824.8228759765625</v>
+        <v>824.8229370117188</v>
       </c>
       <c r="G405" t="n">
         <v>60.91999816894531</v>
@@ -13458,7 +13458,7 @@
         <v>1015.099975585938</v>
       </c>
       <c r="F407" t="n">
-        <v>843.1763916015625</v>
+        <v>843.1764526367188</v>
       </c>
       <c r="G407" t="n">
         <v>69.48000335693359</v>
@@ -13478,7 +13478,7 @@
         <v>45161</v>
       </c>
       <c r="B408" t="n">
-        <v>1940.551147460938</v>
+        <v>1940.55126953125</v>
       </c>
       <c r="C408" t="n">
         <v>890.4000244140625</v>
@@ -13490,7 +13490,7 @@
         <v>971.5</v>
       </c>
       <c r="F408" t="n">
-        <v>814.7581176757812</v>
+        <v>814.758056640625</v>
       </c>
       <c r="G408" t="n">
         <v>64.56999969482422</v>
@@ -13586,7 +13586,7 @@
         <v>980.0999755859375</v>
       </c>
       <c r="F411" t="n">
-        <v>796.7498779296875</v>
+        <v>796.7499389648438</v>
       </c>
       <c r="G411" t="n">
         <v>64.36000061035156</v>
@@ -13618,7 +13618,7 @@
         <v>974.5</v>
       </c>
       <c r="F412" t="n">
-        <v>812.6365966796875</v>
+        <v>812.6365356445312</v>
       </c>
       <c r="G412" t="n">
         <v>66.54000091552734</v>
@@ -13638,7 +13638,7 @@
         <v>45168</v>
       </c>
       <c r="B413" t="n">
-        <v>1975.407470703125</v>
+        <v>1975.407592773438</v>
       </c>
       <c r="C413" t="n">
         <v>841.7000122070312</v>
@@ -13670,7 +13670,7 @@
         <v>45169</v>
       </c>
       <c r="B414" t="n">
-        <v>1980.542114257812</v>
+        <v>1980.542236328125</v>
       </c>
       <c r="C414" t="n">
         <v>811.9500122070312</v>
@@ -13714,7 +13714,7 @@
         <v>949.0999755859375</v>
       </c>
       <c r="F415" t="n">
-        <v>788.9052124023438</v>
+        <v>788.9053344726562</v>
       </c>
       <c r="G415" t="n">
         <v>66.05000305175781</v>
@@ -13778,7 +13778,7 @@
         <v>962.0999755859375</v>
       </c>
       <c r="F417" t="n">
-        <v>794.2830200195312</v>
+        <v>794.2830810546875</v>
       </c>
       <c r="G417" t="n">
         <v>68.48999786376953</v>
@@ -13798,7 +13798,7 @@
         <v>45175</v>
       </c>
       <c r="B418" t="n">
-        <v>2017.817749023438</v>
+        <v>2017.817626953125</v>
       </c>
       <c r="C418" t="n">
         <v>855.9500122070312</v>
@@ -13810,7 +13810,7 @@
         <v>1006.099975585938</v>
       </c>
       <c r="F418" t="n">
-        <v>796.355224609375</v>
+        <v>796.3551635742188</v>
       </c>
       <c r="G418" t="n">
         <v>69.51000213623047</v>
@@ -13830,7 +13830,7 @@
         <v>45176</v>
       </c>
       <c r="B419" t="n">
-        <v>2016.089721679688</v>
+        <v>2016.08984375</v>
       </c>
       <c r="C419" t="n">
         <v>839.4000244140625</v>
@@ -13862,7 +13862,7 @@
         <v>45177</v>
       </c>
       <c r="B420" t="n">
-        <v>1998.8095703125</v>
+        <v>1998.809692382812</v>
       </c>
       <c r="C420" t="n">
         <v>833</v>
@@ -13874,7 +13874,7 @@
         <v>1001.200012207031</v>
       </c>
       <c r="F420" t="n">
-        <v>814.0673828125</v>
+        <v>814.0673217773438</v>
       </c>
       <c r="G420" t="n">
         <v>73.83000183105469</v>
@@ -14022,7 +14022,7 @@
         <v>45184</v>
       </c>
       <c r="B425" t="n">
-        <v>2001.376953125</v>
+        <v>2001.377075195312</v>
       </c>
       <c r="C425" t="n">
         <v>846.0999755859375</v>
@@ -14034,7 +14034,7 @@
         <v>1006.450012207031</v>
       </c>
       <c r="F425" t="n">
-        <v>834.4437866210938</v>
+        <v>834.4436645507812</v>
       </c>
       <c r="G425" t="n">
         <v>75.87999725341797</v>
@@ -14066,7 +14066,7 @@
         <v>1004.950012207031</v>
       </c>
       <c r="F426" t="n">
-        <v>820.2345581054688</v>
+        <v>820.2344970703125</v>
       </c>
       <c r="G426" t="n">
         <v>75</v>
@@ -14098,7 +14098,7 @@
         <v>1008.950012207031</v>
       </c>
       <c r="F427" t="n">
-        <v>807.2093505859375</v>
+        <v>807.2094116210938</v>
       </c>
       <c r="G427" t="n">
         <v>73.68000030517578</v>
@@ -14130,7 +14130,7 @@
         <v>1023.450012207031</v>
       </c>
       <c r="F428" t="n">
-        <v>820.0864868164062</v>
+        <v>820.0865478515625</v>
       </c>
       <c r="G428" t="n">
         <v>76.48999786376953</v>
@@ -14150,7 +14150,7 @@
         <v>45191</v>
       </c>
       <c r="B429" t="n">
-        <v>1953.634521484375</v>
+        <v>1953.634643554688</v>
       </c>
       <c r="C429" t="n">
         <v>839.0999755859375</v>
@@ -14162,7 +14162,7 @@
         <v>1018.799987792969</v>
       </c>
       <c r="F429" t="n">
-        <v>816.0902099609375</v>
+        <v>816.0901489257812</v>
       </c>
       <c r="G429" t="n">
         <v>76.77999877929688</v>
@@ -14194,7 +14194,7 @@
         <v>1013.799987792969</v>
       </c>
       <c r="F430" t="n">
-        <v>814.7088012695312</v>
+        <v>814.708740234375</v>
       </c>
       <c r="G430" t="n">
         <v>76.23000335693359</v>
@@ -14246,7 +14246,7 @@
         <v>45196</v>
       </c>
       <c r="B432" t="n">
-        <v>1994.366088867188</v>
+        <v>1994.3662109375</v>
       </c>
       <c r="C432" t="n">
         <v>816.2000122070312</v>
@@ -14310,7 +14310,7 @@
         <v>45198</v>
       </c>
       <c r="B434" t="n">
-        <v>1986.96044921875</v>
+        <v>1986.960571289062</v>
       </c>
       <c r="C434" t="n">
         <v>810.25</v>
@@ -14354,7 +14354,7 @@
         <v>973.9500122070312</v>
       </c>
       <c r="F435" t="n">
-        <v>820.3825073242188</v>
+        <v>820.382568359375</v>
       </c>
       <c r="G435" t="n">
         <v>73.33999633789062</v>
@@ -14386,7 +14386,7 @@
         <v>971.9000244140625</v>
       </c>
       <c r="F436" t="n">
-        <v>813.672607421875</v>
+        <v>813.6726684570312</v>
       </c>
       <c r="G436" t="n">
         <v>74.41000366210938</v>
@@ -14438,7 +14438,7 @@
         <v>45205</v>
       </c>
       <c r="B438" t="n">
-        <v>1984.689208984375</v>
+        <v>1984.689331054688</v>
       </c>
       <c r="C438" t="n">
         <v>806</v>
@@ -14450,7 +14450,7 @@
         <v>961.25</v>
       </c>
       <c r="F438" t="n">
-        <v>819.7412109375</v>
+        <v>819.7411499023438</v>
       </c>
       <c r="G438" t="n">
         <v>72.86000061035156</v>
@@ -14546,7 +14546,7 @@
         <v>962.4500122070312</v>
       </c>
       <c r="F441" t="n">
-        <v>804.0517578125</v>
+        <v>804.0518188476562</v>
       </c>
       <c r="G441" t="n">
         <v>69.95999908447266</v>
@@ -14642,7 +14642,7 @@
         <v>938.7999877929688</v>
       </c>
       <c r="F444" t="n">
-        <v>794.9737548828125</v>
+        <v>794.9738159179688</v>
       </c>
       <c r="G444" t="n">
         <v>65.93000030517578</v>
@@ -14694,7 +14694,7 @@
         <v>45217</v>
       </c>
       <c r="B446" t="n">
-        <v>1988.73779296875</v>
+        <v>1988.737915039062</v>
       </c>
       <c r="C446" t="n">
         <v>764.9000244140625</v>
@@ -14726,7 +14726,7 @@
         <v>45218</v>
       </c>
       <c r="B447" t="n">
-        <v>2005.030517578125</v>
+        <v>2005.030395507812</v>
       </c>
       <c r="C447" t="n">
         <v>759.4000244140625</v>
@@ -14802,7 +14802,7 @@
         <v>880.7999877929688</v>
       </c>
       <c r="F449" t="n">
-        <v>761.2269897460938</v>
+        <v>761.2269287109375</v>
       </c>
       <c r="G449" t="n">
         <v>63.29000091552734</v>
@@ -14834,7 +14834,7 @@
         <v>876.1500244140625</v>
       </c>
       <c r="F450" t="n">
-        <v>758.9081420898438</v>
+        <v>758.9080810546875</v>
       </c>
       <c r="G450" t="n">
         <v>62.54000091552734</v>
@@ -14866,7 +14866,7 @@
         <v>848.1500244140625</v>
       </c>
       <c r="F451" t="n">
-        <v>760.1414794921875</v>
+        <v>760.1415405273438</v>
       </c>
       <c r="G451" t="n">
         <v>65.47000122070312</v>
@@ -14962,7 +14962,7 @@
         <v>911.6500244140625</v>
       </c>
       <c r="F454" t="n">
-        <v>774.3507080078125</v>
+        <v>774.3507690429688</v>
       </c>
       <c r="G454" t="n">
         <v>72.61000061035156</v>
@@ -14994,7 +14994,7 @@
         <v>880.25</v>
       </c>
       <c r="F455" t="n">
-        <v>758.9081420898438</v>
+        <v>758.9080810546875</v>
       </c>
       <c r="G455" t="n">
         <v>73.04000091552734</v>
@@ -15026,7 +15026,7 @@
         <v>892.0999755859375</v>
       </c>
       <c r="F456" t="n">
-        <v>764.0392456054688</v>
+        <v>764.0391845703125</v>
       </c>
       <c r="G456" t="n">
         <v>74.58999633789062</v>
@@ -15090,7 +15090,7 @@
         <v>926.5</v>
       </c>
       <c r="F458" t="n">
-        <v>791.8655395507812</v>
+        <v>791.865478515625</v>
       </c>
       <c r="G458" t="n">
         <v>78.80000305175781</v>
@@ -15122,7 +15122,7 @@
         <v>932.1500244140625</v>
       </c>
       <c r="F459" t="n">
-        <v>786.9810791015625</v>
+        <v>786.9811401367188</v>
       </c>
       <c r="G459" t="n">
         <v>76.76000213623047</v>
@@ -15206,7 +15206,7 @@
         <v>45240</v>
       </c>
       <c r="B462" t="n">
-        <v>1802.360107421875</v>
+        <v>1802.359985351562</v>
       </c>
       <c r="C462" t="n">
         <v>760.4500122070312</v>
@@ -15250,7 +15250,7 @@
         <v>940.1500244140625</v>
       </c>
       <c r="F463" t="n">
-        <v>799.1180419921875</v>
+        <v>799.1181030273438</v>
       </c>
       <c r="G463" t="n">
         <v>78.12000274658203</v>
@@ -15314,7 +15314,7 @@
         <v>941.3499755859375</v>
       </c>
       <c r="F465" t="n">
-        <v>802.818359375</v>
+        <v>802.8184204101562</v>
       </c>
       <c r="G465" t="n">
         <v>77.91000366210938</v>
@@ -15366,7 +15366,7 @@
         <v>45250</v>
       </c>
       <c r="B467" t="n">
-        <v>1805.470458984375</v>
+        <v>1805.470336914062</v>
       </c>
       <c r="C467" t="n">
         <v>727.5</v>
@@ -15474,7 +15474,7 @@
         <v>930.7000122070312</v>
       </c>
       <c r="F470" t="n">
-        <v>782.590087890625</v>
+        <v>782.5900268554688</v>
       </c>
       <c r="G470" t="n">
         <v>76.33999633789062</v>
@@ -15494,7 +15494,7 @@
         <v>45254</v>
       </c>
       <c r="B471" t="n">
-        <v>1797.620239257812</v>
+        <v>1797.620361328125</v>
       </c>
       <c r="C471" t="n">
         <v>729.0999755859375</v>
@@ -15506,7 +15506,7 @@
         <v>937.9000244140625</v>
       </c>
       <c r="F471" t="n">
-        <v>785.007568359375</v>
+        <v>785.0076293945312</v>
       </c>
       <c r="G471" t="n">
         <v>79.44000244140625</v>
@@ -15526,7 +15526,7 @@
         <v>45258</v>
       </c>
       <c r="B472" t="n">
-        <v>1845.510864257812</v>
+        <v>1845.5107421875</v>
       </c>
       <c r="C472" t="n">
         <v>865.0999755859375</v>
@@ -15558,7 +15558,7 @@
         <v>45259</v>
       </c>
       <c r="B473" t="n">
-        <v>1848.275634765625</v>
+        <v>1848.275756835938</v>
       </c>
       <c r="C473" t="n">
         <v>875.7000122070312</v>
@@ -15602,7 +15602,7 @@
         <v>1028.800048828125</v>
       </c>
       <c r="F474" t="n">
-        <v>814.5606689453125</v>
+        <v>814.5607299804688</v>
       </c>
       <c r="G474" t="n">
         <v>86.30000305175781</v>
@@ -15666,7 +15666,7 @@
         <v>1123.75</v>
       </c>
       <c r="F476" t="n">
-        <v>867.0064086914062</v>
+        <v>867.00634765625</v>
       </c>
       <c r="G476" t="n">
         <v>92.94000244140625</v>
@@ -15698,7 +15698,7 @@
         <v>1348.5</v>
       </c>
       <c r="F477" t="n">
-        <v>999.6746826171875</v>
+        <v>999.6746215820312</v>
       </c>
       <c r="G477" t="n">
         <v>107.629997253418</v>
@@ -15718,7 +15718,7 @@
         <v>45266</v>
       </c>
       <c r="B478" t="n">
-        <v>2101.502685546875</v>
+        <v>2101.5029296875</v>
       </c>
       <c r="C478" t="n">
         <v>1164.300048828125</v>
@@ -15730,7 +15730,7 @@
         <v>1563.449951171875</v>
       </c>
       <c r="F478" t="n">
-        <v>1004.460388183594</v>
+        <v>1004.46044921875</v>
       </c>
       <c r="G478" t="n">
         <v>112.0899963378906</v>
@@ -15782,7 +15782,7 @@
         <v>45268</v>
       </c>
       <c r="B480" t="n">
-        <v>2110.9326171875</v>
+        <v>2110.932373046875</v>
       </c>
       <c r="C480" t="n">
         <v>1131.5</v>
@@ -15826,7 +15826,7 @@
         <v>1530</v>
       </c>
       <c r="F481" t="n">
-        <v>1018.2255859375</v>
+        <v>1018.225524902344</v>
       </c>
       <c r="G481" t="n">
         <v>105.2300033569336</v>
@@ -15846,7 +15846,7 @@
         <v>45272</v>
       </c>
       <c r="B482" t="n">
-        <v>2148.109130859375</v>
+        <v>2148.109375</v>
       </c>
       <c r="C482" t="n">
         <v>1089.150024414062</v>
@@ -15878,7 +15878,7 @@
         <v>45273</v>
       </c>
       <c r="B483" t="n">
-        <v>2156.749267578125</v>
+        <v>2156.74951171875</v>
       </c>
       <c r="C483" t="n">
         <v>1030.900024414062</v>
@@ -15890,7 +15890,7 @@
         <v>1427.699951171875</v>
       </c>
       <c r="F483" t="n">
-        <v>1049.40673828125</v>
+        <v>1049.406860351562</v>
       </c>
       <c r="G483" t="n">
         <v>101.1399993896484</v>
@@ -15922,7 +15922,7 @@
         <v>1508.300048828125</v>
       </c>
       <c r="F484" t="n">
-        <v>1060.458374023438</v>
+        <v>1060.458251953125</v>
       </c>
       <c r="G484" t="n">
         <v>105.7900009155273</v>
@@ -15954,7 +15954,7 @@
         <v>1526.650024414062</v>
       </c>
       <c r="F485" t="n">
-        <v>1064.25732421875</v>
+        <v>1064.257446289062</v>
       </c>
       <c r="G485" t="n">
         <v>107.7699966430664</v>
@@ -15974,7 +15974,7 @@
         <v>45278</v>
       </c>
       <c r="B486" t="n">
-        <v>2209.132568359375</v>
+        <v>2209.1328125</v>
       </c>
       <c r="C486" t="n">
         <v>1043.050048828125</v>
@@ -16006,7 +16006,7 @@
         <v>45279</v>
       </c>
       <c r="B487" t="n">
-        <v>2175.066162109375</v>
+        <v>2175.06640625</v>
       </c>
       <c r="C487" t="n">
         <v>1076.199951171875</v>
@@ -16038,7 +16038,7 @@
         <v>45280</v>
       </c>
       <c r="B488" t="n">
-        <v>2060.42529296875</v>
+        <v>2060.425537109375</v>
       </c>
       <c r="C488" t="n">
         <v>998.9000244140625</v>
@@ -16134,7 +16134,7 @@
         <v>45286</v>
       </c>
       <c r="B491" t="n">
-        <v>2086.987548828125</v>
+        <v>2086.9873046875</v>
       </c>
       <c r="C491" t="n">
         <v>1041.599975585938</v>
@@ -16146,7 +16146,7 @@
         <v>1600.199951171875</v>
       </c>
       <c r="F491" t="n">
-        <v>1015.117309570312</v>
+        <v>1015.117370605469</v>
       </c>
       <c r="G491" t="n">
         <v>102.3399963378906</v>
@@ -16210,7 +16210,7 @@
         <v>1561</v>
       </c>
       <c r="F493" t="n">
-        <v>1003.4736328125</v>
+        <v>1003.473693847656</v>
       </c>
       <c r="G493" t="n">
         <v>104.6800003051758</v>
@@ -16242,7 +16242,7 @@
         <v>1597</v>
       </c>
       <c r="F494" t="n">
-        <v>1010.775634765625</v>
+        <v>1010.775573730469</v>
       </c>
       <c r="G494" t="n">
         <v>105.0299987792969</v>
@@ -16262,7 +16262,7 @@
         <v>45292</v>
       </c>
       <c r="B495" t="n">
-        <v>2215.106689453125</v>
+        <v>2215.10693359375</v>
       </c>
       <c r="C495" t="n">
         <v>1055.050048828125</v>
@@ -16338,7 +16338,7 @@
         <v>1697.25</v>
       </c>
       <c r="F497" t="n">
-        <v>1079.749389648438</v>
+        <v>1079.749267578125</v>
       </c>
       <c r="G497" t="n">
         <v>108.9000015258789</v>
@@ -16370,7 +16370,7 @@
         <v>1692.5</v>
       </c>
       <c r="F498" t="n">
-        <v>1108.315551757812</v>
+        <v>1108.315673828125</v>
       </c>
       <c r="G498" t="n">
         <v>111.7099990844727</v>
@@ -16422,7 +16422,7 @@
         <v>45299</v>
       </c>
       <c r="B500" t="n">
-        <v>2325.156005859375</v>
+        <v>2325.15576171875</v>
       </c>
       <c r="C500" t="n">
         <v>1143.5</v>
@@ -16454,7 +16454,7 @@
         <v>45300</v>
       </c>
       <c r="B501" t="n">
-        <v>2280.62255859375</v>
+        <v>2280.622802734375</v>
       </c>
       <c r="C501" t="n">
         <v>1164.099975585938</v>
@@ -16518,7 +16518,7 @@
         <v>45302</v>
       </c>
       <c r="B503" t="n">
-        <v>2292.57080078125</v>
+        <v>2292.570556640625</v>
       </c>
       <c r="C503" t="n">
         <v>1159.699951171875</v>
@@ -16550,7 +16550,7 @@
         <v>45303</v>
       </c>
       <c r="B504" t="n">
-        <v>2303.0869140625</v>
+        <v>2303.086669921875</v>
       </c>
       <c r="C504" t="n">
         <v>1152.199951171875</v>
@@ -16594,7 +16594,7 @@
         <v>1694.800048828125</v>
       </c>
       <c r="F505" t="n">
-        <v>1187.15673828125</v>
+        <v>1187.156860351562</v>
       </c>
       <c r="G505" t="n">
         <v>108.2300033569336</v>
@@ -16614,7 +16614,7 @@
         <v>45307</v>
       </c>
       <c r="B506" t="n">
-        <v>2265.61376953125</v>
+        <v>2265.613525390625</v>
       </c>
       <c r="C506" t="n">
         <v>1126.349975585938</v>
@@ -16626,7 +16626,7 @@
         <v>1666.800048828125</v>
       </c>
       <c r="F506" t="n">
-        <v>1177.5361328125</v>
+        <v>1177.536010742188</v>
       </c>
       <c r="G506" t="n">
         <v>106.4599990844727</v>
@@ -16722,7 +16722,7 @@
         <v>1570.75</v>
       </c>
       <c r="F509" t="n">
-        <v>1137.177978515625</v>
+        <v>1137.178100585938</v>
       </c>
       <c r="G509" t="n">
         <v>103.3499984741211</v>
@@ -16806,7 +16806,7 @@
         <v>45316</v>
       </c>
       <c r="B512" t="n">
-        <v>2436.63720703125</v>
+        <v>2436.636962890625</v>
       </c>
       <c r="C512" t="n">
         <v>1061.800048828125</v>
@@ -16882,7 +16882,7 @@
         <v>1679.449951171875</v>
       </c>
       <c r="F514" t="n">
-        <v>1171.615600585938</v>
+        <v>1171.615478515625</v>
       </c>
       <c r="G514" t="n">
         <v>111.6600036621094</v>
@@ -16902,7 +16902,7 @@
         <v>45322</v>
       </c>
       <c r="B515" t="n">
-        <v>2512.32373046875</v>
+        <v>2512.323974609375</v>
       </c>
       <c r="C515" t="n">
         <v>1067.849975585938</v>
@@ -16914,7 +16914,7 @@
         <v>1669.449951171875</v>
       </c>
       <c r="F515" t="n">
-        <v>1191.646606445312</v>
+        <v>1191.646484375</v>
       </c>
       <c r="G515" t="n">
         <v>112.5400009155273</v>
@@ -16998,7 +16998,7 @@
         <v>45327</v>
       </c>
       <c r="B518" t="n">
-        <v>2454.9541015625</v>
+        <v>2454.953857421875</v>
       </c>
       <c r="C518" t="n">
         <v>1022.599975585938</v>
@@ -17042,7 +17042,7 @@
         <v>1721.650024414062</v>
       </c>
       <c r="F519" t="n">
-        <v>1256.229248046875</v>
+        <v>1256.229125976562</v>
       </c>
       <c r="G519" t="n">
         <v>109.9400024414062</v>
@@ -17074,7 +17074,7 @@
         <v>1866</v>
       </c>
       <c r="F520" t="n">
-        <v>1239.010498046875</v>
+        <v>1239.010620117188</v>
       </c>
       <c r="G520" t="n">
         <v>113.9400024414062</v>
@@ -17106,7 +17106,7 @@
         <v>1827.949951171875</v>
       </c>
       <c r="F521" t="n">
-        <v>1228.698974609375</v>
+        <v>1228.698852539062</v>
       </c>
       <c r="G521" t="n">
         <v>112.7399978637695</v>
@@ -17126,7 +17126,7 @@
         <v>45331</v>
       </c>
       <c r="B522" t="n">
-        <v>2595.021240234375</v>
+        <v>2595.02099609375</v>
       </c>
       <c r="C522" t="n">
         <v>1054.699951171875</v>
@@ -17170,7 +17170,7 @@
         <v>1842.599975585938</v>
       </c>
       <c r="F523" t="n">
-        <v>1232.7939453125</v>
+        <v>1232.793823242188</v>
       </c>
       <c r="G523" t="n">
         <v>112.370002746582</v>
@@ -17190,7 +17190,7 @@
         <v>45335</v>
       </c>
       <c r="B524" t="n">
-        <v>2581.740234375</v>
+        <v>2581.740478515625</v>
       </c>
       <c r="C524" t="n">
         <v>1044.800048828125</v>
@@ -17202,7 +17202,7 @@
         <v>1815.550048828125</v>
       </c>
       <c r="F524" t="n">
-        <v>1248.039306640625</v>
+        <v>1248.039184570312</v>
       </c>
       <c r="G524" t="n">
         <v>112.4199981689453</v>
@@ -17234,7 +17234,7 @@
         <v>1852.25</v>
       </c>
       <c r="F525" t="n">
-        <v>1251.048828125</v>
+        <v>1251.048706054688</v>
       </c>
       <c r="G525" t="n">
         <v>112.7799987792969</v>
@@ -17254,7 +17254,7 @@
         <v>45337</v>
       </c>
       <c r="B526" t="n">
-        <v>2604.50048828125</v>
+        <v>2604.500244140625</v>
       </c>
       <c r="C526" t="n">
         <v>1052</v>
@@ -17286,7 +17286,7 @@
         <v>45338</v>
       </c>
       <c r="B527" t="n">
-        <v>2686.21044921875</v>
+        <v>2686.210205078125</v>
       </c>
       <c r="C527" t="n">
         <v>1061.599975585938</v>
@@ -17318,7 +17318,7 @@
         <v>45341</v>
       </c>
       <c r="B528" t="n">
-        <v>2636.937744140625</v>
+        <v>2636.9375</v>
       </c>
       <c r="C528" t="n">
         <v>1074.449951171875</v>
@@ -17330,7 +17330,7 @@
         <v>1955.050048828125</v>
       </c>
       <c r="F528" t="n">
-        <v>1289.679931640625</v>
+        <v>1289.680053710938</v>
       </c>
       <c r="G528" t="n">
         <v>113.5299987792969</v>
@@ -17362,7 +17362,7 @@
         <v>1926.650024414062</v>
       </c>
       <c r="F529" t="n">
-        <v>1283.266235351562</v>
+        <v>1283.26611328125</v>
       </c>
       <c r="G529" t="n">
         <v>110.7300033569336</v>
@@ -17382,7 +17382,7 @@
         <v>45343</v>
       </c>
       <c r="B530" t="n">
-        <v>2633.234619140625</v>
+        <v>2633.23486328125</v>
       </c>
       <c r="C530" t="n">
         <v>1064.800048828125</v>
@@ -17394,7 +17394,7 @@
         <v>1904.949951171875</v>
       </c>
       <c r="F530" t="n">
-        <v>1273.891967773438</v>
+        <v>1273.89208984375</v>
       </c>
       <c r="G530" t="n">
         <v>108.1500015258789</v>
@@ -17426,7 +17426,7 @@
         <v>1922.650024414062</v>
       </c>
       <c r="F531" t="n">
-        <v>1293.57763671875</v>
+        <v>1293.577758789062</v>
       </c>
       <c r="G531" t="n">
         <v>112.4499969482422</v>
@@ -17510,7 +17510,7 @@
         <v>45349</v>
       </c>
       <c r="B534" t="n">
-        <v>2635.8515625</v>
+        <v>2635.851318359375</v>
       </c>
       <c r="C534" t="n">
         <v>1122.699951171875</v>
@@ -17522,7 +17522,7 @@
         <v>1979.5</v>
       </c>
       <c r="F534" t="n">
-        <v>1311.832397460938</v>
+        <v>1311.83251953125</v>
       </c>
       <c r="G534" t="n">
         <v>113.3399963378906</v>
@@ -17586,7 +17586,7 @@
         <v>1895.050048828125</v>
       </c>
       <c r="F536" t="n">
-        <v>1303.001098632812</v>
+        <v>1303.0009765625</v>
       </c>
       <c r="G536" t="n">
         <v>109.9899978637695</v>
@@ -17606,7 +17606,7 @@
         <v>45352</v>
       </c>
       <c r="B537" t="n">
-        <v>2661.57421875</v>
+        <v>2661.573974609375</v>
       </c>
       <c r="C537" t="n">
         <v>1072.400024414062</v>
@@ -17618,7 +17618,7 @@
         <v>1969.550048828125</v>
       </c>
       <c r="F537" t="n">
-        <v>1304.579956054688</v>
+        <v>1304.579833984375</v>
       </c>
       <c r="G537" t="n">
         <v>110.8300018310547</v>
@@ -17670,7 +17670,7 @@
         <v>45356</v>
       </c>
       <c r="B539" t="n">
-        <v>2635.20947265625</v>
+        <v>2635.209716796875</v>
       </c>
       <c r="C539" t="n">
         <v>1070.300048828125</v>
@@ -17682,7 +17682,7 @@
         <v>1947.400024414062</v>
       </c>
       <c r="F539" t="n">
-        <v>1320.565307617188</v>
+        <v>1320.565185546875</v>
       </c>
       <c r="G539" t="n">
         <v>114.7699966430664</v>
@@ -17714,7 +17714,7 @@
         <v>1910.5</v>
       </c>
       <c r="F540" t="n">
-        <v>1307.244140625</v>
+        <v>1307.244262695312</v>
       </c>
       <c r="G540" t="n">
         <v>115.3399963378906</v>
@@ -17746,7 +17746,7 @@
         <v>1929.099975585938</v>
       </c>
       <c r="F541" t="n">
-        <v>1307.885375976562</v>
+        <v>1307.885498046875</v>
       </c>
       <c r="G541" t="n">
         <v>113.370002746582</v>
@@ -17778,7 +17778,7 @@
         <v>1930.300048828125</v>
       </c>
       <c r="F542" t="n">
-        <v>1309.365600585938</v>
+        <v>1309.36572265625</v>
       </c>
       <c r="G542" t="n">
         <v>113.3899993896484</v>
@@ -17798,7 +17798,7 @@
         <v>45363</v>
       </c>
       <c r="B543" t="n">
-        <v>2529.406494140625</v>
+        <v>2529.40625</v>
       </c>
       <c r="C543" t="n">
         <v>1037.25</v>
@@ -17810,7 +17810,7 @@
         <v>1897.099975585938</v>
       </c>
       <c r="F543" t="n">
-        <v>1284.0556640625</v>
+        <v>1284.055541992188</v>
       </c>
       <c r="G543" t="n">
         <v>111.2200012207031</v>
@@ -17842,7 +17842,7 @@
         <v>1725</v>
       </c>
       <c r="F544" t="n">
-        <v>1193.521484375</v>
+        <v>1193.521362304688</v>
       </c>
       <c r="G544" t="n">
         <v>105.6600036621094</v>
@@ -17874,7 +17874,7 @@
         <v>1895.300048828125</v>
       </c>
       <c r="F545" t="n">
-        <v>1251.048828125</v>
+        <v>1251.048706054688</v>
       </c>
       <c r="G545" t="n">
         <v>107.5699996948242</v>
@@ -17894,7 +17894,7 @@
         <v>45366</v>
       </c>
       <c r="B546" t="n">
-        <v>2471.4931640625</v>
+        <v>2471.493408203125</v>
       </c>
       <c r="C546" t="n">
         <v>1045.849975585938</v>
@@ -18066,7 +18066,7 @@
         <v>1851.75</v>
       </c>
       <c r="F551" t="n">
-        <v>1264.616577148438</v>
+        <v>1264.61669921875</v>
       </c>
       <c r="G551" t="n">
         <v>106.2099990844727</v>
@@ -18098,7 +18098,7 @@
         <v>1859</v>
       </c>
       <c r="F552" t="n">
-        <v>1286.9169921875</v>
+        <v>1286.917114257812</v>
       </c>
       <c r="G552" t="n">
         <v>104.4000015258789</v>
@@ -18162,7 +18162,7 @@
         <v>1835.150024414062</v>
       </c>
       <c r="F554" t="n">
-        <v>1324.068237304688</v>
+        <v>1324.068115234375</v>
       </c>
       <c r="G554" t="n">
         <v>106.7600021362305</v>
@@ -18182,7 +18182,7 @@
         <v>45383</v>
       </c>
       <c r="B555" t="n">
-        <v>2512.570556640625</v>
+        <v>2512.57080078125</v>
       </c>
       <c r="C555" t="n">
         <v>1112</v>
@@ -18226,7 +18226,7 @@
         <v>1892.650024414062</v>
       </c>
       <c r="F556" t="n">
-        <v>1385.542602539062</v>
+        <v>1385.54248046875</v>
       </c>
       <c r="G556" t="n">
         <v>117.6900024414062</v>
@@ -18258,7 +18258,7 @@
         <v>1878.949951171875</v>
       </c>
       <c r="F557" t="n">
-        <v>1378.684692382812</v>
+        <v>1378.6845703125</v>
       </c>
       <c r="G557" t="n">
         <v>123.5699996948242</v>
@@ -18278,7 +18278,7 @@
         <v>45386</v>
       </c>
       <c r="B558" t="n">
-        <v>2583.36962890625</v>
+        <v>2583.369384765625</v>
       </c>
       <c r="C558" t="n">
         <v>1102</v>
@@ -18342,7 +18342,7 @@
         <v>45390</v>
       </c>
       <c r="B560" t="n">
-        <v>2549.994140625</v>
+        <v>2549.994384765625</v>
       </c>
       <c r="C560" t="n">
         <v>1075.849975585938</v>
@@ -18406,7 +18406,7 @@
         <v>45392</v>
       </c>
       <c r="B562" t="n">
-        <v>2492.969970703125</v>
+        <v>2492.97021484375</v>
       </c>
       <c r="C562" t="n">
         <v>1064.25</v>
@@ -18418,7 +18418,7 @@
         <v>1907.5</v>
       </c>
       <c r="F562" t="n">
-        <v>1334.3798828125</v>
+        <v>1334.379760742188</v>
       </c>
       <c r="G562" t="n">
         <v>123.5699996948242</v>
@@ -18450,7 +18450,7 @@
         <v>1884.050048828125</v>
       </c>
       <c r="F563" t="n">
-        <v>1326.386962890625</v>
+        <v>1326.387084960938</v>
       </c>
       <c r="G563" t="n">
         <v>119.0400009155273</v>
@@ -18470,7 +18470,7 @@
         <v>45397</v>
       </c>
       <c r="B564" t="n">
-        <v>2411.75390625</v>
+        <v>2411.753662109375</v>
       </c>
       <c r="C564" t="n">
         <v>1039.449951171875</v>
@@ -18514,7 +18514,7 @@
         <v>1811.650024414062</v>
       </c>
       <c r="F565" t="n">
-        <v>1287.065063476562</v>
+        <v>1287.065185546875</v>
       </c>
       <c r="G565" t="n">
         <v>120.3199996948242</v>
@@ -18534,7 +18534,7 @@
         <v>45400</v>
       </c>
       <c r="B566" t="n">
-        <v>2381.686279296875</v>
+        <v>2381.6865234375</v>
       </c>
       <c r="C566" t="n">
         <v>1038.75</v>
@@ -18546,7 +18546,7 @@
         <v>1775.449951171875</v>
       </c>
       <c r="F566" t="n">
-        <v>1278.381713867188</v>
+        <v>1278.3818359375</v>
       </c>
       <c r="G566" t="n">
         <v>119.620002746582</v>
@@ -18642,7 +18642,7 @@
         <v>1816.400024414062</v>
       </c>
       <c r="F569" t="n">
-        <v>1304.579956054688</v>
+        <v>1304.579833984375</v>
       </c>
       <c r="G569" t="n">
         <v>120.4899978637695</v>
@@ -18674,7 +18674,7 @@
         <v>1808.300048828125</v>
       </c>
       <c r="F570" t="n">
-        <v>1303.001098632812</v>
+        <v>1303.0009765625</v>
       </c>
       <c r="G570" t="n">
         <v>119.3000030517578</v>
@@ -18738,7 +18738,7 @@
         <v>1806.650024414062</v>
       </c>
       <c r="F572" t="n">
-        <v>1307.046752929688</v>
+        <v>1307.046630859375</v>
       </c>
       <c r="G572" t="n">
         <v>118.3199996948242</v>
@@ -18834,7 +18834,7 @@
         <v>1786.849975585938</v>
       </c>
       <c r="F575" t="n">
-        <v>1321.05859375</v>
+        <v>1321.058715820312</v>
       </c>
       <c r="G575" t="n">
         <v>121.620002746582</v>
@@ -18866,7 +18866,7 @@
         <v>1799.800048828125</v>
       </c>
       <c r="F576" t="n">
-        <v>1302.803833007812</v>
+        <v>1302.8037109375</v>
       </c>
       <c r="G576" t="n">
         <v>120.9400024414062</v>
@@ -18918,7 +18918,7 @@
         <v>45419</v>
       </c>
       <c r="B578" t="n">
-        <v>2405.8291015625</v>
+        <v>2405.829345703125</v>
       </c>
       <c r="C578" t="n">
         <v>1021.549987792969</v>
@@ -18930,7 +18930,7 @@
         <v>1726</v>
       </c>
       <c r="F578" t="n">
-        <v>1270.58642578125</v>
+        <v>1270.586547851562</v>
       </c>
       <c r="G578" t="n">
         <v>116.1100006103516</v>
@@ -18950,7 +18950,7 @@
         <v>45420</v>
       </c>
       <c r="B579" t="n">
-        <v>2408.93994140625</v>
+        <v>2408.939697265625</v>
       </c>
       <c r="C579" t="n">
         <v>1019.5</v>
@@ -18982,7 +18982,7 @@
         <v>45421</v>
       </c>
       <c r="B580" t="n">
-        <v>2385.7841796875</v>
+        <v>2385.784423828125</v>
       </c>
       <c r="C580" t="n">
         <v>980.0499877929688</v>
@@ -18994,7 +18994,7 @@
         <v>1712.150024414062</v>
       </c>
       <c r="F580" t="n">
-        <v>1228.0576171875</v>
+        <v>1228.057739257812</v>
       </c>
       <c r="G580" t="n">
         <v>122.5599975585938</v>
@@ -19046,7 +19046,7 @@
         <v>45425</v>
       </c>
       <c r="B582" t="n">
-        <v>2334.042724609375</v>
+        <v>2334.04296875</v>
       </c>
       <c r="C582" t="n">
         <v>991.0499877929688</v>
@@ -19090,7 +19090,7 @@
         <v>1788.800048828125</v>
       </c>
       <c r="F583" t="n">
-        <v>1313.608642578125</v>
+        <v>1313.608764648438</v>
       </c>
       <c r="G583" t="n">
         <v>125.6100006103516</v>
@@ -19142,7 +19142,7 @@
         <v>45428</v>
       </c>
       <c r="B585" t="n">
-        <v>2454.855224609375</v>
+        <v>2454.85546875</v>
       </c>
       <c r="C585" t="n">
         <v>1031</v>
@@ -19154,7 +19154,7 @@
         <v>1844.400024414062</v>
       </c>
       <c r="F585" t="n">
-        <v>1327.225952148438</v>
+        <v>1327.225830078125</v>
       </c>
       <c r="G585" t="n">
         <v>128.0700073242188</v>
@@ -19174,7 +19174,7 @@
         <v>45429</v>
       </c>
       <c r="B586" t="n">
-        <v>2490.25439453125</v>
+        <v>2490.254638671875</v>
       </c>
       <c r="C586" t="n">
         <v>1035.150024414062</v>
@@ -19302,7 +19302,7 @@
         <v>45436</v>
       </c>
       <c r="B590" t="n">
-        <v>2576.45751953125</v>
+        <v>2576.457275390625</v>
       </c>
       <c r="C590" t="n">
         <v>1106.699951171875</v>
@@ -19314,7 +19314,7 @@
         <v>1926.650024414062</v>
       </c>
       <c r="F590" t="n">
-        <v>1397.334228515625</v>
+        <v>1397.334350585938</v>
       </c>
       <c r="G590" t="n">
         <v>141.3999938964844</v>
@@ -19398,7 +19398,7 @@
         <v>45441</v>
       </c>
       <c r="B593" t="n">
-        <v>2504.6220703125</v>
+        <v>2504.621826171875</v>
       </c>
       <c r="C593" t="n">
         <v>1085.699951171875</v>
@@ -19442,7 +19442,7 @@
         <v>1874.900024414062</v>
       </c>
       <c r="F594" t="n">
-        <v>1365.166381835938</v>
+        <v>1365.166259765625</v>
       </c>
       <c r="G594" t="n">
         <v>139.6799926757812</v>
@@ -19474,7 +19474,7 @@
         <v>1908.349975585938</v>
       </c>
       <c r="F595" t="n">
-        <v>1418.35205078125</v>
+        <v>1418.351928710938</v>
       </c>
       <c r="G595" t="n">
         <v>151.1600036621094</v>
@@ -19538,7 +19538,7 @@
         <v>1646</v>
       </c>
       <c r="F597" t="n">
-        <v>1232.399291992188</v>
+        <v>1232.399169921875</v>
       </c>
       <c r="G597" t="n">
         <v>144.5899963378906</v>
@@ -19570,7 +19570,7 @@
         <v>1828.849975585938</v>
       </c>
       <c r="F598" t="n">
-        <v>1336.649169921875</v>
+        <v>1336.649291992188</v>
       </c>
       <c r="G598" t="n">
         <v>145.3300018310547</v>
@@ -19602,7 +19602,7 @@
         <v>1865.199951171875</v>
       </c>
       <c r="F599" t="n">
-        <v>1335.02099609375</v>
+        <v>1335.021118164062</v>
       </c>
       <c r="G599" t="n">
         <v>149.8699951171875</v>
@@ -19622,7 +19622,7 @@
         <v>45450</v>
       </c>
       <c r="B600" t="n">
-        <v>2467.69189453125</v>
+        <v>2467.692138671875</v>
       </c>
       <c r="C600" t="n">
         <v>1020.049987792969</v>
@@ -19666,7 +19666,7 @@
         <v>1880.349975585938</v>
       </c>
       <c r="F601" t="n">
-        <v>1365.709106445312</v>
+        <v>1365.708984375</v>
       </c>
       <c r="G601" t="n">
         <v>153.9400024414062</v>
@@ -19718,7 +19718,7 @@
         <v>45455</v>
       </c>
       <c r="B603" t="n">
-        <v>2591.4169921875</v>
+        <v>2591.416748046875</v>
       </c>
       <c r="C603" t="n">
         <v>1020.5</v>
@@ -19730,7 +19730,7 @@
         <v>1827.349975585938</v>
       </c>
       <c r="F603" t="n">
-        <v>1375.477783203125</v>
+        <v>1375.477661132812</v>
       </c>
       <c r="G603" t="n">
         <v>152.4400024414062</v>
@@ -19750,7 +19750,7 @@
         <v>45456</v>
       </c>
       <c r="B604" t="n">
-        <v>2602.673828125</v>
+        <v>2602.674072265625</v>
       </c>
       <c r="C604" t="n">
         <v>1017.650024414062</v>
@@ -39601,7 +39601,7 @@
         <v>-6.264570350682453</v>
       </c>
       <c r="F30" t="n">
-        <v>3.272694881032501</v>
+        <v>3.272703769186336</v>
       </c>
       <c r="G30" t="n">
         <v>-4.921938516247337</v>
@@ -39633,7 +39633,7 @@
         <v>6.158036863040528</v>
       </c>
       <c r="F31" t="n">
-        <v>8.491204232254468</v>
+        <v>8.491194894970967</v>
       </c>
       <c r="G31" t="n">
         <v>23.40599746783077</v>
@@ -39665,7 +39665,7 @@
         <v>-2.043429665210794</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.263178235505569</v>
+        <v>-1.26316913262442</v>
       </c>
       <c r="G32" t="n">
         <v>14.73397846832833</v>
@@ -39697,7 +39697,7 @@
         <v>-3.160867674766898</v>
       </c>
       <c r="F33" t="n">
-        <v>1.61681664689155</v>
+        <v>1.616816798361365</v>
       </c>
       <c r="G33" t="n">
         <v>-2.936626775408835</v>
@@ -39717,7 +39717,7 @@
         <v>45351</v>
       </c>
       <c r="B34" t="n">
-        <v>3.340806909066818</v>
+        <v>3.340796866695905</v>
       </c>
       <c r="C34" t="n">
         <v>-0.2809383404587251</v>
@@ -39729,7 +39729,7 @@
         <v>13.51343881245972</v>
       </c>
       <c r="F34" t="n">
-        <v>9.344590215355119</v>
+        <v>9.344591172599625</v>
       </c>
       <c r="G34" t="n">
         <v>-2.265863720466688</v>
@@ -39749,7 +39749,7 @@
         <v>45322</v>
       </c>
       <c r="B35" t="n">
-        <v>15.06160205942875</v>
+        <v>15.06161324079485</v>
       </c>
       <c r="C35" t="n">
         <v>2.113313467457556</v>
@@ -39761,7 +39761,7 @@
         <v>4.536628125978392</v>
       </c>
       <c r="F35" t="n">
-        <v>17.8942749962139</v>
+        <v>17.89427003830248</v>
       </c>
       <c r="G35" t="n">
         <v>7.150340115695419</v>
@@ -39793,7 +39793,7 @@
         <v>55.22938610073884</v>
       </c>
       <c r="F36" t="n">
-        <v>24.08844095975935</v>
+        <v>24.08842416877926</v>
       </c>
       <c r="G36" t="n">
         <v>21.70335465261326</v>
@@ -39825,7 +39825,7 @@
         <v>12.8503286652526</v>
       </c>
       <c r="F37" t="n">
-        <v>5.192732507593223</v>
+        <v>5.192732098296493</v>
       </c>
       <c r="G37" t="n">
         <v>18.85415552448646</v>
@@ -39845,7 +39845,7 @@
         <v>45230</v>
       </c>
       <c r="B38" t="n">
-        <v>-6.16474106694157</v>
+        <v>-6.164746831776336</v>
       </c>
       <c r="C38" t="n">
         <v>-4.992287837955112</v>
@@ -39857,7 +39857,7 @@
         <v>-7.648280214024627</v>
       </c>
       <c r="F38" t="n">
-        <v>-4.896085900373349</v>
+        <v>-4.896078404180482</v>
       </c>
       <c r="G38" t="n">
         <v>-3.815071313970964</v>
@@ -39877,7 +39877,7 @@
         <v>45199</v>
       </c>
       <c r="B39" t="n">
-        <v>0.3240696026977741</v>
+        <v>0.3240695827238183</v>
       </c>
       <c r="C39" t="n">
         <v>-0.20937399858032</v>
@@ -39909,7 +39909,7 @@
         <v>45169</v>
       </c>
       <c r="B40" t="n">
-        <v>-0.6021178610348565</v>
+        <v>-0.6021117346664995</v>
       </c>
       <c r="C40" t="n">
         <v>-1.066163015700394</v>
@@ -39959,10 +39959,10 @@
         <v>9.385628401317447</v>
       </c>
       <c r="H41" t="n">
-        <v>9.344487405733215</v>
+        <v>9.344479433073394</v>
       </c>
       <c r="I41" t="n">
-        <v>1.429244213687864</v>
+        <v>1.429253683962362</v>
       </c>
       <c r="J41" t="n">
         <v>0.6376483051671933</v>
@@ -39991,10 +39991,10 @@
         <v>0.08011399015193099</v>
       </c>
       <c r="H42" t="n">
-        <v>0.5429566903628613</v>
+        <v>0.5429713919922641</v>
       </c>
       <c r="I42" t="n">
-        <v>-1.437938329899247</v>
+        <v>-1.437947532468964</v>
       </c>
       <c r="J42" t="n">
         <v>-4.413619280952474</v>
@@ -40011,22 +40011,22 @@
         <v>-24.55194044908406</v>
       </c>
       <c r="D43" t="n">
-        <v>29.52804511100025</v>
+        <v>29.52805333994046</v>
       </c>
       <c r="E43" t="n">
         <v>2.807572261517488</v>
       </c>
       <c r="F43" t="n">
-        <v>8.447095607106657</v>
+        <v>8.447075783026436</v>
       </c>
       <c r="G43" t="n">
         <v>11.02957293714546</v>
       </c>
       <c r="H43" t="n">
-        <v>6.834808014231619</v>
+        <v>6.834800182265521</v>
       </c>
       <c r="I43" t="n">
-        <v>-29.71957628908746</v>
+        <v>-29.71957174362697</v>
       </c>
       <c r="J43" t="n">
         <v>25.50777634729149</v>
@@ -40043,22 +40043,22 @@
         <v>3.66547140892719</v>
       </c>
       <c r="D44" t="n">
-        <v>9.968866765784234</v>
+        <v>9.968859779442596</v>
       </c>
       <c r="E44" t="n">
         <v>7.927137678102603</v>
       </c>
       <c r="F44" t="n">
-        <v>7.817673773248646</v>
+        <v>7.817693482274435</v>
       </c>
       <c r="G44" t="n">
         <v>17.35386633308638</v>
       </c>
       <c r="H44" t="n">
-        <v>8.466692553990661</v>
+        <v>8.466701768317897</v>
       </c>
       <c r="I44" t="n">
-        <v>8.902337505334469</v>
+        <v>8.902338132359366</v>
       </c>
       <c r="J44" t="n">
         <v>-1.121540913255659</v>
@@ -40081,16 +40081,16 @@
         <v>81.56811180262491</v>
       </c>
       <c r="F45" t="n">
-        <v>6.658794148900937</v>
+        <v>6.658782938311325</v>
       </c>
       <c r="G45" t="n">
         <v>30.96377100161289</v>
       </c>
       <c r="H45" t="n">
-        <v>6.854716860385679</v>
+        <v>6.854717482614991</v>
       </c>
       <c r="I45" t="n">
-        <v>27.88299727935213</v>
+        <v>27.8829882720756</v>
       </c>
       <c r="J45" t="n">
         <v>0.815147568504071</v>
@@ -40101,25 +40101,25 @@
         <v>44985</v>
       </c>
       <c r="B46" t="n">
-        <v>-12.02053840462104</v>
+        <v>-12.02053285062928</v>
       </c>
       <c r="C46" t="n">
         <v>-63.75986333629861</v>
       </c>
       <c r="D46" t="n">
-        <v>-54.139346989149</v>
+        <v>-54.13934321739424</v>
       </c>
       <c r="E46" t="n">
         <v>-60.34806944094112</v>
       </c>
       <c r="F46" t="n">
-        <v>-3.297148955633478</v>
+        <v>-3.297148620506318</v>
       </c>
       <c r="G46" t="n">
         <v>-34.62913019188968</v>
       </c>
       <c r="H46" t="n">
-        <v>-14.73080652967672</v>
+        <v>-14.73081426989218</v>
       </c>
       <c r="I46" t="n">
         <v>-67.81377477152465</v>
@@ -40133,19 +40133,19 @@
         <v>44957</v>
       </c>
       <c r="B47" t="n">
-        <v>-19.38482284752069</v>
+        <v>-19.38482793661753</v>
       </c>
       <c r="C47" t="n">
         <v>-31.48595153036594</v>
       </c>
       <c r="D47" t="n">
-        <v>-22.9230130346567</v>
+        <v>-22.92302425975112</v>
       </c>
       <c r="E47" t="n">
         <v>-36.64458052185531</v>
       </c>
       <c r="F47" t="n">
-        <v>-25.11306112398533</v>
+        <v>-25.11305351236375</v>
       </c>
       <c r="G47" t="n">
         <v>-25.28793450920587</v>
@@ -40171,13 +40171,13 @@
         <v>-10.97644834106928</v>
       </c>
       <c r="D48" t="n">
-        <v>-1.519941977349792</v>
+        <v>-1.51994188246356</v>
       </c>
       <c r="E48" t="n">
         <v>-8.726669084425943</v>
       </c>
       <c r="F48" t="n">
-        <v>-7.139618906309286</v>
+        <v>-7.139625469848454</v>
       </c>
       <c r="G48" t="n">
         <v>-9.977464913384882</v>
@@ -40186,7 +40186,7 @@
         <v>-8.173465264910885</v>
       </c>
       <c r="I48" t="n">
-        <v>1.654391241401121</v>
+        <v>1.654398082501785</v>
       </c>
       <c r="J48" t="n">
         <v>-22.51848593969048</v>
@@ -40197,19 +40197,19 @@
         <v>44895</v>
       </c>
       <c r="B49" t="n">
-        <v>7.235474811139953</v>
+        <v>7.235485960020571</v>
       </c>
       <c r="C49" t="n">
         <v>-13.14539844090323</v>
       </c>
       <c r="D49" t="n">
-        <v>17.04132606638209</v>
+        <v>17.04133337298384</v>
       </c>
       <c r="E49" t="n">
         <v>0.6467306237967874</v>
       </c>
       <c r="F49" t="n">
-        <v>6.975887478934362</v>
+        <v>6.975903128898064</v>
       </c>
       <c r="G49" t="n">
         <v>-0.6419831048444791</v>
@@ -40218,7 +40218,7 @@
         <v>7.092594636276428</v>
       </c>
       <c r="I49" t="n">
-        <v>0.8299009436074867</v>
+        <v>0.8298941579935271</v>
       </c>
       <c r="J49" t="n">
         <v>38.71017491622961</v>
@@ -40229,28 +40229,28 @@
         <v>44865</v>
       </c>
       <c r="B50" t="n">
-        <v>-1.049379852050869</v>
+        <v>-1.049390139584339</v>
       </c>
       <c r="C50" t="n">
         <v>1.790379399037678</v>
       </c>
       <c r="D50" t="n">
-        <v>-3.133913155489276</v>
+        <v>-3.133906299676048</v>
       </c>
       <c r="E50" t="n">
         <v>-6.984259690113759</v>
       </c>
       <c r="F50" t="n">
-        <v>0.3533793058025037</v>
+        <v>0.3533717178334728</v>
       </c>
       <c r="G50" t="n">
         <v>-10.33466386438756</v>
       </c>
       <c r="H50" t="n">
-        <v>3.365025301034952</v>
+        <v>3.365019075528308</v>
       </c>
       <c r="I50" t="n">
-        <v>7.87460157490274</v>
+        <v>7.874609471274563</v>
       </c>
       <c r="J50" t="n">
         <v>-13.75150501852815</v>
@@ -40261,13 +40261,13 @@
         <v>44834</v>
       </c>
       <c r="B51" t="n">
-        <v>5.041947065704555</v>
+        <v>5.041935714636137</v>
       </c>
       <c r="C51" t="n">
         <v>-16.93892268070564</v>
       </c>
       <c r="D51" t="n">
-        <v>8.183191253858269</v>
+        <v>8.183191880428421</v>
       </c>
       <c r="E51" t="n">
         <v>-7.199733431542765</v>
@@ -40279,10 +40279,10 @@
         <v>-9.771716243293183</v>
       </c>
       <c r="H51" t="n">
-        <v>25.37386069556771</v>
+        <v>25.37386824663102</v>
       </c>
       <c r="I51" t="n">
-        <v>-10.81723467446301</v>
+        <v>-10.81723538062699</v>
       </c>
       <c r="J51" t="n">
         <v>-20.88017226023993</v>
@@ -40293,13 +40293,13 @@
         <v>44804</v>
       </c>
       <c r="B52" t="n">
-        <v>3.2459361784547</v>
+        <v>3.245947335443344</v>
       </c>
       <c r="C52" t="n">
         <v>27.37007418275781</v>
       </c>
       <c r="D52" t="n">
-        <v>24.33248723788313</v>
+        <v>24.33247771800031</v>
       </c>
       <c r="E52" t="n">
         <v>12.02464734774498</v>
@@ -40311,10 +40311,10 @@
         <v>31.85220530081916</v>
       </c>
       <c r="H52" t="n">
-        <v>9.725192544846495</v>
+        <v>9.725183453655561</v>
       </c>
       <c r="I52" t="n">
-        <v>19.75410011643701</v>
+        <v>19.75410166075582</v>
       </c>
       <c r="J52" t="n">
         <v>83.74902135029218</v>
@@ -40337,16 +40337,16 @@
         <v>12.70211332333331</v>
       </c>
       <c r="F53" t="n">
-        <v>14.42461753424029</v>
+        <v>14.42459618268113</v>
       </c>
       <c r="G53" t="n">
         <v>19.44074810734559</v>
       </c>
       <c r="H53" t="n">
-        <v>3.250677044378025</v>
+        <v>3.250676766290717</v>
       </c>
       <c r="I53" t="n">
-        <v>30.69885938210128</v>
+        <v>30.69884916444059</v>
       </c>
       <c r="J53" t="n">
         <v>45.79545801336116</v>
@@ -40369,16 +40369,16 @@
         <v>2.151990548444327</v>
       </c>
       <c r="F54" t="n">
-        <v>-9.164018026937349</v>
+        <v>-9.164008775321298</v>
       </c>
       <c r="G54" t="n">
         <v>-18.6852305428317</v>
       </c>
       <c r="H54" t="n">
-        <v>-1.732545046843736</v>
+        <v>-1.732536640307691</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2085154657297417</v>
+        <v>-0.2085256408230207</v>
       </c>
       <c r="J54" t="n">
         <v>3.2258064516129</v>
@@ -40401,16 +40401,16 @@
         <v>-34.47516583955436</v>
       </c>
       <c r="F55" t="n">
-        <v>-13.60930339146794</v>
+        <v>-13.60928974471389</v>
       </c>
       <c r="G55" t="n">
         <v>15.30230404450439</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.7522815575130015</v>
+        <v>-0.7522732769821516</v>
       </c>
       <c r="I55" t="n">
-        <v>-2.164478240198264</v>
+        <v>-2.164458504802436</v>
       </c>
       <c r="J55" t="n">
         <v>-10.23953527808792</v>
@@ -40421,28 +40421,28 @@
         <v>44681</v>
       </c>
       <c r="B56" t="n">
-        <v>11.25278683308917</v>
+        <v>11.25277362572343</v>
       </c>
       <c r="C56" t="n">
         <v>17.7923744286306</v>
       </c>
       <c r="D56" t="n">
-        <v>15.7463816796007</v>
+        <v>15.74637465106719</v>
       </c>
       <c r="E56" t="n">
         <v>50.56145204702873</v>
       </c>
       <c r="F56" t="n">
-        <v>10.61741275388277</v>
+        <v>10.61741361378157</v>
       </c>
       <c r="G56" t="n">
         <v>51.45866829146802</v>
       </c>
       <c r="H56" t="n">
-        <v>24.37760979872503</v>
+        <v>24.37761232843647</v>
       </c>
       <c r="I56" t="n">
-        <v>14.00828596826276</v>
+        <v>14.00827459518674</v>
       </c>
       <c r="J56" t="n">
         <v>-16.3215872474704</v>
@@ -40453,25 +40453,25 @@
         <v>44651</v>
       </c>
       <c r="B57" t="n">
-        <v>2.977280497056323</v>
+        <v>2.977292721997449</v>
       </c>
       <c r="C57" t="n">
         <v>10.95155597333577</v>
       </c>
       <c r="D57" t="n">
-        <v>22.51816022061508</v>
+        <v>22.51816766035562</v>
       </c>
       <c r="E57" t="n">
         <v>3.867848856109002</v>
       </c>
       <c r="F57" t="n">
-        <v>9.427571411441527</v>
+        <v>9.427562548959667</v>
       </c>
       <c r="G57" t="n">
         <v>49.57575942530777</v>
       </c>
       <c r="H57" t="n">
-        <v>-2.747507433571683</v>
+        <v>-2.747517525648757</v>
       </c>
       <c r="I57" t="n">
         <v>35.33520825688752</v>
@@ -40485,19 +40485,19 @@
         <v>44620</v>
       </c>
       <c r="B58" t="n">
-        <v>-8.601122038754028</v>
+        <v>-8.601111826336716</v>
       </c>
       <c r="C58" t="n">
         <v>8.295696174558387</v>
       </c>
       <c r="D58" t="n">
-        <v>-4.110909594302981</v>
+        <v>-4.110902753671142</v>
       </c>
       <c r="E58" t="n">
         <v>-1.834542248835702</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.228541856401</v>
+        <v>-1.228533210339366</v>
       </c>
       <c r="G58" t="n">
         <v>16.47058823529413</v>
@@ -40943,7 +40943,7 @@
         <v>-2.52567773584268</v>
       </c>
       <c r="F12" t="n">
-        <v>10.62650280954685</v>
+        <v>10.62651300857786</v>
       </c>
       <c r="G12" t="n">
         <v>34.61970620542895</v>
@@ -40975,7 +40975,7 @@
         <v>14.91233715805025</v>
       </c>
       <c r="F13" t="n">
-        <v>30.99526658175804</v>
+        <v>30.99526241494317</v>
       </c>
       <c r="G13" t="n">
         <v>1.64715164909115</v>
@@ -40995,7 +40995,7 @@
         <v>45291</v>
       </c>
       <c r="B14" t="n">
-        <v>9.889440308456376</v>
+        <v>9.889433557321748</v>
       </c>
       <c r="C14" t="n">
         <v>29.06510336315953</v>
@@ -41007,7 +41007,7 @@
         <v>61.77885432844141</v>
       </c>
       <c r="F14" t="n">
-        <v>24.14106185820877</v>
+        <v>24.1410543620159</v>
       </c>
       <c r="G14" t="n">
         <v>39.13101305001452</v>
@@ -41027,7 +41027,7 @@
         <v>45199</v>
       </c>
       <c r="B15" t="n">
-        <v>11.5138851303904</v>
+        <v>11.51389198132435</v>
       </c>
       <c r="C15" t="n">
         <v>5.604431410883026</v>
@@ -41045,10 +41045,10 @@
         <v>51.07063441994313</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3229764699508975</v>
+        <v>0.3229691550785674</v>
       </c>
       <c r="I15" t="n">
-        <v>-6.28072516525251</v>
+        <v>-6.280716414844623</v>
       </c>
       <c r="J15" t="n">
         <v>-8.333332214981715</v>
@@ -41077,10 +41077,10 @@
         <v>30.40188313846057</v>
       </c>
       <c r="H16" t="n">
-        <v>16.5093619544856</v>
+        <v>16.50938034711897</v>
       </c>
       <c r="I16" t="n">
-        <v>-24.563530978128</v>
+        <v>-24.56353270822924</v>
       </c>
       <c r="J16" t="n">
         <v>18.62284690483378</v>
@@ -41097,7 +41097,7 @@
         <v>-61.64719560517645</v>
       </c>
       <c r="D17" t="n">
-        <v>-54.63216110402858</v>
+        <v>-54.63216397994308</v>
       </c>
       <c r="E17" t="n">
         <v>-54.3871000029952</v>
@@ -41109,10 +41109,10 @@
         <v>-36.03738976394022</v>
       </c>
       <c r="H17" t="n">
-        <v>-30.25185472226123</v>
+        <v>-30.25186064741821</v>
       </c>
       <c r="I17" t="n">
-        <v>-76.50188726461326</v>
+        <v>-76.50188891967301</v>
       </c>
       <c r="J17" t="n">
         <v>-44.5633303309966</v>
@@ -41129,7 +41129,7 @@
         <v>-21.29460874309583</v>
       </c>
       <c r="D18" t="n">
-        <v>11.65014337487069</v>
+        <v>11.65015835466292</v>
       </c>
       <c r="E18" t="n">
         <v>-14.55237052788174</v>
@@ -41141,10 +41141,10 @@
         <v>-19.79919371493109</v>
       </c>
       <c r="H18" t="n">
-        <v>1.648564929586116</v>
+        <v>1.648558807459066</v>
       </c>
       <c r="I18" t="n">
-        <v>10.56933284767878</v>
+        <v>10.56934094130371</v>
       </c>
       <c r="J18" t="n">
         <v>-7.304651090116887</v>
@@ -41161,22 +41161,22 @@
         <v>32.99376139327897</v>
       </c>
       <c r="D19" t="n">
-        <v>57.79699390368796</v>
+        <v>57.79698273541764</v>
       </c>
       <c r="E19" t="n">
         <v>17.16418311736432</v>
       </c>
       <c r="F19" t="n">
-        <v>22.95739684156284</v>
+        <v>22.95737389779264</v>
       </c>
       <c r="G19" t="n">
         <v>42.09624763531581</v>
       </c>
       <c r="H19" t="n">
-        <v>42.03855951339208</v>
+        <v>42.03855591709831</v>
       </c>
       <c r="I19" t="n">
-        <v>39.58640544331568</v>
+        <v>39.58639522565499</v>
       </c>
       <c r="J19" t="n">
         <v>111.9602203369141</v>
@@ -41187,25 +41187,25 @@
         <v>44742</v>
       </c>
       <c r="B20" t="n">
-        <v>1.366693812815045</v>
+        <v>1.36668177907604</v>
       </c>
       <c r="C20" t="n">
         <v>4.454954472923656</v>
       </c>
       <c r="D20" t="n">
-        <v>8.743022633679765</v>
+        <v>8.74301603041523</v>
       </c>
       <c r="E20" t="n">
         <v>0.7781910896766497</v>
       </c>
       <c r="F20" t="n">
-        <v>-13.19427116070798</v>
+        <v>-13.19424793245996</v>
       </c>
       <c r="G20" t="n">
         <v>42.00431940783369</v>
       </c>
       <c r="H20" t="n">
-        <v>21.30325276170784</v>
+        <v>21.30327572677184</v>
       </c>
       <c r="I20" t="n">
         <v>11.30802202191454</v>

--- a/dashboards/Adani Group.xlsx
+++ b/dashboards/Adani Group.xlsx
@@ -486,7 +486,7 @@
         <v>44564</v>
       </c>
       <c r="B2" t="n">
-        <v>2152.12109375</v>
+        <v>2152.120849609375</v>
       </c>
       <c r="C2" t="n">
         <v>1731.099975585938</v>
@@ -498,7 +498,7 @@
         <v>1346.900024414062</v>
       </c>
       <c r="F2" t="n">
-        <v>717.017822265625</v>
+        <v>717.0178833007812</v>
       </c>
       <c r="G2" t="n">
         <v>20.26000022888184</v>
@@ -507,7 +507,7 @@
         <v>372.3961181640625</v>
       </c>
       <c r="I2" t="n">
-        <v>1741.248657226562</v>
+        <v>1741.24853515625</v>
       </c>
       <c r="J2" t="n">
         <v>114.9499969482422</v>
@@ -518,28 +518,28 @@
         <v>44565</v>
       </c>
       <c r="B3" t="n">
-        <v>2126.26318359375</v>
+        <v>2126.262939453125</v>
       </c>
       <c r="C3" t="n">
         <v>1754.949951171875</v>
       </c>
       <c r="D3" t="n">
-        <v>1715.171142578125</v>
+        <v>1715.171264648438</v>
       </c>
       <c r="E3" t="n">
         <v>1366.699951171875</v>
       </c>
       <c r="F3" t="n">
-        <v>719.5975341796875</v>
+        <v>719.597412109375</v>
       </c>
       <c r="G3" t="n">
         <v>20.11000061035156</v>
       </c>
       <c r="H3" t="n">
-        <v>375.7159729003906</v>
+        <v>375.7160034179688</v>
       </c>
       <c r="I3" t="n">
-        <v>1751.383666992188</v>
+        <v>1751.383544921875</v>
       </c>
       <c r="J3" t="n">
         <v>114.25</v>
@@ -550,7 +550,7 @@
         <v>44566</v>
       </c>
       <c r="B4" t="n">
-        <v>2142.513916015625</v>
+        <v>2142.51416015625</v>
       </c>
       <c r="C4" t="n">
         <v>1761.050048828125</v>
@@ -562,16 +562,16 @@
         <v>1399.650024414062</v>
       </c>
       <c r="F4" t="n">
-        <v>734.8314208984375</v>
+        <v>734.8313598632812</v>
       </c>
       <c r="G4" t="n">
         <v>19.96999931335449</v>
       </c>
       <c r="H4" t="n">
-        <v>378.8433227539062</v>
+        <v>378.8433532714844</v>
       </c>
       <c r="I4" t="n">
-        <v>1769.107666015625</v>
+        <v>1769.107543945312</v>
       </c>
       <c r="J4" t="n">
         <v>125.6500015258789</v>
@@ -582,7 +582,7 @@
         <v>44567</v>
       </c>
       <c r="B5" t="n">
-        <v>2129.130615234375</v>
+        <v>2129.131103515625</v>
       </c>
       <c r="C5" t="n">
         <v>1760.050048828125</v>
@@ -603,7 +603,7 @@
         <v>372.4442443847656</v>
       </c>
       <c r="I5" t="n">
-        <v>1795.868530273438</v>
+        <v>1795.86865234375</v>
       </c>
       <c r="J5" t="n">
         <v>119.9499969482422</v>
@@ -614,7 +614,7 @@
         <v>44568</v>
       </c>
       <c r="B6" t="n">
-        <v>2183.9052734375</v>
+        <v>2183.905517578125</v>
       </c>
       <c r="C6" t="n">
         <v>1776</v>
@@ -632,10 +632,10 @@
         <v>20.04000091552734</v>
       </c>
       <c r="H6" t="n">
-        <v>382.2593688964844</v>
+        <v>382.2593078613281</v>
       </c>
       <c r="I6" t="n">
-        <v>1785.184204101562</v>
+        <v>1785.18408203125</v>
       </c>
       <c r="J6" t="n">
         <v>120.0500030517578</v>
@@ -646,7 +646,7 @@
         <v>44571</v>
       </c>
       <c r="B7" t="n">
-        <v>2217.88818359375</v>
+        <v>2217.888427734375</v>
       </c>
       <c r="C7" t="n">
         <v>1819.699951171875</v>
@@ -667,7 +667,7 @@
         <v>384.2801208496094</v>
       </c>
       <c r="I7" t="n">
-        <v>1760.769897460938</v>
+        <v>1760.77001953125</v>
       </c>
       <c r="J7" t="n">
         <v>120.0500030517578</v>
@@ -678,28 +678,28 @@
         <v>44572</v>
       </c>
       <c r="B8" t="n">
-        <v>2196.332763671875</v>
+        <v>2196.33251953125</v>
       </c>
       <c r="C8" t="n">
         <v>1867.449951171875</v>
       </c>
       <c r="D8" t="n">
-        <v>1839.793090820312</v>
+        <v>1839.79296875</v>
       </c>
       <c r="E8" t="n">
         <v>1567.949951171875</v>
       </c>
       <c r="F8" t="n">
-        <v>744.7601928710938</v>
+        <v>744.76025390625</v>
       </c>
       <c r="G8" t="n">
         <v>21.70999908447266</v>
       </c>
       <c r="H8" t="n">
-        <v>382.6442260742188</v>
+        <v>382.6442565917969</v>
       </c>
       <c r="I8" t="n">
-        <v>1777.345703125</v>
+        <v>1777.345581054688</v>
       </c>
       <c r="J8" t="n">
         <v>119.6999969482422</v>
@@ -710,13 +710,13 @@
         <v>44573</v>
       </c>
       <c r="B9" t="n">
-        <v>2212.7744140625</v>
+        <v>2212.774169921875</v>
       </c>
       <c r="C9" t="n">
         <v>1928.25</v>
       </c>
       <c r="D9" t="n">
-        <v>1826.023559570312</v>
+        <v>1826.023681640625</v>
       </c>
       <c r="E9" t="n">
         <v>1647.550048828125</v>
@@ -728,10 +728,10 @@
         <v>23.8799991607666</v>
       </c>
       <c r="H9" t="n">
-        <v>382.8848266601562</v>
+        <v>382.8847961425781</v>
       </c>
       <c r="I9" t="n">
-        <v>1794.071166992188</v>
+        <v>1794.071044921875</v>
       </c>
       <c r="J9" t="n">
         <v>120</v>
@@ -742,7 +742,7 @@
         <v>44574</v>
       </c>
       <c r="B10" t="n">
-        <v>2212.153076171875</v>
+        <v>2212.152587890625</v>
       </c>
       <c r="C10" t="n">
         <v>2019.699951171875</v>
@@ -760,7 +760,7 @@
         <v>23.29000091552734</v>
       </c>
       <c r="H10" t="n">
-        <v>381.4414367675781</v>
+        <v>381.44140625</v>
       </c>
       <c r="I10" t="n">
         <v>1818.585083007812</v>
@@ -786,7 +786,7 @@
         <v>1697.949951171875</v>
       </c>
       <c r="F11" t="n">
-        <v>759.3613891601562</v>
+        <v>759.3614501953125</v>
       </c>
       <c r="G11" t="n">
         <v>23.43000030517578</v>
@@ -795,7 +795,7 @@
         <v>387.5037231445312</v>
       </c>
       <c r="I11" t="n">
-        <v>1803.207763671875</v>
+        <v>1803.207641601562</v>
       </c>
       <c r="J11" t="n">
         <v>118.9000015258789</v>
@@ -806,7 +806,7 @@
         <v>44578</v>
       </c>
       <c r="B12" t="n">
-        <v>2273.81005859375</v>
+        <v>2273.809814453125</v>
       </c>
       <c r="C12" t="n">
         <v>2002.699951171875</v>
@@ -818,16 +818,16 @@
         <v>1835.300048828125</v>
       </c>
       <c r="F12" t="n">
-        <v>758.33935546875</v>
+        <v>758.3394165039062</v>
       </c>
       <c r="G12" t="n">
         <v>23.20999908447266</v>
       </c>
       <c r="H12" t="n">
-        <v>392.4111938476562</v>
+        <v>392.4112243652344</v>
       </c>
       <c r="I12" t="n">
-        <v>1796.168090820312</v>
+        <v>1796.168212890625</v>
       </c>
       <c r="J12" t="n">
         <v>117.4000015258789</v>
@@ -859,7 +859,7 @@
         <v>366.2857666015625</v>
       </c>
       <c r="I13" t="n">
-        <v>1812.793701171875</v>
+        <v>1812.793579101562</v>
       </c>
       <c r="J13" t="n">
         <v>115.5999984741211</v>
@@ -870,7 +870,7 @@
         <v>44580</v>
       </c>
       <c r="B14" t="n">
-        <v>2133.43310546875</v>
+        <v>2133.432861328125</v>
       </c>
       <c r="C14" t="n">
         <v>2043.25</v>
@@ -882,7 +882,7 @@
         <v>1938.449951171875</v>
       </c>
       <c r="F14" t="n">
-        <v>724.4158935546875</v>
+        <v>724.4158325195312</v>
       </c>
       <c r="G14" t="n">
         <v>22.78000068664551</v>
@@ -891,7 +891,7 @@
         <v>360.7046508789062</v>
       </c>
       <c r="I14" t="n">
-        <v>1792.273803710938</v>
+        <v>1792.27392578125</v>
       </c>
       <c r="J14" t="n">
         <v>117.3000030517578</v>
@@ -914,13 +914,13 @@
         <v>1966.699951171875</v>
       </c>
       <c r="F15" t="n">
-        <v>718.3807373046875</v>
+        <v>718.3806762695312</v>
       </c>
       <c r="G15" t="n">
         <v>22.75</v>
       </c>
       <c r="H15" t="n">
-        <v>360.9452209472656</v>
+        <v>360.9451599121094</v>
       </c>
       <c r="I15" t="n">
         <v>1801.060913085938</v>
@@ -934,19 +934,19 @@
         <v>44582</v>
       </c>
       <c r="B16" t="n">
-        <v>2118.090087890625</v>
+        <v>2118.09033203125</v>
       </c>
       <c r="C16" t="n">
         <v>2066.800048828125</v>
       </c>
       <c r="D16" t="n">
-        <v>1824.277465820312</v>
+        <v>1824.277587890625</v>
       </c>
       <c r="E16" t="n">
         <v>1934.550048828125</v>
       </c>
       <c r="F16" t="n">
-        <v>704.6554565429688</v>
+        <v>704.6555786132812</v>
       </c>
       <c r="G16" t="n">
         <v>21.98999977111816</v>
@@ -972,7 +972,7 @@
         <v>2035.900024414062</v>
       </c>
       <c r="D17" t="n">
-        <v>1711.978515625</v>
+        <v>1711.978393554688</v>
       </c>
       <c r="E17" t="n">
         <v>1837.849975585938</v>
@@ -984,10 +984,10 @@
         <v>20.55999946594238</v>
       </c>
       <c r="H17" t="n">
-        <v>339.5348510742188</v>
+        <v>339.5348205566406</v>
       </c>
       <c r="I17" t="n">
-        <v>1778.543823242188</v>
+        <v>1778.543701171875</v>
       </c>
       <c r="J17" t="n">
         <v>106.6999969482422</v>
@@ -998,28 +998,28 @@
         <v>44586</v>
       </c>
       <c r="B18" t="n">
-        <v>2083.867919921875</v>
+        <v>2083.86767578125</v>
       </c>
       <c r="C18" t="n">
         <v>1992.449951171875</v>
       </c>
       <c r="D18" t="n">
-        <v>1737.521240234375</v>
+        <v>1737.521362304688</v>
       </c>
       <c r="E18" t="n">
         <v>1929</v>
       </c>
       <c r="F18" t="n">
-        <v>692.19580078125</v>
+        <v>692.1957397460938</v>
       </c>
       <c r="G18" t="n">
         <v>21.43000030517578</v>
       </c>
       <c r="H18" t="n">
-        <v>338.2357788085938</v>
+        <v>338.2357482910156</v>
       </c>
       <c r="I18" t="n">
-        <v>1822.529296875</v>
+        <v>1822.529174804688</v>
       </c>
       <c r="J18" t="n">
         <v>108.8000030517578</v>
@@ -1036,19 +1036,19 @@
         <v>2009.300048828125</v>
       </c>
       <c r="D19" t="n">
-        <v>1682.244750976562</v>
+        <v>1682.24462890625</v>
       </c>
       <c r="E19" t="n">
         <v>1910.25</v>
       </c>
       <c r="F19" t="n">
-        <v>690.2490234375</v>
+        <v>690.2489013671875</v>
       </c>
       <c r="G19" t="n">
         <v>21.1299991607666</v>
       </c>
       <c r="H19" t="n">
-        <v>338.3800964355469</v>
+        <v>338.380126953125</v>
       </c>
       <c r="I19" t="n">
         <v>1828.071166992188</v>
@@ -1062,7 +1062,7 @@
         <v>44589</v>
       </c>
       <c r="B20" t="n">
-        <v>2118.281494140625</v>
+        <v>2118.28125</v>
       </c>
       <c r="C20" t="n">
         <v>1986.800048828125</v>
@@ -1074,16 +1074,16 @@
         <v>1938.400024414062</v>
       </c>
       <c r="F20" t="n">
-        <v>691.2711181640625</v>
+        <v>691.2710571289062</v>
       </c>
       <c r="G20" t="n">
         <v>21.14999961853027</v>
       </c>
       <c r="H20" t="n">
-        <v>347.0885925292969</v>
+        <v>347.088623046875</v>
       </c>
       <c r="I20" t="n">
-        <v>1828.22119140625</v>
+        <v>1828.221069335938</v>
       </c>
       <c r="J20" t="n">
         <v>112.8499984741211</v>
@@ -1094,13 +1094,13 @@
         <v>44592</v>
       </c>
       <c r="B21" t="n">
-        <v>2185.004638671875</v>
+        <v>2185.005126953125</v>
       </c>
       <c r="C21" t="n">
         <v>1970.900024414062</v>
       </c>
       <c r="D21" t="n">
-        <v>1711.130126953125</v>
+        <v>1711.130249023438</v>
       </c>
       <c r="E21" t="n">
         <v>1877.849975585938</v>
@@ -1112,7 +1112,7 @@
         <v>21.25</v>
       </c>
       <c r="H21" t="n">
-        <v>351.3706359863281</v>
+        <v>351.3706665039062</v>
       </c>
       <c r="I21" t="n">
         <v>1818.585083007812</v>
@@ -1126,7 +1126,7 @@
         <v>44593</v>
       </c>
       <c r="B22" t="n">
-        <v>2229.7421875</v>
+        <v>2229.741943359375</v>
       </c>
       <c r="C22" t="n">
         <v>1986.900024414062</v>
@@ -1144,7 +1144,7 @@
         <v>21.60000038146973</v>
       </c>
       <c r="H22" t="n">
-        <v>366.0451965332031</v>
+        <v>366.045166015625</v>
       </c>
       <c r="I22" t="n">
         <v>1861.921630859375</v>
@@ -1170,13 +1170,13 @@
         <v>1916.300048828125</v>
       </c>
       <c r="F23" t="n">
-        <v>725.3892822265625</v>
+        <v>725.3893432617188</v>
       </c>
       <c r="G23" t="n">
         <v>21.67000007629395</v>
       </c>
       <c r="H23" t="n">
-        <v>365.6603088378906</v>
+        <v>365.6602783203125</v>
       </c>
       <c r="I23" t="n">
         <v>1874.353515625</v>
@@ -1190,19 +1190,19 @@
         <v>44595</v>
       </c>
       <c r="B24" t="n">
-        <v>2192.5087890625</v>
+        <v>2192.509033203125</v>
       </c>
       <c r="C24" t="n">
         <v>2006.199951171875</v>
       </c>
       <c r="D24" t="n">
-        <v>1747.947875976562</v>
+        <v>1747.948120117188</v>
       </c>
       <c r="E24" t="n">
         <v>1912.550048828125</v>
       </c>
       <c r="F24" t="n">
-        <v>713.02685546875</v>
+        <v>713.0269165039062</v>
       </c>
       <c r="G24" t="n">
         <v>21.52000045776367</v>
@@ -1211,7 +1211,7 @@
         <v>367.4885864257812</v>
       </c>
       <c r="I24" t="n">
-        <v>1848.940673828125</v>
+        <v>1848.940795898438</v>
       </c>
       <c r="J24" t="n">
         <v>115.1500015258789</v>
@@ -1222,7 +1222,7 @@
         <v>44596</v>
       </c>
       <c r="B25" t="n">
-        <v>2174.4892578125</v>
+        <v>2174.48974609375</v>
       </c>
       <c r="C25" t="n">
         <v>2033.099975585938</v>
@@ -1240,10 +1240,10 @@
         <v>21.70999908447266</v>
       </c>
       <c r="H25" t="n">
-        <v>366.0451965332031</v>
+        <v>366.045166015625</v>
       </c>
       <c r="I25" t="n">
-        <v>1848.391357421875</v>
+        <v>1848.3916015625</v>
       </c>
       <c r="J25" t="n">
         <v>112.9499969482422</v>
@@ -1318,7 +1318,7 @@
         <v>44601</v>
       </c>
       <c r="B28" t="n">
-        <v>2208.47265625</v>
+        <v>2208.472900390625</v>
       </c>
       <c r="C28" t="n">
         <v>1955.199951171875</v>
@@ -1336,7 +1336,7 @@
         <v>21.52000045776367</v>
       </c>
       <c r="H28" t="n">
-        <v>368.3546447753906</v>
+        <v>368.3546142578125</v>
       </c>
       <c r="I28" t="n">
         <v>1762.417358398438</v>
@@ -1350,13 +1350,13 @@
         <v>44602</v>
       </c>
       <c r="B29" t="n">
-        <v>2202.0205078125</v>
+        <v>2202.020263671875</v>
       </c>
       <c r="C29" t="n">
         <v>2036.400024414062</v>
       </c>
       <c r="D29" t="n">
-        <v>1782.121826171875</v>
+        <v>1782.121704101562</v>
       </c>
       <c r="E29" t="n">
         <v>1907.949951171875</v>
@@ -1371,7 +1371,7 @@
         <v>360.7046508789062</v>
       </c>
       <c r="I29" t="n">
-        <v>1807.90087890625</v>
+        <v>1807.901000976562</v>
       </c>
       <c r="J29" t="n">
         <v>140.8500061035156</v>
@@ -1394,7 +1394,7 @@
         <v>1907.599975585938</v>
       </c>
       <c r="F30" t="n">
-        <v>704.4608764648438</v>
+        <v>704.4608154296875</v>
       </c>
       <c r="G30" t="n">
         <v>25</v>
@@ -1426,7 +1426,7 @@
         <v>1862.150024414062</v>
       </c>
       <c r="F31" t="n">
-        <v>677.2538452148438</v>
+        <v>677.25390625</v>
       </c>
       <c r="G31" t="n">
         <v>22.67000007629395</v>
@@ -1435,7 +1435,7 @@
         <v>341.6999206542969</v>
       </c>
       <c r="I31" t="n">
-        <v>1709.794555664062</v>
+        <v>1709.794677734375</v>
       </c>
       <c r="J31" t="n">
         <v>174.3000030517578</v>
@@ -1452,7 +1452,7 @@
         <v>1926.949951171875</v>
       </c>
       <c r="D32" t="n">
-        <v>1740.364990234375</v>
+        <v>1740.364868164062</v>
       </c>
       <c r="E32" t="n">
         <v>1889.5</v>
@@ -1464,7 +1464,7 @@
         <v>23.59000015258789</v>
       </c>
       <c r="H32" t="n">
-        <v>349.8310241699219</v>
+        <v>349.8310546875</v>
       </c>
       <c r="I32" t="n">
         <v>1735.1572265625</v>
@@ -1484,7 +1484,7 @@
         <v>1932.550048828125</v>
       </c>
       <c r="D33" t="n">
-        <v>1734.228515625</v>
+        <v>1734.228637695312</v>
       </c>
       <c r="E33" t="n">
         <v>1931.75</v>
@@ -1496,7 +1496,7 @@
         <v>25.35000038146973</v>
       </c>
       <c r="H33" t="n">
-        <v>347.0885925292969</v>
+        <v>347.088623046875</v>
       </c>
       <c r="I33" t="n">
         <v>1683.882568359375</v>
@@ -1510,7 +1510,7 @@
         <v>44609</v>
       </c>
       <c r="B34" t="n">
-        <v>2128.701171875</v>
+        <v>2128.700927734375</v>
       </c>
       <c r="C34" t="n">
         <v>2020.849975585938</v>
@@ -1522,7 +1522,7 @@
         <v>2047.599975585938</v>
       </c>
       <c r="F34" t="n">
-        <v>714.681640625</v>
+        <v>714.6817016601562</v>
       </c>
       <c r="G34" t="n">
         <v>26.39999961853027</v>
@@ -1531,7 +1531,7 @@
         <v>346.2225646972656</v>
       </c>
       <c r="I34" t="n">
-        <v>1724.3232421875</v>
+        <v>1724.323364257812</v>
       </c>
       <c r="J34" t="n">
         <v>163.6000061035156</v>
@@ -1548,7 +1548,7 @@
         <v>1958.099975585938</v>
       </c>
       <c r="D35" t="n">
-        <v>1732.432739257812</v>
+        <v>1732.4326171875</v>
       </c>
       <c r="E35" t="n">
         <v>2041.849975585938</v>
@@ -1563,7 +1563,7 @@
         <v>325.5820007324219</v>
       </c>
       <c r="I35" t="n">
-        <v>1662.763549804688</v>
+        <v>1662.763427734375</v>
       </c>
       <c r="J35" t="n">
         <v>164.6499938964844</v>
@@ -1574,7 +1574,7 @@
         <v>44613</v>
       </c>
       <c r="B36" t="n">
-        <v>2088.599609375</v>
+        <v>2088.599853515625</v>
       </c>
       <c r="C36" t="n">
         <v>1895.900024414062</v>
@@ -1586,7 +1586,7 @@
         <v>1955.900024414062</v>
       </c>
       <c r="F36" t="n">
-        <v>692.19580078125</v>
+        <v>692.1957397460938</v>
       </c>
       <c r="G36" t="n">
         <v>24.03000068664551</v>
@@ -1656,10 +1656,10 @@
         <v>25.11000061035156</v>
       </c>
       <c r="H38" t="n">
-        <v>318.4612426757812</v>
+        <v>318.4612731933594</v>
       </c>
       <c r="I38" t="n">
-        <v>1639.39794921875</v>
+        <v>1639.397827148438</v>
       </c>
       <c r="J38" t="n">
         <v>149.6999969482422</v>
@@ -1670,7 +1670,7 @@
         <v>44616</v>
       </c>
       <c r="B39" t="n">
-        <v>1925.232299804688</v>
+        <v>1925.232177734375</v>
       </c>
       <c r="C39" t="n">
         <v>1957.300048828125</v>
@@ -1702,19 +1702,19 @@
         <v>44617</v>
       </c>
       <c r="B40" t="n">
-        <v>1968.774536132812</v>
+        <v>1968.774658203125</v>
       </c>
       <c r="C40" t="n">
         <v>2032.849975585938</v>
       </c>
       <c r="D40" t="n">
-        <v>1615.094482421875</v>
+        <v>1615.094604492188</v>
       </c>
       <c r="E40" t="n">
         <v>1923.5</v>
       </c>
       <c r="F40" t="n">
-        <v>676.6697998046875</v>
+        <v>676.6697387695312</v>
       </c>
       <c r="G40" t="n">
         <v>24.80999946594238</v>
@@ -1723,7 +1723,7 @@
         <v>297.0508422851562</v>
       </c>
       <c r="I40" t="n">
-        <v>1570.89794921875</v>
+        <v>1570.898071289062</v>
       </c>
       <c r="J40" t="n">
         <v>143.9499969482422</v>
@@ -1740,22 +1740,22 @@
         <v>2134.39990234375</v>
       </c>
       <c r="D41" t="n">
-        <v>1640.787231445312</v>
+        <v>1640.787109375</v>
       </c>
       <c r="E41" t="n">
         <v>1843.400024414062</v>
       </c>
       <c r="F41" t="n">
-        <v>688.6914672851562</v>
+        <v>688.6915283203125</v>
       </c>
       <c r="G41" t="n">
         <v>24.75</v>
       </c>
       <c r="H41" t="n">
-        <v>302.3914794921875</v>
+        <v>302.3914489746094</v>
       </c>
       <c r="I41" t="n">
-        <v>1586.17578125</v>
+        <v>1586.175659179688</v>
       </c>
       <c r="J41" t="n">
         <v>149.25</v>
@@ -1778,7 +1778,7 @@
         <v>1882.550048828125</v>
       </c>
       <c r="F42" t="n">
-        <v>691.4169921875</v>
+        <v>691.4170532226562</v>
       </c>
       <c r="G42" t="n">
         <v>24.6200008392334</v>
@@ -1787,7 +1787,7 @@
         <v>292.6725769042969</v>
       </c>
       <c r="I42" t="n">
-        <v>1665.45947265625</v>
+        <v>1665.459594726562</v>
       </c>
       <c r="J42" t="n">
         <v>153.5</v>
@@ -1836,22 +1836,22 @@
         <v>2323.199951171875</v>
       </c>
       <c r="D44" t="n">
-        <v>1611.402709960938</v>
+        <v>1611.40283203125</v>
       </c>
       <c r="E44" t="n">
         <v>1894.300048828125</v>
       </c>
       <c r="F44" t="n">
-        <v>681.536865234375</v>
+        <v>681.5369873046875</v>
       </c>
       <c r="G44" t="n">
         <v>23.95000076293945</v>
       </c>
       <c r="H44" t="n">
-        <v>281.5584716796875</v>
+        <v>281.5584106445312</v>
       </c>
       <c r="I44" t="n">
-        <v>1802.55859375</v>
+        <v>1802.558471679688</v>
       </c>
       <c r="J44" t="n">
         <v>167.6999969482422</v>
@@ -1868,19 +1868,19 @@
         <v>2207.35009765625</v>
       </c>
       <c r="D45" t="n">
-        <v>1560.56640625</v>
+        <v>1560.566162109375</v>
       </c>
       <c r="E45" t="n">
         <v>1803.75</v>
       </c>
       <c r="F45" t="n">
-        <v>659.781005859375</v>
+        <v>659.7810668945312</v>
       </c>
       <c r="G45" t="n">
         <v>23.29000091552734</v>
       </c>
       <c r="H45" t="n">
-        <v>270.588623046875</v>
+        <v>270.5885925292969</v>
       </c>
       <c r="I45" t="n">
         <v>1712.440673828125</v>
@@ -1894,7 +1894,7 @@
         <v>44628</v>
       </c>
       <c r="B46" t="n">
-        <v>1875.61962890625</v>
+        <v>1875.619873046875</v>
       </c>
       <c r="C46" t="n">
         <v>2217</v>
@@ -1906,16 +1906,16 @@
         <v>1783.949951171875</v>
       </c>
       <c r="F46" t="n">
-        <v>670.5372924804688</v>
+        <v>670.5372314453125</v>
       </c>
       <c r="G46" t="n">
         <v>23.73999977111816</v>
       </c>
       <c r="H46" t="n">
-        <v>272.2244873046875</v>
+        <v>272.2244567871094</v>
       </c>
       <c r="I46" t="n">
-        <v>1627.265502929688</v>
+        <v>1627.265380859375</v>
       </c>
       <c r="J46" t="n">
         <v>172.3500061035156</v>
@@ -1932,22 +1932,22 @@
         <v>2164.64990234375</v>
       </c>
       <c r="D47" t="n">
-        <v>1652.860473632812</v>
+        <v>1652.8603515625</v>
       </c>
       <c r="E47" t="n">
         <v>1828.75</v>
       </c>
       <c r="F47" t="n">
-        <v>695.115966796875</v>
+        <v>695.1160888671875</v>
       </c>
       <c r="G47" t="n">
         <v>24.26000022888184</v>
       </c>
       <c r="H47" t="n">
-        <v>280.6442260742188</v>
+        <v>280.6442565917969</v>
       </c>
       <c r="I47" t="n">
-        <v>1612.986328125</v>
+        <v>1612.986450195312</v>
       </c>
       <c r="J47" t="n">
         <v>176.3500061035156</v>
@@ -1970,13 +1970,13 @@
         <v>1881.849975585938</v>
       </c>
       <c r="F48" t="n">
-        <v>710.9827880859375</v>
+        <v>710.9827270507812</v>
       </c>
       <c r="G48" t="n">
         <v>24.5</v>
       </c>
       <c r="H48" t="n">
-        <v>282.1357727050781</v>
+        <v>282.1358032226562</v>
       </c>
       <c r="I48" t="n">
         <v>1693.568481445312</v>
@@ -1990,19 +1990,19 @@
         <v>44631</v>
       </c>
       <c r="B49" t="n">
-        <v>1951.902587890625</v>
+        <v>1951.902465820312</v>
       </c>
       <c r="C49" t="n">
         <v>2307.25</v>
       </c>
       <c r="D49" t="n">
-        <v>1730.237426757812</v>
+        <v>1730.237548828125</v>
       </c>
       <c r="E49" t="n">
         <v>1860.050048828125</v>
       </c>
       <c r="F49" t="n">
-        <v>710.0579223632812</v>
+        <v>710.0579833984375</v>
       </c>
       <c r="G49" t="n">
         <v>24.36000061035156</v>
@@ -2022,7 +2022,7 @@
         <v>44634</v>
       </c>
       <c r="B50" t="n">
-        <v>1967.340942382812</v>
+        <v>1967.3408203125</v>
       </c>
       <c r="C50" t="n">
         <v>2268.300048828125</v>
@@ -2034,7 +2034,7 @@
         <v>1822.400024414062</v>
       </c>
       <c r="F50" t="n">
-        <v>711.1287231445312</v>
+        <v>711.1287841796875</v>
       </c>
       <c r="G50" t="n">
         <v>24.43000030517578</v>
@@ -2043,7 +2043,7 @@
         <v>280.2112731933594</v>
       </c>
       <c r="I50" t="n">
-        <v>1647.935180664062</v>
+        <v>1647.93505859375</v>
       </c>
       <c r="J50" t="n">
         <v>162.8999938964844</v>
@@ -2060,13 +2060,13 @@
         <v>2217.550048828125</v>
       </c>
       <c r="D51" t="n">
-        <v>1697.610473632812</v>
+        <v>1697.6103515625</v>
       </c>
       <c r="E51" t="n">
         <v>1798.75</v>
       </c>
       <c r="F51" t="n">
-        <v>702.1246948242188</v>
+        <v>702.1246337890625</v>
       </c>
       <c r="G51" t="n">
         <v>24.45999908447266</v>
@@ -2118,13 +2118,13 @@
         <v>44637</v>
       </c>
       <c r="B53" t="n">
-        <v>2029.093383789062</v>
+        <v>2029.09326171875</v>
       </c>
       <c r="C53" t="n">
         <v>2389.800048828125</v>
       </c>
       <c r="D53" t="n">
-        <v>1815.59716796875</v>
+        <v>1815.597045898438</v>
       </c>
       <c r="E53" t="n">
         <v>1901.199951171875</v>
@@ -2136,7 +2136,7 @@
         <v>25.02000045776367</v>
       </c>
       <c r="H53" t="n">
-        <v>294.6452331542969</v>
+        <v>294.645263671875</v>
       </c>
       <c r="I53" t="n">
         <v>1764.214965820312</v>
@@ -2150,7 +2150,7 @@
         <v>44641</v>
       </c>
       <c r="B54" t="n">
-        <v>1965.142211914062</v>
+        <v>1965.14208984375</v>
       </c>
       <c r="C54" t="n">
         <v>2289.050048828125</v>
@@ -2162,16 +2162,16 @@
         <v>1876.050048828125</v>
       </c>
       <c r="F54" t="n">
-        <v>715.6065063476562</v>
+        <v>715.6064453125</v>
       </c>
       <c r="G54" t="n">
         <v>24.90999984741211</v>
       </c>
       <c r="H54" t="n">
-        <v>289.0159606933594</v>
+        <v>289.0159912109375</v>
       </c>
       <c r="I54" t="n">
-        <v>1811.495727539062</v>
+        <v>1811.49560546875</v>
       </c>
       <c r="J54" t="n">
         <v>227.25</v>
@@ -2182,7 +2182,7 @@
         <v>44642</v>
       </c>
       <c r="B55" t="n">
-        <v>1967.579833984375</v>
+        <v>1967.579711914062</v>
       </c>
       <c r="C55" t="n">
         <v>2338.050048828125</v>
@@ -2194,7 +2194,7 @@
         <v>1877.449951171875</v>
       </c>
       <c r="F55" t="n">
-        <v>719.5001831054688</v>
+        <v>719.5000610351562</v>
       </c>
       <c r="G55" t="n">
         <v>24.75</v>
@@ -2203,7 +2203,7 @@
         <v>289.5452270507812</v>
       </c>
       <c r="I55" t="n">
-        <v>1881.193237304688</v>
+        <v>1881.193359375</v>
       </c>
       <c r="J55" t="n">
         <v>238.6000061035156</v>
@@ -2214,13 +2214,13 @@
         <v>44643</v>
       </c>
       <c r="B56" t="n">
-        <v>1978.525146484375</v>
+        <v>1978.525024414062</v>
       </c>
       <c r="C56" t="n">
         <v>2406.699951171875</v>
       </c>
       <c r="D56" t="n">
-        <v>1806.96630859375</v>
+        <v>1806.966186523438</v>
       </c>
       <c r="E56" t="n">
         <v>1921.400024414062</v>
@@ -2235,7 +2235,7 @@
         <v>286.6103210449219</v>
       </c>
       <c r="I56" t="n">
-        <v>1895.222778320312</v>
+        <v>1895.223022460938</v>
       </c>
       <c r="J56" t="n">
         <v>250.5</v>
@@ -2246,13 +2246,13 @@
         <v>44644</v>
       </c>
       <c r="B57" t="n">
-        <v>1988.705444335938</v>
+        <v>1988.70556640625</v>
       </c>
       <c r="C57" t="n">
         <v>2414.39990234375</v>
       </c>
       <c r="D57" t="n">
-        <v>1828.7177734375</v>
+        <v>1828.717895507812</v>
       </c>
       <c r="E57" t="n">
         <v>1911.400024414062</v>
@@ -2264,7 +2264,7 @@
         <v>26.43000030517578</v>
       </c>
       <c r="H57" t="n">
-        <v>285.8404846191406</v>
+        <v>285.8404541015625</v>
       </c>
       <c r="I57" t="n">
         <v>1976.853271484375</v>
@@ -2278,7 +2278,7 @@
         <v>44645</v>
       </c>
       <c r="B58" t="n">
-        <v>1973.219482421875</v>
+        <v>1973.219604492188</v>
       </c>
       <c r="C58" t="n">
         <v>2448.75</v>
@@ -2290,7 +2290,7 @@
         <v>1921.25</v>
       </c>
       <c r="F58" t="n">
-        <v>723.4911499023438</v>
+        <v>723.4910888671875</v>
       </c>
       <c r="G58" t="n">
         <v>28.63999938964844</v>
@@ -2299,7 +2299,7 @@
         <v>286.5621948242188</v>
       </c>
       <c r="I58" t="n">
-        <v>2051.593994140625</v>
+        <v>2051.59375</v>
       </c>
       <c r="J58" t="n">
         <v>252.1000061035156</v>
@@ -2310,19 +2310,19 @@
         <v>44648</v>
       </c>
       <c r="B59" t="n">
-        <v>1968.869995117188</v>
+        <v>1968.8701171875</v>
       </c>
       <c r="C59" t="n">
         <v>2439</v>
       </c>
       <c r="D59" t="n">
-        <v>1905.446411132812</v>
+        <v>1905.446533203125</v>
       </c>
       <c r="E59" t="n">
         <v>1930.849975585938</v>
       </c>
       <c r="F59" t="n">
-        <v>717.4072265625</v>
+        <v>717.4072875976562</v>
       </c>
       <c r="G59" t="n">
         <v>30.45000076293945</v>
@@ -2342,7 +2342,7 @@
         <v>44649</v>
       </c>
       <c r="B60" t="n">
-        <v>2034.733520507812</v>
+        <v>2034.733642578125</v>
       </c>
       <c r="C60" t="n">
         <v>2461.550048828125</v>
@@ -2363,7 +2363,7 @@
         <v>291.0367431640625</v>
       </c>
       <c r="I60" t="n">
-        <v>2177.609130859375</v>
+        <v>2177.609375</v>
       </c>
       <c r="J60" t="n">
         <v>227.5500030517578</v>
@@ -2386,7 +2386,7 @@
         <v>1857.150024414062</v>
       </c>
       <c r="F61" t="n">
-        <v>746.9991455078125</v>
+        <v>746.9990844726562</v>
       </c>
       <c r="G61" t="n">
         <v>34.29999923706055</v>
@@ -2395,7 +2395,7 @@
         <v>297.8175964355469</v>
       </c>
       <c r="I61" t="n">
-        <v>2121.541015625</v>
+        <v>2121.541259765625</v>
       </c>
       <c r="J61" t="n">
         <v>238.8999938964844</v>
@@ -2412,22 +2412,22 @@
         <v>2368.14990234375</v>
       </c>
       <c r="D62" t="n">
-        <v>2010.262329101562</v>
+        <v>2010.262573242188</v>
       </c>
       <c r="E62" t="n">
         <v>1914.699951171875</v>
       </c>
       <c r="F62" t="n">
-        <v>753.6182861328125</v>
+        <v>753.6183471679688</v>
       </c>
       <c r="G62" t="n">
         <v>37.02000045776367</v>
       </c>
       <c r="H62" t="n">
-        <v>294.0831909179688</v>
+        <v>294.0832214355469</v>
       </c>
       <c r="I62" t="n">
-        <v>2146.654296875</v>
+        <v>2146.654541015625</v>
       </c>
       <c r="J62" t="n">
         <v>227</v>
@@ -2450,7 +2450,7 @@
         <v>1945.099975585938</v>
       </c>
       <c r="F63" t="n">
-        <v>764.8612670898438</v>
+        <v>764.861328125</v>
       </c>
       <c r="G63" t="n">
         <v>40.68999862670898</v>
@@ -2476,13 +2476,13 @@
         <v>2453.5</v>
       </c>
       <c r="D64" t="n">
-        <v>2061.248779296875</v>
+        <v>2061.24853515625</v>
       </c>
       <c r="E64" t="n">
         <v>2110.449951171875</v>
       </c>
       <c r="F64" t="n">
-        <v>796.7892456054688</v>
+        <v>796.789306640625</v>
       </c>
       <c r="G64" t="n">
         <v>42.38999938964844</v>
@@ -2502,7 +2502,7 @@
         <v>44656</v>
       </c>
       <c r="B65" t="n">
-        <v>2111.84765625</v>
+        <v>2111.847412109375</v>
       </c>
       <c r="C65" t="n">
         <v>2443.85009765625</v>
@@ -2523,7 +2523,7 @@
         <v>311.3302001953125</v>
       </c>
       <c r="I65" t="n">
-        <v>2464.53857421875</v>
+        <v>2464.538818359375</v>
       </c>
       <c r="J65" t="n">
         <v>224.5</v>
@@ -2540,7 +2540,7 @@
         <v>2484.050048828125</v>
       </c>
       <c r="D66" t="n">
-        <v>2155.188720703125</v>
+        <v>2155.18896484375</v>
       </c>
       <c r="E66" t="n">
         <v>2197.39990234375</v>
@@ -2552,7 +2552,7 @@
         <v>48.95000076293945</v>
       </c>
       <c r="H66" t="n">
-        <v>315.162841796875</v>
+        <v>315.1628723144531</v>
       </c>
       <c r="I66" t="n">
         <v>2533.23779296875</v>
@@ -2572,7 +2572,7 @@
         <v>2449.64990234375</v>
       </c>
       <c r="D67" t="n">
-        <v>2094.374755859375</v>
+        <v>2094.37451171875</v>
       </c>
       <c r="E67" t="n">
         <v>2166</v>
@@ -2584,7 +2584,7 @@
         <v>46.5099983215332</v>
       </c>
       <c r="H67" t="n">
-        <v>319.9782409667969</v>
+        <v>319.978271484375</v>
       </c>
       <c r="I67" t="n">
         <v>2359.242919921875</v>
@@ -2610,7 +2610,7 @@
         <v>2321.85009765625</v>
       </c>
       <c r="F68" t="n">
-        <v>816.9877319335938</v>
+        <v>816.9876098632812</v>
       </c>
       <c r="G68" t="n">
         <v>44.18999862670898</v>
@@ -2636,7 +2636,7 @@
         <v>2756.5</v>
       </c>
       <c r="D69" t="n">
-        <v>2175.34375</v>
+        <v>2175.343505859375</v>
       </c>
       <c r="E69" t="n">
         <v>2665.14990234375</v>
@@ -2651,7 +2651,7 @@
         <v>353.9808654785156</v>
       </c>
       <c r="I69" t="n">
-        <v>2661.100830078125</v>
+        <v>2661.1005859375</v>
       </c>
       <c r="J69" t="n">
         <v>214.4499969482422</v>
@@ -2674,13 +2674,13 @@
         <v>2792.39990234375</v>
       </c>
       <c r="F70" t="n">
-        <v>822.4387817382812</v>
+        <v>822.4388427734375</v>
       </c>
       <c r="G70" t="n">
         <v>46.15999984741211</v>
       </c>
       <c r="H70" t="n">
-        <v>353.4403686523438</v>
+        <v>353.4403381347656</v>
       </c>
       <c r="I70" t="n">
         <v>2498.388916015625</v>
@@ -2712,7 +2712,7 @@
         <v>44.65000152587891</v>
       </c>
       <c r="H71" t="n">
-        <v>362.8255004882812</v>
+        <v>362.8254699707031</v>
       </c>
       <c r="I71" t="n">
         <v>2497.190673828125</v>
@@ -2738,7 +2738,7 @@
         <v>2970.5</v>
       </c>
       <c r="F72" t="n">
-        <v>820.29736328125</v>
+        <v>820.2973022460938</v>
       </c>
       <c r="G72" t="n">
         <v>46.88000106811523</v>
@@ -2758,13 +2758,13 @@
         <v>44670</v>
       </c>
       <c r="B73" t="n">
-        <v>2020.335815429688</v>
+        <v>2020.335693359375</v>
       </c>
       <c r="C73" t="n">
         <v>2598.050048828125</v>
       </c>
       <c r="D73" t="n">
-        <v>2163.47021484375</v>
+        <v>2163.470458984375</v>
       </c>
       <c r="E73" t="n">
         <v>2911.949951171875</v>
@@ -2776,10 +2776,10 @@
         <v>46.4900016784668</v>
       </c>
       <c r="H73" t="n">
-        <v>348.1336059570312</v>
+        <v>348.1336364746094</v>
       </c>
       <c r="I73" t="n">
-        <v>2365.93310546875</v>
+        <v>2365.933349609375</v>
       </c>
       <c r="J73" t="n">
         <v>218.75</v>
@@ -2796,7 +2796,7 @@
         <v>2687.550048828125</v>
       </c>
       <c r="D74" t="n">
-        <v>2179.085693359375</v>
+        <v>2179.08544921875</v>
       </c>
       <c r="E74" t="n">
         <v>2810.85009765625</v>
@@ -2811,7 +2811,7 @@
         <v>364.8891906738281</v>
       </c>
       <c r="I74" t="n">
-        <v>2474.7734375</v>
+        <v>2474.773681640625</v>
       </c>
       <c r="J74" t="n">
         <v>213.0500030517578</v>
@@ -2834,16 +2834,16 @@
         <v>2811.5</v>
       </c>
       <c r="F75" t="n">
-        <v>827.8899536132812</v>
+        <v>827.889892578125</v>
       </c>
       <c r="G75" t="n">
         <v>49.36000061035156</v>
       </c>
       <c r="H75" t="n">
-        <v>370.8347473144531</v>
+        <v>370.8347778320312</v>
       </c>
       <c r="I75" t="n">
-        <v>2439.775146484375</v>
+        <v>2439.77490234375</v>
       </c>
       <c r="J75" t="n">
         <v>214.3500061035156</v>
@@ -2866,7 +2866,7 @@
         <v>2882.800048828125</v>
       </c>
       <c r="F76" t="n">
-        <v>850.9111938476562</v>
+        <v>850.9112548828125</v>
       </c>
       <c r="G76" t="n">
         <v>51.81999969482422</v>
@@ -2875,7 +2875,7 @@
         <v>367.7391357421875</v>
       </c>
       <c r="I76" t="n">
-        <v>2409.46923828125</v>
+        <v>2409.469482421875</v>
       </c>
       <c r="J76" t="n">
         <v>211.1999969482422</v>
@@ -2886,7 +2886,7 @@
         <v>44676</v>
       </c>
       <c r="B77" t="n">
-        <v>2222.27099609375</v>
+        <v>2222.271240234375</v>
       </c>
       <c r="C77" t="n">
         <v>2615.89990234375</v>
@@ -2898,7 +2898,7 @@
         <v>2824</v>
       </c>
       <c r="F77" t="n">
-        <v>836.6993408203125</v>
+        <v>836.6992797851562</v>
       </c>
       <c r="G77" t="n">
         <v>54.40999984741211</v>
@@ -2918,7 +2918,7 @@
         <v>44677</v>
       </c>
       <c r="B78" t="n">
-        <v>2270.704345703125</v>
+        <v>2270.7041015625</v>
       </c>
       <c r="C78" t="n">
         <v>2812.550048828125</v>
@@ -2936,7 +2936,7 @@
         <v>57.13000106811523</v>
       </c>
       <c r="H78" t="n">
-        <v>378.5000305175781</v>
+        <v>378.5000915527344</v>
       </c>
       <c r="I78" t="n">
         <v>2558.750732421875</v>
@@ -2962,7 +2962,7 @@
         <v>2841.64990234375</v>
       </c>
       <c r="F79" t="n">
-        <v>863.7116088867188</v>
+        <v>863.711669921875</v>
       </c>
       <c r="G79" t="n">
         <v>59.84000015258789</v>
@@ -2971,7 +2971,7 @@
         <v>377.9104309082031</v>
       </c>
       <c r="I79" t="n">
-        <v>2499.337646484375</v>
+        <v>2499.337890625</v>
       </c>
       <c r="J79" t="n">
         <v>200.8999938964844</v>
@@ -2982,7 +2982,7 @@
         <v>44679</v>
       </c>
       <c r="B80" t="n">
-        <v>2334.95361328125</v>
+        <v>2334.9541015625</v>
       </c>
       <c r="C80" t="n">
         <v>2796.64990234375</v>
@@ -3000,10 +3000,10 @@
         <v>56.84999847412109</v>
       </c>
       <c r="H80" t="n">
-        <v>376.7311401367188</v>
+        <v>376.7311706542969</v>
       </c>
       <c r="I80" t="n">
-        <v>2558.8505859375</v>
+        <v>2558.850830078125</v>
       </c>
       <c r="J80" t="n">
         <v>199.8999938964844</v>
@@ -3020,13 +3020,13 @@
         <v>2789.5</v>
       </c>
       <c r="D81" t="n">
-        <v>2326.8056640625</v>
+        <v>2326.805908203125</v>
       </c>
       <c r="E81" t="n">
         <v>2882.800048828125</v>
       </c>
       <c r="F81" t="n">
-        <v>833.6331176757812</v>
+        <v>833.633056640625</v>
       </c>
       <c r="G81" t="n">
         <v>56.06999969482422</v>
@@ -3035,7 +3035,7 @@
         <v>365.773681640625</v>
       </c>
       <c r="I81" t="n">
-        <v>2447.363525390625</v>
+        <v>2447.36376953125</v>
       </c>
       <c r="J81" t="n">
         <v>189.9499969482422</v>
@@ -3064,10 +3064,10 @@
         <v>56.06999969482422</v>
       </c>
       <c r="H82" t="n">
-        <v>371.6209106445312</v>
+        <v>371.6209411621094</v>
       </c>
       <c r="I82" t="n">
-        <v>2484.559326171875</v>
+        <v>2484.55908203125</v>
       </c>
       <c r="J82" t="n">
         <v>186.3999938964844</v>
@@ -3090,16 +3090,16 @@
         <v>2671.35009765625</v>
       </c>
       <c r="F83" t="n">
-        <v>791.1920776367188</v>
+        <v>791.192138671875</v>
       </c>
       <c r="G83" t="n">
         <v>53.27000045776367</v>
       </c>
       <c r="H83" t="n">
-        <v>361.7444458007812</v>
+        <v>361.7444763183594</v>
       </c>
       <c r="I83" t="n">
-        <v>2443.469482421875</v>
+        <v>2443.4697265625</v>
       </c>
       <c r="J83" t="n">
         <v>180.25</v>
@@ -3116,7 +3116,7 @@
         <v>2801.64990234375</v>
       </c>
       <c r="D84" t="n">
-        <v>2250.376220703125</v>
+        <v>2250.37646484375</v>
       </c>
       <c r="E84" t="n">
         <v>2845.89990234375</v>
@@ -3131,7 +3131,7 @@
         <v>360.0246887207031</v>
       </c>
       <c r="I84" t="n">
-        <v>2446.91455078125</v>
+        <v>2446.914794921875</v>
       </c>
       <c r="J84" t="n">
         <v>180.3500061035156</v>
@@ -3142,19 +3142,19 @@
         <v>44687</v>
       </c>
       <c r="B85" t="n">
-        <v>2205.963134765625</v>
+        <v>2205.962890625</v>
       </c>
       <c r="C85" t="n">
         <v>2816.5</v>
       </c>
       <c r="D85" t="n">
-        <v>2242.693115234375</v>
+        <v>2242.693359375</v>
       </c>
       <c r="E85" t="n">
         <v>2874.800048828125</v>
       </c>
       <c r="F85" t="n">
-        <v>789.8294677734375</v>
+        <v>789.8292846679688</v>
       </c>
       <c r="G85" t="n">
         <v>58.40999984741211</v>
@@ -3163,7 +3163,7 @@
         <v>359.091064453125</v>
       </c>
       <c r="I85" t="n">
-        <v>2434.0830078125</v>
+        <v>2434.083251953125</v>
       </c>
       <c r="J85" t="n">
         <v>174.3500061035156</v>
@@ -3180,7 +3180,7 @@
         <v>2703.449951171875</v>
       </c>
       <c r="D86" t="n">
-        <v>2192.755126953125</v>
+        <v>2192.7548828125</v>
       </c>
       <c r="E86" t="n">
         <v>2706.39990234375</v>
@@ -3218,7 +3218,7 @@
         <v>2486.699951171875</v>
       </c>
       <c r="F87" t="n">
-        <v>748.6538696289062</v>
+        <v>748.6539306640625</v>
       </c>
       <c r="G87" t="n">
         <v>53.5099983215332</v>
@@ -3227,7 +3227,7 @@
         <v>352.0154113769531</v>
       </c>
       <c r="I87" t="n">
-        <v>2357.19580078125</v>
+        <v>2357.195556640625</v>
       </c>
       <c r="J87" t="n">
         <v>166.1499938964844</v>
@@ -3238,28 +3238,28 @@
         <v>44692</v>
       </c>
       <c r="B88" t="n">
-        <v>2129.53125</v>
+        <v>2129.531005859375</v>
       </c>
       <c r="C88" t="n">
         <v>2296</v>
       </c>
       <c r="D88" t="n">
-        <v>2114.579833984375</v>
+        <v>2114.57958984375</v>
       </c>
       <c r="E88" t="n">
         <v>2648.050048828125</v>
       </c>
       <c r="F88" t="n">
-        <v>739.6985473632812</v>
+        <v>739.698486328125</v>
       </c>
       <c r="G88" t="n">
         <v>51.06000137329102</v>
       </c>
       <c r="H88" t="n">
-        <v>352.8507385253906</v>
+        <v>352.8507080078125</v>
       </c>
       <c r="I88" t="n">
-        <v>2351.604248046875</v>
+        <v>2351.60400390625</v>
       </c>
       <c r="J88" t="n">
         <v>157.9499969482422</v>
@@ -3270,28 +3270,28 @@
         <v>44693</v>
       </c>
       <c r="B89" t="n">
-        <v>2139.109619140625</v>
+        <v>2139.109375</v>
       </c>
       <c r="C89" t="n">
         <v>2187.050048828125</v>
       </c>
       <c r="D89" t="n">
-        <v>2040.644653320312</v>
+        <v>2040.64453125</v>
       </c>
       <c r="E89" t="n">
         <v>2436.800048828125</v>
       </c>
       <c r="F89" t="n">
-        <v>694.3373413085938</v>
+        <v>694.3372802734375</v>
       </c>
       <c r="G89" t="n">
         <v>48.5099983215332</v>
       </c>
       <c r="H89" t="n">
-        <v>367.1003723144531</v>
+        <v>367.100341796875</v>
       </c>
       <c r="I89" t="n">
-        <v>2290.74365234375</v>
+        <v>2290.743408203125</v>
       </c>
       <c r="J89" t="n">
         <v>150.3500061035156</v>
@@ -3302,13 +3302,13 @@
         <v>44694</v>
       </c>
       <c r="B90" t="n">
-        <v>2076.136962890625</v>
+        <v>2076.13720703125</v>
       </c>
       <c r="C90" t="n">
         <v>2190.60009765625</v>
       </c>
       <c r="D90" t="n">
-        <v>2049.57470703125</v>
+        <v>2049.574462890625</v>
       </c>
       <c r="E90" t="n">
         <v>2171.550048828125</v>
@@ -3334,7 +3334,7 @@
         <v>44697</v>
       </c>
       <c r="B91" t="n">
-        <v>2157.5791015625</v>
+        <v>2157.578857421875</v>
       </c>
       <c r="C91" t="n">
         <v>2249.89990234375</v>
@@ -3346,7 +3346,7 @@
         <v>2281.699951171875</v>
       </c>
       <c r="F91" t="n">
-        <v>693.55859375</v>
+        <v>693.5585327148438</v>
       </c>
       <c r="G91" t="n">
         <v>53.47000122070312</v>
@@ -3355,7 +3355,7 @@
         <v>361.6461791992188</v>
       </c>
       <c r="I91" t="n">
-        <v>2385.055419921875</v>
+        <v>2385.05517578125</v>
       </c>
       <c r="J91" t="n">
         <v>165.3500061035156</v>
@@ -3372,19 +3372,19 @@
         <v>2333.39990234375</v>
       </c>
       <c r="D92" t="n">
-        <v>2179.983642578125</v>
+        <v>2179.98388671875</v>
       </c>
       <c r="E92" t="n">
         <v>2285.800048828125</v>
       </c>
       <c r="F92" t="n">
-        <v>724.9512939453125</v>
+        <v>724.9512329101562</v>
       </c>
       <c r="G92" t="n">
         <v>56.13999938964844</v>
       </c>
       <c r="H92" t="n">
-        <v>362.4323425292969</v>
+        <v>362.432373046875</v>
       </c>
       <c r="I92" t="n">
         <v>2496.84130859375</v>
@@ -3398,7 +3398,7 @@
         <v>44699</v>
       </c>
       <c r="B93" t="n">
-        <v>2197.3173828125</v>
+        <v>2197.317626953125</v>
       </c>
       <c r="C93" t="n">
         <v>2316</v>
@@ -3416,7 +3416,7 @@
         <v>58.93999862670898</v>
       </c>
       <c r="H93" t="n">
-        <v>354.8653259277344</v>
+        <v>354.8652954101562</v>
       </c>
       <c r="I93" t="n">
         <v>2482.06298828125</v>
@@ -3442,16 +3442,16 @@
         <v>2317.5</v>
       </c>
       <c r="F94" t="n">
-        <v>713.31884765625</v>
+        <v>713.3189086914062</v>
       </c>
       <c r="G94" t="n">
         <v>59.47999954223633</v>
       </c>
       <c r="H94" t="n">
-        <v>357.7152709960938</v>
+        <v>357.7152099609375</v>
       </c>
       <c r="I94" t="n">
-        <v>2375.02001953125</v>
+        <v>2375.019775390625</v>
       </c>
       <c r="J94" t="n">
         <v>167.3999938964844</v>
@@ -3480,10 +3480,10 @@
         <v>62.45000076293945</v>
       </c>
       <c r="H95" t="n">
-        <v>356.7325134277344</v>
+        <v>356.7325439453125</v>
       </c>
       <c r="I95" t="n">
-        <v>2376.867431640625</v>
+        <v>2376.8671875</v>
       </c>
       <c r="J95" t="n">
         <v>168.3999938964844</v>
@@ -3500,13 +3500,13 @@
         <v>2199.199951171875</v>
       </c>
       <c r="D96" t="n">
-        <v>2165.815185546875</v>
+        <v>2165.8154296875</v>
       </c>
       <c r="E96" t="n">
         <v>2248.35009765625</v>
       </c>
       <c r="F96" t="n">
-        <v>733.517333984375</v>
+        <v>733.5172729492188</v>
       </c>
       <c r="G96" t="n">
         <v>65.56999969482422</v>
@@ -3515,7 +3515,7 @@
         <v>357.1747436523438</v>
       </c>
       <c r="I96" t="n">
-        <v>2328.188720703125</v>
+        <v>2328.188232421875</v>
       </c>
       <c r="J96" t="n">
         <v>160.6000061035156</v>
@@ -3526,7 +3526,7 @@
         <v>44705</v>
       </c>
       <c r="B97" t="n">
-        <v>2172.069580078125</v>
+        <v>2172.06982421875</v>
       </c>
       <c r="C97" t="n">
         <v>2196.5</v>
@@ -3570,7 +3570,7 @@
         <v>2187.35009765625</v>
       </c>
       <c r="F98" t="n">
-        <v>689.0809326171875</v>
+        <v>689.0808715820312</v>
       </c>
       <c r="G98" t="n">
         <v>59.86999893188477</v>
@@ -3596,7 +3596,7 @@
         <v>2148.10009765625</v>
       </c>
       <c r="D99" t="n">
-        <v>2041.841918945312</v>
+        <v>2041.842041015625</v>
       </c>
       <c r="E99" t="n">
         <v>2164</v>
@@ -3622,7 +3622,7 @@
         <v>44708</v>
       </c>
       <c r="B100" t="n">
-        <v>2159.396484375</v>
+        <v>2159.396728515625</v>
       </c>
       <c r="C100" t="n">
         <v>2186.25</v>
@@ -3634,7 +3634,7 @@
         <v>2166.449951171875</v>
       </c>
       <c r="F100" t="n">
-        <v>684.4085083007812</v>
+        <v>684.408447265625</v>
       </c>
       <c r="G100" t="n">
         <v>65.62000274658203</v>
@@ -3643,7 +3643,7 @@
         <v>359.9755249023438</v>
       </c>
       <c r="I100" t="n">
-        <v>2452.855712890625</v>
+        <v>2452.855224609375</v>
       </c>
       <c r="J100" t="n">
         <v>154.6999969482422</v>
@@ -3672,7 +3672,7 @@
         <v>68.05000305175781</v>
       </c>
       <c r="H101" t="n">
-        <v>365.1348571777344</v>
+        <v>365.1348876953125</v>
       </c>
       <c r="I101" t="n">
         <v>2585.711181640625</v>
@@ -3686,7 +3686,7 @@
         <v>44712</v>
       </c>
       <c r="B102" t="n">
-        <v>2159.740234375</v>
+        <v>2159.740478515625</v>
       </c>
       <c r="C102" t="n">
         <v>2055</v>
@@ -3698,7 +3698,7 @@
         <v>1888.949951171875</v>
       </c>
       <c r="F102" t="n">
-        <v>720.1814575195312</v>
+        <v>720.1815185546875</v>
       </c>
       <c r="G102" t="n">
         <v>64.65000152587891</v>
@@ -3707,7 +3707,7 @@
         <v>363.0220336914062</v>
       </c>
       <c r="I102" t="n">
-        <v>2394.391357421875</v>
+        <v>2394.3916015625</v>
       </c>
       <c r="J102" t="n">
         <v>170.5</v>
@@ -3730,13 +3730,13 @@
         <v>1848.400024414062</v>
       </c>
       <c r="F103" t="n">
-        <v>717.3099365234375</v>
+        <v>717.3098754882812</v>
       </c>
       <c r="G103" t="n">
         <v>61.41999816894531</v>
       </c>
       <c r="H103" t="n">
-        <v>365.2331237792969</v>
+        <v>365.2331848144531</v>
       </c>
       <c r="I103" t="n">
         <v>2322.49658203125</v>
@@ -3750,7 +3750,7 @@
         <v>44714</v>
       </c>
       <c r="B104" t="n">
-        <v>2160.08447265625</v>
+        <v>2160.084228515625</v>
       </c>
       <c r="C104" t="n">
         <v>2025.699951171875</v>
@@ -3768,10 +3768,10 @@
         <v>59.06999969482422</v>
       </c>
       <c r="H104" t="n">
-        <v>367.0512390136719</v>
+        <v>367.0512084960938</v>
       </c>
       <c r="I104" t="n">
-        <v>2442.271484375</v>
+        <v>2442.271728515625</v>
       </c>
       <c r="J104" t="n">
         <v>173.0500030517578</v>
@@ -3782,13 +3782,13 @@
         <v>44715</v>
       </c>
       <c r="B105" t="n">
-        <v>2095.588623046875</v>
+        <v>2095.5888671875</v>
       </c>
       <c r="C105" t="n">
         <v>1956.050048828125</v>
       </c>
       <c r="D105" t="n">
-        <v>2185.122314453125</v>
+        <v>2185.1220703125</v>
       </c>
       <c r="E105" t="n">
         <v>1855.900024414062</v>
@@ -3820,13 +3820,13 @@
         <v>2017.099975585938</v>
       </c>
       <c r="D106" t="n">
-        <v>2220.09423828125</v>
+        <v>2220.093994140625</v>
       </c>
       <c r="E106" t="n">
         <v>1802.349975585938</v>
       </c>
       <c r="F106" t="n">
-        <v>721.5442504882812</v>
+        <v>721.5443725585938</v>
       </c>
       <c r="G106" t="n">
         <v>59.65999984741211</v>
@@ -3846,13 +3846,13 @@
         <v>44719</v>
       </c>
       <c r="B107" t="n">
-        <v>2100.746337890625</v>
+        <v>2100.74658203125</v>
       </c>
       <c r="C107" t="n">
         <v>2046</v>
       </c>
       <c r="D107" t="n">
-        <v>2222.58837890625</v>
+        <v>2222.588623046875</v>
       </c>
       <c r="E107" t="n">
         <v>1829.25</v>
@@ -3867,7 +3867,7 @@
         <v>357.0764770507812</v>
       </c>
       <c r="I107" t="n">
-        <v>2495.293212890625</v>
+        <v>2495.29345703125</v>
       </c>
       <c r="J107" t="n">
         <v>206.5</v>
@@ -3878,13 +3878,13 @@
         <v>44720</v>
       </c>
       <c r="B108" t="n">
-        <v>2097.946533203125</v>
+        <v>2097.9462890625</v>
       </c>
       <c r="C108" t="n">
         <v>2091.89990234375</v>
       </c>
       <c r="D108" t="n">
-        <v>2172.350341796875</v>
+        <v>2172.3505859375</v>
       </c>
       <c r="E108" t="n">
         <v>1801.900024414062</v>
@@ -3896,7 +3896,7 @@
         <v>56.90000152587891</v>
       </c>
       <c r="H108" t="n">
-        <v>356.7816162109375</v>
+        <v>356.7816467285156</v>
       </c>
       <c r="I108" t="n">
         <v>2443.76904296875</v>
@@ -3916,7 +3916,7 @@
         <v>2116.5</v>
       </c>
       <c r="D109" t="n">
-        <v>2214.2568359375</v>
+        <v>2214.257080078125</v>
       </c>
       <c r="E109" t="n">
         <v>1812.650024414062</v>
@@ -3942,19 +3942,19 @@
         <v>44722</v>
       </c>
       <c r="B110" t="n">
-        <v>2097.847900390625</v>
+        <v>2097.84814453125</v>
       </c>
       <c r="C110" t="n">
         <v>2051.89990234375</v>
       </c>
       <c r="D110" t="n">
-        <v>2198.193359375</v>
+        <v>2198.193115234375</v>
       </c>
       <c r="E110" t="n">
         <v>1757.599975585938</v>
       </c>
       <c r="F110" t="n">
-        <v>707.0890502929688</v>
+        <v>707.0891723632812</v>
       </c>
       <c r="G110" t="n">
         <v>56.02000045776367</v>
@@ -3963,7 +3963,7 @@
         <v>358.8453674316406</v>
       </c>
       <c r="I110" t="n">
-        <v>2394.790771484375</v>
+        <v>2394.791015625</v>
       </c>
       <c r="J110" t="n">
         <v>199.3000030517578</v>
@@ -3986,13 +3986,13 @@
         <v>1798.699951171875</v>
       </c>
       <c r="F111" t="n">
-        <v>676.7671508789062</v>
+        <v>676.7672729492188</v>
       </c>
       <c r="G111" t="n">
         <v>53.2400016784668</v>
       </c>
       <c r="H111" t="n">
-        <v>356.437744140625</v>
+        <v>356.4377136230469</v>
       </c>
       <c r="I111" t="n">
         <v>2334.129638671875</v>
@@ -4012,13 +4012,13 @@
         <v>2057.5</v>
       </c>
       <c r="D112" t="n">
-        <v>2191.5576171875</v>
+        <v>2191.557373046875</v>
       </c>
       <c r="E112" t="n">
         <v>1788.75</v>
       </c>
       <c r="F112" t="n">
-        <v>685.9660034179688</v>
+        <v>685.9659423828125</v>
       </c>
       <c r="G112" t="n">
         <v>53.33000183105469</v>
@@ -4038,13 +4038,13 @@
         <v>44727</v>
       </c>
       <c r="B113" t="n">
-        <v>2085.322509765625</v>
+        <v>2085.322265625</v>
       </c>
       <c r="C113" t="n">
         <v>2057.300048828125</v>
       </c>
       <c r="D113" t="n">
-        <v>2179.734375</v>
+        <v>2179.734130859375</v>
       </c>
       <c r="E113" t="n">
         <v>1757.849975585938</v>
@@ -4070,25 +4070,25 @@
         <v>44728</v>
       </c>
       <c r="B114" t="n">
-        <v>2047.597900390625</v>
+        <v>2047.597534179688</v>
       </c>
       <c r="C114" t="n">
         <v>2124.64990234375</v>
       </c>
       <c r="D114" t="n">
-        <v>2078.3603515625</v>
+        <v>2078.360595703125</v>
       </c>
       <c r="E114" t="n">
         <v>1711.099975585938</v>
       </c>
       <c r="F114" t="n">
-        <v>663.577392578125</v>
+        <v>663.5773315429688</v>
       </c>
       <c r="G114" t="n">
         <v>51.86000061035156</v>
       </c>
       <c r="H114" t="n">
-        <v>353.1946716308594</v>
+        <v>353.1946411132812</v>
       </c>
       <c r="I114" t="n">
         <v>2373.022705078125</v>
@@ -4114,7 +4114,7 @@
         <v>1711.25</v>
       </c>
       <c r="F115" t="n">
-        <v>651.1663208007812</v>
+        <v>651.166259765625</v>
       </c>
       <c r="G115" t="n">
         <v>52.2599983215332</v>
@@ -4123,7 +4123,7 @@
         <v>351.1800842285156</v>
       </c>
       <c r="I115" t="n">
-        <v>2145.90576171875</v>
+        <v>2145.905517578125</v>
       </c>
       <c r="J115" t="n">
         <v>177.3999938964844</v>
@@ -4166,13 +4166,13 @@
         <v>44733</v>
       </c>
       <c r="B117" t="n">
-        <v>2049.562255859375</v>
+        <v>2049.5625</v>
       </c>
       <c r="C117" t="n">
         <v>2215.050048828125</v>
       </c>
       <c r="D117" t="n">
-        <v>2156.98486328125</v>
+        <v>2156.985107421875</v>
       </c>
       <c r="E117" t="n">
         <v>1809.099975585938</v>
@@ -4184,10 +4184,10 @@
         <v>50.81000137329102</v>
       </c>
       <c r="H117" t="n">
-        <v>352.7032775878906</v>
+        <v>352.7033081054688</v>
       </c>
       <c r="I117" t="n">
-        <v>2379.41357421875</v>
+        <v>2379.413330078125</v>
       </c>
       <c r="J117" t="n">
         <v>170.75</v>
@@ -4198,13 +4198,13 @@
         <v>44734</v>
       </c>
       <c r="B118" t="n">
-        <v>2026.03369140625</v>
+        <v>2026.033935546875</v>
       </c>
       <c r="C118" t="n">
         <v>2122.35009765625</v>
       </c>
       <c r="D118" t="n">
-        <v>2084.546875</v>
+        <v>2084.546630859375</v>
       </c>
       <c r="E118" t="n">
         <v>1736.099975585938</v>
@@ -4216,10 +4216,10 @@
         <v>49.45999908447266</v>
       </c>
       <c r="H118" t="n">
-        <v>351.7697143554688</v>
+        <v>351.7696838378906</v>
       </c>
       <c r="I118" t="n">
-        <v>2267.477294921875</v>
+        <v>2267.4775390625</v>
       </c>
       <c r="J118" t="n">
         <v>172.3500061035156</v>
@@ -4230,7 +4230,7 @@
         <v>44735</v>
       </c>
       <c r="B119" t="n">
-        <v>2053.6396484375</v>
+        <v>2053.639404296875</v>
       </c>
       <c r="C119" t="n">
         <v>2105</v>
@@ -4248,7 +4248,7 @@
         <v>50.52000045776367</v>
       </c>
       <c r="H119" t="n">
-        <v>352.7524108886719</v>
+        <v>352.7524719238281</v>
       </c>
       <c r="I119" t="n">
         <v>2261.33642578125</v>
@@ -4262,28 +4262,28 @@
         <v>44736</v>
       </c>
       <c r="B120" t="n">
-        <v>2061.30224609375</v>
+        <v>2061.302490234375</v>
       </c>
       <c r="C120" t="n">
         <v>2152.10009765625</v>
       </c>
       <c r="D120" t="n">
-        <v>2156.6357421875</v>
+        <v>2156.635498046875</v>
       </c>
       <c r="E120" t="n">
         <v>1857.599975585938</v>
       </c>
       <c r="F120" t="n">
-        <v>668.1524658203125</v>
+        <v>668.1525268554688</v>
       </c>
       <c r="G120" t="n">
         <v>52.88999938964844</v>
       </c>
       <c r="H120" t="n">
-        <v>354.3739318847656</v>
+        <v>354.3739929199219</v>
       </c>
       <c r="I120" t="n">
-        <v>2288.247314453125</v>
+        <v>2288.2470703125</v>
       </c>
       <c r="J120" t="n">
         <v>171.8000030517578</v>
@@ -4358,28 +4358,28 @@
         <v>44741</v>
       </c>
       <c r="B123" t="n">
-        <v>2117.34912109375</v>
+        <v>2117.349365234375</v>
       </c>
       <c r="C123" t="n">
         <v>2347.89990234375</v>
       </c>
       <c r="D123" t="n">
-        <v>2215.1552734375</v>
+        <v>2215.15478515625</v>
       </c>
       <c r="E123" t="n">
         <v>1901.699951171875</v>
       </c>
       <c r="F123" t="n">
-        <v>659.781005859375</v>
+        <v>659.7810668945312</v>
       </c>
       <c r="G123" t="n">
         <v>54.0099983215332</v>
       </c>
       <c r="H123" t="n">
-        <v>359.1893310546875</v>
+        <v>359.1893615722656</v>
       </c>
       <c r="I123" t="n">
-        <v>2344.2646484375</v>
+        <v>2344.264892578125</v>
       </c>
       <c r="J123" t="n">
         <v>176.8999938964844</v>
@@ -4396,22 +4396,22 @@
         <v>2473.64990234375</v>
       </c>
       <c r="D124" t="n">
-        <v>2186.019775390625</v>
+        <v>2186.02001953125</v>
       </c>
       <c r="E124" t="n">
         <v>1929.599975585938</v>
       </c>
       <c r="F124" t="n">
-        <v>654.1839599609375</v>
+        <v>654.1838989257812</v>
       </c>
       <c r="G124" t="n">
         <v>52.56999969482422</v>
       </c>
       <c r="H124" t="n">
-        <v>356.7325134277344</v>
+        <v>356.7325439453125</v>
       </c>
       <c r="I124" t="n">
-        <v>2389.398681640625</v>
+        <v>2389.3984375</v>
       </c>
       <c r="J124" t="n">
         <v>176</v>
@@ -4422,7 +4422,7 @@
         <v>44743</v>
       </c>
       <c r="B125" t="n">
-        <v>2128.990966796875</v>
+        <v>2128.99072265625</v>
       </c>
       <c r="C125" t="n">
         <v>2400.64990234375</v>
@@ -4434,13 +4434,13 @@
         <v>1963.650024414062</v>
       </c>
       <c r="F125" t="n">
-        <v>659.87841796875</v>
+        <v>659.8784790039062</v>
       </c>
       <c r="G125" t="n">
         <v>52.65000152587891</v>
       </c>
       <c r="H125" t="n">
-        <v>361.2039794921875</v>
+        <v>361.2039489746094</v>
       </c>
       <c r="I125" t="n">
         <v>2385.50439453125</v>
@@ -4466,7 +4466,7 @@
         <v>1883.599975585938</v>
       </c>
       <c r="F126" t="n">
-        <v>663.869384765625</v>
+        <v>663.8693237304688</v>
       </c>
       <c r="G126" t="n">
         <v>52.34000015258789</v>
@@ -4475,7 +4475,7 @@
         <v>362.1866760253906</v>
       </c>
       <c r="I126" t="n">
-        <v>2393.29345703125</v>
+        <v>2393.29296875</v>
       </c>
       <c r="J126" t="n">
         <v>168.8000030517578</v>
@@ -4486,25 +4486,25 @@
         <v>44747</v>
       </c>
       <c r="B127" t="n">
-        <v>2110.27587890625</v>
+        <v>2110.275634765625</v>
       </c>
       <c r="C127" t="n">
         <v>2476.300048828125</v>
       </c>
       <c r="D127" t="n">
-        <v>2241.446044921875</v>
+        <v>2241.4462890625</v>
       </c>
       <c r="E127" t="n">
         <v>1876.400024414062</v>
       </c>
       <c r="F127" t="n">
-        <v>660.7058715820312</v>
+        <v>660.705810546875</v>
       </c>
       <c r="G127" t="n">
         <v>52.54999923706055</v>
       </c>
       <c r="H127" t="n">
-        <v>360.3194885253906</v>
+        <v>360.3195190429688</v>
       </c>
       <c r="I127" t="n">
         <v>2406.9228515625</v>
@@ -4536,10 +4536,10 @@
         <v>52.54000091552734</v>
       </c>
       <c r="H128" t="n">
-        <v>361.891845703125</v>
+        <v>361.8918762207031</v>
       </c>
       <c r="I128" t="n">
-        <v>2471.728271484375</v>
+        <v>2471.72802734375</v>
       </c>
       <c r="J128" t="n">
         <v>164.8500061035156</v>
@@ -4556,19 +4556,19 @@
         <v>2466.10009765625</v>
       </c>
       <c r="D129" t="n">
-        <v>2269.234619140625</v>
+        <v>2269.234375</v>
       </c>
       <c r="E129" t="n">
         <v>1909.699951171875</v>
       </c>
       <c r="F129" t="n">
-        <v>684.8952026367188</v>
+        <v>684.8951416015625</v>
       </c>
       <c r="G129" t="n">
         <v>55.11999893188477</v>
       </c>
       <c r="H129" t="n">
-        <v>360.6143188476562</v>
+        <v>360.6143493652344</v>
       </c>
       <c r="I129" t="n">
         <v>2482.113037109375</v>
@@ -4594,13 +4594,13 @@
         <v>1921</v>
       </c>
       <c r="F130" t="n">
-        <v>696.6735229492188</v>
+        <v>696.673583984375</v>
       </c>
       <c r="G130" t="n">
         <v>54.31000137329102</v>
       </c>
       <c r="H130" t="n">
-        <v>362.0884399414062</v>
+        <v>362.0884094238281</v>
       </c>
       <c r="I130" t="n">
         <v>2537.082275390625</v>
@@ -4614,13 +4614,13 @@
         <v>44753</v>
       </c>
       <c r="B131" t="n">
-        <v>2145.88818359375</v>
+        <v>2145.888427734375</v>
       </c>
       <c r="C131" t="n">
         <v>2690.949951171875</v>
       </c>
       <c r="D131" t="n">
-        <v>2367.964111328125</v>
+        <v>2367.9638671875</v>
       </c>
       <c r="E131" t="n">
         <v>2207.35009765625</v>
@@ -4632,10 +4632,10 @@
         <v>57.02000045776367</v>
       </c>
       <c r="H131" t="n">
-        <v>362.8255004882812</v>
+        <v>362.8254699707031</v>
       </c>
       <c r="I131" t="n">
-        <v>2712.6748046875</v>
+        <v>2712.675048828125</v>
       </c>
       <c r="J131" t="n">
         <v>191.0500030517578</v>
@@ -4646,7 +4646,7 @@
         <v>44754</v>
       </c>
       <c r="B132" t="n">
-        <v>2129.137939453125</v>
+        <v>2129.13818359375</v>
       </c>
       <c r="C132" t="n">
         <v>2749.800048828125</v>
@@ -4658,16 +4658,16 @@
         <v>2294.75</v>
       </c>
       <c r="F132" t="n">
-        <v>712.4429321289062</v>
+        <v>712.44287109375</v>
       </c>
       <c r="G132" t="n">
         <v>58.54999923706055</v>
       </c>
       <c r="H132" t="n">
-        <v>364.4961242675781</v>
+        <v>364.49609375</v>
       </c>
       <c r="I132" t="n">
-        <v>2793.456787109375</v>
+        <v>2793.45703125</v>
       </c>
       <c r="J132" t="n">
         <v>196.8500061035156</v>
@@ -4678,13 +4678,13 @@
         <v>44755</v>
       </c>
       <c r="B133" t="n">
-        <v>2135.32763671875</v>
+        <v>2135.3271484375</v>
       </c>
       <c r="C133" t="n">
         <v>2730.800048828125</v>
       </c>
       <c r="D133" t="n">
-        <v>2348.258056640625</v>
+        <v>2348.2578125</v>
       </c>
       <c r="E133" t="n">
         <v>2104.75</v>
@@ -4710,7 +4710,7 @@
         <v>44756</v>
       </c>
       <c r="B134" t="n">
-        <v>2122.310546875</v>
+        <v>2122.310302734375</v>
       </c>
       <c r="C134" t="n">
         <v>2889.14990234375</v>
@@ -4722,13 +4722,13 @@
         <v>2087</v>
       </c>
       <c r="F134" t="n">
-        <v>710.0762329101562</v>
+        <v>710.076171875</v>
       </c>
       <c r="G134" t="n">
         <v>56.7400016784668</v>
       </c>
       <c r="H134" t="n">
-        <v>363.5133666992188</v>
+        <v>363.5133972167969</v>
       </c>
       <c r="I134" t="n">
         <v>2761.06298828125</v>
@@ -4742,7 +4742,7 @@
         <v>44757</v>
       </c>
       <c r="B135" t="n">
-        <v>2102.711669921875</v>
+        <v>2102.711181640625</v>
       </c>
       <c r="C135" t="n">
         <v>2889.35009765625</v>
@@ -4754,7 +4754,7 @@
         <v>2072.64990234375</v>
       </c>
       <c r="F135" t="n">
-        <v>716.398193359375</v>
+        <v>716.3982543945312</v>
       </c>
       <c r="G135" t="n">
         <v>57.34999847412109</v>
@@ -4806,13 +4806,13 @@
         <v>44761</v>
       </c>
       <c r="B137" t="n">
-        <v>2130.660888671875</v>
+        <v>2130.6611328125</v>
       </c>
       <c r="C137" t="n">
         <v>3029.75</v>
       </c>
       <c r="D137" t="n">
-        <v>2446.847900390625</v>
+        <v>2446.84814453125</v>
       </c>
       <c r="E137" t="n">
         <v>2109</v>
@@ -4824,7 +4824,7 @@
         <v>58.66999816894531</v>
       </c>
       <c r="H137" t="n">
-        <v>364.5452880859375</v>
+        <v>364.5452575683594</v>
       </c>
       <c r="I137" t="n">
         <v>2828.470703125</v>
@@ -4838,7 +4838,7 @@
         <v>44762</v>
       </c>
       <c r="B138" t="n">
-        <v>2120.93505859375</v>
+        <v>2120.934814453125</v>
       </c>
       <c r="C138" t="n">
         <v>3018.75</v>
@@ -4850,13 +4850,13 @@
         <v>2084.300048828125</v>
       </c>
       <c r="F138" t="n">
-        <v>728.7972412109375</v>
+        <v>728.7971801757812</v>
       </c>
       <c r="G138" t="n">
         <v>57.97999954223633</v>
       </c>
       <c r="H138" t="n">
-        <v>361.4988098144531</v>
+        <v>361.498779296875</v>
       </c>
       <c r="I138" t="n">
         <v>2776.14208984375</v>
@@ -4870,7 +4870,7 @@
         <v>44763</v>
       </c>
       <c r="B139" t="n">
-        <v>2136.309814453125</v>
+        <v>2136.31005859375</v>
       </c>
       <c r="C139" t="n">
         <v>3043.75</v>
@@ -4882,7 +4882,7 @@
         <v>2109.75</v>
       </c>
       <c r="F139" t="n">
-        <v>739.2849731445312</v>
+        <v>739.284912109375</v>
       </c>
       <c r="G139" t="n">
         <v>58.79999923706055</v>
@@ -4914,7 +4914,7 @@
         <v>2120.449951171875</v>
       </c>
       <c r="F140" t="n">
-        <v>739.2849731445312</v>
+        <v>739.284912109375</v>
       </c>
       <c r="G140" t="n">
         <v>58.2599983215332</v>
@@ -4940,7 +4940,7 @@
         <v>2969.75</v>
       </c>
       <c r="D141" t="n">
-        <v>2545.968017578125</v>
+        <v>2545.9677734375</v>
       </c>
       <c r="E141" t="n">
         <v>2137.60009765625</v>
@@ -4984,7 +4984,7 @@
         <v>59.54000091552734</v>
       </c>
       <c r="H142" t="n">
-        <v>363.5625</v>
+        <v>363.5625305175781</v>
       </c>
       <c r="I142" t="n">
         <v>2894.230224609375</v>
@@ -4998,7 +4998,7 @@
         <v>44769</v>
       </c>
       <c r="B143" t="n">
-        <v>2151.733642578125</v>
+        <v>2151.73388671875</v>
       </c>
       <c r="C143" t="n">
         <v>2996.10009765625</v>
@@ -5016,7 +5016,7 @@
         <v>62.4900016784668</v>
       </c>
       <c r="H143" t="n">
-        <v>364.4469604492188</v>
+        <v>364.4469909667969</v>
       </c>
       <c r="I143" t="n">
         <v>2956.04541015625</v>
@@ -5030,7 +5030,7 @@
         <v>44770</v>
       </c>
       <c r="B144" t="n">
-        <v>2142.40087890625</v>
+        <v>2142.400634765625</v>
       </c>
       <c r="C144" t="n">
         <v>3012.64990234375</v>
@@ -5048,7 +5048,7 @@
         <v>64.38999938964844</v>
       </c>
       <c r="H144" t="n">
-        <v>364.4469604492188</v>
+        <v>364.4469909667969</v>
       </c>
       <c r="I144" t="n">
         <v>3001.78271484375</v>
@@ -5068,13 +5068,13 @@
         <v>3109.60009765625</v>
       </c>
       <c r="D145" t="n">
-        <v>2564.533935546875</v>
+        <v>2564.53369140625</v>
       </c>
       <c r="E145" t="n">
         <v>2174.699951171875</v>
       </c>
       <c r="F145" t="n">
-        <v>748.5474243164062</v>
+        <v>748.54736328125</v>
       </c>
       <c r="G145" t="n">
         <v>62.79000091552734</v>
@@ -5094,7 +5094,7 @@
         <v>44774</v>
       </c>
       <c r="B146" t="n">
-        <v>2187.3955078125</v>
+        <v>2187.395263671875</v>
       </c>
       <c r="C146" t="n">
         <v>3261.75</v>
@@ -5112,7 +5112,7 @@
         <v>64.37000274658203</v>
       </c>
       <c r="H146" t="n">
-        <v>368.9183959960938</v>
+        <v>368.9184265136719</v>
       </c>
       <c r="I146" t="n">
         <v>3213.24267578125</v>
@@ -5126,7 +5126,7 @@
         <v>44775</v>
       </c>
       <c r="B147" t="n">
-        <v>2188.475830078125</v>
+        <v>2188.47607421875</v>
       </c>
       <c r="C147" t="n">
         <v>3421.449951171875</v>
@@ -5138,13 +5138,13 @@
         <v>2296.14990234375</v>
       </c>
       <c r="F147" t="n">
-        <v>786.3815307617188</v>
+        <v>786.3814697265625</v>
       </c>
       <c r="G147" t="n">
         <v>65.70999908447266</v>
       </c>
       <c r="H147" t="n">
-        <v>372.1122741699219</v>
+        <v>372.1123046875</v>
       </c>
       <c r="I147" t="n">
         <v>3244.39990234375</v>
@@ -5158,7 +5158,7 @@
         <v>44776</v>
       </c>
       <c r="B148" t="n">
-        <v>2197.07177734375</v>
+        <v>2197.072021484375</v>
       </c>
       <c r="C148" t="n">
         <v>3505.35009765625</v>
@@ -5190,7 +5190,7 @@
         <v>44777</v>
       </c>
       <c r="B149" t="n">
-        <v>2183.220458984375</v>
+        <v>2183.22021484375</v>
       </c>
       <c r="C149" t="n">
         <v>3530.449951171875</v>
@@ -5222,13 +5222,13 @@
         <v>44778</v>
       </c>
       <c r="B150" t="n">
-        <v>2215.148681640625</v>
+        <v>2215.14892578125</v>
       </c>
       <c r="C150" t="n">
         <v>3313.550048828125</v>
       </c>
       <c r="D150" t="n">
-        <v>2693.4990234375</v>
+        <v>2693.499267578125</v>
       </c>
       <c r="E150" t="n">
         <v>2106.199951171875</v>
@@ -5240,7 +5240,7 @@
         <v>66.41000366210938</v>
       </c>
       <c r="H150" t="n">
-        <v>376.0432434082031</v>
+        <v>376.043212890625</v>
       </c>
       <c r="I150" t="n">
         <v>3342.814697265625</v>
@@ -5272,7 +5272,7 @@
         <v>65.72000122070312</v>
       </c>
       <c r="H151" t="n">
-        <v>373.6355285644531</v>
+        <v>373.6355590820312</v>
       </c>
       <c r="I151" t="n">
         <v>3360.39111328125</v>
@@ -5286,7 +5286,7 @@
         <v>44783</v>
       </c>
       <c r="B152" t="n">
-        <v>2187.83740234375</v>
+        <v>2187.837646484375</v>
       </c>
       <c r="C152" t="n">
         <v>3436.14990234375</v>
@@ -5304,7 +5304,7 @@
         <v>67.94999694824219</v>
       </c>
       <c r="H152" t="n">
-        <v>373.4881286621094</v>
+        <v>373.4880981445312</v>
       </c>
       <c r="I152" t="n">
         <v>3346.809326171875</v>
@@ -5330,13 +5330,13 @@
         <v>2164.89990234375</v>
       </c>
       <c r="F153" t="n">
-        <v>777.02099609375</v>
+        <v>777.0210571289062</v>
       </c>
       <c r="G153" t="n">
         <v>68.48000335693359</v>
       </c>
       <c r="H153" t="n">
-        <v>373.6355285644531</v>
+        <v>373.6355590820312</v>
       </c>
       <c r="I153" t="n">
         <v>3347.708251953125</v>
@@ -5400,7 +5400,7 @@
         <v>72.47000122070312</v>
       </c>
       <c r="H155" t="n">
-        <v>389.2610473632812</v>
+        <v>389.2610168457031</v>
       </c>
       <c r="I155" t="n">
         <v>3484.920166015625</v>
@@ -5414,13 +5414,13 @@
         <v>44790</v>
       </c>
       <c r="B156" t="n">
-        <v>2243</v>
+        <v>2242.999755859375</v>
       </c>
       <c r="C156" t="n">
         <v>3597.64990234375</v>
       </c>
       <c r="D156" t="n">
-        <v>3003.185791015625</v>
+        <v>3003.185546875</v>
       </c>
       <c r="E156" t="n">
         <v>2227.050048828125</v>
@@ -5432,7 +5432,7 @@
         <v>76.08999633789062</v>
       </c>
       <c r="H156" t="n">
-        <v>391.4230346679688</v>
+        <v>391.4230041503906</v>
       </c>
       <c r="I156" t="n">
         <v>3467.094482421875</v>
@@ -5452,13 +5452,13 @@
         <v>3599.550048828125</v>
       </c>
       <c r="D157" t="n">
-        <v>3147.922607421875</v>
+        <v>3147.92236328125</v>
       </c>
       <c r="E157" t="n">
         <v>2296.35009765625</v>
       </c>
       <c r="F157" t="n">
-        <v>816.5214233398438</v>
+        <v>816.5213623046875</v>
       </c>
       <c r="G157" t="n">
         <v>79.88999938964844</v>
@@ -5478,7 +5478,7 @@
         <v>44792</v>
       </c>
       <c r="B158" t="n">
-        <v>2309.509521484375</v>
+        <v>2309.509765625</v>
       </c>
       <c r="C158" t="n">
         <v>3635.25</v>
@@ -5496,7 +5496,7 @@
         <v>82.38999938964844</v>
       </c>
       <c r="H158" t="n">
-        <v>413.1906433105469</v>
+        <v>413.1906127929688</v>
       </c>
       <c r="I158" t="n">
         <v>3386.25537109375</v>
@@ -5528,7 +5528,7 @@
         <v>86.5</v>
       </c>
       <c r="H159" t="n">
-        <v>400.9555358886719</v>
+        <v>400.95556640625</v>
       </c>
       <c r="I159" t="n">
         <v>3359.69189453125</v>
@@ -5542,7 +5542,7 @@
         <v>44796</v>
       </c>
       <c r="B160" t="n">
-        <v>2255.673095703125</v>
+        <v>2255.67333984375</v>
       </c>
       <c r="C160" t="n">
         <v>3601.89990234375</v>
@@ -5554,7 +5554,7 @@
         <v>2412.89990234375</v>
       </c>
       <c r="F160" t="n">
-        <v>815.9823608398438</v>
+        <v>815.982421875</v>
       </c>
       <c r="G160" t="n">
         <v>82.18000030517578</v>
@@ -5574,19 +5574,19 @@
         <v>44797</v>
       </c>
       <c r="B161" t="n">
-        <v>2261.174560546875</v>
+        <v>2261.1748046875</v>
       </c>
       <c r="C161" t="n">
         <v>3700.39990234375</v>
       </c>
       <c r="D161" t="n">
-        <v>3128.956787109375</v>
+        <v>3128.95703125</v>
       </c>
       <c r="E161" t="n">
         <v>2358.85009765625</v>
       </c>
       <c r="F161" t="n">
-        <v>819.7069091796875</v>
+        <v>819.7069702148438</v>
       </c>
       <c r="G161" t="n">
         <v>78.08000183105469</v>
@@ -5606,13 +5606,13 @@
         <v>44798</v>
       </c>
       <c r="B162" t="n">
-        <v>2244.03125</v>
+        <v>2244.031494140625</v>
       </c>
       <c r="C162" t="n">
         <v>3715.800048828125</v>
       </c>
       <c r="D162" t="n">
-        <v>3060.781005859375</v>
+        <v>3060.78125</v>
       </c>
       <c r="E162" t="n">
         <v>2368.300048828125</v>
@@ -5644,7 +5644,7 @@
         <v>3751.199951171875</v>
       </c>
       <c r="D163" t="n">
-        <v>3133.847900390625</v>
+        <v>3133.84814453125</v>
       </c>
       <c r="E163" t="n">
         <v>2392.75</v>
@@ -5656,7 +5656,7 @@
         <v>75.09999847412109</v>
       </c>
       <c r="H163" t="n">
-        <v>395.8944702148438</v>
+        <v>395.8945007324219</v>
       </c>
       <c r="I163" t="n">
         <v>3454.9111328125</v>
@@ -5670,7 +5670,7 @@
         <v>44802</v>
       </c>
       <c r="B164" t="n">
-        <v>2248.3544921875</v>
+        <v>2248.354248046875</v>
       </c>
       <c r="C164" t="n">
         <v>3855.550048828125</v>
@@ -5702,7 +5702,7 @@
         <v>44803</v>
       </c>
       <c r="B165" t="n">
-        <v>2259.258544921875</v>
+        <v>2259.25927734375</v>
       </c>
       <c r="C165" t="n">
         <v>3960.699951171875</v>
@@ -5714,13 +5714,13 @@
         <v>2436.199951171875</v>
       </c>
       <c r="F165" t="n">
-        <v>825.44091796875</v>
+        <v>825.4408569335938</v>
       </c>
       <c r="G165" t="n">
         <v>82.79000091552734</v>
       </c>
       <c r="H165" t="n">
-        <v>404.1494445800781</v>
+        <v>404.1494140625</v>
       </c>
       <c r="I165" t="n">
         <v>3739.820556640625</v>
@@ -5772,7 +5772,7 @@
         <v>3866.550048828125</v>
       </c>
       <c r="D167" t="n">
-        <v>3349.70556640625</v>
+        <v>3349.705322265625</v>
       </c>
       <c r="E167" t="n">
         <v>2383.10009765625</v>
@@ -5784,7 +5784,7 @@
         <v>80.25</v>
       </c>
       <c r="H167" t="n">
-        <v>408.4243774414062</v>
+        <v>408.4243469238281</v>
       </c>
       <c r="I167" t="n">
         <v>3617.887939453125</v>
@@ -5798,7 +5798,7 @@
         <v>44809</v>
       </c>
       <c r="B168" t="n">
-        <v>2247.911865234375</v>
+        <v>2247.912109375</v>
       </c>
       <c r="C168" t="n">
         <v>3881.25</v>
@@ -5836,19 +5836,19 @@
         <v>3964.050048828125</v>
       </c>
       <c r="D169" t="n">
-        <v>3429.56005859375</v>
+        <v>3429.559814453125</v>
       </c>
       <c r="E169" t="n">
         <v>2374.89990234375</v>
       </c>
       <c r="F169" t="n">
-        <v>833.4782104492188</v>
+        <v>833.4781494140625</v>
       </c>
       <c r="G169" t="n">
         <v>81.55000305175781</v>
       </c>
       <c r="H169" t="n">
-        <v>428.9635009765625</v>
+        <v>428.9634704589844</v>
       </c>
       <c r="I169" t="n">
         <v>3677.8056640625</v>
@@ -5862,13 +5862,13 @@
         <v>44811</v>
       </c>
       <c r="B170" t="n">
-        <v>2363.05126953125</v>
+        <v>2363.051025390625</v>
       </c>
       <c r="C170" t="n">
         <v>3893.10009765625</v>
       </c>
       <c r="D170" t="n">
-        <v>3467.44091796875</v>
+        <v>3467.441162109375</v>
       </c>
       <c r="E170" t="n">
         <v>2346.949951171875</v>
@@ -5906,7 +5906,7 @@
         <v>2334.050048828125</v>
       </c>
       <c r="F171" t="n">
-        <v>867.48974609375</v>
+        <v>867.4896850585938</v>
       </c>
       <c r="G171" t="n">
         <v>80.37999725341797</v>
@@ -5958,7 +5958,7 @@
         <v>44816</v>
       </c>
       <c r="B173" t="n">
-        <v>2456.871826171875</v>
+        <v>2456.8720703125</v>
       </c>
       <c r="C173" t="n">
         <v>4006</v>
@@ -5970,13 +5970,13 @@
         <v>2355.949951171875</v>
       </c>
       <c r="F173" t="n">
-        <v>919.8792114257812</v>
+        <v>919.879150390625</v>
       </c>
       <c r="G173" t="n">
         <v>79.51999664306641</v>
       </c>
       <c r="H173" t="n">
-        <v>467.4375305175781</v>
+        <v>467.4375</v>
       </c>
       <c r="I173" t="n">
         <v>3630.42041015625</v>
@@ -5990,7 +5990,7 @@
         <v>44817</v>
       </c>
       <c r="B174" t="n">
-        <v>2527.556640625</v>
+        <v>2527.556396484375</v>
       </c>
       <c r="C174" t="n">
         <v>4037.050048828125</v>
@@ -6002,13 +6002,13 @@
         <v>2335.64990234375</v>
       </c>
       <c r="F174" t="n">
-        <v>929.9747924804688</v>
+        <v>929.974853515625</v>
       </c>
       <c r="G174" t="n">
         <v>78.72000122070312</v>
       </c>
       <c r="H174" t="n">
-        <v>478.1001892089844</v>
+        <v>478.1002197265625</v>
       </c>
       <c r="I174" t="n">
         <v>3599.812255859375</v>
@@ -6040,7 +6040,7 @@
         <v>76.91000366210938</v>
       </c>
       <c r="H175" t="n">
-        <v>515.5422973632812</v>
+        <v>515.5423583984375</v>
       </c>
       <c r="I175" t="n">
         <v>3559.517578125</v>
@@ -6054,7 +6054,7 @@
         <v>44819</v>
       </c>
       <c r="B176" t="n">
-        <v>2699.380859375</v>
+        <v>2699.380615234375</v>
       </c>
       <c r="C176" t="n">
         <v>4105.39990234375</v>
@@ -6066,7 +6066,7 @@
         <v>2343.89990234375</v>
       </c>
       <c r="F176" t="n">
-        <v>949.3329467773438</v>
+        <v>949.3330078125</v>
       </c>
       <c r="G176" t="n">
         <v>79.83999633789062</v>
@@ -6092,7 +6092,7 @@
         <v>4094.75</v>
       </c>
       <c r="D177" t="n">
-        <v>3695.476318359375</v>
+        <v>3695.47607421875</v>
       </c>
       <c r="E177" t="n">
         <v>2316.60009765625</v>
@@ -6104,7 +6104,7 @@
         <v>77.55000305175781</v>
       </c>
       <c r="H177" t="n">
-        <v>507.7787475585938</v>
+        <v>507.7787780761719</v>
       </c>
       <c r="I177" t="n">
         <v>3523.96630859375</v>
@@ -6124,7 +6124,7 @@
         <v>4029.39990234375</v>
       </c>
       <c r="D178" t="n">
-        <v>3771.787353515625</v>
+        <v>3771.787109375</v>
       </c>
       <c r="E178" t="n">
         <v>2346.35009765625</v>
@@ -6136,7 +6136,7 @@
         <v>78.37000274658203</v>
       </c>
       <c r="H178" t="n">
-        <v>555.1465454101562</v>
+        <v>555.1466064453125</v>
       </c>
       <c r="I178" t="n">
         <v>3615.091796875</v>
@@ -6156,13 +6156,13 @@
         <v>4021.550048828125</v>
       </c>
       <c r="D179" t="n">
-        <v>3827.58544921875</v>
+        <v>3827.585693359375</v>
       </c>
       <c r="E179" t="n">
         <v>2399.949951171875</v>
       </c>
       <c r="F179" t="n">
-        <v>950.9992065429688</v>
+        <v>950.999267578125</v>
       </c>
       <c r="G179" t="n">
         <v>79.65000152587891</v>
@@ -6182,13 +6182,13 @@
         <v>44825</v>
       </c>
       <c r="B180" t="n">
-        <v>2486.687744140625</v>
+        <v>2486.68798828125</v>
       </c>
       <c r="C180" t="n">
         <v>3865.75</v>
       </c>
       <c r="D180" t="n">
-        <v>3633.489013671875</v>
+        <v>3633.4892578125</v>
       </c>
       <c r="E180" t="n">
         <v>2362.800048828125</v>
@@ -6226,7 +6226,7 @@
         <v>2363.60009765625</v>
       </c>
       <c r="F181" t="n">
-        <v>927.8674926757812</v>
+        <v>927.8675537109375</v>
       </c>
       <c r="G181" t="n">
         <v>79.25</v>
@@ -6278,7 +6278,7 @@
         <v>44830</v>
       </c>
       <c r="B183" t="n">
-        <v>2336.427734375</v>
+        <v>2336.427490234375</v>
       </c>
       <c r="C183" t="n">
         <v>3713</v>
@@ -6290,7 +6290,7 @@
         <v>2210.35009765625</v>
       </c>
       <c r="F183" t="n">
-        <v>846.2693481445312</v>
+        <v>846.269287109375</v>
       </c>
       <c r="G183" t="n">
         <v>73.30000305175781</v>
@@ -6310,7 +6310,7 @@
         <v>44831</v>
       </c>
       <c r="B184" t="n">
-        <v>2331.7119140625</v>
+        <v>2331.712158203125</v>
       </c>
       <c r="C184" t="n">
         <v>3606.5</v>
@@ -6348,7 +6348,7 @@
         <v>3602.10009765625</v>
       </c>
       <c r="D185" t="n">
-        <v>3542.3046875</v>
+        <v>3542.304931640625</v>
       </c>
       <c r="E185" t="n">
         <v>2051.050048828125</v>
@@ -6360,7 +6360,7 @@
         <v>73.55000305175781</v>
       </c>
       <c r="H185" t="n">
-        <v>491.4162292480469</v>
+        <v>491.4161987304688</v>
       </c>
       <c r="I185" t="n">
         <v>3443.327392578125</v>
@@ -6374,25 +6374,25 @@
         <v>44833</v>
       </c>
       <c r="B186" t="n">
-        <v>2332.301513671875</v>
+        <v>2332.3017578125</v>
       </c>
       <c r="C186" t="n">
         <v>3406.39990234375</v>
       </c>
       <c r="D186" t="n">
-        <v>3464.396484375</v>
+        <v>3464.396240234375</v>
       </c>
       <c r="E186" t="n">
         <v>2004.050048828125</v>
       </c>
       <c r="F186" t="n">
-        <v>800.2018432617188</v>
+        <v>800.2017822265625</v>
       </c>
       <c r="G186" t="n">
         <v>73.88999938964844</v>
       </c>
       <c r="H186" t="n">
-        <v>497.6074829101562</v>
+        <v>497.6074523925781</v>
       </c>
       <c r="I186" t="n">
         <v>3367.630859375</v>
@@ -6424,7 +6424,7 @@
         <v>74.69999694824219</v>
       </c>
       <c r="H187" t="n">
-        <v>506.69775390625</v>
+        <v>506.6977233886719</v>
       </c>
       <c r="I187" t="n">
         <v>3335.275390625</v>
@@ -6540,7 +6540,7 @@
         <v>3278.60009765625</v>
       </c>
       <c r="D191" t="n">
-        <v>3271.6474609375</v>
+        <v>3271.647216796875</v>
       </c>
       <c r="E191" t="n">
         <v>2204.14990234375</v>
@@ -6552,7 +6552,7 @@
         <v>74.56999969482422</v>
       </c>
       <c r="H191" t="n">
-        <v>512.7906494140625</v>
+        <v>512.7907104492188</v>
       </c>
       <c r="I191" t="n">
         <v>3183.23388671875</v>
@@ -6584,7 +6584,7 @@
         <v>73.06999969482422</v>
       </c>
       <c r="H192" t="n">
-        <v>513.6261596679688</v>
+        <v>513.6260986328125</v>
       </c>
       <c r="I192" t="n">
         <v>3156.67041015625</v>
@@ -6598,7 +6598,7 @@
         <v>44845</v>
       </c>
       <c r="B193" t="n">
-        <v>2270.99853515625</v>
+        <v>2270.998779296875</v>
       </c>
       <c r="C193" t="n">
         <v>3154.35009765625</v>
@@ -6648,7 +6648,7 @@
         <v>71.36000061035156</v>
       </c>
       <c r="H194" t="n">
-        <v>496.7230529785156</v>
+        <v>496.7230224609375</v>
       </c>
       <c r="I194" t="n">
         <v>3198.462890625</v>
@@ -6662,19 +6662,19 @@
         <v>44847</v>
       </c>
       <c r="B195" t="n">
-        <v>2214.264404296875</v>
+        <v>2214.26416015625</v>
       </c>
       <c r="C195" t="n">
         <v>3121.10009765625</v>
       </c>
       <c r="D195" t="n">
-        <v>3227.77685546875</v>
+        <v>3227.777099609375</v>
       </c>
       <c r="E195" t="n">
         <v>2083.35009765625</v>
       </c>
       <c r="F195" t="n">
-        <v>769.1797485351562</v>
+        <v>769.1798095703125</v>
       </c>
       <c r="G195" t="n">
         <v>69.37000274658203</v>
@@ -6732,7 +6732,7 @@
         <v>3074.35009765625</v>
       </c>
       <c r="D197" t="n">
-        <v>3206.765625</v>
+        <v>3206.765380859375</v>
       </c>
       <c r="E197" t="n">
         <v>2154.449951171875</v>
@@ -6758,7 +6758,7 @@
         <v>44852</v>
       </c>
       <c r="B198" t="n">
-        <v>2180.223876953125</v>
+        <v>2180.2236328125</v>
       </c>
       <c r="C198" t="n">
         <v>3243</v>
@@ -6770,7 +6770,7 @@
         <v>2153.75</v>
       </c>
       <c r="F198" t="n">
-        <v>793.8797607421875</v>
+        <v>793.8798217773438</v>
       </c>
       <c r="G198" t="n">
         <v>69.12000274658203</v>
@@ -6802,7 +6802,7 @@
         <v>2119.800048828125</v>
       </c>
       <c r="F199" t="n">
-        <v>789.076904296875</v>
+        <v>789.0769653320312</v>
       </c>
       <c r="G199" t="n">
         <v>66.72000122070312</v>
@@ -6822,25 +6822,25 @@
         <v>44854</v>
       </c>
       <c r="B200" t="n">
-        <v>2247.3720703125</v>
+        <v>2247.371826171875</v>
       </c>
       <c r="C200" t="n">
         <v>3270.050048828125</v>
       </c>
       <c r="D200" t="n">
-        <v>3351.003173828125</v>
+        <v>3351.0029296875</v>
       </c>
       <c r="E200" t="n">
         <v>2138.89990234375</v>
       </c>
       <c r="F200" t="n">
-        <v>803.779296875</v>
+        <v>803.7793579101562</v>
       </c>
       <c r="G200" t="n">
         <v>67.69000244140625</v>
       </c>
       <c r="H200" t="n">
-        <v>508.7615051269531</v>
+        <v>508.761474609375</v>
       </c>
       <c r="I200" t="n">
         <v>3272.611328125</v>
@@ -6854,7 +6854,7 @@
         <v>44855</v>
       </c>
       <c r="B201" t="n">
-        <v>2216.86767578125</v>
+        <v>2216.867919921875</v>
       </c>
       <c r="C201" t="n">
         <v>3273.699951171875</v>
@@ -6886,7 +6886,7 @@
         <v>44858</v>
       </c>
       <c r="B202" t="n">
-        <v>2217.408203125</v>
+        <v>2217.407958984375</v>
       </c>
       <c r="C202" t="n">
         <v>3283.949951171875</v>
@@ -6898,7 +6898,7 @@
         <v>2121.25</v>
       </c>
       <c r="F202" t="n">
-        <v>789.5181274414062</v>
+        <v>789.51806640625</v>
       </c>
       <c r="G202" t="n">
         <v>67.11000061035156</v>
@@ -6918,7 +6918,7 @@
         <v>44859</v>
       </c>
       <c r="B203" t="n">
-        <v>2207.97705078125</v>
+        <v>2207.977294921875</v>
       </c>
       <c r="C203" t="n">
         <v>3188.449951171875</v>
@@ -6936,7 +6936,7 @@
         <v>66.47000122070312</v>
       </c>
       <c r="H203" t="n">
-        <v>504.2408752441406</v>
+        <v>504.2409057617188</v>
       </c>
       <c r="I203" t="n">
         <v>3378.316162109375</v>
@@ -6962,13 +6962,13 @@
         <v>2117.60009765625</v>
       </c>
       <c r="F204" t="n">
-        <v>804.95556640625</v>
+        <v>804.9555053710938</v>
       </c>
       <c r="G204" t="n">
         <v>67.48000335693359</v>
       </c>
       <c r="H204" t="n">
-        <v>518.4905395507812</v>
+        <v>518.4906005859375</v>
       </c>
       <c r="I204" t="n">
         <v>3502.945068359375</v>
@@ -7000,7 +7000,7 @@
         <v>66.66000366210938</v>
       </c>
       <c r="H205" t="n">
-        <v>511.1200561523438</v>
+        <v>511.1200256347656</v>
       </c>
       <c r="I205" t="n">
         <v>3439.33251953125</v>
@@ -7020,13 +7020,13 @@
         <v>3348.699951171875</v>
       </c>
       <c r="D206" t="n">
-        <v>3341.370361328125</v>
+        <v>3341.37060546875</v>
       </c>
       <c r="E206" t="n">
         <v>2102.89990234375</v>
       </c>
       <c r="F206" t="n">
-        <v>807.2099609375</v>
+        <v>807.2098999023438</v>
       </c>
       <c r="G206" t="n">
         <v>66.98000335693359</v>
@@ -7046,7 +7046,7 @@
         <v>44866</v>
       </c>
       <c r="B207" t="n">
-        <v>2385.35205078125</v>
+        <v>2385.351806640625</v>
       </c>
       <c r="C207" t="n">
         <v>3342.449951171875</v>
@@ -7090,7 +7090,7 @@
         <v>2137.050048828125</v>
       </c>
       <c r="F208" t="n">
-        <v>816.8645629882812</v>
+        <v>816.864501953125</v>
       </c>
       <c r="G208" t="n">
         <v>68.62999725341797</v>
@@ -7110,7 +7110,7 @@
         <v>44868</v>
       </c>
       <c r="B209" t="n">
-        <v>2412.171630859375</v>
+        <v>2412.171875</v>
       </c>
       <c r="C209" t="n">
         <v>3292.14990234375</v>
@@ -7148,13 +7148,13 @@
         <v>3319.449951171875</v>
       </c>
       <c r="D210" t="n">
-        <v>3826.2880859375</v>
+        <v>3826.288330078125</v>
       </c>
       <c r="E210" t="n">
         <v>2121.25</v>
       </c>
       <c r="F210" t="n">
-        <v>845.7792358398438</v>
+        <v>845.7791748046875</v>
       </c>
       <c r="G210" t="n">
         <v>69.37000274658203</v>
@@ -7186,13 +7186,13 @@
         <v>2165.699951171875</v>
       </c>
       <c r="F211" t="n">
-        <v>836.0756225585938</v>
+        <v>836.07568359375</v>
       </c>
       <c r="G211" t="n">
         <v>69.72000122070312</v>
       </c>
       <c r="H211" t="n">
-        <v>558.2911987304688</v>
+        <v>558.291259765625</v>
       </c>
       <c r="I211" t="n">
         <v>3795.194580078125</v>
@@ -7206,7 +7206,7 @@
         <v>44874</v>
       </c>
       <c r="B212" t="n">
-        <v>2395.470947265625</v>
+        <v>2395.470703125</v>
       </c>
       <c r="C212" t="n">
         <v>3290</v>
@@ -7224,7 +7224,7 @@
         <v>73.16000366210938</v>
       </c>
       <c r="H212" t="n">
-        <v>554.75341796875</v>
+        <v>554.7534790039062</v>
       </c>
       <c r="I212" t="n">
         <v>3790.00146484375</v>
@@ -7256,7 +7256,7 @@
         <v>74.27999877929688</v>
       </c>
       <c r="H213" t="n">
-        <v>548.5130615234375</v>
+        <v>548.5131225585938</v>
       </c>
       <c r="I213" t="n">
         <v>3702.0224609375</v>
@@ -7270,7 +7270,7 @@
         <v>44876</v>
       </c>
       <c r="B214" t="n">
-        <v>2348.609375</v>
+        <v>2348.609619140625</v>
       </c>
       <c r="C214" t="n">
         <v>3292.050048828125</v>
@@ -7282,13 +7282,13 @@
         <v>2196.699951171875</v>
       </c>
       <c r="F214" t="n">
-        <v>876.7522583007812</v>
+        <v>876.752197265625</v>
       </c>
       <c r="G214" t="n">
         <v>72.04000091552734</v>
       </c>
       <c r="H214" t="n">
-        <v>547.9234619140625</v>
+        <v>547.9234008789062</v>
       </c>
       <c r="I214" t="n">
         <v>3795.39404296875</v>
@@ -7302,7 +7302,7 @@
         <v>44879</v>
       </c>
       <c r="B215" t="n">
-        <v>2392.62158203125</v>
+        <v>2392.621826171875</v>
       </c>
       <c r="C215" t="n">
         <v>3287.64990234375</v>
@@ -7314,7 +7314,7 @@
         <v>2178.550048828125</v>
       </c>
       <c r="F215" t="n">
-        <v>877.291259765625</v>
+        <v>877.2913208007812</v>
       </c>
       <c r="G215" t="n">
         <v>71.95999908447266</v>
@@ -7340,7 +7340,7 @@
         <v>3290.300048828125</v>
       </c>
       <c r="D216" t="n">
-        <v>4050.430419921875</v>
+        <v>4050.4306640625</v>
       </c>
       <c r="E216" t="n">
         <v>2196.949951171875</v>
@@ -7366,7 +7366,7 @@
         <v>44881</v>
       </c>
       <c r="B217" t="n">
-        <v>2422.24169921875</v>
+        <v>2422.241455078125</v>
       </c>
       <c r="C217" t="n">
         <v>3271.14990234375</v>
@@ -7378,13 +7378,13 @@
         <v>2110.14990234375</v>
       </c>
       <c r="F217" t="n">
-        <v>869.7440795898438</v>
+        <v>869.7440185546875</v>
       </c>
       <c r="G217" t="n">
         <v>69.02999877929688</v>
       </c>
       <c r="H217" t="n">
-        <v>567.2341918945312</v>
+        <v>567.2342529296875</v>
       </c>
       <c r="I217" t="n">
         <v>3804.431640625</v>
@@ -7442,7 +7442,7 @@
         <v>2085.39990234375</v>
       </c>
       <c r="F219" t="n">
-        <v>871.2633666992188</v>
+        <v>871.2633056640625</v>
       </c>
       <c r="G219" t="n">
         <v>67.30000305175781</v>
@@ -7468,13 +7468,13 @@
         <v>3018.699951171875</v>
       </c>
       <c r="D220" t="n">
-        <v>3994.582275390625</v>
+        <v>3994.58203125</v>
       </c>
       <c r="E220" t="n">
         <v>2003.300048828125</v>
       </c>
       <c r="F220" t="n">
-        <v>854.3065795898438</v>
+        <v>854.3065185546875</v>
       </c>
       <c r="G220" t="n">
         <v>66.23999786376953</v>
@@ -7500,7 +7500,7 @@
         <v>2875.14990234375</v>
       </c>
       <c r="D221" t="n">
-        <v>4026.673583984375</v>
+        <v>4026.673828125</v>
       </c>
       <c r="E221" t="n">
         <v>1986.099975585938</v>
@@ -7532,7 +7532,7 @@
         <v>2856.85009765625</v>
       </c>
       <c r="D222" t="n">
-        <v>3896.2109375</v>
+        <v>3896.211181640625</v>
       </c>
       <c r="E222" t="n">
         <v>2036.5</v>
@@ -7544,7 +7544,7 @@
         <v>65.19000244140625</v>
       </c>
       <c r="H222" t="n">
-        <v>553.1810913085938</v>
+        <v>553.1810302734375</v>
       </c>
       <c r="I222" t="n">
         <v>3747.309814453125</v>
@@ -7602,7 +7602,7 @@
         <v>2023.949951171875</v>
       </c>
       <c r="F224" t="n">
-        <v>862.1478271484375</v>
+        <v>862.1478881835938</v>
       </c>
       <c r="G224" t="n">
         <v>64.79000091552734</v>
@@ -7640,7 +7640,7 @@
         <v>65.65000152587891</v>
       </c>
       <c r="H225" t="n">
-        <v>558.6351928710938</v>
+        <v>558.6353149414062</v>
       </c>
       <c r="I225" t="n">
         <v>3600.2119140625</v>
@@ -7666,13 +7666,13 @@
         <v>2012.050048828125</v>
       </c>
       <c r="F226" t="n">
-        <v>860.775634765625</v>
+        <v>860.7756958007812</v>
       </c>
       <c r="G226" t="n">
         <v>64.94000244140625</v>
       </c>
       <c r="H226" t="n">
-        <v>555.1956176757812</v>
+        <v>555.1957397460938</v>
       </c>
       <c r="I226" t="n">
         <v>3595.06884765625</v>
@@ -7686,7 +7686,7 @@
         <v>44895</v>
       </c>
       <c r="B227" t="n">
-        <v>2518.174560546875</v>
+        <v>2518.17431640625</v>
       </c>
       <c r="C227" t="n">
         <v>2908.5</v>
@@ -7730,7 +7730,7 @@
         <v>2113.550048828125</v>
       </c>
       <c r="F228" t="n">
-        <v>872.880615234375</v>
+        <v>872.8805541992188</v>
       </c>
       <c r="G228" t="n">
         <v>66.08000183105469</v>
@@ -7756,7 +7756,7 @@
         <v>2745.699951171875</v>
       </c>
       <c r="D229" t="n">
-        <v>3915.376220703125</v>
+        <v>3915.3759765625</v>
       </c>
       <c r="E229" t="n">
         <v>2062.300048828125</v>
@@ -7768,7 +7768,7 @@
         <v>65.05999755859375</v>
       </c>
       <c r="H229" t="n">
-        <v>567.97119140625</v>
+        <v>567.9712524414062</v>
       </c>
       <c r="I229" t="n">
         <v>3574.74658203125</v>
@@ -7782,7 +7782,7 @@
         <v>44900</v>
       </c>
       <c r="B230" t="n">
-        <v>2575.007080078125</v>
+        <v>2575.0068359375</v>
       </c>
       <c r="C230" t="n">
         <v>2716.14990234375</v>
@@ -7800,7 +7800,7 @@
         <v>64.61000061035156</v>
       </c>
       <c r="H230" t="n">
-        <v>563.4506225585938</v>
+        <v>563.45068359375</v>
       </c>
       <c r="I230" t="n">
         <v>3585.182373046875</v>
@@ -7846,7 +7846,7 @@
         <v>44902</v>
       </c>
       <c r="B232" t="n">
-        <v>2560.123291015625</v>
+        <v>2560.12353515625</v>
       </c>
       <c r="C232" t="n">
         <v>2741.550048828125</v>
@@ -7896,7 +7896,7 @@
         <v>64.75</v>
       </c>
       <c r="H233" t="n">
-        <v>577.60205078125</v>
+        <v>577.6019897460938</v>
       </c>
       <c r="I233" t="n">
         <v>3689.839111328125</v>
@@ -7910,7 +7910,7 @@
         <v>44904</v>
       </c>
       <c r="B234" t="n">
-        <v>2573.43505859375</v>
+        <v>2573.435302734375</v>
       </c>
       <c r="C234" t="n">
         <v>2646.39990234375</v>
@@ -7942,7 +7942,7 @@
         <v>44907</v>
       </c>
       <c r="B235" t="n">
-        <v>2595.932373046875</v>
+        <v>2595.9326171875</v>
       </c>
       <c r="C235" t="n">
         <v>2687.85009765625</v>
@@ -7960,7 +7960,7 @@
         <v>62.04000091552734</v>
       </c>
       <c r="H235" t="n">
-        <v>574.9485473632812</v>
+        <v>574.9486694335938</v>
       </c>
       <c r="I235" t="n">
         <v>3636.012939453125</v>
@@ -7992,7 +7992,7 @@
         <v>64.59999847412109</v>
       </c>
       <c r="H236" t="n">
-        <v>574.457275390625</v>
+        <v>574.4573364257812</v>
       </c>
       <c r="I236" t="n">
         <v>3581.3876953125</v>
@@ -8006,7 +8006,7 @@
         <v>44909</v>
       </c>
       <c r="B237" t="n">
-        <v>2621.671630859375</v>
+        <v>2621.671875</v>
       </c>
       <c r="C237" t="n">
         <v>2672.449951171875</v>
@@ -8024,7 +8024,7 @@
         <v>63.86999893188477</v>
       </c>
       <c r="H237" t="n">
-        <v>572.14794921875</v>
+        <v>572.1478271484375</v>
       </c>
       <c r="I237" t="n">
         <v>3513.031494140625</v>
@@ -8050,13 +8050,13 @@
         <v>2024.900024414062</v>
       </c>
       <c r="F238" t="n">
-        <v>866.4114379882812</v>
+        <v>866.4114990234375</v>
       </c>
       <c r="G238" t="n">
         <v>63.09000015258789</v>
       </c>
       <c r="H238" t="n">
-        <v>551.5104370117188</v>
+        <v>551.510498046875</v>
       </c>
       <c r="I238" t="n">
         <v>3545.88671875</v>
@@ -8070,7 +8070,7 @@
         <v>44911</v>
       </c>
       <c r="B239" t="n">
-        <v>2570.7333984375</v>
+        <v>2570.733642578125</v>
       </c>
       <c r="C239" t="n">
         <v>2643.5</v>
@@ -8108,7 +8108,7 @@
         <v>2679.300048828125</v>
       </c>
       <c r="D240" t="n">
-        <v>4067.8984375</v>
+        <v>4067.898681640625</v>
       </c>
       <c r="E240" t="n">
         <v>2062.050048828125</v>
@@ -8134,7 +8134,7 @@
         <v>44915</v>
       </c>
       <c r="B241" t="n">
-        <v>2546.91015625</v>
+        <v>2546.909912109375</v>
       </c>
       <c r="C241" t="n">
         <v>2688.35009765625</v>
@@ -8146,7 +8146,7 @@
         <v>2061.64990234375</v>
       </c>
       <c r="F241" t="n">
-        <v>866.70556640625</v>
+        <v>866.7056274414062</v>
       </c>
       <c r="G241" t="n">
         <v>61.15000152587891</v>
@@ -8166,7 +8166,7 @@
         <v>44916</v>
       </c>
       <c r="B242" t="n">
-        <v>2496.266357421875</v>
+        <v>2496.2666015625</v>
       </c>
       <c r="C242" t="n">
         <v>2615.75</v>
@@ -8178,7 +8178,7 @@
         <v>1968.25</v>
       </c>
       <c r="F242" t="n">
-        <v>840.6333618164062</v>
+        <v>840.6334228515625</v>
       </c>
       <c r="G242" t="n">
         <v>58.09999847412109</v>
@@ -8198,7 +8198,7 @@
         <v>44917</v>
       </c>
       <c r="B243" t="n">
-        <v>2469.49560546875</v>
+        <v>2469.495849609375</v>
       </c>
       <c r="C243" t="n">
         <v>2518</v>
@@ -8210,7 +8210,7 @@
         <v>1980.75</v>
       </c>
       <c r="F243" t="n">
-        <v>839.8983154296875</v>
+        <v>839.8982543945312</v>
       </c>
       <c r="G243" t="n">
         <v>55.20000076293945</v>
@@ -8230,7 +8230,7 @@
         <v>44918</v>
       </c>
       <c r="B244" t="n">
-        <v>2332.3505859375</v>
+        <v>2332.350830078125</v>
       </c>
       <c r="C244" t="n">
         <v>2270.199951171875</v>
@@ -8248,7 +8248,7 @@
         <v>52.43999862670898</v>
       </c>
       <c r="H244" t="n">
-        <v>482.7681579589844</v>
+        <v>482.7681884765625</v>
       </c>
       <c r="I244" t="n">
         <v>3228.172607421875</v>
@@ -8280,7 +8280,7 @@
         <v>55.06000137329102</v>
       </c>
       <c r="H245" t="n">
-        <v>505.2728271484375</v>
+        <v>505.2728576660156</v>
       </c>
       <c r="I245" t="n">
         <v>3307.163818359375</v>
@@ -8294,7 +8294,7 @@
         <v>44922</v>
       </c>
       <c r="B246" t="n">
-        <v>2434.42333984375</v>
+        <v>2434.423583984375</v>
       </c>
       <c r="C246" t="n">
         <v>2501.800048828125</v>
@@ -8326,7 +8326,7 @@
         <v>44923</v>
       </c>
       <c r="B247" t="n">
-        <v>2412.171630859375</v>
+        <v>2412.171875</v>
       </c>
       <c r="C247" t="n">
         <v>2564.449951171875</v>
@@ -8344,7 +8344,7 @@
         <v>60.70000076293945</v>
       </c>
       <c r="H247" t="n">
-        <v>509.4494323730469</v>
+        <v>509.4495239257812</v>
       </c>
       <c r="I247" t="n">
         <v>3600.861083984375</v>
@@ -8370,7 +8370,7 @@
         <v>1910.25</v>
       </c>
       <c r="F248" t="n">
-        <v>803.2892456054688</v>
+        <v>803.289306640625</v>
       </c>
       <c r="G248" t="n">
         <v>60.90000152587891</v>
@@ -8390,7 +8390,7 @@
         <v>44925</v>
       </c>
       <c r="B249" t="n">
-        <v>2398.663818359375</v>
+        <v>2398.66357421875</v>
       </c>
       <c r="C249" t="n">
         <v>2589.25</v>
@@ -8408,7 +8408,7 @@
         <v>59.90999984741211</v>
       </c>
       <c r="H249" t="n">
-        <v>515.0509643554688</v>
+        <v>515.051025390625</v>
       </c>
       <c r="I249" t="n">
         <v>3687.791748046875</v>
@@ -8466,13 +8466,13 @@
         <v>1892.949951171875</v>
       </c>
       <c r="F251" t="n">
-        <v>804.1715087890625</v>
+        <v>804.1714477539062</v>
       </c>
       <c r="G251" t="n">
         <v>58.95000076293945</v>
       </c>
       <c r="H251" t="n">
-        <v>521.78271484375</v>
+        <v>521.7827758789062</v>
       </c>
       <c r="I251" t="n">
         <v>3593.720703125</v>
@@ -8486,13 +8486,13 @@
         <v>44930</v>
       </c>
       <c r="B252" t="n">
-        <v>2366.931884765625</v>
+        <v>2366.931640625</v>
       </c>
       <c r="C252" t="n">
         <v>2512.699951171875</v>
       </c>
       <c r="D252" t="n">
-        <v>3820.099365234375</v>
+        <v>3820.099609375</v>
       </c>
       <c r="E252" t="n">
         <v>1860.5</v>
@@ -8504,7 +8504,7 @@
         <v>57.31999969482422</v>
       </c>
       <c r="H252" t="n">
-        <v>509.8915710449219</v>
+        <v>509.8916320800781</v>
       </c>
       <c r="I252" t="n">
         <v>3472.537109375</v>
@@ -8518,7 +8518,7 @@
         <v>44931</v>
       </c>
       <c r="B253" t="n">
-        <v>2397.2880859375</v>
+        <v>2397.288330078125</v>
       </c>
       <c r="C253" t="n">
         <v>2554.14990234375</v>
@@ -8530,13 +8530,13 @@
         <v>1860</v>
       </c>
       <c r="F253" t="n">
-        <v>803.3383178710938</v>
+        <v>803.3382568359375</v>
       </c>
       <c r="G253" t="n">
         <v>57.75</v>
       </c>
       <c r="H253" t="n">
-        <v>515.6897583007812</v>
+        <v>515.6898193359375</v>
       </c>
       <c r="I253" t="n">
         <v>3628.722900390625</v>
@@ -8568,7 +8568,7 @@
         <v>56.68000030517578</v>
       </c>
       <c r="H254" t="n">
-        <v>510.8252563476562</v>
+        <v>510.8252258300781</v>
       </c>
       <c r="I254" t="n">
         <v>3550.530029296875</v>
@@ -8582,13 +8582,13 @@
         <v>44935</v>
       </c>
       <c r="B255" t="n">
-        <v>2421.30810546875</v>
+        <v>2421.308349609375</v>
       </c>
       <c r="C255" t="n">
         <v>2614.5</v>
       </c>
       <c r="D255" t="n">
-        <v>3848.298095703125</v>
+        <v>3848.2978515625</v>
       </c>
       <c r="E255" t="n">
         <v>1891.449951171875</v>
@@ -8600,7 +8600,7 @@
         <v>57.54000091552734</v>
       </c>
       <c r="H255" t="n">
-        <v>515.6897583007812</v>
+        <v>515.6898193359375</v>
       </c>
       <c r="I255" t="n">
         <v>3624.029296875</v>
@@ -8614,7 +8614,7 @@
         <v>44936</v>
       </c>
       <c r="B256" t="n">
-        <v>2376.411865234375</v>
+        <v>2376.412109375</v>
       </c>
       <c r="C256" t="n">
         <v>2652</v>
@@ -8632,7 +8632,7 @@
         <v>55.84000015258789</v>
       </c>
       <c r="H256" t="n">
-        <v>505.5675964355469</v>
+        <v>505.567626953125</v>
       </c>
       <c r="I256" t="n">
         <v>3651.3916015625</v>
@@ -8664,7 +8664,7 @@
         <v>55.2400016784668</v>
       </c>
       <c r="H257" t="n">
-        <v>499.3272399902344</v>
+        <v>499.3272094726562</v>
       </c>
       <c r="I257" t="n">
         <v>3611.546630859375</v>
@@ -8696,7 +8696,7 @@
         <v>54.72999954223633</v>
       </c>
       <c r="H258" t="n">
-        <v>501.5875549316406</v>
+        <v>501.5875244140625</v>
       </c>
       <c r="I258" t="n">
         <v>3644.051513671875</v>
@@ -8728,7 +8728,7 @@
         <v>55.7400016784668</v>
       </c>
       <c r="H259" t="n">
-        <v>509.6950988769531</v>
+        <v>509.6951599121094</v>
       </c>
       <c r="I259" t="n">
         <v>3710.011474609375</v>
@@ -8742,7 +8742,7 @@
         <v>44942</v>
       </c>
       <c r="B260" t="n">
-        <v>2319.873779296875</v>
+        <v>2319.8740234375</v>
       </c>
       <c r="C260" t="n">
         <v>2703.10009765625</v>
@@ -8760,7 +8760,7 @@
         <v>54.59000015258789</v>
       </c>
       <c r="H260" t="n">
-        <v>508.0735778808594</v>
+        <v>508.0735473632812</v>
       </c>
       <c r="I260" t="n">
         <v>3725.58984375</v>
@@ -8780,19 +8780,19 @@
         <v>2725.050048828125</v>
       </c>
       <c r="D261" t="n">
-        <v>3632.740234375</v>
+        <v>3632.740478515625</v>
       </c>
       <c r="E261" t="n">
         <v>2166.14990234375</v>
       </c>
       <c r="F261" t="n">
-        <v>769.1797485351562</v>
+        <v>769.1798095703125</v>
       </c>
       <c r="G261" t="n">
         <v>56.38999938964844</v>
       </c>
       <c r="H261" t="n">
-        <v>508.56494140625</v>
+        <v>508.5649108886719</v>
       </c>
       <c r="I261" t="n">
         <v>3844.7265625</v>
@@ -8806,7 +8806,7 @@
         <v>44944</v>
       </c>
       <c r="B262" t="n">
-        <v>2323.410400390625</v>
+        <v>2323.410888671875</v>
       </c>
       <c r="C262" t="n">
         <v>2710.75</v>
@@ -8824,7 +8824,7 @@
         <v>55.7400016784668</v>
       </c>
       <c r="H262" t="n">
-        <v>511.4639892578125</v>
+        <v>511.4640197753906</v>
       </c>
       <c r="I262" t="n">
         <v>3800.237548828125</v>
@@ -8838,7 +8838,7 @@
         <v>44945</v>
       </c>
       <c r="B263" t="n">
-        <v>2349.1005859375</v>
+        <v>2349.100830078125</v>
       </c>
       <c r="C263" t="n">
         <v>2734.10009765625</v>
@@ -8856,7 +8856,7 @@
         <v>55.5099983215332</v>
       </c>
       <c r="H263" t="n">
-        <v>510.2847595214844</v>
+        <v>510.2847290039062</v>
       </c>
       <c r="I263" t="n">
         <v>3830.29638671875</v>
@@ -8876,7 +8876,7 @@
         <v>2737.949951171875</v>
       </c>
       <c r="D264" t="n">
-        <v>3449.872802734375</v>
+        <v>3449.873046875</v>
       </c>
       <c r="E264" t="n">
         <v>1975.599975585938</v>
@@ -8888,7 +8888,7 @@
         <v>55.0099983215332</v>
       </c>
       <c r="H264" t="n">
-        <v>508.8106689453125</v>
+        <v>508.8106384277344</v>
       </c>
       <c r="I264" t="n">
         <v>3913.531982421875</v>
@@ -8908,7 +8908,7 @@
         <v>2784.10009765625</v>
       </c>
       <c r="D265" t="n">
-        <v>3430.109130859375</v>
+        <v>3430.10888671875</v>
       </c>
       <c r="E265" t="n">
         <v>1931.849975585938</v>
@@ -8934,7 +8934,7 @@
         <v>44950</v>
       </c>
       <c r="B266" t="n">
-        <v>2294.625732421875</v>
+        <v>2294.6259765625</v>
       </c>
       <c r="C266" t="n">
         <v>2762.14990234375</v>
@@ -8946,7 +8946,7 @@
         <v>1916.800048828125</v>
       </c>
       <c r="F266" t="n">
-        <v>746.0970458984375</v>
+        <v>746.0969848632812</v>
       </c>
       <c r="G266" t="n">
         <v>54.93000030517578</v>
@@ -8978,13 +8978,13 @@
         <v>1857.800048828125</v>
       </c>
       <c r="F267" t="n">
-        <v>699.0004272460938</v>
+        <v>699.0003662109375</v>
       </c>
       <c r="G267" t="n">
         <v>52.20000076293945</v>
       </c>
       <c r="H267" t="n">
-        <v>452.2543029785156</v>
+        <v>452.2542724609375</v>
       </c>
       <c r="I267" t="n">
         <v>3654.986572265625</v>
@@ -8998,7 +8998,7 @@
         <v>44953</v>
       </c>
       <c r="B268" t="n">
-        <v>1846.69384765625</v>
+        <v>1846.693969726562</v>
       </c>
       <c r="C268" t="n">
         <v>2014.199951171875</v>
@@ -9016,7 +9016,7 @@
         <v>49.59000015258789</v>
       </c>
       <c r="H268" t="n">
-        <v>373.8812561035156</v>
+        <v>373.8812255859375</v>
       </c>
       <c r="I268" t="n">
         <v>2923.9892578125</v>
@@ -9030,7 +9030,7 @@
         <v>44956</v>
       </c>
       <c r="B269" t="n">
-        <v>1870.664916992188</v>
+        <v>1870.664794921875</v>
       </c>
       <c r="C269" t="n">
         <v>1708.199951171875</v>
@@ -9062,13 +9062,13 @@
         <v>44957</v>
       </c>
       <c r="B270" t="n">
-        <v>1933.686889648438</v>
+        <v>1933.686767578125</v>
       </c>
       <c r="C270" t="n">
         <v>1774</v>
       </c>
       <c r="D270" t="n">
-        <v>2968.49853515625</v>
+        <v>2968.498779296875</v>
       </c>
       <c r="E270" t="n">
         <v>1223.900024414062</v>
@@ -9094,19 +9094,19 @@
         <v>44958</v>
       </c>
       <c r="B271" t="n">
-        <v>1813.9794921875</v>
+        <v>1813.979614257812</v>
       </c>
       <c r="C271" t="n">
         <v>1723.5</v>
       </c>
       <c r="D271" t="n">
-        <v>2131.471923828125</v>
+        <v>2131.4716796875</v>
       </c>
       <c r="E271" t="n">
         <v>1155.349975585938</v>
       </c>
       <c r="F271" t="n">
-        <v>485.32568359375</v>
+        <v>485.3257141113281</v>
       </c>
       <c r="G271" t="n">
         <v>42.52999877929688</v>
@@ -9126,7 +9126,7 @@
         <v>44959</v>
       </c>
       <c r="B272" t="n">
-        <v>1808.870849609375</v>
+        <v>1808.87109375</v>
       </c>
       <c r="C272" t="n">
         <v>1551.150024414062</v>
@@ -9158,7 +9158,7 @@
         <v>44960</v>
       </c>
       <c r="B273" t="n">
-        <v>1892.867309570312</v>
+        <v>1892.867431640625</v>
       </c>
       <c r="C273" t="n">
         <v>1396.050048828125</v>
@@ -9170,7 +9170,7 @@
         <v>935.9000244140625</v>
       </c>
       <c r="F273" t="n">
-        <v>488.9523010253906</v>
+        <v>488.9523315429688</v>
       </c>
       <c r="G273" t="n">
         <v>38.38999938964844</v>
@@ -9190,7 +9190,7 @@
         <v>44963</v>
       </c>
       <c r="B274" t="n">
-        <v>1934.914916992188</v>
+        <v>1934.914794921875</v>
       </c>
       <c r="C274" t="n">
         <v>1256.449951171875</v>
@@ -9228,7 +9228,7 @@
         <v>1252.199951171875</v>
       </c>
       <c r="D275" t="n">
-        <v>1799.675537109375</v>
+        <v>1799.675415039062</v>
       </c>
       <c r="E275" t="n">
         <v>844.6500244140625</v>
@@ -9254,13 +9254,13 @@
         <v>44965</v>
       </c>
       <c r="B276" t="n">
-        <v>1939.041015625</v>
+        <v>1939.040771484375</v>
       </c>
       <c r="C276" t="n">
         <v>1314.800048828125</v>
       </c>
       <c r="D276" t="n">
-        <v>2160.3193359375</v>
+        <v>2160.319580078125</v>
       </c>
       <c r="E276" t="n">
         <v>802.4500122070312</v>
@@ -9324,7 +9324,7 @@
         <v>1186.650024414062</v>
       </c>
       <c r="D278" t="n">
-        <v>1843.595581054688</v>
+        <v>1843.595458984375</v>
       </c>
       <c r="E278" t="n">
         <v>724.25</v>
@@ -9350,13 +9350,13 @@
         <v>44970</v>
       </c>
       <c r="B279" t="n">
-        <v>1791.08935546875</v>
+        <v>1791.089477539062</v>
       </c>
       <c r="C279" t="n">
         <v>1127.349975585938</v>
       </c>
       <c r="D279" t="n">
-        <v>1714.530517578125</v>
+        <v>1714.530395507812</v>
       </c>
       <c r="E279" t="n">
         <v>688.0499877929688</v>
@@ -9368,7 +9368,7 @@
         <v>31.20000076293945</v>
       </c>
       <c r="H279" t="n">
-        <v>336.537353515625</v>
+        <v>336.5373229980469</v>
       </c>
       <c r="I279" t="n">
         <v>1191.016357421875</v>
@@ -9382,13 +9382,13 @@
         <v>44971</v>
       </c>
       <c r="B280" t="n">
-        <v>1798.113525390625</v>
+        <v>1798.113647460938</v>
       </c>
       <c r="C280" t="n">
         <v>1071</v>
       </c>
       <c r="D280" t="n">
-        <v>1746.522094726562</v>
+        <v>1746.522216796875</v>
       </c>
       <c r="E280" t="n">
         <v>653.6500244140625</v>
@@ -9414,7 +9414,7 @@
         <v>44972</v>
       </c>
       <c r="B281" t="n">
-        <v>1819.579345703125</v>
+        <v>1819.579467773438</v>
       </c>
       <c r="C281" t="n">
         <v>1017.450012207031</v>
@@ -9478,19 +9478,19 @@
         <v>44974</v>
       </c>
       <c r="B283" t="n">
-        <v>1807.053466796875</v>
+        <v>1807.053588867188</v>
       </c>
       <c r="C283" t="n">
         <v>920.4000244140625</v>
       </c>
       <c r="D283" t="n">
-        <v>1719.571166992188</v>
+        <v>1719.5712890625</v>
       </c>
       <c r="E283" t="n">
         <v>628.6500244140625</v>
       </c>
       <c r="F283" t="n">
-        <v>567.1689453125</v>
+        <v>567.1690063476562</v>
       </c>
       <c r="G283" t="n">
         <v>31.03000068664551</v>
@@ -9516,19 +9516,19 @@
         <v>874.4000244140625</v>
       </c>
       <c r="D284" t="n">
-        <v>1618.505126953125</v>
+        <v>1618.505249023438</v>
       </c>
       <c r="E284" t="n">
         <v>597.25</v>
       </c>
       <c r="F284" t="n">
-        <v>568.1981201171875</v>
+        <v>568.1981811523438</v>
       </c>
       <c r="G284" t="n">
         <v>32.58000183105469</v>
       </c>
       <c r="H284" t="n">
-        <v>346.3647155761719</v>
+        <v>346.3646850585938</v>
       </c>
       <c r="I284" t="n">
         <v>921.685791015625</v>
@@ -9542,7 +9542,7 @@
         <v>44978</v>
       </c>
       <c r="B285" t="n">
-        <v>1796.2470703125</v>
+        <v>1796.246948242188</v>
       </c>
       <c r="C285" t="n">
         <v>830.7000122070312</v>
@@ -9574,7 +9574,7 @@
         <v>44979</v>
       </c>
       <c r="B286" t="n">
-        <v>1721.386962890625</v>
+        <v>1721.386840820312</v>
       </c>
       <c r="C286" t="n">
         <v>789.2000122070312</v>
@@ -9606,7 +9606,7 @@
         <v>44980</v>
       </c>
       <c r="B287" t="n">
-        <v>1697.170532226562</v>
+        <v>1697.17041015625</v>
       </c>
       <c r="C287" t="n">
         <v>749.75</v>
@@ -9618,7 +9618,7 @@
         <v>512.0999755859375</v>
       </c>
       <c r="F287" t="n">
-        <v>540.9006958007812</v>
+        <v>540.9007568359375</v>
       </c>
       <c r="G287" t="n">
         <v>30.8700008392334</v>
@@ -9656,7 +9656,7 @@
         <v>29.32999992370605</v>
       </c>
       <c r="H288" t="n">
-        <v>339.2889404296875</v>
+        <v>339.2890014648438</v>
       </c>
       <c r="I288" t="n">
         <v>750.770263671875</v>
@@ -9702,7 +9702,7 @@
         <v>44985</v>
       </c>
       <c r="B290" t="n">
-        <v>1701.24755859375</v>
+        <v>1701.247436523438</v>
       </c>
       <c r="C290" t="n">
         <v>642.9000244140625</v>
@@ -9720,7 +9720,7 @@
         <v>29.26000022888184</v>
       </c>
       <c r="H290" t="n">
-        <v>336.193359375</v>
+        <v>336.1933898925781</v>
       </c>
       <c r="I290" t="n">
         <v>677.6204833984375</v>
@@ -9734,13 +9734,13 @@
         <v>44986</v>
       </c>
       <c r="B291" t="n">
-        <v>1738.333618164062</v>
+        <v>1738.33349609375</v>
       </c>
       <c r="C291" t="n">
         <v>675</v>
       </c>
       <c r="D291" t="n">
-        <v>1561.458984375</v>
+        <v>1561.459106445312</v>
       </c>
       <c r="E291" t="n">
         <v>509.5499877929688</v>
@@ -9766,13 +9766,13 @@
         <v>44987</v>
       </c>
       <c r="B292" t="n">
-        <v>1769.672607421875</v>
+        <v>1769.672729492188</v>
       </c>
       <c r="C292" t="n">
         <v>708.75</v>
       </c>
       <c r="D292" t="n">
-        <v>1604.330810546875</v>
+        <v>1604.330932617188</v>
       </c>
       <c r="E292" t="n">
         <v>535</v>
@@ -9798,13 +9798,13 @@
         <v>44988</v>
       </c>
       <c r="B293" t="n">
-        <v>1860.74267578125</v>
+        <v>1860.742431640625</v>
       </c>
       <c r="C293" t="n">
         <v>744.1500244140625</v>
       </c>
       <c r="D293" t="n">
-        <v>1876.086547851562</v>
+        <v>1876.08642578125</v>
       </c>
       <c r="E293" t="n">
         <v>561.75</v>
@@ -9816,7 +9816,7 @@
         <v>33.86000061035156</v>
       </c>
       <c r="H293" t="n">
-        <v>385.0843811035156</v>
+        <v>385.0844116210938</v>
       </c>
       <c r="I293" t="n">
         <v>780.2297973632812</v>
@@ -9830,13 +9830,13 @@
         <v>44991</v>
       </c>
       <c r="B294" t="n">
-        <v>1832.9892578125</v>
+        <v>1832.989379882812</v>
       </c>
       <c r="C294" t="n">
         <v>781.3499755859375</v>
       </c>
       <c r="D294" t="n">
-        <v>1979.298583984375</v>
+        <v>1979.298706054688</v>
       </c>
       <c r="E294" t="n">
         <v>589.7999877929688</v>
@@ -9848,7 +9848,7 @@
         <v>35.54999923706055</v>
       </c>
       <c r="H294" t="n">
-        <v>378.8440551757812</v>
+        <v>378.8440246582031</v>
       </c>
       <c r="I294" t="n">
         <v>819.2263793945312</v>
@@ -9880,7 +9880,7 @@
         <v>37.31999969482422</v>
       </c>
       <c r="H295" t="n">
-        <v>385.3300476074219</v>
+        <v>385.330078125</v>
       </c>
       <c r="I295" t="n">
         <v>860.170166015625</v>
@@ -9894,7 +9894,7 @@
         <v>44994</v>
       </c>
       <c r="B296" t="n">
-        <v>1827.389526367188</v>
+        <v>1827.389404296875</v>
       </c>
       <c r="C296" t="n">
         <v>861.4000244140625</v>
@@ -9926,13 +9926,13 @@
         <v>44995</v>
       </c>
       <c r="B297" t="n">
-        <v>1814.421752929688</v>
+        <v>1814.421508789062</v>
       </c>
       <c r="C297" t="n">
         <v>904.4500122070312</v>
       </c>
       <c r="D297" t="n">
-        <v>1892.756225585938</v>
+        <v>1892.756103515625</v>
       </c>
       <c r="E297" t="n">
         <v>682.7000122070312</v>
@@ -9958,13 +9958,13 @@
         <v>44998</v>
       </c>
       <c r="B298" t="n">
-        <v>1738.873901367188</v>
+        <v>1738.873779296875</v>
       </c>
       <c r="C298" t="n">
         <v>949.6500244140625</v>
       </c>
       <c r="D298" t="n">
-        <v>1870.995727539062</v>
+        <v>1870.995849609375</v>
       </c>
       <c r="E298" t="n">
         <v>716.7999877929688</v>
@@ -9990,7 +9990,7 @@
         <v>44999</v>
       </c>
       <c r="B299" t="n">
-        <v>1707.829833984375</v>
+        <v>1707.829711914062</v>
       </c>
       <c r="C299" t="n">
         <v>902.2000122070312</v>
@@ -10022,13 +10022,13 @@
         <v>45000</v>
       </c>
       <c r="B300" t="n">
-        <v>1709.4013671875</v>
+        <v>1709.401489257812</v>
       </c>
       <c r="C300" t="n">
         <v>928.3499755859375</v>
       </c>
       <c r="D300" t="n">
-        <v>1835.66015625</v>
+        <v>1835.660034179688</v>
       </c>
       <c r="E300" t="n">
         <v>740.4000244140625</v>
@@ -10054,19 +10054,19 @@
         <v>45001</v>
       </c>
       <c r="B301" t="n">
-        <v>1719.5205078125</v>
+        <v>1719.520385742188</v>
       </c>
       <c r="C301" t="n">
         <v>973.7000122070312</v>
       </c>
       <c r="D301" t="n">
-        <v>1840.451293945312</v>
+        <v>1840.451416015625</v>
       </c>
       <c r="E301" t="n">
         <v>777.4000244140625</v>
       </c>
       <c r="F301" t="n">
-        <v>666.1160888671875</v>
+        <v>666.1160278320312</v>
       </c>
       <c r="G301" t="n">
         <v>39.7400016784668</v>
@@ -10092,7 +10092,7 @@
         <v>1022.349975585938</v>
       </c>
       <c r="D302" t="n">
-        <v>1873.141845703125</v>
+        <v>1873.141967773438</v>
       </c>
       <c r="E302" t="n">
         <v>816.25</v>
@@ -10104,7 +10104,7 @@
         <v>39.9900016784668</v>
       </c>
       <c r="H302" t="n">
-        <v>371.9157409667969</v>
+        <v>371.915771484375</v>
       </c>
       <c r="I302" t="n">
         <v>896.5203247070312</v>
@@ -10118,13 +10118,13 @@
         <v>45005</v>
       </c>
       <c r="B303" t="n">
-        <v>1665.7822265625</v>
+        <v>1665.782348632812</v>
       </c>
       <c r="C303" t="n">
         <v>1009.099975585938</v>
       </c>
       <c r="D303" t="n">
-        <v>1801.671752929688</v>
+        <v>1801.671875</v>
       </c>
       <c r="E303" t="n">
         <v>848.6500244140625</v>
@@ -10150,13 +10150,13 @@
         <v>45006</v>
       </c>
       <c r="B304" t="n">
-        <v>1694.272216796875</v>
+        <v>1694.272338867188</v>
       </c>
       <c r="C304" t="n">
         <v>1006.099975585938</v>
       </c>
       <c r="D304" t="n">
-        <v>1820.936889648438</v>
+        <v>1820.936767578125</v>
       </c>
       <c r="E304" t="n">
         <v>891.0499877929688</v>
@@ -10168,7 +10168,7 @@
         <v>39.93999862670898</v>
       </c>
       <c r="H304" t="n">
-        <v>364.4961242675781</v>
+        <v>364.49609375</v>
       </c>
       <c r="I304" t="n">
         <v>889.579833984375</v>
@@ -10194,7 +10194,7 @@
         <v>935.5999755859375</v>
       </c>
       <c r="F305" t="n">
-        <v>644.1114501953125</v>
+        <v>644.1115112304688</v>
       </c>
       <c r="G305" t="n">
         <v>40.81000137329102</v>
@@ -10214,13 +10214,13 @@
         <v>45008</v>
       </c>
       <c r="B306" t="n">
-        <v>1707.7314453125</v>
+        <v>1707.731323242188</v>
       </c>
       <c r="C306" t="n">
         <v>1084.400024414062</v>
       </c>
       <c r="D306" t="n">
-        <v>1790.74169921875</v>
+        <v>1790.741821289062</v>
       </c>
       <c r="E306" t="n">
         <v>982.3499755859375</v>
@@ -10232,7 +10232,7 @@
         <v>40.27999877929688</v>
       </c>
       <c r="H306" t="n">
-        <v>365.7244873046875</v>
+        <v>365.7245483398438</v>
       </c>
       <c r="I306" t="n">
         <v>980.704833984375</v>
@@ -10258,13 +10258,13 @@
         <v>1029.349975585938</v>
       </c>
       <c r="F307" t="n">
-        <v>625.3414306640625</v>
+        <v>625.3414916992188</v>
       </c>
       <c r="G307" t="n">
         <v>38.52000045776367</v>
       </c>
       <c r="H307" t="n">
-        <v>365.3805847167969</v>
+        <v>365.3805541992188</v>
       </c>
       <c r="I307" t="n">
         <v>1006.070129394531</v>
@@ -10278,7 +10278,7 @@
         <v>45012</v>
       </c>
       <c r="B308" t="n">
-        <v>1655.319580078125</v>
+        <v>1655.319458007812</v>
       </c>
       <c r="C308" t="n">
         <v>1068.400024414062</v>
@@ -10310,7 +10310,7 @@
         <v>45013</v>
       </c>
       <c r="B309" t="n">
-        <v>1585.568115234375</v>
+        <v>1585.568237304688</v>
       </c>
       <c r="C309" t="n">
         <v>1015</v>
@@ -10328,7 +10328,7 @@
         <v>34.77000045776367</v>
       </c>
       <c r="H309" t="n">
-        <v>352.7524108886719</v>
+        <v>352.7524719238281</v>
       </c>
       <c r="I309" t="n">
         <v>908.70361328125</v>
@@ -10342,7 +10342,7 @@
         <v>45014</v>
       </c>
       <c r="B310" t="n">
-        <v>1597.307983398438</v>
+        <v>1597.307861328125</v>
       </c>
       <c r="C310" t="n">
         <v>1003.450012207031</v>
@@ -10374,13 +10374,13 @@
         <v>45016</v>
       </c>
       <c r="B311" t="n">
-        <v>1637.881591796875</v>
+        <v>1637.881713867188</v>
       </c>
       <c r="C311" t="n">
         <v>993.0499877929688</v>
       </c>
       <c r="D311" t="n">
-        <v>1747.270874023438</v>
+        <v>1747.270751953125</v>
       </c>
       <c r="E311" t="n">
         <v>881.1500244140625</v>
@@ -10392,7 +10392,7 @@
         <v>38.31999969482422</v>
       </c>
       <c r="H311" t="n">
-        <v>359.2384338378906</v>
+        <v>359.2384643554688</v>
       </c>
       <c r="I311" t="n">
         <v>866.5614013671875</v>
@@ -10412,7 +10412,7 @@
         <v>943.4000244140625</v>
       </c>
       <c r="D312" t="n">
-        <v>1714.330688476562</v>
+        <v>1714.330810546875</v>
       </c>
       <c r="E312" t="n">
         <v>837.4500122070312</v>
@@ -10438,19 +10438,19 @@
         <v>45021</v>
       </c>
       <c r="B313" t="n">
-        <v>1658.266845703125</v>
+        <v>1658.266723632812</v>
       </c>
       <c r="C313" t="n">
         <v>907.8499755859375</v>
       </c>
       <c r="D313" t="n">
-        <v>1694.916015625</v>
+        <v>1694.916137695312</v>
       </c>
       <c r="E313" t="n">
         <v>815.5999755859375</v>
       </c>
       <c r="F313" t="n">
-        <v>624.1162109375</v>
+        <v>624.1162719726562</v>
       </c>
       <c r="G313" t="n">
         <v>38.02000045776367</v>
@@ -10470,19 +10470,19 @@
         <v>45022</v>
       </c>
       <c r="B314" t="n">
-        <v>1681.893798828125</v>
+        <v>1681.893920898438</v>
       </c>
       <c r="C314" t="n">
         <v>953.2000122070312</v>
       </c>
       <c r="D314" t="n">
-        <v>1750.864379882812</v>
+        <v>1750.864501953125</v>
       </c>
       <c r="E314" t="n">
         <v>856.3499755859375</v>
       </c>
       <c r="F314" t="n">
-        <v>628.8699951171875</v>
+        <v>628.8699340820312</v>
       </c>
       <c r="G314" t="n">
         <v>38.43999862670898</v>
@@ -10514,7 +10514,7 @@
         <v>899.1500244140625</v>
       </c>
       <c r="F315" t="n">
-        <v>639.0636596679688</v>
+        <v>639.063720703125</v>
       </c>
       <c r="G315" t="n">
         <v>38.79999923706055</v>
@@ -10534,7 +10534,7 @@
         <v>45027</v>
       </c>
       <c r="B316" t="n">
-        <v>1706.84716796875</v>
+        <v>1706.847290039062</v>
       </c>
       <c r="C316" t="n">
         <v>1050.849975585938</v>
@@ -10566,7 +10566,7 @@
         <v>45028</v>
       </c>
       <c r="B317" t="n">
-        <v>1727.0849609375</v>
+        <v>1727.085083007812</v>
       </c>
       <c r="C317" t="n">
         <v>1043.449951171875</v>
@@ -10578,7 +10578,7 @@
         <v>941.8499755859375</v>
       </c>
       <c r="F317" t="n">
-        <v>644.6996459960938</v>
+        <v>644.6995849609375</v>
       </c>
       <c r="G317" t="n">
         <v>38.4900016784668</v>
@@ -10604,19 +10604,19 @@
         <v>1030.849975585938</v>
       </c>
       <c r="D318" t="n">
-        <v>1867.352416992188</v>
+        <v>1867.352294921875</v>
       </c>
       <c r="E318" t="n">
         <v>941.1500244140625</v>
       </c>
       <c r="F318" t="n">
-        <v>648.522216796875</v>
+        <v>648.5221557617188</v>
       </c>
       <c r="G318" t="n">
         <v>37.83000183105469</v>
       </c>
       <c r="H318" t="n">
-        <v>385.87060546875</v>
+        <v>385.8705749511719</v>
       </c>
       <c r="I318" t="n">
         <v>912.8978881835938</v>
@@ -10636,7 +10636,7 @@
         <v>1039.5</v>
       </c>
       <c r="D319" t="n">
-        <v>1875.337768554688</v>
+        <v>1875.337890625</v>
       </c>
       <c r="E319" t="n">
         <v>962.5499877929688</v>
@@ -10662,25 +10662,25 @@
         <v>45034</v>
       </c>
       <c r="B320" t="n">
-        <v>1729.148071289062</v>
+        <v>1729.14794921875</v>
       </c>
       <c r="C320" t="n">
         <v>1032.050048828125</v>
       </c>
       <c r="D320" t="n">
-        <v>1847.588256835938</v>
+        <v>1847.58837890625</v>
       </c>
       <c r="E320" t="n">
         <v>952.25</v>
       </c>
       <c r="F320" t="n">
-        <v>645.483642578125</v>
+        <v>645.4835815429688</v>
       </c>
       <c r="G320" t="n">
         <v>37.66999816894531</v>
       </c>
       <c r="H320" t="n">
-        <v>376.4363403320312</v>
+        <v>376.4363098144531</v>
       </c>
       <c r="I320" t="n">
         <v>946.7514038085938</v>
@@ -10694,7 +10694,7 @@
         <v>45035</v>
       </c>
       <c r="B321" t="n">
-        <v>1718.5380859375</v>
+        <v>1718.537963867188</v>
       </c>
       <c r="C321" t="n">
         <v>1017.700012207031</v>
@@ -10706,13 +10706,13 @@
         <v>935.7999877929688</v>
       </c>
       <c r="F321" t="n">
-        <v>645.336669921875</v>
+        <v>645.3367309570312</v>
       </c>
       <c r="G321" t="n">
         <v>37.45999908447266</v>
       </c>
       <c r="H321" t="n">
-        <v>373.4881286621094</v>
+        <v>373.4880981445312</v>
       </c>
       <c r="I321" t="n">
         <v>929.0756225585938</v>
@@ -10726,13 +10726,13 @@
         <v>45036</v>
       </c>
       <c r="B322" t="n">
-        <v>1707.535034179688</v>
+        <v>1707.534912109375</v>
       </c>
       <c r="C322" t="n">
         <v>1011.099975585938</v>
       </c>
       <c r="D322" t="n">
-        <v>1839.552978515625</v>
+        <v>1839.552856445312</v>
       </c>
       <c r="E322" t="n">
         <v>933.0499877929688</v>
@@ -10744,7 +10744,7 @@
         <v>39.15999984741211</v>
       </c>
       <c r="H322" t="n">
-        <v>374.1269226074219</v>
+        <v>374.1268920898438</v>
       </c>
       <c r="I322" t="n">
         <v>926.9285888671875</v>
@@ -10758,7 +10758,7 @@
         <v>45037</v>
       </c>
       <c r="B323" t="n">
-        <v>1687.739135742188</v>
+        <v>1687.7392578125</v>
       </c>
       <c r="C323" t="n">
         <v>994.9000244140625</v>
@@ -10770,13 +10770,13 @@
         <v>916.2000122070312</v>
       </c>
       <c r="F323" t="n">
-        <v>648.4730834960938</v>
+        <v>648.47314453125</v>
       </c>
       <c r="G323" t="n">
         <v>39.84999847412109</v>
       </c>
       <c r="H323" t="n">
-        <v>368.6235656738281</v>
+        <v>368.6236267089844</v>
       </c>
       <c r="I323" t="n">
         <v>916.5428466796875</v>
@@ -10822,7 +10822,7 @@
         <v>45041</v>
       </c>
       <c r="B325" t="n">
-        <v>1705.619140625</v>
+        <v>1705.619384765625</v>
       </c>
       <c r="C325" t="n">
         <v>1012.950012207031</v>
@@ -10834,13 +10834,13 @@
         <v>931.1500244140625</v>
       </c>
       <c r="F325" t="n">
-        <v>658.1277465820312</v>
+        <v>658.1278076171875</v>
       </c>
       <c r="G325" t="n">
         <v>41.13000106811523</v>
       </c>
       <c r="H325" t="n">
-        <v>375.8958435058594</v>
+        <v>375.8958129882812</v>
       </c>
       <c r="I325" t="n">
         <v>933.968994140625</v>
@@ -10872,7 +10872,7 @@
         <v>42.27000045776367</v>
       </c>
       <c r="H326" t="n">
-        <v>379.7776489257812</v>
+        <v>379.7776184082031</v>
       </c>
       <c r="I326" t="n">
         <v>918.789794921875</v>
@@ -10904,7 +10904,7 @@
         <v>42.83000183105469</v>
       </c>
       <c r="H327" t="n">
-        <v>382.0870361328125</v>
+        <v>382.0870056152344</v>
       </c>
       <c r="I327" t="n">
         <v>915.84375</v>
@@ -10918,7 +10918,7 @@
         <v>45044</v>
       </c>
       <c r="B328" t="n">
-        <v>1731.849731445312</v>
+        <v>1731.849609375</v>
       </c>
       <c r="C328" t="n">
         <v>1029.449951171875</v>
@@ -10936,7 +10936,7 @@
         <v>44.97000122070312</v>
       </c>
       <c r="H328" t="n">
-        <v>389.6541442871094</v>
+        <v>389.6541137695312</v>
       </c>
       <c r="I328" t="n">
         <v>943.7056274414062</v>
@@ -10962,7 +10962,7 @@
         <v>974.6500244140625</v>
       </c>
       <c r="F329" t="n">
-        <v>667.9783325195312</v>
+        <v>667.9783935546875</v>
       </c>
       <c r="G329" t="n">
         <v>47.18999862670898</v>
@@ -10982,25 +10982,25 @@
         <v>45049</v>
       </c>
       <c r="B330" t="n">
-        <v>1712.938232421875</v>
+        <v>1712.938110351562</v>
       </c>
       <c r="C330" t="n">
         <v>993.0499877929688</v>
       </c>
       <c r="D330" t="n">
-        <v>1835.66015625</v>
+        <v>1835.660034179688</v>
       </c>
       <c r="E330" t="n">
         <v>942.0499877929688</v>
       </c>
       <c r="F330" t="n">
-        <v>656.363525390625</v>
+        <v>656.3634643554688</v>
       </c>
       <c r="G330" t="n">
         <v>46.33000183105469</v>
       </c>
       <c r="H330" t="n">
-        <v>377.0259399414062</v>
+        <v>377.0260009765625</v>
       </c>
       <c r="I330" t="n">
         <v>921.685791015625</v>
@@ -11020,7 +11020,7 @@
         <v>1011.549987792969</v>
       </c>
       <c r="D331" t="n">
-        <v>1907.778930664062</v>
+        <v>1907.77880859375</v>
       </c>
       <c r="E331" t="n">
         <v>945.5499877929688</v>
@@ -11032,7 +11032,7 @@
         <v>47.63000106811523</v>
       </c>
       <c r="H331" t="n">
-        <v>381.5956726074219</v>
+        <v>381.595703125</v>
       </c>
       <c r="I331" t="n">
         <v>928.9259033203125</v>
@@ -11084,7 +11084,7 @@
         <v>949.0499877929688</v>
       </c>
       <c r="D333" t="n">
-        <v>1884.071899414062</v>
+        <v>1884.072021484375</v>
       </c>
       <c r="E333" t="n">
         <v>917.2999877929688</v>
@@ -11096,7 +11096,7 @@
         <v>47.7400016784668</v>
       </c>
       <c r="H333" t="n">
-        <v>398.4987182617188</v>
+        <v>398.4986877441406</v>
       </c>
       <c r="I333" t="n">
         <v>871.7044067382812</v>
@@ -11110,7 +11110,7 @@
         <v>45055</v>
       </c>
       <c r="B334" t="n">
-        <v>1728.362060546875</v>
+        <v>1728.362182617188</v>
       </c>
       <c r="C334" t="n">
         <v>901.5999755859375</v>
@@ -11128,7 +11128,7 @@
         <v>48.06000137329102</v>
       </c>
       <c r="H334" t="n">
-        <v>398.6461486816406</v>
+        <v>398.6461181640625</v>
       </c>
       <c r="I334" t="n">
         <v>843.9423828125</v>
@@ -11142,7 +11142,7 @@
         <v>45056</v>
       </c>
       <c r="B335" t="n">
-        <v>1720.355346679688</v>
+        <v>1720.35546875</v>
       </c>
       <c r="C335" t="n">
         <v>890.6500244140625</v>
@@ -11160,7 +11160,7 @@
         <v>47.63999938964844</v>
       </c>
       <c r="H335" t="n">
-        <v>401.2503356933594</v>
+        <v>401.2503662109375</v>
       </c>
       <c r="I335" t="n">
         <v>834.9547729492188</v>
@@ -11174,7 +11174,7 @@
         <v>45057</v>
       </c>
       <c r="B336" t="n">
-        <v>1754.740112304688</v>
+        <v>1754.739868164062</v>
       </c>
       <c r="C336" t="n">
         <v>917.25</v>
@@ -11218,7 +11218,7 @@
         <v>895.5999755859375</v>
       </c>
       <c r="F337" t="n">
-        <v>686.1112670898438</v>
+        <v>686.1112060546875</v>
       </c>
       <c r="G337" t="n">
         <v>48.16999816894531</v>
@@ -11238,7 +11238,7 @@
         <v>45061</v>
       </c>
       <c r="B338" t="n">
-        <v>1768.248168945312</v>
+        <v>1768.248046875</v>
       </c>
       <c r="C338" t="n">
         <v>840.5999755859375</v>
@@ -11256,7 +11256,7 @@
         <v>47.16999816894531</v>
       </c>
       <c r="H338" t="n">
-        <v>399.5797119140625</v>
+        <v>399.5797424316406</v>
       </c>
       <c r="I338" t="n">
         <v>776.3851318359375</v>
@@ -11270,13 +11270,13 @@
         <v>45062</v>
       </c>
       <c r="B339" t="n">
-        <v>1752.136596679688</v>
+        <v>1752.136474609375</v>
       </c>
       <c r="C339" t="n">
         <v>812.0999755859375</v>
       </c>
       <c r="D339" t="n">
-        <v>1885.718872070312</v>
+        <v>1885.718994140625</v>
       </c>
       <c r="E339" t="n">
         <v>874.1500244140625</v>
@@ -11288,7 +11288,7 @@
         <v>47.2400016784668</v>
       </c>
       <c r="H339" t="n">
-        <v>393.9781494140625</v>
+        <v>393.9781188964844</v>
       </c>
       <c r="I339" t="n">
         <v>737.5882568359375</v>
@@ -11320,7 +11320,7 @@
         <v>46.86999893188477</v>
       </c>
       <c r="H340" t="n">
-        <v>399.2848815917969</v>
+        <v>399.284912109375</v>
       </c>
       <c r="I340" t="n">
         <v>700.7388305664062</v>
@@ -11334,13 +11334,13 @@
         <v>45064</v>
       </c>
       <c r="B341" t="n">
-        <v>1682.336059570312</v>
+        <v>1682.3359375</v>
       </c>
       <c r="C341" t="n">
         <v>751.5999755859375</v>
       </c>
       <c r="D341" t="n">
-        <v>1886.5673828125</v>
+        <v>1886.567504882812</v>
       </c>
       <c r="E341" t="n">
         <v>860.5499877929688</v>
@@ -11352,7 +11352,7 @@
         <v>45.0099983215332</v>
       </c>
       <c r="H341" t="n">
-        <v>392.1600952148438</v>
+        <v>392.1600646972656</v>
       </c>
       <c r="I341" t="n">
         <v>665.7369384765625</v>
@@ -11366,7 +11366,7 @@
         <v>45065</v>
       </c>
       <c r="B342" t="n">
-        <v>1698.644165039062</v>
+        <v>1698.643920898438</v>
       </c>
       <c r="C342" t="n">
         <v>787.3499755859375</v>
@@ -11378,7 +11378,7 @@
         <v>896.9500122070312</v>
       </c>
       <c r="F342" t="n">
-        <v>674.4473876953125</v>
+        <v>674.4473266601562</v>
       </c>
       <c r="G342" t="n">
         <v>47.22000122070312</v>
@@ -11398,7 +11398,7 @@
         <v>45068</v>
       </c>
       <c r="B343" t="n">
-        <v>1781.510620117188</v>
+        <v>1781.5107421875</v>
       </c>
       <c r="C343" t="n">
         <v>826.7000122070312</v>
@@ -11416,7 +11416,7 @@
         <v>49.58000183105469</v>
       </c>
       <c r="H343" t="n">
-        <v>416.5810546875</v>
+        <v>416.5809936523438</v>
       </c>
       <c r="I343" t="n">
         <v>721.5103149414062</v>
@@ -11430,25 +11430,25 @@
         <v>45069</v>
       </c>
       <c r="B344" t="n">
-        <v>1787.4541015625</v>
+        <v>1787.454345703125</v>
       </c>
       <c r="C344" t="n">
         <v>868</v>
       </c>
       <c r="D344" t="n">
-        <v>2628.916748046875</v>
+        <v>2628.91650390625</v>
       </c>
       <c r="E344" t="n">
         <v>988.7999877929688</v>
       </c>
       <c r="F344" t="n">
-        <v>719.4856567382812</v>
+        <v>719.485595703125</v>
       </c>
       <c r="G344" t="n">
         <v>52.04999923706055</v>
       </c>
       <c r="H344" t="n">
-        <v>419.9223327636719</v>
+        <v>419.9223022460938</v>
       </c>
       <c r="I344" t="n">
         <v>757.5608520507812</v>
@@ -11468,7 +11468,7 @@
         <v>911.4000244140625</v>
       </c>
       <c r="D345" t="n">
-        <v>2471.104248046875</v>
+        <v>2471.10400390625</v>
       </c>
       <c r="E345" t="n">
         <v>984.25</v>
@@ -11494,13 +11494,13 @@
         <v>45071</v>
       </c>
       <c r="B346" t="n">
-        <v>1746.880737304688</v>
+        <v>1746.880615234375</v>
       </c>
       <c r="C346" t="n">
         <v>891.75</v>
       </c>
       <c r="D346" t="n">
-        <v>2532.841796875</v>
+        <v>2532.841552734375</v>
       </c>
       <c r="E346" t="n">
         <v>970.6500244140625</v>
@@ -11512,7 +11512,7 @@
         <v>51.83000183105469</v>
       </c>
       <c r="H346" t="n">
-        <v>411.9621887207031</v>
+        <v>411.962158203125</v>
       </c>
       <c r="I346" t="n">
         <v>795.3092041015625</v>
@@ -11526,7 +11526,7 @@
         <v>45072</v>
       </c>
       <c r="B347" t="n">
-        <v>1753.610107421875</v>
+        <v>1753.610229492188</v>
       </c>
       <c r="C347" t="n">
         <v>850.0999755859375</v>
@@ -11538,7 +11538,7 @@
         <v>963.3499755859375</v>
       </c>
       <c r="F347" t="n">
-        <v>712.428466796875</v>
+        <v>712.4285278320312</v>
       </c>
       <c r="G347" t="n">
         <v>51.61000061035156</v>
@@ -11558,7 +11558,7 @@
         <v>45075</v>
       </c>
       <c r="B348" t="n">
-        <v>1762.844848632812</v>
+        <v>1762.844970703125</v>
       </c>
       <c r="C348" t="n">
         <v>832.2000122070312</v>
@@ -11570,7 +11570,7 @@
         <v>977.8499755859375</v>
       </c>
       <c r="F348" t="n">
-        <v>722.8673095703125</v>
+        <v>722.8672485351562</v>
       </c>
       <c r="G348" t="n">
         <v>51.27999877929688</v>
@@ -11602,7 +11602,7 @@
         <v>966.8499755859375</v>
       </c>
       <c r="F349" t="n">
-        <v>719.4856567382812</v>
+        <v>719.485595703125</v>
       </c>
       <c r="G349" t="n">
         <v>50.22000122070312</v>
@@ -11640,7 +11640,7 @@
         <v>49.93000030517578</v>
       </c>
       <c r="H350" t="n">
-        <v>416.2861938476562</v>
+        <v>416.2862243652344</v>
       </c>
       <c r="I350" t="n">
         <v>663.2402954101562</v>
@@ -11698,7 +11698,7 @@
         <v>983.5499877929688</v>
       </c>
       <c r="F352" t="n">
-        <v>721.9850463867188</v>
+        <v>721.985107421875</v>
       </c>
       <c r="G352" t="n">
         <v>51.13000106811523</v>
@@ -11718,7 +11718,7 @@
         <v>45082</v>
       </c>
       <c r="B353" t="n">
-        <v>1778.612670898438</v>
+        <v>1778.612548828125</v>
       </c>
       <c r="C353" t="n">
         <v>828</v>
@@ -11736,7 +11736,7 @@
         <v>51.88999938964844</v>
       </c>
       <c r="H353" t="n">
-        <v>431.469482421875</v>
+        <v>431.4694519042969</v>
       </c>
       <c r="I353" t="n">
         <v>680.5665283203125</v>
@@ -11768,7 +11768,7 @@
         <v>52.59999847412109</v>
       </c>
       <c r="H354" t="n">
-        <v>451.222412109375</v>
+        <v>451.2223510742188</v>
       </c>
       <c r="I354" t="n">
         <v>677.4707641601562</v>
@@ -11794,13 +11794,13 @@
         <v>985.5499877929688</v>
       </c>
       <c r="F355" t="n">
-        <v>728.9932250976562</v>
+        <v>728.9932861328125</v>
       </c>
       <c r="G355" t="n">
         <v>54.97000122070312</v>
       </c>
       <c r="H355" t="n">
-        <v>447.881103515625</v>
+        <v>447.8811340332031</v>
       </c>
       <c r="I355" t="n">
         <v>679.1184692382812</v>
@@ -11814,19 +11814,19 @@
         <v>45085</v>
       </c>
       <c r="B356" t="n">
-        <v>1801.306518554688</v>
+        <v>1801.306396484375</v>
       </c>
       <c r="C356" t="n">
         <v>829.25</v>
       </c>
       <c r="D356" t="n">
-        <v>2424.73828125</v>
+        <v>2424.738037109375</v>
       </c>
       <c r="E356" t="n">
         <v>976</v>
       </c>
       <c r="F356" t="n">
-        <v>721.7891235351562</v>
+        <v>721.7890625</v>
       </c>
       <c r="G356" t="n">
         <v>55.83000183105469</v>
@@ -11846,7 +11846,7 @@
         <v>45086</v>
       </c>
       <c r="B357" t="n">
-        <v>1804.990356445312</v>
+        <v>1804.990600585938</v>
       </c>
       <c r="C357" t="n">
         <v>830.7000122070312</v>
@@ -11864,7 +11864,7 @@
         <v>55.2400016784668</v>
       </c>
       <c r="H357" t="n">
-        <v>447.8320007324219</v>
+        <v>447.83203125</v>
       </c>
       <c r="I357" t="n">
         <v>668.1834716796875</v>
@@ -11878,7 +11878,7 @@
         <v>45089</v>
       </c>
       <c r="B358" t="n">
-        <v>1806.218505859375</v>
+        <v>1806.218627929688</v>
       </c>
       <c r="C358" t="n">
         <v>830.4000244140625</v>
@@ -11928,7 +11928,7 @@
         <v>53.56000137329102</v>
       </c>
       <c r="H359" t="n">
-        <v>451.02587890625</v>
+        <v>451.0258483886719</v>
       </c>
       <c r="I359" t="n">
         <v>662.24169921875</v>
@@ -11942,7 +11942,7 @@
         <v>45091</v>
       </c>
       <c r="B360" t="n">
-        <v>1822.231811523438</v>
+        <v>1822.23193359375</v>
       </c>
       <c r="C360" t="n">
         <v>808.5499877929688</v>
@@ -11960,7 +11960,7 @@
         <v>53.04999923706055</v>
       </c>
       <c r="H360" t="n">
-        <v>456.5783081054688</v>
+        <v>456.5783386230469</v>
       </c>
       <c r="I360" t="n">
         <v>653.4536743164062</v>
@@ -11986,13 +11986,13 @@
         <v>962.5999755859375</v>
       </c>
       <c r="F361" t="n">
-        <v>724.8275756835938</v>
+        <v>724.8275146484375</v>
       </c>
       <c r="G361" t="n">
         <v>53.84999847412109</v>
       </c>
       <c r="H361" t="n">
-        <v>450.4361877441406</v>
+        <v>450.4362487792969</v>
       </c>
       <c r="I361" t="n">
         <v>668.1834716796875</v>
@@ -12012,7 +12012,7 @@
         <v>810.9000244140625</v>
       </c>
       <c r="D362" t="n">
-        <v>2505.042236328125</v>
+        <v>2505.0419921875</v>
       </c>
       <c r="E362" t="n">
         <v>975.0499877929688</v>
@@ -12024,7 +12024,7 @@
         <v>53.22000122070312</v>
       </c>
       <c r="H362" t="n">
-        <v>452.9421691894531</v>
+        <v>452.9421997070312</v>
       </c>
       <c r="I362" t="n">
         <v>670.3306274414062</v>
@@ -12044,7 +12044,7 @@
         <v>806.5999755859375</v>
       </c>
       <c r="D363" t="n">
-        <v>2397.03857421875</v>
+        <v>2397.038818359375</v>
       </c>
       <c r="E363" t="n">
         <v>960.3499755859375</v>
@@ -12088,7 +12088,7 @@
         <v>52.34000015258789</v>
       </c>
       <c r="H364" t="n">
-        <v>441.1985168457031</v>
+        <v>441.1985473632812</v>
       </c>
       <c r="I364" t="n">
         <v>657.6978759765625</v>
@@ -12102,7 +12102,7 @@
         <v>45098</v>
       </c>
       <c r="B365" t="n">
-        <v>1813.39013671875</v>
+        <v>1813.390258789062</v>
       </c>
       <c r="C365" t="n">
         <v>806.7000122070312</v>
@@ -12114,13 +12114,13 @@
         <v>977</v>
       </c>
       <c r="F365" t="n">
-        <v>734.5802001953125</v>
+        <v>734.5801391601562</v>
       </c>
       <c r="G365" t="n">
         <v>52.13000106811523</v>
       </c>
       <c r="H365" t="n">
-        <v>440.3631591796875</v>
+        <v>440.3631896972656</v>
       </c>
       <c r="I365" t="n">
         <v>654.9017333984375</v>
@@ -12134,7 +12134,7 @@
         <v>45099</v>
       </c>
       <c r="B366" t="n">
-        <v>1799.538208007812</v>
+        <v>1799.537963867188</v>
       </c>
       <c r="C366" t="n">
         <v>804.4000244140625</v>
@@ -12178,7 +12178,7 @@
         <v>959.8499755859375</v>
       </c>
       <c r="F367" t="n">
-        <v>700.1276245117188</v>
+        <v>700.1275634765625</v>
       </c>
       <c r="G367" t="n">
         <v>48.47999954223633</v>
@@ -12204,13 +12204,13 @@
         <v>770.75</v>
       </c>
       <c r="D368" t="n">
-        <v>2291.4306640625</v>
+        <v>2291.430908203125</v>
       </c>
       <c r="E368" t="n">
         <v>968.4500122070312</v>
       </c>
       <c r="F368" t="n">
-        <v>710.0271606445312</v>
+        <v>710.0272216796875</v>
       </c>
       <c r="G368" t="n">
         <v>50.11999893188477</v>
@@ -12236,19 +12236,19 @@
         <v>773.2000122070312</v>
       </c>
       <c r="D369" t="n">
-        <v>2280.301025390625</v>
+        <v>2280.30126953125</v>
       </c>
       <c r="E369" t="n">
         <v>959.5499877929688</v>
       </c>
       <c r="F369" t="n">
-        <v>705.95947265625</v>
+        <v>705.9595336914062</v>
       </c>
       <c r="G369" t="n">
         <v>50.61999893188477</v>
       </c>
       <c r="H369" t="n">
-        <v>426.3592834472656</v>
+        <v>426.3592529296875</v>
       </c>
       <c r="I369" t="n">
         <v>640.621337890625</v>
@@ -12262,13 +12262,13 @@
         <v>45105</v>
       </c>
       <c r="B370" t="n">
-        <v>1780.479125976562</v>
+        <v>1780.479248046875</v>
       </c>
       <c r="C370" t="n">
         <v>819.1500244140625</v>
       </c>
       <c r="D370" t="n">
-        <v>2397.63720703125</v>
+        <v>2397.637451171875</v>
       </c>
       <c r="E370" t="n">
         <v>956.6500244140625</v>
@@ -12280,7 +12280,7 @@
         <v>50.93000030517578</v>
       </c>
       <c r="H370" t="n">
-        <v>426.7523498535156</v>
+        <v>426.7523193359375</v>
       </c>
       <c r="I370" t="n">
         <v>653.6034545898438</v>
@@ -12294,7 +12294,7 @@
         <v>45107</v>
       </c>
       <c r="B371" t="n">
-        <v>1781.805297851562</v>
+        <v>1781.805419921875</v>
       </c>
       <c r="C371" t="n">
         <v>767.25</v>
@@ -12306,7 +12306,7 @@
         <v>945.9000244140625</v>
       </c>
       <c r="F371" t="n">
-        <v>724.5825805664062</v>
+        <v>724.58251953125</v>
       </c>
       <c r="G371" t="n">
         <v>49.97000122070312</v>
@@ -12326,7 +12326,7 @@
         <v>45110</v>
       </c>
       <c r="B372" t="n">
-        <v>1793.005004882812</v>
+        <v>1793.0048828125</v>
       </c>
       <c r="C372" t="n">
         <v>773.25</v>
@@ -12376,7 +12376,7 @@
         <v>49.41999816894531</v>
       </c>
       <c r="H373" t="n">
-        <v>425.2290954589844</v>
+        <v>425.2291259765625</v>
       </c>
       <c r="I373" t="n">
         <v>649.2594604492188</v>
@@ -12390,7 +12390,7 @@
         <v>45112</v>
       </c>
       <c r="B374" t="n">
-        <v>1788.780639648438</v>
+        <v>1788.780517578125</v>
       </c>
       <c r="C374" t="n">
         <v>770</v>
@@ -12408,7 +12408,7 @@
         <v>49.13000106811523</v>
       </c>
       <c r="H374" t="n">
-        <v>424.9342651367188</v>
+        <v>424.9342346191406</v>
       </c>
       <c r="I374" t="n">
         <v>649.0098266601562</v>
@@ -12422,13 +12422,13 @@
         <v>45113</v>
       </c>
       <c r="B375" t="n">
-        <v>1788.338500976562</v>
+        <v>1788.338623046875</v>
       </c>
       <c r="C375" t="n">
         <v>769.3499755859375</v>
       </c>
       <c r="D375" t="n">
-        <v>2398.5361328125</v>
+        <v>2398.535888671875</v>
       </c>
       <c r="E375" t="n">
         <v>962.2000122070312</v>
@@ -12454,13 +12454,13 @@
         <v>45114</v>
       </c>
       <c r="B376" t="n">
-        <v>1768.98486328125</v>
+        <v>1768.984741210938</v>
       </c>
       <c r="C376" t="n">
         <v>759.8499755859375</v>
       </c>
       <c r="D376" t="n">
-        <v>2376.428955078125</v>
+        <v>2376.42919921875</v>
       </c>
       <c r="E376" t="n">
         <v>951</v>
@@ -12492,7 +12492,7 @@
         <v>749.8499755859375</v>
       </c>
       <c r="D377" t="n">
-        <v>2407.037841796875</v>
+        <v>2407.0380859375</v>
       </c>
       <c r="E377" t="n">
         <v>959.4500122070312</v>
@@ -12530,7 +12530,7 @@
         <v>965.1500244140625</v>
       </c>
       <c r="F378" t="n">
-        <v>715.4180908203125</v>
+        <v>715.4180297851562</v>
       </c>
       <c r="G378" t="n">
         <v>48.84000015258789</v>
@@ -12550,7 +12550,7 @@
         <v>45119</v>
       </c>
       <c r="B379" t="n">
-        <v>1767.157958984375</v>
+        <v>1767.158081054688</v>
       </c>
       <c r="C379" t="n">
         <v>752.6500244140625</v>
@@ -12582,19 +12582,19 @@
         <v>45120</v>
       </c>
       <c r="B380" t="n">
-        <v>1748.248657226562</v>
+        <v>1748.248779296875</v>
       </c>
       <c r="C380" t="n">
         <v>745.2000122070312</v>
       </c>
       <c r="D380" t="n">
-        <v>2358.902099609375</v>
+        <v>2358.90234375</v>
       </c>
       <c r="E380" t="n">
         <v>947.0499877929688</v>
       </c>
       <c r="F380" t="n">
-        <v>702.9700927734375</v>
+        <v>702.9700317382812</v>
       </c>
       <c r="G380" t="n">
         <v>47.43999862670898</v>
@@ -12620,13 +12620,13 @@
         <v>742.2999877929688</v>
       </c>
       <c r="D381" t="n">
-        <v>2372.933837890625</v>
+        <v>2372.93359375</v>
       </c>
       <c r="E381" t="n">
         <v>965.2000122070312</v>
       </c>
       <c r="F381" t="n">
-        <v>711.6934814453125</v>
+        <v>711.6934204101562</v>
       </c>
       <c r="G381" t="n">
         <v>48.38000106811523</v>
@@ -12658,7 +12658,7 @@
         <v>965.2999877929688</v>
       </c>
       <c r="F382" t="n">
-        <v>716.545166015625</v>
+        <v>716.5452270507812</v>
       </c>
       <c r="G382" t="n">
         <v>49.13999938964844</v>
@@ -12678,7 +12678,7 @@
         <v>45125</v>
       </c>
       <c r="B383" t="n">
-        <v>1772.53955078125</v>
+        <v>1772.539672851562</v>
       </c>
       <c r="C383" t="n">
         <v>783</v>
@@ -12710,7 +12710,7 @@
         <v>45126</v>
       </c>
       <c r="B384" t="n">
-        <v>1777.427490234375</v>
+        <v>1777.427368164062</v>
       </c>
       <c r="C384" t="n">
         <v>779.0999755859375</v>
@@ -12722,7 +12722,7 @@
         <v>979.6500244140625</v>
       </c>
       <c r="F384" t="n">
-        <v>716.8883056640625</v>
+        <v>716.8883666992188</v>
       </c>
       <c r="G384" t="n">
         <v>49.13999938964844</v>
@@ -12748,7 +12748,7 @@
         <v>780.2999877929688</v>
       </c>
       <c r="D385" t="n">
-        <v>2416.525390625</v>
+        <v>2416.525146484375</v>
       </c>
       <c r="E385" t="n">
         <v>985</v>
@@ -12806,13 +12806,13 @@
         <v>45131</v>
       </c>
       <c r="B387" t="n">
-        <v>1781.920288085938</v>
+        <v>1781.920166015625</v>
       </c>
       <c r="C387" t="n">
         <v>773.25</v>
       </c>
       <c r="D387" t="n">
-        <v>2414.9775390625</v>
+        <v>2414.977294921875</v>
       </c>
       <c r="E387" t="n">
         <v>989.1500244140625</v>
@@ -12838,7 +12838,7 @@
         <v>45132</v>
       </c>
       <c r="B388" t="n">
-        <v>1867.974853515625</v>
+        <v>1867.974975585938</v>
       </c>
       <c r="C388" t="n">
         <v>834.8499755859375</v>
@@ -12870,13 +12870,13 @@
         <v>45133</v>
       </c>
       <c r="B389" t="n">
-        <v>1898.338500976562</v>
+        <v>1898.33837890625</v>
       </c>
       <c r="C389" t="n">
         <v>814.9500122070312</v>
       </c>
       <c r="D389" t="n">
-        <v>2467.457275390625</v>
+        <v>2467.45751953125</v>
       </c>
       <c r="E389" t="n">
         <v>1140.400024414062</v>
@@ -12934,7 +12934,7 @@
         <v>45135</v>
       </c>
       <c r="B391" t="n">
-        <v>1924.40673828125</v>
+        <v>1924.406616210938</v>
       </c>
       <c r="C391" t="n">
         <v>814.7999877929688</v>
@@ -12966,7 +12966,7 @@
         <v>45138</v>
       </c>
       <c r="B392" t="n">
-        <v>1992.539428710938</v>
+        <v>1992.53955078125</v>
       </c>
       <c r="C392" t="n">
         <v>820.7000122070312</v>
@@ -12978,7 +12978,7 @@
         <v>1093.300048828125</v>
       </c>
       <c r="F392" t="n">
-        <v>767.5421752929688</v>
+        <v>767.5421142578125</v>
       </c>
       <c r="G392" t="n">
         <v>54.65999984741211</v>
@@ -13062,7 +13062,7 @@
         <v>45141</v>
       </c>
       <c r="B395" t="n">
-        <v>2002.660766601562</v>
+        <v>2002.66064453125</v>
       </c>
       <c r="C395" t="n">
         <v>796.7000122070312</v>
@@ -13126,7 +13126,7 @@
         <v>45145</v>
       </c>
       <c r="B397" t="n">
-        <v>2005.524291992188</v>
+        <v>2005.524169921875</v>
       </c>
       <c r="C397" t="n">
         <v>832.7000122070312</v>
@@ -13158,13 +13158,13 @@
         <v>45146</v>
       </c>
       <c r="B398" t="n">
-        <v>1975.802490234375</v>
+        <v>1975.802368164062</v>
       </c>
       <c r="C398" t="n">
         <v>823.5999755859375</v>
       </c>
       <c r="D398" t="n">
-        <v>2471.252197265625</v>
+        <v>2471.25244140625</v>
       </c>
       <c r="E398" t="n">
         <v>984.2999877929688</v>
@@ -13190,13 +13190,13 @@
         <v>45147</v>
       </c>
       <c r="B399" t="n">
-        <v>1962.175903320312</v>
+        <v>1962.176025390625</v>
       </c>
       <c r="C399" t="n">
         <v>811.9500122070312</v>
       </c>
       <c r="D399" t="n">
-        <v>2503.759033203125</v>
+        <v>2503.75927734375</v>
       </c>
       <c r="E399" t="n">
         <v>971.2999877929688</v>
@@ -13222,7 +13222,7 @@
         <v>45148</v>
       </c>
       <c r="B400" t="n">
-        <v>1936.30517578125</v>
+        <v>1936.305053710938</v>
       </c>
       <c r="C400" t="n">
         <v>820.7999877929688</v>
@@ -13254,13 +13254,13 @@
         <v>45149</v>
       </c>
       <c r="B401" t="n">
-        <v>1929.097045898438</v>
+        <v>1929.096923828125</v>
       </c>
       <c r="C401" t="n">
         <v>831.7000122070312</v>
       </c>
       <c r="D401" t="n">
-        <v>2536.115966796875</v>
+        <v>2536.11572265625</v>
       </c>
       <c r="E401" t="n">
         <v>971.3499755859375</v>
@@ -13286,7 +13286,7 @@
         <v>45152</v>
       </c>
       <c r="B402" t="n">
-        <v>1886.341186523438</v>
+        <v>1886.341064453125</v>
       </c>
       <c r="C402" t="n">
         <v>808.2999877929688</v>
@@ -13318,13 +13318,13 @@
         <v>45154</v>
       </c>
       <c r="B403" t="n">
-        <v>1868.369873046875</v>
+        <v>1868.369995117188</v>
       </c>
       <c r="C403" t="n">
         <v>818.0999755859375</v>
       </c>
       <c r="D403" t="n">
-        <v>2441.841552734375</v>
+        <v>2441.841796875</v>
       </c>
       <c r="E403" t="n">
         <v>948.5</v>
@@ -13382,7 +13382,7 @@
         <v>45156</v>
       </c>
       <c r="B405" t="n">
-        <v>1909.792724609375</v>
+        <v>1909.792602539062</v>
       </c>
       <c r="C405" t="n">
         <v>871.9000244140625</v>
@@ -13394,7 +13394,7 @@
         <v>994.75</v>
       </c>
       <c r="F405" t="n">
-        <v>824.8228759765625</v>
+        <v>824.8229370117188</v>
       </c>
       <c r="G405" t="n">
         <v>60.91999816894531</v>
@@ -13414,7 +13414,7 @@
         <v>45159</v>
       </c>
       <c r="B406" t="n">
-        <v>1947.1669921875</v>
+        <v>1947.166870117188</v>
       </c>
       <c r="C406" t="n">
         <v>923.5499877929688</v>
@@ -13426,7 +13426,7 @@
         <v>1020.049987792969</v>
       </c>
       <c r="F406" t="n">
-        <v>846.778076171875</v>
+        <v>846.7780151367188</v>
       </c>
       <c r="G406" t="n">
         <v>64.97000122070312</v>
@@ -13478,7 +13478,7 @@
         <v>45161</v>
       </c>
       <c r="B408" t="n">
-        <v>1940.55126953125</v>
+        <v>1940.551147460938</v>
       </c>
       <c r="C408" t="n">
         <v>890.4000244140625</v>
@@ -13516,7 +13516,7 @@
         <v>895.1500244140625</v>
       </c>
       <c r="D409" t="n">
-        <v>2536.16552734375</v>
+        <v>2536.165771484375</v>
       </c>
       <c r="E409" t="n">
         <v>983.6500244140625</v>
@@ -13574,7 +13574,7 @@
         <v>45166</v>
       </c>
       <c r="B411" t="n">
-        <v>1960.299926757812</v>
+        <v>1960.2998046875</v>
       </c>
       <c r="C411" t="n">
         <v>864.9500122070312</v>
@@ -13612,13 +13612,13 @@
         <v>857.1500244140625</v>
       </c>
       <c r="D412" t="n">
-        <v>2503.109619140625</v>
+        <v>2503.10986328125</v>
       </c>
       <c r="E412" t="n">
         <v>974.5</v>
       </c>
       <c r="F412" t="n">
-        <v>812.6365966796875</v>
+        <v>812.6365356445312</v>
       </c>
       <c r="G412" t="n">
         <v>66.54000091552734</v>
@@ -13650,7 +13650,7 @@
         <v>970.5</v>
       </c>
       <c r="F413" t="n">
-        <v>807.8507690429688</v>
+        <v>807.850830078125</v>
       </c>
       <c r="G413" t="n">
         <v>65.68000030517578</v>
@@ -13676,7 +13676,7 @@
         <v>811.9500122070312</v>
       </c>
       <c r="D414" t="n">
-        <v>2416.026123046875</v>
+        <v>2416.02587890625</v>
       </c>
       <c r="E414" t="n">
         <v>928.6500244140625</v>
@@ -13702,7 +13702,7 @@
         <v>45170</v>
       </c>
       <c r="B415" t="n">
-        <v>1985.97314453125</v>
+        <v>1985.973022460938</v>
       </c>
       <c r="C415" t="n">
         <v>824.9000244140625</v>
@@ -13714,7 +13714,7 @@
         <v>949.0999755859375</v>
       </c>
       <c r="F415" t="n">
-        <v>788.9052734375</v>
+        <v>788.9053344726562</v>
       </c>
       <c r="G415" t="n">
         <v>66.05000305175781</v>
@@ -13740,7 +13740,7 @@
         <v>817.5999755859375</v>
       </c>
       <c r="D416" t="n">
-        <v>2467.307861328125</v>
+        <v>2467.3076171875</v>
       </c>
       <c r="E416" t="n">
         <v>959.2000122070312</v>
@@ -13778,7 +13778,7 @@
         <v>962.0999755859375</v>
       </c>
       <c r="F417" t="n">
-        <v>794.2830200195312</v>
+        <v>794.2830810546875</v>
       </c>
       <c r="G417" t="n">
         <v>68.48999786376953</v>
@@ -13804,7 +13804,7 @@
         <v>855.9500122070312</v>
       </c>
       <c r="D418" t="n">
-        <v>2493.1728515625</v>
+        <v>2493.173095703125</v>
       </c>
       <c r="E418" t="n">
         <v>1006.099975585938</v>
@@ -13862,13 +13862,13 @@
         <v>45177</v>
       </c>
       <c r="B420" t="n">
-        <v>1998.809692382812</v>
+        <v>1998.8095703125</v>
       </c>
       <c r="C420" t="n">
         <v>833</v>
       </c>
       <c r="D420" t="n">
-        <v>2515.94287109375</v>
+        <v>2515.942626953125</v>
       </c>
       <c r="E420" t="n">
         <v>1001.200012207031</v>
@@ -13894,13 +13894,13 @@
         <v>45180</v>
       </c>
       <c r="B421" t="n">
-        <v>2025.27294921875</v>
+        <v>2025.272827148438</v>
       </c>
       <c r="C421" t="n">
         <v>874.9000244140625</v>
       </c>
       <c r="D421" t="n">
-        <v>2611.46533203125</v>
+        <v>2611.465087890625</v>
       </c>
       <c r="E421" t="n">
         <v>1014.650024414062</v>
@@ -13926,13 +13926,13 @@
         <v>45181</v>
       </c>
       <c r="B422" t="n">
-        <v>1985.676879882812</v>
+        <v>1985.6767578125</v>
       </c>
       <c r="C422" t="n">
         <v>852.2999877929688</v>
       </c>
       <c r="D422" t="n">
-        <v>2532.321044921875</v>
+        <v>2532.32080078125</v>
       </c>
       <c r="E422" t="n">
         <v>1004.799987792969</v>
@@ -13964,7 +13964,7 @@
         <v>836.9000244140625</v>
       </c>
       <c r="D423" t="n">
-        <v>2515.54296875</v>
+        <v>2515.543212890625</v>
       </c>
       <c r="E423" t="n">
         <v>985.7999877929688</v>
@@ -13996,13 +13996,13 @@
         <v>851.75</v>
       </c>
       <c r="D424" t="n">
-        <v>2516.442138671875</v>
+        <v>2516.44189453125</v>
       </c>
       <c r="E424" t="n">
         <v>983.7999877929688</v>
       </c>
       <c r="F424" t="n">
-        <v>838.5386352539062</v>
+        <v>838.5386962890625</v>
       </c>
       <c r="G424" t="n">
         <v>75.43000030517578</v>
@@ -14028,7 +14028,7 @@
         <v>846.0999755859375</v>
       </c>
       <c r="D425" t="n">
-        <v>2536.665283203125</v>
+        <v>2536.6650390625</v>
       </c>
       <c r="E425" t="n">
         <v>1006.450012207031</v>
@@ -14054,7 +14054,7 @@
         <v>45187</v>
       </c>
       <c r="B426" t="n">
-        <v>1981.480224609375</v>
+        <v>1981.480102539062</v>
       </c>
       <c r="C426" t="n">
         <v>855.0999755859375</v>
@@ -14086,7 +14086,7 @@
         <v>45189</v>
       </c>
       <c r="B427" t="n">
-        <v>1954.91845703125</v>
+        <v>1954.918334960938</v>
       </c>
       <c r="C427" t="n">
         <v>855.2000122070312</v>
@@ -14098,7 +14098,7 @@
         <v>1008.950012207031</v>
       </c>
       <c r="F427" t="n">
-        <v>807.20947265625</v>
+        <v>807.2094116210938</v>
       </c>
       <c r="G427" t="n">
         <v>73.68000030517578</v>
@@ -14118,7 +14118,7 @@
         <v>45190</v>
       </c>
       <c r="B428" t="n">
-        <v>1968.742309570312</v>
+        <v>1968.742431640625</v>
       </c>
       <c r="C428" t="n">
         <v>847.3499755859375</v>
@@ -14162,7 +14162,7 @@
         <v>1018.799987792969</v>
       </c>
       <c r="F429" t="n">
-        <v>816.0901489257812</v>
+        <v>816.0902099609375</v>
       </c>
       <c r="G429" t="n">
         <v>76.77999877929688</v>
@@ -14246,19 +14246,19 @@
         <v>45196</v>
       </c>
       <c r="B432" t="n">
-        <v>1994.3662109375</v>
+        <v>1994.366088867188</v>
       </c>
       <c r="C432" t="n">
         <v>816.2000122070312</v>
       </c>
       <c r="D432" t="n">
-        <v>2479.990478515625</v>
+        <v>2479.99072265625</v>
       </c>
       <c r="E432" t="n">
         <v>1018.75</v>
       </c>
       <c r="F432" t="n">
-        <v>819.69189453125</v>
+        <v>819.6918334960938</v>
       </c>
       <c r="G432" t="n">
         <v>75.06999969482422</v>
@@ -14284,13 +14284,13 @@
         <v>830.5</v>
       </c>
       <c r="D433" t="n">
-        <v>2471.951171875</v>
+        <v>2471.951416015625</v>
       </c>
       <c r="E433" t="n">
         <v>1012.450012207031</v>
       </c>
       <c r="F433" t="n">
-        <v>812.1924438476562</v>
+        <v>812.1925048828125</v>
       </c>
       <c r="G433" t="n">
         <v>75.08000183105469</v>
@@ -14316,7 +14316,7 @@
         <v>810.25</v>
       </c>
       <c r="D434" t="n">
-        <v>2410.682861328125</v>
+        <v>2410.68310546875</v>
       </c>
       <c r="E434" t="n">
         <v>987.1500244140625</v>
@@ -14386,7 +14386,7 @@
         <v>971.9000244140625</v>
       </c>
       <c r="F436" t="n">
-        <v>813.6725463867188</v>
+        <v>813.672607421875</v>
       </c>
       <c r="G436" t="n">
         <v>74.41000366210938</v>
@@ -14438,7 +14438,7 @@
         <v>45205</v>
       </c>
       <c r="B438" t="n">
-        <v>1984.689331054688</v>
+        <v>1984.689208984375</v>
       </c>
       <c r="C438" t="n">
         <v>806</v>
@@ -14476,7 +14476,7 @@
         <v>778.9000244140625</v>
       </c>
       <c r="D439" t="n">
-        <v>2439.344970703125</v>
+        <v>2439.34521484375</v>
       </c>
       <c r="E439" t="n">
         <v>938.9500122070312</v>
@@ -14508,13 +14508,13 @@
         <v>786</v>
       </c>
       <c r="D440" t="n">
-        <v>2494.970703125</v>
+        <v>2494.970947265625</v>
       </c>
       <c r="E440" t="n">
         <v>939.75</v>
       </c>
       <c r="F440" t="n">
-        <v>808.6402587890625</v>
+        <v>808.6401977539062</v>
       </c>
       <c r="G440" t="n">
         <v>69.93000030517578</v>
@@ -14540,13 +14540,13 @@
         <v>798.2000122070312</v>
       </c>
       <c r="D441" t="n">
-        <v>2485.28369140625</v>
+        <v>2485.283447265625</v>
       </c>
       <c r="E441" t="n">
         <v>962.4500122070312</v>
       </c>
       <c r="F441" t="n">
-        <v>804.0518798828125</v>
+        <v>804.0518188476562</v>
       </c>
       <c r="G441" t="n">
         <v>69.95999908447266</v>
@@ -14566,7 +14566,7 @@
         <v>45211</v>
       </c>
       <c r="B442" t="n">
-        <v>2004.043090820312</v>
+        <v>2004.04296875</v>
       </c>
       <c r="C442" t="n">
         <v>793.7000122070312</v>
@@ -14598,13 +14598,13 @@
         <v>45212</v>
       </c>
       <c r="B443" t="n">
-        <v>1985.182983398438</v>
+        <v>1985.18310546875</v>
       </c>
       <c r="C443" t="n">
         <v>785.2000122070312</v>
       </c>
       <c r="D443" t="n">
-        <v>2451.27880859375</v>
+        <v>2451.279052734375</v>
       </c>
       <c r="E443" t="n">
         <v>948.9000244140625</v>
@@ -14642,7 +14642,7 @@
         <v>938.7999877929688</v>
       </c>
       <c r="F444" t="n">
-        <v>794.9737548828125</v>
+        <v>794.9738159179688</v>
       </c>
       <c r="G444" t="n">
         <v>65.93000030517578</v>
@@ -14662,7 +14662,7 @@
         <v>45216</v>
       </c>
       <c r="B445" t="n">
-        <v>2013.966796875</v>
+        <v>2013.966674804688</v>
       </c>
       <c r="C445" t="n">
         <v>774.9000244140625</v>
@@ -14694,19 +14694,19 @@
         <v>45217</v>
       </c>
       <c r="B446" t="n">
-        <v>1988.737915039062</v>
+        <v>1988.73779296875</v>
       </c>
       <c r="C446" t="n">
         <v>764.9000244140625</v>
       </c>
       <c r="D446" t="n">
-        <v>2403.14306640625</v>
+        <v>2403.143310546875</v>
       </c>
       <c r="E446" t="n">
         <v>939.0499877929688</v>
       </c>
       <c r="F446" t="n">
-        <v>788.0172119140625</v>
+        <v>788.0171508789062</v>
       </c>
       <c r="G446" t="n">
         <v>66.79000091552734</v>
@@ -14758,7 +14758,7 @@
         <v>45219</v>
       </c>
       <c r="B448" t="n">
-        <v>1938.477661132812</v>
+        <v>1938.4775390625</v>
       </c>
       <c r="C448" t="n">
         <v>764.3499755859375</v>
@@ -14802,7 +14802,7 @@
         <v>880.7999877929688</v>
       </c>
       <c r="F449" t="n">
-        <v>761.22705078125</v>
+        <v>761.2269897460938</v>
       </c>
       <c r="G449" t="n">
         <v>63.29000091552734</v>
@@ -14828,7 +14828,7 @@
         <v>718.9000244140625</v>
       </c>
       <c r="D450" t="n">
-        <v>2253.991943359375</v>
+        <v>2253.9921875</v>
       </c>
       <c r="E450" t="n">
         <v>876.1500244140625</v>
@@ -14892,7 +14892,7 @@
         <v>764.5</v>
       </c>
       <c r="D452" t="n">
-        <v>2258.68603515625</v>
+        <v>2258.685791015625</v>
       </c>
       <c r="E452" t="n">
         <v>870.9000244140625</v>
@@ -14918,7 +14918,7 @@
         <v>45229</v>
       </c>
       <c r="B453" t="n">
-        <v>1863.284545898438</v>
+        <v>1863.28466796875</v>
       </c>
       <c r="C453" t="n">
         <v>759.25</v>
@@ -14956,13 +14956,13 @@
         <v>769.7999877929688</v>
       </c>
       <c r="D454" t="n">
-        <v>2291.592041015625</v>
+        <v>2291.591796875</v>
       </c>
       <c r="E454" t="n">
         <v>911.6500244140625</v>
       </c>
       <c r="F454" t="n">
-        <v>774.3507080078125</v>
+        <v>774.3507690429688</v>
       </c>
       <c r="G454" t="n">
         <v>72.61000061035156</v>
@@ -15014,19 +15014,19 @@
         <v>45232</v>
       </c>
       <c r="B456" t="n">
-        <v>1840.721801757812</v>
+        <v>1840.7216796875</v>
       </c>
       <c r="C456" t="n">
         <v>752.25</v>
       </c>
       <c r="D456" t="n">
-        <v>2212.347900390625</v>
+        <v>2212.34765625</v>
       </c>
       <c r="E456" t="n">
         <v>892.0999755859375</v>
       </c>
       <c r="F456" t="n">
-        <v>764.0391845703125</v>
+        <v>764.0392456054688</v>
       </c>
       <c r="G456" t="n">
         <v>74.58999633789062</v>
@@ -15046,7 +15046,7 @@
         <v>45233</v>
       </c>
       <c r="B457" t="n">
-        <v>1836.475830078125</v>
+        <v>1836.475708007812</v>
       </c>
       <c r="C457" t="n">
         <v>765.5</v>
@@ -15078,19 +15078,19 @@
         <v>45236</v>
       </c>
       <c r="B458" t="n">
-        <v>1840.869995117188</v>
+        <v>1840.869873046875</v>
       </c>
       <c r="C458" t="n">
         <v>771.8499755859375</v>
       </c>
       <c r="D458" t="n">
-        <v>2243.007080078125</v>
+        <v>2243.0068359375</v>
       </c>
       <c r="E458" t="n">
         <v>926.5</v>
       </c>
       <c r="F458" t="n">
-        <v>791.8655395507812</v>
+        <v>791.865478515625</v>
       </c>
       <c r="G458" t="n">
         <v>78.80000305175781</v>
@@ -15110,7 +15110,7 @@
         <v>45237</v>
       </c>
       <c r="B459" t="n">
-        <v>1837.21630859375</v>
+        <v>1837.216430664062</v>
       </c>
       <c r="C459" t="n">
         <v>762.0499877929688</v>
@@ -15154,7 +15154,7 @@
         <v>946.6500244140625</v>
       </c>
       <c r="F460" t="n">
-        <v>807.8507690429688</v>
+        <v>807.850830078125</v>
       </c>
       <c r="G460" t="n">
         <v>78.68000030517578</v>
@@ -15212,7 +15212,7 @@
         <v>760.4500122070312</v>
       </c>
       <c r="D462" t="n">
-        <v>2202.161376953125</v>
+        <v>2202.16162109375</v>
       </c>
       <c r="E462" t="n">
         <v>938.7000122070312</v>
@@ -15244,13 +15244,13 @@
         <v>759</v>
       </c>
       <c r="D463" t="n">
-        <v>2210.699951171875</v>
+        <v>2210.69970703125</v>
       </c>
       <c r="E463" t="n">
         <v>940.1500244140625</v>
       </c>
       <c r="F463" t="n">
-        <v>799.1180419921875</v>
+        <v>799.1181030273438</v>
       </c>
       <c r="G463" t="n">
         <v>78.12000274658203</v>
@@ -15270,7 +15270,7 @@
         <v>45245</v>
       </c>
       <c r="B464" t="n">
-        <v>1813.271118164062</v>
+        <v>1813.271240234375</v>
       </c>
       <c r="C464" t="n">
         <v>754.3499755859375</v>
@@ -15366,13 +15366,13 @@
         <v>45250</v>
       </c>
       <c r="B467" t="n">
-        <v>1805.470336914062</v>
+        <v>1805.470458984375</v>
       </c>
       <c r="C467" t="n">
         <v>727.5</v>
       </c>
       <c r="D467" t="n">
-        <v>2146.9853515625</v>
+        <v>2146.985107421875</v>
       </c>
       <c r="E467" t="n">
         <v>926.2000122070312</v>
@@ -15404,7 +15404,7 @@
         <v>731.7999877929688</v>
       </c>
       <c r="D468" t="n">
-        <v>2193.72265625</v>
+        <v>2193.722412109375</v>
       </c>
       <c r="E468" t="n">
         <v>926.5999755859375</v>
@@ -15430,7 +15430,7 @@
         <v>45252</v>
       </c>
       <c r="B469" t="n">
-        <v>1792.436279296875</v>
+        <v>1792.436401367188</v>
       </c>
       <c r="C469" t="n">
         <v>726.9500122070312</v>
@@ -15442,7 +15442,7 @@
         <v>914.4500122070312</v>
       </c>
       <c r="F469" t="n">
-        <v>781.4059448242188</v>
+        <v>781.406005859375</v>
       </c>
       <c r="G469" t="n">
         <v>77.44000244140625</v>
@@ -15462,19 +15462,19 @@
         <v>45253</v>
       </c>
       <c r="B470" t="n">
-        <v>1796.830444335938</v>
+        <v>1796.830322265625</v>
       </c>
       <c r="C470" t="n">
         <v>723.0499877929688</v>
       </c>
       <c r="D470" t="n">
-        <v>2172.35107421875</v>
+        <v>2172.351318359375</v>
       </c>
       <c r="E470" t="n">
         <v>930.7000122070312</v>
       </c>
       <c r="F470" t="n">
-        <v>782.590087890625</v>
+        <v>782.5900268554688</v>
       </c>
       <c r="G470" t="n">
         <v>76.33999633789062</v>
@@ -15494,7 +15494,7 @@
         <v>45254</v>
       </c>
       <c r="B471" t="n">
-        <v>1797.620361328125</v>
+        <v>1797.620239257812</v>
       </c>
       <c r="C471" t="n">
         <v>729.0999755859375</v>
@@ -15596,7 +15596,7 @@
         <v>872.6500244140625</v>
       </c>
       <c r="D474" t="n">
-        <v>2355.406982421875</v>
+        <v>2355.40673828125</v>
       </c>
       <c r="E474" t="n">
         <v>1028.800048828125</v>
@@ -15628,7 +15628,7 @@
         <v>854.7000122070312</v>
       </c>
       <c r="D475" t="n">
-        <v>2359.55126953125</v>
+        <v>2359.551513671875</v>
       </c>
       <c r="E475" t="n">
         <v>1026.5</v>
@@ -15666,7 +15666,7 @@
         <v>1123.75</v>
       </c>
       <c r="F476" t="n">
-        <v>867.0064697265625</v>
+        <v>867.0064086914062</v>
       </c>
       <c r="G476" t="n">
         <v>92.94000244140625</v>
@@ -15692,7 +15692,7 @@
         <v>1084.400024414062</v>
       </c>
       <c r="D477" t="n">
-        <v>2955.40625</v>
+        <v>2955.406494140625</v>
       </c>
       <c r="E477" t="n">
         <v>1348.5</v>
@@ -15730,7 +15730,7 @@
         <v>1563.449951171875</v>
       </c>
       <c r="F478" t="n">
-        <v>1004.460388183594</v>
+        <v>1004.46044921875</v>
       </c>
       <c r="G478" t="n">
         <v>112.0899963378906</v>
@@ -15826,7 +15826,7 @@
         <v>1530</v>
       </c>
       <c r="F481" t="n">
-        <v>1018.2255859375</v>
+        <v>1018.225524902344</v>
       </c>
       <c r="G481" t="n">
         <v>105.2300033569336</v>
@@ -15846,19 +15846,19 @@
         <v>45272</v>
       </c>
       <c r="B482" t="n">
-        <v>2148.109619140625</v>
+        <v>2148.109130859375</v>
       </c>
       <c r="C482" t="n">
         <v>1089.150024414062</v>
       </c>
       <c r="D482" t="n">
-        <v>2853.841552734375</v>
+        <v>2853.841796875</v>
       </c>
       <c r="E482" t="n">
         <v>1463.900024414062</v>
       </c>
       <c r="F482" t="n">
-        <v>1028.142456054688</v>
+        <v>1028.142333984375</v>
       </c>
       <c r="G482" t="n">
         <v>103.3899993896484</v>
@@ -15878,7 +15878,7 @@
         <v>45273</v>
       </c>
       <c r="B483" t="n">
-        <v>2156.74951171875</v>
+        <v>2156.749267578125</v>
       </c>
       <c r="C483" t="n">
         <v>1030.900024414062</v>
@@ -15890,7 +15890,7 @@
         <v>1427.699951171875</v>
       </c>
       <c r="F483" t="n">
-        <v>1049.40673828125</v>
+        <v>1049.406860351562</v>
       </c>
       <c r="G483" t="n">
         <v>101.1399993896484</v>
@@ -15910,7 +15910,7 @@
         <v>45274</v>
       </c>
       <c r="B484" t="n">
-        <v>2206.2197265625</v>
+        <v>2206.219970703125</v>
       </c>
       <c r="C484" t="n">
         <v>1074.75</v>
@@ -16038,13 +16038,13 @@
         <v>45280</v>
       </c>
       <c r="B488" t="n">
-        <v>2060.425537109375</v>
+        <v>2060.42529296875</v>
       </c>
       <c r="C488" t="n">
         <v>998.9000244140625</v>
       </c>
       <c r="D488" t="n">
-        <v>2780.140380859375</v>
+        <v>2780.14013671875</v>
       </c>
       <c r="E488" t="n">
         <v>1452.150024414062</v>
@@ -16134,7 +16134,7 @@
         <v>45286</v>
       </c>
       <c r="B491" t="n">
-        <v>2086.9873046875</v>
+        <v>2086.987548828125</v>
       </c>
       <c r="C491" t="n">
         <v>1041.599975585938</v>
@@ -16178,7 +16178,7 @@
         <v>1601.099975585938</v>
       </c>
       <c r="F492" t="n">
-        <v>1010.824951171875</v>
+        <v>1010.825012207031</v>
       </c>
       <c r="G492" t="n">
         <v>104.4899978637695</v>
@@ -16210,7 +16210,7 @@
         <v>1561</v>
       </c>
       <c r="F493" t="n">
-        <v>1003.473693847656</v>
+        <v>1003.4736328125</v>
       </c>
       <c r="G493" t="n">
         <v>104.6800003051758</v>
@@ -16230,7 +16230,7 @@
         <v>45289</v>
       </c>
       <c r="B494" t="n">
-        <v>2183.45947265625</v>
+        <v>2183.459716796875</v>
       </c>
       <c r="C494" t="n">
         <v>1045.75</v>
@@ -16262,7 +16262,7 @@
         <v>45292</v>
       </c>
       <c r="B495" t="n">
-        <v>2215.10693359375</v>
+        <v>2215.106689453125</v>
       </c>
       <c r="C495" t="n">
         <v>1055.050048828125</v>
@@ -16294,7 +16294,7 @@
         <v>45293</v>
       </c>
       <c r="B496" t="n">
-        <v>2238.804931640625</v>
+        <v>2238.80517578125</v>
       </c>
       <c r="C496" t="n">
         <v>1062.449951171875</v>
@@ -16370,7 +16370,7 @@
         <v>1692.5</v>
       </c>
       <c r="F498" t="n">
-        <v>1108.315673828125</v>
+        <v>1108.315551757812</v>
       </c>
       <c r="G498" t="n">
         <v>111.7099990844727</v>
@@ -16402,7 +16402,7 @@
         <v>1674</v>
       </c>
       <c r="F499" t="n">
-        <v>1138.954223632812</v>
+        <v>1138.9541015625</v>
       </c>
       <c r="G499" t="n">
         <v>110.2200012207031</v>
@@ -16434,7 +16434,7 @@
         <v>1680.050048828125</v>
       </c>
       <c r="F500" t="n">
-        <v>1153.360595703125</v>
+        <v>1153.360717773438</v>
       </c>
       <c r="G500" t="n">
         <v>108.3399963378906</v>
@@ -16454,7 +16454,7 @@
         <v>45300</v>
       </c>
       <c r="B501" t="n">
-        <v>2280.622802734375</v>
+        <v>2280.62255859375</v>
       </c>
       <c r="C501" t="n">
         <v>1164.099975585938</v>
@@ -16486,19 +16486,19 @@
         <v>45301</v>
       </c>
       <c r="B502" t="n">
-        <v>2277.611083984375</v>
+        <v>2277.611328125</v>
       </c>
       <c r="C502" t="n">
         <v>1170.300048828125</v>
       </c>
       <c r="D502" t="n">
-        <v>3094.071044921875</v>
+        <v>3094.0712890625</v>
       </c>
       <c r="E502" t="n">
         <v>1723.25</v>
       </c>
       <c r="F502" t="n">
-        <v>1198.257690429688</v>
+        <v>1198.2578125</v>
       </c>
       <c r="G502" t="n">
         <v>108.4599990844727</v>
@@ -16524,13 +16524,13 @@
         <v>1159.699951171875</v>
       </c>
       <c r="D503" t="n">
-        <v>3076.794189453125</v>
+        <v>3076.7939453125</v>
       </c>
       <c r="E503" t="n">
         <v>1714.150024414062</v>
       </c>
       <c r="F503" t="n">
-        <v>1187.008911132812</v>
+        <v>1187.0087890625</v>
       </c>
       <c r="G503" t="n">
         <v>108.0299987792969</v>
@@ -16550,13 +16550,13 @@
         <v>45303</v>
       </c>
       <c r="B504" t="n">
-        <v>2303.086669921875</v>
+        <v>2303.0869140625</v>
       </c>
       <c r="C504" t="n">
         <v>1152.199951171875</v>
       </c>
       <c r="D504" t="n">
-        <v>3099.963623046875</v>
+        <v>3099.96337890625</v>
       </c>
       <c r="E504" t="n">
         <v>1710.699951171875</v>
@@ -16582,7 +16582,7 @@
         <v>45306</v>
       </c>
       <c r="B505" t="n">
-        <v>2291.237548828125</v>
+        <v>2291.23779296875</v>
       </c>
       <c r="C505" t="n">
         <v>1152.199951171875</v>
@@ -16614,19 +16614,19 @@
         <v>45307</v>
       </c>
       <c r="B506" t="n">
-        <v>2265.614013671875</v>
+        <v>2265.61376953125</v>
       </c>
       <c r="C506" t="n">
         <v>1126.349975585938</v>
       </c>
       <c r="D506" t="n">
-        <v>3052.427001953125</v>
+        <v>3052.4267578125</v>
       </c>
       <c r="E506" t="n">
         <v>1666.800048828125</v>
       </c>
       <c r="F506" t="n">
-        <v>1177.5361328125</v>
+        <v>1177.536010742188</v>
       </c>
       <c r="G506" t="n">
         <v>106.4599990844727</v>
@@ -16658,7 +16658,7 @@
         <v>1615</v>
       </c>
       <c r="F507" t="n">
-        <v>1151.387329101562</v>
+        <v>1151.38720703125</v>
       </c>
       <c r="G507" t="n">
         <v>104.2900009155273</v>
@@ -16690,7 +16690,7 @@
         <v>1588.25</v>
       </c>
       <c r="F508" t="n">
-        <v>1138.756958007812</v>
+        <v>1138.7568359375</v>
       </c>
       <c r="G508" t="n">
         <v>104.7099990844727</v>
@@ -16710,7 +16710,7 @@
         <v>45310</v>
       </c>
       <c r="B509" t="n">
-        <v>2248.48193359375</v>
+        <v>2248.482177734375</v>
       </c>
       <c r="C509" t="n">
         <v>1050.550048828125</v>
@@ -16722,7 +16722,7 @@
         <v>1570.75</v>
       </c>
       <c r="F509" t="n">
-        <v>1137.177978515625</v>
+        <v>1137.178100585938</v>
       </c>
       <c r="G509" t="n">
         <v>103.3499984741211</v>
@@ -16786,7 +16786,7 @@
         <v>1641.349975585938</v>
       </c>
       <c r="F511" t="n">
-        <v>1105.750122070312</v>
+        <v>1105.75</v>
       </c>
       <c r="G511" t="n">
         <v>103.9899978637695</v>
@@ -16818,7 +16818,7 @@
         <v>1664.800048828125</v>
       </c>
       <c r="F512" t="n">
-        <v>1131.109741210938</v>
+        <v>1131.109619140625</v>
       </c>
       <c r="G512" t="n">
         <v>108.6600036621094</v>
@@ -16838,13 +16838,13 @@
         <v>45320</v>
       </c>
       <c r="B513" t="n">
-        <v>2461.56982421875</v>
+        <v>2461.569580078125</v>
       </c>
       <c r="C513" t="n">
         <v>1098.050048828125</v>
       </c>
       <c r="D513" t="n">
-        <v>3060.56591796875</v>
+        <v>3060.565673828125</v>
       </c>
       <c r="E513" t="n">
         <v>1715.5</v>
@@ -16876,7 +16876,7 @@
         <v>1072.699951171875</v>
       </c>
       <c r="D514" t="n">
-        <v>3086.98046875</v>
+        <v>3086.980712890625</v>
       </c>
       <c r="E514" t="n">
         <v>1679.449951171875</v>
@@ -16902,7 +16902,7 @@
         <v>45322</v>
       </c>
       <c r="B515" t="n">
-        <v>2512.323974609375</v>
+        <v>2512.32373046875</v>
       </c>
       <c r="C515" t="n">
         <v>1067.849975585938</v>
@@ -16914,7 +16914,7 @@
         <v>1669.449951171875</v>
       </c>
       <c r="F515" t="n">
-        <v>1191.646606445312</v>
+        <v>1191.646484375</v>
       </c>
       <c r="G515" t="n">
         <v>112.5400009155273</v>
@@ -16934,13 +16934,13 @@
         <v>45323</v>
       </c>
       <c r="B516" t="n">
-        <v>2498.203369140625</v>
+        <v>2498.20361328125</v>
       </c>
       <c r="C516" t="n">
         <v>1067.699951171875</v>
       </c>
       <c r="D516" t="n">
-        <v>3149.297607421875</v>
+        <v>3149.29736328125</v>
       </c>
       <c r="E516" t="n">
         <v>1665.949951171875</v>
@@ -16966,7 +16966,7 @@
         <v>45324</v>
       </c>
       <c r="B517" t="n">
-        <v>2468.037109375</v>
+        <v>2468.037353515625</v>
       </c>
       <c r="C517" t="n">
         <v>1052.050048828125</v>
@@ -16978,7 +16978,7 @@
         <v>1674.25</v>
       </c>
       <c r="F517" t="n">
-        <v>1244.733642578125</v>
+        <v>1244.733520507812</v>
       </c>
       <c r="G517" t="n">
         <v>111.879997253418</v>
@@ -16998,13 +16998,13 @@
         <v>45327</v>
       </c>
       <c r="B518" t="n">
-        <v>2454.953857421875</v>
+        <v>2454.9541015625</v>
       </c>
       <c r="C518" t="n">
         <v>1022.599975585938</v>
       </c>
       <c r="D518" t="n">
-        <v>3169.220947265625</v>
+        <v>3169.220703125</v>
       </c>
       <c r="E518" t="n">
         <v>1668.650024414062</v>
@@ -17036,7 +17036,7 @@
         <v>1029</v>
       </c>
       <c r="D519" t="n">
-        <v>3199.48046875</v>
+        <v>3199.480712890625</v>
       </c>
       <c r="E519" t="n">
         <v>1721.650024414062</v>
@@ -17068,13 +17068,13 @@
         <v>1065.849975585938</v>
       </c>
       <c r="D520" t="n">
-        <v>3225.545654296875</v>
+        <v>3225.5458984375</v>
       </c>
       <c r="E520" t="n">
         <v>1866</v>
       </c>
       <c r="F520" t="n">
-        <v>1239.010498046875</v>
+        <v>1239.010620117188</v>
       </c>
       <c r="G520" t="n">
         <v>113.9400024414062</v>
@@ -17094,7 +17094,7 @@
         <v>45330</v>
       </c>
       <c r="B521" t="n">
-        <v>2479.29443359375</v>
+        <v>2479.294189453125</v>
       </c>
       <c r="C521" t="n">
         <v>1049.900024414062</v>
@@ -17126,19 +17126,19 @@
         <v>45331</v>
       </c>
       <c r="B522" t="n">
-        <v>2595.021484375</v>
+        <v>2595.021240234375</v>
       </c>
       <c r="C522" t="n">
         <v>1054.699951171875</v>
       </c>
       <c r="D522" t="n">
-        <v>3210.915283203125</v>
+        <v>3210.91552734375</v>
       </c>
       <c r="E522" t="n">
         <v>1880.699951171875</v>
       </c>
       <c r="F522" t="n">
-        <v>1254.650390625</v>
+        <v>1254.650512695312</v>
       </c>
       <c r="G522" t="n">
         <v>113.9000015258789</v>
@@ -17190,13 +17190,13 @@
         <v>45335</v>
       </c>
       <c r="B524" t="n">
-        <v>2581.740478515625</v>
+        <v>2581.740234375</v>
       </c>
       <c r="C524" t="n">
         <v>1044.800048828125</v>
       </c>
       <c r="D524" t="n">
-        <v>3174.21435546875</v>
+        <v>3174.214111328125</v>
       </c>
       <c r="E524" t="n">
         <v>1815.550048828125</v>
@@ -17228,7 +17228,7 @@
         <v>1036.949951171875</v>
       </c>
       <c r="D525" t="n">
-        <v>3202.926025390625</v>
+        <v>3202.92578125</v>
       </c>
       <c r="E525" t="n">
         <v>1852.25</v>
@@ -17260,7 +17260,7 @@
         <v>1052</v>
       </c>
       <c r="D526" t="n">
-        <v>3189.543701171875</v>
+        <v>3189.5439453125</v>
       </c>
       <c r="E526" t="n">
         <v>1900.75</v>
@@ -17350,7 +17350,7 @@
         <v>45342</v>
       </c>
       <c r="B529" t="n">
-        <v>2652.93408203125</v>
+        <v>2652.933837890625</v>
       </c>
       <c r="C529" t="n">
         <v>1069.800048828125</v>
@@ -17362,7 +17362,7 @@
         <v>1926.650024414062</v>
       </c>
       <c r="F529" t="n">
-        <v>1283.266235351562</v>
+        <v>1283.26611328125</v>
       </c>
       <c r="G529" t="n">
         <v>110.7300033569336</v>
@@ -17382,7 +17382,7 @@
         <v>45343</v>
       </c>
       <c r="B530" t="n">
-        <v>2633.23486328125</v>
+        <v>2633.234619140625</v>
       </c>
       <c r="C530" t="n">
         <v>1064.800048828125</v>
@@ -17490,7 +17490,7 @@
         <v>1970.449951171875</v>
       </c>
       <c r="F533" t="n">
-        <v>1320.417236328125</v>
+        <v>1320.417114257812</v>
       </c>
       <c r="G533" t="n">
         <v>114.0899963378906</v>
@@ -17516,7 +17516,7 @@
         <v>1122.699951171875</v>
       </c>
       <c r="D534" t="n">
-        <v>3297.8994140625</v>
+        <v>3297.899169921875</v>
       </c>
       <c r="E534" t="n">
         <v>1979.5</v>
@@ -17542,7 +17542,7 @@
         <v>45350</v>
       </c>
       <c r="B535" t="n">
-        <v>2540.909912109375</v>
+        <v>2540.91015625</v>
       </c>
       <c r="C535" t="n">
         <v>1076.449951171875</v>
@@ -17580,7 +17580,7 @@
         <v>1064.849975585938</v>
       </c>
       <c r="D536" t="n">
-        <v>3281.021728515625</v>
+        <v>3281.021484375</v>
       </c>
       <c r="E536" t="n">
         <v>1895.050048828125</v>
@@ -17618,7 +17618,7 @@
         <v>1969.550048828125</v>
       </c>
       <c r="F537" t="n">
-        <v>1304.579956054688</v>
+        <v>1304.579833984375</v>
       </c>
       <c r="G537" t="n">
         <v>110.8300018310547</v>
@@ -17638,13 +17638,13 @@
         <v>45355</v>
       </c>
       <c r="B538" t="n">
-        <v>2661.771728515625</v>
+        <v>2661.771484375</v>
       </c>
       <c r="C538" t="n">
         <v>1064.349975585938</v>
       </c>
       <c r="D538" t="n">
-        <v>3312.7294921875</v>
+        <v>3312.729248046875</v>
       </c>
       <c r="E538" t="n">
         <v>1940.699951171875</v>
@@ -17676,13 +17676,13 @@
         <v>1070.300048828125</v>
       </c>
       <c r="D539" t="n">
-        <v>3305.78857421875</v>
+        <v>3305.788818359375</v>
       </c>
       <c r="E539" t="n">
         <v>1947.400024414062</v>
       </c>
       <c r="F539" t="n">
-        <v>1320.5654296875</v>
+        <v>1320.565307617188</v>
       </c>
       <c r="G539" t="n">
         <v>114.7699966430664</v>
@@ -17714,7 +17714,7 @@
         <v>1910.5</v>
       </c>
       <c r="F540" t="n">
-        <v>1307.244262695312</v>
+        <v>1307.244140625</v>
       </c>
       <c r="G540" t="n">
         <v>115.3399963378906</v>
@@ -17740,7 +17740,7 @@
         <v>1069.599975585938</v>
       </c>
       <c r="D541" t="n">
-        <v>3222.25048828125</v>
+        <v>3222.250244140625</v>
       </c>
       <c r="E541" t="n">
         <v>1929.099975585938</v>
@@ -17842,7 +17842,7 @@
         <v>1725</v>
       </c>
       <c r="F544" t="n">
-        <v>1193.521484375</v>
+        <v>1193.521362304688</v>
       </c>
       <c r="G544" t="n">
         <v>105.6600036621094</v>
@@ -17894,19 +17894,19 @@
         <v>45366</v>
       </c>
       <c r="B546" t="n">
-        <v>2471.493408203125</v>
+        <v>2471.4931640625</v>
       </c>
       <c r="C546" t="n">
         <v>1045.849975585938</v>
       </c>
       <c r="D546" t="n">
-        <v>3128.02587890625</v>
+        <v>3128.025634765625</v>
       </c>
       <c r="E546" t="n">
         <v>1902.599975585938</v>
       </c>
       <c r="F546" t="n">
-        <v>1265.998168945312</v>
+        <v>1265.998046875</v>
       </c>
       <c r="G546" t="n">
         <v>106.0800018310547</v>
@@ -17926,7 +17926,7 @@
         <v>45369</v>
       </c>
       <c r="B547" t="n">
-        <v>2410.864990234375</v>
+        <v>2410.865234375</v>
       </c>
       <c r="C547" t="n">
         <v>1008.849975585938</v>
@@ -18066,7 +18066,7 @@
         <v>1851.75</v>
       </c>
       <c r="F551" t="n">
-        <v>1264.616455078125</v>
+        <v>1264.616577148438</v>
       </c>
       <c r="G551" t="n">
         <v>106.2099990844727</v>
@@ -18098,7 +18098,7 @@
         <v>1859</v>
       </c>
       <c r="F552" t="n">
-        <v>1286.9169921875</v>
+        <v>1286.917114257812</v>
       </c>
       <c r="G552" t="n">
         <v>104.4000015258789</v>
@@ -18150,13 +18150,13 @@
         <v>45379</v>
       </c>
       <c r="B554" t="n">
-        <v>2460.385009765625</v>
+        <v>2460.384765625</v>
       </c>
       <c r="C554" t="n">
         <v>1026.699951171875</v>
       </c>
       <c r="D554" t="n">
-        <v>3192.83935546875</v>
+        <v>3192.839599609375</v>
       </c>
       <c r="E554" t="n">
         <v>1835.150024414062</v>
@@ -18182,7 +18182,7 @@
         <v>45383</v>
       </c>
       <c r="B555" t="n">
-        <v>2512.57080078125</v>
+        <v>2512.570556640625</v>
       </c>
       <c r="C555" t="n">
         <v>1112</v>
@@ -18220,7 +18220,7 @@
         <v>1098.349975585938</v>
       </c>
       <c r="D556" t="n">
-        <v>3264.393798828125</v>
+        <v>3264.39404296875</v>
       </c>
       <c r="E556" t="n">
         <v>1892.650024414062</v>
@@ -18246,13 +18246,13 @@
         <v>45385</v>
       </c>
       <c r="B557" t="n">
-        <v>2600.84716796875</v>
+        <v>2600.846923828125</v>
       </c>
       <c r="C557" t="n">
         <v>1094.75</v>
       </c>
       <c r="D557" t="n">
-        <v>3229.14111328125</v>
+        <v>3229.140869140625</v>
       </c>
       <c r="E557" t="n">
         <v>1878.949951171875</v>
@@ -18278,13 +18278,13 @@
         <v>45386</v>
       </c>
       <c r="B558" t="n">
-        <v>2583.369384765625</v>
+        <v>2583.36962890625</v>
       </c>
       <c r="C558" t="n">
         <v>1102</v>
       </c>
       <c r="D558" t="n">
-        <v>3206.521240234375</v>
+        <v>3206.521484375</v>
       </c>
       <c r="E558" t="n">
         <v>1890.849975585938</v>
@@ -18310,13 +18310,13 @@
         <v>45387</v>
       </c>
       <c r="B559" t="n">
-        <v>2542.73681640625</v>
+        <v>2542.736572265625</v>
       </c>
       <c r="C559" t="n">
         <v>1096.300048828125</v>
       </c>
       <c r="D559" t="n">
-        <v>3220.502685546875</v>
+        <v>3220.50244140625</v>
       </c>
       <c r="E559" t="n">
         <v>1901.949951171875</v>
@@ -18380,13 +18380,13 @@
         <v>1071.25</v>
       </c>
       <c r="D561" t="n">
-        <v>3194.187744140625</v>
+        <v>3194.1875</v>
       </c>
       <c r="E561" t="n">
         <v>1916.199951171875</v>
       </c>
       <c r="F561" t="n">
-        <v>1338.524169921875</v>
+        <v>1338.524047851562</v>
       </c>
       <c r="G561" t="n">
         <v>123.2699966430664</v>
@@ -18412,7 +18412,7 @@
         <v>1064.25</v>
       </c>
       <c r="D562" t="n">
-        <v>3237.679443359375</v>
+        <v>3237.6796875</v>
       </c>
       <c r="E562" t="n">
         <v>1907.5</v>
@@ -18438,7 +18438,7 @@
         <v>45394</v>
       </c>
       <c r="B563" t="n">
-        <v>2437.27880859375</v>
+        <v>2437.279052734375</v>
       </c>
       <c r="C563" t="n">
         <v>1068.900024414062</v>
@@ -18470,7 +18470,7 @@
         <v>45397</v>
       </c>
       <c r="B564" t="n">
-        <v>2411.753662109375</v>
+        <v>2411.75390625</v>
       </c>
       <c r="C564" t="n">
         <v>1039.449951171875</v>
@@ -18508,13 +18508,13 @@
         <v>1051.75</v>
       </c>
       <c r="D565" t="n">
-        <v>3102.260009765625</v>
+        <v>3102.26025390625</v>
       </c>
       <c r="E565" t="n">
         <v>1811.650024414062</v>
       </c>
       <c r="F565" t="n">
-        <v>1287.065063476562</v>
+        <v>1287.065185546875</v>
       </c>
       <c r="G565" t="n">
         <v>120.3199996948242</v>
@@ -18534,7 +18534,7 @@
         <v>45400</v>
       </c>
       <c r="B566" t="n">
-        <v>2381.6865234375</v>
+        <v>2381.686279296875</v>
       </c>
       <c r="C566" t="n">
         <v>1038.75</v>
@@ -18546,7 +18546,7 @@
         <v>1775.449951171875</v>
       </c>
       <c r="F566" t="n">
-        <v>1278.381713867188</v>
+        <v>1278.3818359375</v>
       </c>
       <c r="G566" t="n">
         <v>119.620002746582</v>
@@ -18566,7 +18566,7 @@
         <v>45401</v>
       </c>
       <c r="B567" t="n">
-        <v>2374.92236328125</v>
+        <v>2374.922607421875</v>
       </c>
       <c r="C567" t="n">
         <v>1040.599975585938</v>
@@ -18598,7 +18598,7 @@
         <v>45404</v>
       </c>
       <c r="B568" t="n">
-        <v>2373.3427734375</v>
+        <v>2373.342529296875</v>
       </c>
       <c r="C568" t="n">
         <v>1042.949951171875</v>
@@ -18642,7 +18642,7 @@
         <v>1816.400024414062</v>
       </c>
       <c r="F569" t="n">
-        <v>1304.579956054688</v>
+        <v>1304.579833984375</v>
       </c>
       <c r="G569" t="n">
         <v>120.4899978637695</v>
@@ -18668,7 +18668,7 @@
         <v>1047.849975585938</v>
       </c>
       <c r="D570" t="n">
-        <v>3039.493896484375</v>
+        <v>3039.494140625</v>
       </c>
       <c r="E570" t="n">
         <v>1808.300048828125</v>
@@ -18700,7 +18700,7 @@
         <v>1050.150024414062</v>
       </c>
       <c r="D571" t="n">
-        <v>3111.098388671875</v>
+        <v>3111.09814453125</v>
       </c>
       <c r="E571" t="n">
         <v>1812.650024414062</v>
@@ -18738,7 +18738,7 @@
         <v>1806.650024414062</v>
       </c>
       <c r="F572" t="n">
-        <v>1307.046875</v>
+        <v>1307.046752929688</v>
       </c>
       <c r="G572" t="n">
         <v>118.3199996948242</v>
@@ -18764,13 +18764,13 @@
         <v>1061</v>
       </c>
       <c r="D573" t="n">
-        <v>3077.09375</v>
+        <v>3077.093994140625</v>
       </c>
       <c r="E573" t="n">
         <v>1806.849975585938</v>
       </c>
       <c r="F573" t="n">
-        <v>1299.794189453125</v>
+        <v>1299.794067382812</v>
       </c>
       <c r="G573" t="n">
         <v>119.2200012207031</v>
@@ -18796,13 +18796,13 @@
         <v>1065.199951171875</v>
       </c>
       <c r="D574" t="n">
-        <v>3050.629150390625</v>
+        <v>3050.62890625</v>
       </c>
       <c r="E574" t="n">
         <v>1797.650024414062</v>
       </c>
       <c r="F574" t="n">
-        <v>1307.3427734375</v>
+        <v>1307.342895507812</v>
       </c>
       <c r="G574" t="n">
         <v>122.4899978637695</v>
@@ -18860,7 +18860,7 @@
         <v>1061.550048828125</v>
       </c>
       <c r="D576" t="n">
-        <v>2989.260986328125</v>
+        <v>2989.26123046875</v>
       </c>
       <c r="E576" t="n">
         <v>1799.800048828125</v>
@@ -18892,7 +18892,7 @@
         <v>1058.5</v>
       </c>
       <c r="D577" t="n">
-        <v>2870.819091796875</v>
+        <v>2870.81884765625</v>
       </c>
       <c r="E577" t="n">
         <v>1766.650024414062</v>
@@ -18918,7 +18918,7 @@
         <v>45419</v>
       </c>
       <c r="B578" t="n">
-        <v>2405.829345703125</v>
+        <v>2405.8291015625</v>
       </c>
       <c r="C578" t="n">
         <v>1021.549987792969</v>
@@ -18950,7 +18950,7 @@
         <v>45420</v>
       </c>
       <c r="B579" t="n">
-        <v>2408.939697265625</v>
+        <v>2408.93994140625</v>
       </c>
       <c r="C579" t="n">
         <v>1019.5</v>
@@ -18962,7 +18962,7 @@
         <v>1773</v>
       </c>
       <c r="F579" t="n">
-        <v>1260.324340820312</v>
+        <v>1260.32421875</v>
       </c>
       <c r="G579" t="n">
         <v>116.129997253418</v>
@@ -19026,7 +19026,7 @@
         <v>1714.75</v>
       </c>
       <c r="F581" t="n">
-        <v>1249.963256835938</v>
+        <v>1249.96337890625</v>
       </c>
       <c r="G581" t="n">
         <v>120.620002746582</v>
@@ -19046,7 +19046,7 @@
         <v>45425</v>
       </c>
       <c r="B582" t="n">
-        <v>2334.04296875</v>
+        <v>2334.042724609375</v>
       </c>
       <c r="C582" t="n">
         <v>991.0499877929688</v>
@@ -19058,7 +19058,7 @@
         <v>1715.150024414062</v>
       </c>
       <c r="F582" t="n">
-        <v>1289.088134765625</v>
+        <v>1289.088012695312</v>
       </c>
       <c r="G582" t="n">
         <v>118.9800033569336</v>
@@ -19110,7 +19110,7 @@
         <v>45427</v>
       </c>
       <c r="B584" t="n">
-        <v>2457.866455078125</v>
+        <v>2457.86669921875</v>
       </c>
       <c r="C584" t="n">
         <v>1021.650024414062</v>
@@ -19122,7 +19122,7 @@
         <v>1839.150024414062</v>
       </c>
       <c r="F584" t="n">
-        <v>1320.12109375</v>
+        <v>1320.121215820312</v>
       </c>
       <c r="G584" t="n">
         <v>127.9499969482422</v>
@@ -19142,7 +19142,7 @@
         <v>45428</v>
       </c>
       <c r="B585" t="n">
-        <v>2454.85546875</v>
+        <v>2454.855224609375</v>
       </c>
       <c r="C585" t="n">
         <v>1031</v>
@@ -19174,13 +19174,13 @@
         <v>45429</v>
       </c>
       <c r="B586" t="n">
-        <v>2490.254638671875</v>
+        <v>2490.25439453125</v>
       </c>
       <c r="C586" t="n">
         <v>1035.150024414062</v>
       </c>
       <c r="D586" t="n">
-        <v>3056.42138671875</v>
+        <v>3056.421630859375</v>
       </c>
       <c r="E586" t="n">
         <v>1833</v>
@@ -19218,7 +19218,7 @@
         <v>1859.349975585938</v>
       </c>
       <c r="F587" t="n">
-        <v>1367.139770507812</v>
+        <v>1367.1396484375</v>
       </c>
       <c r="G587" t="n">
         <v>136.0099945068359</v>
@@ -19244,7 +19244,7 @@
         <v>1086.949951171875</v>
       </c>
       <c r="D588" t="n">
-        <v>3136.76416015625</v>
+        <v>3136.763916015625</v>
       </c>
       <c r="E588" t="n">
         <v>1866.449951171875</v>
@@ -19270,7 +19270,7 @@
         <v>45435</v>
       </c>
       <c r="B589" t="n">
-        <v>2583.517333984375</v>
+        <v>2583.517578125</v>
       </c>
       <c r="C589" t="n">
         <v>1099.599975585938</v>
@@ -19398,7 +19398,7 @@
         <v>45441</v>
       </c>
       <c r="B593" t="n">
-        <v>2504.621826171875</v>
+        <v>2504.6220703125</v>
       </c>
       <c r="C593" t="n">
         <v>1085.699951171875</v>
@@ -19442,7 +19442,7 @@
         <v>1874.900024414062</v>
       </c>
       <c r="F594" t="n">
-        <v>1365.166259765625</v>
+        <v>1365.166381835938</v>
       </c>
       <c r="G594" t="n">
         <v>139.6799926757812</v>
@@ -19468,7 +19468,7 @@
         <v>1122.800048828125</v>
       </c>
       <c r="D595" t="n">
-        <v>3406.803955078125</v>
+        <v>3406.80419921875</v>
       </c>
       <c r="E595" t="n">
         <v>1908.349975585938</v>
@@ -19494,7 +19494,7 @@
         <v>45446</v>
       </c>
       <c r="B596" t="n">
-        <v>2649.08349609375</v>
+        <v>2649.0830078125</v>
       </c>
       <c r="C596" t="n">
         <v>1221.949951171875</v>
@@ -19506,7 +19506,7 @@
         <v>2038</v>
       </c>
       <c r="F596" t="n">
-        <v>1562.959838867188</v>
+        <v>1562.9599609375</v>
       </c>
       <c r="G596" t="n">
         <v>174.8999938964844</v>
@@ -19564,7 +19564,7 @@
         <v>951.7000122070312</v>
       </c>
       <c r="D598" t="n">
-        <v>3111.198486328125</v>
+        <v>3111.1982421875</v>
       </c>
       <c r="E598" t="n">
         <v>1828.849975585938</v>
@@ -19596,7 +19596,7 @@
         <v>1001.049987792969</v>
       </c>
       <c r="D599" t="n">
-        <v>3181.404541015625</v>
+        <v>3181.40478515625</v>
       </c>
       <c r="E599" t="n">
         <v>1865.199951171875</v>
@@ -19622,19 +19622,19 @@
         <v>45450</v>
       </c>
       <c r="B600" t="n">
-        <v>2467.692138671875</v>
+        <v>2467.69189453125</v>
       </c>
       <c r="C600" t="n">
         <v>1020.049987792969</v>
       </c>
       <c r="D600" t="n">
-        <v>3215.259521484375</v>
+        <v>3215.259765625</v>
       </c>
       <c r="E600" t="n">
         <v>1864.25</v>
       </c>
       <c r="F600" t="n">
-        <v>1360.577758789062</v>
+        <v>1360.577880859375</v>
       </c>
       <c r="G600" t="n">
         <v>153.4100036621094</v>
@@ -19654,13 +19654,13 @@
         <v>45453</v>
       </c>
       <c r="B601" t="n">
-        <v>2511.13916015625</v>
+        <v>2511.138916015625</v>
       </c>
       <c r="C601" t="n">
         <v>1026.800048828125</v>
       </c>
       <c r="D601" t="n">
-        <v>3215.808837890625</v>
+        <v>3215.80908203125</v>
       </c>
       <c r="E601" t="n">
         <v>1880.349975585938</v>
@@ -19692,13 +19692,13 @@
         <v>1017.849975585938</v>
       </c>
       <c r="D602" t="n">
-        <v>3216.95703125</v>
+        <v>3216.957275390625</v>
       </c>
       <c r="E602" t="n">
         <v>1855.699951171875</v>
       </c>
       <c r="F602" t="n">
-        <v>1384.851806640625</v>
+        <v>1384.851928710938</v>
       </c>
       <c r="G602" t="n">
         <v>152.5700073242188</v>
@@ -19750,13 +19750,13 @@
         <v>45456</v>
       </c>
       <c r="B604" t="n">
-        <v>2602.673583984375</v>
+        <v>2602.673828125</v>
       </c>
       <c r="C604" t="n">
         <v>1017.650024414062</v>
       </c>
       <c r="D604" t="n">
-        <v>3220.502685546875</v>
+        <v>3220.50244140625</v>
       </c>
       <c r="E604" t="n">
         <v>1797.550048828125</v>
@@ -19878,7 +19878,7 @@
         <v>45463</v>
       </c>
       <c r="B608" t="n">
-        <v>2597.07861328125</v>
+        <v>2597.078857421875</v>
       </c>
       <c r="C608" t="n">
         <v>1016.5</v>
@@ -19910,7 +19910,7 @@
         <v>45464</v>
       </c>
       <c r="B609" t="n">
-        <v>2564.9453125</v>
+        <v>2564.945068359375</v>
       </c>
       <c r="C609" t="n">
         <v>1010.549987792969</v>
@@ -20006,7 +20006,7 @@
         <v>45469</v>
       </c>
       <c r="B612" t="n">
-        <v>2565.63818359375</v>
+        <v>2565.638427734375</v>
       </c>
       <c r="C612" t="n">
         <v>1005.099975585938</v>
@@ -20070,7 +20070,7 @@
         <v>45471</v>
       </c>
       <c r="B614" t="n">
-        <v>2593.51416015625</v>
+        <v>2593.513916015625</v>
       </c>
       <c r="C614" t="n">
         <v>997.3499755859375</v>
@@ -20102,7 +20102,7 @@
         <v>45474</v>
       </c>
       <c r="B615" t="n">
-        <v>2722.791259765625</v>
+        <v>2722.791015625</v>
       </c>
       <c r="C615" t="n">
         <v>999.2000122070312</v>
@@ -20166,7 +20166,7 @@
         <v>45476</v>
       </c>
       <c r="B617" t="n">
-        <v>2740.615478515625</v>
+        <v>2740.61572265625</v>
       </c>
       <c r="C617" t="n">
         <v>1035.199951171875</v>
@@ -20262,7 +20262,7 @@
         <v>45481</v>
       </c>
       <c r="B620" t="n">
-        <v>2646.9873046875</v>
+        <v>2646.987548828125</v>
       </c>
       <c r="C620" t="n">
         <v>998.4000244140625</v>
@@ -20326,7 +20326,7 @@
         <v>45483</v>
       </c>
       <c r="B622" t="n">
-        <v>2627.1826171875</v>
+        <v>2627.182373046875</v>
       </c>
       <c r="C622" t="n">
         <v>1003.25</v>
@@ -20390,7 +20390,7 @@
         <v>45485</v>
       </c>
       <c r="B624" t="n">
-        <v>2659.959716796875</v>
+        <v>2659.95947265625</v>
       </c>
       <c r="C624" t="n">
         <v>1004.799987792969</v>
@@ -20454,7 +20454,7 @@
         <v>45489</v>
       </c>
       <c r="B626" t="n">
-        <v>2689.370361328125</v>
+        <v>2689.3701171875</v>
       </c>
       <c r="C626" t="n">
         <v>1022.25</v>
@@ -20486,7 +20486,7 @@
         <v>45491</v>
       </c>
       <c r="B627" t="n">
-        <v>2660.2568359375</v>
+        <v>2660.256591796875</v>
       </c>
       <c r="C627" t="n">
         <v>1010.450012207031</v>
@@ -20518,7 +20518,7 @@
         <v>45492</v>
       </c>
       <c r="B628" t="n">
-        <v>2594.256591796875</v>
+        <v>2594.2568359375</v>
       </c>
       <c r="C628" t="n">
         <v>1010.700012207031</v>
@@ -20614,7 +20614,7 @@
         <v>45497</v>
       </c>
       <c r="B631" t="n">
-        <v>2593.811279296875</v>
+        <v>2593.81103515625</v>
       </c>
       <c r="C631" t="n">
         <v>1036.199951171875</v>
@@ -20710,7 +20710,7 @@
         <v>45502</v>
       </c>
       <c r="B634" t="n">
-        <v>2578.907958984375</v>
+        <v>2578.90771484375</v>
       </c>
       <c r="C634" t="n">
         <v>1051.949951171875</v>
@@ -20742,7 +20742,7 @@
         <v>45503</v>
       </c>
       <c r="B635" t="n">
-        <v>2565.489990234375</v>
+        <v>2565.48974609375</v>
       </c>
       <c r="C635" t="n">
         <v>1124.900024414062</v>
@@ -20774,7 +20774,7 @@
         <v>45504</v>
       </c>
       <c r="B636" t="n">
-        <v>2565.390625</v>
+        <v>2565.390869140625</v>
       </c>
       <c r="C636" t="n">
         <v>1138.050048828125</v>
@@ -20838,7 +20838,7 @@
         <v>45506</v>
       </c>
       <c r="B638" t="n">
-        <v>2411.5556640625</v>
+        <v>2411.555419921875</v>
       </c>
       <c r="C638" t="n">
         <v>1261.800048828125</v>
@@ -20902,7 +20902,7 @@
         <v>45510</v>
       </c>
       <c r="B640" t="n">
-        <v>2319.51171875</v>
+        <v>2319.511962890625</v>
       </c>
       <c r="C640" t="n">
         <v>1124.849975585938</v>
@@ -21062,7 +21062,7 @@
         <v>45517</v>
       </c>
       <c r="B645" t="n">
-        <v>2282.328125</v>
+        <v>2282.327880859375</v>
       </c>
       <c r="C645" t="n">
         <v>1071.25</v>
@@ -21126,7 +21126,7 @@
         <v>45520</v>
       </c>
       <c r="B647" t="n">
-        <v>2315.105224609375</v>
+        <v>2315.10498046875</v>
       </c>
       <c r="C647" t="n">
         <v>1085.300048828125</v>
@@ -21478,7 +21478,7 @@
         <v>45537</v>
       </c>
       <c r="B658" t="n">
-        <v>2313.3720703125</v>
+        <v>2313.372314453125</v>
       </c>
       <c r="C658" t="n">
         <v>1034.099975585938</v>
@@ -21510,7 +21510,7 @@
         <v>45538</v>
       </c>
       <c r="B659" t="n">
-        <v>2318.47216796875</v>
+        <v>2318.471923828125</v>
       </c>
       <c r="C659" t="n">
         <v>1029.199951171875</v>
@@ -21670,7 +21670,7 @@
         <v>45545</v>
       </c>
       <c r="B664" t="n">
-        <v>2419.527099609375</v>
+        <v>2419.52734375</v>
       </c>
       <c r="C664" t="n">
         <v>1014</v>
@@ -21926,7 +21926,7 @@
         <v>45555</v>
       </c>
       <c r="B672" t="n">
-        <v>2419.378662109375</v>
+        <v>2419.37841796875</v>
       </c>
       <c r="C672" t="n">
         <v>1007.150024414062</v>
@@ -22214,7 +22214,7 @@
         <v>45569</v>
       </c>
       <c r="B681" t="n">
-        <v>2410.0205078125</v>
+        <v>2410.020751953125</v>
       </c>
       <c r="C681" t="n">
         <v>962.75</v>
@@ -22310,7 +22310,7 @@
         <v>45574</v>
       </c>
       <c r="B684" t="n">
-        <v>2316.986572265625</v>
+        <v>2316.98681640625</v>
       </c>
       <c r="C684" t="n">
         <v>983.2999877929688</v>
@@ -22438,7 +22438,7 @@
         <v>45580</v>
       </c>
       <c r="B688" t="n">
-        <v>2272.42529296875</v>
+        <v>2272.425537109375</v>
       </c>
       <c r="C688" t="n">
         <v>1004.700012207031</v>
@@ -22470,7 +22470,7 @@
         <v>45581</v>
       </c>
       <c r="B689" t="n">
-        <v>2283.02099609375</v>
+        <v>2283.021240234375</v>
       </c>
       <c r="C689" t="n">
         <v>1032.650024414062</v>
@@ -22502,7 +22502,7 @@
         <v>45582</v>
       </c>
       <c r="B690" t="n">
-        <v>2243.014892578125</v>
+        <v>2243.01513671875</v>
       </c>
       <c r="C690" t="n">
         <v>1021.650024414062</v>
@@ -22534,7 +22534,7 @@
         <v>45583</v>
       </c>
       <c r="B691" t="n">
-        <v>2263.364501953125</v>
+        <v>2263.36474609375</v>
       </c>
       <c r="C691" t="n">
         <v>1043.300048828125</v>
@@ -22598,7 +22598,7 @@
         <v>45587</v>
       </c>
       <c r="B693" t="n">
-        <v>2224.44775390625</v>
+        <v>2224.447998046875</v>
       </c>
       <c r="C693" t="n">
         <v>1009.849975585938</v>
@@ -22758,7 +22758,7 @@
         <v>45594</v>
       </c>
       <c r="B698" t="n">
-        <v>2305.9453125</v>
+        <v>2305.945068359375</v>
       </c>
       <c r="C698" t="n">
         <v>930.5999755859375</v>
@@ -23046,7 +23046,7 @@
         <v>45607</v>
       </c>
       <c r="B707" t="n">
-        <v>2250.59033203125</v>
+        <v>2250.590576171875</v>
       </c>
       <c r="C707" t="n">
         <v>901.9500122070312</v>
@@ -23590,7 +23590,7 @@
         <v>45632</v>
       </c>
       <c r="B724" t="n">
-        <v>2236.3310546875</v>
+        <v>2236.330810546875</v>
       </c>
       <c r="C724" t="n">
         <v>808.3499755859375</v>
@@ -23718,7 +23718,7 @@
         <v>45638</v>
       </c>
       <c r="B728" t="n">
-        <v>2207.71240234375</v>
+        <v>2207.712646484375</v>
       </c>
       <c r="C728" t="n">
         <v>818.1500244140625</v>
@@ -23910,7 +23910,7 @@
         <v>45646</v>
       </c>
       <c r="B734" t="n">
-        <v>2043.529052734375</v>
+        <v>2043.529174804688</v>
       </c>
       <c r="C734" t="n">
         <v>767.5499877929688</v>
@@ -24006,7 +24006,7 @@
         <v>45652</v>
       </c>
       <c r="B737" t="n">
-        <v>2067.295166015625</v>
+        <v>2067.294921875</v>
       </c>
       <c r="C737" t="n">
         <v>792.2999877929688</v>
@@ -24070,7 +24070,7 @@
         <v>45656</v>
       </c>
       <c r="B739" t="n">
-        <v>2039.815673828125</v>
+        <v>2039.815551757812</v>
       </c>
       <c r="C739" t="n">
         <v>826.25</v>
@@ -24198,7 +24198,7 @@
         <v>45660</v>
       </c>
       <c r="B743" t="n">
-        <v>2034.913940429688</v>
+        <v>2034.913818359375</v>
       </c>
       <c r="C743" t="n">
         <v>821.25</v>
@@ -24230,7 +24230,7 @@
         <v>45663</v>
       </c>
       <c r="B744" t="n">
-        <v>1964.754760742188</v>
+        <v>1964.754638671875</v>
       </c>
       <c r="C744" t="n">
         <v>768.5999755859375</v>
@@ -24358,7 +24358,7 @@
         <v>45667</v>
       </c>
       <c r="B748" t="n">
-        <v>1912.222045898438</v>
+        <v>1912.22216796875</v>
       </c>
       <c r="C748" t="n">
         <v>729.25</v>
@@ -24550,7 +24550,7 @@
         <v>45677</v>
       </c>
       <c r="B754" t="n">
-        <v>1986.144165039062</v>
+        <v>1986.14404296875</v>
       </c>
       <c r="C754" t="n">
         <v>815.75</v>
@@ -24582,7 +24582,7 @@
         <v>45678</v>
       </c>
       <c r="B755" t="n">
-        <v>1997.829223632812</v>
+        <v>1997.8291015625</v>
       </c>
       <c r="C755" t="n">
         <v>813.3499755859375</v>
@@ -24646,7 +24646,7 @@
         <v>45680</v>
       </c>
       <c r="B757" t="n">
-        <v>2025.258911132812</v>
+        <v>2025.259033203125</v>
       </c>
       <c r="C757" t="n">
         <v>808.7999877929688</v>
@@ -24742,7 +24742,7 @@
         <v>45685</v>
       </c>
       <c r="B760" t="n">
-        <v>1981.68798828125</v>
+        <v>1981.688110351562</v>
       </c>
       <c r="C760" t="n">
         <v>747.5999755859375</v>
@@ -24774,7 +24774,7 @@
         <v>45686</v>
       </c>
       <c r="B761" t="n">
-        <v>1982.381225585938</v>
+        <v>1982.38134765625</v>
       </c>
       <c r="C761" t="n">
         <v>744.7000122070312</v>
@@ -25094,7 +25094,7 @@
         <v>45699</v>
       </c>
       <c r="B771" t="n">
-        <v>1916.4306640625</v>
+        <v>1916.430541992188</v>
       </c>
       <c r="C771" t="n">
         <v>732.0499877929688</v>
@@ -25318,7 +25318,7 @@
         <v>45708</v>
       </c>
       <c r="B778" t="n">
-        <v>1868.452880859375</v>
+        <v>1868.453002929688</v>
       </c>
       <c r="C778" t="n">
         <v>678</v>
@@ -25414,7 +25414,7 @@
         <v>45713</v>
       </c>
       <c r="B781" t="n">
-        <v>1816.167724609375</v>
+        <v>1816.167846679688</v>
       </c>
       <c r="C781" t="n">
         <v>669.7000122070312</v>
@@ -25446,7 +25446,7 @@
         <v>45715</v>
       </c>
       <c r="B782" t="n">
-        <v>1807.503173828125</v>
+        <v>1807.503051757812</v>
       </c>
       <c r="C782" t="n">
         <v>661.7000122070312</v>
@@ -25574,7 +25574,7 @@
         <v>45721</v>
       </c>
       <c r="B786" t="n">
-        <v>1839.141479492188</v>
+        <v>1839.1416015625</v>
       </c>
       <c r="C786" t="n">
         <v>709.4500122070312</v>
@@ -25606,7 +25606,7 @@
         <v>45722</v>
       </c>
       <c r="B787" t="n">
-        <v>1851.61865234375</v>
+        <v>1851.618774414062</v>
       </c>
       <c r="C787" t="n">
         <v>733.25</v>
@@ -25638,7 +25638,7 @@
         <v>45723</v>
       </c>
       <c r="B788" t="n">
-        <v>1867.36376953125</v>
+        <v>1867.363647460938</v>
       </c>
       <c r="C788" t="n">
         <v>747.5999755859375</v>
@@ -25670,7 +25670,7 @@
         <v>45726</v>
       </c>
       <c r="B789" t="n">
-        <v>1842.458862304688</v>
+        <v>1842.458984375</v>
       </c>
       <c r="C789" t="n">
         <v>759.0999755859375</v>
@@ -25766,7 +25766,7 @@
         <v>45729</v>
       </c>
       <c r="B792" t="n">
-        <v>1835.923217773438</v>
+        <v>1835.92333984375</v>
       </c>
       <c r="C792" t="n">
         <v>783.2000122070312</v>
@@ -26022,7 +26022,7 @@
         <v>45742</v>
       </c>
       <c r="B800" t="n">
-        <v>1914.846069335938</v>
+        <v>1914.84619140625</v>
       </c>
       <c r="C800" t="n">
         <v>803</v>
@@ -26150,7 +26150,7 @@
         <v>45749</v>
       </c>
       <c r="B804" t="n">
-        <v>1944.7021484375</v>
+        <v>1944.702270507812</v>
       </c>
       <c r="C804" t="n">
         <v>867.9000244140625</v>
@@ -26214,7 +26214,7 @@
         <v>45751</v>
       </c>
       <c r="B806" t="n">
-        <v>1947.12841796875</v>
+        <v>1947.128295898438</v>
       </c>
       <c r="C806" t="n">
         <v>859.4000244140625</v>
@@ -26246,7 +26246,7 @@
         <v>45754</v>
       </c>
       <c r="B807" t="n">
-        <v>1910.291015625</v>
+        <v>1910.290893554688</v>
       </c>
       <c r="C807" t="n">
         <v>815.0499877929688</v>
@@ -26470,7 +26470,7 @@
         <v>45768</v>
       </c>
       <c r="B814" t="n">
-        <v>2068.03759765625</v>
+        <v>2068.037841796875</v>
       </c>
       <c r="C814" t="n">
         <v>937.5</v>
@@ -26502,7 +26502,7 @@
         <v>45769</v>
       </c>
       <c r="B815" t="n">
-        <v>2061.4033203125</v>
+        <v>2061.403076171875</v>
       </c>
       <c r="C815" t="n">
         <v>929.5999755859375</v>
@@ -26534,7 +26534,7 @@
         <v>45770</v>
       </c>
       <c r="B816" t="n">
-        <v>2031.893676757812</v>
+        <v>2031.8935546875</v>
       </c>
       <c r="C816" t="n">
         <v>938.7999877929688</v>
@@ -26630,7 +26630,7 @@
         <v>45775</v>
       </c>
       <c r="B819" t="n">
-        <v>1906.330078125</v>
+        <v>1906.329956054688</v>
       </c>
       <c r="C819" t="n">
         <v>925.2999877929688</v>
@@ -26694,7 +26694,7 @@
         <v>45777</v>
       </c>
       <c r="B821" t="n">
-        <v>1869.591796875</v>
+        <v>1869.591674804688</v>
       </c>
       <c r="C821" t="n">
         <v>899.6500244140625</v>
@@ -26790,7 +26790,7 @@
         <v>45783</v>
       </c>
       <c r="B824" t="n">
-        <v>1830.872924804688</v>
+        <v>1830.873046875</v>
       </c>
       <c r="C824" t="n">
         <v>907.4000244140625</v>
@@ -26822,7 +26822,7 @@
         <v>45784</v>
       </c>
       <c r="B825" t="n">
-        <v>1826.911987304688</v>
+        <v>1826.912109375</v>
       </c>
       <c r="C825" t="n">
         <v>871.5999755859375</v>
@@ -27014,7 +27014,7 @@
         <v>45792</v>
       </c>
       <c r="B831" t="n">
-        <v>1865.234741210938</v>
+        <v>1865.234619140625</v>
       </c>
       <c r="C831" t="n">
         <v>910.7999877929688</v>
@@ -27046,7 +27046,7 @@
         <v>45793</v>
       </c>
       <c r="B832" t="n">
-        <v>1909.597900390625</v>
+        <v>1909.597778320312</v>
       </c>
       <c r="C832" t="n">
         <v>915.0499877929688</v>
@@ -27206,7 +27206,7 @@
         <v>45800</v>
       </c>
       <c r="B837" t="n">
-        <v>1940.295654296875</v>
+        <v>1940.295532226562</v>
       </c>
       <c r="C837" t="n">
         <v>876.5499877929688</v>
@@ -27302,7 +27302,7 @@
         <v>45805</v>
       </c>
       <c r="B840" t="n">
-        <v>1901.378662109375</v>
+        <v>1901.378784179688</v>
       </c>
       <c r="C840" t="n">
         <v>869</v>
@@ -27462,7 +27462,7 @@
         <v>45812</v>
       </c>
       <c r="B845" t="n">
-        <v>1858.698974609375</v>
+        <v>1858.699096679688</v>
       </c>
       <c r="C845" t="n">
         <v>866</v>
@@ -27494,7 +27494,7 @@
         <v>45813</v>
       </c>
       <c r="B846" t="n">
-        <v>1866.522094726562</v>
+        <v>1866.52197265625</v>
       </c>
       <c r="C846" t="n">
         <v>872.2000122070312</v>
@@ -27590,7 +27590,7 @@
         <v>45818</v>
       </c>
       <c r="B849" t="n">
-        <v>1894.447021484375</v>
+        <v>1894.446899414062</v>
       </c>
       <c r="C849" t="n">
         <v>915.5</v>
@@ -39412,7 +39412,7 @@
         <v>45808</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.2754233304186782</v>
+        <v>-0.2754168191518525</v>
       </c>
       <c r="C19" t="n">
         <v>-3.606959520527531</v>
@@ -39444,7 +39444,7 @@
         <v>45777</v>
       </c>
       <c r="B20" t="n">
-        <v>-2.813169140423921</v>
+        <v>-2.813175485994568</v>
       </c>
       <c r="C20" t="n">
         <v>3.170874359410836</v>
@@ -39700,7 +39700,7 @@
         <v>45535</v>
       </c>
       <c r="B28" t="n">
-        <v>-10.09398696592259</v>
+        <v>-10.09399552201066</v>
       </c>
       <c r="C28" t="n">
         <v>-11.48016509015537</v>
@@ -39732,7 +39732,7 @@
         <v>45504</v>
       </c>
       <c r="B29" t="n">
-        <v>-1.084379472003949</v>
+        <v>-1.084360747067248</v>
       </c>
       <c r="C29" t="n">
         <v>14.10739225812152</v>
@@ -39764,13 +39764,13 @@
         <v>45473</v>
       </c>
       <c r="B30" t="n">
-        <v>3.146557068662492</v>
+        <v>3.146547358954588</v>
       </c>
       <c r="C30" t="n">
         <v>-11.17296649328798</v>
       </c>
       <c r="D30" t="n">
-        <v>-6.82890662348562</v>
+        <v>-6.828913300373296</v>
       </c>
       <c r="E30" t="n">
         <v>-6.264570350682453</v>
@@ -39802,13 +39802,13 @@
         <v>5.407444639185499</v>
       </c>
       <c r="D31" t="n">
-        <v>11.67545404992583</v>
+        <v>11.6754709902287</v>
       </c>
       <c r="E31" t="n">
         <v>6.158036863040528</v>
       </c>
       <c r="F31" t="n">
-        <v>8.491214362386735</v>
+        <v>8.491204232254468</v>
       </c>
       <c r="G31" t="n">
         <v>23.40599746783077</v>
@@ -39828,19 +39828,19 @@
         <v>45412</v>
       </c>
       <c r="B32" t="n">
-        <v>1.609329554839545</v>
+        <v>1.609339637394758</v>
       </c>
       <c r="C32" t="n">
         <v>3.749878429044062</v>
       </c>
       <c r="D32" t="n">
-        <v>-4.454035710708237</v>
+        <v>-4.454050663139286</v>
       </c>
       <c r="E32" t="n">
         <v>-2.043429665210794</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.26318745484254</v>
+        <v>-1.263178235505569</v>
       </c>
       <c r="G32" t="n">
         <v>14.73397846832833</v>
@@ -39860,13 +39860,13 @@
         <v>45382</v>
       </c>
       <c r="B33" t="n">
-        <v>-5.233329286665189</v>
+        <v>-5.23333869023176</v>
       </c>
       <c r="C33" t="n">
         <v>-3.582666599871998</v>
       </c>
       <c r="D33" t="n">
-        <v>-2.687649773254319</v>
+        <v>-2.687635091253382</v>
       </c>
       <c r="E33" t="n">
         <v>-3.160867674766898</v>
@@ -39892,19 +39892,19 @@
         <v>45351</v>
       </c>
       <c r="B34" t="n">
-        <v>3.340796866695905</v>
+        <v>3.340806909066818</v>
       </c>
       <c r="C34" t="n">
         <v>-0.2809383404587251</v>
       </c>
       <c r="D34" t="n">
-        <v>4.563974846568541</v>
+        <v>4.563967065969599</v>
       </c>
       <c r="E34" t="n">
         <v>13.51343881245972</v>
       </c>
       <c r="F34" t="n">
-        <v>9.344590215355119</v>
+        <v>9.344601416435694</v>
       </c>
       <c r="G34" t="n">
         <v>-2.265863720466688</v>
@@ -39924,7 +39924,7 @@
         <v>45322</v>
       </c>
       <c r="B35" t="n">
-        <v>15.06162610625654</v>
+        <v>15.06160205942875</v>
       </c>
       <c r="C35" t="n">
         <v>2.113313467457556</v>
@@ -39936,7 +39936,7 @@
         <v>4.536628125978392</v>
       </c>
       <c r="F35" t="n">
-        <v>17.89428211519826</v>
+        <v>17.89427003830248</v>
       </c>
       <c r="G35" t="n">
         <v>7.150340115695419</v>
@@ -39956,13 +39956,13 @@
         <v>45291</v>
       </c>
       <c r="B36" t="n">
-        <v>17.89874743332984</v>
+        <v>17.89876061602194</v>
       </c>
       <c r="C36" t="n">
         <v>19.83612797148144</v>
       </c>
       <c r="D36" t="n">
-        <v>20.79242956930774</v>
+        <v>20.79244208958237</v>
       </c>
       <c r="E36" t="n">
         <v>55.22938610073884</v>
@@ -39994,13 +39994,13 @@
         <v>13.36061811535836</v>
       </c>
       <c r="D37" t="n">
-        <v>2.784742670775175</v>
+        <v>2.784742967454901</v>
       </c>
       <c r="E37" t="n">
         <v>12.8503286652526</v>
       </c>
       <c r="F37" t="n">
-        <v>5.192740389700856</v>
+        <v>5.192732098296493</v>
       </c>
       <c r="G37" t="n">
         <v>18.85415552448646</v>
@@ -40026,13 +40026,13 @@
         <v>-4.992287837955112</v>
       </c>
       <c r="D38" t="n">
-        <v>-4.9401280534632</v>
+        <v>-4.940147808046014</v>
       </c>
       <c r="E38" t="n">
         <v>-7.648280214024627</v>
       </c>
       <c r="F38" t="n">
-        <v>-4.896085900373349</v>
+        <v>-4.896078404180482</v>
       </c>
       <c r="G38" t="n">
         <v>-3.815071313970964</v>
@@ -40058,7 +40058,7 @@
         <v>-0.20937399858032</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.2211591036942795</v>
+        <v>-0.2211389159423538</v>
       </c>
       <c r="E39" t="n">
         <v>6.299466802567633</v>
@@ -40084,19 +40084,19 @@
         <v>45169</v>
       </c>
       <c r="B40" t="n">
-        <v>-0.6021117715540814</v>
+        <v>-0.6021178610348565</v>
       </c>
       <c r="C40" t="n">
         <v>-1.066163015700394</v>
       </c>
       <c r="D40" t="n">
-        <v>-2.927122971947371</v>
+        <v>-2.927132781209218</v>
       </c>
       <c r="E40" t="n">
         <v>-15.05991192358821</v>
       </c>
       <c r="F40" t="n">
-        <v>1.844830359818861</v>
+        <v>1.844838458547282</v>
       </c>
       <c r="G40" t="n">
         <v>17.56312168975038</v>
@@ -40116,7 +40116,7 @@
         <v>45138</v>
       </c>
       <c r="B41" t="n">
-        <v>11.82700102606444</v>
+        <v>11.82700021580443</v>
       </c>
       <c r="C41" t="n">
         <v>6.966440170352728</v>
@@ -40128,7 +40128,7 @@
         <v>15.58304478376236</v>
       </c>
       <c r="F41" t="n">
-        <v>5.928874896906988</v>
+        <v>5.928875396325339</v>
       </c>
       <c r="G41" t="n">
         <v>9.385628401317447</v>
@@ -40148,7 +40148,7 @@
         <v>45107</v>
       </c>
       <c r="B42" t="n">
-        <v>2.053786671141311</v>
+        <v>2.053793662779313</v>
       </c>
       <c r="C42" t="n">
         <v>-1.216687531673721</v>
@@ -40160,13 +40160,13 @@
         <v>-3.252530162210432</v>
       </c>
       <c r="F42" t="n">
-        <v>0.05415024319990192</v>
+        <v>0.05414181514649119</v>
       </c>
       <c r="G42" t="n">
         <v>0.08011399015193099</v>
       </c>
       <c r="H42" t="n">
-        <v>0.5429640610794095</v>
+        <v>0.5429566903628613</v>
       </c>
       <c r="I42" t="n">
         <v>-1.437929259655957</v>
@@ -40180,7 +40180,7 @@
         <v>45077</v>
       </c>
       <c r="B43" t="n">
-        <v>0.8140160155767351</v>
+        <v>0.8140231215046256</v>
       </c>
       <c r="C43" t="n">
         <v>-24.55194044908406</v>
@@ -40198,7 +40198,7 @@
         <v>11.02957293714546</v>
       </c>
       <c r="H43" t="n">
-        <v>6.83479181500084</v>
+        <v>6.834808014231619</v>
       </c>
       <c r="I43" t="n">
         <v>-29.71957821123238</v>
@@ -40212,13 +40212,13 @@
         <v>45046</v>
       </c>
       <c r="B44" t="n">
-        <v>5.737175392840688</v>
+        <v>5.737160059376079</v>
       </c>
       <c r="C44" t="n">
         <v>3.66547140892719</v>
       </c>
       <c r="D44" t="n">
-        <v>9.968859779442596</v>
+        <v>9.96886746224337</v>
       </c>
       <c r="E44" t="n">
         <v>7.927137678102603</v>
@@ -40230,7 +40230,7 @@
         <v>17.35386633308638</v>
       </c>
       <c r="H44" t="n">
-        <v>8.466719477722728</v>
+        <v>8.466701768317897</v>
       </c>
       <c r="I44" t="n">
         <v>8.902338132359366</v>
@@ -40244,13 +40244,13 @@
         <v>45016</v>
       </c>
       <c r="B45" t="n">
-        <v>-3.724676428000473</v>
+        <v>-3.724662344575824</v>
       </c>
       <c r="C45" t="n">
         <v>54.46413907015047</v>
       </c>
       <c r="D45" t="n">
-        <v>28.34621056745881</v>
+        <v>28.34620160075407</v>
       </c>
       <c r="E45" t="n">
         <v>81.56811180262491</v>
@@ -40262,7 +40262,7 @@
         <v>30.96377100161289</v>
       </c>
       <c r="H45" t="n">
-        <v>6.854708405226262</v>
+        <v>6.854707782997771</v>
       </c>
       <c r="I45" t="n">
         <v>27.88299979085103</v>
@@ -40276,13 +40276,13 @@
         <v>44985</v>
       </c>
       <c r="B46" t="n">
-        <v>-12.02052577896658</v>
+        <v>-12.02052653780166</v>
       </c>
       <c r="C46" t="n">
         <v>-63.75986333629861</v>
       </c>
       <c r="D46" t="n">
-        <v>-54.13933499301339</v>
+        <v>-54.13933876476883</v>
       </c>
       <c r="E46" t="n">
         <v>-60.34806944094112</v>
@@ -40294,7 +40294,7 @@
         <v>-34.62913019188968</v>
       </c>
       <c r="H46" t="n">
-        <v>-14.73080766987297</v>
+        <v>-14.73079992965691</v>
       </c>
       <c r="I46" t="n">
         <v>-67.81377767062695</v>
@@ -40308,13 +40308,13 @@
         <v>44957</v>
       </c>
       <c r="B47" t="n">
-        <v>-19.38483105268873</v>
+        <v>-19.38482793661753</v>
       </c>
       <c r="C47" t="n">
         <v>-31.48595153036594</v>
       </c>
       <c r="D47" t="n">
-        <v>-22.92301937376114</v>
+        <v>-22.9230130346567</v>
       </c>
       <c r="E47" t="n">
         <v>-36.64458052185531</v>
@@ -40326,7 +40326,7 @@
         <v>-25.28793450920587</v>
       </c>
       <c r="H47" t="n">
-        <v>-23.44972119173867</v>
+        <v>-23.44973026318596</v>
       </c>
       <c r="I47" t="n">
         <v>-42.91130303183772</v>
@@ -40340,7 +40340,7 @@
         <v>44926</v>
       </c>
       <c r="B48" t="n">
-        <v>-4.745927627890323</v>
+        <v>-4.745928088014839</v>
       </c>
       <c r="C48" t="n">
         <v>-10.97644834106928</v>
@@ -40358,7 +40358,7 @@
         <v>-9.977464913384882</v>
       </c>
       <c r="H48" t="n">
-        <v>-8.173465264910885</v>
+        <v>-8.173454383178235</v>
       </c>
       <c r="I48" t="n">
         <v>1.654398082501785</v>
@@ -40372,19 +40372,19 @@
         <v>44895</v>
       </c>
       <c r="B49" t="n">
-        <v>7.235496356655302</v>
+        <v>7.235485960020571</v>
       </c>
       <c r="C49" t="n">
         <v>-13.14539844090323</v>
       </c>
       <c r="D49" t="n">
-        <v>17.04132606638209</v>
+        <v>17.04131751463913</v>
       </c>
       <c r="E49" t="n">
         <v>0.6467306237967874</v>
       </c>
       <c r="F49" t="n">
-        <v>6.9758950401835</v>
+        <v>6.975903128898064</v>
       </c>
       <c r="G49" t="n">
         <v>-0.6419831048444791</v>
@@ -40410,19 +40410,19 @@
         <v>1.790379399037678</v>
       </c>
       <c r="D50" t="n">
-        <v>-3.133913155489276</v>
+        <v>-3.133906077870086</v>
       </c>
       <c r="E50" t="n">
         <v>-6.984259690113759</v>
       </c>
       <c r="F50" t="n">
-        <v>0.3533793058025037</v>
+        <v>0.3533717178334728</v>
       </c>
       <c r="G50" t="n">
         <v>-10.33466386438756</v>
       </c>
       <c r="H50" t="n">
-        <v>3.365019075528308</v>
+        <v>3.365025301034952</v>
       </c>
       <c r="I50" t="n">
         <v>7.87460157490274</v>
@@ -40436,7 +40436,7 @@
         <v>44834</v>
       </c>
       <c r="B51" t="n">
-        <v>5.041980574076521</v>
+        <v>5.041946520860452</v>
       </c>
       <c r="C51" t="n">
         <v>-16.93892268070564</v>
@@ -40448,13 +40448,13 @@
         <v>-7.199733431542765</v>
       </c>
       <c r="F51" t="n">
-        <v>-2.55299014553656</v>
+        <v>-2.552982940061543</v>
       </c>
       <c r="G51" t="n">
         <v>-9.771716243293183</v>
       </c>
       <c r="H51" t="n">
-        <v>25.37385877957157</v>
+        <v>25.37386069556771</v>
       </c>
       <c r="I51" t="n">
         <v>-10.81723467446301</v>
@@ -40468,25 +40468,25 @@
         <v>44804</v>
       </c>
       <c r="B52" t="n">
-        <v>3.245925383613568</v>
+        <v>3.245958854583253</v>
       </c>
       <c r="C52" t="n">
         <v>27.37007418275781</v>
       </c>
       <c r="D52" t="n">
-        <v>24.33247771800031</v>
+        <v>24.3324895543076</v>
       </c>
       <c r="E52" t="n">
         <v>12.02464734774498</v>
       </c>
       <c r="F52" t="n">
-        <v>10.27236099604043</v>
+        <v>10.27236183362958</v>
       </c>
       <c r="G52" t="n">
         <v>31.85220530081916</v>
       </c>
       <c r="H52" t="n">
-        <v>9.725191739073624</v>
+        <v>9.725183453655561</v>
       </c>
       <c r="I52" t="n">
         <v>19.75410011643701</v>
@@ -40506,22 +40506,22 @@
         <v>25.70898148157286</v>
       </c>
       <c r="D53" t="n">
-        <v>17.3152212261489</v>
+        <v>17.31519695579755</v>
       </c>
       <c r="E53" t="n">
         <v>12.70211332333331</v>
       </c>
       <c r="F53" t="n">
-        <v>14.42460685845972</v>
+        <v>14.4246082042711</v>
       </c>
       <c r="G53" t="n">
         <v>19.44074810734559</v>
       </c>
       <c r="H53" t="n">
-        <v>3.250685599129</v>
+        <v>3.250676766290717</v>
       </c>
       <c r="I53" t="n">
-        <v>30.69884602773665</v>
+        <v>30.69885938210128</v>
       </c>
       <c r="J53" t="n">
         <v>45.79545801336116</v>
@@ -40532,28 +40532,28 @@
         <v>44742</v>
       </c>
       <c r="B54" t="n">
-        <v>-3.477523248148151</v>
+        <v>-3.477534159208084</v>
       </c>
       <c r="C54" t="n">
         <v>20.37225802159368</v>
       </c>
       <c r="D54" t="n">
-        <v>1.077235336416615</v>
+        <v>1.077246624996753</v>
       </c>
       <c r="E54" t="n">
         <v>2.151990548444327</v>
       </c>
       <c r="F54" t="n">
-        <v>-9.16400955196821</v>
+        <v>-9.16402572525814</v>
       </c>
       <c r="G54" t="n">
         <v>-18.6852305428317</v>
       </c>
       <c r="H54" t="n">
-        <v>-1.732545046843736</v>
+        <v>-1.732536640307691</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2085154444687709</v>
+        <v>-0.2085358159142237</v>
       </c>
       <c r="J54" t="n">
         <v>3.2258064516129</v>
@@ -40564,19 +40564,19 @@
         <v>44712</v>
       </c>
       <c r="B55" t="n">
-        <v>-5.603502733415966</v>
+        <v>-5.60349206267905</v>
       </c>
       <c r="C55" t="n">
         <v>-26.33088367090877</v>
       </c>
       <c r="D55" t="n">
-        <v>-7.051877972794152</v>
+        <v>-7.051887725396422</v>
       </c>
       <c r="E55" t="n">
         <v>-34.47516583955436</v>
       </c>
       <c r="F55" t="n">
-        <v>-13.60930339146794</v>
+        <v>-13.60928974471389</v>
       </c>
       <c r="G55" t="n">
         <v>15.30230404450439</v>
@@ -40585,7 +40585,7 @@
         <v>-0.7522815575130015</v>
       </c>
       <c r="I55" t="n">
-        <v>-2.164458504802436</v>
+        <v>-2.164458288883464</v>
       </c>
       <c r="J55" t="n">
         <v>-10.23953527808792</v>
@@ -40602,22 +40602,22 @@
         <v>17.7923744286306</v>
       </c>
       <c r="D56" t="n">
-        <v>15.74636953488597</v>
+        <v>15.74636762253454</v>
       </c>
       <c r="E56" t="n">
         <v>50.56145204702873</v>
       </c>
       <c r="F56" t="n">
-        <v>10.61742171272997</v>
+        <v>10.61740465493502</v>
       </c>
       <c r="G56" t="n">
         <v>51.45866829146802</v>
       </c>
       <c r="H56" t="n">
-        <v>24.37762270562873</v>
+        <v>24.37760979872503</v>
       </c>
       <c r="I56" t="n">
-        <v>14.00827459518674</v>
+        <v>14.00827300201519</v>
       </c>
       <c r="J56" t="n">
         <v>-16.3215872474704</v>
@@ -40634,22 +40634,22 @@
         <v>10.95155597333577</v>
       </c>
       <c r="D57" t="n">
-        <v>22.51816022061508</v>
+        <v>22.51818421513112</v>
       </c>
       <c r="E57" t="n">
         <v>3.867848856109002</v>
       </c>
       <c r="F57" t="n">
-        <v>9.427562548959667</v>
+        <v>9.427561713443723</v>
       </c>
       <c r="G57" t="n">
         <v>49.57575942530777</v>
       </c>
       <c r="H57" t="n">
-        <v>-2.747527340443268</v>
+        <v>-2.747507433571683</v>
       </c>
       <c r="I57" t="n">
-        <v>35.33520825688752</v>
+        <v>35.33523406391175</v>
       </c>
       <c r="J57" t="n">
         <v>52.09380234505863</v>
@@ -40660,28 +40660,28 @@
         <v>44620</v>
       </c>
       <c r="B58" t="n">
-        <v>-8.60111741306685</v>
+        <v>-8.601137837897932</v>
       </c>
       <c r="C58" t="n">
         <v>8.295696174558387</v>
       </c>
       <c r="D58" t="n">
-        <v>-4.110902753671142</v>
+        <v>-4.110916728202496</v>
       </c>
       <c r="E58" t="n">
         <v>-1.834542248835702</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.228533210339366</v>
+        <v>-1.228524456736058</v>
       </c>
       <c r="G58" t="n">
         <v>16.47058823529413</v>
       </c>
       <c r="H58" t="n">
-        <v>-13.93945636824542</v>
+        <v>-13.93947252815208</v>
       </c>
       <c r="I58" t="n">
-        <v>-12.77967711983119</v>
+        <v>-12.7796838322096</v>
       </c>
       <c r="J58" t="n">
         <v>34.45945945945945</v>
@@ -41074,7 +41074,7 @@
         <v>45565</v>
       </c>
       <c r="B11" t="n">
-        <v>-4.032002533362878</v>
+        <v>-4.031993499408316</v>
       </c>
       <c r="C11" t="n">
         <v>1.233273086601194</v>
@@ -41106,13 +41106,13 @@
         <v>45473</v>
       </c>
       <c r="B12" t="n">
-        <v>5.410907230462558</v>
+        <v>5.410907767379491</v>
       </c>
       <c r="C12" t="n">
         <v>-2.858671177731864</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.5851488048130182</v>
+        <v>-0.5851564065741277</v>
       </c>
       <c r="E12" t="n">
         <v>-2.52567773584268</v>
@@ -41138,13 +41138,13 @@
         <v>45382</v>
       </c>
       <c r="B13" t="n">
-        <v>12.68287964935233</v>
+        <v>12.68285586850086</v>
       </c>
       <c r="C13" t="n">
         <v>-1.821663765539083</v>
       </c>
       <c r="D13" t="n">
-        <v>12.22029170357897</v>
+        <v>12.22030028450933</v>
       </c>
       <c r="E13" t="n">
         <v>14.91233715805025</v>
@@ -41170,13 +41170,13 @@
         <v>45291</v>
       </c>
       <c r="B14" t="n">
-        <v>9.889428021315737</v>
+        <v>9.889440308456376</v>
       </c>
       <c r="C14" t="n">
         <v>29.06510336315953</v>
       </c>
       <c r="D14" t="n">
-        <v>18.02271323010156</v>
+        <v>18.02270127741525</v>
       </c>
       <c r="E14" t="n">
         <v>61.77885432844141</v>
@@ -41202,19 +41202,19 @@
         <v>45199</v>
       </c>
       <c r="B15" t="n">
-        <v>11.51389277013355</v>
+        <v>11.5138851303904</v>
       </c>
       <c r="C15" t="n">
         <v>5.604431410883026</v>
       </c>
       <c r="D15" t="n">
-        <v>1.131416619271675</v>
+        <v>1.131426861302121</v>
       </c>
       <c r="E15" t="n">
         <v>4.360925989567699</v>
       </c>
       <c r="F15" t="n">
-        <v>12.3702687456182</v>
+        <v>12.37027821111969</v>
       </c>
       <c r="G15" t="n">
         <v>51.07063441994313</v>
@@ -41234,25 +41234,25 @@
         <v>45107</v>
       </c>
       <c r="B16" t="n">
-        <v>8.787186251772505</v>
+        <v>8.78718559686893</v>
       </c>
       <c r="C16" t="n">
         <v>-22.73802835392045</v>
       </c>
       <c r="D16" t="n">
-        <v>36.42493388999573</v>
+        <v>36.42494342110834</v>
       </c>
       <c r="E16" t="n">
         <v>7.348351382394469</v>
       </c>
       <c r="F16" t="n">
-        <v>16.98845100360824</v>
+        <v>16.98844114909532</v>
       </c>
       <c r="G16" t="n">
         <v>30.40188313846057</v>
       </c>
       <c r="H16" t="n">
-        <v>16.50938174960339</v>
+        <v>16.50937185204364</v>
       </c>
       <c r="I16" t="n">
         <v>-24.56352566485572</v>
@@ -41266,13 +41266,13 @@
         <v>45016</v>
       </c>
       <c r="B17" t="n">
-        <v>-31.71691759134699</v>
+        <v>-31.71690555226574</v>
       </c>
       <c r="C17" t="n">
         <v>-61.64719560517645</v>
       </c>
       <c r="D17" t="n">
-        <v>-54.63216110402858</v>
+        <v>-54.63216427358078</v>
       </c>
       <c r="E17" t="n">
         <v>-54.3871000029952</v>
@@ -41284,7 +41284,7 @@
         <v>-36.03738976394022</v>
       </c>
       <c r="H17" t="n">
-        <v>-30.25186657257517</v>
+        <v>-30.2518689127907</v>
       </c>
       <c r="I17" t="n">
         <v>-76.50188891967301</v>
@@ -41298,7 +41298,7 @@
         <v>44926</v>
       </c>
       <c r="B18" t="n">
-        <v>1.074254997477486</v>
+        <v>1.074244709945082</v>
       </c>
       <c r="C18" t="n">
         <v>-21.29460874309583</v>
@@ -41316,7 +41316,7 @@
         <v>-19.79919371493109</v>
       </c>
       <c r="H18" t="n">
-        <v>1.648558807459066</v>
+        <v>1.648576975260174</v>
       </c>
       <c r="I18" t="n">
         <v>10.56933284767878</v>
@@ -41336,22 +41336,22 @@
         <v>32.99376139327897</v>
       </c>
       <c r="D19" t="n">
-        <v>57.79701152688477</v>
+        <v>57.79699390368796</v>
       </c>
       <c r="E19" t="n">
         <v>17.16418311736432</v>
       </c>
       <c r="F19" t="n">
-        <v>22.95738536967666</v>
+        <v>22.95739684156284</v>
       </c>
       <c r="G19" t="n">
         <v>42.09624763531581</v>
       </c>
       <c r="H19" t="n">
-        <v>42.03856806814304</v>
+        <v>42.03854736234809</v>
       </c>
       <c r="I19" t="n">
-        <v>39.58639118085186</v>
+        <v>39.58640544331568</v>
       </c>
       <c r="J19" t="n">
         <v>111.9602203369141</v>
@@ -41368,22 +41368,22 @@
         <v>4.454954472923656</v>
       </c>
       <c r="D20" t="n">
-        <v>8.743010488965041</v>
+        <v>8.743009427151494</v>
       </c>
       <c r="E20" t="n">
         <v>0.7781910896766497</v>
       </c>
       <c r="F20" t="n">
-        <v>-13.19425603140837</v>
+        <v>-13.19427116070798</v>
       </c>
       <c r="G20" t="n">
         <v>42.00431940783369</v>
       </c>
       <c r="H20" t="n">
-        <v>21.30326534957958</v>
+        <v>21.30326313889901</v>
       </c>
       <c r="I20" t="n">
-        <v>11.30803339499058</v>
+        <v>11.30800936277003</v>
       </c>
       <c r="J20" t="n">
         <v>-22.46696035242291</v>

--- a/dashboards/Adani Group.xlsx
+++ b/dashboards/Adani Group.xlsx
@@ -486,7 +486,7 @@
         <v>44564</v>
       </c>
       <c r="B2" t="n">
-        <v>2152.12109375</v>
+        <v>2152.120849609375</v>
       </c>
       <c r="C2" t="n">
         <v>1731.099975585938</v>
@@ -518,7 +518,7 @@
         <v>44565</v>
       </c>
       <c r="B3" t="n">
-        <v>2126.262939453125</v>
+        <v>2126.26318359375</v>
       </c>
       <c r="C3" t="n">
         <v>1754.949951171875</v>
@@ -530,13 +530,13 @@
         <v>1366.699951171875</v>
       </c>
       <c r="F3" t="n">
-        <v>719.5974731445312</v>
+        <v>719.5973510742188</v>
       </c>
       <c r="G3" t="n">
         <v>20.11000061035156</v>
       </c>
       <c r="H3" t="n">
-        <v>375.7160034179688</v>
+        <v>375.7159729003906</v>
       </c>
       <c r="I3" t="n">
         <v>1751.383544921875</v>
@@ -550,13 +550,13 @@
         <v>44566</v>
       </c>
       <c r="B4" t="n">
-        <v>2142.51416015625</v>
+        <v>2142.513916015625</v>
       </c>
       <c r="C4" t="n">
         <v>1761.050048828125</v>
       </c>
       <c r="D4" t="n">
-        <v>1711.629028320312</v>
+        <v>1711.629150390625</v>
       </c>
       <c r="E4" t="n">
         <v>1399.650024414062</v>
@@ -571,7 +571,7 @@
         <v>378.8433227539062</v>
       </c>
       <c r="I4" t="n">
-        <v>1769.107788085938</v>
+        <v>1769.107543945312</v>
       </c>
       <c r="J4" t="n">
         <v>125.6500015258789</v>
@@ -588,13 +588,13 @@
         <v>1760.050048828125</v>
       </c>
       <c r="D5" t="n">
-        <v>1709.2841796875</v>
+        <v>1709.284301757812</v>
       </c>
       <c r="E5" t="n">
         <v>1409.800048828125</v>
       </c>
       <c r="F5" t="n">
-        <v>720.1328735351562</v>
+        <v>720.1328125</v>
       </c>
       <c r="G5" t="n">
         <v>19.96999931335449</v>
@@ -603,7 +603,7 @@
         <v>372.4442443847656</v>
       </c>
       <c r="I5" t="n">
-        <v>1795.868408203125</v>
+        <v>1795.868530273438</v>
       </c>
       <c r="J5" t="n">
         <v>119.9499969482422</v>
@@ -620,22 +620,22 @@
         <v>1776</v>
       </c>
       <c r="D6" t="n">
-        <v>1695.315307617188</v>
+        <v>1695.315551757812</v>
       </c>
       <c r="E6" t="n">
         <v>1423.099975585938</v>
       </c>
       <c r="F6" t="n">
-        <v>716.53125</v>
+        <v>716.5311889648438</v>
       </c>
       <c r="G6" t="n">
         <v>20.04000091552734</v>
       </c>
       <c r="H6" t="n">
-        <v>382.2593078613281</v>
+        <v>382.2593383789062</v>
       </c>
       <c r="I6" t="n">
-        <v>1785.184204101562</v>
+        <v>1785.18408203125</v>
       </c>
       <c r="J6" t="n">
         <v>120.0500030517578</v>
@@ -646,7 +646,7 @@
         <v>44571</v>
       </c>
       <c r="B7" t="n">
-        <v>2217.888427734375</v>
+        <v>2217.88818359375</v>
       </c>
       <c r="C7" t="n">
         <v>1819.699951171875</v>
@@ -664,10 +664,10 @@
         <v>21.73999977111816</v>
       </c>
       <c r="H7" t="n">
-        <v>384.2800598144531</v>
+        <v>384.2800903320312</v>
       </c>
       <c r="I7" t="n">
-        <v>1760.769775390625</v>
+        <v>1760.77001953125</v>
       </c>
       <c r="J7" t="n">
         <v>120.0500030517578</v>
@@ -699,7 +699,7 @@
         <v>382.6442565917969</v>
       </c>
       <c r="I8" t="n">
-        <v>1777.345581054688</v>
+        <v>1777.345458984375</v>
       </c>
       <c r="J8" t="n">
         <v>119.6999969482422</v>
@@ -710,13 +710,13 @@
         <v>44573</v>
       </c>
       <c r="B9" t="n">
-        <v>2212.774169921875</v>
+        <v>2212.7744140625</v>
       </c>
       <c r="C9" t="n">
         <v>1928.25</v>
       </c>
       <c r="D9" t="n">
-        <v>1826.023559570312</v>
+        <v>1826.023803710938</v>
       </c>
       <c r="E9" t="n">
         <v>1647.550048828125</v>
@@ -731,7 +731,7 @@
         <v>382.8848266601562</v>
       </c>
       <c r="I9" t="n">
-        <v>1794.071166992188</v>
+        <v>1794.071044921875</v>
       </c>
       <c r="J9" t="n">
         <v>120</v>
@@ -742,7 +742,7 @@
         <v>44574</v>
       </c>
       <c r="B10" t="n">
-        <v>2212.153076171875</v>
+        <v>2212.15283203125</v>
       </c>
       <c r="C10" t="n">
         <v>2019.699951171875</v>
@@ -754,7 +754,7 @@
         <v>1661.800048828125</v>
       </c>
       <c r="F10" t="n">
-        <v>751.6715087890625</v>
+        <v>751.6715698242188</v>
       </c>
       <c r="G10" t="n">
         <v>23.29000091552734</v>
@@ -763,7 +763,7 @@
         <v>381.44140625</v>
       </c>
       <c r="I10" t="n">
-        <v>1818.585205078125</v>
+        <v>1818.585083007812</v>
       </c>
       <c r="J10" t="n">
         <v>119.9499969482422</v>
@@ -792,10 +792,10 @@
         <v>23.43000030517578</v>
       </c>
       <c r="H11" t="n">
-        <v>387.5037231445312</v>
+        <v>387.5036926269531</v>
       </c>
       <c r="I11" t="n">
-        <v>1803.207763671875</v>
+        <v>1803.207641601562</v>
       </c>
       <c r="J11" t="n">
         <v>118.9000015258789</v>
@@ -806,7 +806,7 @@
         <v>44578</v>
       </c>
       <c r="B12" t="n">
-        <v>2273.81005859375</v>
+        <v>2273.809814453125</v>
       </c>
       <c r="C12" t="n">
         <v>2002.699951171875</v>
@@ -818,16 +818,16 @@
         <v>1835.300048828125</v>
       </c>
       <c r="F12" t="n">
-        <v>758.33935546875</v>
+        <v>758.3394165039062</v>
       </c>
       <c r="G12" t="n">
         <v>23.20999908447266</v>
       </c>
       <c r="H12" t="n">
-        <v>392.4112243652344</v>
+        <v>392.4112548828125</v>
       </c>
       <c r="I12" t="n">
-        <v>1796.16796875</v>
+        <v>1796.168212890625</v>
       </c>
       <c r="J12" t="n">
         <v>117.4000015258789</v>
@@ -838,19 +838,19 @@
         <v>44579</v>
       </c>
       <c r="B13" t="n">
-        <v>2153.9375</v>
+        <v>2153.937255859375</v>
       </c>
       <c r="C13" t="n">
         <v>2026.75</v>
       </c>
       <c r="D13" t="n">
-        <v>1836.849365234375</v>
+        <v>1836.849487304688</v>
       </c>
       <c r="E13" t="n">
         <v>1900.099975585938</v>
       </c>
       <c r="F13" t="n">
-        <v>742.6674194335938</v>
+        <v>742.6673583984375</v>
       </c>
       <c r="G13" t="n">
         <v>21.95000076293945</v>
@@ -876,22 +876,22 @@
         <v>2043.25</v>
       </c>
       <c r="D14" t="n">
-        <v>1845.18115234375</v>
+        <v>1845.180908203125</v>
       </c>
       <c r="E14" t="n">
         <v>1938.449951171875</v>
       </c>
       <c r="F14" t="n">
-        <v>724.4158935546875</v>
+        <v>724.4158325195312</v>
       </c>
       <c r="G14" t="n">
         <v>22.78000068664551</v>
       </c>
       <c r="H14" t="n">
-        <v>360.7046508789062</v>
+        <v>360.70458984375</v>
       </c>
       <c r="I14" t="n">
-        <v>1792.273803710938</v>
+        <v>1792.27392578125</v>
       </c>
       <c r="J14" t="n">
         <v>117.3000030517578</v>
@@ -902,28 +902,28 @@
         <v>44581</v>
       </c>
       <c r="B15" t="n">
-        <v>2154.654052734375</v>
+        <v>2154.654296875</v>
       </c>
       <c r="C15" t="n">
         <v>2039.75</v>
       </c>
       <c r="D15" t="n">
-        <v>1861.694091796875</v>
+        <v>1861.693969726562</v>
       </c>
       <c r="E15" t="n">
         <v>1966.699951171875</v>
       </c>
       <c r="F15" t="n">
-        <v>718.380615234375</v>
+        <v>718.3806762695312</v>
       </c>
       <c r="G15" t="n">
         <v>22.75</v>
       </c>
       <c r="H15" t="n">
-        <v>360.9452209472656</v>
+        <v>360.9451904296875</v>
       </c>
       <c r="I15" t="n">
-        <v>1801.060791015625</v>
+        <v>1801.060913085938</v>
       </c>
       <c r="J15" t="n">
         <v>119.8000030517578</v>
@@ -946,7 +946,7 @@
         <v>1934.550048828125</v>
       </c>
       <c r="F16" t="n">
-        <v>704.655517578125</v>
+        <v>704.6555786132812</v>
       </c>
       <c r="G16" t="n">
         <v>21.98999977111816</v>
@@ -955,7 +955,7 @@
         <v>354.7386169433594</v>
       </c>
       <c r="I16" t="n">
-        <v>1824.626342773438</v>
+        <v>1824.62646484375</v>
       </c>
       <c r="J16" t="n">
         <v>114.4000015258789</v>
@@ -966,7 +966,7 @@
         <v>44585</v>
       </c>
       <c r="B17" t="n">
-        <v>2071.918701171875</v>
+        <v>2071.9189453125</v>
       </c>
       <c r="C17" t="n">
         <v>2035.900024414062</v>
@@ -978,16 +978,16 @@
         <v>1837.849975585938</v>
       </c>
       <c r="F17" t="n">
-        <v>683.7757568359375</v>
+        <v>683.7758178710938</v>
       </c>
       <c r="G17" t="n">
         <v>20.55999946594238</v>
       </c>
       <c r="H17" t="n">
-        <v>339.5348510742188</v>
+        <v>339.5348205566406</v>
       </c>
       <c r="I17" t="n">
-        <v>1778.5439453125</v>
+        <v>1778.543701171875</v>
       </c>
       <c r="J17" t="n">
         <v>106.6999969482422</v>
@@ -1004,7 +1004,7 @@
         <v>1992.449951171875</v>
       </c>
       <c r="D18" t="n">
-        <v>1737.521484375</v>
+        <v>1737.521240234375</v>
       </c>
       <c r="E18" t="n">
         <v>1929</v>
@@ -1016,10 +1016,10 @@
         <v>21.43000030517578</v>
       </c>
       <c r="H18" t="n">
-        <v>338.2357788085938</v>
+        <v>338.2357482910156</v>
       </c>
       <c r="I18" t="n">
-        <v>1822.529418945312</v>
+        <v>1822.529174804688</v>
       </c>
       <c r="J18" t="n">
         <v>108.8000030517578</v>
@@ -1048,10 +1048,10 @@
         <v>21.1299991607666</v>
       </c>
       <c r="H19" t="n">
-        <v>338.3800659179688</v>
+        <v>338.380126953125</v>
       </c>
       <c r="I19" t="n">
-        <v>1828.071411132812</v>
+        <v>1828.071166992188</v>
       </c>
       <c r="J19" t="n">
         <v>117.5999984741211</v>
@@ -1062,28 +1062,28 @@
         <v>44589</v>
       </c>
       <c r="B20" t="n">
-        <v>2118.281494140625</v>
+        <v>2118.28125</v>
       </c>
       <c r="C20" t="n">
         <v>1986.800048828125</v>
       </c>
       <c r="D20" t="n">
-        <v>1689.927612304688</v>
+        <v>1689.927490234375</v>
       </c>
       <c r="E20" t="n">
         <v>1938.400024414062</v>
       </c>
       <c r="F20" t="n">
-        <v>691.2711181640625</v>
+        <v>691.2710571289062</v>
       </c>
       <c r="G20" t="n">
         <v>21.14999961853027</v>
       </c>
       <c r="H20" t="n">
-        <v>347.0885925292969</v>
+        <v>347.088623046875</v>
       </c>
       <c r="I20" t="n">
-        <v>1828.220947265625</v>
+        <v>1828.221069335938</v>
       </c>
       <c r="J20" t="n">
         <v>112.8499984741211</v>
@@ -1094,7 +1094,7 @@
         <v>44592</v>
       </c>
       <c r="B21" t="n">
-        <v>2185.004638671875</v>
+        <v>2185.0048828125</v>
       </c>
       <c r="C21" t="n">
         <v>1970.900024414062</v>
@@ -1115,7 +1115,7 @@
         <v>351.3706665039062</v>
       </c>
       <c r="I21" t="n">
-        <v>1818.585205078125</v>
+        <v>1818.585083007812</v>
       </c>
       <c r="J21" t="n">
         <v>111</v>
@@ -1144,10 +1144,10 @@
         <v>21.60000038146973</v>
       </c>
       <c r="H22" t="n">
-        <v>366.045166015625</v>
+        <v>366.0451965332031</v>
       </c>
       <c r="I22" t="n">
-        <v>1861.921875</v>
+        <v>1861.921630859375</v>
       </c>
       <c r="J22" t="n">
         <v>110.9000015258789</v>
@@ -1158,7 +1158,7 @@
         <v>44594</v>
       </c>
       <c r="B23" t="n">
-        <v>2204.8876953125</v>
+        <v>2204.887939453125</v>
       </c>
       <c r="C23" t="n">
         <v>2016</v>
@@ -1179,7 +1179,7 @@
         <v>365.6602783203125</v>
       </c>
       <c r="I23" t="n">
-        <v>1874.353393554688</v>
+        <v>1874.353515625</v>
       </c>
       <c r="J23" t="n">
         <v>112.0500030517578</v>
@@ -1196,7 +1196,7 @@
         <v>2006.199951171875</v>
       </c>
       <c r="D24" t="n">
-        <v>1747.94775390625</v>
+        <v>1747.947998046875</v>
       </c>
       <c r="E24" t="n">
         <v>1912.550048828125</v>
@@ -1208,7 +1208,7 @@
         <v>21.52000045776367</v>
       </c>
       <c r="H24" t="n">
-        <v>367.4885864257812</v>
+        <v>367.4886169433594</v>
       </c>
       <c r="I24" t="n">
         <v>1848.940795898438</v>
@@ -1222,25 +1222,25 @@
         <v>44596</v>
       </c>
       <c r="B25" t="n">
-        <v>2174.489501953125</v>
+        <v>2174.4892578125</v>
       </c>
       <c r="C25" t="n">
         <v>2033.099975585938</v>
       </c>
       <c r="D25" t="n">
-        <v>1753.385864257812</v>
+        <v>1753.385986328125</v>
       </c>
       <c r="E25" t="n">
         <v>1950.349975585938</v>
       </c>
       <c r="F25" t="n">
-        <v>707.6244506835938</v>
+        <v>707.62451171875</v>
       </c>
       <c r="G25" t="n">
         <v>21.70999908447266</v>
       </c>
       <c r="H25" t="n">
-        <v>366.045166015625</v>
+        <v>366.0451965332031</v>
       </c>
       <c r="I25" t="n">
         <v>1848.391479492188</v>
@@ -1254,13 +1254,13 @@
         <v>44599</v>
       </c>
       <c r="B26" t="n">
-        <v>2181.611328125</v>
+        <v>2181.611083984375</v>
       </c>
       <c r="C26" t="n">
         <v>2028.5</v>
       </c>
       <c r="D26" t="n">
-        <v>1727.94287109375</v>
+        <v>1727.942749023438</v>
       </c>
       <c r="E26" t="n">
         <v>2024.650024414062</v>
@@ -1272,7 +1272,7 @@
         <v>22.34000015258789</v>
       </c>
       <c r="H26" t="n">
-        <v>368.2102661132812</v>
+        <v>368.2102966308594</v>
       </c>
       <c r="I26" t="n">
         <v>1817.48681640625</v>
@@ -1286,7 +1286,7 @@
         <v>44600</v>
       </c>
       <c r="B27" t="n">
-        <v>2203.16748046875</v>
+        <v>2203.167236328125</v>
       </c>
       <c r="C27" t="n">
         <v>1968.300048828125</v>
@@ -1304,10 +1304,10 @@
         <v>21.6299991607666</v>
       </c>
       <c r="H27" t="n">
-        <v>362.0998840332031</v>
+        <v>362.0999145507812</v>
       </c>
       <c r="I27" t="n">
-        <v>1806.403076171875</v>
+        <v>1806.402954101562</v>
       </c>
       <c r="J27" t="n">
         <v>115.5999984741211</v>
@@ -1330,7 +1330,7 @@
         <v>1919.800048828125</v>
       </c>
       <c r="F28" t="n">
-        <v>713.95166015625</v>
+        <v>713.9517211914062</v>
       </c>
       <c r="G28" t="n">
         <v>21.52000045776367</v>
@@ -1339,7 +1339,7 @@
         <v>368.3545837402344</v>
       </c>
       <c r="I28" t="n">
-        <v>1762.41748046875</v>
+        <v>1762.417358398438</v>
       </c>
       <c r="J28" t="n">
         <v>117.4000015258789</v>
@@ -1356,7 +1356,7 @@
         <v>2036.400024414062</v>
       </c>
       <c r="D29" t="n">
-        <v>1782.121826171875</v>
+        <v>1782.12158203125</v>
       </c>
       <c r="E29" t="n">
         <v>1907.949951171875</v>
@@ -1368,10 +1368,10 @@
         <v>24.54999923706055</v>
       </c>
       <c r="H29" t="n">
-        <v>360.7046508789062</v>
+        <v>360.70458984375</v>
       </c>
       <c r="I29" t="n">
-        <v>1807.900756835938</v>
+        <v>1807.901000976562</v>
       </c>
       <c r="J29" t="n">
         <v>140.8500061035156</v>
@@ -1382,7 +1382,7 @@
         <v>44603</v>
       </c>
       <c r="B30" t="n">
-        <v>2150.20947265625</v>
+        <v>2150.209228515625</v>
       </c>
       <c r="C30" t="n">
         <v>2016.050048828125</v>
@@ -1394,7 +1394,7 @@
         <v>1907.599975585938</v>
       </c>
       <c r="F30" t="n">
-        <v>704.4609375</v>
+        <v>704.4608764648438</v>
       </c>
       <c r="G30" t="n">
         <v>25</v>
@@ -1403,7 +1403,7 @@
         <v>354.0168762207031</v>
       </c>
       <c r="I30" t="n">
-        <v>1787.680541992188</v>
+        <v>1787.6806640625</v>
       </c>
       <c r="J30" t="n">
         <v>161.1999969482422</v>
@@ -1420,7 +1420,7 @@
         <v>1915.25</v>
       </c>
       <c r="D31" t="n">
-        <v>1660.243896484375</v>
+        <v>1660.24365234375</v>
       </c>
       <c r="E31" t="n">
         <v>1862.150024414062</v>
@@ -1432,10 +1432,10 @@
         <v>22.67000007629395</v>
       </c>
       <c r="H31" t="n">
-        <v>341.6999206542969</v>
+        <v>341.6998901367188</v>
       </c>
       <c r="I31" t="n">
-        <v>1709.794555664062</v>
+        <v>1709.794677734375</v>
       </c>
       <c r="J31" t="n">
         <v>174.3000030517578</v>
@@ -1452,7 +1452,7 @@
         <v>1926.949951171875</v>
       </c>
       <c r="D32" t="n">
-        <v>1740.364868164062</v>
+        <v>1740.364990234375</v>
       </c>
       <c r="E32" t="n">
         <v>1889.5</v>
@@ -1464,10 +1464,10 @@
         <v>23.59000015258789</v>
       </c>
       <c r="H32" t="n">
-        <v>349.8310241699219</v>
+        <v>349.8310546875</v>
       </c>
       <c r="I32" t="n">
-        <v>1735.157348632812</v>
+        <v>1735.1572265625</v>
       </c>
       <c r="J32" t="n">
         <v>156.8999938964844</v>
@@ -1490,16 +1490,16 @@
         <v>1931.75</v>
       </c>
       <c r="F33" t="n">
-        <v>721.0576171875</v>
+        <v>721.0575561523438</v>
       </c>
       <c r="G33" t="n">
         <v>25.35000038146973</v>
       </c>
       <c r="H33" t="n">
-        <v>347.0885925292969</v>
+        <v>347.088623046875</v>
       </c>
       <c r="I33" t="n">
-        <v>1683.882690429688</v>
+        <v>1683.882568359375</v>
       </c>
       <c r="J33" t="n">
         <v>165.8500061035156</v>
@@ -1510,7 +1510,7 @@
         <v>44609</v>
       </c>
       <c r="B34" t="n">
-        <v>2128.700927734375</v>
+        <v>2128.701171875</v>
       </c>
       <c r="C34" t="n">
         <v>2020.849975585938</v>
@@ -1522,7 +1522,7 @@
         <v>2047.599975585938</v>
       </c>
       <c r="F34" t="n">
-        <v>714.6817016601562</v>
+        <v>714.6817626953125</v>
       </c>
       <c r="G34" t="n">
         <v>26.39999961853027</v>
@@ -1531,7 +1531,7 @@
         <v>346.2225646972656</v>
       </c>
       <c r="I34" t="n">
-        <v>1724.3232421875</v>
+        <v>1724.323364257812</v>
       </c>
       <c r="J34" t="n">
         <v>163.6000061035156</v>
@@ -1542,7 +1542,7 @@
         <v>44610</v>
       </c>
       <c r="B35" t="n">
-        <v>2085.014892578125</v>
+        <v>2085.01513671875</v>
       </c>
       <c r="C35" t="n">
         <v>1958.099975585938</v>
@@ -1580,7 +1580,7 @@
         <v>1895.900024414062</v>
       </c>
       <c r="D36" t="n">
-        <v>1681.4462890625</v>
+        <v>1681.446411132812</v>
       </c>
       <c r="E36" t="n">
         <v>1955.900024414062</v>
@@ -1592,10 +1592,10 @@
         <v>24.03000068664551</v>
       </c>
       <c r="H36" t="n">
-        <v>325.7744445800781</v>
+        <v>325.7744750976562</v>
       </c>
       <c r="I36" t="n">
-        <v>1588.771850585938</v>
+        <v>1588.77197265625</v>
       </c>
       <c r="J36" t="n">
         <v>162.3999938964844</v>
@@ -1606,7 +1606,7 @@
         <v>44614</v>
       </c>
       <c r="B37" t="n">
-        <v>2069.959228515625</v>
+        <v>2069.958984375</v>
       </c>
       <c r="C37" t="n">
         <v>1969.099975585938</v>
@@ -1618,7 +1618,7 @@
         <v>1971.949951171875</v>
       </c>
       <c r="F37" t="n">
-        <v>686.7933959960938</v>
+        <v>686.7933349609375</v>
       </c>
       <c r="G37" t="n">
         <v>24.11000061035156</v>
@@ -1638,13 +1638,13 @@
         <v>44615</v>
       </c>
       <c r="B38" t="n">
-        <v>2056.48046875</v>
+        <v>2056.480712890625</v>
       </c>
       <c r="C38" t="n">
         <v>2060.14990234375</v>
       </c>
       <c r="D38" t="n">
-        <v>1684.9384765625</v>
+        <v>1684.938598632812</v>
       </c>
       <c r="E38" t="n">
         <v>1987.349975585938</v>
@@ -1659,7 +1659,7 @@
         <v>318.4612426757812</v>
       </c>
       <c r="I38" t="n">
-        <v>1639.397705078125</v>
+        <v>1639.397827148438</v>
       </c>
       <c r="J38" t="n">
         <v>149.6999969482422</v>
@@ -1670,13 +1670,13 @@
         <v>44616</v>
       </c>
       <c r="B39" t="n">
-        <v>1925.232177734375</v>
+        <v>1925.232299804688</v>
       </c>
       <c r="C39" t="n">
         <v>1957.300048828125</v>
       </c>
       <c r="D39" t="n">
-        <v>1540.511108398438</v>
+        <v>1540.510986328125</v>
       </c>
       <c r="E39" t="n">
         <v>1849.75</v>
@@ -1688,7 +1688,7 @@
         <v>22.22999954223633</v>
       </c>
       <c r="H39" t="n">
-        <v>295.366943359375</v>
+        <v>295.3669128417969</v>
       </c>
       <c r="I39" t="n">
         <v>1562.760131835938</v>
@@ -1702,7 +1702,7 @@
         <v>44617</v>
       </c>
       <c r="B40" t="n">
-        <v>1968.774780273438</v>
+        <v>1968.7744140625</v>
       </c>
       <c r="C40" t="n">
         <v>2032.849975585938</v>
@@ -1720,10 +1720,10 @@
         <v>24.80999946594238</v>
       </c>
       <c r="H40" t="n">
-        <v>297.0509033203125</v>
+        <v>297.0508728027344</v>
       </c>
       <c r="I40" t="n">
-        <v>1570.898071289062</v>
+        <v>1570.89794921875</v>
       </c>
       <c r="J40" t="n">
         <v>143.9499969482422</v>
@@ -1734,19 +1734,19 @@
         <v>44620</v>
       </c>
       <c r="B41" t="n">
-        <v>1997.069946289062</v>
+        <v>1997.069702148438</v>
       </c>
       <c r="C41" t="n">
         <v>2134.39990234375</v>
       </c>
       <c r="D41" t="n">
-        <v>1640.787231445312</v>
+        <v>1640.787109375</v>
       </c>
       <c r="E41" t="n">
         <v>1843.400024414062</v>
       </c>
       <c r="F41" t="n">
-        <v>688.69140625</v>
+        <v>688.6914672851562</v>
       </c>
       <c r="G41" t="n">
         <v>24.75</v>
@@ -1755,7 +1755,7 @@
         <v>302.3914489746094</v>
       </c>
       <c r="I41" t="n">
-        <v>1586.175659179688</v>
+        <v>1586.17578125</v>
       </c>
       <c r="J41" t="n">
         <v>149.25</v>
@@ -1772,13 +1772,13 @@
         <v>2241.050048828125</v>
       </c>
       <c r="D42" t="n">
-        <v>1638.143188476562</v>
+        <v>1638.14306640625</v>
       </c>
       <c r="E42" t="n">
         <v>1882.550048828125</v>
       </c>
       <c r="F42" t="n">
-        <v>691.4170532226562</v>
+        <v>691.4169921875</v>
       </c>
       <c r="G42" t="n">
         <v>24.6200008392334</v>
@@ -1787,7 +1787,7 @@
         <v>292.6725463867188</v>
       </c>
       <c r="I42" t="n">
-        <v>1665.45947265625</v>
+        <v>1665.459594726562</v>
       </c>
       <c r="J42" t="n">
         <v>153.5</v>
@@ -1798,13 +1798,13 @@
         <v>44623</v>
       </c>
       <c r="B43" t="n">
-        <v>1869.78857421875</v>
+        <v>1869.788452148438</v>
       </c>
       <c r="C43" t="n">
         <v>2353.10009765625</v>
       </c>
       <c r="D43" t="n">
-        <v>1640.138671875</v>
+        <v>1640.138793945312</v>
       </c>
       <c r="E43" t="n">
         <v>1950.900024414062</v>
@@ -1819,7 +1819,7 @@
         <v>279.2490234375</v>
       </c>
       <c r="I43" t="n">
-        <v>1748.6875</v>
+        <v>1748.687622070312</v>
       </c>
       <c r="J43" t="n">
         <v>155.5500030517578</v>
@@ -1836,13 +1836,13 @@
         <v>2323.199951171875</v>
       </c>
       <c r="D44" t="n">
-        <v>1611.402709960938</v>
+        <v>1611.402954101562</v>
       </c>
       <c r="E44" t="n">
         <v>1894.300048828125</v>
       </c>
       <c r="F44" t="n">
-        <v>681.5369873046875</v>
+        <v>681.5369262695312</v>
       </c>
       <c r="G44" t="n">
         <v>23.95000076293945</v>
@@ -1862,7 +1862,7 @@
         <v>44627</v>
       </c>
       <c r="B45" t="n">
-        <v>1864.196411132812</v>
+        <v>1864.196533203125</v>
       </c>
       <c r="C45" t="n">
         <v>2207.35009765625</v>
@@ -1900,22 +1900,22 @@
         <v>2217</v>
       </c>
       <c r="D46" t="n">
-        <v>1598.032470703125</v>
+        <v>1598.03271484375</v>
       </c>
       <c r="E46" t="n">
         <v>1783.949951171875</v>
       </c>
       <c r="F46" t="n">
-        <v>670.5372314453125</v>
+        <v>670.5372924804688</v>
       </c>
       <c r="G46" t="n">
         <v>23.73999977111816</v>
       </c>
       <c r="H46" t="n">
-        <v>272.2244873046875</v>
+        <v>272.2244567871094</v>
       </c>
       <c r="I46" t="n">
-        <v>1627.265625</v>
+        <v>1627.265502929688</v>
       </c>
       <c r="J46" t="n">
         <v>172.3500061035156</v>
@@ -1932,13 +1932,13 @@
         <v>2164.64990234375</v>
       </c>
       <c r="D47" t="n">
-        <v>1652.8603515625</v>
+        <v>1652.860229492188</v>
       </c>
       <c r="E47" t="n">
         <v>1828.75</v>
       </c>
       <c r="F47" t="n">
-        <v>695.1160278320312</v>
+        <v>695.1160888671875</v>
       </c>
       <c r="G47" t="n">
         <v>24.26000022888184</v>
@@ -1947,7 +1947,7 @@
         <v>280.6442565917969</v>
       </c>
       <c r="I47" t="n">
-        <v>1612.986450195312</v>
+        <v>1612.986328125</v>
       </c>
       <c r="J47" t="n">
         <v>176.3500061035156</v>
@@ -1958,28 +1958,28 @@
         <v>44630</v>
       </c>
       <c r="B48" t="n">
-        <v>1957.351196289062</v>
+        <v>1957.35107421875</v>
       </c>
       <c r="C48" t="n">
         <v>2272.75</v>
       </c>
       <c r="D48" t="n">
-        <v>1738.968017578125</v>
+        <v>1738.967895507812</v>
       </c>
       <c r="E48" t="n">
         <v>1881.849975585938</v>
       </c>
       <c r="F48" t="n">
-        <v>710.9827270507812</v>
+        <v>710.9827880859375</v>
       </c>
       <c r="G48" t="n">
         <v>24.5</v>
       </c>
       <c r="H48" t="n">
-        <v>282.1358032226562</v>
+        <v>282.1357727050781</v>
       </c>
       <c r="I48" t="n">
-        <v>1693.568481445312</v>
+        <v>1693.568359375</v>
       </c>
       <c r="J48" t="n">
         <v>171.3500061035156</v>
@@ -1990,13 +1990,13 @@
         <v>44631</v>
       </c>
       <c r="B49" t="n">
-        <v>1951.902587890625</v>
+        <v>1951.902465820312</v>
       </c>
       <c r="C49" t="n">
         <v>2307.25</v>
       </c>
       <c r="D49" t="n">
-        <v>1730.237426757812</v>
+        <v>1730.237548828125</v>
       </c>
       <c r="E49" t="n">
         <v>1860.050048828125</v>
@@ -2028,7 +2028,7 @@
         <v>2268.300048828125</v>
       </c>
       <c r="D50" t="n">
-        <v>1732.233154296875</v>
+        <v>1732.233032226562</v>
       </c>
       <c r="E50" t="n">
         <v>1822.400024414062</v>
@@ -2040,7 +2040,7 @@
         <v>24.43000030517578</v>
       </c>
       <c r="H50" t="n">
-        <v>280.2112731933594</v>
+        <v>280.2112426757812</v>
       </c>
       <c r="I50" t="n">
         <v>1647.935180664062</v>
@@ -2054,13 +2054,13 @@
         <v>44635</v>
       </c>
       <c r="B51" t="n">
-        <v>1969.53955078125</v>
+        <v>1969.539428710938</v>
       </c>
       <c r="C51" t="n">
         <v>2217.550048828125</v>
       </c>
       <c r="D51" t="n">
-        <v>1697.610473632812</v>
+        <v>1697.6103515625</v>
       </c>
       <c r="E51" t="n">
         <v>1798.75</v>
@@ -2072,7 +2072,7 @@
         <v>24.45999908447266</v>
       </c>
       <c r="H51" t="n">
-        <v>283.964111328125</v>
+        <v>283.9640808105469</v>
       </c>
       <c r="I51" t="n">
         <v>1622.023315429688</v>
@@ -2092,7 +2092,7 @@
         <v>2305.39990234375</v>
       </c>
       <c r="D52" t="n">
-        <v>1754.084350585938</v>
+        <v>1754.084228515625</v>
       </c>
       <c r="E52" t="n">
         <v>1833.650024414062</v>
@@ -2107,7 +2107,7 @@
         <v>297.6763610839844</v>
       </c>
       <c r="I52" t="n">
-        <v>1682.63427734375</v>
+        <v>1682.634399414062</v>
       </c>
       <c r="J52" t="n">
         <v>197.0500030517578</v>
@@ -2124,7 +2124,7 @@
         <v>2389.800048828125</v>
       </c>
       <c r="D53" t="n">
-        <v>1815.597045898438</v>
+        <v>1815.596923828125</v>
       </c>
       <c r="E53" t="n">
         <v>1901.199951171875</v>
@@ -2139,7 +2139,7 @@
         <v>294.6452331542969</v>
       </c>
       <c r="I53" t="n">
-        <v>1764.215087890625</v>
+        <v>1764.214965820312</v>
       </c>
       <c r="J53" t="n">
         <v>206.6000061035156</v>
@@ -2156,22 +2156,22 @@
         <v>2289.050048828125</v>
       </c>
       <c r="D54" t="n">
-        <v>1798.93408203125</v>
+        <v>1798.934204101562</v>
       </c>
       <c r="E54" t="n">
         <v>1876.050048828125</v>
       </c>
       <c r="F54" t="n">
-        <v>715.6065063476562</v>
+        <v>715.6064453125</v>
       </c>
       <c r="G54" t="n">
         <v>24.90999984741211</v>
       </c>
       <c r="H54" t="n">
-        <v>289.0159606933594</v>
+        <v>289.0160217285156</v>
       </c>
       <c r="I54" t="n">
-        <v>1811.495483398438</v>
+        <v>1811.49560546875</v>
       </c>
       <c r="J54" t="n">
         <v>227.25</v>
@@ -2182,7 +2182,7 @@
         <v>44642</v>
       </c>
       <c r="B55" t="n">
-        <v>1967.579833984375</v>
+        <v>1967.579711914062</v>
       </c>
       <c r="C55" t="n">
         <v>2338.050048828125</v>
@@ -2194,16 +2194,16 @@
         <v>1877.449951171875</v>
       </c>
       <c r="F55" t="n">
-        <v>719.5001831054688</v>
+        <v>719.5001220703125</v>
       </c>
       <c r="G55" t="n">
         <v>24.75</v>
       </c>
       <c r="H55" t="n">
-        <v>289.5451965332031</v>
+        <v>289.5452270507812</v>
       </c>
       <c r="I55" t="n">
-        <v>1881.193481445312</v>
+        <v>1881.193237304688</v>
       </c>
       <c r="J55" t="n">
         <v>238.6000061035156</v>
@@ -2214,7 +2214,7 @@
         <v>44643</v>
       </c>
       <c r="B56" t="n">
-        <v>1978.525146484375</v>
+        <v>1978.525024414062</v>
       </c>
       <c r="C56" t="n">
         <v>2406.699951171875</v>
@@ -2226,7 +2226,7 @@
         <v>1921.400024414062</v>
       </c>
       <c r="F56" t="n">
-        <v>714.24365234375</v>
+        <v>714.2437133789062</v>
       </c>
       <c r="G56" t="n">
         <v>26.04000091552734</v>
@@ -2235,7 +2235,7 @@
         <v>286.6103210449219</v>
       </c>
       <c r="I56" t="n">
-        <v>1895.222900390625</v>
+        <v>1895.223022460938</v>
       </c>
       <c r="J56" t="n">
         <v>250.5</v>
@@ -2252,13 +2252,13 @@
         <v>2414.39990234375</v>
       </c>
       <c r="D57" t="n">
-        <v>1828.717651367188</v>
+        <v>1828.7177734375</v>
       </c>
       <c r="E57" t="n">
         <v>1911.400024414062</v>
       </c>
       <c r="F57" t="n">
-        <v>713.95166015625</v>
+        <v>713.9517211914062</v>
       </c>
       <c r="G57" t="n">
         <v>26.43000030517578</v>
@@ -2278,13 +2278,13 @@
         <v>44645</v>
       </c>
       <c r="B58" t="n">
-        <v>1973.2197265625</v>
+        <v>1973.219482421875</v>
       </c>
       <c r="C58" t="n">
         <v>2448.75</v>
       </c>
       <c r="D58" t="n">
-        <v>1862.841552734375</v>
+        <v>1862.841674804688</v>
       </c>
       <c r="E58" t="n">
         <v>1921.25</v>
@@ -2299,7 +2299,7 @@
         <v>286.5621643066406</v>
       </c>
       <c r="I58" t="n">
-        <v>2051.59375</v>
+        <v>2051.593505859375</v>
       </c>
       <c r="J58" t="n">
         <v>252.1000061035156</v>
@@ -2310,7 +2310,7 @@
         <v>44648</v>
       </c>
       <c r="B59" t="n">
-        <v>1968.8701171875</v>
+        <v>1968.869995117188</v>
       </c>
       <c r="C59" t="n">
         <v>2439</v>
@@ -2322,7 +2322,7 @@
         <v>1930.849975585938</v>
       </c>
       <c r="F59" t="n">
-        <v>717.4072875976562</v>
+        <v>717.4072265625</v>
       </c>
       <c r="G59" t="n">
         <v>30.45000076293945</v>
@@ -2348,7 +2348,7 @@
         <v>2461.550048828125</v>
       </c>
       <c r="D60" t="n">
-        <v>1912.9794921875</v>
+        <v>1912.979614257812</v>
       </c>
       <c r="E60" t="n">
         <v>1923.300048828125</v>
@@ -2360,10 +2360,10 @@
         <v>34.70999908447266</v>
       </c>
       <c r="H60" t="n">
-        <v>291.0367126464844</v>
+        <v>291.0367736816406</v>
       </c>
       <c r="I60" t="n">
-        <v>2177.609375</v>
+        <v>2177.609130859375</v>
       </c>
       <c r="J60" t="n">
         <v>227.5500030517578</v>
@@ -2380,7 +2380,7 @@
         <v>2377.39990234375</v>
       </c>
       <c r="D61" t="n">
-        <v>1990.805908203125</v>
+        <v>1990.805786132812</v>
       </c>
       <c r="E61" t="n">
         <v>1857.150024414062</v>
@@ -2395,7 +2395,7 @@
         <v>297.8175964355469</v>
       </c>
       <c r="I61" t="n">
-        <v>2121.541015625</v>
+        <v>2121.541259765625</v>
       </c>
       <c r="J61" t="n">
         <v>238.8999938964844</v>
@@ -2424,7 +2424,7 @@
         <v>37.02000045776367</v>
       </c>
       <c r="H62" t="n">
-        <v>294.0832214355469</v>
+        <v>294.0831909179688</v>
       </c>
       <c r="I62" t="n">
         <v>2146.654541015625</v>
@@ -2438,7 +2438,7 @@
         <v>44652</v>
       </c>
       <c r="B63" t="n">
-        <v>2056.193603515625</v>
+        <v>2056.194091796875</v>
       </c>
       <c r="C63" t="n">
         <v>2421.449951171875</v>
@@ -2456,10 +2456,10 @@
         <v>40.68999862670898</v>
       </c>
       <c r="H63" t="n">
-        <v>299.684814453125</v>
+        <v>299.6847839355469</v>
       </c>
       <c r="I63" t="n">
-        <v>2246.20849609375</v>
+        <v>2246.208740234375</v>
       </c>
       <c r="J63" t="n">
         <v>223.25</v>
@@ -2470,13 +2470,13 @@
         <v>44655</v>
       </c>
       <c r="B64" t="n">
-        <v>2082.1787109375</v>
+        <v>2082.178466796875</v>
       </c>
       <c r="C64" t="n">
         <v>2453.5</v>
       </c>
       <c r="D64" t="n">
-        <v>2061.24853515625</v>
+        <v>2061.248779296875</v>
       </c>
       <c r="E64" t="n">
         <v>2110.449951171875</v>
@@ -2488,7 +2488,7 @@
         <v>42.38999938964844</v>
       </c>
       <c r="H64" t="n">
-        <v>306.2691040039062</v>
+        <v>306.2691345214844</v>
       </c>
       <c r="I64" t="n">
         <v>2366.332763671875</v>
@@ -2502,13 +2502,13 @@
         <v>44656</v>
       </c>
       <c r="B65" t="n">
-        <v>2111.84765625</v>
+        <v>2111.847412109375</v>
       </c>
       <c r="C65" t="n">
         <v>2443.85009765625</v>
       </c>
       <c r="D65" t="n">
-        <v>2135.084228515625</v>
+        <v>2135.083984375</v>
       </c>
       <c r="E65" t="n">
         <v>2189.800048828125</v>
@@ -2520,7 +2520,7 @@
         <v>46.61999893188477</v>
       </c>
       <c r="H65" t="n">
-        <v>311.3301696777344</v>
+        <v>311.3302001953125</v>
       </c>
       <c r="I65" t="n">
         <v>2464.53857421875</v>
@@ -2540,7 +2540,7 @@
         <v>2484.050048828125</v>
       </c>
       <c r="D66" t="n">
-        <v>2155.189208984375</v>
+        <v>2155.18896484375</v>
       </c>
       <c r="E66" t="n">
         <v>2197.39990234375</v>
@@ -2572,7 +2572,7 @@
         <v>2449.64990234375</v>
       </c>
       <c r="D67" t="n">
-        <v>2094.37451171875</v>
+        <v>2094.375</v>
       </c>
       <c r="E67" t="n">
         <v>2166</v>
@@ -2584,10 +2584,10 @@
         <v>46.5099983215332</v>
       </c>
       <c r="H67" t="n">
-        <v>319.9782409667969</v>
+        <v>319.978271484375</v>
       </c>
       <c r="I67" t="n">
-        <v>2359.242919921875</v>
+        <v>2359.24267578125</v>
       </c>
       <c r="J67" t="n">
         <v>212.1999969482422</v>
@@ -2598,7 +2598,7 @@
         <v>44659</v>
       </c>
       <c r="B68" t="n">
-        <v>2132.3798828125</v>
+        <v>2132.380126953125</v>
       </c>
       <c r="C68" t="n">
         <v>2540.25</v>
@@ -2610,13 +2610,13 @@
         <v>2321.85009765625</v>
       </c>
       <c r="F68" t="n">
-        <v>816.9877319335938</v>
+        <v>816.9876708984375</v>
       </c>
       <c r="G68" t="n">
         <v>44.18999862670898</v>
       </c>
       <c r="H68" t="n">
-        <v>331.5253601074219</v>
+        <v>331.525390625</v>
       </c>
       <c r="I68" t="n">
         <v>2423.548828125</v>
@@ -2630,13 +2630,13 @@
         <v>44662</v>
       </c>
       <c r="B69" t="n">
-        <v>2193.6337890625</v>
+        <v>2193.633544921875</v>
       </c>
       <c r="C69" t="n">
         <v>2756.5</v>
       </c>
       <c r="D69" t="n">
-        <v>2175.34375</v>
+        <v>2175.343994140625</v>
       </c>
       <c r="E69" t="n">
         <v>2665.14990234375</v>
@@ -2668,19 +2668,19 @@
         <v>2680.550048828125</v>
       </c>
       <c r="D70" t="n">
-        <v>2192.056884765625</v>
+        <v>2192.056640625</v>
       </c>
       <c r="E70" t="n">
         <v>2792.39990234375</v>
       </c>
       <c r="F70" t="n">
-        <v>822.4387817382812</v>
+        <v>822.4388427734375</v>
       </c>
       <c r="G70" t="n">
         <v>46.15999984741211</v>
       </c>
       <c r="H70" t="n">
-        <v>353.4403381347656</v>
+        <v>353.4403686523438</v>
       </c>
       <c r="I70" t="n">
         <v>2498.38916015625</v>
@@ -2694,7 +2694,7 @@
         <v>44664</v>
       </c>
       <c r="B71" t="n">
-        <v>2169.809814453125</v>
+        <v>2169.81005859375</v>
       </c>
       <c r="C71" t="n">
         <v>2690.75</v>
@@ -2715,7 +2715,7 @@
         <v>362.8254699707031</v>
       </c>
       <c r="I71" t="n">
-        <v>2497.19091796875</v>
+        <v>2497.190673828125</v>
       </c>
       <c r="J71" t="n">
         <v>200.1000061035156</v>
@@ -2726,19 +2726,19 @@
         <v>44669</v>
       </c>
       <c r="B72" t="n">
-        <v>2117.300048828125</v>
+        <v>2117.30029296875</v>
       </c>
       <c r="C72" t="n">
         <v>2728.300048828125</v>
       </c>
       <c r="D72" t="n">
-        <v>2228.874267578125</v>
+        <v>2228.874755859375</v>
       </c>
       <c r="E72" t="n">
         <v>2970.5</v>
       </c>
       <c r="F72" t="n">
-        <v>820.2973022460938</v>
+        <v>820.29736328125</v>
       </c>
       <c r="G72" t="n">
         <v>46.88000106811523</v>
@@ -2747,7 +2747,7 @@
         <v>357.1256103515625</v>
       </c>
       <c r="I72" t="n">
-        <v>2491.349365234375</v>
+        <v>2491.349609375</v>
       </c>
       <c r="J72" t="n">
         <v>210.1000061035156</v>
@@ -2758,7 +2758,7 @@
         <v>44670</v>
       </c>
       <c r="B73" t="n">
-        <v>2020.335693359375</v>
+        <v>2020.335815429688</v>
       </c>
       <c r="C73" t="n">
         <v>2598.050048828125</v>
@@ -2790,19 +2790,19 @@
         <v>44671</v>
       </c>
       <c r="B74" t="n">
-        <v>2169.417236328125</v>
+        <v>2169.4169921875</v>
       </c>
       <c r="C74" t="n">
         <v>2687.550048828125</v>
       </c>
       <c r="D74" t="n">
-        <v>2179.085205078125</v>
+        <v>2179.08544921875</v>
       </c>
       <c r="E74" t="n">
         <v>2810.85009765625</v>
       </c>
       <c r="F74" t="n">
-        <v>805.6474609375</v>
+        <v>805.6473999023438</v>
       </c>
       <c r="G74" t="n">
         <v>47.0099983215332</v>
@@ -2811,7 +2811,7 @@
         <v>364.8891906738281</v>
       </c>
       <c r="I74" t="n">
-        <v>2474.773681640625</v>
+        <v>2474.7734375</v>
       </c>
       <c r="J74" t="n">
         <v>213.0500030517578</v>
@@ -2822,28 +2822,28 @@
         <v>44672</v>
       </c>
       <c r="B75" t="n">
-        <v>2230.1796875</v>
+        <v>2230.179443359375</v>
       </c>
       <c r="C75" t="n">
         <v>2699.60009765625</v>
       </c>
       <c r="D75" t="n">
-        <v>2281.25732421875</v>
+        <v>2281.2578125</v>
       </c>
       <c r="E75" t="n">
         <v>2811.5</v>
       </c>
       <c r="F75" t="n">
-        <v>827.8899536132812</v>
+        <v>827.889892578125</v>
       </c>
       <c r="G75" t="n">
         <v>49.36000061035156</v>
       </c>
       <c r="H75" t="n">
-        <v>370.8347473144531</v>
+        <v>370.8347778320312</v>
       </c>
       <c r="I75" t="n">
-        <v>2439.775146484375</v>
+        <v>2439.77490234375</v>
       </c>
       <c r="J75" t="n">
         <v>214.3500061035156</v>
@@ -2860,13 +2860,13 @@
         <v>2658.550048828125</v>
       </c>
       <c r="D76" t="n">
-        <v>2268.236328125</v>
+        <v>2268.23681640625</v>
       </c>
       <c r="E76" t="n">
         <v>2882.800048828125</v>
       </c>
       <c r="F76" t="n">
-        <v>850.9112548828125</v>
+        <v>850.9113159179688</v>
       </c>
       <c r="G76" t="n">
         <v>51.81999969482422</v>
@@ -2875,7 +2875,7 @@
         <v>367.7391357421875</v>
       </c>
       <c r="I76" t="n">
-        <v>2409.468994140625</v>
+        <v>2409.46923828125</v>
       </c>
       <c r="J76" t="n">
         <v>211.1999969482422</v>
@@ -2886,13 +2886,13 @@
         <v>44676</v>
       </c>
       <c r="B77" t="n">
-        <v>2222.27099609375</v>
+        <v>2222.271240234375</v>
       </c>
       <c r="C77" t="n">
         <v>2615.89990234375</v>
       </c>
       <c r="D77" t="n">
-        <v>2279.1123046875</v>
+        <v>2279.112548828125</v>
       </c>
       <c r="E77" t="n">
         <v>2824</v>
@@ -2904,7 +2904,7 @@
         <v>54.40999984741211</v>
       </c>
       <c r="H77" t="n">
-        <v>369.8520202636719</v>
+        <v>369.85205078125</v>
       </c>
       <c r="I77" t="n">
         <v>2416.458984375</v>
@@ -2918,13 +2918,13 @@
         <v>44677</v>
       </c>
       <c r="B78" t="n">
-        <v>2270.704345703125</v>
+        <v>2270.7041015625</v>
       </c>
       <c r="C78" t="n">
         <v>2812.550048828125</v>
       </c>
       <c r="D78" t="n">
-        <v>2389.965087890625</v>
+        <v>2389.96484375</v>
       </c>
       <c r="E78" t="n">
         <v>2952.449951171875</v>
@@ -2936,10 +2936,10 @@
         <v>57.13000106811523</v>
       </c>
       <c r="H78" t="n">
-        <v>378.5000915527344</v>
+        <v>378.5000610351562</v>
       </c>
       <c r="I78" t="n">
-        <v>2558.7509765625</v>
+        <v>2558.75048828125</v>
       </c>
       <c r="J78" t="n">
         <v>206.3500061035156</v>
@@ -2950,7 +2950,7 @@
         <v>44678</v>
       </c>
       <c r="B79" t="n">
-        <v>2308.576171875</v>
+        <v>2308.575927734375</v>
       </c>
       <c r="C79" t="n">
         <v>2712.199951171875</v>
@@ -2971,7 +2971,7 @@
         <v>377.9104309082031</v>
       </c>
       <c r="I79" t="n">
-        <v>2499.337890625</v>
+        <v>2499.337646484375</v>
       </c>
       <c r="J79" t="n">
         <v>200.8999938964844</v>
@@ -2988,22 +2988,22 @@
         <v>2796.64990234375</v>
       </c>
       <c r="D80" t="n">
-        <v>2373.252197265625</v>
+        <v>2373.25244140625</v>
       </c>
       <c r="E80" t="n">
         <v>2912.199951171875</v>
       </c>
       <c r="F80" t="n">
-        <v>863.516845703125</v>
+        <v>863.5169067382812</v>
       </c>
       <c r="G80" t="n">
         <v>56.84999847412109</v>
       </c>
       <c r="H80" t="n">
-        <v>376.731201171875</v>
+        <v>376.7311706542969</v>
       </c>
       <c r="I80" t="n">
-        <v>2558.850830078125</v>
+        <v>2558.8505859375</v>
       </c>
       <c r="J80" t="n">
         <v>199.8999938964844</v>
@@ -3014,7 +3014,7 @@
         <v>44680</v>
       </c>
       <c r="B81" t="n">
-        <v>2287.9453125</v>
+        <v>2287.945556640625</v>
       </c>
       <c r="C81" t="n">
         <v>2789.5</v>
@@ -3067,7 +3067,7 @@
         <v>371.6209411621094</v>
       </c>
       <c r="I82" t="n">
-        <v>2484.559326171875</v>
+        <v>2484.55908203125</v>
       </c>
       <c r="J82" t="n">
         <v>186.3999938964844</v>
@@ -3078,13 +3078,13 @@
         <v>44685</v>
       </c>
       <c r="B83" t="n">
-        <v>2259.652099609375</v>
+        <v>2259.65234375</v>
       </c>
       <c r="C83" t="n">
         <v>2783.300048828125</v>
       </c>
       <c r="D83" t="n">
-        <v>2248.7802734375</v>
+        <v>2248.780029296875</v>
       </c>
       <c r="E83" t="n">
         <v>2671.35009765625</v>
@@ -3099,7 +3099,7 @@
         <v>361.7444763183594</v>
       </c>
       <c r="I83" t="n">
-        <v>2443.4697265625</v>
+        <v>2443.469482421875</v>
       </c>
       <c r="J83" t="n">
         <v>180.25</v>
@@ -3116,19 +3116,19 @@
         <v>2801.64990234375</v>
       </c>
       <c r="D84" t="n">
-        <v>2250.376708984375</v>
+        <v>2250.376220703125</v>
       </c>
       <c r="E84" t="n">
         <v>2845.89990234375</v>
       </c>
       <c r="F84" t="n">
-        <v>789.78076171875</v>
+        <v>789.7807006835938</v>
       </c>
       <c r="G84" t="n">
         <v>55.63000106811523</v>
       </c>
       <c r="H84" t="n">
-        <v>360.024658203125</v>
+        <v>360.0246887207031</v>
       </c>
       <c r="I84" t="n">
         <v>2446.91455078125</v>
@@ -3148,13 +3148,13 @@
         <v>2816.5</v>
       </c>
       <c r="D85" t="n">
-        <v>2242.693603515625</v>
+        <v>2242.693359375</v>
       </c>
       <c r="E85" t="n">
         <v>2874.800048828125</v>
       </c>
       <c r="F85" t="n">
-        <v>789.8294067382812</v>
+        <v>789.8292846679688</v>
       </c>
       <c r="G85" t="n">
         <v>58.40999984741211</v>
@@ -3163,7 +3163,7 @@
         <v>359.091064453125</v>
       </c>
       <c r="I85" t="n">
-        <v>2434.08349609375</v>
+        <v>2434.083251953125</v>
       </c>
       <c r="J85" t="n">
         <v>174.3500061035156</v>
@@ -3174,7 +3174,7 @@
         <v>44690</v>
       </c>
       <c r="B86" t="n">
-        <v>2193.6337890625</v>
+        <v>2193.633544921875</v>
       </c>
       <c r="C86" t="n">
         <v>2703.449951171875</v>
@@ -3186,13 +3186,13 @@
         <v>2706.39990234375</v>
       </c>
       <c r="F86" t="n">
-        <v>771.5291137695312</v>
+        <v>771.5291748046875</v>
       </c>
       <c r="G86" t="n">
         <v>56.31999969482422</v>
       </c>
       <c r="H86" t="n">
-        <v>360.4177856445312</v>
+        <v>360.4177551269531</v>
       </c>
       <c r="I86" t="n">
         <v>2371.774658203125</v>
@@ -3206,19 +3206,19 @@
         <v>44691</v>
       </c>
       <c r="B87" t="n">
-        <v>2159.88818359375</v>
+        <v>2159.8876953125</v>
       </c>
       <c r="C87" t="n">
         <v>2482.550048828125</v>
       </c>
       <c r="D87" t="n">
-        <v>2104.801513671875</v>
+        <v>2104.80126953125</v>
       </c>
       <c r="E87" t="n">
         <v>2486.699951171875</v>
       </c>
       <c r="F87" t="n">
-        <v>748.6539916992188</v>
+        <v>748.6539306640625</v>
       </c>
       <c r="G87" t="n">
         <v>53.5099983215332</v>
@@ -3227,7 +3227,7 @@
         <v>352.0154418945312</v>
       </c>
       <c r="I87" t="n">
-        <v>2357.19580078125</v>
+        <v>2357.196044921875</v>
       </c>
       <c r="J87" t="n">
         <v>166.1499938964844</v>
@@ -3244,7 +3244,7 @@
         <v>2296</v>
       </c>
       <c r="D88" t="n">
-        <v>2114.57958984375</v>
+        <v>2114.579345703125</v>
       </c>
       <c r="E88" t="n">
         <v>2648.050048828125</v>
@@ -3259,7 +3259,7 @@
         <v>352.8507080078125</v>
       </c>
       <c r="I88" t="n">
-        <v>2351.60400390625</v>
+        <v>2351.604248046875</v>
       </c>
       <c r="J88" t="n">
         <v>157.9499969482422</v>
@@ -3276,7 +3276,7 @@
         <v>2187.050048828125</v>
       </c>
       <c r="D89" t="n">
-        <v>2040.64453125</v>
+        <v>2040.644653320312</v>
       </c>
       <c r="E89" t="n">
         <v>2436.800048828125</v>
@@ -3291,7 +3291,7 @@
         <v>367.1003723144531</v>
       </c>
       <c r="I89" t="n">
-        <v>2290.743408203125</v>
+        <v>2290.74365234375</v>
       </c>
       <c r="J89" t="n">
         <v>150.3500061035156</v>
@@ -3314,7 +3314,7 @@
         <v>2171.550048828125</v>
       </c>
       <c r="F90" t="n">
-        <v>687.134033203125</v>
+        <v>687.1340942382812</v>
       </c>
       <c r="G90" t="n">
         <v>50.93000030517578</v>
@@ -3334,7 +3334,7 @@
         <v>44697</v>
       </c>
       <c r="B91" t="n">
-        <v>2157.578857421875</v>
+        <v>2157.5791015625</v>
       </c>
       <c r="C91" t="n">
         <v>2249.89990234375</v>
@@ -3346,16 +3346,16 @@
         <v>2281.699951171875</v>
       </c>
       <c r="F91" t="n">
-        <v>693.5586547851562</v>
+        <v>693.55859375</v>
       </c>
       <c r="G91" t="n">
         <v>53.47000122070312</v>
       </c>
       <c r="H91" t="n">
-        <v>361.6461791992188</v>
+        <v>361.6462097167969</v>
       </c>
       <c r="I91" t="n">
-        <v>2385.054931640625</v>
+        <v>2385.05517578125</v>
       </c>
       <c r="J91" t="n">
         <v>165.3500061035156</v>
@@ -3372,7 +3372,7 @@
         <v>2333.39990234375</v>
       </c>
       <c r="D92" t="n">
-        <v>2179.98388671875</v>
+        <v>2179.9833984375</v>
       </c>
       <c r="E92" t="n">
         <v>2285.800048828125</v>
@@ -3404,13 +3404,13 @@
         <v>2316</v>
       </c>
       <c r="D93" t="n">
-        <v>2176.2421875</v>
+        <v>2176.241943359375</v>
       </c>
       <c r="E93" t="n">
         <v>2396.10009765625</v>
       </c>
       <c r="F93" t="n">
-        <v>739.60107421875</v>
+        <v>739.6011352539062</v>
       </c>
       <c r="G93" t="n">
         <v>58.93999862670898</v>
@@ -3419,7 +3419,7 @@
         <v>354.8653259277344</v>
       </c>
       <c r="I93" t="n">
-        <v>2482.06298828125</v>
+        <v>2482.062744140625</v>
       </c>
       <c r="J93" t="n">
         <v>176.1999969482422</v>
@@ -3462,19 +3462,19 @@
         <v>44701</v>
       </c>
       <c r="B95" t="n">
-        <v>2200.01904296875</v>
+        <v>2200.019287109375</v>
       </c>
       <c r="C95" t="n">
         <v>2310.949951171875</v>
       </c>
       <c r="D95" t="n">
-        <v>2214.606201171875</v>
+        <v>2214.6064453125</v>
       </c>
       <c r="E95" t="n">
         <v>2273.64990234375</v>
       </c>
       <c r="F95" t="n">
-        <v>747.1451416015625</v>
+        <v>747.1450805664062</v>
       </c>
       <c r="G95" t="n">
         <v>62.45000076293945</v>
@@ -3483,7 +3483,7 @@
         <v>356.7325134277344</v>
       </c>
       <c r="I95" t="n">
-        <v>2376.867431640625</v>
+        <v>2376.86767578125</v>
       </c>
       <c r="J95" t="n">
         <v>168.3999938964844</v>
@@ -3500,13 +3500,13 @@
         <v>2199.199951171875</v>
       </c>
       <c r="D96" t="n">
-        <v>2165.8154296875</v>
+        <v>2165.81494140625</v>
       </c>
       <c r="E96" t="n">
         <v>2248.35009765625</v>
       </c>
       <c r="F96" t="n">
-        <v>733.5172729492188</v>
+        <v>733.517333984375</v>
       </c>
       <c r="G96" t="n">
         <v>65.56999969482422</v>
@@ -3526,19 +3526,19 @@
         <v>44705</v>
       </c>
       <c r="B97" t="n">
-        <v>2172.069580078125</v>
+        <v>2172.06982421875</v>
       </c>
       <c r="C97" t="n">
         <v>2196.5</v>
       </c>
       <c r="D97" t="n">
-        <v>2155.38818359375</v>
+        <v>2155.388427734375</v>
       </c>
       <c r="E97" t="n">
         <v>2136.300048828125</v>
       </c>
       <c r="F97" t="n">
-        <v>732.1544799804688</v>
+        <v>732.154541015625</v>
       </c>
       <c r="G97" t="n">
         <v>62.29999923706055</v>
@@ -3547,7 +3547,7 @@
         <v>355.2092895507812</v>
       </c>
       <c r="I97" t="n">
-        <v>2324.84326171875</v>
+        <v>2324.843505859375</v>
       </c>
       <c r="J97" t="n">
         <v>159.0500030517578</v>
@@ -3558,7 +3558,7 @@
         <v>44706</v>
       </c>
       <c r="B98" t="n">
-        <v>2147.65673828125</v>
+        <v>2147.656494140625</v>
       </c>
       <c r="C98" t="n">
         <v>2087.949951171875</v>
@@ -3570,7 +3570,7 @@
         <v>2187.35009765625</v>
       </c>
       <c r="F98" t="n">
-        <v>689.0808715820312</v>
+        <v>689.080810546875</v>
       </c>
       <c r="G98" t="n">
         <v>59.86999893188477</v>
@@ -3579,7 +3579,7 @@
         <v>355.4549865722656</v>
       </c>
       <c r="I98" t="n">
-        <v>2213.7060546875</v>
+        <v>2213.705810546875</v>
       </c>
       <c r="J98" t="n">
         <v>155.3500061035156</v>
@@ -3596,13 +3596,13 @@
         <v>2148.10009765625</v>
       </c>
       <c r="D99" t="n">
-        <v>2041.841918945312</v>
+        <v>2041.842041015625</v>
       </c>
       <c r="E99" t="n">
         <v>2164</v>
       </c>
       <c r="F99" t="n">
-        <v>682.8509521484375</v>
+        <v>682.8510131835938</v>
       </c>
       <c r="G99" t="n">
         <v>62.86000061035156</v>
@@ -3622,28 +3622,28 @@
         <v>44708</v>
       </c>
       <c r="B100" t="n">
-        <v>2159.396484375</v>
+        <v>2159.396728515625</v>
       </c>
       <c r="C100" t="n">
         <v>2186.25</v>
       </c>
       <c r="D100" t="n">
-        <v>2075.5166015625</v>
+        <v>2075.516845703125</v>
       </c>
       <c r="E100" t="n">
         <v>2166.449951171875</v>
       </c>
       <c r="F100" t="n">
-        <v>684.4085083007812</v>
+        <v>684.408447265625</v>
       </c>
       <c r="G100" t="n">
         <v>65.62000274658203</v>
       </c>
       <c r="H100" t="n">
-        <v>359.9755249023438</v>
+        <v>359.9755554199219</v>
       </c>
       <c r="I100" t="n">
-        <v>2452.85546875</v>
+        <v>2452.855712890625</v>
       </c>
       <c r="J100" t="n">
         <v>154.6999969482422</v>
@@ -3654,7 +3654,7 @@
         <v>44711</v>
       </c>
       <c r="B101" t="n">
-        <v>2169.515625</v>
+        <v>2169.515380859375</v>
       </c>
       <c r="C101" t="n">
         <v>2162</v>
@@ -3666,16 +3666,16 @@
         <v>2151.64990234375</v>
       </c>
       <c r="F101" t="n">
-        <v>715.1683349609375</v>
+        <v>715.1683959960938</v>
       </c>
       <c r="G101" t="n">
         <v>68.05000305175781</v>
       </c>
       <c r="H101" t="n">
-        <v>365.1348571777344</v>
+        <v>365.1348876953125</v>
       </c>
       <c r="I101" t="n">
-        <v>2585.711181640625</v>
+        <v>2585.71142578125</v>
       </c>
       <c r="J101" t="n">
         <v>162.3999938964844</v>
@@ -3686,13 +3686,13 @@
         <v>44712</v>
       </c>
       <c r="B102" t="n">
-        <v>2159.740234375</v>
+        <v>2159.740478515625</v>
       </c>
       <c r="C102" t="n">
         <v>2055</v>
       </c>
       <c r="D102" t="n">
-        <v>2162.72216796875</v>
+        <v>2162.721923828125</v>
       </c>
       <c r="E102" t="n">
         <v>1888.949951171875</v>
@@ -3724,7 +3724,7 @@
         <v>1957.900024414062</v>
       </c>
       <c r="D103" t="n">
-        <v>2146.109130859375</v>
+        <v>2146.109375</v>
       </c>
       <c r="E103" t="n">
         <v>1848.400024414062</v>
@@ -3739,7 +3739,7 @@
         <v>365.2331848144531</v>
       </c>
       <c r="I103" t="n">
-        <v>2322.496826171875</v>
+        <v>2322.49658203125</v>
       </c>
       <c r="J103" t="n">
         <v>179</v>
@@ -3768,7 +3768,7 @@
         <v>59.06999969482422</v>
       </c>
       <c r="H104" t="n">
-        <v>367.0512390136719</v>
+        <v>367.0512084960938</v>
       </c>
       <c r="I104" t="n">
         <v>2442.271484375</v>
@@ -3794,13 +3794,13 @@
         <v>1855.900024414062</v>
       </c>
       <c r="F105" t="n">
-        <v>720.230224609375</v>
+        <v>720.2301635742188</v>
       </c>
       <c r="G105" t="n">
         <v>56.81999969482422</v>
       </c>
       <c r="H105" t="n">
-        <v>360.565185546875</v>
+        <v>360.5651550292969</v>
       </c>
       <c r="I105" t="n">
         <v>2386.952392578125</v>
@@ -3814,13 +3814,13 @@
         <v>44718</v>
       </c>
       <c r="B106" t="n">
-        <v>2100.6484375</v>
+        <v>2100.64794921875</v>
       </c>
       <c r="C106" t="n">
         <v>2017.099975585938</v>
       </c>
       <c r="D106" t="n">
-        <v>2220.09423828125</v>
+        <v>2220.093994140625</v>
       </c>
       <c r="E106" t="n">
         <v>1802.349975585938</v>
@@ -3832,7 +3832,7 @@
         <v>59.65999984741211</v>
       </c>
       <c r="H106" t="n">
-        <v>358.5997314453125</v>
+        <v>358.5997009277344</v>
       </c>
       <c r="I106" t="n">
         <v>2476.47119140625</v>
@@ -3852,13 +3852,13 @@
         <v>2046</v>
       </c>
       <c r="D107" t="n">
-        <v>2222.5888671875</v>
+        <v>2222.58837890625</v>
       </c>
       <c r="E107" t="n">
         <v>1829.25</v>
       </c>
       <c r="F107" t="n">
-        <v>715.0224609375</v>
+        <v>715.0223999023438</v>
       </c>
       <c r="G107" t="n">
         <v>58.27999877929688</v>
@@ -3867,7 +3867,7 @@
         <v>357.0764770507812</v>
       </c>
       <c r="I107" t="n">
-        <v>2495.293212890625</v>
+        <v>2495.29345703125</v>
       </c>
       <c r="J107" t="n">
         <v>206.5</v>
@@ -3878,13 +3878,13 @@
         <v>44720</v>
       </c>
       <c r="B108" t="n">
-        <v>2097.94677734375</v>
+        <v>2097.946533203125</v>
       </c>
       <c r="C108" t="n">
         <v>2091.89990234375</v>
       </c>
       <c r="D108" t="n">
-        <v>2172.350830078125</v>
+        <v>2172.3505859375</v>
       </c>
       <c r="E108" t="n">
         <v>1801.900024414062</v>
@@ -3899,7 +3899,7 @@
         <v>356.7816467285156</v>
       </c>
       <c r="I108" t="n">
-        <v>2443.76904296875</v>
+        <v>2443.769287109375</v>
       </c>
       <c r="J108" t="n">
         <v>210.6999969482422</v>
@@ -3922,7 +3922,7 @@
         <v>1812.650024414062</v>
       </c>
       <c r="F109" t="n">
-        <v>715.9472045898438</v>
+        <v>715.9471435546875</v>
       </c>
       <c r="G109" t="n">
         <v>57.54999923706055</v>
@@ -3942,7 +3942,7 @@
         <v>44722</v>
       </c>
       <c r="B110" t="n">
-        <v>2097.84814453125</v>
+        <v>2097.847900390625</v>
       </c>
       <c r="C110" t="n">
         <v>2051.89990234375</v>
@@ -3960,10 +3960,10 @@
         <v>56.02000045776367</v>
       </c>
       <c r="H110" t="n">
-        <v>358.8453674316406</v>
+        <v>358.8453979492188</v>
       </c>
       <c r="I110" t="n">
-        <v>2394.791015625</v>
+        <v>2394.790771484375</v>
       </c>
       <c r="J110" t="n">
         <v>199.3000030517578</v>
@@ -3995,7 +3995,7 @@
         <v>356.4377136230469</v>
       </c>
       <c r="I111" t="n">
-        <v>2334.129638671875</v>
+        <v>2334.1298828125</v>
       </c>
       <c r="J111" t="n">
         <v>180</v>
@@ -4006,19 +4006,19 @@
         <v>44726</v>
       </c>
       <c r="B112" t="n">
-        <v>2078.887939453125</v>
+        <v>2078.8876953125</v>
       </c>
       <c r="C112" t="n">
         <v>2057.5</v>
       </c>
       <c r="D112" t="n">
-        <v>2191.5576171875</v>
+        <v>2191.557861328125</v>
       </c>
       <c r="E112" t="n">
         <v>1788.75</v>
       </c>
       <c r="F112" t="n">
-        <v>685.9659423828125</v>
+        <v>685.9658813476562</v>
       </c>
       <c r="G112" t="n">
         <v>53.33000183105469</v>
@@ -4044,7 +4044,7 @@
         <v>2057.300048828125</v>
       </c>
       <c r="D113" t="n">
-        <v>2179.734130859375</v>
+        <v>2179.734375</v>
       </c>
       <c r="E113" t="n">
         <v>1757.849975585938</v>
@@ -4056,7 +4056,7 @@
         <v>54.40999984741211</v>
       </c>
       <c r="H113" t="n">
-        <v>355.7006530761719</v>
+        <v>355.70068359375</v>
       </c>
       <c r="I113" t="n">
         <v>2348.359130859375</v>
@@ -4070,7 +4070,7 @@
         <v>44728</v>
       </c>
       <c r="B114" t="n">
-        <v>2047.597900390625</v>
+        <v>2047.597778320312</v>
       </c>
       <c r="C114" t="n">
         <v>2124.64990234375</v>
@@ -4108,7 +4108,7 @@
         <v>2032.599975585938</v>
       </c>
       <c r="D115" t="n">
-        <v>2091.132080078125</v>
+        <v>2091.1318359375</v>
       </c>
       <c r="E115" t="n">
         <v>1711.25</v>
@@ -4120,7 +4120,7 @@
         <v>52.2599983215332</v>
       </c>
       <c r="H115" t="n">
-        <v>351.1800842285156</v>
+        <v>351.1800537109375</v>
       </c>
       <c r="I115" t="n">
         <v>2145.905517578125</v>
@@ -4134,7 +4134,7 @@
         <v>44732</v>
       </c>
       <c r="B116" t="n">
-        <v>2024.167114257812</v>
+        <v>2024.1669921875</v>
       </c>
       <c r="C116" t="n">
         <v>2060.25</v>
@@ -4146,16 +4146,16 @@
         <v>1743.650024414062</v>
       </c>
       <c r="F116" t="n">
-        <v>645.5205078125</v>
+        <v>645.5205688476562</v>
       </c>
       <c r="G116" t="n">
         <v>49.65000152587891</v>
       </c>
       <c r="H116" t="n">
-        <v>351.1309204101562</v>
+        <v>351.1308898925781</v>
       </c>
       <c r="I116" t="n">
-        <v>1986.289428710938</v>
+        <v>1986.289306640625</v>
       </c>
       <c r="J116" t="n">
         <v>162.25</v>
@@ -4187,7 +4187,7 @@
         <v>352.7032775878906</v>
       </c>
       <c r="I117" t="n">
-        <v>2379.413330078125</v>
+        <v>2379.41357421875</v>
       </c>
       <c r="J117" t="n">
         <v>170.75</v>
@@ -4198,7 +4198,7 @@
         <v>44734</v>
       </c>
       <c r="B118" t="n">
-        <v>2026.03369140625</v>
+        <v>2026.033813476562</v>
       </c>
       <c r="C118" t="n">
         <v>2122.35009765625</v>
@@ -4219,7 +4219,7 @@
         <v>351.7696838378906</v>
       </c>
       <c r="I118" t="n">
-        <v>2267.4775390625</v>
+        <v>2267.477294921875</v>
       </c>
       <c r="J118" t="n">
         <v>172.3500061035156</v>
@@ -4230,13 +4230,13 @@
         <v>44735</v>
       </c>
       <c r="B119" t="n">
-        <v>2053.639892578125</v>
+        <v>2053.639404296875</v>
       </c>
       <c r="C119" t="n">
         <v>2105</v>
       </c>
       <c r="D119" t="n">
-        <v>2105.6494140625</v>
+        <v>2105.649658203125</v>
       </c>
       <c r="E119" t="n">
         <v>1796.75</v>
@@ -4248,10 +4248,10 @@
         <v>50.52000045776367</v>
       </c>
       <c r="H119" t="n">
-        <v>352.75244140625</v>
+        <v>352.7524719238281</v>
       </c>
       <c r="I119" t="n">
-        <v>2261.336181640625</v>
+        <v>2261.33642578125</v>
       </c>
       <c r="J119" t="n">
         <v>173</v>
@@ -4268,7 +4268,7 @@
         <v>2152.10009765625</v>
       </c>
       <c r="D120" t="n">
-        <v>2156.635498046875</v>
+        <v>2156.6357421875</v>
       </c>
       <c r="E120" t="n">
         <v>1857.599975585938</v>
@@ -4294,7 +4294,7 @@
         <v>44739</v>
       </c>
       <c r="B121" t="n">
-        <v>2078.642333984375</v>
+        <v>2078.641845703125</v>
       </c>
       <c r="C121" t="n">
         <v>2140.550048828125</v>
@@ -4306,16 +4306,16 @@
         <v>1917.650024414062</v>
       </c>
       <c r="F121" t="n">
-        <v>669.4664916992188</v>
+        <v>669.466552734375</v>
       </c>
       <c r="G121" t="n">
         <v>54.58000183105469</v>
       </c>
       <c r="H121" t="n">
-        <v>358.8453674316406</v>
+        <v>358.8453979492188</v>
       </c>
       <c r="I121" t="n">
-        <v>2286.44970703125</v>
+        <v>2286.449462890625</v>
       </c>
       <c r="J121" t="n">
         <v>175.75</v>
@@ -4326,28 +4326,28 @@
         <v>44740</v>
       </c>
       <c r="B122" t="n">
-        <v>2090.578369140625</v>
+        <v>2090.57861328125</v>
       </c>
       <c r="C122" t="n">
         <v>2163.39990234375</v>
       </c>
       <c r="D122" t="n">
-        <v>2199.689453125</v>
+        <v>2199.689697265625</v>
       </c>
       <c r="E122" t="n">
         <v>1909.849975585938</v>
       </c>
       <c r="F122" t="n">
-        <v>660.0243530273438</v>
+        <v>660.0244140625</v>
       </c>
       <c r="G122" t="n">
         <v>54.04999923706055</v>
       </c>
       <c r="H122" t="n">
-        <v>360.1229248046875</v>
+        <v>360.1229553222656</v>
       </c>
       <c r="I122" t="n">
-        <v>2390.896728515625</v>
+        <v>2390.896240234375</v>
       </c>
       <c r="J122" t="n">
         <v>178.3500061035156</v>
@@ -4358,13 +4358,13 @@
         <v>44741</v>
       </c>
       <c r="B123" t="n">
-        <v>2117.349365234375</v>
+        <v>2117.34912109375</v>
       </c>
       <c r="C123" t="n">
         <v>2347.89990234375</v>
       </c>
       <c r="D123" t="n">
-        <v>2215.155029296875</v>
+        <v>2215.1552734375</v>
       </c>
       <c r="E123" t="n">
         <v>1901.699951171875</v>
@@ -4379,7 +4379,7 @@
         <v>359.1893615722656</v>
       </c>
       <c r="I123" t="n">
-        <v>2344.264892578125</v>
+        <v>2344.2646484375</v>
       </c>
       <c r="J123" t="n">
         <v>176.8999938964844</v>
@@ -4428,7 +4428,7 @@
         <v>2400.64990234375</v>
       </c>
       <c r="D125" t="n">
-        <v>2227.228271484375</v>
+        <v>2227.22802734375</v>
       </c>
       <c r="E125" t="n">
         <v>1963.650024414062</v>
@@ -4440,7 +4440,7 @@
         <v>52.65000152587891</v>
       </c>
       <c r="H125" t="n">
-        <v>361.2039184570312</v>
+        <v>361.2039489746094</v>
       </c>
       <c r="I125" t="n">
         <v>2385.504150390625</v>
@@ -4454,28 +4454,28 @@
         <v>44746</v>
       </c>
       <c r="B126" t="n">
-        <v>2126.53466796875</v>
+        <v>2126.534912109375</v>
       </c>
       <c r="C126" t="n">
         <v>2423.10009765625</v>
       </c>
       <c r="D126" t="n">
-        <v>2256.812255859375</v>
+        <v>2256.81201171875</v>
       </c>
       <c r="E126" t="n">
         <v>1883.599975585938</v>
       </c>
       <c r="F126" t="n">
-        <v>663.8695068359375</v>
+        <v>663.869384765625</v>
       </c>
       <c r="G126" t="n">
         <v>52.34000015258789</v>
       </c>
       <c r="H126" t="n">
-        <v>362.1867065429688</v>
+        <v>362.1866760253906</v>
       </c>
       <c r="I126" t="n">
-        <v>2393.29296875</v>
+        <v>2393.293212890625</v>
       </c>
       <c r="J126" t="n">
         <v>168.8000030517578</v>
@@ -4492,7 +4492,7 @@
         <v>2476.300048828125</v>
       </c>
       <c r="D127" t="n">
-        <v>2241.446533203125</v>
+        <v>2241.4462890625</v>
       </c>
       <c r="E127" t="n">
         <v>1876.400024414062</v>
@@ -4539,7 +4539,7 @@
         <v>361.8918762207031</v>
       </c>
       <c r="I128" t="n">
-        <v>2471.72802734375</v>
+        <v>2471.728271484375</v>
       </c>
       <c r="J128" t="n">
         <v>164.8500061035156</v>
@@ -4550,7 +4550,7 @@
         <v>44749</v>
       </c>
       <c r="B129" t="n">
-        <v>2130.218994140625</v>
+        <v>2130.21875</v>
       </c>
       <c r="C129" t="n">
         <v>2466.10009765625</v>
@@ -4571,7 +4571,7 @@
         <v>360.6143493652344</v>
       </c>
       <c r="I129" t="n">
-        <v>2482.113037109375</v>
+        <v>2482.11279296875</v>
       </c>
       <c r="J129" t="n">
         <v>167.4499969482422</v>
@@ -4582,13 +4582,13 @@
         <v>44750</v>
       </c>
       <c r="B130" t="n">
-        <v>2131.201171875</v>
+        <v>2131.201416015625</v>
       </c>
       <c r="C130" t="n">
         <v>2545.89990234375</v>
       </c>
       <c r="D130" t="n">
-        <v>2287.942626953125</v>
+        <v>2287.9423828125</v>
       </c>
       <c r="E130" t="n">
         <v>1921</v>
@@ -4600,10 +4600,10 @@
         <v>54.31000137329102</v>
       </c>
       <c r="H130" t="n">
-        <v>362.0884094238281</v>
+        <v>362.0884399414062</v>
       </c>
       <c r="I130" t="n">
-        <v>2537.08251953125</v>
+        <v>2537.082275390625</v>
       </c>
       <c r="J130" t="n">
         <v>190.5</v>
@@ -4614,13 +4614,13 @@
         <v>44753</v>
       </c>
       <c r="B131" t="n">
-        <v>2145.888427734375</v>
+        <v>2145.88818359375</v>
       </c>
       <c r="C131" t="n">
         <v>2690.949951171875</v>
       </c>
       <c r="D131" t="n">
-        <v>2367.9638671875</v>
+        <v>2367.964111328125</v>
       </c>
       <c r="E131" t="n">
         <v>2207.35009765625</v>
@@ -4664,7 +4664,7 @@
         <v>58.54999923706055</v>
       </c>
       <c r="H132" t="n">
-        <v>364.4961242675781</v>
+        <v>364.49609375</v>
       </c>
       <c r="I132" t="n">
         <v>2793.45703125</v>
@@ -4684,7 +4684,7 @@
         <v>2730.800048828125</v>
       </c>
       <c r="D133" t="n">
-        <v>2348.2578125</v>
+        <v>2348.258056640625</v>
       </c>
       <c r="E133" t="n">
         <v>2104.75</v>
@@ -4696,10 +4696,10 @@
         <v>57.33000183105469</v>
       </c>
       <c r="H133" t="n">
-        <v>364.7909545898438</v>
+        <v>364.7909240722656</v>
       </c>
       <c r="I133" t="n">
-        <v>2668.1904296875</v>
+        <v>2668.18994140625</v>
       </c>
       <c r="J133" t="n">
         <v>201.6000061035156</v>
@@ -4710,7 +4710,7 @@
         <v>44756</v>
       </c>
       <c r="B134" t="n">
-        <v>2122.310546875</v>
+        <v>2122.310302734375</v>
       </c>
       <c r="C134" t="n">
         <v>2889.14990234375</v>
@@ -4722,7 +4722,7 @@
         <v>2087</v>
       </c>
       <c r="F134" t="n">
-        <v>710.076171875</v>
+        <v>710.0762329101562</v>
       </c>
       <c r="G134" t="n">
         <v>56.7400016784668</v>
@@ -4748,7 +4748,7 @@
         <v>2889.35009765625</v>
       </c>
       <c r="D135" t="n">
-        <v>2400.8818359375</v>
+        <v>2400.881591796875</v>
       </c>
       <c r="E135" t="n">
         <v>2072.64990234375</v>
@@ -4774,19 +4774,19 @@
         <v>44760</v>
       </c>
       <c r="B136" t="n">
-        <v>2135.76953125</v>
+        <v>2135.769287109375</v>
       </c>
       <c r="C136" t="n">
         <v>2980.5</v>
       </c>
       <c r="D136" t="n">
-        <v>2419.198486328125</v>
+        <v>2419.1982421875</v>
       </c>
       <c r="E136" t="n">
         <v>2093.25</v>
       </c>
       <c r="F136" t="n">
-        <v>725.0726318359375</v>
+        <v>725.0725708007812</v>
       </c>
       <c r="G136" t="n">
         <v>57.97000122070312</v>
@@ -4806,7 +4806,7 @@
         <v>44761</v>
       </c>
       <c r="B137" t="n">
-        <v>2130.6611328125</v>
+        <v>2130.660888671875</v>
       </c>
       <c r="C137" t="n">
         <v>3029.75</v>
@@ -4824,7 +4824,7 @@
         <v>58.66999816894531</v>
       </c>
       <c r="H137" t="n">
-        <v>364.5452880859375</v>
+        <v>364.5452575683594</v>
       </c>
       <c r="I137" t="n">
         <v>2828.470703125</v>
@@ -4838,13 +4838,13 @@
         <v>44762</v>
       </c>
       <c r="B138" t="n">
-        <v>2120.93505859375</v>
+        <v>2120.934814453125</v>
       </c>
       <c r="C138" t="n">
         <v>3018.75</v>
       </c>
       <c r="D138" t="n">
-        <v>2446.6484375</v>
+        <v>2446.648681640625</v>
       </c>
       <c r="E138" t="n">
         <v>2084.300048828125</v>
@@ -4876,7 +4876,7 @@
         <v>3043.75</v>
       </c>
       <c r="D139" t="n">
-        <v>2490.9677734375</v>
+        <v>2490.968017578125</v>
       </c>
       <c r="E139" t="n">
         <v>2109.75</v>
@@ -4908,7 +4908,7 @@
         <v>2977.449951171875</v>
       </c>
       <c r="D140" t="n">
-        <v>2494.8603515625</v>
+        <v>2494.86083984375</v>
       </c>
       <c r="E140" t="n">
         <v>2120.449951171875</v>
@@ -4940,7 +4940,7 @@
         <v>2969.75</v>
       </c>
       <c r="D141" t="n">
-        <v>2545.9677734375</v>
+        <v>2545.968017578125</v>
       </c>
       <c r="E141" t="n">
         <v>2137.60009765625</v>
@@ -4972,13 +4972,13 @@
         <v>2993.75</v>
       </c>
       <c r="D142" t="n">
-        <v>2555.051025390625</v>
+        <v>2555.05078125</v>
       </c>
       <c r="E142" t="n">
         <v>2103.64990234375</v>
       </c>
       <c r="F142" t="n">
-        <v>734.237060546875</v>
+        <v>734.2371215820312</v>
       </c>
       <c r="G142" t="n">
         <v>59.54000091552734</v>
@@ -5042,7 +5042,7 @@
         <v>2143.949951171875</v>
       </c>
       <c r="F144" t="n">
-        <v>749.33154296875</v>
+        <v>749.3314819335938</v>
       </c>
       <c r="G144" t="n">
         <v>64.38999938964844</v>
@@ -5062,7 +5062,7 @@
         <v>44771</v>
       </c>
       <c r="B145" t="n">
-        <v>2188.230224609375</v>
+        <v>2188.23046875</v>
       </c>
       <c r="C145" t="n">
         <v>3109.60009765625</v>
@@ -5080,7 +5080,7 @@
         <v>62.79000091552734</v>
       </c>
       <c r="H145" t="n">
-        <v>368.3287658691406</v>
+        <v>368.3287353515625</v>
       </c>
       <c r="I145" t="n">
         <v>3122.916748046875</v>
@@ -5112,7 +5112,7 @@
         <v>64.37000274658203</v>
       </c>
       <c r="H146" t="n">
-        <v>368.9184265136719</v>
+        <v>368.9183959960938</v>
       </c>
       <c r="I146" t="n">
         <v>3213.24267578125</v>
@@ -5138,13 +5138,13 @@
         <v>2296.14990234375</v>
       </c>
       <c r="F147" t="n">
-        <v>786.381591796875</v>
+        <v>786.3815307617188</v>
       </c>
       <c r="G147" t="n">
         <v>65.70999908447266</v>
       </c>
       <c r="H147" t="n">
-        <v>372.1122741699219</v>
+        <v>372.1123046875</v>
       </c>
       <c r="I147" t="n">
         <v>3244.400146484375</v>
@@ -5222,7 +5222,7 @@
         <v>44778</v>
       </c>
       <c r="B150" t="n">
-        <v>2215.148681640625</v>
+        <v>2215.14892578125</v>
       </c>
       <c r="C150" t="n">
         <v>3313.550048828125</v>
@@ -5240,7 +5240,7 @@
         <v>66.41000366210938</v>
       </c>
       <c r="H150" t="n">
-        <v>376.043212890625</v>
+        <v>376.0432434082031</v>
       </c>
       <c r="I150" t="n">
         <v>3342.81494140625</v>
@@ -5298,13 +5298,13 @@
         <v>2164.949951171875</v>
       </c>
       <c r="F152" t="n">
-        <v>774.86474609375</v>
+        <v>774.8646850585938</v>
       </c>
       <c r="G152" t="n">
         <v>67.94999694824219</v>
       </c>
       <c r="H152" t="n">
-        <v>373.4880981445312</v>
+        <v>373.4881286621094</v>
       </c>
       <c r="I152" t="n">
         <v>3346.809326171875</v>
@@ -5330,7 +5330,7 @@
         <v>2164.89990234375</v>
       </c>
       <c r="F153" t="n">
-        <v>777.0210571289062</v>
+        <v>777.02099609375</v>
       </c>
       <c r="G153" t="n">
         <v>68.48000335693359</v>
@@ -5362,13 +5362,13 @@
         <v>2176</v>
       </c>
       <c r="F154" t="n">
-        <v>772.7083129882812</v>
+        <v>772.708251953125</v>
       </c>
       <c r="G154" t="n">
         <v>69.02999877929688</v>
       </c>
       <c r="H154" t="n">
-        <v>378.1560974121094</v>
+        <v>378.1561279296875</v>
       </c>
       <c r="I154" t="n">
         <v>3420.7080078125</v>
@@ -5414,13 +5414,13 @@
         <v>44790</v>
       </c>
       <c r="B156" t="n">
-        <v>2243.000244140625</v>
+        <v>2242.999755859375</v>
       </c>
       <c r="C156" t="n">
         <v>3597.64990234375</v>
       </c>
       <c r="D156" t="n">
-        <v>3003.185791015625</v>
+        <v>3003.185546875</v>
       </c>
       <c r="E156" t="n">
         <v>2227.050048828125</v>
@@ -5446,7 +5446,7 @@
         <v>44791</v>
       </c>
       <c r="B157" t="n">
-        <v>2282.001708984375</v>
+        <v>2282.001953125</v>
       </c>
       <c r="C157" t="n">
         <v>3599.550048828125</v>
@@ -5478,13 +5478,13 @@
         <v>44792</v>
       </c>
       <c r="B158" t="n">
-        <v>2309.509765625</v>
+        <v>2309.509521484375</v>
       </c>
       <c r="C158" t="n">
         <v>3635.25</v>
       </c>
       <c r="D158" t="n">
-        <v>3124.51513671875</v>
+        <v>3124.514892578125</v>
       </c>
       <c r="E158" t="n">
         <v>2411.35009765625</v>
@@ -5496,7 +5496,7 @@
         <v>82.38999938964844</v>
       </c>
       <c r="H158" t="n">
-        <v>413.1906433105469</v>
+        <v>413.1906127929688</v>
       </c>
       <c r="I158" t="n">
         <v>3386.25537109375</v>
@@ -5522,7 +5522,7 @@
         <v>2519.75</v>
       </c>
       <c r="F159" t="n">
-        <v>823.57861328125</v>
+        <v>823.5785522460938</v>
       </c>
       <c r="G159" t="n">
         <v>86.5</v>
@@ -5548,7 +5548,7 @@
         <v>3601.89990234375</v>
       </c>
       <c r="D160" t="n">
-        <v>3025.1455078125</v>
+        <v>3025.145751953125</v>
       </c>
       <c r="E160" t="n">
         <v>2412.89990234375</v>
@@ -5560,7 +5560,7 @@
         <v>82.18000030517578</v>
       </c>
       <c r="H160" t="n">
-        <v>398.4496154785156</v>
+        <v>398.4495849609375</v>
       </c>
       <c r="I160" t="n">
         <v>3426.25048828125</v>
@@ -5580,19 +5580,19 @@
         <v>3700.39990234375</v>
       </c>
       <c r="D161" t="n">
-        <v>3128.95703125</v>
+        <v>3128.956787109375</v>
       </c>
       <c r="E161" t="n">
         <v>2358.85009765625</v>
       </c>
       <c r="F161" t="n">
-        <v>819.7069091796875</v>
+        <v>819.7069702148438</v>
       </c>
       <c r="G161" t="n">
         <v>78.08000183105469</v>
       </c>
       <c r="H161" t="n">
-        <v>397.1720581054688</v>
+        <v>397.1720275878906</v>
       </c>
       <c r="I161" t="n">
         <v>3423.10498046875</v>
@@ -5606,7 +5606,7 @@
         <v>44798</v>
       </c>
       <c r="B162" t="n">
-        <v>2244.03125</v>
+        <v>2244.031494140625</v>
       </c>
       <c r="C162" t="n">
         <v>3715.800048828125</v>
@@ -5624,7 +5624,7 @@
         <v>78.69999694824219</v>
       </c>
       <c r="H162" t="n">
-        <v>390.2928466796875</v>
+        <v>390.2928771972656</v>
       </c>
       <c r="I162" t="n">
         <v>3360.59033203125</v>
@@ -5638,13 +5638,13 @@
         <v>44799</v>
       </c>
       <c r="B163" t="n">
-        <v>2245.30859375</v>
+        <v>2245.308837890625</v>
       </c>
       <c r="C163" t="n">
         <v>3751.199951171875</v>
       </c>
       <c r="D163" t="n">
-        <v>3133.84814453125</v>
+        <v>3133.847900390625</v>
       </c>
       <c r="E163" t="n">
         <v>2392.75</v>
@@ -5656,7 +5656,7 @@
         <v>75.09999847412109</v>
       </c>
       <c r="H163" t="n">
-        <v>395.8945007324219</v>
+        <v>395.8944702148438</v>
       </c>
       <c r="I163" t="n">
         <v>3454.9111328125</v>
@@ -5670,13 +5670,13 @@
         <v>44802</v>
       </c>
       <c r="B164" t="n">
-        <v>2248.354248046875</v>
+        <v>2248.3544921875</v>
       </c>
       <c r="C164" t="n">
         <v>3855.550048828125</v>
       </c>
       <c r="D164" t="n">
-        <v>3136.892578125</v>
+        <v>3136.892333984375</v>
       </c>
       <c r="E164" t="n">
         <v>2337.85009765625</v>
@@ -5688,7 +5688,7 @@
         <v>78.84999847412109</v>
       </c>
       <c r="H164" t="n">
-        <v>396.4841003417969</v>
+        <v>396.484130859375</v>
       </c>
       <c r="I164" t="n">
         <v>3532.5546875</v>
@@ -5708,7 +5708,7 @@
         <v>3960.699951171875</v>
       </c>
       <c r="D165" t="n">
-        <v>3188.548583984375</v>
+        <v>3188.548828125</v>
       </c>
       <c r="E165" t="n">
         <v>2436.199951171875</v>
@@ -5740,7 +5740,7 @@
         <v>3880.449951171875</v>
       </c>
       <c r="D166" t="n">
-        <v>3227.3779296875</v>
+        <v>3227.377685546875</v>
       </c>
       <c r="E166" t="n">
         <v>2393.10009765625</v>
@@ -5778,13 +5778,13 @@
         <v>2383.10009765625</v>
       </c>
       <c r="F167" t="n">
-        <v>835.0465087890625</v>
+        <v>835.0464477539062</v>
       </c>
       <c r="G167" t="n">
         <v>80.25</v>
       </c>
       <c r="H167" t="n">
-        <v>408.42431640625</v>
+        <v>408.4243469238281</v>
       </c>
       <c r="I167" t="n">
         <v>3617.8876953125</v>
@@ -5798,7 +5798,7 @@
         <v>44809</v>
       </c>
       <c r="B168" t="n">
-        <v>2247.912109375</v>
+        <v>2247.911865234375</v>
       </c>
       <c r="C168" t="n">
         <v>3881.25</v>
@@ -5816,7 +5816,7 @@
         <v>77.97000122070312</v>
       </c>
       <c r="H168" t="n">
-        <v>410.7337646484375</v>
+        <v>410.7337951660156</v>
       </c>
       <c r="I168" t="n">
         <v>3525.763916015625</v>
@@ -5848,7 +5848,7 @@
         <v>81.55000305175781</v>
       </c>
       <c r="H169" t="n">
-        <v>428.9634704589844</v>
+        <v>428.9635009765625</v>
       </c>
       <c r="I169" t="n">
         <v>3677.8056640625</v>
@@ -5862,7 +5862,7 @@
         <v>44811</v>
       </c>
       <c r="B170" t="n">
-        <v>2363.05126953125</v>
+        <v>2363.051025390625</v>
       </c>
       <c r="C170" t="n">
         <v>3893.10009765625</v>
@@ -5894,7 +5894,7 @@
         <v>44812</v>
       </c>
       <c r="B171" t="n">
-        <v>2378.572998046875</v>
+        <v>2378.5732421875</v>
       </c>
       <c r="C171" t="n">
         <v>3925.949951171875</v>
@@ -5906,13 +5906,13 @@
         <v>2334.050048828125</v>
       </c>
       <c r="F171" t="n">
-        <v>867.4896850585938</v>
+        <v>867.48974609375</v>
       </c>
       <c r="G171" t="n">
         <v>80.37999725341797</v>
       </c>
       <c r="H171" t="n">
-        <v>453.9249267578125</v>
+        <v>453.9248962402344</v>
       </c>
       <c r="I171" t="n">
         <v>3624.927978515625</v>
@@ -5926,13 +5926,13 @@
         <v>44813</v>
       </c>
       <c r="B172" t="n">
-        <v>2324.00048828125</v>
+        <v>2324</v>
       </c>
       <c r="C172" t="n">
         <v>3931.10009765625</v>
       </c>
       <c r="D172" t="n">
-        <v>3444.931884765625</v>
+        <v>3444.93212890625</v>
       </c>
       <c r="E172" t="n">
         <v>2315.89990234375</v>
@@ -5976,7 +5976,7 @@
         <v>79.51999664306641</v>
       </c>
       <c r="H173" t="n">
-        <v>467.4375</v>
+        <v>467.4375305175781</v>
       </c>
       <c r="I173" t="n">
         <v>3630.42041015625</v>
@@ -6002,7 +6002,7 @@
         <v>2335.64990234375</v>
       </c>
       <c r="F174" t="n">
-        <v>929.974853515625</v>
+        <v>929.9747924804688</v>
       </c>
       <c r="G174" t="n">
         <v>78.72000122070312</v>
@@ -6022,13 +6022,13 @@
         <v>44818</v>
       </c>
       <c r="B175" t="n">
-        <v>2694.959716796875</v>
+        <v>2694.9599609375</v>
       </c>
       <c r="C175" t="n">
         <v>3978.14990234375</v>
       </c>
       <c r="D175" t="n">
-        <v>3565.61279296875</v>
+        <v>3565.6123046875</v>
       </c>
       <c r="E175" t="n">
         <v>2293.60009765625</v>
@@ -6060,7 +6060,7 @@
         <v>4105.39990234375</v>
       </c>
       <c r="D176" t="n">
-        <v>3741.8916015625</v>
+        <v>3741.891845703125</v>
       </c>
       <c r="E176" t="n">
         <v>2343.89990234375</v>
@@ -6092,7 +6092,7 @@
         <v>4094.75</v>
       </c>
       <c r="D177" t="n">
-        <v>3695.47607421875</v>
+        <v>3695.476318359375</v>
       </c>
       <c r="E177" t="n">
         <v>2316.60009765625</v>
@@ -6104,7 +6104,7 @@
         <v>77.55000305175781</v>
       </c>
       <c r="H177" t="n">
-        <v>507.7787780761719</v>
+        <v>507.7787475585938</v>
       </c>
       <c r="I177" t="n">
         <v>3523.96630859375</v>
@@ -6118,13 +6118,13 @@
         <v>44823</v>
       </c>
       <c r="B178" t="n">
-        <v>2594.655517578125</v>
+        <v>2594.6552734375</v>
       </c>
       <c r="C178" t="n">
         <v>4029.39990234375</v>
       </c>
       <c r="D178" t="n">
-        <v>3771.787353515625</v>
+        <v>3771.787109375</v>
       </c>
       <c r="E178" t="n">
         <v>2346.35009765625</v>
@@ -6136,7 +6136,7 @@
         <v>78.37000274658203</v>
       </c>
       <c r="H178" t="n">
-        <v>555.1466064453125</v>
+        <v>555.1465454101562</v>
       </c>
       <c r="I178" t="n">
         <v>3615.09130859375</v>
@@ -6150,7 +6150,7 @@
         <v>44824</v>
       </c>
       <c r="B179" t="n">
-        <v>2677.66943359375</v>
+        <v>2677.669677734375</v>
       </c>
       <c r="C179" t="n">
         <v>4021.550048828125</v>
@@ -6162,7 +6162,7 @@
         <v>2399.949951171875</v>
       </c>
       <c r="F179" t="n">
-        <v>950.999267578125</v>
+        <v>950.9992065429688</v>
       </c>
       <c r="G179" t="n">
         <v>79.65000152587891</v>
@@ -6214,19 +6214,19 @@
         <v>44826</v>
       </c>
       <c r="B181" t="n">
-        <v>2510.757080078125</v>
+        <v>2510.75732421875</v>
       </c>
       <c r="C181" t="n">
         <v>3997.89990234375</v>
       </c>
       <c r="D181" t="n">
-        <v>3709.55078125</v>
+        <v>3709.550537109375</v>
       </c>
       <c r="E181" t="n">
         <v>2363.60009765625</v>
       </c>
       <c r="F181" t="n">
-        <v>927.8675537109375</v>
+        <v>927.8674926757812</v>
       </c>
       <c r="G181" t="n">
         <v>79.25</v>
@@ -6264,7 +6264,7 @@
         <v>77.12000274658203</v>
       </c>
       <c r="H182" t="n">
-        <v>530.0377197265625</v>
+        <v>530.0376586914062</v>
       </c>
       <c r="I182" t="n">
         <v>3540.393798828125</v>
@@ -6316,13 +6316,13 @@
         <v>3606.5</v>
       </c>
       <c r="D184" t="n">
-        <v>3552.635986328125</v>
+        <v>3552.63623046875</v>
       </c>
       <c r="E184" t="n">
         <v>2146.300048828125</v>
       </c>
       <c r="F184" t="n">
-        <v>827.4501953125</v>
+        <v>827.4502563476562</v>
       </c>
       <c r="G184" t="n">
         <v>74.51000213623047</v>
@@ -6348,19 +6348,19 @@
         <v>3602.10009765625</v>
       </c>
       <c r="D185" t="n">
-        <v>3542.3046875</v>
+        <v>3542.30517578125</v>
       </c>
       <c r="E185" t="n">
         <v>2051.050048828125</v>
       </c>
       <c r="F185" t="n">
-        <v>810.689453125</v>
+        <v>810.6895141601562</v>
       </c>
       <c r="G185" t="n">
         <v>73.55000305175781</v>
       </c>
       <c r="H185" t="n">
-        <v>491.4161987304688</v>
+        <v>491.416259765625</v>
       </c>
       <c r="I185" t="n">
         <v>3443.3271484375</v>
@@ -6392,7 +6392,7 @@
         <v>73.88999938964844</v>
       </c>
       <c r="H186" t="n">
-        <v>497.6074523925781</v>
+        <v>497.6074829101562</v>
       </c>
       <c r="I186" t="n">
         <v>3367.631103515625</v>
@@ -6406,7 +6406,7 @@
         <v>44834</v>
       </c>
       <c r="B187" t="n">
-        <v>2373.169921875</v>
+        <v>2373.169677734375</v>
       </c>
       <c r="C187" t="n">
         <v>3289.800048828125</v>
@@ -6424,7 +6424,7 @@
         <v>74.69999694824219</v>
       </c>
       <c r="H187" t="n">
-        <v>506.6977233886719</v>
+        <v>506.6976928710938</v>
       </c>
       <c r="I187" t="n">
         <v>3335.275390625</v>
@@ -6438,13 +6438,13 @@
         <v>44837</v>
       </c>
       <c r="B188" t="n">
-        <v>2260.830810546875</v>
+        <v>2260.8310546875</v>
       </c>
       <c r="C188" t="n">
         <v>3123.64990234375</v>
       </c>
       <c r="D188" t="n">
-        <v>3151.566162109375</v>
+        <v>3151.565673828125</v>
       </c>
       <c r="E188" t="n">
         <v>2074.050048828125</v>
@@ -6476,7 +6476,7 @@
         <v>3318.60009765625</v>
       </c>
       <c r="D189" t="n">
-        <v>3231.81982421875</v>
+        <v>3231.819580078125</v>
       </c>
       <c r="E189" t="n">
         <v>2134.199951171875</v>
@@ -6488,7 +6488,7 @@
         <v>70.5</v>
       </c>
       <c r="H189" t="n">
-        <v>483.7017517089844</v>
+        <v>483.7017822265625</v>
       </c>
       <c r="I189" t="n">
         <v>3211.74462890625</v>
@@ -6508,19 +6508,19 @@
         <v>3358.75</v>
       </c>
       <c r="D190" t="n">
-        <v>3279.033935546875</v>
+        <v>3279.0341796875</v>
       </c>
       <c r="E190" t="n">
         <v>2201.699951171875</v>
       </c>
       <c r="F190" t="n">
-        <v>807.7489624023438</v>
+        <v>807.7490234375</v>
       </c>
       <c r="G190" t="n">
         <v>74.01999664306641</v>
       </c>
       <c r="H190" t="n">
-        <v>498.1480102539062</v>
+        <v>498.14794921875</v>
       </c>
       <c r="I190" t="n">
         <v>3303.46923828125</v>
@@ -6534,13 +6534,13 @@
         <v>44841</v>
       </c>
       <c r="B191" t="n">
-        <v>2342.813232421875</v>
+        <v>2342.8134765625</v>
       </c>
       <c r="C191" t="n">
         <v>3278.60009765625</v>
       </c>
       <c r="D191" t="n">
-        <v>3271.647216796875</v>
+        <v>3271.6474609375</v>
       </c>
       <c r="E191" t="n">
         <v>2204.14990234375</v>
@@ -6566,13 +6566,13 @@
         <v>44844</v>
       </c>
       <c r="B192" t="n">
-        <v>2327.5859375</v>
+        <v>2327.585693359375</v>
       </c>
       <c r="C192" t="n">
         <v>3191.449951171875</v>
       </c>
       <c r="D192" t="n">
-        <v>3240.354248046875</v>
+        <v>3240.3544921875</v>
       </c>
       <c r="E192" t="n">
         <v>2155.89990234375</v>
@@ -6598,7 +6598,7 @@
         <v>44845</v>
       </c>
       <c r="B193" t="n">
-        <v>2270.998779296875</v>
+        <v>2270.99853515625</v>
       </c>
       <c r="C193" t="n">
         <v>3154.35009765625</v>
@@ -6610,7 +6610,7 @@
         <v>2128.800048828125</v>
       </c>
       <c r="F193" t="n">
-        <v>781.5297241210938</v>
+        <v>781.52978515625</v>
       </c>
       <c r="G193" t="n">
         <v>71.37000274658203</v>
@@ -6630,13 +6630,13 @@
         <v>44846</v>
       </c>
       <c r="B194" t="n">
-        <v>2276.05810546875</v>
+        <v>2276.058349609375</v>
       </c>
       <c r="C194" t="n">
         <v>3187.949951171875</v>
       </c>
       <c r="D194" t="n">
-        <v>3217.794921875</v>
+        <v>3217.79541015625</v>
       </c>
       <c r="E194" t="n">
         <v>2099.10009765625</v>
@@ -6662,13 +6662,13 @@
         <v>44847</v>
       </c>
       <c r="B195" t="n">
-        <v>2214.2646484375</v>
+        <v>2214.26416015625</v>
       </c>
       <c r="C195" t="n">
         <v>3121.10009765625</v>
       </c>
       <c r="D195" t="n">
-        <v>3227.777099609375</v>
+        <v>3227.77734375</v>
       </c>
       <c r="E195" t="n">
         <v>2083.35009765625</v>
@@ -6694,13 +6694,13 @@
         <v>44848</v>
       </c>
       <c r="B196" t="n">
-        <v>2204.194580078125</v>
+        <v>2204.19482421875</v>
       </c>
       <c r="C196" t="n">
         <v>3035.300048828125</v>
       </c>
       <c r="D196" t="n">
-        <v>3203.6708984375</v>
+        <v>3203.671142578125</v>
       </c>
       <c r="E196" t="n">
         <v>2033.150024414062</v>
@@ -6726,13 +6726,13 @@
         <v>44851</v>
       </c>
       <c r="B197" t="n">
-        <v>2230.1796875</v>
+        <v>2230.179443359375</v>
       </c>
       <c r="C197" t="n">
         <v>3074.35009765625</v>
       </c>
       <c r="D197" t="n">
-        <v>3206.765380859375</v>
+        <v>3206.76513671875</v>
       </c>
       <c r="E197" t="n">
         <v>2154.449951171875</v>
@@ -6744,7 +6744,7 @@
         <v>68.12999725341797</v>
       </c>
       <c r="H197" t="n">
-        <v>511.562255859375</v>
+        <v>511.5621948242188</v>
       </c>
       <c r="I197" t="n">
         <v>3095.054931640625</v>
@@ -6758,13 +6758,13 @@
         <v>44852</v>
       </c>
       <c r="B198" t="n">
-        <v>2180.22412109375</v>
+        <v>2180.2236328125</v>
       </c>
       <c r="C198" t="n">
         <v>3243</v>
       </c>
       <c r="D198" t="n">
-        <v>3278.3349609375</v>
+        <v>3278.335205078125</v>
       </c>
       <c r="E198" t="n">
         <v>2153.75</v>
@@ -6802,13 +6802,13 @@
         <v>2119.800048828125</v>
       </c>
       <c r="F199" t="n">
-        <v>789.0770263671875</v>
+        <v>789.0769653320312</v>
       </c>
       <c r="G199" t="n">
         <v>66.72000122070312</v>
       </c>
       <c r="H199" t="n">
-        <v>501.8823547363281</v>
+        <v>501.8823852539062</v>
       </c>
       <c r="I199" t="n">
         <v>3162.51220703125</v>
@@ -6828,7 +6828,7 @@
         <v>3270.050048828125</v>
       </c>
       <c r="D200" t="n">
-        <v>3351.003173828125</v>
+        <v>3351.0029296875</v>
       </c>
       <c r="E200" t="n">
         <v>2138.89990234375</v>
@@ -6840,7 +6840,7 @@
         <v>67.69000244140625</v>
       </c>
       <c r="H200" t="n">
-        <v>508.761474609375</v>
+        <v>508.7615356445312</v>
       </c>
       <c r="I200" t="n">
         <v>3272.611572265625</v>
@@ -6854,13 +6854,13 @@
         <v>44855</v>
       </c>
       <c r="B201" t="n">
-        <v>2216.86767578125</v>
+        <v>2216.867919921875</v>
       </c>
       <c r="C201" t="n">
         <v>3273.699951171875</v>
       </c>
       <c r="D201" t="n">
-        <v>3305.884765625</v>
+        <v>3305.885009765625</v>
       </c>
       <c r="E201" t="n">
         <v>2105.300048828125</v>
@@ -6872,7 +6872,7 @@
         <v>66.44000244140625</v>
       </c>
       <c r="H201" t="n">
-        <v>503.74951171875</v>
+        <v>503.7495422363281</v>
       </c>
       <c r="I201" t="n">
         <v>3257.2822265625</v>
@@ -6892,7 +6892,7 @@
         <v>3283.949951171875</v>
       </c>
       <c r="D202" t="n">
-        <v>3303.789306640625</v>
+        <v>3303.788818359375</v>
       </c>
       <c r="E202" t="n">
         <v>2121.25</v>
@@ -6904,7 +6904,7 @@
         <v>67.11000061035156</v>
       </c>
       <c r="H202" t="n">
-        <v>507.975341796875</v>
+        <v>507.9753112792969</v>
       </c>
       <c r="I202" t="n">
         <v>3262.82470703125</v>
@@ -6918,7 +6918,7 @@
         <v>44859</v>
       </c>
       <c r="B203" t="n">
-        <v>2207.97705078125</v>
+        <v>2207.977294921875</v>
       </c>
       <c r="C203" t="n">
         <v>3188.449951171875</v>
@@ -6930,7 +6930,7 @@
         <v>2079.89990234375</v>
       </c>
       <c r="F203" t="n">
-        <v>784.47021484375</v>
+        <v>784.4702758789062</v>
       </c>
       <c r="G203" t="n">
         <v>66.47000122070312</v>
@@ -6956,7 +6956,7 @@
         <v>3282.449951171875</v>
       </c>
       <c r="D204" t="n">
-        <v>3318.96142578125</v>
+        <v>3318.961181640625</v>
       </c>
       <c r="E204" t="n">
         <v>2117.60009765625</v>
@@ -6988,7 +6988,7 @@
         <v>3277.949951171875</v>
       </c>
       <c r="D205" t="n">
-        <v>3317.264404296875</v>
+        <v>3317.26416015625</v>
       </c>
       <c r="E205" t="n">
         <v>2098.550048828125</v>
@@ -7000,7 +7000,7 @@
         <v>66.66000366210938</v>
       </c>
       <c r="H205" t="n">
-        <v>511.1200256347656</v>
+        <v>511.1200866699219</v>
       </c>
       <c r="I205" t="n">
         <v>3439.33251953125</v>
@@ -7014,7 +7014,7 @@
         <v>44865</v>
       </c>
       <c r="B206" t="n">
-        <v>2348.265869140625</v>
+        <v>2348.26611328125</v>
       </c>
       <c r="C206" t="n">
         <v>3348.699951171875</v>
@@ -7046,19 +7046,19 @@
         <v>44866</v>
       </c>
       <c r="B207" t="n">
-        <v>2385.351806640625</v>
+        <v>2385.35205078125</v>
       </c>
       <c r="C207" t="n">
         <v>3342.449951171875</v>
       </c>
       <c r="D207" t="n">
-        <v>3569.2060546875</v>
+        <v>3569.20556640625</v>
       </c>
       <c r="E207" t="n">
         <v>2121.25</v>
       </c>
       <c r="F207" t="n">
-        <v>825.0978393554688</v>
+        <v>825.0977783203125</v>
       </c>
       <c r="G207" t="n">
         <v>69.77999877929688</v>
@@ -7084,7 +7084,7 @@
         <v>3308.60009765625</v>
       </c>
       <c r="D208" t="n">
-        <v>3574.19677734375</v>
+        <v>3574.196533203125</v>
       </c>
       <c r="E208" t="n">
         <v>2137.050048828125</v>
@@ -7148,7 +7148,7 @@
         <v>3319.449951171875</v>
       </c>
       <c r="D210" t="n">
-        <v>3826.288330078125</v>
+        <v>3826.2880859375</v>
       </c>
       <c r="E210" t="n">
         <v>2121.25</v>
@@ -7174,13 +7174,13 @@
         <v>44872</v>
       </c>
       <c r="B211" t="n">
-        <v>2441.25146484375</v>
+        <v>2441.251220703125</v>
       </c>
       <c r="C211" t="n">
         <v>3332.449951171875</v>
       </c>
       <c r="D211" t="n">
-        <v>3953.406982421875</v>
+        <v>3953.4072265625</v>
       </c>
       <c r="E211" t="n">
         <v>2165.699951171875</v>
@@ -7206,13 +7206,13 @@
         <v>44874</v>
       </c>
       <c r="B212" t="n">
-        <v>2395.470703125</v>
+        <v>2395.470947265625</v>
       </c>
       <c r="C212" t="n">
         <v>3290</v>
       </c>
       <c r="D212" t="n">
-        <v>3989.9404296875</v>
+        <v>3989.940185546875</v>
       </c>
       <c r="E212" t="n">
         <v>2215.5</v>
@@ -7250,13 +7250,13 @@
         <v>2176</v>
       </c>
       <c r="F213" t="n">
-        <v>875.7230224609375</v>
+        <v>875.7230834960938</v>
       </c>
       <c r="G213" t="n">
         <v>74.27999877929688</v>
       </c>
       <c r="H213" t="n">
-        <v>548.5131225585938</v>
+        <v>548.5130615234375</v>
       </c>
       <c r="I213" t="n">
         <v>3702.0224609375</v>
@@ -7270,7 +7270,7 @@
         <v>44876</v>
       </c>
       <c r="B214" t="n">
-        <v>2348.609375</v>
+        <v>2348.609619140625</v>
       </c>
       <c r="C214" t="n">
         <v>3292.050048828125</v>
@@ -7282,13 +7282,13 @@
         <v>2196.699951171875</v>
       </c>
       <c r="F214" t="n">
-        <v>876.752197265625</v>
+        <v>876.7521362304688</v>
       </c>
       <c r="G214" t="n">
         <v>72.04000091552734</v>
       </c>
       <c r="H214" t="n">
-        <v>547.9234008789062</v>
+        <v>547.9234619140625</v>
       </c>
       <c r="I214" t="n">
         <v>3795.394287109375</v>
@@ -7302,13 +7302,13 @@
         <v>44879</v>
       </c>
       <c r="B215" t="n">
-        <v>2392.621826171875</v>
+        <v>2392.62158203125</v>
       </c>
       <c r="C215" t="n">
         <v>3287.64990234375</v>
       </c>
       <c r="D215" t="n">
-        <v>4015.244384765625</v>
+        <v>4015.244140625</v>
       </c>
       <c r="E215" t="n">
         <v>2178.550048828125</v>
@@ -7320,7 +7320,7 @@
         <v>71.95999908447266</v>
       </c>
       <c r="H215" t="n">
-        <v>570.2807006835938</v>
+        <v>570.2806396484375</v>
       </c>
       <c r="I215" t="n">
         <v>3864.9990234375</v>
@@ -7334,7 +7334,7 @@
         <v>44880</v>
       </c>
       <c r="B216" t="n">
-        <v>2435.062255859375</v>
+        <v>2435.06201171875</v>
       </c>
       <c r="C216" t="n">
         <v>3290.300048828125</v>
@@ -7346,7 +7346,7 @@
         <v>2196.949951171875</v>
       </c>
       <c r="F216" t="n">
-        <v>888.9061889648438</v>
+        <v>888.90625</v>
       </c>
       <c r="G216" t="n">
         <v>71.41000366210938</v>
@@ -7384,7 +7384,7 @@
         <v>69.02999877929688</v>
       </c>
       <c r="H217" t="n">
-        <v>567.2341918945312</v>
+        <v>567.2342529296875</v>
       </c>
       <c r="I217" t="n">
         <v>3804.431640625</v>
@@ -7398,7 +7398,7 @@
         <v>44882</v>
       </c>
       <c r="B218" t="n">
-        <v>2405.09814453125</v>
+        <v>2405.098388671875</v>
       </c>
       <c r="C218" t="n">
         <v>3117.550048828125</v>
@@ -7410,7 +7410,7 @@
         <v>2102.60009765625</v>
       </c>
       <c r="F218" t="n">
-        <v>873.1746215820312</v>
+        <v>873.174560546875</v>
       </c>
       <c r="G218" t="n">
         <v>67.19999694824219</v>
@@ -7506,13 +7506,13 @@
         <v>1986.099975585938</v>
       </c>
       <c r="F221" t="n">
-        <v>864.9413452148438</v>
+        <v>864.9412841796875</v>
       </c>
       <c r="G221" t="n">
         <v>65.69999694824219</v>
       </c>
       <c r="H221" t="n">
-        <v>556.0801391601562</v>
+        <v>556.0802001953125</v>
       </c>
       <c r="I221" t="n">
         <v>3666.370849609375</v>
@@ -7526,13 +7526,13 @@
         <v>44888</v>
       </c>
       <c r="B222" t="n">
-        <v>2415.659423828125</v>
+        <v>2415.6591796875</v>
       </c>
       <c r="C222" t="n">
         <v>2856.85009765625</v>
       </c>
       <c r="D222" t="n">
-        <v>3896.211181640625</v>
+        <v>3896.2109375</v>
       </c>
       <c r="E222" t="n">
         <v>2036.5</v>
@@ -7544,7 +7544,7 @@
         <v>65.19000244140625</v>
       </c>
       <c r="H222" t="n">
-        <v>553.1810302734375</v>
+        <v>553.1810913085938</v>
       </c>
       <c r="I222" t="n">
         <v>3747.31005859375</v>
@@ -7564,13 +7564,13 @@
         <v>2790.85009765625</v>
       </c>
       <c r="D223" t="n">
-        <v>3913.978515625</v>
+        <v>3913.978759765625</v>
       </c>
       <c r="E223" t="n">
         <v>2043.050048828125</v>
       </c>
       <c r="F223" t="n">
-        <v>859.2564086914062</v>
+        <v>859.25634765625</v>
       </c>
       <c r="G223" t="n">
         <v>64.98999786376953</v>
@@ -7590,7 +7590,7 @@
         <v>44890</v>
       </c>
       <c r="B224" t="n">
-        <v>2463.158935546875</v>
+        <v>2463.1591796875</v>
       </c>
       <c r="C224" t="n">
         <v>2739.60009765625</v>
@@ -7622,7 +7622,7 @@
         <v>44893</v>
       </c>
       <c r="B225" t="n">
-        <v>2482.66015625</v>
+        <v>2482.659912109375</v>
       </c>
       <c r="C225" t="n">
         <v>2716.14990234375</v>
@@ -7634,7 +7634,7 @@
         <v>1990.699951171875</v>
       </c>
       <c r="F225" t="n">
-        <v>861.1676025390625</v>
+        <v>861.1676635742188</v>
       </c>
       <c r="G225" t="n">
         <v>65.65000152587891</v>
@@ -7666,7 +7666,7 @@
         <v>2012.050048828125</v>
       </c>
       <c r="F226" t="n">
-        <v>860.775634765625</v>
+        <v>860.7755737304688</v>
       </c>
       <c r="G226" t="n">
         <v>64.94000244140625</v>
@@ -7686,7 +7686,7 @@
         <v>44895</v>
       </c>
       <c r="B227" t="n">
-        <v>2518.174560546875</v>
+        <v>2518.17431640625</v>
       </c>
       <c r="C227" t="n">
         <v>2908.5</v>
@@ -7718,13 +7718,13 @@
         <v>44896</v>
       </c>
       <c r="B228" t="n">
-        <v>2532.0263671875</v>
+        <v>2532.026611328125</v>
       </c>
       <c r="C228" t="n">
         <v>2834.25</v>
       </c>
       <c r="D228" t="n">
-        <v>3907.98974609375</v>
+        <v>3907.989501953125</v>
       </c>
       <c r="E228" t="n">
         <v>2113.550048828125</v>
@@ -7750,7 +7750,7 @@
         <v>44897</v>
       </c>
       <c r="B229" t="n">
-        <v>2563.41455078125</v>
+        <v>2563.414794921875</v>
       </c>
       <c r="C229" t="n">
         <v>2745.699951171875</v>
@@ -7762,7 +7762,7 @@
         <v>2062.300048828125</v>
       </c>
       <c r="F229" t="n">
-        <v>870.5772094726562</v>
+        <v>870.5772705078125</v>
       </c>
       <c r="G229" t="n">
         <v>65.05999755859375</v>
@@ -7794,13 +7794,13 @@
         <v>2042.099975585938</v>
       </c>
       <c r="F230" t="n">
-        <v>875.4290161132812</v>
+        <v>875.428955078125</v>
       </c>
       <c r="G230" t="n">
         <v>64.61000061035156</v>
       </c>
       <c r="H230" t="n">
-        <v>563.45068359375</v>
+        <v>563.4506225585938</v>
       </c>
       <c r="I230" t="n">
         <v>3585.1826171875</v>
@@ -7814,13 +7814,13 @@
         <v>44901</v>
       </c>
       <c r="B231" t="n">
-        <v>2575.05615234375</v>
+        <v>2575.055908203125</v>
       </c>
       <c r="C231" t="n">
         <v>2773</v>
       </c>
       <c r="D231" t="n">
-        <v>4024.4775390625</v>
+        <v>4024.477783203125</v>
       </c>
       <c r="E231" t="n">
         <v>2063.300048828125</v>
@@ -7832,7 +7832,7 @@
         <v>64.95999908447266</v>
       </c>
       <c r="H231" t="n">
-        <v>570.9686279296875</v>
+        <v>570.9685668945312</v>
       </c>
       <c r="I231" t="n">
         <v>3691.78662109375</v>
@@ -7864,7 +7864,7 @@
         <v>64.88999938964844</v>
       </c>
       <c r="H232" t="n">
-        <v>571.9512939453125</v>
+        <v>571.9512329101562</v>
       </c>
       <c r="I232" t="n">
         <v>3725.240478515625</v>
@@ -7878,7 +7878,7 @@
         <v>44903</v>
       </c>
       <c r="B233" t="n">
-        <v>2575.154541015625</v>
+        <v>2575.154296875</v>
       </c>
       <c r="C233" t="n">
         <v>2691.39990234375</v>
@@ -7896,7 +7896,7 @@
         <v>64.75</v>
       </c>
       <c r="H233" t="n">
-        <v>577.60205078125</v>
+        <v>577.6021118164062</v>
       </c>
       <c r="I233" t="n">
         <v>3689.839111328125</v>
@@ -7916,7 +7916,7 @@
         <v>2646.39990234375</v>
       </c>
       <c r="D234" t="n">
-        <v>3989.541015625</v>
+        <v>3989.541259765625</v>
       </c>
       <c r="E234" t="n">
         <v>2053.449951171875</v>
@@ -7928,7 +7928,7 @@
         <v>63.20999908447266</v>
       </c>
       <c r="H234" t="n">
-        <v>570.9686279296875</v>
+        <v>570.9685668945312</v>
       </c>
       <c r="I234" t="n">
         <v>3616.33984375</v>
@@ -7980,7 +7980,7 @@
         <v>2652.800048828125</v>
       </c>
       <c r="D236" t="n">
-        <v>4052.825927734375</v>
+        <v>4052.826171875</v>
       </c>
       <c r="E236" t="n">
         <v>2021.400024414062</v>
@@ -7992,7 +7992,7 @@
         <v>64.59999847412109</v>
       </c>
       <c r="H236" t="n">
-        <v>574.457275390625</v>
+        <v>574.4572143554688</v>
       </c>
       <c r="I236" t="n">
         <v>3581.387939453125</v>
@@ -8006,13 +8006,13 @@
         <v>44909</v>
       </c>
       <c r="B237" t="n">
-        <v>2621.671630859375</v>
+        <v>2621.671875</v>
       </c>
       <c r="C237" t="n">
         <v>2672.449951171875</v>
       </c>
       <c r="D237" t="n">
-        <v>4048.43359375</v>
+        <v>4048.433837890625</v>
       </c>
       <c r="E237" t="n">
         <v>2018.150024414062</v>
@@ -8038,7 +8038,7 @@
         <v>44910</v>
       </c>
       <c r="B238" t="n">
-        <v>2589.15380859375</v>
+        <v>2589.153564453125</v>
       </c>
       <c r="C238" t="n">
         <v>2657</v>
@@ -8076,7 +8076,7 @@
         <v>2643.5</v>
       </c>
       <c r="D239" t="n">
-        <v>3973.570068359375</v>
+        <v>3973.5703125</v>
       </c>
       <c r="E239" t="n">
         <v>2044.25</v>
@@ -8120,7 +8120,7 @@
         <v>61.15999984741211</v>
       </c>
       <c r="H240" t="n">
-        <v>554.1146850585938</v>
+        <v>554.1146240234375</v>
       </c>
       <c r="I240" t="n">
         <v>3613.49365234375</v>
@@ -8134,19 +8134,19 @@
         <v>44915</v>
       </c>
       <c r="B241" t="n">
-        <v>2546.91015625</v>
+        <v>2546.909912109375</v>
       </c>
       <c r="C241" t="n">
         <v>2688.35009765625</v>
       </c>
       <c r="D241" t="n">
-        <v>4157.73486328125</v>
+        <v>4157.7353515625</v>
       </c>
       <c r="E241" t="n">
         <v>2061.64990234375</v>
       </c>
       <c r="F241" t="n">
-        <v>866.7056274414062</v>
+        <v>866.70556640625</v>
       </c>
       <c r="G241" t="n">
         <v>61.15000152587891</v>
@@ -8166,19 +8166,19 @@
         <v>44916</v>
       </c>
       <c r="B242" t="n">
-        <v>2496.266357421875</v>
+        <v>2496.2666015625</v>
       </c>
       <c r="C242" t="n">
         <v>2615.75</v>
       </c>
       <c r="D242" t="n">
-        <v>3894.86328125</v>
+        <v>3894.863037109375</v>
       </c>
       <c r="E242" t="n">
         <v>1968.25</v>
       </c>
       <c r="F242" t="n">
-        <v>840.6333618164062</v>
+        <v>840.6334228515625</v>
       </c>
       <c r="G242" t="n">
         <v>58.09999847412109</v>
@@ -8236,13 +8236,13 @@
         <v>2270.199951171875</v>
       </c>
       <c r="D244" t="n">
-        <v>3635.5849609375</v>
+        <v>3635.585205078125</v>
       </c>
       <c r="E244" t="n">
         <v>1809.050048828125</v>
       </c>
       <c r="F244" t="n">
-        <v>778.3441772460938</v>
+        <v>778.34423828125</v>
       </c>
       <c r="G244" t="n">
         <v>52.43999862670898</v>
@@ -8262,7 +8262,7 @@
         <v>44921</v>
       </c>
       <c r="B245" t="n">
-        <v>2381.02880859375</v>
+        <v>2381.029052734375</v>
       </c>
       <c r="C245" t="n">
         <v>2466.14990234375</v>
@@ -8274,13 +8274,13 @@
         <v>1876.849975585938</v>
       </c>
       <c r="F245" t="n">
-        <v>790.05712890625</v>
+        <v>790.0570678710938</v>
       </c>
       <c r="G245" t="n">
         <v>55.06000137329102</v>
       </c>
       <c r="H245" t="n">
-        <v>505.2728576660156</v>
+        <v>505.2728271484375</v>
       </c>
       <c r="I245" t="n">
         <v>3307.163818359375</v>
@@ -8300,7 +8300,7 @@
         <v>2501.800048828125</v>
       </c>
       <c r="D246" t="n">
-        <v>3762.80322265625</v>
+        <v>3762.803466796875</v>
       </c>
       <c r="E246" t="n">
         <v>1908.699951171875</v>
@@ -8312,7 +8312,7 @@
         <v>57.81000137329102</v>
       </c>
       <c r="H246" t="n">
-        <v>514.2648315429688</v>
+        <v>514.2647705078125</v>
       </c>
       <c r="I246" t="n">
         <v>3348.307373046875</v>
@@ -8332,19 +8332,19 @@
         <v>2564.449951171875</v>
       </c>
       <c r="D247" t="n">
-        <v>3790.802978515625</v>
+        <v>3790.802734375</v>
       </c>
       <c r="E247" t="n">
         <v>1897.849975585938</v>
       </c>
       <c r="F247" t="n">
-        <v>794.2718505859375</v>
+        <v>794.2717895507812</v>
       </c>
       <c r="G247" t="n">
         <v>60.70000076293945</v>
       </c>
       <c r="H247" t="n">
-        <v>509.449462890625</v>
+        <v>509.4494018554688</v>
       </c>
       <c r="I247" t="n">
         <v>3600.861083984375</v>
@@ -8364,7 +8364,7 @@
         <v>2669.5</v>
       </c>
       <c r="D248" t="n">
-        <v>3803.67919921875</v>
+        <v>3803.679443359375</v>
       </c>
       <c r="E248" t="n">
         <v>1910.25</v>
@@ -8390,19 +8390,19 @@
         <v>44925</v>
       </c>
       <c r="B249" t="n">
-        <v>2398.663818359375</v>
+        <v>2398.66357421875</v>
       </c>
       <c r="C249" t="n">
         <v>2589.25</v>
       </c>
       <c r="D249" t="n">
-        <v>3851.3427734375</v>
+        <v>3851.342529296875</v>
       </c>
       <c r="E249" t="n">
         <v>1931.800048828125</v>
       </c>
       <c r="F249" t="n">
-        <v>801.8680419921875</v>
+        <v>801.8679809570312</v>
       </c>
       <c r="G249" t="n">
         <v>59.90999984741211</v>
@@ -8454,7 +8454,7 @@
         <v>44929</v>
       </c>
       <c r="B251" t="n">
-        <v>2399.744384765625</v>
+        <v>2399.744140625</v>
       </c>
       <c r="C251" t="n">
         <v>2576.550048828125</v>
@@ -8486,13 +8486,13 @@
         <v>44930</v>
       </c>
       <c r="B252" t="n">
-        <v>2366.931884765625</v>
+        <v>2366.931640625</v>
       </c>
       <c r="C252" t="n">
         <v>2512.699951171875</v>
       </c>
       <c r="D252" t="n">
-        <v>3820.099609375</v>
+        <v>3820.09912109375</v>
       </c>
       <c r="E252" t="n">
         <v>1860.5</v>
@@ -8504,7 +8504,7 @@
         <v>57.31999969482422</v>
       </c>
       <c r="H252" t="n">
-        <v>509.8916320800781</v>
+        <v>509.8915710449219</v>
       </c>
       <c r="I252" t="n">
         <v>3472.537109375</v>
@@ -8518,7 +8518,7 @@
         <v>44931</v>
       </c>
       <c r="B253" t="n">
-        <v>2397.288330078125</v>
+        <v>2397.2880859375</v>
       </c>
       <c r="C253" t="n">
         <v>2554.14990234375</v>
@@ -8530,13 +8530,13 @@
         <v>1860</v>
       </c>
       <c r="F253" t="n">
-        <v>803.3382568359375</v>
+        <v>803.3383178710938</v>
       </c>
       <c r="G253" t="n">
         <v>57.75</v>
       </c>
       <c r="H253" t="n">
-        <v>515.6898193359375</v>
+        <v>515.6897583007812</v>
       </c>
       <c r="I253" t="n">
         <v>3628.722900390625</v>
@@ -8550,7 +8550,7 @@
         <v>44932</v>
       </c>
       <c r="B254" t="n">
-        <v>2373.46484375</v>
+        <v>2373.464599609375</v>
       </c>
       <c r="C254" t="n">
         <v>2523.35009765625</v>
@@ -8562,13 +8562,13 @@
         <v>1838.25</v>
       </c>
       <c r="F254" t="n">
-        <v>790.106201171875</v>
+        <v>790.1061401367188</v>
       </c>
       <c r="G254" t="n">
         <v>56.68000030517578</v>
       </c>
       <c r="H254" t="n">
-        <v>510.8252868652344</v>
+        <v>510.8252258300781</v>
       </c>
       <c r="I254" t="n">
         <v>3550.530029296875</v>
@@ -8582,25 +8582,25 @@
         <v>44935</v>
       </c>
       <c r="B255" t="n">
-        <v>2421.30810546875</v>
+        <v>2421.308349609375</v>
       </c>
       <c r="C255" t="n">
         <v>2614.5</v>
       </c>
       <c r="D255" t="n">
-        <v>3848.298095703125</v>
+        <v>3848.29833984375</v>
       </c>
       <c r="E255" t="n">
         <v>1891.449951171875</v>
       </c>
       <c r="F255" t="n">
-        <v>800.44677734375</v>
+        <v>800.4468383789062</v>
       </c>
       <c r="G255" t="n">
         <v>57.54000091552734</v>
       </c>
       <c r="H255" t="n">
-        <v>515.6898193359375</v>
+        <v>515.6897583007812</v>
       </c>
       <c r="I255" t="n">
         <v>3624.029296875</v>
@@ -8626,13 +8626,13 @@
         <v>1895.199951171875</v>
       </c>
       <c r="F256" t="n">
-        <v>780.5986938476562</v>
+        <v>780.5986328125</v>
       </c>
       <c r="G256" t="n">
         <v>55.84000015258789</v>
       </c>
       <c r="H256" t="n">
-        <v>505.567626953125</v>
+        <v>505.5675964355469</v>
       </c>
       <c r="I256" t="n">
         <v>3651.3916015625</v>
@@ -8646,13 +8646,13 @@
         <v>44937</v>
       </c>
       <c r="B257" t="n">
-        <v>2352.833984375</v>
+        <v>2352.833740234375</v>
       </c>
       <c r="C257" t="n">
         <v>2585.35009765625</v>
       </c>
       <c r="D257" t="n">
-        <v>3629.197021484375</v>
+        <v>3629.196533203125</v>
       </c>
       <c r="E257" t="n">
         <v>1877.150024414062</v>
@@ -8684,13 +8684,13 @@
         <v>2624</v>
       </c>
       <c r="D258" t="n">
-        <v>3640.575927734375</v>
+        <v>3640.576171875</v>
       </c>
       <c r="E258" t="n">
         <v>1889.849975585938</v>
       </c>
       <c r="F258" t="n">
-        <v>777.217041015625</v>
+        <v>777.2171020507812</v>
       </c>
       <c r="G258" t="n">
         <v>54.72999954223633</v>
@@ -8716,7 +8716,7 @@
         <v>2689.050048828125</v>
       </c>
       <c r="D259" t="n">
-        <v>3714.391845703125</v>
+        <v>3714.3916015625</v>
       </c>
       <c r="E259" t="n">
         <v>1915.650024414062</v>
@@ -8728,7 +8728,7 @@
         <v>55.7400016784668</v>
       </c>
       <c r="H259" t="n">
-        <v>509.6951599121094</v>
+        <v>509.6950988769531</v>
       </c>
       <c r="I259" t="n">
         <v>3710.011474609375</v>
@@ -8748,19 +8748,19 @@
         <v>2703.10009765625</v>
       </c>
       <c r="D260" t="n">
-        <v>3613.2255859375</v>
+        <v>3613.22607421875</v>
       </c>
       <c r="E260" t="n">
         <v>2089.800048828125</v>
       </c>
       <c r="F260" t="n">
-        <v>771.4341430664062</v>
+        <v>771.4342041015625</v>
       </c>
       <c r="G260" t="n">
         <v>54.59000015258789</v>
       </c>
       <c r="H260" t="n">
-        <v>508.0735778808594</v>
+        <v>508.0735473632812</v>
       </c>
       <c r="I260" t="n">
         <v>3725.58984375</v>
@@ -8774,13 +8774,13 @@
         <v>44943</v>
       </c>
       <c r="B261" t="n">
-        <v>2304.744873046875</v>
+        <v>2304.74462890625</v>
       </c>
       <c r="C261" t="n">
         <v>2725.050048828125</v>
       </c>
       <c r="D261" t="n">
-        <v>3632.74072265625</v>
+        <v>3632.740478515625</v>
       </c>
       <c r="E261" t="n">
         <v>2166.14990234375</v>
@@ -8792,7 +8792,7 @@
         <v>56.38999938964844</v>
       </c>
       <c r="H261" t="n">
-        <v>508.5649108886719</v>
+        <v>508.5649719238281</v>
       </c>
       <c r="I261" t="n">
         <v>3844.7265625</v>
@@ -8806,7 +8806,7 @@
         <v>44944</v>
       </c>
       <c r="B262" t="n">
-        <v>2323.410400390625</v>
+        <v>2323.41064453125</v>
       </c>
       <c r="C262" t="n">
         <v>2710.75</v>
@@ -8838,7 +8838,7 @@
         <v>44945</v>
       </c>
       <c r="B263" t="n">
-        <v>2349.1005859375</v>
+        <v>2349.100830078125</v>
       </c>
       <c r="C263" t="n">
         <v>2734.10009765625</v>
@@ -8850,13 +8850,13 @@
         <v>1954.300048828125</v>
       </c>
       <c r="F263" t="n">
-        <v>760.6524047851562</v>
+        <v>760.65234375</v>
       </c>
       <c r="G263" t="n">
         <v>55.5099983215332</v>
       </c>
       <c r="H263" t="n">
-        <v>510.2847900390625</v>
+        <v>510.2847290039062</v>
       </c>
       <c r="I263" t="n">
         <v>3830.296142578125</v>
@@ -8876,7 +8876,7 @@
         <v>2737.949951171875</v>
       </c>
       <c r="D264" t="n">
-        <v>3449.873046875</v>
+        <v>3449.872802734375</v>
       </c>
       <c r="E264" t="n">
         <v>1975.599975585938</v>
@@ -8888,7 +8888,7 @@
         <v>55.0099983215332</v>
       </c>
       <c r="H264" t="n">
-        <v>508.8106079101562</v>
+        <v>508.8106384277344</v>
       </c>
       <c r="I264" t="n">
         <v>3913.531982421875</v>
@@ -8902,7 +8902,7 @@
         <v>44949</v>
       </c>
       <c r="B265" t="n">
-        <v>2282.591064453125</v>
+        <v>2282.59130859375</v>
       </c>
       <c r="C265" t="n">
         <v>2784.10009765625</v>
@@ -8914,7 +8914,7 @@
         <v>1931.849975585938</v>
       </c>
       <c r="F265" t="n">
-        <v>753.7911987304688</v>
+        <v>753.791259765625</v>
       </c>
       <c r="G265" t="n">
         <v>54.63999938964844</v>
@@ -8940,13 +8940,13 @@
         <v>2762.14990234375</v>
       </c>
       <c r="D266" t="n">
-        <v>3435.7490234375</v>
+        <v>3435.74853515625</v>
       </c>
       <c r="E266" t="n">
         <v>1916.800048828125</v>
       </c>
       <c r="F266" t="n">
-        <v>746.0970458984375</v>
+        <v>746.0969848632812</v>
       </c>
       <c r="G266" t="n">
         <v>54.93000030517578</v>
@@ -8966,13 +8966,13 @@
         <v>44951</v>
       </c>
       <c r="B267" t="n">
-        <v>2127.614990234375</v>
+        <v>2127.615478515625</v>
       </c>
       <c r="C267" t="n">
         <v>2517.75</v>
       </c>
       <c r="D267" t="n">
-        <v>3382.795166015625</v>
+        <v>3382.794921875</v>
       </c>
       <c r="E267" t="n">
         <v>1857.800048828125</v>
@@ -8984,7 +8984,7 @@
         <v>52.20000076293945</v>
       </c>
       <c r="H267" t="n">
-        <v>452.2542724609375</v>
+        <v>452.2543029785156</v>
       </c>
       <c r="I267" t="n">
         <v>3654.986572265625</v>
@@ -9030,19 +9030,19 @@
         <v>44956</v>
       </c>
       <c r="B269" t="n">
-        <v>1870.664916992188</v>
+        <v>1870.664794921875</v>
       </c>
       <c r="C269" t="n">
         <v>1708.199951171875</v>
       </c>
       <c r="D269" t="n">
-        <v>2887.596435546875</v>
+        <v>2887.59619140625</v>
       </c>
       <c r="E269" t="n">
         <v>1189</v>
       </c>
       <c r="F269" t="n">
-        <v>585.1549072265625</v>
+        <v>585.1548461914062</v>
       </c>
       <c r="G269" t="n">
         <v>47.11000061035156</v>
@@ -9062,7 +9062,7 @@
         <v>44957</v>
       </c>
       <c r="B270" t="n">
-        <v>1933.686889648438</v>
+        <v>1933.686767578125</v>
       </c>
       <c r="C270" t="n">
         <v>1774</v>
@@ -9080,7 +9080,7 @@
         <v>44.7599983215332</v>
       </c>
       <c r="H270" t="n">
-        <v>394.27294921875</v>
+        <v>394.2729797363281</v>
       </c>
       <c r="I270" t="n">
         <v>2105.3125</v>
@@ -9100,7 +9100,7 @@
         <v>1723.5</v>
       </c>
       <c r="D271" t="n">
-        <v>2131.47216796875</v>
+        <v>2131.471923828125</v>
       </c>
       <c r="E271" t="n">
         <v>1155.349975585938</v>
@@ -9126,25 +9126,25 @@
         <v>44959</v>
       </c>
       <c r="B272" t="n">
-        <v>1808.870849609375</v>
+        <v>1808.870971679688</v>
       </c>
       <c r="C272" t="n">
         <v>1551.150024414062</v>
       </c>
       <c r="D272" t="n">
-        <v>1562.407348632812</v>
+        <v>1562.4072265625</v>
       </c>
       <c r="E272" t="n">
         <v>1039.849975585938</v>
       </c>
       <c r="F272" t="n">
-        <v>453.2745361328125</v>
+        <v>453.2745056152344</v>
       </c>
       <c r="G272" t="n">
         <v>40.40999984741211</v>
       </c>
       <c r="H272" t="n">
-        <v>346.4629516601562</v>
+        <v>346.4629211425781</v>
       </c>
       <c r="I272" t="n">
         <v>1705.36083984375</v>
@@ -9164,7 +9164,7 @@
         <v>1396.050048828125</v>
       </c>
       <c r="D273" t="n">
-        <v>1583.918334960938</v>
+        <v>1583.918212890625</v>
       </c>
       <c r="E273" t="n">
         <v>935.9000244140625</v>
@@ -9176,7 +9176,7 @@
         <v>38.38999938964844</v>
       </c>
       <c r="H273" t="n">
-        <v>367.1495056152344</v>
+        <v>367.1495361328125</v>
       </c>
       <c r="I273" t="n">
         <v>1620.127807617188</v>
@@ -9190,7 +9190,7 @@
         <v>44963</v>
       </c>
       <c r="B274" t="n">
-        <v>1934.914916992188</v>
+        <v>1934.914794921875</v>
       </c>
       <c r="C274" t="n">
         <v>1256.449951171875</v>
@@ -9202,13 +9202,13 @@
         <v>889.0999755859375</v>
       </c>
       <c r="F274" t="n">
-        <v>534.627685546875</v>
+        <v>534.6277465820312</v>
       </c>
       <c r="G274" t="n">
         <v>36.47000122070312</v>
       </c>
       <c r="H274" t="n">
-        <v>373.1933288574219</v>
+        <v>373.1932983398438</v>
       </c>
       <c r="I274" t="n">
         <v>1539.138916015625</v>
@@ -9222,19 +9222,19 @@
         <v>44964</v>
       </c>
       <c r="B275" t="n">
-        <v>1958.984008789062</v>
+        <v>1958.984130859375</v>
       </c>
       <c r="C275" t="n">
         <v>1252.199951171875</v>
       </c>
       <c r="D275" t="n">
-        <v>1799.675537109375</v>
+        <v>1799.675415039062</v>
       </c>
       <c r="E275" t="n">
         <v>844.6500244140625</v>
       </c>
       <c r="F275" t="n">
-        <v>542.175048828125</v>
+        <v>542.1749877929688</v>
       </c>
       <c r="G275" t="n">
         <v>34.65000152587891</v>
@@ -9254,7 +9254,7 @@
         <v>44965</v>
       </c>
       <c r="B276" t="n">
-        <v>1939.041015625</v>
+        <v>1939.040893554688</v>
       </c>
       <c r="C276" t="n">
         <v>1314.800048828125</v>
@@ -9266,7 +9266,7 @@
         <v>802.4500122070312</v>
       </c>
       <c r="F276" t="n">
-        <v>587.3602905273438</v>
+        <v>587.3602294921875</v>
       </c>
       <c r="G276" t="n">
         <v>36.38000106811523</v>
@@ -9292,7 +9292,7 @@
         <v>1249.099975585938</v>
       </c>
       <c r="D277" t="n">
-        <v>1922.20263671875</v>
+        <v>1922.202514648438</v>
       </c>
       <c r="E277" t="n">
         <v>762.3499755859375</v>
@@ -9324,19 +9324,19 @@
         <v>1186.650024414062</v>
       </c>
       <c r="D278" t="n">
-        <v>1843.595703125</v>
+        <v>1843.595458984375</v>
       </c>
       <c r="E278" t="n">
         <v>724.25</v>
       </c>
       <c r="F278" t="n">
-        <v>572.3638305664062</v>
+        <v>572.3638916015625</v>
       </c>
       <c r="G278" t="n">
         <v>32.84000015258789</v>
       </c>
       <c r="H278" t="n">
-        <v>354.5705261230469</v>
+        <v>354.5704956054688</v>
       </c>
       <c r="I278" t="n">
         <v>1253.680419921875</v>
@@ -9356,7 +9356,7 @@
         <v>1127.349975585938</v>
       </c>
       <c r="D279" t="n">
-        <v>1714.530517578125</v>
+        <v>1714.530395507812</v>
       </c>
       <c r="E279" t="n">
         <v>688.0499877929688</v>
@@ -9368,7 +9368,7 @@
         <v>31.20000076293945</v>
       </c>
       <c r="H279" t="n">
-        <v>336.537353515625</v>
+        <v>336.5373229980469</v>
       </c>
       <c r="I279" t="n">
         <v>1191.016357421875</v>
@@ -9414,7 +9414,7 @@
         <v>44972</v>
       </c>
       <c r="B281" t="n">
-        <v>1819.579467773438</v>
+        <v>1819.579345703125</v>
       </c>
       <c r="C281" t="n">
         <v>1017.450012207031</v>
@@ -9432,7 +9432,7 @@
         <v>28.15999984741211</v>
       </c>
       <c r="H281" t="n">
-        <v>338.8959045410156</v>
+        <v>338.8958740234375</v>
       </c>
       <c r="I281" t="n">
         <v>1074.92578125</v>
@@ -9458,13 +9458,13 @@
         <v>616.2999877929688</v>
       </c>
       <c r="F282" t="n">
-        <v>565.747802734375</v>
+        <v>565.7477416992188</v>
       </c>
       <c r="G282" t="n">
         <v>29.55999946594238</v>
       </c>
       <c r="H282" t="n">
-        <v>341.794921875</v>
+        <v>341.7949523925781</v>
       </c>
       <c r="I282" t="n">
         <v>1021.199279785156</v>
@@ -9478,13 +9478,13 @@
         <v>44974</v>
       </c>
       <c r="B283" t="n">
-        <v>1807.053466796875</v>
+        <v>1807.053588867188</v>
       </c>
       <c r="C283" t="n">
         <v>920.4000244140625</v>
       </c>
       <c r="D283" t="n">
-        <v>1719.5712890625</v>
+        <v>1719.571166992188</v>
       </c>
       <c r="E283" t="n">
         <v>628.6500244140625</v>
@@ -9496,7 +9496,7 @@
         <v>31.03000068664551</v>
       </c>
       <c r="H283" t="n">
-        <v>347.1999816894531</v>
+        <v>347.2000122070312</v>
       </c>
       <c r="I283" t="n">
         <v>970.1693115234375</v>
@@ -9510,7 +9510,7 @@
         <v>44977</v>
       </c>
       <c r="B284" t="n">
-        <v>1818.105712890625</v>
+        <v>1818.105590820312</v>
       </c>
       <c r="C284" t="n">
         <v>874.4000244140625</v>
@@ -9522,13 +9522,13 @@
         <v>597.25</v>
       </c>
       <c r="F284" t="n">
-        <v>568.1981201171875</v>
+        <v>568.1981811523438</v>
       </c>
       <c r="G284" t="n">
         <v>32.58000183105469</v>
       </c>
       <c r="H284" t="n">
-        <v>346.3647155761719</v>
+        <v>346.3646850585938</v>
       </c>
       <c r="I284" t="n">
         <v>921.685791015625</v>
@@ -9542,7 +9542,7 @@
         <v>44978</v>
       </c>
       <c r="B285" t="n">
-        <v>1796.246948242188</v>
+        <v>1796.2470703125</v>
       </c>
       <c r="C285" t="n">
         <v>830.7000122070312</v>
@@ -9574,13 +9574,13 @@
         <v>44979</v>
       </c>
       <c r="B286" t="n">
-        <v>1721.386962890625</v>
+        <v>1721.386840820312</v>
       </c>
       <c r="C286" t="n">
         <v>789.2000122070312</v>
       </c>
       <c r="D286" t="n">
-        <v>1402.298583984375</v>
+        <v>1402.298461914062</v>
       </c>
       <c r="E286" t="n">
         <v>539.0499877929688</v>
@@ -9592,7 +9592,7 @@
         <v>32.4900016784668</v>
       </c>
       <c r="H286" t="n">
-        <v>329.6090087890625</v>
+        <v>329.6090393066406</v>
       </c>
       <c r="I286" t="n">
         <v>831.8590087890625</v>
@@ -9606,13 +9606,13 @@
         <v>44980</v>
       </c>
       <c r="B287" t="n">
-        <v>1697.17041015625</v>
+        <v>1697.170532226562</v>
       </c>
       <c r="C287" t="n">
         <v>749.75</v>
       </c>
       <c r="D287" t="n">
-        <v>1380.138916015625</v>
+        <v>1380.138793945312</v>
       </c>
       <c r="E287" t="n">
         <v>512.0999755859375</v>
@@ -9624,7 +9624,7 @@
         <v>30.8700008392334</v>
       </c>
       <c r="H287" t="n">
-        <v>331.0831298828125</v>
+        <v>331.0831604003906</v>
       </c>
       <c r="I287" t="n">
         <v>790.2659912109375</v>
@@ -9638,7 +9638,7 @@
         <v>44981</v>
       </c>
       <c r="B288" t="n">
-        <v>1699.577270507812</v>
+        <v>1699.5771484375</v>
       </c>
       <c r="C288" t="n">
         <v>712.2999877929688</v>
@@ -9650,13 +9650,13 @@
         <v>486.5</v>
       </c>
       <c r="F288" t="n">
-        <v>547.8108520507812</v>
+        <v>547.8109130859375</v>
       </c>
       <c r="G288" t="n">
         <v>29.32999992370605</v>
       </c>
       <c r="H288" t="n">
-        <v>339.2889709472656</v>
+        <v>339.2890014648438</v>
       </c>
       <c r="I288" t="n">
         <v>750.770263671875</v>
@@ -9670,13 +9670,13 @@
         <v>44984</v>
       </c>
       <c r="B289" t="n">
-        <v>1664.996459960938</v>
+        <v>1664.996337890625</v>
       </c>
       <c r="C289" t="n">
         <v>676.7000122070312</v>
       </c>
       <c r="D289" t="n">
-        <v>1191.332397460938</v>
+        <v>1191.33251953125</v>
       </c>
       <c r="E289" t="n">
         <v>462.2000122070312</v>
@@ -9708,13 +9708,13 @@
         <v>642.9000244140625</v>
       </c>
       <c r="D290" t="n">
-        <v>1361.372924804688</v>
+        <v>1361.373046875</v>
       </c>
       <c r="E290" t="n">
         <v>485.2999877929688</v>
       </c>
       <c r="F290" t="n">
-        <v>580.6951293945312</v>
+        <v>580.6951904296875</v>
       </c>
       <c r="G290" t="n">
         <v>29.26000022888184</v>
@@ -9734,7 +9734,7 @@
         <v>44986</v>
       </c>
       <c r="B291" t="n">
-        <v>1738.33349609375</v>
+        <v>1738.333618164062</v>
       </c>
       <c r="C291" t="n">
         <v>675</v>
@@ -9746,13 +9746,13 @@
         <v>509.5499877929688</v>
       </c>
       <c r="F291" t="n">
-        <v>590.1536865234375</v>
+        <v>590.1537475585938</v>
       </c>
       <c r="G291" t="n">
         <v>30.71999931335449</v>
       </c>
       <c r="H291" t="n">
-        <v>347.4948425292969</v>
+        <v>347.4948120117188</v>
       </c>
       <c r="I291" t="n">
         <v>710.6752319335938</v>
@@ -9772,7 +9772,7 @@
         <v>708.75</v>
       </c>
       <c r="D292" t="n">
-        <v>1604.330932617188</v>
+        <v>1604.3310546875</v>
       </c>
       <c r="E292" t="n">
         <v>535</v>
@@ -9804,7 +9804,7 @@
         <v>744.1500244140625</v>
       </c>
       <c r="D293" t="n">
-        <v>1876.086547851562</v>
+        <v>1876.08642578125</v>
       </c>
       <c r="E293" t="n">
         <v>561.75</v>
@@ -9830,7 +9830,7 @@
         <v>44991</v>
       </c>
       <c r="B294" t="n">
-        <v>1832.9892578125</v>
+        <v>1832.989379882812</v>
       </c>
       <c r="C294" t="n">
         <v>781.3499755859375</v>
@@ -9862,13 +9862,13 @@
         <v>44993</v>
       </c>
       <c r="B295" t="n">
-        <v>1853.325317382812</v>
+        <v>1853.3251953125</v>
       </c>
       <c r="C295" t="n">
         <v>820.4000244140625</v>
       </c>
       <c r="D295" t="n">
-        <v>2035.945678710938</v>
+        <v>2035.94580078125</v>
       </c>
       <c r="E295" t="n">
         <v>619.25</v>
@@ -9912,7 +9912,7 @@
         <v>39.18000030517578</v>
       </c>
       <c r="H296" t="n">
-        <v>378.057861328125</v>
+        <v>378.0578918457031</v>
       </c>
       <c r="I296" t="n">
         <v>903.1611938476562</v>
@@ -9932,13 +9932,13 @@
         <v>904.4500122070312</v>
       </c>
       <c r="D297" t="n">
-        <v>1892.755981445312</v>
+        <v>1892.756225585938</v>
       </c>
       <c r="E297" t="n">
         <v>682.7000122070312</v>
       </c>
       <c r="F297" t="n">
-        <v>683.954833984375</v>
+        <v>683.9548950195312</v>
       </c>
       <c r="G297" t="n">
         <v>40.97999954223633</v>
@@ -9964,7 +9964,7 @@
         <v>949.6500244140625</v>
       </c>
       <c r="D298" t="n">
-        <v>1870.995849609375</v>
+        <v>1870.995727539062</v>
       </c>
       <c r="E298" t="n">
         <v>716.7999877929688</v>
@@ -9976,7 +9976,7 @@
         <v>43.02000045776367</v>
       </c>
       <c r="H298" t="n">
-        <v>361.6461791992188</v>
+        <v>361.6462097167969</v>
       </c>
       <c r="I298" t="n">
         <v>995.6842651367188</v>
@@ -9990,13 +9990,13 @@
         <v>44999</v>
       </c>
       <c r="B299" t="n">
-        <v>1707.829833984375</v>
+        <v>1707.829711914062</v>
       </c>
       <c r="C299" t="n">
         <v>902.2000122070312</v>
       </c>
       <c r="D299" t="n">
-        <v>1735.043212890625</v>
+        <v>1735.04296875</v>
       </c>
       <c r="E299" t="n">
         <v>706.0999755859375</v>
@@ -10028,7 +10028,7 @@
         <v>928.3499755859375</v>
       </c>
       <c r="D300" t="n">
-        <v>1835.660034179688</v>
+        <v>1835.66015625</v>
       </c>
       <c r="E300" t="n">
         <v>740.4000244140625</v>
@@ -10040,7 +10040,7 @@
         <v>40.36000061035156</v>
       </c>
       <c r="H300" t="n">
-        <v>358.8453674316406</v>
+        <v>358.8453979492188</v>
       </c>
       <c r="I300" t="n">
         <v>918.5900268554688</v>
@@ -10054,7 +10054,7 @@
         <v>45001</v>
       </c>
       <c r="B301" t="n">
-        <v>1719.5205078125</v>
+        <v>1719.520385742188</v>
       </c>
       <c r="C301" t="n">
         <v>973.7000122070312</v>
@@ -10072,7 +10072,7 @@
         <v>39.7400016784668</v>
       </c>
       <c r="H301" t="n">
-        <v>372.2596740722656</v>
+        <v>372.2597045898438</v>
       </c>
       <c r="I301" t="n">
         <v>887.1831665039062</v>
@@ -10092,13 +10092,13 @@
         <v>1022.349975585938</v>
       </c>
       <c r="D302" t="n">
-        <v>1873.141845703125</v>
+        <v>1873.141967773438</v>
       </c>
       <c r="E302" t="n">
         <v>816.25</v>
       </c>
       <c r="F302" t="n">
-        <v>666.8511962890625</v>
+        <v>666.8511352539062</v>
       </c>
       <c r="G302" t="n">
         <v>39.9900016784668</v>
@@ -10118,13 +10118,13 @@
         <v>45005</v>
       </c>
       <c r="B303" t="n">
-        <v>1665.7822265625</v>
+        <v>1665.782104492188</v>
       </c>
       <c r="C303" t="n">
         <v>1009.099975585938</v>
       </c>
       <c r="D303" t="n">
-        <v>1801.671752929688</v>
+        <v>1801.671997070312</v>
       </c>
       <c r="E303" t="n">
         <v>848.6500244140625</v>
@@ -10150,25 +10150,25 @@
         <v>45006</v>
       </c>
       <c r="B304" t="n">
-        <v>1694.272338867188</v>
+        <v>1694.272216796875</v>
       </c>
       <c r="C304" t="n">
         <v>1006.099975585938</v>
       </c>
       <c r="D304" t="n">
-        <v>1820.936889648438</v>
+        <v>1820.936767578125</v>
       </c>
       <c r="E304" t="n">
         <v>891.0499877929688</v>
       </c>
       <c r="F304" t="n">
-        <v>651.6096801757812</v>
+        <v>651.6097412109375</v>
       </c>
       <c r="G304" t="n">
         <v>39.93999862670898</v>
       </c>
       <c r="H304" t="n">
-        <v>364.4961242675781</v>
+        <v>364.49609375</v>
       </c>
       <c r="I304" t="n">
         <v>889.579833984375</v>
@@ -10188,19 +10188,19 @@
         <v>1032.800048828125</v>
       </c>
       <c r="D305" t="n">
-        <v>1812.10302734375</v>
+        <v>1812.102905273438</v>
       </c>
       <c r="E305" t="n">
         <v>935.5999755859375</v>
       </c>
       <c r="F305" t="n">
-        <v>644.1115112304688</v>
+        <v>644.111572265625</v>
       </c>
       <c r="G305" t="n">
         <v>40.81000137329102</v>
       </c>
       <c r="H305" t="n">
-        <v>369.0658264160156</v>
+        <v>369.0657958984375</v>
       </c>
       <c r="I305" t="n">
         <v>934.0188598632812</v>
@@ -10220,7 +10220,7 @@
         <v>1084.400024414062</v>
       </c>
       <c r="D306" t="n">
-        <v>1790.74169921875</v>
+        <v>1790.741821289062</v>
       </c>
       <c r="E306" t="n">
         <v>982.3499755859375</v>
@@ -10246,13 +10246,13 @@
         <v>45009</v>
       </c>
       <c r="B307" t="n">
-        <v>1670.93994140625</v>
+        <v>1670.940063476562</v>
       </c>
       <c r="C307" t="n">
         <v>1124.550048828125</v>
       </c>
       <c r="D307" t="n">
-        <v>1737.48876953125</v>
+        <v>1737.488647460938</v>
       </c>
       <c r="E307" t="n">
         <v>1029.349975585938</v>
@@ -10284,7 +10284,7 @@
         <v>1068.400024414062</v>
       </c>
       <c r="D308" t="n">
-        <v>1719.920654296875</v>
+        <v>1719.920776367188</v>
       </c>
       <c r="E308" t="n">
         <v>984.9000244140625</v>
@@ -10310,13 +10310,13 @@
         <v>45013</v>
       </c>
       <c r="B309" t="n">
-        <v>1585.568115234375</v>
+        <v>1585.568237304688</v>
       </c>
       <c r="C309" t="n">
         <v>1015</v>
       </c>
       <c r="D309" t="n">
-        <v>1597.942626953125</v>
+        <v>1597.942504882812</v>
       </c>
       <c r="E309" t="n">
         <v>935.6500244140625</v>
@@ -10328,7 +10328,7 @@
         <v>34.77000045776367</v>
       </c>
       <c r="H309" t="n">
-        <v>352.75244140625</v>
+        <v>352.7524719238281</v>
       </c>
       <c r="I309" t="n">
         <v>908.7035522460938</v>
@@ -10342,13 +10342,13 @@
         <v>45014</v>
       </c>
       <c r="B310" t="n">
-        <v>1597.30810546875</v>
+        <v>1597.307983398438</v>
       </c>
       <c r="C310" t="n">
         <v>1003.450012207031</v>
       </c>
       <c r="D310" t="n">
-        <v>1737.2392578125</v>
+        <v>1737.239013671875</v>
       </c>
       <c r="E310" t="n">
         <v>894.3499755859375</v>
@@ -10360,7 +10360,7 @@
         <v>36.5</v>
       </c>
       <c r="H310" t="n">
-        <v>357.616943359375</v>
+        <v>357.6169738769531</v>
       </c>
       <c r="I310" t="n">
         <v>870.5060424804688</v>
@@ -10380,13 +10380,13 @@
         <v>993.0499877929688</v>
       </c>
       <c r="D311" t="n">
-        <v>1747.270874023438</v>
+        <v>1747.270751953125</v>
       </c>
       <c r="E311" t="n">
         <v>881.1500244140625</v>
       </c>
       <c r="F311" t="n">
-        <v>619.362548828125</v>
+        <v>619.3624877929688</v>
       </c>
       <c r="G311" t="n">
         <v>38.31999969482422</v>
@@ -10418,13 +10418,13 @@
         <v>837.4500122070312</v>
       </c>
       <c r="F312" t="n">
-        <v>615.34375</v>
+        <v>615.3438110351562</v>
       </c>
       <c r="G312" t="n">
         <v>38.11000061035156</v>
       </c>
       <c r="H312" t="n">
-        <v>368.3287658691406</v>
+        <v>368.3287353515625</v>
       </c>
       <c r="I312" t="n">
         <v>844.192138671875</v>
@@ -10438,19 +10438,19 @@
         <v>45021</v>
       </c>
       <c r="B313" t="n">
-        <v>1658.266845703125</v>
+        <v>1658.266723632812</v>
       </c>
       <c r="C313" t="n">
         <v>907.8499755859375</v>
       </c>
       <c r="D313" t="n">
-        <v>1694.916259765625</v>
+        <v>1694.916015625</v>
       </c>
       <c r="E313" t="n">
         <v>815.5999755859375</v>
       </c>
       <c r="F313" t="n">
-        <v>624.1162109375</v>
+        <v>624.1162719726562</v>
       </c>
       <c r="G313" t="n">
         <v>38.02000045776367</v>
@@ -10476,7 +10476,7 @@
         <v>953.2000122070312</v>
       </c>
       <c r="D314" t="n">
-        <v>1750.864501953125</v>
+        <v>1750.864379882812</v>
       </c>
       <c r="E314" t="n">
         <v>856.3499755859375</v>
@@ -10508,7 +10508,7 @@
         <v>1000.849975585938</v>
       </c>
       <c r="D315" t="n">
-        <v>1793.985961914062</v>
+        <v>1793.98583984375</v>
       </c>
       <c r="E315" t="n">
         <v>899.1500244140625</v>
@@ -10520,7 +10520,7 @@
         <v>38.79999923706055</v>
       </c>
       <c r="H315" t="n">
-        <v>377.7138977050781</v>
+        <v>377.7138671875</v>
       </c>
       <c r="I315" t="n">
         <v>904.9088745117188</v>
@@ -10566,25 +10566,25 @@
         <v>45028</v>
       </c>
       <c r="B317" t="n">
-        <v>1727.0849609375</v>
+        <v>1727.085083007812</v>
       </c>
       <c r="C317" t="n">
         <v>1043.449951171875</v>
       </c>
       <c r="D317" t="n">
-        <v>1843.895141601562</v>
+        <v>1843.89501953125</v>
       </c>
       <c r="E317" t="n">
         <v>941.8499755859375</v>
       </c>
       <c r="F317" t="n">
-        <v>644.6995239257812</v>
+        <v>644.6995849609375</v>
       </c>
       <c r="G317" t="n">
         <v>38.4900016784668</v>
       </c>
       <c r="H317" t="n">
-        <v>389.2118835449219</v>
+        <v>389.2119140625</v>
       </c>
       <c r="I317" t="n">
         <v>937.56396484375</v>
@@ -10616,7 +10616,7 @@
         <v>37.83000183105469</v>
       </c>
       <c r="H318" t="n">
-        <v>385.8705749511719</v>
+        <v>385.87060546875</v>
       </c>
       <c r="I318" t="n">
         <v>912.8978881835938</v>
@@ -10630,7 +10630,7 @@
         <v>45033</v>
       </c>
       <c r="B319" t="n">
-        <v>1752.971557617188</v>
+        <v>1752.9716796875</v>
       </c>
       <c r="C319" t="n">
         <v>1039.5</v>
@@ -10648,7 +10648,7 @@
         <v>37.88999938964844</v>
       </c>
       <c r="H319" t="n">
-        <v>384.7895812988281</v>
+        <v>384.78955078125</v>
       </c>
       <c r="I319" t="n">
         <v>945.503173828125</v>
@@ -10662,13 +10662,13 @@
         <v>45034</v>
       </c>
       <c r="B320" t="n">
-        <v>1729.14794921875</v>
+        <v>1729.148071289062</v>
       </c>
       <c r="C320" t="n">
         <v>1032.050048828125</v>
       </c>
       <c r="D320" t="n">
-        <v>1847.58837890625</v>
+        <v>1847.588256835938</v>
       </c>
       <c r="E320" t="n">
         <v>952.25</v>
@@ -10680,7 +10680,7 @@
         <v>37.66999816894531</v>
       </c>
       <c r="H320" t="n">
-        <v>376.4363403320312</v>
+        <v>376.4363098144531</v>
       </c>
       <c r="I320" t="n">
         <v>946.7513427734375</v>
@@ -10706,13 +10706,13 @@
         <v>935.7999877929688</v>
       </c>
       <c r="F321" t="n">
-        <v>645.3367309570312</v>
+        <v>645.3367919921875</v>
       </c>
       <c r="G321" t="n">
         <v>37.45999908447266</v>
       </c>
       <c r="H321" t="n">
-        <v>373.4880981445312</v>
+        <v>373.4881286621094</v>
       </c>
       <c r="I321" t="n">
         <v>929.0756225585938</v>
@@ -10726,13 +10726,13 @@
         <v>45036</v>
       </c>
       <c r="B322" t="n">
-        <v>1707.535034179688</v>
+        <v>1707.534790039062</v>
       </c>
       <c r="C322" t="n">
         <v>1011.099975585938</v>
       </c>
       <c r="D322" t="n">
-        <v>1839.553100585938</v>
+        <v>1839.552978515625</v>
       </c>
       <c r="E322" t="n">
         <v>933.0499877929688</v>
@@ -10758,7 +10758,7 @@
         <v>45037</v>
       </c>
       <c r="B323" t="n">
-        <v>1687.7392578125</v>
+        <v>1687.739135742188</v>
       </c>
       <c r="C323" t="n">
         <v>994.9000244140625</v>
@@ -10776,7 +10776,7 @@
         <v>39.84999847412109</v>
       </c>
       <c r="H323" t="n">
-        <v>368.6235961914062</v>
+        <v>368.6236267089844</v>
       </c>
       <c r="I323" t="n">
         <v>916.5428466796875</v>
@@ -10822,7 +10822,7 @@
         <v>45041</v>
       </c>
       <c r="B325" t="n">
-        <v>1705.619140625</v>
+        <v>1705.619262695312</v>
       </c>
       <c r="C325" t="n">
         <v>1012.950012207031</v>
@@ -10886,13 +10886,13 @@
         <v>45043</v>
       </c>
       <c r="B327" t="n">
-        <v>1720.060668945312</v>
+        <v>1720.060546875</v>
       </c>
       <c r="C327" t="n">
         <v>982.2999877929688</v>
       </c>
       <c r="D327" t="n">
-        <v>1849.684448242188</v>
+        <v>1849.684692382812</v>
       </c>
       <c r="E327" t="n">
         <v>917.0499877929688</v>
@@ -10924,7 +10924,7 @@
         <v>1029.449951171875</v>
       </c>
       <c r="D328" t="n">
-        <v>1921.453857421875</v>
+        <v>1921.453979492188</v>
       </c>
       <c r="E328" t="n">
         <v>951</v>
@@ -10936,7 +10936,7 @@
         <v>44.97000122070312</v>
       </c>
       <c r="H328" t="n">
-        <v>389.6541137695312</v>
+        <v>389.6540832519531</v>
       </c>
       <c r="I328" t="n">
         <v>943.7056274414062</v>
@@ -10968,7 +10968,7 @@
         <v>47.18999862670898</v>
       </c>
       <c r="H329" t="n">
-        <v>387.5903625488281</v>
+        <v>387.59033203125</v>
       </c>
       <c r="I329" t="n">
         <v>957.736328125</v>
@@ -10982,13 +10982,13 @@
         <v>45049</v>
       </c>
       <c r="B330" t="n">
-        <v>1712.938232421875</v>
+        <v>1712.938110351562</v>
       </c>
       <c r="C330" t="n">
         <v>993.0499877929688</v>
       </c>
       <c r="D330" t="n">
-        <v>1835.660034179688</v>
+        <v>1835.66015625</v>
       </c>
       <c r="E330" t="n">
         <v>942.0499877929688</v>
@@ -11000,7 +11000,7 @@
         <v>46.33000183105469</v>
       </c>
       <c r="H330" t="n">
-        <v>377.0259704589844</v>
+        <v>377.0260009765625</v>
       </c>
       <c r="I330" t="n">
         <v>921.685791015625</v>
@@ -11014,13 +11014,13 @@
         <v>45050</v>
       </c>
       <c r="B331" t="n">
-        <v>1735.239013671875</v>
+        <v>1735.238891601562</v>
       </c>
       <c r="C331" t="n">
         <v>1011.549987792969</v>
       </c>
       <c r="D331" t="n">
-        <v>1907.77880859375</v>
+        <v>1907.778930664062</v>
       </c>
       <c r="E331" t="n">
         <v>945.5499877929688</v>
@@ -11046,25 +11046,25 @@
         <v>45051</v>
       </c>
       <c r="B332" t="n">
-        <v>1733.618041992188</v>
+        <v>1733.6181640625</v>
       </c>
       <c r="C332" t="n">
         <v>999</v>
       </c>
       <c r="D332" t="n">
-        <v>1916.8125</v>
+        <v>1916.812622070312</v>
       </c>
       <c r="E332" t="n">
         <v>940.5499877929688</v>
       </c>
       <c r="F332" t="n">
-        <v>670.3306884765625</v>
+        <v>670.3307495117188</v>
       </c>
       <c r="G332" t="n">
         <v>47.97000122070312</v>
       </c>
       <c r="H332" t="n">
-        <v>393.6341857910156</v>
+        <v>393.6341552734375</v>
       </c>
       <c r="I332" t="n">
         <v>917.54150390625</v>
@@ -11084,13 +11084,13 @@
         <v>949.0499877929688</v>
       </c>
       <c r="D333" t="n">
-        <v>1884.072021484375</v>
+        <v>1884.072143554688</v>
       </c>
       <c r="E333" t="n">
         <v>917.2999877929688</v>
       </c>
       <c r="F333" t="n">
-        <v>671.5068969726562</v>
+        <v>671.5069580078125</v>
       </c>
       <c r="G333" t="n">
         <v>47.7400016784668</v>
@@ -11110,7 +11110,7 @@
         <v>45055</v>
       </c>
       <c r="B334" t="n">
-        <v>1728.362182617188</v>
+        <v>1728.362060546875</v>
       </c>
       <c r="C334" t="n">
         <v>901.5999755859375</v>
@@ -11142,25 +11142,25 @@
         <v>45056</v>
       </c>
       <c r="B335" t="n">
-        <v>1720.35546875</v>
+        <v>1720.355346679688</v>
       </c>
       <c r="C335" t="n">
         <v>890.6500244140625</v>
       </c>
       <c r="D335" t="n">
-        <v>1888.713500976562</v>
+        <v>1888.713623046875</v>
       </c>
       <c r="E335" t="n">
         <v>902.3499755859375</v>
       </c>
       <c r="F335" t="n">
-        <v>677.289794921875</v>
+        <v>677.2898559570312</v>
       </c>
       <c r="G335" t="n">
         <v>47.63999938964844</v>
       </c>
       <c r="H335" t="n">
-        <v>401.2503662109375</v>
+        <v>401.2503356933594</v>
       </c>
       <c r="I335" t="n">
         <v>834.9547729492188</v>
@@ -11174,7 +11174,7 @@
         <v>45057</v>
       </c>
       <c r="B336" t="n">
-        <v>1754.739990234375</v>
+        <v>1754.739868164062</v>
       </c>
       <c r="C336" t="n">
         <v>917.25</v>
@@ -11186,7 +11186,7 @@
         <v>913.5499877929688</v>
       </c>
       <c r="F336" t="n">
-        <v>694.7366943359375</v>
+        <v>694.7366333007812</v>
       </c>
       <c r="G336" t="n">
         <v>48.52999877929688</v>
@@ -11244,13 +11244,13 @@
         <v>840.5999755859375</v>
       </c>
       <c r="D338" t="n">
-        <v>1912.570190429688</v>
+        <v>1912.570068359375</v>
       </c>
       <c r="E338" t="n">
         <v>868.7000122070312</v>
       </c>
       <c r="F338" t="n">
-        <v>680.279296875</v>
+        <v>680.2793579101562</v>
       </c>
       <c r="G338" t="n">
         <v>47.16999816894531</v>
@@ -11270,7 +11270,7 @@
         <v>45062</v>
       </c>
       <c r="B339" t="n">
-        <v>1752.136596679688</v>
+        <v>1752.136352539062</v>
       </c>
       <c r="C339" t="n">
         <v>812.0999755859375</v>
@@ -11288,7 +11288,7 @@
         <v>47.2400016784668</v>
       </c>
       <c r="H339" t="n">
-        <v>393.9781188964844</v>
+        <v>393.9781494140625</v>
       </c>
       <c r="I339" t="n">
         <v>737.5883178710938</v>
@@ -11302,19 +11302,19 @@
         <v>45063</v>
       </c>
       <c r="B340" t="n">
-        <v>1727.232421875</v>
+        <v>1727.232299804688</v>
       </c>
       <c r="C340" t="n">
         <v>790</v>
       </c>
       <c r="D340" t="n">
-        <v>1896.050048828125</v>
+        <v>1896.050170898438</v>
       </c>
       <c r="E340" t="n">
         <v>875.4000244140625</v>
       </c>
       <c r="F340" t="n">
-        <v>671.0167236328125</v>
+        <v>671.0167846679688</v>
       </c>
       <c r="G340" t="n">
         <v>46.86999893188477</v>
@@ -11334,25 +11334,25 @@
         <v>45064</v>
       </c>
       <c r="B341" t="n">
-        <v>1682.3359375</v>
+        <v>1682.336059570312</v>
       </c>
       <c r="C341" t="n">
         <v>751.5999755859375</v>
       </c>
       <c r="D341" t="n">
-        <v>1886.5673828125</v>
+        <v>1886.567504882812</v>
       </c>
       <c r="E341" t="n">
         <v>860.5499877929688</v>
       </c>
       <c r="F341" t="n">
-        <v>651.7567138671875</v>
+        <v>651.7566528320312</v>
       </c>
       <c r="G341" t="n">
         <v>45.0099983215332</v>
       </c>
       <c r="H341" t="n">
-        <v>392.1600646972656</v>
+        <v>392.1600952148438</v>
       </c>
       <c r="I341" t="n">
         <v>665.7368774414062</v>
@@ -11366,13 +11366,13 @@
         <v>45065</v>
       </c>
       <c r="B342" t="n">
-        <v>1698.64404296875</v>
+        <v>1698.644165039062</v>
       </c>
       <c r="C342" t="n">
         <v>787.3499755859375</v>
       </c>
       <c r="D342" t="n">
-        <v>1952.497436523438</v>
+        <v>1952.49755859375</v>
       </c>
       <c r="E342" t="n">
         <v>896.9500122070312</v>
@@ -11430,7 +11430,7 @@
         <v>45069</v>
       </c>
       <c r="B344" t="n">
-        <v>1787.454223632812</v>
+        <v>1787.454345703125</v>
       </c>
       <c r="C344" t="n">
         <v>868</v>
@@ -11442,7 +11442,7 @@
         <v>988.7999877929688</v>
       </c>
       <c r="F344" t="n">
-        <v>719.4857177734375</v>
+        <v>719.4856567382812</v>
       </c>
       <c r="G344" t="n">
         <v>52.04999923706055</v>
@@ -11494,7 +11494,7 @@
         <v>45071</v>
       </c>
       <c r="B346" t="n">
-        <v>1746.880737304688</v>
+        <v>1746.880615234375</v>
       </c>
       <c r="C346" t="n">
         <v>891.75</v>
@@ -11512,7 +11512,7 @@
         <v>51.83000183105469</v>
       </c>
       <c r="H346" t="n">
-        <v>411.9621887207031</v>
+        <v>411.962158203125</v>
       </c>
       <c r="I346" t="n">
         <v>795.3092651367188</v>
@@ -11526,7 +11526,7 @@
         <v>45072</v>
       </c>
       <c r="B347" t="n">
-        <v>1753.610229492188</v>
+        <v>1753.610107421875</v>
       </c>
       <c r="C347" t="n">
         <v>850.0999755859375</v>
@@ -11544,7 +11544,7 @@
         <v>51.61000061035156</v>
       </c>
       <c r="H347" t="n">
-        <v>417.2197875976562</v>
+        <v>417.2198181152344</v>
       </c>
       <c r="I347" t="n">
         <v>759.6580810546875</v>
@@ -11558,13 +11558,13 @@
         <v>45075</v>
       </c>
       <c r="B348" t="n">
-        <v>1762.844970703125</v>
+        <v>1762.8447265625</v>
       </c>
       <c r="C348" t="n">
         <v>832.2000122070312</v>
       </c>
       <c r="D348" t="n">
-        <v>2529.44775390625</v>
+        <v>2529.447509765625</v>
       </c>
       <c r="E348" t="n">
         <v>977.8499755859375</v>
@@ -11602,7 +11602,7 @@
         <v>966.8499755859375</v>
       </c>
       <c r="F349" t="n">
-        <v>719.4857177734375</v>
+        <v>719.4856567382812</v>
       </c>
       <c r="G349" t="n">
         <v>50.22000122070312</v>
@@ -11622,7 +11622,7 @@
         <v>45077</v>
       </c>
       <c r="B350" t="n">
-        <v>1745.947387695312</v>
+        <v>1745.947143554688</v>
       </c>
       <c r="C350" t="n">
         <v>776.7000122070312</v>
@@ -11640,7 +11640,7 @@
         <v>49.93000030517578</v>
       </c>
       <c r="H350" t="n">
-        <v>416.2862243652344</v>
+        <v>416.2861938476562</v>
       </c>
       <c r="I350" t="n">
         <v>663.2403564453125</v>
@@ -11654,13 +11654,13 @@
         <v>45078</v>
       </c>
       <c r="B351" t="n">
-        <v>1768.64111328125</v>
+        <v>1768.641235351562</v>
       </c>
       <c r="C351" t="n">
         <v>815.5</v>
       </c>
       <c r="D351" t="n">
-        <v>2487.623779296875</v>
+        <v>2487.62353515625</v>
       </c>
       <c r="E351" t="n">
         <v>993.9500122070312</v>
@@ -11692,7 +11692,7 @@
         <v>794.6500244140625</v>
       </c>
       <c r="D352" t="n">
-        <v>2440.609375</v>
+        <v>2440.609619140625</v>
       </c>
       <c r="E352" t="n">
         <v>983.5499877929688</v>
@@ -11718,13 +11718,13 @@
         <v>45082</v>
       </c>
       <c r="B353" t="n">
-        <v>1778.612670898438</v>
+        <v>1778.612548828125</v>
       </c>
       <c r="C353" t="n">
         <v>828</v>
       </c>
       <c r="D353" t="n">
-        <v>2429.529541015625</v>
+        <v>2429.529296875</v>
       </c>
       <c r="E353" t="n">
         <v>987.8499755859375</v>
@@ -11750,7 +11750,7 @@
         <v>45083</v>
       </c>
       <c r="B354" t="n">
-        <v>1823.65625</v>
+        <v>1823.656372070312</v>
       </c>
       <c r="C354" t="n">
         <v>816.25</v>
@@ -11782,19 +11782,19 @@
         <v>45084</v>
       </c>
       <c r="B355" t="n">
-        <v>1819.186279296875</v>
+        <v>1819.186401367188</v>
       </c>
       <c r="C355" t="n">
         <v>837.25</v>
       </c>
       <c r="D355" t="n">
-        <v>2435.119384765625</v>
+        <v>2435.119140625</v>
       </c>
       <c r="E355" t="n">
         <v>985.5499877929688</v>
       </c>
       <c r="F355" t="n">
-        <v>728.9932861328125</v>
+        <v>728.9932250976562</v>
       </c>
       <c r="G355" t="n">
         <v>54.97000122070312</v>
@@ -11826,7 +11826,7 @@
         <v>976</v>
       </c>
       <c r="F356" t="n">
-        <v>721.7890625</v>
+        <v>721.7891235351562</v>
       </c>
       <c r="G356" t="n">
         <v>55.83000183105469</v>
@@ -11852,7 +11852,7 @@
         <v>830.7000122070312</v>
       </c>
       <c r="D357" t="n">
-        <v>2446.6982421875</v>
+        <v>2446.697998046875</v>
       </c>
       <c r="E357" t="n">
         <v>963.6500244140625</v>
@@ -11878,7 +11878,7 @@
         <v>45089</v>
       </c>
       <c r="B358" t="n">
-        <v>1806.218505859375</v>
+        <v>1806.218627929688</v>
       </c>
       <c r="C358" t="n">
         <v>830.4000244140625</v>
@@ -11890,7 +11890,7 @@
         <v>961.0999755859375</v>
       </c>
       <c r="F358" t="n">
-        <v>727.3759765625</v>
+        <v>727.3759155273438</v>
       </c>
       <c r="G358" t="n">
         <v>54.31000137329102</v>
@@ -11928,7 +11928,7 @@
         <v>53.56000137329102</v>
       </c>
       <c r="H359" t="n">
-        <v>451.0258483886719</v>
+        <v>451.02587890625</v>
       </c>
       <c r="I359" t="n">
         <v>662.2416381835938</v>
@@ -11948,7 +11948,7 @@
         <v>808.5499877929688</v>
       </c>
       <c r="D360" t="n">
-        <v>2452.6875</v>
+        <v>2452.687255859375</v>
       </c>
       <c r="E360" t="n">
         <v>957.6500244140625</v>
@@ -11974,13 +11974,13 @@
         <v>45092</v>
       </c>
       <c r="B361" t="n">
-        <v>1817.467041015625</v>
+        <v>1817.467163085938</v>
       </c>
       <c r="C361" t="n">
         <v>814.7000122070312</v>
       </c>
       <c r="D361" t="n">
-        <v>2481.1357421875</v>
+        <v>2481.135498046875</v>
       </c>
       <c r="E361" t="n">
         <v>962.5999755859375</v>
@@ -12006,7 +12006,7 @@
         <v>45093</v>
       </c>
       <c r="B362" t="n">
-        <v>1822.821166992188</v>
+        <v>1822.8212890625</v>
       </c>
       <c r="C362" t="n">
         <v>810.9000244140625</v>
@@ -12018,7 +12018,7 @@
         <v>975.0499877929688</v>
       </c>
       <c r="F362" t="n">
-        <v>732.5708618164062</v>
+        <v>732.57080078125</v>
       </c>
       <c r="G362" t="n">
         <v>53.22000122070312</v>
@@ -12044,19 +12044,19 @@
         <v>806.5999755859375</v>
       </c>
       <c r="D363" t="n">
-        <v>2397.038818359375</v>
+        <v>2397.038330078125</v>
       </c>
       <c r="E363" t="n">
         <v>960.3499755859375</v>
       </c>
       <c r="F363" t="n">
-        <v>721.053955078125</v>
+        <v>721.0540161132812</v>
       </c>
       <c r="G363" t="n">
         <v>52.72999954223633</v>
       </c>
       <c r="H363" t="n">
-        <v>445.0311889648438</v>
+        <v>445.0312194824219</v>
       </c>
       <c r="I363" t="n">
         <v>656.6492919921875</v>
@@ -12108,7 +12108,7 @@
         <v>806.7000122070312</v>
       </c>
       <c r="D365" t="n">
-        <v>2401.580078125</v>
+        <v>2401.580322265625</v>
       </c>
       <c r="E365" t="n">
         <v>977</v>
@@ -12134,13 +12134,13 @@
         <v>45099</v>
       </c>
       <c r="B366" t="n">
-        <v>1799.538208007812</v>
+        <v>1799.5380859375</v>
       </c>
       <c r="C366" t="n">
         <v>804.4000244140625</v>
       </c>
       <c r="D366" t="n">
-        <v>2392.89599609375</v>
+        <v>2392.896240234375</v>
       </c>
       <c r="E366" t="n">
         <v>974.8499755859375</v>
@@ -12152,7 +12152,7 @@
         <v>51.31999969482422</v>
       </c>
       <c r="H366" t="n">
-        <v>437.1693115234375</v>
+        <v>437.1693420410156</v>
       </c>
       <c r="I366" t="n">
         <v>654.252685546875</v>
@@ -12178,13 +12178,13 @@
         <v>959.8499755859375</v>
       </c>
       <c r="F367" t="n">
-        <v>700.1275024414062</v>
+        <v>700.1275634765625</v>
       </c>
       <c r="G367" t="n">
         <v>48.47999954223633</v>
       </c>
       <c r="H367" t="n">
-        <v>418.4482116699219</v>
+        <v>418.4481811523438</v>
       </c>
       <c r="I367" t="n">
         <v>633.43115234375</v>
@@ -12198,19 +12198,19 @@
         <v>45103</v>
       </c>
       <c r="B368" t="n">
-        <v>1760.781982421875</v>
+        <v>1760.78173828125</v>
       </c>
       <c r="C368" t="n">
         <v>770.75</v>
       </c>
       <c r="D368" t="n">
-        <v>2291.4306640625</v>
+        <v>2291.43115234375</v>
       </c>
       <c r="E368" t="n">
         <v>968.4500122070312</v>
       </c>
       <c r="F368" t="n">
-        <v>710.0271606445312</v>
+        <v>710.027099609375</v>
       </c>
       <c r="G368" t="n">
         <v>50.11999893188477</v>
@@ -12230,7 +12230,7 @@
         <v>45104</v>
       </c>
       <c r="B369" t="n">
-        <v>1757.146728515625</v>
+        <v>1757.14697265625</v>
       </c>
       <c r="C369" t="n">
         <v>773.2000122070312</v>
@@ -12262,25 +12262,25 @@
         <v>45105</v>
       </c>
       <c r="B370" t="n">
-        <v>1780.479125976562</v>
+        <v>1780.479248046875</v>
       </c>
       <c r="C370" t="n">
         <v>819.1500244140625</v>
       </c>
       <c r="D370" t="n">
-        <v>2397.637451171875</v>
+        <v>2397.6376953125</v>
       </c>
       <c r="E370" t="n">
         <v>956.6500244140625</v>
       </c>
       <c r="F370" t="n">
-        <v>741.490234375</v>
+        <v>741.4902954101562</v>
       </c>
       <c r="G370" t="n">
         <v>50.93000030517578</v>
       </c>
       <c r="H370" t="n">
-        <v>426.7522888183594</v>
+        <v>426.7523193359375</v>
       </c>
       <c r="I370" t="n">
         <v>653.603515625</v>
@@ -12294,7 +12294,7 @@
         <v>45107</v>
       </c>
       <c r="B371" t="n">
-        <v>1781.805297851562</v>
+        <v>1781.805419921875</v>
       </c>
       <c r="C371" t="n">
         <v>767.25</v>
@@ -12306,7 +12306,7 @@
         <v>945.9000244140625</v>
       </c>
       <c r="F371" t="n">
-        <v>724.58251953125</v>
+        <v>724.5824584960938</v>
       </c>
       <c r="G371" t="n">
         <v>49.97000122070312</v>
@@ -12326,7 +12326,7 @@
         <v>45110</v>
       </c>
       <c r="B372" t="n">
-        <v>1793.005004882812</v>
+        <v>1793.0048828125</v>
       </c>
       <c r="C372" t="n">
         <v>773.25</v>
@@ -12338,7 +12338,7 @@
         <v>942.8499755859375</v>
       </c>
       <c r="F372" t="n">
-        <v>722.7692260742188</v>
+        <v>722.769287109375</v>
       </c>
       <c r="G372" t="n">
         <v>49.68999862670898</v>
@@ -12364,19 +12364,19 @@
         <v>770.5999755859375</v>
       </c>
       <c r="D373" t="n">
-        <v>2383.363525390625</v>
+        <v>2383.36328125</v>
       </c>
       <c r="E373" t="n">
         <v>946</v>
       </c>
       <c r="F373" t="n">
-        <v>726.98388671875</v>
+        <v>726.9839477539062</v>
       </c>
       <c r="G373" t="n">
         <v>49.41999816894531</v>
       </c>
       <c r="H373" t="n">
-        <v>425.2291259765625</v>
+        <v>425.2290954589844</v>
       </c>
       <c r="I373" t="n">
         <v>649.2594604492188</v>
@@ -12390,7 +12390,7 @@
         <v>45112</v>
       </c>
       <c r="B374" t="n">
-        <v>1788.78076171875</v>
+        <v>1788.780639648438</v>
       </c>
       <c r="C374" t="n">
         <v>770</v>
@@ -12408,7 +12408,7 @@
         <v>49.13000106811523</v>
       </c>
       <c r="H374" t="n">
-        <v>424.9342346191406</v>
+        <v>424.9342651367188</v>
       </c>
       <c r="I374" t="n">
         <v>649.0098266601562</v>
@@ -12428,19 +12428,19 @@
         <v>769.3499755859375</v>
       </c>
       <c r="D375" t="n">
-        <v>2398.535888671875</v>
+        <v>2398.53564453125</v>
       </c>
       <c r="E375" t="n">
         <v>962.2000122070312</v>
       </c>
       <c r="F375" t="n">
-        <v>725.3666381835938</v>
+        <v>725.36669921875</v>
       </c>
       <c r="G375" t="n">
         <v>49.29000091552734</v>
       </c>
       <c r="H375" t="n">
-        <v>424.0498046875</v>
+        <v>424.0497741699219</v>
       </c>
       <c r="I375" t="n">
         <v>647.8613891601562</v>
@@ -12460,19 +12460,19 @@
         <v>759.8499755859375</v>
       </c>
       <c r="D376" t="n">
-        <v>2376.42919921875</v>
+        <v>2376.428955078125</v>
       </c>
       <c r="E376" t="n">
         <v>951</v>
       </c>
       <c r="F376" t="n">
-        <v>704.4402465820312</v>
+        <v>704.4403076171875</v>
       </c>
       <c r="G376" t="n">
         <v>48.75</v>
       </c>
       <c r="H376" t="n">
-        <v>413.077880859375</v>
+        <v>413.0779113769531</v>
       </c>
       <c r="I376" t="n">
         <v>642.6165161132812</v>
@@ -12492,7 +12492,7 @@
         <v>749.8499755859375</v>
       </c>
       <c r="D377" t="n">
-        <v>2407.0380859375</v>
+        <v>2407.037841796875</v>
       </c>
       <c r="E377" t="n">
         <v>959.4500122070312</v>
@@ -12524,7 +12524,7 @@
         <v>754.0499877929688</v>
       </c>
       <c r="D378" t="n">
-        <v>2419.6708984375</v>
+        <v>2419.671142578125</v>
       </c>
       <c r="E378" t="n">
         <v>965.1500244140625</v>
@@ -12536,7 +12536,7 @@
         <v>48.84000015258789</v>
       </c>
       <c r="H378" t="n">
-        <v>414.9065246582031</v>
+        <v>414.9065551757812</v>
       </c>
       <c r="I378" t="n">
         <v>640.2689208984375</v>
@@ -12556,7 +12556,7 @@
         <v>752.6500244140625</v>
       </c>
       <c r="D379" t="n">
-        <v>2384.717529296875</v>
+        <v>2384.7177734375</v>
       </c>
       <c r="E379" t="n">
         <v>954.5499877929688</v>
@@ -12588,19 +12588,19 @@
         <v>745.2000122070312</v>
       </c>
       <c r="D380" t="n">
-        <v>2358.90234375</v>
+        <v>2358.902099609375</v>
       </c>
       <c r="E380" t="n">
         <v>947.0499877929688</v>
       </c>
       <c r="F380" t="n">
-        <v>702.969970703125</v>
+        <v>702.9700317382812</v>
       </c>
       <c r="G380" t="n">
         <v>47.43999862670898</v>
       </c>
       <c r="H380" t="n">
-        <v>412.0894165039062</v>
+        <v>412.0894470214844</v>
       </c>
       <c r="I380" t="n">
         <v>629.6292724609375</v>
@@ -12626,7 +12626,7 @@
         <v>965.2000122070312</v>
       </c>
       <c r="F381" t="n">
-        <v>711.6934204101562</v>
+        <v>711.6934814453125</v>
       </c>
       <c r="G381" t="n">
         <v>48.38000106811523</v>
@@ -12684,13 +12684,13 @@
         <v>783</v>
       </c>
       <c r="D383" t="n">
-        <v>2413.678955078125</v>
+        <v>2413.67919921875</v>
       </c>
       <c r="E383" t="n">
         <v>973.75</v>
       </c>
       <c r="F383" t="n">
-        <v>713.7028198242188</v>
+        <v>713.7027587890625</v>
       </c>
       <c r="G383" t="n">
         <v>49.31000137329102</v>
@@ -12722,13 +12722,13 @@
         <v>979.6500244140625</v>
       </c>
       <c r="F384" t="n">
-        <v>716.8882446289062</v>
+        <v>716.8883056640625</v>
       </c>
       <c r="G384" t="n">
         <v>49.13999938964844</v>
       </c>
       <c r="H384" t="n">
-        <v>414.4617004394531</v>
+        <v>414.4617309570312</v>
       </c>
       <c r="I384" t="n">
         <v>640.5186157226562</v>
@@ -12792,7 +12792,7 @@
         <v>48.34999847412109</v>
       </c>
       <c r="H386" t="n">
-        <v>411.2986755371094</v>
+        <v>411.2986450195312</v>
       </c>
       <c r="I386" t="n">
         <v>635.573486328125</v>
@@ -12818,13 +12818,13 @@
         <v>989.1500244140625</v>
       </c>
       <c r="F387" t="n">
-        <v>720.7108764648438</v>
+        <v>720.7109375</v>
       </c>
       <c r="G387" t="n">
         <v>47.59999847412109</v>
       </c>
       <c r="H387" t="n">
-        <v>417.8719482421875</v>
+        <v>417.8719177246094</v>
       </c>
       <c r="I387" t="n">
         <v>630.478515625</v>
@@ -12844,7 +12844,7 @@
         <v>834.8499755859375</v>
       </c>
       <c r="D388" t="n">
-        <v>2463.362548828125</v>
+        <v>2463.36279296875</v>
       </c>
       <c r="E388" t="n">
         <v>1088.050048828125</v>
@@ -12882,7 +12882,7 @@
         <v>1140.400024414062</v>
       </c>
       <c r="F389" t="n">
-        <v>737.7166748046875</v>
+        <v>737.7166137695312</v>
       </c>
       <c r="G389" t="n">
         <v>51.09999847412109</v>
@@ -12984,7 +12984,7 @@
         <v>54.65999984741211</v>
       </c>
       <c r="H392" t="n">
-        <v>457.657470703125</v>
+        <v>457.6575012207031</v>
       </c>
       <c r="I392" t="n">
         <v>663.0464477539062</v>
@@ -13112,7 +13112,7 @@
         <v>55.70000076293945</v>
       </c>
       <c r="H396" t="n">
-        <v>466.3065490722656</v>
+        <v>466.3065185546875</v>
       </c>
       <c r="I396" t="n">
         <v>649.01025390625</v>
@@ -13144,7 +13144,7 @@
         <v>54.65999984741211</v>
       </c>
       <c r="H397" t="n">
-        <v>468.6294250488281</v>
+        <v>468.62939453125</v>
       </c>
       <c r="I397" t="n">
         <v>650.0592651367188</v>
@@ -13164,7 +13164,7 @@
         <v>823.5999755859375</v>
       </c>
       <c r="D398" t="n">
-        <v>2471.25244140625</v>
+        <v>2471.252197265625</v>
       </c>
       <c r="E398" t="n">
         <v>984.2999877929688</v>
@@ -13176,7 +13176,7 @@
         <v>56.04999923706055</v>
       </c>
       <c r="H398" t="n">
-        <v>460.820556640625</v>
+        <v>460.8205871582031</v>
       </c>
       <c r="I398" t="n">
         <v>651.7075805664062</v>
@@ -13208,7 +13208,7 @@
         <v>55.43000030517578</v>
       </c>
       <c r="H399" t="n">
-        <v>457.3114929199219</v>
+        <v>457.3115234375</v>
       </c>
       <c r="I399" t="n">
         <v>646.2129516601562</v>
@@ -13228,7 +13228,7 @@
         <v>820.7999877929688</v>
       </c>
       <c r="D400" t="n">
-        <v>2548.998291015625</v>
+        <v>2548.99853515625</v>
       </c>
       <c r="E400" t="n">
         <v>973.9000244140625</v>
@@ -13240,7 +13240,7 @@
         <v>56.38000106811523</v>
       </c>
       <c r="H400" t="n">
-        <v>451.9244079589844</v>
+        <v>451.9244384765625</v>
       </c>
       <c r="I400" t="n">
         <v>646.2129516601562</v>
@@ -13368,7 +13368,7 @@
         <v>57.31000137329102</v>
       </c>
       <c r="H404" t="n">
-        <v>440.8536682128906</v>
+        <v>440.8536376953125</v>
       </c>
       <c r="I404" t="n">
         <v>633.075927734375</v>
@@ -13400,7 +13400,7 @@
         <v>60.91999816894531</v>
       </c>
       <c r="H405" t="n">
-        <v>447.822265625</v>
+        <v>447.8222961425781</v>
       </c>
       <c r="I405" t="n">
         <v>653.85546875</v>
@@ -13432,7 +13432,7 @@
         <v>64.97000122070312</v>
       </c>
       <c r="H406" t="n">
-        <v>459.8815002441406</v>
+        <v>459.8815307617188</v>
       </c>
       <c r="I406" t="n">
         <v>663.8456420898438</v>
@@ -13464,7 +13464,7 @@
         <v>69.48000335693359</v>
       </c>
       <c r="H407" t="n">
-        <v>458.4482421875</v>
+        <v>458.4482727050781</v>
       </c>
       <c r="I407" t="n">
         <v>671.8876953125</v>
@@ -13496,7 +13496,7 @@
         <v>64.56999969482422</v>
       </c>
       <c r="H408" t="n">
-        <v>448.0694274902344</v>
+        <v>448.0693969726562</v>
       </c>
       <c r="I408" t="n">
         <v>653.5558471679688</v>
@@ -13516,7 +13516,7 @@
         <v>895.1500244140625</v>
       </c>
       <c r="D409" t="n">
-        <v>2536.165771484375</v>
+        <v>2536.16552734375</v>
       </c>
       <c r="E409" t="n">
         <v>983.6500244140625</v>
@@ -13592,7 +13592,7 @@
         <v>64.36000061035156</v>
       </c>
       <c r="H411" t="n">
-        <v>433.7861938476562</v>
+        <v>433.7861328125</v>
       </c>
       <c r="I411" t="n">
         <v>654.9544067382812</v>
@@ -13612,7 +13612,7 @@
         <v>857.1500244140625</v>
       </c>
       <c r="D412" t="n">
-        <v>2503.10986328125</v>
+        <v>2503.109619140625</v>
       </c>
       <c r="E412" t="n">
         <v>974.5</v>
@@ -13624,7 +13624,7 @@
         <v>66.54000091552734</v>
       </c>
       <c r="H412" t="n">
-        <v>436.1090698242188</v>
+        <v>436.1090393066406</v>
       </c>
       <c r="I412" t="n">
         <v>656.1531982421875</v>
@@ -13644,7 +13644,7 @@
         <v>841.7000122070312</v>
       </c>
       <c r="D413" t="n">
-        <v>2509.7509765625</v>
+        <v>2509.751220703125</v>
       </c>
       <c r="E413" t="n">
         <v>970.5</v>
@@ -13656,7 +13656,7 @@
         <v>65.68000030517578</v>
       </c>
       <c r="H413" t="n">
-        <v>438.9261169433594</v>
+        <v>438.9261474609375</v>
       </c>
       <c r="I413" t="n">
         <v>651.8074951171875</v>
@@ -13688,7 +13688,7 @@
         <v>64.26000213623047</v>
       </c>
       <c r="H414" t="n">
-        <v>423.4567565917969</v>
+        <v>423.4567260742188</v>
       </c>
       <c r="I414" t="n">
         <v>635.1738891601562</v>
@@ -13752,7 +13752,7 @@
         <v>68.34999847412109</v>
       </c>
       <c r="H416" t="n">
-        <v>436.0596313476562</v>
+        <v>436.0596008300781</v>
       </c>
       <c r="I416" t="n">
         <v>631.8272094726562</v>
@@ -13784,7 +13784,7 @@
         <v>68.48999786376953</v>
       </c>
       <c r="H417" t="n">
-        <v>435.12060546875</v>
+        <v>435.1205749511719</v>
       </c>
       <c r="I417" t="n">
         <v>632.7762451171875</v>
@@ -13804,7 +13804,7 @@
         <v>855.9500122070312</v>
       </c>
       <c r="D418" t="n">
-        <v>2493.173095703125</v>
+        <v>2493.1728515625</v>
       </c>
       <c r="E418" t="n">
         <v>1006.099975585938</v>
@@ -13816,7 +13816,7 @@
         <v>69.51000213623047</v>
       </c>
       <c r="H418" t="n">
-        <v>432.6988525390625</v>
+        <v>432.6988220214844</v>
       </c>
       <c r="I418" t="n">
         <v>644.065185546875</v>
@@ -13964,7 +13964,7 @@
         <v>836.9000244140625</v>
       </c>
       <c r="D423" t="n">
-        <v>2515.543212890625</v>
+        <v>2515.54296875</v>
       </c>
       <c r="E423" t="n">
         <v>985.7999877929688</v>
@@ -13976,7 +13976,7 @@
         <v>75.41999816894531</v>
       </c>
       <c r="H423" t="n">
-        <v>438.7778930664062</v>
+        <v>438.7778625488281</v>
       </c>
       <c r="I423" t="n">
         <v>635.923095703125</v>
@@ -14072,7 +14072,7 @@
         <v>75</v>
       </c>
       <c r="H426" t="n">
-        <v>431.6115417480469</v>
+        <v>431.6115112304688</v>
       </c>
       <c r="I426" t="n">
         <v>638.5206298828125</v>
@@ -14104,7 +14104,7 @@
         <v>73.68000030517578</v>
       </c>
       <c r="H427" t="n">
-        <v>423.2095947265625</v>
+        <v>423.2096252441406</v>
       </c>
       <c r="I427" t="n">
         <v>636.1729125976562</v>
@@ -14124,7 +14124,7 @@
         <v>847.3499755859375</v>
       </c>
       <c r="D428" t="n">
-        <v>2475.94580078125</v>
+        <v>2475.946044921875</v>
       </c>
       <c r="E428" t="n">
         <v>1023.450012207031</v>
@@ -14136,7 +14136,7 @@
         <v>76.48999786376953</v>
       </c>
       <c r="H428" t="n">
-        <v>421.1832580566406</v>
+        <v>421.1832885742188</v>
       </c>
       <c r="I428" t="n">
         <v>638.9701538085938</v>
@@ -14188,7 +14188,7 @@
         <v>830.4000244140625</v>
       </c>
       <c r="D430" t="n">
-        <v>2478.79248046875</v>
+        <v>2478.792236328125</v>
       </c>
       <c r="E430" t="n">
         <v>1013.799987792969</v>
@@ -14200,7 +14200,7 @@
         <v>76.23000335693359</v>
       </c>
       <c r="H430" t="n">
-        <v>418.0202026367188</v>
+        <v>418.0201721191406</v>
       </c>
       <c r="I430" t="n">
         <v>633.6753540039062</v>
@@ -14220,7 +14220,7 @@
         <v>817.8499755859375</v>
       </c>
       <c r="D431" t="n">
-        <v>2454.67431640625</v>
+        <v>2454.674560546875</v>
       </c>
       <c r="E431" t="n">
         <v>1012.299987792969</v>
@@ -14232,7 +14232,7 @@
         <v>75.5</v>
       </c>
       <c r="H431" t="n">
-        <v>424.7911376953125</v>
+        <v>424.7911682128906</v>
       </c>
       <c r="I431" t="n">
         <v>633.4755249023438</v>
@@ -14252,7 +14252,7 @@
         <v>816.2000122070312</v>
       </c>
       <c r="D432" t="n">
-        <v>2479.99072265625</v>
+        <v>2479.990478515625</v>
       </c>
       <c r="E432" t="n">
         <v>1018.75</v>
@@ -14264,7 +14264,7 @@
         <v>75.06999969482422</v>
       </c>
       <c r="H432" t="n">
-        <v>425.4830627441406</v>
+        <v>425.4830932617188</v>
       </c>
       <c r="I432" t="n">
         <v>627.0319213867188</v>
@@ -14284,7 +14284,7 @@
         <v>830.5</v>
       </c>
       <c r="D433" t="n">
-        <v>2471.95166015625</v>
+        <v>2471.951416015625</v>
       </c>
       <c r="E433" t="n">
         <v>1012.450012207031</v>
@@ -14316,7 +14316,7 @@
         <v>810.25</v>
       </c>
       <c r="D434" t="n">
-        <v>2410.68310546875</v>
+        <v>2410.682861328125</v>
       </c>
       <c r="E434" t="n">
         <v>987.1500244140625</v>
@@ -14328,7 +14328,7 @@
         <v>75.48999786376953</v>
       </c>
       <c r="H434" t="n">
-        <v>419.8982849121094</v>
+        <v>419.8982543945312</v>
       </c>
       <c r="I434" t="n">
         <v>612.6461181640625</v>
@@ -14392,7 +14392,7 @@
         <v>74.41000366210938</v>
       </c>
       <c r="H436" t="n">
-        <v>424.6922912597656</v>
+        <v>424.6923217773438</v>
       </c>
       <c r="I436" t="n">
         <v>610.0986328125</v>
@@ -14444,7 +14444,7 @@
         <v>806</v>
       </c>
       <c r="D438" t="n">
-        <v>2474.797607421875</v>
+        <v>2474.7978515625</v>
       </c>
       <c r="E438" t="n">
         <v>961.25</v>
@@ -14456,7 +14456,7 @@
         <v>72.86000061035156</v>
       </c>
       <c r="H438" t="n">
-        <v>430.6725158691406</v>
+        <v>430.6724853515625</v>
       </c>
       <c r="I438" t="n">
         <v>604.0045776367188</v>
@@ -14476,7 +14476,7 @@
         <v>778.9000244140625</v>
       </c>
       <c r="D439" t="n">
-        <v>2439.344970703125</v>
+        <v>2439.34521484375</v>
       </c>
       <c r="E439" t="n">
         <v>938.9500122070312</v>
@@ -14488,7 +14488,7 @@
         <v>68.40000152587891</v>
       </c>
       <c r="H439" t="n">
-        <v>425.2359619140625</v>
+        <v>425.2359924316406</v>
       </c>
       <c r="I439" t="n">
         <v>589.7186889648438</v>
@@ -14552,7 +14552,7 @@
         <v>69.95999908447266</v>
       </c>
       <c r="H441" t="n">
-        <v>439.9640808105469</v>
+        <v>439.9640502929688</v>
       </c>
       <c r="I441" t="n">
         <v>610.7479858398438</v>
@@ -14604,7 +14604,7 @@
         <v>785.2000122070312</v>
       </c>
       <c r="D443" t="n">
-        <v>2451.279296875</v>
+        <v>2451.279052734375</v>
       </c>
       <c r="E443" t="n">
         <v>948.9000244140625</v>
@@ -14648,7 +14648,7 @@
         <v>65.93000030517578</v>
       </c>
       <c r="H444" t="n">
-        <v>438.1353759765625</v>
+        <v>438.1353454589844</v>
       </c>
       <c r="I444" t="n">
         <v>594.6138916015625</v>
@@ -14732,7 +14732,7 @@
         <v>759.4000244140625</v>
       </c>
       <c r="D447" t="n">
-        <v>2398.99853515625</v>
+        <v>2398.998779296875</v>
       </c>
       <c r="E447" t="n">
         <v>933</v>
@@ -14744,7 +14744,7 @@
         <v>68.88999938964844</v>
       </c>
       <c r="H447" t="n">
-        <v>432.40234375</v>
+        <v>432.4023132324219</v>
       </c>
       <c r="I447" t="n">
         <v>591.3670654296875</v>
@@ -14840,7 +14840,7 @@
         <v>62.54000091552734</v>
       </c>
       <c r="H450" t="n">
-        <v>413.1273193359375</v>
+        <v>413.1273498535156</v>
       </c>
       <c r="I450" t="n">
         <v>549.907958984375</v>
@@ -14860,7 +14860,7 @@
         <v>739.0999755859375</v>
       </c>
       <c r="D451" t="n">
-        <v>2200.263671875</v>
+        <v>2200.263916015625</v>
       </c>
       <c r="E451" t="n">
         <v>848.1500244140625</v>
@@ -14872,7 +14872,7 @@
         <v>65.47000122070312</v>
       </c>
       <c r="H451" t="n">
-        <v>411.4963684082031</v>
+        <v>411.496337890625</v>
       </c>
       <c r="I451" t="n">
         <v>533.224365234375</v>
@@ -14892,7 +14892,7 @@
         <v>764.5</v>
       </c>
       <c r="D452" t="n">
-        <v>2258.685791015625</v>
+        <v>2258.68603515625</v>
       </c>
       <c r="E452" t="n">
         <v>870.9000244140625</v>
@@ -14924,7 +14924,7 @@
         <v>759.25</v>
       </c>
       <c r="D453" t="n">
-        <v>2296.036376953125</v>
+        <v>2296.0361328125</v>
       </c>
       <c r="E453" t="n">
         <v>915.25</v>
@@ -14936,7 +14936,7 @@
         <v>71.58999633789062</v>
       </c>
       <c r="H453" t="n">
-        <v>417.0811462402344</v>
+        <v>417.0811767578125</v>
       </c>
       <c r="I453" t="n">
         <v>563.1448974609375</v>
@@ -14956,7 +14956,7 @@
         <v>769.7999877929688</v>
       </c>
       <c r="D454" t="n">
-        <v>2291.592041015625</v>
+        <v>2291.591796875</v>
       </c>
       <c r="E454" t="n">
         <v>911.6500244140625</v>
@@ -15032,7 +15032,7 @@
         <v>74.58999633789062</v>
       </c>
       <c r="H456" t="n">
-        <v>414.8571166992188</v>
+        <v>414.8571472167969</v>
       </c>
       <c r="I456" t="n">
         <v>553.254638671875</v>
@@ -15180,7 +15180,7 @@
         <v>750.2000122070312</v>
       </c>
       <c r="D461" t="n">
-        <v>2211.69873046875</v>
+        <v>2211.698486328125</v>
       </c>
       <c r="E461" t="n">
         <v>938.0999755859375</v>
@@ -15224,7 +15224,7 @@
         <v>79.87999725341797</v>
       </c>
       <c r="H462" t="n">
-        <v>413.2756042480469</v>
+        <v>413.2755737304688</v>
       </c>
       <c r="I462" t="n">
         <v>538.9686889648438</v>
@@ -15244,7 +15244,7 @@
         <v>759</v>
       </c>
       <c r="D463" t="n">
-        <v>2210.69970703125</v>
+        <v>2210.699951171875</v>
       </c>
       <c r="E463" t="n">
         <v>940.1500244140625</v>
@@ -15276,7 +15276,7 @@
         <v>754.3499755859375</v>
       </c>
       <c r="D464" t="n">
-        <v>2222.434326171875</v>
+        <v>2222.43408203125</v>
       </c>
       <c r="E464" t="n">
         <v>950.1500244140625</v>
@@ -15288,7 +15288,7 @@
         <v>78.19999694824219</v>
       </c>
       <c r="H464" t="n">
-        <v>413.3250122070312</v>
+        <v>413.3249816894531</v>
       </c>
       <c r="I464" t="n">
         <v>539.218505859375</v>
@@ -15308,7 +15308,7 @@
         <v>747.2000122070312</v>
       </c>
       <c r="D465" t="n">
-        <v>2202.96044921875</v>
+        <v>2202.960205078125</v>
       </c>
       <c r="E465" t="n">
         <v>941.3499755859375</v>
@@ -15340,7 +15340,7 @@
         <v>741.2000122070312</v>
       </c>
       <c r="D466" t="n">
-        <v>2205.8564453125</v>
+        <v>2205.856689453125</v>
       </c>
       <c r="E466" t="n">
         <v>936.0999755859375</v>
@@ -15352,7 +15352,7 @@
         <v>77.45999908447266</v>
       </c>
       <c r="H466" t="n">
-        <v>416.240966796875</v>
+        <v>416.2409973144531</v>
       </c>
       <c r="I466" t="n">
         <v>533.5241088867188</v>
@@ -15372,7 +15372,7 @@
         <v>727.5</v>
       </c>
       <c r="D467" t="n">
-        <v>2146.98486328125</v>
+        <v>2146.985107421875</v>
       </c>
       <c r="E467" t="n">
         <v>926.2000122070312</v>
@@ -15436,7 +15436,7 @@
         <v>726.9500122070312</v>
       </c>
       <c r="D469" t="n">
-        <v>2169.75439453125</v>
+        <v>2169.754638671875</v>
       </c>
       <c r="E469" t="n">
         <v>914.4500122070312</v>
@@ -15468,7 +15468,7 @@
         <v>723.0499877929688</v>
       </c>
       <c r="D470" t="n">
-        <v>2172.351318359375</v>
+        <v>2172.35107421875</v>
       </c>
       <c r="E470" t="n">
         <v>930.7000122070312</v>
@@ -15480,7 +15480,7 @@
         <v>76.33999633789062</v>
       </c>
       <c r="H470" t="n">
-        <v>410.8044128417969</v>
+        <v>410.804443359375</v>
       </c>
       <c r="I470" t="n">
         <v>530.0774536132812</v>
@@ -15532,7 +15532,7 @@
         <v>865.0999755859375</v>
       </c>
       <c r="D472" t="n">
-        <v>2420.270263671875</v>
+        <v>2420.2705078125</v>
       </c>
       <c r="E472" t="n">
         <v>1052.800048828125</v>
@@ -15544,7 +15544,7 @@
         <v>89.23999786376953</v>
       </c>
       <c r="H472" t="n">
-        <v>426.2244567871094</v>
+        <v>426.2244262695312</v>
       </c>
       <c r="I472" t="n">
         <v>643.565673828125</v>
@@ -15576,7 +15576,7 @@
         <v>86.62000274658203</v>
       </c>
       <c r="H473" t="n">
-        <v>430.6230773925781</v>
+        <v>430.623046875</v>
       </c>
       <c r="I473" t="n">
         <v>731.8286743164062</v>
@@ -15596,7 +15596,7 @@
         <v>872.6500244140625</v>
       </c>
       <c r="D474" t="n">
-        <v>2355.40673828125</v>
+        <v>2355.406982421875</v>
       </c>
       <c r="E474" t="n">
         <v>1028.800048828125</v>
@@ -15628,7 +15628,7 @@
         <v>854.7000122070312</v>
       </c>
       <c r="D475" t="n">
-        <v>2359.551513671875</v>
+        <v>2359.55126953125</v>
       </c>
       <c r="E475" t="n">
         <v>1026.5</v>
@@ -15704,7 +15704,7 @@
         <v>107.629997253418</v>
       </c>
       <c r="H477" t="n">
-        <v>503.1761169433594</v>
+        <v>503.1760864257812</v>
       </c>
       <c r="I477" t="n">
         <v>876.9855346679688</v>
@@ -15864,7 +15864,7 @@
         <v>103.3899993896484</v>
       </c>
       <c r="H482" t="n">
-        <v>495.5649719238281</v>
+        <v>495.56494140625</v>
       </c>
       <c r="I482" t="n">
         <v>1113.102783203125</v>
@@ -15896,7 +15896,7 @@
         <v>101.1399993896484</v>
       </c>
       <c r="H483" t="n">
-        <v>503.1761169433594</v>
+        <v>503.1760864257812</v>
       </c>
       <c r="I483" t="n">
         <v>1003.560668945312</v>
@@ -16056,7 +16056,7 @@
         <v>101.7600021362305</v>
       </c>
       <c r="H488" t="n">
-        <v>484.790771484375</v>
+        <v>484.7907409667969</v>
       </c>
       <c r="I488" t="n">
         <v>959.75390625</v>
@@ -16184,7 +16184,7 @@
         <v>104.4899978637695</v>
       </c>
       <c r="H492" t="n">
-        <v>511.0343933105469</v>
+        <v>511.0343627929688</v>
       </c>
       <c r="I492" t="n">
         <v>998.1161499023438</v>
@@ -16216,7 +16216,7 @@
         <v>104.6800003051758</v>
       </c>
       <c r="H493" t="n">
-        <v>508.316162109375</v>
+        <v>508.3161315917969</v>
       </c>
       <c r="I493" t="n">
         <v>979.3845825195312</v>
@@ -16280,7 +16280,7 @@
         <v>104.6500015258789</v>
       </c>
       <c r="H495" t="n">
-        <v>528.134765625</v>
+        <v>528.1347045898438</v>
       </c>
       <c r="I495" t="n">
         <v>999.9642944335938</v>
@@ -16364,7 +16364,7 @@
         <v>1179.800048828125</v>
       </c>
       <c r="D498" t="n">
-        <v>2994.304443359375</v>
+        <v>2994.30419921875</v>
       </c>
       <c r="E498" t="n">
         <v>1692.5</v>
@@ -16376,7 +16376,7 @@
         <v>111.7099990844727</v>
       </c>
       <c r="H498" t="n">
-        <v>543.1099853515625</v>
+        <v>543.1099243164062</v>
       </c>
       <c r="I498" t="n">
         <v>1114.001831054688</v>
@@ -16408,7 +16408,7 @@
         <v>110.2200012207031</v>
       </c>
       <c r="H499" t="n">
-        <v>536.091796875</v>
+        <v>536.0918579101562</v>
       </c>
       <c r="I499" t="n">
         <v>1089.47607421875</v>
@@ -16440,7 +16440,7 @@
         <v>108.3399963378906</v>
       </c>
       <c r="H500" t="n">
-        <v>524.08203125</v>
+        <v>524.0820922851562</v>
       </c>
       <c r="I500" t="n">
         <v>1067.197998046875</v>
@@ -16492,7 +16492,7 @@
         <v>1170.300048828125</v>
       </c>
       <c r="D502" t="n">
-        <v>3094.071044921875</v>
+        <v>3094.0712890625</v>
       </c>
       <c r="E502" t="n">
         <v>1723.25</v>
@@ -16588,7 +16588,7 @@
         <v>1152.199951171875</v>
       </c>
       <c r="D505" t="n">
-        <v>3085.3828125</v>
+        <v>3085.382568359375</v>
       </c>
       <c r="E505" t="n">
         <v>1694.800048828125</v>
@@ -16600,7 +16600,7 @@
         <v>108.2300033569336</v>
       </c>
       <c r="H505" t="n">
-        <v>525.3176879882812</v>
+        <v>525.317626953125</v>
       </c>
       <c r="I505" t="n">
         <v>1057.45751953125</v>
@@ -16632,7 +16632,7 @@
         <v>106.4599990844727</v>
       </c>
       <c r="H506" t="n">
-        <v>522.5994262695312</v>
+        <v>522.599365234375</v>
       </c>
       <c r="I506" t="n">
         <v>1025.039672851562</v>
@@ -16664,7 +16664,7 @@
         <v>104.2900009155273</v>
       </c>
       <c r="H507" t="n">
-        <v>514.5433959960938</v>
+        <v>514.5433349609375</v>
       </c>
       <c r="I507" t="n">
         <v>1003.111145019531</v>
@@ -16728,7 +16728,7 @@
         <v>103.3499984741211</v>
       </c>
       <c r="H509" t="n">
-        <v>530.9024658203125</v>
+        <v>530.9024047851562</v>
       </c>
       <c r="I509" t="n">
         <v>989.5245971679688</v>
@@ -16792,7 +16792,7 @@
         <v>103.9899978637695</v>
       </c>
       <c r="H511" t="n">
-        <v>521.3638305664062</v>
+        <v>521.36376953125</v>
       </c>
       <c r="I511" t="n">
         <v>1001.213134765625</v>
@@ -16908,7 +16908,7 @@
         <v>1067.849975585938</v>
       </c>
       <c r="D515" t="n">
-        <v>3137.81298828125</v>
+        <v>3137.812744140625</v>
       </c>
       <c r="E515" t="n">
         <v>1669.449951171875</v>
@@ -16920,7 +16920,7 @@
         <v>112.5400009155273</v>
       </c>
       <c r="H515" t="n">
-        <v>553.8347778320312</v>
+        <v>553.834716796875</v>
       </c>
       <c r="I515" t="n">
         <v>1011.353088378906</v>
@@ -16940,7 +16940,7 @@
         <v>1067.699951171875</v>
       </c>
       <c r="D516" t="n">
-        <v>3149.297607421875</v>
+        <v>3149.29736328125</v>
       </c>
       <c r="E516" t="n">
         <v>1665.949951171875</v>
@@ -16972,7 +16972,7 @@
         <v>1052.050048828125</v>
       </c>
       <c r="D517" t="n">
-        <v>3153.241943359375</v>
+        <v>3153.2421875</v>
       </c>
       <c r="E517" t="n">
         <v>1674.25</v>
@@ -16984,7 +16984,7 @@
         <v>111.879997253418</v>
       </c>
       <c r="H517" t="n">
-        <v>550.9682006835938</v>
+        <v>550.96826171875</v>
       </c>
       <c r="I517" t="n">
         <v>998.2659912109375</v>
@@ -17016,7 +17016,7 @@
         <v>109.2600021362305</v>
       </c>
       <c r="H518" t="n">
-        <v>548.5958862304688</v>
+        <v>548.595947265625</v>
       </c>
       <c r="I518" t="n">
         <v>988.0759887695312</v>
@@ -17048,7 +17048,7 @@
         <v>109.9400024414062</v>
       </c>
       <c r="H519" t="n">
-        <v>560.0620727539062</v>
+        <v>560.06201171875</v>
       </c>
       <c r="I519" t="n">
         <v>993.97021484375</v>
@@ -17080,7 +17080,7 @@
         <v>113.9400024414062</v>
       </c>
       <c r="H520" t="n">
-        <v>561.6436157226562</v>
+        <v>561.6436767578125</v>
       </c>
       <c r="I520" t="n">
         <v>1039.02587890625</v>
@@ -17112,7 +17112,7 @@
         <v>112.7399978637695</v>
       </c>
       <c r="H521" t="n">
-        <v>556.8494873046875</v>
+        <v>556.8495483398438</v>
       </c>
       <c r="I521" t="n">
         <v>1022.092407226562</v>
@@ -17132,7 +17132,7 @@
         <v>1054.699951171875</v>
       </c>
       <c r="D522" t="n">
-        <v>3210.915283203125</v>
+        <v>3210.9150390625</v>
       </c>
       <c r="E522" t="n">
         <v>1880.699951171875</v>
@@ -17144,7 +17144,7 @@
         <v>113.9000015258789</v>
       </c>
       <c r="H522" t="n">
-        <v>569.5513305664062</v>
+        <v>569.55126953125</v>
       </c>
       <c r="I522" t="n">
         <v>1022.741882324219</v>
@@ -17240,7 +17240,7 @@
         <v>112.7799987792969</v>
       </c>
       <c r="H525" t="n">
-        <v>564.3124389648438</v>
+        <v>564.3123779296875</v>
       </c>
       <c r="I525" t="n">
         <v>1009.5048828125</v>
@@ -17260,7 +17260,7 @@
         <v>1052</v>
       </c>
       <c r="D526" t="n">
-        <v>3189.543701171875</v>
+        <v>3189.5439453125</v>
       </c>
       <c r="E526" t="n">
         <v>1900.75</v>
@@ -17324,7 +17324,7 @@
         <v>1074.449951171875</v>
       </c>
       <c r="D528" t="n">
-        <v>3254.457275390625</v>
+        <v>3254.45751953125</v>
       </c>
       <c r="E528" t="n">
         <v>1955.050048828125</v>
@@ -17368,7 +17368,7 @@
         <v>110.7300033569336</v>
       </c>
       <c r="H529" t="n">
-        <v>582.0059204101562</v>
+        <v>582.005859375</v>
       </c>
       <c r="I529" t="n">
         <v>1011.053405761719</v>
@@ -17388,7 +17388,7 @@
         <v>1064.800048828125</v>
       </c>
       <c r="D530" t="n">
-        <v>3218.904541015625</v>
+        <v>3218.90478515625</v>
       </c>
       <c r="E530" t="n">
         <v>1904.949951171875</v>
@@ -17400,7 +17400,7 @@
         <v>108.1500015258789</v>
       </c>
       <c r="H530" t="n">
-        <v>581.0173950195312</v>
+        <v>581.0174560546875</v>
       </c>
       <c r="I530" t="n">
         <v>1020.044494628906</v>
@@ -17420,7 +17420,7 @@
         <v>1058.900024414062</v>
       </c>
       <c r="D531" t="n">
-        <v>3258.701416015625</v>
+        <v>3258.70166015625</v>
       </c>
       <c r="E531" t="n">
         <v>1922.650024414062</v>
@@ -17484,7 +17484,7 @@
         <v>1176.150024414062</v>
       </c>
       <c r="D533" t="n">
-        <v>3323.3154296875</v>
+        <v>3323.315185546875</v>
       </c>
       <c r="E533" t="n">
         <v>1970.449951171875</v>
@@ -17496,7 +17496,7 @@
         <v>114.0899963378906</v>
       </c>
       <c r="H533" t="n">
-        <v>601.577392578125</v>
+        <v>601.5773315429688</v>
       </c>
       <c r="I533" t="n">
         <v>1074.490966796875</v>
@@ -17548,7 +17548,7 @@
         <v>1076.449951171875</v>
       </c>
       <c r="D535" t="n">
-        <v>3214.710205078125</v>
+        <v>3214.7099609375</v>
       </c>
       <c r="E535" t="n">
         <v>1918.150024414062</v>
@@ -17560,7 +17560,7 @@
         <v>109.9199981689453</v>
       </c>
       <c r="H535" t="n">
-        <v>582.45068359375</v>
+        <v>582.4507446289062</v>
       </c>
       <c r="I535" t="n">
         <v>1017.896606445312</v>
@@ -17592,7 +17592,7 @@
         <v>109.9899978637695</v>
       </c>
       <c r="H536" t="n">
-        <v>598.9086303710938</v>
+        <v>598.90869140625</v>
       </c>
       <c r="I536" t="n">
         <v>1024.640014648438</v>
@@ -17612,7 +17612,7 @@
         <v>1072.400024414062</v>
       </c>
       <c r="D537" t="n">
-        <v>3314.3271484375</v>
+        <v>3314.327392578125</v>
       </c>
       <c r="E537" t="n">
         <v>1969.550048828125</v>
@@ -17656,7 +17656,7 @@
         <v>111.9800033569336</v>
       </c>
       <c r="H538" t="n">
-        <v>610.0287475585938</v>
+        <v>610.02880859375</v>
       </c>
       <c r="I538" t="n">
         <v>1024.889770507812</v>
@@ -17676,7 +17676,7 @@
         <v>1070.300048828125</v>
       </c>
       <c r="D539" t="n">
-        <v>3305.78857421875</v>
+        <v>3305.788330078125</v>
       </c>
       <c r="E539" t="n">
         <v>1947.400024414062</v>
@@ -17688,7 +17688,7 @@
         <v>114.7699966430664</v>
       </c>
       <c r="H539" t="n">
-        <v>606.0254516601562</v>
+        <v>606.0255126953125</v>
       </c>
       <c r="I539" t="n">
         <v>1019.145385742188</v>
@@ -17720,7 +17720,7 @@
         <v>115.3399963378906</v>
       </c>
       <c r="H540" t="n">
-        <v>591.3963012695312</v>
+        <v>591.396240234375</v>
       </c>
       <c r="I540" t="n">
         <v>1004.859497070312</v>
@@ -17804,7 +17804,7 @@
         <v>1037.25</v>
       </c>
       <c r="D543" t="n">
-        <v>3118.338623046875</v>
+        <v>3118.3388671875</v>
       </c>
       <c r="E543" t="n">
         <v>1897.099975585938</v>
@@ -17900,7 +17900,7 @@
         <v>1045.849975585938</v>
       </c>
       <c r="D546" t="n">
-        <v>3128.02587890625</v>
+        <v>3128.025634765625</v>
       </c>
       <c r="E546" t="n">
         <v>1902.599975585938</v>
@@ -17912,7 +17912,7 @@
         <v>106.0800018310547</v>
       </c>
       <c r="H546" t="n">
-        <v>593.8179931640625</v>
+        <v>593.8180541992188</v>
       </c>
       <c r="I546" t="n">
         <v>988.0260620117188</v>
@@ -17944,7 +17944,7 @@
         <v>105.879997253418</v>
       </c>
       <c r="H547" t="n">
-        <v>577.90380859375</v>
+        <v>577.9037475585938</v>
       </c>
       <c r="I547" t="n">
         <v>946.317138671875</v>
@@ -17976,7 +17976,7 @@
         <v>103.6399993896484</v>
       </c>
       <c r="H548" t="n">
-        <v>573.60400390625</v>
+        <v>573.6039428710938</v>
       </c>
       <c r="I548" t="n">
         <v>943.7197875976562</v>
@@ -18008,7 +18008,7 @@
         <v>102.9700012207031</v>
       </c>
       <c r="H549" t="n">
-        <v>569.6995849609375</v>
+        <v>569.6995239257812</v>
       </c>
       <c r="I549" t="n">
         <v>935.1781616210938</v>
@@ -18040,7 +18040,7 @@
         <v>104.8499984741211</v>
       </c>
       <c r="H550" t="n">
-        <v>580.42431640625</v>
+        <v>580.4243774414062</v>
       </c>
       <c r="I550" t="n">
         <v>935.1282348632812</v>
@@ -18072,7 +18072,7 @@
         <v>106.2099990844727</v>
       </c>
       <c r="H551" t="n">
-        <v>582.5494995117188</v>
+        <v>582.549560546875</v>
       </c>
       <c r="I551" t="n">
         <v>937.9254150390625</v>
@@ -18092,7 +18092,7 @@
         <v>1045.900024414062</v>
       </c>
       <c r="D552" t="n">
-        <v>3105.805419921875</v>
+        <v>3105.8056640625</v>
       </c>
       <c r="E552" t="n">
         <v>1859</v>
@@ -18136,7 +18136,7 @@
         <v>103.3099975585938</v>
       </c>
       <c r="H553" t="n">
-        <v>594.559326171875</v>
+        <v>594.5593872070312</v>
       </c>
       <c r="I553" t="n">
         <v>918.8941650390625</v>
@@ -18156,7 +18156,7 @@
         <v>1026.699951171875</v>
       </c>
       <c r="D554" t="n">
-        <v>3192.839599609375</v>
+        <v>3192.83935546875</v>
       </c>
       <c r="E554" t="n">
         <v>1835.150024414062</v>
@@ -18232,7 +18232,7 @@
         <v>117.6900024414062</v>
       </c>
       <c r="H556" t="n">
-        <v>627.3762817382812</v>
+        <v>627.376220703125</v>
       </c>
       <c r="I556" t="n">
         <v>975.2886352539062</v>
@@ -18264,7 +18264,7 @@
         <v>123.5699996948242</v>
       </c>
       <c r="H557" t="n">
-        <v>627.6234130859375</v>
+        <v>627.6233520507812</v>
       </c>
       <c r="I557" t="n">
         <v>974.93896484375</v>
@@ -18284,7 +18284,7 @@
         <v>1102</v>
       </c>
       <c r="D558" t="n">
-        <v>3206.521240234375</v>
+        <v>3206.52099609375</v>
       </c>
       <c r="E558" t="n">
         <v>1890.849975585938</v>
@@ -18348,7 +18348,7 @@
         <v>1075.849975585938</v>
       </c>
       <c r="D560" t="n">
-        <v>3220.2529296875</v>
+        <v>3220.252685546875</v>
       </c>
       <c r="E560" t="n">
         <v>1919.099975585938</v>
@@ -18360,7 +18360,7 @@
         <v>122.2099990844727</v>
       </c>
       <c r="H560" t="n">
-        <v>623.274169921875</v>
+        <v>623.2741088867188</v>
       </c>
       <c r="I560" t="n">
         <v>965.847900390625</v>
@@ -18412,7 +18412,7 @@
         <v>1064.25</v>
       </c>
       <c r="D562" t="n">
-        <v>3237.6796875</v>
+        <v>3237.679443359375</v>
       </c>
       <c r="E562" t="n">
         <v>1907.5</v>
@@ -18424,7 +18424,7 @@
         <v>123.5699996948242</v>
       </c>
       <c r="H562" t="n">
-        <v>618.4307861328125</v>
+        <v>618.4307250976562</v>
       </c>
       <c r="I562" t="n">
         <v>960.3533935546875</v>
@@ -18444,7 +18444,7 @@
         <v>1068.900024414062</v>
       </c>
       <c r="D563" t="n">
-        <v>3205.6220703125</v>
+        <v>3205.622314453125</v>
       </c>
       <c r="E563" t="n">
         <v>1884.050048828125</v>
@@ -18456,7 +18456,7 @@
         <v>119.0400009155273</v>
       </c>
       <c r="H563" t="n">
-        <v>601.824462890625</v>
+        <v>601.8245239257812</v>
       </c>
       <c r="I563" t="n">
         <v>947.1163330078125</v>
@@ -18520,7 +18520,7 @@
         <v>120.3199996948242</v>
       </c>
       <c r="H565" t="n">
-        <v>610.4241943359375</v>
+        <v>610.4241333007812</v>
       </c>
       <c r="I565" t="n">
         <v>926.8363647460938</v>
@@ -18552,7 +18552,7 @@
         <v>119.620002746582</v>
       </c>
       <c r="H566" t="n">
-        <v>608.1506958007812</v>
+        <v>608.150634765625</v>
       </c>
       <c r="I566" t="n">
         <v>919.243896484375</v>
@@ -18572,7 +18572,7 @@
         <v>1040.599975585938</v>
       </c>
       <c r="D567" t="n">
-        <v>3022.916015625</v>
+        <v>3022.916259765625</v>
       </c>
       <c r="E567" t="n">
         <v>1770.050048828125</v>
@@ -18604,7 +18604,7 @@
         <v>1042.949951171875</v>
       </c>
       <c r="D568" t="n">
-        <v>3059.267822265625</v>
+        <v>3059.267578125</v>
       </c>
       <c r="E568" t="n">
         <v>1793.75</v>
@@ -18616,7 +18616,7 @@
         <v>119.379997253418</v>
       </c>
       <c r="H568" t="n">
-        <v>609.1885375976562</v>
+        <v>609.1885986328125</v>
       </c>
       <c r="I568" t="n">
         <v>917.6454467773438</v>
@@ -18680,7 +18680,7 @@
         <v>119.3000030517578</v>
       </c>
       <c r="H570" t="n">
-        <v>637.0137329101562</v>
+        <v>637.0137939453125</v>
       </c>
       <c r="I570" t="n">
         <v>918.594482421875</v>
@@ -18700,7 +18700,7 @@
         <v>1050.150024414062</v>
       </c>
       <c r="D571" t="n">
-        <v>3111.0986328125</v>
+        <v>3111.098388671875</v>
       </c>
       <c r="E571" t="n">
         <v>1812.650024414062</v>
@@ -18712,7 +18712,7 @@
         <v>118.4700012207031</v>
       </c>
       <c r="H571" t="n">
-        <v>630.9841918945312</v>
+        <v>630.984130859375</v>
       </c>
       <c r="I571" t="n">
         <v>917.245849609375</v>
@@ -18744,7 +18744,7 @@
         <v>118.3199996948242</v>
       </c>
       <c r="H572" t="n">
-        <v>625.0533447265625</v>
+        <v>625.0532836914062</v>
       </c>
       <c r="I572" t="n">
         <v>918.244873046875</v>
@@ -18776,7 +18776,7 @@
         <v>119.2200012207031</v>
       </c>
       <c r="H573" t="n">
-        <v>622.384521484375</v>
+        <v>622.3845825195312</v>
       </c>
       <c r="I573" t="n">
         <v>918.1448974609375</v>
@@ -18840,7 +18840,7 @@
         <v>121.620002746582</v>
       </c>
       <c r="H575" t="n">
-        <v>618.4801635742188</v>
+        <v>618.4801025390625</v>
       </c>
       <c r="I575" t="n">
         <v>931.2320556640625</v>
@@ -18872,7 +18872,7 @@
         <v>120.9400024414062</v>
       </c>
       <c r="H576" t="n">
-        <v>615.2676391601562</v>
+        <v>615.267578125</v>
       </c>
       <c r="I576" t="n">
         <v>929.4837646484375</v>
@@ -18904,7 +18904,7 @@
         <v>117.8099975585938</v>
       </c>
       <c r="H577" t="n">
-        <v>600.440673828125</v>
+        <v>600.4407348632812</v>
       </c>
       <c r="I577" t="n">
         <v>916.2468872070312</v>
@@ -19000,7 +19000,7 @@
         <v>122.5599975585938</v>
       </c>
       <c r="H580" t="n">
-        <v>567.6731567382812</v>
+        <v>567.6732177734375</v>
       </c>
       <c r="I580" t="n">
         <v>877.6848754882812</v>
@@ -19032,7 +19032,7 @@
         <v>120.620002746582</v>
       </c>
       <c r="H581" t="n">
-        <v>575.0866088867188</v>
+        <v>575.086669921875</v>
       </c>
       <c r="I581" t="n">
         <v>866.1961669921875</v>
@@ -19084,7 +19084,7 @@
         <v>1022.049987792969</v>
       </c>
       <c r="D583" t="n">
-        <v>3033.501953125</v>
+        <v>3033.502197265625</v>
       </c>
       <c r="E583" t="n">
         <v>1788.800048828125</v>
@@ -19096,7 +19096,7 @@
         <v>125.6100006103516</v>
       </c>
       <c r="H583" t="n">
-        <v>603.1589965820312</v>
+        <v>603.1590576171875</v>
       </c>
       <c r="I583" t="n">
         <v>908.054931640625</v>
@@ -19128,7 +19128,7 @@
         <v>127.9499969482422</v>
       </c>
       <c r="H584" t="n">
-        <v>606.173828125</v>
+        <v>606.1737670898438</v>
       </c>
       <c r="I584" t="n">
         <v>915.6973266601562</v>
@@ -19160,7 +19160,7 @@
         <v>128.0700073242188</v>
       </c>
       <c r="H585" t="n">
-        <v>608.2990112304688</v>
+        <v>608.2989501953125</v>
       </c>
       <c r="I585" t="n">
         <v>905.906982421875</v>
@@ -19212,7 +19212,7 @@
         <v>1061.400024414062</v>
       </c>
       <c r="D587" t="n">
-        <v>3113.34521484375</v>
+        <v>3113.345458984375</v>
       </c>
       <c r="E587" t="n">
         <v>1859.349975585938</v>
@@ -19244,7 +19244,7 @@
         <v>1086.949951171875</v>
       </c>
       <c r="D588" t="n">
-        <v>3136.764404296875</v>
+        <v>3136.76416015625</v>
       </c>
       <c r="E588" t="n">
         <v>1866.449951171875</v>
@@ -19276,7 +19276,7 @@
         <v>1099.599975585938</v>
       </c>
       <c r="D589" t="n">
-        <v>3382.7861328125</v>
+        <v>3382.785888671875</v>
       </c>
       <c r="E589" t="n">
         <v>1888.800048828125</v>
@@ -19308,7 +19308,7 @@
         <v>1106.699951171875</v>
       </c>
       <c r="D590" t="n">
-        <v>3380.43896484375</v>
+        <v>3380.439208984375</v>
       </c>
       <c r="E590" t="n">
         <v>1926.650024414062</v>
@@ -19340,7 +19340,7 @@
         <v>1104.349975585938</v>
       </c>
       <c r="D591" t="n">
-        <v>3284.6669921875</v>
+        <v>3284.666748046875</v>
       </c>
       <c r="E591" t="n">
         <v>1929.5</v>
@@ -19384,7 +19384,7 @@
         <v>135.7799987792969</v>
       </c>
       <c r="H592" t="n">
-        <v>622.384521484375</v>
+        <v>622.3845825195312</v>
       </c>
       <c r="I592" t="n">
         <v>950.7628173828125</v>
@@ -19404,7 +19404,7 @@
         <v>1085.699951171875</v>
       </c>
       <c r="D593" t="n">
-        <v>3254.457275390625</v>
+        <v>3254.45751953125</v>
       </c>
       <c r="E593" t="n">
         <v>1879.599975585938</v>
@@ -19416,7 +19416,7 @@
         <v>135.8500061035156</v>
       </c>
       <c r="H593" t="n">
-        <v>622.829345703125</v>
+        <v>622.8292846679688</v>
       </c>
       <c r="I593" t="n">
         <v>949.813720703125</v>
@@ -19468,7 +19468,7 @@
         <v>1122.800048828125</v>
       </c>
       <c r="D595" t="n">
-        <v>3406.803955078125</v>
+        <v>3406.8037109375</v>
       </c>
       <c r="E595" t="n">
         <v>1908.349975585938</v>
@@ -19500,7 +19500,7 @@
         <v>1221.949951171875</v>
       </c>
       <c r="D596" t="n">
-        <v>3640.392333984375</v>
+        <v>3640.39208984375</v>
       </c>
       <c r="E596" t="n">
         <v>2038</v>
@@ -19512,7 +19512,7 @@
         <v>174.8999938964844</v>
       </c>
       <c r="H596" t="n">
-        <v>663.0596313476562</v>
+        <v>663.0596923828125</v>
       </c>
       <c r="I596" t="n">
         <v>1118.297729492188</v>
@@ -19576,7 +19576,7 @@
         <v>145.3300018310547</v>
       </c>
       <c r="H598" t="n">
-        <v>591.9893798828125</v>
+        <v>591.9894409179688</v>
       </c>
       <c r="I598" t="n">
         <v>935.3280029296875</v>
@@ -19628,7 +19628,7 @@
         <v>1020.049987792969</v>
       </c>
       <c r="D600" t="n">
-        <v>3215.259521484375</v>
+        <v>3215.25927734375</v>
       </c>
       <c r="E600" t="n">
         <v>1864.25</v>
@@ -19640,7 +19640,7 @@
         <v>153.4100036621094</v>
       </c>
       <c r="H600" t="n">
-        <v>614.1307983398438</v>
+        <v>614.130859375</v>
       </c>
       <c r="I600" t="n">
         <v>977.1367797851562</v>
@@ -19660,7 +19660,7 @@
         <v>1026.800048828125</v>
       </c>
       <c r="D601" t="n">
-        <v>3215.808837890625</v>
+        <v>3215.80859375</v>
       </c>
       <c r="E601" t="n">
         <v>1880.349975585938</v>
@@ -19724,7 +19724,7 @@
         <v>1020.5</v>
       </c>
       <c r="D603" t="n">
-        <v>3214.76025390625</v>
+        <v>3214.760009765625</v>
       </c>
       <c r="E603" t="n">
         <v>1827.349975585938</v>
@@ -19800,7 +19800,7 @@
         <v>149.3500061035156</v>
       </c>
       <c r="H605" t="n">
-        <v>671.4066772460938</v>
+        <v>671.4066162109375</v>
       </c>
       <c r="I605" t="n">
         <v>945.8179321289062</v>
@@ -19832,7 +19832,7 @@
         <v>149.6300048828125</v>
       </c>
       <c r="H606" t="n">
-        <v>668.3331298828125</v>
+        <v>668.3331909179688</v>
       </c>
       <c r="I606" t="n">
         <v>939.5724487304688</v>
@@ -19864,7 +19864,7 @@
         <v>147.7299957275391</v>
       </c>
       <c r="H607" t="n">
-        <v>661.0955810546875</v>
+        <v>661.0956420898438</v>
       </c>
       <c r="I607" t="n">
         <v>926.731689453125</v>
@@ -20024,7 +20024,7 @@
         <v>143.9799957275391</v>
       </c>
       <c r="H612" t="n">
-        <v>651.4290161132812</v>
+        <v>651.4290771484375</v>
       </c>
       <c r="I612" t="n">
         <v>893.0060424804688</v>
@@ -20056,7 +20056,7 @@
         <v>143.1399993896484</v>
       </c>
       <c r="H613" t="n">
-        <v>654.998291015625</v>
+        <v>654.9982299804688</v>
       </c>
       <c r="I613" t="n">
         <v>902.1494140625</v>
@@ -20152,7 +20152,7 @@
         <v>142.1199951171875</v>
       </c>
       <c r="H616" t="n">
-        <v>686.4270629882812</v>
+        <v>686.427001953125</v>
       </c>
       <c r="I616" t="n">
         <v>903.9481201171875</v>
@@ -20504,7 +20504,7 @@
         <v>139.8999938964844</v>
       </c>
       <c r="H627" t="n">
-        <v>684.3450317382812</v>
+        <v>684.344970703125</v>
       </c>
       <c r="I627" t="n">
         <v>889.4585571289062</v>
@@ -20568,7 +20568,7 @@
         <v>139.2299957275391</v>
       </c>
       <c r="H629" t="n">
-        <v>681.221923828125</v>
+        <v>681.2219848632812</v>
       </c>
       <c r="I629" t="n">
         <v>885.4614868164062</v>
@@ -20600,7 +20600,7 @@
         <v>139.4799957275391</v>
       </c>
       <c r="H630" t="n">
-        <v>685.435546875</v>
+        <v>685.4356079101562</v>
       </c>
       <c r="I630" t="n">
         <v>878.5164794921875</v>
@@ -20952,7 +20952,7 @@
         <v>138.3800048828125</v>
       </c>
       <c r="H641" t="n">
-        <v>637.7966918945312</v>
+        <v>637.796630859375</v>
       </c>
       <c r="I641" t="n">
         <v>874.7692260742188</v>
@@ -20984,7 +20984,7 @@
         <v>138.3099975585938</v>
       </c>
       <c r="H642" t="n">
-        <v>633.0377197265625</v>
+        <v>633.0377807617188</v>
       </c>
       <c r="I642" t="n">
         <v>874.3694458007812</v>
@@ -21112,7 +21112,7 @@
         <v>134.8099975585938</v>
       </c>
       <c r="H646" t="n">
-        <v>617.86865234375</v>
+        <v>617.8685913085938</v>
       </c>
       <c r="I646" t="n">
         <v>842.6423950195312</v>
@@ -21176,7 +21176,7 @@
         <v>139.3999938964844</v>
       </c>
       <c r="H648" t="n">
-        <v>628.2787475585938</v>
+        <v>628.27880859375</v>
       </c>
       <c r="I648" t="n">
         <v>855.73291015625</v>
@@ -21240,7 +21240,7 @@
         <v>139.0299987792969</v>
       </c>
       <c r="H650" t="n">
-        <v>623.8668212890625</v>
+        <v>623.8668823242188</v>
       </c>
       <c r="I650" t="n">
         <v>858.430908203125</v>
@@ -21304,7 +21304,7 @@
         <v>135.1600036621094</v>
       </c>
       <c r="H652" t="n">
-        <v>628.1795654296875</v>
+        <v>628.1796264648438</v>
       </c>
       <c r="I652" t="n">
         <v>857.6815185546875</v>
@@ -21400,7 +21400,7 @@
         <v>128.3099975585938</v>
       </c>
       <c r="H655" t="n">
-        <v>611.1267700195312</v>
+        <v>611.1268310546875</v>
       </c>
       <c r="I655" t="n">
         <v>848.1883544921875</v>
@@ -21432,7 +21432,7 @@
         <v>128.8600006103516</v>
       </c>
       <c r="H656" t="n">
-        <v>607.2601318359375</v>
+        <v>607.2601928710938</v>
       </c>
       <c r="I656" t="n">
         <v>836.8965454101562</v>
@@ -21464,7 +21464,7 @@
         <v>126.4100036621094</v>
       </c>
       <c r="H657" t="n">
-        <v>611.7711791992188</v>
+        <v>611.771240234375</v>
       </c>
       <c r="I657" t="n">
         <v>829.7515869140625</v>
@@ -21528,7 +21528,7 @@
         <v>131.8200073242188</v>
       </c>
       <c r="H659" t="n">
-        <v>612.5148315429688</v>
+        <v>612.5147705078125</v>
       </c>
       <c r="I659" t="n">
         <v>850.4866943359375</v>
@@ -21624,7 +21624,7 @@
         <v>126.9400024414062</v>
       </c>
       <c r="H662" t="n">
-        <v>617.918212890625</v>
+        <v>617.9181518554688</v>
       </c>
       <c r="I662" t="n">
         <v>826.1542358398438</v>
@@ -21656,7 +21656,7 @@
         <v>127.0400009155273</v>
       </c>
       <c r="H663" t="n">
-        <v>624.7592163085938</v>
+        <v>624.7591552734375</v>
       </c>
       <c r="I663" t="n">
         <v>814.1629028320312</v>
@@ -21720,7 +21720,7 @@
         <v>125.4400024414062</v>
       </c>
       <c r="H665" t="n">
-        <v>617.6703491210938</v>
+        <v>617.6702880859375</v>
       </c>
       <c r="I665" t="n">
         <v>804.2200317382812</v>
@@ -21784,7 +21784,7 @@
         <v>126.6900024414062</v>
       </c>
       <c r="H667" t="n">
-        <v>624.2138061523438</v>
+        <v>624.2138671875</v>
       </c>
       <c r="I667" t="n">
         <v>800.1729736328125</v>
@@ -21848,7 +21848,7 @@
         <v>133.2700042724609</v>
       </c>
       <c r="H669" t="n">
-        <v>617.6703491210938</v>
+        <v>617.6702880859375</v>
       </c>
       <c r="I669" t="n">
         <v>798.9238891601562</v>
@@ -21944,7 +21944,7 @@
         <v>133.0299987792969</v>
       </c>
       <c r="H672" t="n">
-        <v>611.2754516601562</v>
+        <v>611.2755126953125</v>
       </c>
       <c r="I672" t="n">
         <v>788.1317138671875</v>
@@ -22200,7 +22200,7 @@
         <v>128.9499969482422</v>
       </c>
       <c r="H680" t="n">
-        <v>612.1678466796875</v>
+        <v>612.1677856445312</v>
       </c>
       <c r="I680" t="n">
         <v>771.6935424804688</v>
@@ -22424,7 +22424,7 @@
         <v>126.8899993896484</v>
       </c>
       <c r="H687" t="n">
-        <v>583.8621215820312</v>
+        <v>583.862060546875</v>
       </c>
       <c r="I687" t="n">
         <v>753.806396484375</v>
@@ -22488,7 +22488,7 @@
         <v>125.1600036621094</v>
       </c>
       <c r="H689" t="n">
-        <v>584.0108032226562</v>
+        <v>584.0107421875</v>
       </c>
       <c r="I689" t="n">
         <v>746.2618408203125</v>
@@ -22648,7 +22648,7 @@
         <v>117.5699996948242</v>
       </c>
       <c r="H694" t="n">
-        <v>551.0947875976562</v>
+        <v>551.0947265625</v>
       </c>
       <c r="I694" t="n">
         <v>699.9452514648438</v>
@@ -22712,7 +22712,7 @@
         <v>118.4599990844727</v>
       </c>
       <c r="H696" t="n">
-        <v>547.9717407226562</v>
+        <v>547.9718017578125</v>
       </c>
       <c r="I696" t="n">
         <v>723.6282348632812</v>
@@ -22776,7 +22776,7 @@
         <v>118.4599990844727</v>
       </c>
       <c r="H698" t="n">
-        <v>570.0809326171875</v>
+        <v>570.0809936523438</v>
       </c>
       <c r="I698" t="n">
         <v>710.3876953125</v>
@@ -22808,7 +22808,7 @@
         <v>118.4100036621094</v>
       </c>
       <c r="H699" t="n">
-        <v>574.74072265625</v>
+        <v>574.7407836914062</v>
       </c>
       <c r="I699" t="n">
         <v>713.0357666015625</v>
@@ -22840,7 +22840,7 @@
         <v>118.5400009155273</v>
       </c>
       <c r="H700" t="n">
-        <v>575.58349609375</v>
+        <v>575.5834350585938</v>
       </c>
       <c r="I700" t="n">
         <v>717.8323364257812</v>
@@ -22968,7 +22968,7 @@
         <v>123.2600021362305</v>
       </c>
       <c r="H704" t="n">
-        <v>577.66552734375</v>
+        <v>577.6655883789062</v>
       </c>
       <c r="I704" t="n">
         <v>741.7650756835938</v>
@@ -23128,7 +23128,7 @@
         <v>109.4000015258789</v>
       </c>
       <c r="H709" t="n">
-        <v>540.6845703125</v>
+        <v>540.6846313476562</v>
       </c>
       <c r="I709" t="n">
         <v>678.4107666015625</v>
@@ -23160,7 +23160,7 @@
         <v>109.8199996948242</v>
       </c>
       <c r="H710" t="n">
-        <v>539.8419189453125</v>
+        <v>539.8418579101562</v>
       </c>
       <c r="I710" t="n">
         <v>683.4072265625</v>
@@ -23224,7 +23224,7 @@
         <v>104.8199996948242</v>
       </c>
       <c r="H712" t="n">
-        <v>544.8486328125</v>
+        <v>544.8486938476562</v>
       </c>
       <c r="I712" t="n">
         <v>671.2659301757812</v>
@@ -23352,7 +23352,7 @@
         <v>87.52999877929688</v>
       </c>
       <c r="H716" t="n">
-        <v>489.4764709472656</v>
+        <v>489.4765014648438</v>
       </c>
       <c r="I716" t="n">
         <v>579.032470703125</v>
@@ -23448,7 +23448,7 @@
         <v>110.9599990844727</v>
       </c>
       <c r="H719" t="n">
-        <v>526.953125</v>
+        <v>526.9530639648438</v>
       </c>
       <c r="I719" t="n">
         <v>811.7645874023438</v>
@@ -23640,7 +23640,7 @@
         <v>107.1800003051758</v>
       </c>
       <c r="H725" t="n">
-        <v>566.41259765625</v>
+        <v>566.4126586914062</v>
       </c>
       <c r="I725" t="n">
         <v>728.9743041992188</v>
@@ -23800,7 +23800,7 @@
         <v>105.9800033569336</v>
       </c>
       <c r="H730" t="n">
-        <v>572.0142822265625</v>
+        <v>572.0143432617188</v>
       </c>
       <c r="I730" t="n">
         <v>712.1864013671875</v>
@@ -23928,7 +23928,7 @@
         <v>99.58000183105469</v>
       </c>
       <c r="H734" t="n">
-        <v>544.1051025390625</v>
+        <v>544.1050415039062</v>
       </c>
       <c r="I734" t="n">
         <v>673.864013671875</v>
@@ -23992,7 +23992,7 @@
         <v>99.19999694824219</v>
       </c>
       <c r="H736" t="n">
-        <v>538.453857421875</v>
+        <v>538.4537963867188</v>
       </c>
       <c r="I736" t="n">
         <v>670.466552734375</v>
@@ -24024,7 +24024,7 @@
         <v>101.4300003051758</v>
       </c>
       <c r="H737" t="n">
-        <v>544.1051025390625</v>
+        <v>544.1050415039062</v>
       </c>
       <c r="I737" t="n">
         <v>671.5157470703125</v>
@@ -24088,7 +24088,7 @@
         <v>107.8899993896484</v>
       </c>
       <c r="H739" t="n">
-        <v>539.9410400390625</v>
+        <v>539.9409790039062</v>
       </c>
       <c r="I739" t="n">
         <v>750.6087036132812</v>
@@ -24120,7 +24120,7 @@
         <v>105.8899993896484</v>
       </c>
       <c r="H740" t="n">
-        <v>531.21630859375</v>
+        <v>531.2162475585938</v>
       </c>
       <c r="I740" t="n">
         <v>760.5015869140625</v>
@@ -24184,7 +24184,7 @@
         <v>104.3600006103516</v>
       </c>
       <c r="H742" t="n">
-        <v>545.1460571289062</v>
+        <v>545.1461181640625</v>
       </c>
       <c r="I742" t="n">
         <v>733.9207763671875</v>
@@ -24216,7 +24216,7 @@
         <v>104.0899963378906</v>
       </c>
       <c r="H743" t="n">
-        <v>544.0059814453125</v>
+        <v>544.0059204101562</v>
       </c>
       <c r="I743" t="n">
         <v>727.1256713867188</v>
@@ -24280,7 +24280,7 @@
         <v>101.9700012207031</v>
       </c>
       <c r="H745" t="n">
-        <v>531.166748046875</v>
+        <v>531.1666870117188</v>
       </c>
       <c r="I745" t="n">
         <v>702.793212890625</v>
@@ -24312,7 +24312,7 @@
         <v>100.9899978637695</v>
       </c>
       <c r="H746" t="n">
-        <v>533.447021484375</v>
+        <v>533.4470825195312</v>
       </c>
       <c r="I746" t="n">
         <v>704.4420166015625</v>
@@ -24344,7 +24344,7 @@
         <v>99.58000183105469</v>
       </c>
       <c r="H747" t="n">
-        <v>520.7565307617188</v>
+        <v>520.756591796875</v>
       </c>
       <c r="I747" t="n">
         <v>681.658447265625</v>
@@ -24408,7 +24408,7 @@
         <v>89.98000335693359</v>
       </c>
       <c r="H749" t="n">
-        <v>488.9807739257812</v>
+        <v>488.9807434082031</v>
       </c>
       <c r="I749" t="n">
         <v>627.747314453125</v>
@@ -24600,7 +24600,7 @@
         <v>105.75</v>
       </c>
       <c r="H755" t="n">
-        <v>527.2009887695312</v>
+        <v>527.200927734375</v>
       </c>
       <c r="I755" t="n">
         <v>665.81982421875</v>
@@ -24664,7 +24664,7 @@
         <v>104.3600006103516</v>
       </c>
       <c r="H757" t="n">
-        <v>544.1051025390625</v>
+        <v>544.1050415039062</v>
       </c>
       <c r="I757" t="n">
         <v>657.775634765625</v>
@@ -24696,7 +24696,7 @@
         <v>102.9700012207031</v>
       </c>
       <c r="H758" t="n">
-        <v>547.0794677734375</v>
+        <v>547.0794067382812</v>
       </c>
       <c r="I758" t="n">
         <v>641.0377197265625</v>
@@ -24760,7 +24760,7 @@
         <v>99.44000244140625</v>
       </c>
       <c r="H760" t="n">
-        <v>538.5034790039062</v>
+        <v>538.50341796875</v>
       </c>
       <c r="I760" t="n">
         <v>615.6060791015625</v>
@@ -25016,7 +25016,7 @@
         <v>100.6900024414062</v>
       </c>
       <c r="H768" t="n">
-        <v>509.7515869140625</v>
+        <v>509.7515563964844</v>
       </c>
       <c r="I768" t="n">
         <v>634.2426147460938</v>
@@ -25208,7 +25208,7 @@
         <v>97.73000335693359</v>
       </c>
       <c r="H774" t="n">
-        <v>485.3124084472656</v>
+        <v>485.3123779296875</v>
       </c>
       <c r="I774" t="n">
         <v>573.3366088867188</v>
@@ -25240,7 +25240,7 @@
         <v>98.05000305175781</v>
       </c>
       <c r="H775" t="n">
-        <v>484.1226806640625</v>
+        <v>484.1226501464844</v>
       </c>
       <c r="I775" t="n">
         <v>574.0360717773438</v>
@@ -25272,7 +25272,7 @@
         <v>96.94999694824219</v>
       </c>
       <c r="H776" t="n">
-        <v>482.5859375</v>
+        <v>482.5859069824219</v>
       </c>
       <c r="I776" t="n">
         <v>578.9824829101562</v>
@@ -25304,7 +25304,7 @@
         <v>96.51000213623047</v>
       </c>
       <c r="H777" t="n">
-        <v>475.7944946289062</v>
+        <v>475.7945251464844</v>
       </c>
       <c r="I777" t="n">
         <v>582.2301635742188</v>
@@ -25432,7 +25432,7 @@
         <v>99.55999755859375</v>
       </c>
       <c r="H781" t="n">
-        <v>465.2356262207031</v>
+        <v>465.2356567382812</v>
       </c>
       <c r="I781" t="n">
         <v>578.6326904296875</v>
@@ -25464,7 +25464,7 @@
         <v>99.44999694824219</v>
       </c>
       <c r="H782" t="n">
-        <v>465.7809448242188</v>
+        <v>465.7809143066406</v>
       </c>
       <c r="I782" t="n">
         <v>580.33154296875</v>
@@ -25496,7 +25496,7 @@
         <v>95.79000091552734</v>
       </c>
       <c r="H783" t="n">
-        <v>460.972412109375</v>
+        <v>460.9724426269531</v>
       </c>
       <c r="I783" t="n">
         <v>556.74853515625</v>
@@ -25528,7 +25528,7 @@
         <v>96.62999725341797</v>
       </c>
       <c r="H784" t="n">
-        <v>467.7638244628906</v>
+        <v>467.7637939453125</v>
       </c>
       <c r="I784" t="n">
         <v>551.40234375</v>
@@ -25560,7 +25560,7 @@
         <v>96.65000152587891</v>
       </c>
       <c r="H785" t="n">
-        <v>470.9364318847656</v>
+        <v>470.9364624023438</v>
       </c>
       <c r="I785" t="n">
         <v>546.7557373046875</v>
@@ -25624,7 +25624,7 @@
         <v>100.629997253418</v>
       </c>
       <c r="H787" t="n">
-        <v>494.2353820800781</v>
+        <v>494.2354125976562</v>
       </c>
       <c r="I787" t="n">
         <v>595.4706420898438</v>
@@ -25688,7 +25688,7 @@
         <v>101.0100021362305</v>
       </c>
       <c r="H789" t="n">
-        <v>485.4115600585938</v>
+        <v>485.4115295410156</v>
       </c>
       <c r="I789" t="n">
         <v>605.3135375976562</v>
@@ -25816,7 +25816,7 @@
         <v>102.2399978637695</v>
       </c>
       <c r="H793" t="n">
-        <v>486.3534240722656</v>
+        <v>486.3533935546875</v>
       </c>
       <c r="I793" t="n">
         <v>602.9151611328125</v>
@@ -25848,7 +25848,7 @@
         <v>102.2399978637695</v>
       </c>
       <c r="H794" t="n">
-        <v>486.3534240722656</v>
+        <v>486.3533935546875</v>
       </c>
       <c r="I794" t="n">
         <v>602.9151611328125</v>
@@ -25912,7 +25912,7 @@
         <v>103.9300003051758</v>
       </c>
       <c r="H796" t="n">
-        <v>500.3823547363281</v>
+        <v>500.3823852539062</v>
       </c>
       <c r="I796" t="n">
         <v>619.2034912109375</v>
@@ -26040,7 +26040,7 @@
         <v>99.56999969482422</v>
       </c>
       <c r="H800" t="n">
-        <v>527.8949584960938</v>
+        <v>527.89501953125</v>
       </c>
       <c r="I800" t="n">
         <v>597.6190795898438</v>
@@ -26104,7 +26104,7 @@
         <v>101.8600006103516</v>
       </c>
       <c r="H802" t="n">
-        <v>533.7444458007812</v>
+        <v>533.7445068359375</v>
       </c>
       <c r="I802" t="n">
         <v>602.165771484375</v>
@@ -26168,7 +26168,7 @@
         <v>102.7099990844727</v>
       </c>
       <c r="H804" t="n">
-        <v>529.4812622070312</v>
+        <v>529.4813232421875</v>
       </c>
       <c r="I804" t="n">
         <v>598.3185424804688</v>
@@ -26264,7 +26264,7 @@
         <v>101.9899978637695</v>
       </c>
       <c r="H807" t="n">
-        <v>520.7069702148438</v>
+        <v>520.70703125</v>
       </c>
       <c r="I807" t="n">
         <v>569.2894897460938</v>
@@ -26360,7 +26360,7 @@
         <v>103.6500015258789</v>
       </c>
       <c r="H810" t="n">
-        <v>543.9564208984375</v>
+        <v>543.9563598632812</v>
       </c>
       <c r="I810" t="n">
         <v>591.6233520507812</v>
@@ -26456,7 +26456,7 @@
         <v>109.9400024414062</v>
       </c>
       <c r="H813" t="n">
-        <v>564.9254150390625</v>
+        <v>564.9254760742188</v>
       </c>
       <c r="I813" t="n">
         <v>607.8116455078125</v>
@@ -26616,7 +26616,7 @@
         <v>109.870002746582</v>
       </c>
       <c r="H818" t="n">
-        <v>544.0059814453125</v>
+        <v>544.0059204101562</v>
       </c>
       <c r="I818" t="n">
         <v>599.567626953125</v>
@@ -26712,7 +26712,7 @@
         <v>106.4100036621094</v>
       </c>
       <c r="H821" t="n">
-        <v>535.0829467773438</v>
+        <v>535.0830078125</v>
       </c>
       <c r="I821" t="n">
         <v>599.7674560546875</v>
@@ -26776,7 +26776,7 @@
         <v>111.2900009155273</v>
       </c>
       <c r="H823" t="n">
-        <v>536.7684326171875</v>
+        <v>536.7683715820312</v>
       </c>
       <c r="I823" t="n">
         <v>665.0704345703125</v>
@@ -26872,7 +26872,7 @@
         <v>104.0400009155273</v>
       </c>
       <c r="H826" t="n">
-        <v>519.9138793945312</v>
+        <v>519.913818359375</v>
       </c>
       <c r="I826" t="n">
         <v>609.3106079101562</v>
@@ -27128,7 +27128,7 @@
         <v>111.2399978637695</v>
       </c>
       <c r="H834" t="n">
-        <v>557.24169921875</v>
+        <v>557.2417602539062</v>
       </c>
       <c r="I834" t="n">
         <v>659.4744873046875</v>
@@ -27288,7 +27288,7 @@
         <v>110.5100021362305</v>
       </c>
       <c r="H839" t="n">
-        <v>557.8861694335938</v>
+        <v>557.88623046875</v>
       </c>
       <c r="I839" t="n">
         <v>673.8140869140625</v>
@@ -27320,7 +27320,7 @@
         <v>110.1399993896484</v>
       </c>
       <c r="H840" t="n">
-        <v>556.84521484375</v>
+        <v>556.8451538085938</v>
       </c>
       <c r="I840" t="n">
         <v>672.5150146484375</v>
@@ -27352,7 +27352,7 @@
         <v>110.3899993896484</v>
       </c>
       <c r="H841" t="n">
-        <v>556.6469116210938</v>
+        <v>556.6468505859375</v>
       </c>
       <c r="I841" t="n">
         <v>680.2594604492188</v>
@@ -27544,7 +27544,7 @@
         <v>111.0500030517578</v>
       </c>
       <c r="H847" t="n">
-        <v>550.4007568359375</v>
+        <v>550.4008178710938</v>
       </c>
       <c r="I847" t="n">
         <v>679.4600219726562</v>
@@ -27576,7 +27576,7 @@
         <v>112.620002746582</v>
       </c>
       <c r="H848" t="n">
-        <v>555.2092895507812</v>
+        <v>555.209228515625</v>
       </c>
       <c r="I848" t="n">
         <v>690.3021850585938</v>
@@ -39430,7 +39430,7 @@
         <v>2.208437546514141</v>
       </c>
       <c r="H19" t="n">
-        <v>2.556976611417694</v>
+        <v>2.556964913081172</v>
       </c>
       <c r="I19" t="n">
         <v>13.92037319151405</v>
@@ -39462,7 +39462,7 @@
         <v>4.466918343308368</v>
       </c>
       <c r="H20" t="n">
-        <v>0.250775626255817</v>
+        <v>0.2507755975789339</v>
       </c>
       <c r="I20" t="n">
         <v>-0.3982815934182926</v>
@@ -39494,7 +39494,7 @@
         <v>6.336777990196563</v>
       </c>
       <c r="H21" t="n">
-        <v>15.78663533429408</v>
+        <v>15.78664090943846</v>
       </c>
       <c r="I21" t="n">
         <v>8.157585240054344</v>
@@ -39526,7 +39526,7 @@
         <v>-6.673809932633279</v>
       </c>
       <c r="H22" t="n">
-        <v>-9.331122166279437</v>
+        <v>-9.33111616376282</v>
       </c>
       <c r="I22" t="n">
         <v>-13.36494203556915</v>
@@ -39558,7 +39558,7 @@
         <v>-3.069222796045945</v>
       </c>
       <c r="H23" t="n">
-        <v>-4.292649304045937</v>
+        <v>-4.292638307557917</v>
       </c>
       <c r="I23" t="n">
         <v>-15.49833074613296</v>
@@ -39590,7 +39590,7 @@
         <v>-4.569213893886648</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8090252038547074</v>
+        <v>0.8090252975613055</v>
       </c>
       <c r="I24" t="n">
         <v>-6.315008228225805</v>
@@ -39622,7 +39622,7 @@
         <v>-6.394467498322587</v>
       </c>
       <c r="H25" t="n">
-        <v>-8.448882121149136</v>
+        <v>-8.44888301707284</v>
       </c>
       <c r="I25" t="n">
         <v>13.08554187517776</v>
@@ -39654,7 +39654,7 @@
         <v>-9.67004132070446</v>
       </c>
       <c r="H26" t="n">
-        <v>-8.220688992032056</v>
+        <v>-8.220698724355202</v>
       </c>
       <c r="I26" t="n">
         <v>-8.664971619347462</v>
@@ -39686,7 +39686,7 @@
         <v>3.812983091364663</v>
       </c>
       <c r="H27" t="n">
-        <v>2.511957438194501</v>
+        <v>2.511947210787713</v>
       </c>
       <c r="I27" t="n">
         <v>-5.280900942650235</v>
@@ -39718,7 +39718,7 @@
         <v>-13.94240303127289</v>
       </c>
       <c r="H28" t="n">
-        <v>-9.250694296187289</v>
+        <v>-9.250685242315114</v>
       </c>
       <c r="I28" t="n">
         <v>-7.280448841020104</v>
@@ -39770,7 +39770,7 @@
         <v>-11.17296649328798</v>
       </c>
       <c r="D30" t="n">
-        <v>-6.82890662348562</v>
+        <v>-6.828899946596989</v>
       </c>
       <c r="E30" t="n">
         <v>-6.264570350682453</v>
@@ -39802,7 +39802,7 @@
         <v>5.407444639185499</v>
       </c>
       <c r="D31" t="n">
-        <v>11.67545404992583</v>
+        <v>11.67544604696602</v>
       </c>
       <c r="E31" t="n">
         <v>6.158036863040528</v>
@@ -39834,7 +39834,7 @@
         <v>3.749878429044062</v>
       </c>
       <c r="D32" t="n">
-        <v>-4.454043016634746</v>
+        <v>-4.454035710708237</v>
       </c>
       <c r="E32" t="n">
         <v>-2.043429665210794</v>
@@ -39866,7 +39866,7 @@
         <v>-3.582666599871998</v>
       </c>
       <c r="D33" t="n">
-        <v>-2.687642332260465</v>
+        <v>-2.687649773254319</v>
       </c>
       <c r="E33" t="n">
         <v>-3.160867674766898</v>
@@ -39878,7 +39878,7 @@
         <v>-2.936626775408835</v>
       </c>
       <c r="H33" t="n">
-        <v>1.064517683991228</v>
+        <v>1.064507384443547</v>
       </c>
       <c r="I33" t="n">
         <v>-9.662174131992574</v>
@@ -39898,7 +39898,7 @@
         <v>-0.2809383404587251</v>
       </c>
       <c r="D34" t="n">
-        <v>4.563966710865652</v>
+        <v>4.563974846568541</v>
       </c>
       <c r="E34" t="n">
         <v>13.51343881245972</v>
@@ -39910,7 +39910,7 @@
         <v>-2.265863720466688</v>
       </c>
       <c r="H34" t="n">
-        <v>8.138501651251051</v>
+        <v>8.138524589079953</v>
       </c>
       <c r="I34" t="n">
         <v>1.313777198310517</v>
@@ -39930,7 +39930,7 @@
         <v>2.113313467457556</v>
       </c>
       <c r="D35" t="n">
-        <v>10.28625297200523</v>
+        <v>10.28624439107486</v>
       </c>
       <c r="E35" t="n">
         <v>4.536628125978392</v>
@@ -39942,7 +39942,7 @@
         <v>7.150340115695419</v>
       </c>
       <c r="H35" t="n">
-        <v>7.563832778485602</v>
+        <v>7.563820924453313</v>
       </c>
       <c r="I35" t="n">
         <v>2.469761078617028</v>
@@ -39962,7 +39962,7 @@
         <v>19.83612797148144</v>
       </c>
       <c r="D36" t="n">
-        <v>20.79244208958237</v>
+        <v>20.79242956930774</v>
       </c>
       <c r="E36" t="n">
         <v>55.22938610073884</v>
@@ -39994,7 +39994,7 @@
         <v>13.36061811535836</v>
       </c>
       <c r="D37" t="n">
-        <v>2.784732017019165</v>
+        <v>2.784753621212066</v>
       </c>
       <c r="E37" t="n">
         <v>12.8503286652526</v>
@@ -40026,7 +40026,7 @@
         <v>-4.992287837955112</v>
       </c>
       <c r="D38" t="n">
-        <v>-4.940137680600209</v>
+        <v>-4.940138180910026</v>
       </c>
       <c r="E38" t="n">
         <v>-7.648280214024627</v>
@@ -40038,7 +40038,7 @@
         <v>-3.815071313970964</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.0823883492873545</v>
+        <v>-0.08238108742454342</v>
       </c>
       <c r="I38" t="n">
         <v>-7.982062235232867</v>
@@ -40058,7 +40058,7 @@
         <v>-0.20937399858032</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.2211389159423538</v>
+        <v>-0.2211490209924283</v>
       </c>
       <c r="E39" t="n">
         <v>6.299466802567633</v>
@@ -40070,7 +40070,7 @@
         <v>17.47587201091527</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.8403388597050476</v>
+        <v>-0.8403389202663925</v>
       </c>
       <c r="I39" t="n">
         <v>-3.546709236722645</v>
@@ -40102,7 +40102,7 @@
         <v>17.56312168975038</v>
       </c>
       <c r="H40" t="n">
-        <v>-7.472993734546418</v>
+        <v>-7.473006572657748</v>
       </c>
       <c r="I40" t="n">
         <v>-4.203711321909543</v>
@@ -40116,7 +40116,7 @@
         <v>45138</v>
       </c>
       <c r="B41" t="n">
-        <v>11.82700102606444</v>
+        <v>11.82699336487048</v>
       </c>
       <c r="C41" t="n">
         <v>6.966440170352728</v>
@@ -40128,13 +40128,13 @@
         <v>15.58304478376236</v>
       </c>
       <c r="F41" t="n">
-        <v>5.928875396325339</v>
+        <v>5.92888431923726</v>
       </c>
       <c r="G41" t="n">
         <v>9.385628401317447</v>
       </c>
       <c r="H41" t="n">
-        <v>9.344480114409626</v>
+        <v>9.344487405733215</v>
       </c>
       <c r="I41" t="n">
         <v>1.429263020790783</v>
@@ -40148,7 +40148,7 @@
         <v>45107</v>
       </c>
       <c r="B42" t="n">
-        <v>2.053779535910483</v>
+        <v>2.053800798011629</v>
       </c>
       <c r="C42" t="n">
         <v>-1.216687531673721</v>
@@ -40160,13 +40160,13 @@
         <v>-3.252530162210432</v>
       </c>
       <c r="F42" t="n">
-        <v>0.05414181514649119</v>
+        <v>0.05413338709308047</v>
       </c>
       <c r="G42" t="n">
         <v>0.08011399015193099</v>
       </c>
       <c r="H42" t="n">
-        <v>0.5429566903628613</v>
+        <v>0.5429640610794095</v>
       </c>
       <c r="I42" t="n">
         <v>-1.437947532468964</v>
@@ -40180,13 +40180,13 @@
         <v>45077</v>
       </c>
       <c r="B43" t="n">
-        <v>0.814023064127789</v>
+        <v>0.8140089670256812</v>
       </c>
       <c r="C43" t="n">
         <v>-24.55194044908406</v>
       </c>
       <c r="D43" t="n">
-        <v>29.52805333994046</v>
+        <v>29.52804511100025</v>
       </c>
       <c r="E43" t="n">
         <v>2.807572261517488</v>
@@ -40198,7 +40198,7 @@
         <v>11.02957293714546</v>
       </c>
       <c r="H43" t="n">
-        <v>6.834808014231619</v>
+        <v>6.834808549531513</v>
       </c>
       <c r="I43" t="n">
         <v>-29.71957174362697</v>
@@ -40218,19 +40218,19 @@
         <v>3.66547140892719</v>
       </c>
       <c r="D44" t="n">
-        <v>9.968859779442596</v>
+        <v>9.968874448585474</v>
       </c>
       <c r="E44" t="n">
         <v>7.927137678102603</v>
       </c>
       <c r="F44" t="n">
-        <v>7.817663148343112</v>
+        <v>7.817673773248646</v>
       </c>
       <c r="G44" t="n">
         <v>17.35386633308638</v>
       </c>
       <c r="H44" t="n">
-        <v>8.466701768317897</v>
+        <v>8.466693273242566</v>
       </c>
       <c r="I44" t="n">
         <v>8.902338132359366</v>
@@ -40250,13 +40250,13 @@
         <v>54.46413907015047</v>
       </c>
       <c r="D45" t="n">
-        <v>28.34623358431443</v>
+        <v>28.34621310918004</v>
       </c>
       <c r="E45" t="n">
         <v>81.56811180262491</v>
       </c>
       <c r="F45" t="n">
-        <v>6.658815870198675</v>
+        <v>6.658794148900937</v>
       </c>
       <c r="G45" t="n">
         <v>30.96377100161289</v>
@@ -40276,25 +40276,25 @@
         <v>44985</v>
       </c>
       <c r="B46" t="n">
-        <v>-12.02052577896658</v>
+        <v>-12.02052022497403</v>
       </c>
       <c r="C46" t="n">
         <v>-63.75986333629861</v>
       </c>
       <c r="D46" t="n">
-        <v>-54.13934321739424</v>
+        <v>-54.13933910520381</v>
       </c>
       <c r="E46" t="n">
         <v>-60.34806944094112</v>
       </c>
       <c r="F46" t="n">
-        <v>-3.297159119784521</v>
+        <v>-3.297148955633478</v>
       </c>
       <c r="G46" t="n">
         <v>-34.62913019188968</v>
       </c>
       <c r="H46" t="n">
-        <v>-14.73079992965691</v>
+        <v>-14.73080652967672</v>
       </c>
       <c r="I46" t="n">
         <v>-67.81378140307258</v>
@@ -40308,25 +40308,25 @@
         <v>44957</v>
       </c>
       <c r="B47" t="n">
-        <v>-19.38483105268873</v>
+        <v>-19.38482793661753</v>
       </c>
       <c r="C47" t="n">
         <v>-31.48595153036594</v>
       </c>
       <c r="D47" t="n">
-        <v>-22.92302425975112</v>
+        <v>-22.92301937376114</v>
       </c>
       <c r="E47" t="n">
         <v>-36.64458052185531</v>
       </c>
       <c r="F47" t="n">
-        <v>-25.11306682409529</v>
+        <v>-25.11306112398533</v>
       </c>
       <c r="G47" t="n">
         <v>-25.28793450920587</v>
       </c>
       <c r="H47" t="n">
-        <v>-23.44972119173867</v>
+        <v>-23.44971526658171</v>
       </c>
       <c r="I47" t="n">
         <v>-42.91130019100711</v>
@@ -40340,19 +40340,19 @@
         <v>44926</v>
       </c>
       <c r="B48" t="n">
-        <v>-4.745927627890323</v>
+        <v>-4.745928088014839</v>
       </c>
       <c r="C48" t="n">
         <v>-10.97644834106928</v>
       </c>
       <c r="D48" t="n">
-        <v>-1.51994188246356</v>
+        <v>-1.519948125216897</v>
       </c>
       <c r="E48" t="n">
         <v>-8.726669084425943</v>
       </c>
       <c r="F48" t="n">
-        <v>-7.139618401668146</v>
+        <v>-7.139625469848454</v>
       </c>
       <c r="G48" t="n">
         <v>-9.977464913384882</v>
@@ -40372,7 +40372,7 @@
         <v>44895</v>
       </c>
       <c r="B49" t="n">
-        <v>7.235496356655302</v>
+        <v>7.235474811139953</v>
       </c>
       <c r="C49" t="n">
         <v>-13.14539844090323</v>
@@ -40404,7 +40404,7 @@
         <v>44865</v>
       </c>
       <c r="B50" t="n">
-        <v>-1.04940031916041</v>
+        <v>-1.049379852050869</v>
       </c>
       <c r="C50" t="n">
         <v>1.790379399037678</v>
@@ -40422,7 +40422,7 @@
         <v>-10.33466386438756</v>
       </c>
       <c r="H50" t="n">
-        <v>3.365025301034952</v>
+        <v>3.36503152654235</v>
       </c>
       <c r="I50" t="n">
         <v>7.87460157490274</v>
@@ -40436,13 +40436,13 @@
         <v>44834</v>
       </c>
       <c r="B51" t="n">
-        <v>5.041969223002041</v>
+        <v>5.041958416775416</v>
       </c>
       <c r="C51" t="n">
         <v>-16.93892268070564</v>
       </c>
       <c r="D51" t="n">
-        <v>8.183191880428421</v>
+        <v>8.183183597063959</v>
       </c>
       <c r="E51" t="n">
         <v>-7.199733431542765</v>
@@ -40454,7 +40454,7 @@
         <v>-9.771716243293183</v>
       </c>
       <c r="H51" t="n">
-        <v>25.37386069556771</v>
+        <v>25.3738531445044</v>
       </c>
       <c r="I51" t="n">
         <v>-10.81722885248916</v>
@@ -40468,13 +40468,13 @@
         <v>44804</v>
       </c>
       <c r="B52" t="n">
-        <v>3.245936540603456</v>
+        <v>3.245925021466056</v>
       </c>
       <c r="C52" t="n">
         <v>27.37007418275781</v>
       </c>
       <c r="D52" t="n">
-        <v>24.33247771800031</v>
+        <v>24.33248723788313</v>
       </c>
       <c r="E52" t="n">
         <v>12.02464734774498</v>
@@ -40486,7 +40486,7 @@
         <v>31.85220530081916</v>
       </c>
       <c r="H52" t="n">
-        <v>9.725183453655561</v>
+        <v>9.725192544846495</v>
       </c>
       <c r="I52" t="n">
         <v>19.75408293669523</v>
@@ -40500,7 +40500,7 @@
         <v>44773</v>
       </c>
       <c r="B53" t="n">
-        <v>4.969477660673838</v>
+        <v>4.96948937210786</v>
       </c>
       <c r="C53" t="n">
         <v>25.70898148157286</v>
@@ -40518,7 +40518,7 @@
         <v>19.44074810734559</v>
       </c>
       <c r="H53" t="n">
-        <v>3.250685599129</v>
+        <v>3.250677044378025</v>
       </c>
       <c r="I53" t="n">
         <v>30.6988562453963</v>
@@ -40532,13 +40532,13 @@
         <v>44742</v>
       </c>
       <c r="B54" t="n">
-        <v>-3.477523248148151</v>
+        <v>-3.477534159208084</v>
       </c>
       <c r="C54" t="n">
         <v>20.37225802159368</v>
       </c>
       <c r="D54" t="n">
-        <v>1.077246624996753</v>
+        <v>1.077258035184014</v>
       </c>
       <c r="E54" t="n">
         <v>2.151990548444327</v>
@@ -40564,13 +40564,13 @@
         <v>44712</v>
       </c>
       <c r="B55" t="n">
-        <v>-5.603502733415966</v>
+        <v>-5.603502135480998</v>
       </c>
       <c r="C55" t="n">
         <v>-26.33088367090877</v>
       </c>
       <c r="D55" t="n">
-        <v>-7.051877972794152</v>
+        <v>-7.051888465317379</v>
       </c>
       <c r="E55" t="n">
         <v>-34.47516583955436</v>
@@ -40596,7 +40596,7 @@
         <v>44681</v>
       </c>
       <c r="B56" t="n">
-        <v>11.25278549721549</v>
+        <v>11.25279736870752</v>
       </c>
       <c r="C56" t="n">
         <v>17.7923744286306</v>
@@ -40614,7 +40614,7 @@
         <v>51.45866829146802</v>
       </c>
       <c r="H56" t="n">
-        <v>24.37760979872503</v>
+        <v>24.37762270562873</v>
       </c>
       <c r="I56" t="n">
         <v>14.00827300201519</v>
@@ -40628,28 +40628,28 @@
         <v>44651</v>
       </c>
       <c r="B57" t="n">
-        <v>2.977292721997449</v>
+        <v>2.977305310912381</v>
       </c>
       <c r="C57" t="n">
         <v>10.95155597333577</v>
       </c>
       <c r="D57" t="n">
-        <v>22.51816766035562</v>
+        <v>22.51817677539005</v>
       </c>
       <c r="E57" t="n">
         <v>3.867848856109002</v>
       </c>
       <c r="F57" t="n">
-        <v>9.427572246958405</v>
+        <v>9.427562548959667</v>
       </c>
       <c r="G57" t="n">
         <v>49.57575942530777</v>
       </c>
       <c r="H57" t="n">
-        <v>-2.747507433571683</v>
+        <v>-2.747517525648757</v>
       </c>
       <c r="I57" t="n">
-        <v>35.33523406391175</v>
+        <v>35.33522364866361</v>
       </c>
       <c r="J57" t="n">
         <v>52.09380234505863</v>
@@ -40660,19 +40660,19 @@
         <v>44620</v>
       </c>
       <c r="B58" t="n">
-        <v>-8.601111826336716</v>
+        <v>-8.601133212213041</v>
       </c>
       <c r="C58" t="n">
         <v>8.295696174558387</v>
       </c>
       <c r="D58" t="n">
-        <v>-4.110902753671142</v>
+        <v>-4.110909887571157</v>
       </c>
       <c r="E58" t="n">
         <v>-1.834542248835702</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.228550610003543</v>
+        <v>-1.228541856401</v>
       </c>
       <c r="G58" t="n">
         <v>16.47058823529413</v>
@@ -40681,7 +40681,7 @@
         <v>-13.93947252815208</v>
       </c>
       <c r="I58" t="n">
-        <v>-12.77968968676688</v>
+        <v>-12.77967711983119</v>
       </c>
       <c r="J58" t="n">
         <v>34.45945945945945</v>
@@ -40996,7 +40996,7 @@
         <v>15.01079994493293</v>
       </c>
       <c r="H8" t="n">
-        <v>7.655597813986703</v>
+        <v>7.655585503272211</v>
       </c>
       <c r="I8" t="n">
         <v>12.18075339219475</v>
@@ -41028,7 +41028,7 @@
         <v>-3.805835114293932</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4759148328340679</v>
+        <v>0.4759378669163983</v>
       </c>
       <c r="I9" t="n">
         <v>-20.819919136813</v>
@@ -41060,7 +41060,7 @@
         <v>-19.30960692134881</v>
       </c>
       <c r="H10" t="n">
-        <v>-15.29523148281967</v>
+        <v>-15.29524121514283</v>
       </c>
       <c r="I10" t="n">
         <v>-3.235852580585286</v>
@@ -41112,7 +41112,7 @@
         <v>-2.858671177731864</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.5851564065741277</v>
+        <v>-0.5851488048130182</v>
       </c>
       <c r="E12" t="n">
         <v>-2.52567773584268</v>
@@ -41144,7 +41144,7 @@
         <v>-1.821663765539083</v>
       </c>
       <c r="D13" t="n">
-        <v>12.22030028450933</v>
+        <v>12.22029170357897</v>
       </c>
       <c r="E13" t="n">
         <v>14.91233715805025</v>
@@ -41176,7 +41176,7 @@
         <v>29.06510336315953</v>
       </c>
       <c r="D14" t="n">
-        <v>18.02270127741525</v>
+        <v>18.02271323010156</v>
       </c>
       <c r="E14" t="n">
         <v>61.77885432844141</v>
@@ -41188,7 +41188,7 @@
         <v>39.13101305001452</v>
       </c>
       <c r="H14" t="n">
-        <v>22.62241185496832</v>
+        <v>22.62242076698209</v>
       </c>
       <c r="I14" t="n">
         <v>61.10068807325739</v>
@@ -41202,25 +41202,25 @@
         <v>45199</v>
       </c>
       <c r="B15" t="n">
-        <v>11.51389277013355</v>
+        <v>11.5138851303904</v>
       </c>
       <c r="C15" t="n">
         <v>5.604431410883026</v>
       </c>
       <c r="D15" t="n">
-        <v>1.131437219214715</v>
+        <v>1.131426977183203</v>
       </c>
       <c r="E15" t="n">
         <v>4.360925989567699</v>
       </c>
       <c r="F15" t="n">
-        <v>12.37027821111969</v>
+        <v>12.37028767662276</v>
       </c>
       <c r="G15" t="n">
         <v>51.07063441994313</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3229764699508975</v>
+        <v>0.3229691786272859</v>
       </c>
       <c r="I15" t="n">
         <v>-6.280707078016201</v>
@@ -41234,19 +41234,19 @@
         <v>45107</v>
       </c>
       <c r="B16" t="n">
-        <v>8.787178143930685</v>
+        <v>8.78718559686893</v>
       </c>
       <c r="C16" t="n">
         <v>-22.73802835392045</v>
       </c>
       <c r="D16" t="n">
-        <v>36.42491991731245</v>
+        <v>36.4249294484241</v>
       </c>
       <c r="E16" t="n">
         <v>7.348351382394469</v>
       </c>
       <c r="F16" t="n">
-        <v>16.98842962045543</v>
+        <v>16.98843129458243</v>
       </c>
       <c r="G16" t="n">
         <v>30.40188313846057</v>
@@ -41266,19 +41266,19 @@
         <v>45016</v>
       </c>
       <c r="B17" t="n">
-        <v>-31.71691250225065</v>
+        <v>-31.71690555226574</v>
       </c>
       <c r="C17" t="n">
         <v>-61.64719560517645</v>
       </c>
       <c r="D17" t="n">
-        <v>-54.63216397994308</v>
+        <v>-54.63216427358078</v>
       </c>
       <c r="E17" t="n">
         <v>-54.3871000029952</v>
       </c>
       <c r="F17" t="n">
-        <v>-22.76004075566347</v>
+        <v>-22.76004248807164</v>
       </c>
       <c r="G17" t="n">
         <v>-36.03738976394022</v>
@@ -41298,25 +41298,25 @@
         <v>44926</v>
       </c>
       <c r="B18" t="n">
-        <v>1.074254997477486</v>
+        <v>1.074255107991839</v>
       </c>
       <c r="C18" t="n">
         <v>-21.29460874309583</v>
       </c>
       <c r="D18" t="n">
-        <v>11.65015835466292</v>
+        <v>11.65015127704323</v>
       </c>
       <c r="E18" t="n">
         <v>-14.55237052788174</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3107349198410714</v>
+        <v>-0.3107425078101023</v>
       </c>
       <c r="G18" t="n">
         <v>-19.79919371493109</v>
       </c>
       <c r="H18" t="n">
-        <v>1.648564929586116</v>
+        <v>1.648571051713899</v>
       </c>
       <c r="I18" t="n">
         <v>10.5693401676328</v>
@@ -41330,7 +41330,7 @@
         <v>44834</v>
       </c>
       <c r="B19" t="n">
-        <v>13.84104117459124</v>
+        <v>13.84102946315724</v>
       </c>
       <c r="C19" t="n">
         <v>32.99376139327897</v>
@@ -41348,7 +41348,7 @@
         <v>42.09624763531581</v>
       </c>
       <c r="H19" t="n">
-        <v>42.03855951339208</v>
+        <v>42.03855095864111</v>
       </c>
       <c r="I19" t="n">
         <v>39.58639118085186</v>
@@ -41380,7 +41380,7 @@
         <v>42.00431940783369</v>
       </c>
       <c r="H20" t="n">
-        <v>21.30325276170784</v>
+        <v>21.30326534957958</v>
       </c>
       <c r="I20" t="n">
         <v>11.30802073584476</v>
